--- a/3_Automation_Dashboard/SomSaiJai_Dashboard_B1_2026.xlsx
+++ b/3_Automation_Dashboard/SomSaiJai_Dashboard_B1_2026.xlsx
@@ -1168,7 +1168,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F185"/>
+  <dimension ref="A1:F186"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1223,10 +1223,10 @@
         <v>Mar26</v>
       </c>
       <c r="C5" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D5" t="str">
-        <v>Fixed Costs</v>
+        <v>Water</v>
       </c>
       <c r="E5" t="str">
         <v>Unknown</v>
@@ -3643,10 +3643,10 @@
         <v>Apr26</v>
       </c>
       <c r="C126" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D126" t="str">
-        <v>Other</v>
+        <v>Water</v>
       </c>
       <c r="E126" t="str">
         <v>น้ำ500</v>
@@ -4077,7 +4077,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>16/04/2026</v>
+        <v>18/04/2026</v>
       </c>
       <c r="B148" t="str">
         <v>Apr26</v>
@@ -4086,13 +4086,13 @@
         <v>COGS</v>
       </c>
       <c r="D148" t="str">
-        <v>Ice</v>
+        <v>Apple/Melon</v>
       </c>
       <c r="E148" t="str">
-        <v>เครื่องสกัดเย็น 2 เครื่องร้านใหม่</v>
+        <v>แอปเปิ้ล 3 ลัง</v>
       </c>
       <c r="F148">
-        <v>11560</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="149">
@@ -4106,13 +4106,13 @@
         <v>COGS</v>
       </c>
       <c r="D149" t="str">
-        <v>Orange</v>
+        <v>Mango</v>
       </c>
       <c r="E149" t="str">
-        <v>ลงทุนน้ำส้ม</v>
+        <v>16/04/26 มะม่วง 1 ลัง</v>
       </c>
       <c r="F149">
-        <v>9341</v>
+        <v>750</v>
       </c>
     </row>
     <row r="150">
@@ -4123,21 +4123,21 @@
         <v>Apr26</v>
       </c>
       <c r="C150" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D150" t="str">
-        <v>Ice</v>
+        <v>Other</v>
       </c>
       <c r="E150" t="str">
-        <v>ค่าปริ้นgrcode</v>
+        <v>16/4/2569</v>
       </c>
       <c r="F150">
-        <v>60</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>18/04/2026</v>
+        <v>20/04/2026</v>
       </c>
       <c r="B151" t="str">
         <v>Apr26</v>
@@ -4146,18 +4146,18 @@
         <v>COGS</v>
       </c>
       <c r="D151" t="str">
-        <v>Apple/Melon</v>
+        <v>Orange</v>
       </c>
       <c r="E151" t="str">
-        <v>แอปเปิ้ล 3 ลัง</v>
+        <v>ส้ม 40 ตะกร้า ตะกร้าละ 22 โล โลละ 30 บาท</v>
       </c>
       <c r="F151">
-        <v>1050</v>
+        <v>28600</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>18/04/2026</v>
+        <v>20/04/2026</v>
       </c>
       <c r="B152" t="str">
         <v>Apr26</v>
@@ -4166,33 +4166,33 @@
         <v>COGS</v>
       </c>
       <c r="D152" t="str">
-        <v>Mango</v>
+        <v>Transportation</v>
       </c>
       <c r="E152" t="str">
-        <v>16/04/26 มะม่วง 1 ลัง</v>
+        <v>ค่าส่งป้ายเมนูร้านใหม่</v>
       </c>
       <c r="F152">
-        <v>750</v>
+        <v>335</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>18/04/2026</v>
+        <v>20/04/2026</v>
       </c>
       <c r="B153" t="str">
         <v>Apr26</v>
       </c>
       <c r="C153" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D153" t="str">
-        <v>Other</v>
+        <v>Packaging</v>
       </c>
       <c r="E153" t="str">
-        <v>16/4/2569</v>
+        <v>ขวดใหญ่ 98 อัน</v>
       </c>
       <c r="F153">
-        <v>4000</v>
+        <v>338</v>
       </c>
     </row>
     <row r="154">
@@ -4206,13 +4206,13 @@
         <v>COGS</v>
       </c>
       <c r="D154" t="str">
-        <v>Orange</v>
+        <v>Packaging</v>
       </c>
       <c r="E154" t="str">
-        <v>ส้ม 40 ตะกร้า ตะกร้าละ 22 โล โลละ 30 บาท</v>
+        <v>ถุงขยะ 10 แพค</v>
       </c>
       <c r="F154">
-        <v>28600</v>
+        <v>520</v>
       </c>
     </row>
     <row r="155">
@@ -4226,13 +4226,13 @@
         <v>COGS</v>
       </c>
       <c r="D155" t="str">
-        <v>Transportation</v>
+        <v>Watermelon</v>
       </c>
       <c r="E155" t="str">
-        <v>ค่าส่งป้ายเมนูร้านใหม่</v>
+        <v>18/4/26 แตงโม 30 ลูก</v>
       </c>
       <c r="F155">
-        <v>335</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="156">
@@ -4246,18 +4246,18 @@
         <v>COGS</v>
       </c>
       <c r="D156" t="str">
-        <v>Packaging</v>
+        <v>Mango</v>
       </c>
       <c r="E156" t="str">
-        <v>ขวดใหญ่ 98 อัน</v>
+        <v>18/4/26 มะม่วง 25 โล 750</v>
       </c>
       <c r="F156">
-        <v>338</v>
+        <v>750</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>20/04/2026</v>
+        <v>21/04/2026</v>
       </c>
       <c r="B157" t="str">
         <v>Apr26</v>
@@ -4266,18 +4266,18 @@
         <v>COGS</v>
       </c>
       <c r="D157" t="str">
-        <v>Packaging</v>
+        <v>Watermelon</v>
       </c>
       <c r="E157" t="str">
-        <v>ถุงขยะ 10 แพค</v>
+        <v>21/4/26 แตงโม60 ลูก</v>
       </c>
       <c r="F157">
-        <v>520</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>20/04/2026</v>
+        <v>21/04/2026</v>
       </c>
       <c r="B158" t="str">
         <v>Apr26</v>
@@ -4286,18 +4286,18 @@
         <v>COGS</v>
       </c>
       <c r="D158" t="str">
-        <v>Watermelon</v>
+        <v>Transportation</v>
       </c>
       <c r="E158" t="str">
-        <v>18/4/26 แตงโม 30 ลูก</v>
+        <v>Lalamove</v>
       </c>
       <c r="F158">
-        <v>2400</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>20/04/2026</v>
+        <v>21/04/2026</v>
       </c>
       <c r="B159" t="str">
         <v>Apr26</v>
@@ -4306,18 +4306,18 @@
         <v>COGS</v>
       </c>
       <c r="D159" t="str">
-        <v>Mango</v>
+        <v>Apple/Melon</v>
       </c>
       <c r="E159" t="str">
-        <v>18/4/26 มะม่วง 25 โล 750</v>
+        <v>แอปเปิ้ล 4 ลัง</v>
       </c>
       <c r="F159">
-        <v>750</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>20/04/2026</v>
+        <v>23/04/2026</v>
       </c>
       <c r="B160" t="str">
         <v>Apr26</v>
@@ -4326,18 +4326,18 @@
         <v>COGS</v>
       </c>
       <c r="D160" t="str">
-        <v>Packaging</v>
+        <v>Mango</v>
       </c>
       <c r="E160" t="str">
-        <v>ฝาปิดกล่องใส่ผลไม้ 2 อัน</v>
+        <v>มะม่วง 2 ลัง</v>
       </c>
       <c r="F160">
-        <v>692</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>21/04/2026</v>
+        <v>23/04/2026</v>
       </c>
       <c r="B161" t="str">
         <v>Apr26</v>
@@ -4346,18 +4346,18 @@
         <v>COGS</v>
       </c>
       <c r="D161" t="str">
-        <v>Watermelon</v>
+        <v>Apple/Melon</v>
       </c>
       <c r="E161" t="str">
-        <v>21/4/26 แตงโม60 ลูก</v>
+        <v>แอปเปิ้ล 4 ลัง</v>
       </c>
       <c r="F161">
-        <v>4800</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>21/04/2026</v>
+        <v>23/04/2026</v>
       </c>
       <c r="B162" t="str">
         <v>Apr26</v>
@@ -4366,18 +4366,18 @@
         <v>COGS</v>
       </c>
       <c r="D162" t="str">
-        <v>Transportation</v>
+        <v>Ice</v>
       </c>
       <c r="E162" t="str">
-        <v>Lalamove</v>
+        <v>16/4/26 เนื้อ 10 น้ำ 10 21/4/26 เนื้อ 10</v>
       </c>
       <c r="F162">
-        <v>2000</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>21/04/2026</v>
+        <v>23/04/2026</v>
       </c>
       <c r="B163" t="str">
         <v>Apr26</v>
@@ -4386,18 +4386,18 @@
         <v>COGS</v>
       </c>
       <c r="D163" t="str">
-        <v>Apple/Melon</v>
+        <v>Mango</v>
       </c>
       <c r="E163" t="str">
-        <v>แอปเปิ้ล 4 ลัง</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F163">
-        <v>1400</v>
+        <v>780</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>23/04/2026</v>
+        <v>24/04/2026</v>
       </c>
       <c r="B164" t="str">
         <v>Apr26</v>
@@ -4406,18 +4406,18 @@
         <v>COGS</v>
       </c>
       <c r="D164" t="str">
-        <v>Mango</v>
+        <v>Packaging</v>
       </c>
       <c r="E164" t="str">
-        <v>มะม่วง 2 ลัง</v>
+        <v>บาร์เลย 4 ถั่วแดง 3 ถุงละ 60</v>
       </c>
       <c r="F164">
-        <v>1560</v>
+        <v>420</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>23/04/2026</v>
+        <v>24/04/2026</v>
       </c>
       <c r="B165" t="str">
         <v>Apr26</v>
@@ -4426,18 +4426,18 @@
         <v>COGS</v>
       </c>
       <c r="D165" t="str">
-        <v>Apple/Melon</v>
+        <v>Watermelon</v>
       </c>
       <c r="E165" t="str">
-        <v>แอปเปิ้ล 4 ลัง</v>
+        <v>แตงโม 50 ลูก</v>
       </c>
       <c r="F165">
-        <v>1400</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>23/04/2026</v>
+        <v>25/04/2026</v>
       </c>
       <c r="B166" t="str">
         <v>Apr26</v>
@@ -4446,18 +4446,18 @@
         <v>COGS</v>
       </c>
       <c r="D166" t="str">
-        <v>Ice</v>
+        <v>Orange</v>
       </c>
       <c r="E166" t="str">
-        <v>16/4/26 เนื้อ 10 น้ำ 10 21/4/26 เนื้อ 10</v>
+        <v>22/04/69</v>
       </c>
       <c r="F166">
-        <v>2900</v>
+        <v>14400</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>23/04/2026</v>
+        <v>26/04/2026</v>
       </c>
       <c r="B167" t="str">
         <v>Apr26</v>
@@ -4466,18 +4466,18 @@
         <v>COGS</v>
       </c>
       <c r="D167" t="str">
-        <v>Mango</v>
+        <v>Packaging</v>
       </c>
       <c r="E167" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>แก้ว 1 ลัง</v>
       </c>
       <c r="F167">
-        <v>780</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>24/04/2026</v>
+        <v>26/04/2026</v>
       </c>
       <c r="B168" t="str">
         <v>Apr26</v>
@@ -4489,15 +4489,15 @@
         <v>Packaging</v>
       </c>
       <c r="E168" t="str">
-        <v>บาร์เลย 4 ถั่วแดง 3 ถุงละ 60</v>
+        <v>แก้ว3ลัง</v>
       </c>
       <c r="F168">
-        <v>420</v>
+        <v>7090</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>24/04/2026</v>
+        <v>26/04/2026</v>
       </c>
       <c r="B169" t="str">
         <v>Apr26</v>
@@ -4506,18 +4506,18 @@
         <v>COGS</v>
       </c>
       <c r="D169" t="str">
-        <v>Watermelon</v>
+        <v>Mango</v>
       </c>
       <c r="E169" t="str">
-        <v>แตงโม 50 ลูก</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F169">
-        <v>4000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>25/04/2026</v>
+        <v>26/04/2026</v>
       </c>
       <c r="B170" t="str">
         <v>Apr26</v>
@@ -4526,18 +4526,18 @@
         <v>COGS</v>
       </c>
       <c r="D170" t="str">
-        <v>Orange</v>
+        <v>Apple/Melon</v>
       </c>
       <c r="E170" t="str">
-        <v>22/04/69</v>
+        <v>แอปเปิ้ล 4</v>
       </c>
       <c r="F170">
-        <v>14400</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>25/04/2026</v>
+        <v>27/04/2026</v>
       </c>
       <c r="B171" t="str">
         <v>Apr26</v>
@@ -4549,15 +4549,15 @@
         <v>Ice</v>
       </c>
       <c r="E171" t="str">
-        <v>พัดลม 2 ตัว</v>
+        <v>26/4/26 50 ลูก</v>
       </c>
       <c r="F171">
-        <v>1838</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>26/04/2026</v>
+        <v>28/04/2026</v>
       </c>
       <c r="B172" t="str">
         <v>Apr26</v>
@@ -4569,15 +4569,15 @@
         <v>Packaging</v>
       </c>
       <c r="E172" t="str">
-        <v>แก้ว 1 ลัง</v>
+        <v>หลอด 704(20ห่อ)</v>
       </c>
       <c r="F172">
-        <v>1539</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>26/04/2026</v>
+        <v>28/04/2026</v>
       </c>
       <c r="B173" t="str">
         <v>Apr26</v>
@@ -4586,18 +4586,18 @@
         <v>COGS</v>
       </c>
       <c r="D173" t="str">
-        <v>Packaging</v>
+        <v>Orange</v>
       </c>
       <c r="E173" t="str">
-        <v>แก้ว3ลัง</v>
+        <v>รอบ 27/04/69</v>
       </c>
       <c r="F173">
-        <v>7090</v>
+        <v>21600</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>26/04/2026</v>
+        <v>28/04/2026</v>
       </c>
       <c r="B174" t="str">
         <v>Apr26</v>
@@ -4606,18 +4606,18 @@
         <v>COGS</v>
       </c>
       <c r="D174" t="str">
-        <v>Mango</v>
+        <v>Coconut</v>
       </c>
       <c r="E174" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>ค่าส่งมะพร้าว</v>
       </c>
       <c r="F174">
-        <v>780</v>
+        <v>100</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>26/04/2026</v>
+        <v>28/04/2026</v>
       </c>
       <c r="B175" t="str">
         <v>Apr26</v>
@@ -4629,7 +4629,7 @@
         <v>Apple/Melon</v>
       </c>
       <c r="E175" t="str">
-        <v>แอปเปิ้ล 4</v>
+        <v>แอปเปิ้ล 4 ลัง</v>
       </c>
       <c r="F175">
         <v>1400</v>
@@ -4637,7 +4637,7 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>27/04/2026</v>
+        <v>28/04/2026</v>
       </c>
       <c r="B176" t="str">
         <v>Apr26</v>
@@ -4646,18 +4646,18 @@
         <v>COGS</v>
       </c>
       <c r="D176" t="str">
-        <v>Ice</v>
+        <v>Mango</v>
       </c>
       <c r="E176" t="str">
-        <v>26/4/26 50 ลูก</v>
+        <v>มะม่วง 2 ลัง</v>
       </c>
       <c r="F176">
-        <v>4000</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>28/04/2026</v>
+        <v>29/04/2026</v>
       </c>
       <c r="B177" t="str">
         <v>Apr26</v>
@@ -4666,18 +4666,18 @@
         <v>COGS</v>
       </c>
       <c r="D177" t="str">
-        <v>Packaging</v>
+        <v>Milk/Conden</v>
       </c>
       <c r="E177" t="str">
-        <v>หลอด 704(20ห่อ)</v>
+        <v>นมข้นหวาน1ลัง 836</v>
       </c>
       <c r="F177">
-        <v>2110</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>28/04/2026</v>
+        <v>29/04/2026</v>
       </c>
       <c r="B178" t="str">
         <v>Apr26</v>
@@ -4686,18 +4686,18 @@
         <v>COGS</v>
       </c>
       <c r="D178" t="str">
-        <v>Orange</v>
+        <v>Packaging</v>
       </c>
       <c r="E178" t="str">
-        <v>รอบ 27/04/69</v>
+        <v>นมข้นหวาน2ลัง 1602</v>
       </c>
       <c r="F178">
-        <v>21600</v>
+        <v>3210</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>28/04/2026</v>
+        <v>29/04/2026</v>
       </c>
       <c r="B179" t="str">
         <v>Apr26</v>
@@ -4706,18 +4706,18 @@
         <v>COGS</v>
       </c>
       <c r="D179" t="str">
-        <v>Coconut</v>
+        <v>Watermelon</v>
       </c>
       <c r="E179" t="str">
-        <v>ค่าส่งมะพร้าว</v>
+        <v>แตงโม 60 ลูก</v>
       </c>
       <c r="F179">
-        <v>100</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>28/04/2026</v>
+        <v>29/04/2026</v>
       </c>
       <c r="B180" t="str">
         <v>Apr26</v>
@@ -4726,18 +4726,18 @@
         <v>COGS</v>
       </c>
       <c r="D180" t="str">
-        <v>Apple/Melon</v>
+        <v>Transportation</v>
       </c>
       <c r="E180" t="str">
-        <v>แอปเปิ้ล 4 ลัง</v>
+        <v>เนื้อ 10 x 50 500</v>
       </c>
       <c r="F180">
-        <v>1400</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>28/04/2026</v>
+        <v>30/04/2026</v>
       </c>
       <c r="B181" t="str">
         <v>Apr26</v>
@@ -4746,18 +4746,18 @@
         <v>COGS</v>
       </c>
       <c r="D181" t="str">
-        <v>Mango</v>
+        <v>Ice</v>
       </c>
       <c r="E181" t="str">
-        <v>มะม่วง 2 ลัง</v>
+        <v>สับปะรส 3 ตะกร้า</v>
       </c>
       <c r="F181">
-        <v>1560</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>29/04/2026</v>
+        <v>30/04/2026</v>
       </c>
       <c r="B182" t="str">
         <v>Apr26</v>
@@ -4766,78 +4766,98 @@
         <v>OPEX</v>
       </c>
       <c r="D182" t="str">
-        <v>Other</v>
+        <v>Salary</v>
       </c>
       <c r="E182" t="str">
-        <v>นมข้นหวาน1ลัง 836</v>
+        <v>Employee 1</v>
       </c>
       <c r="F182">
-        <v>2160</v>
+        <v>19000</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>29/04/2026</v>
+        <v>30/04/2026</v>
       </c>
       <c r="B183" t="str">
         <v>Apr26</v>
       </c>
       <c r="C183" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D183" t="str">
-        <v>Packaging</v>
+        <v>Salary</v>
       </c>
       <c r="E183" t="str">
-        <v>นมข้นหวาน2ลัง 1602</v>
+        <v>Employee 2</v>
       </c>
       <c r="F183">
-        <v>3210</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>29/04/2026</v>
+        <v>30/04/2026</v>
       </c>
       <c r="B184" t="str">
         <v>Apr26</v>
       </c>
       <c r="C184" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D184" t="str">
-        <v>Watermelon</v>
+        <v>Fixed Costs</v>
       </c>
       <c r="E184" t="str">
-        <v>แตงโม 60 ลูก</v>
+        <v>Rent</v>
       </c>
       <c r="F184">
-        <v>4200</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>29/04/2026</v>
+        <v>30/04/2026</v>
       </c>
       <c r="B185" t="str">
         <v>Apr26</v>
       </c>
       <c r="C185" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D185" t="str">
-        <v>Transportation</v>
+        <v>Investment</v>
       </c>
       <c r="E185" t="str">
-        <v>เนื้อ 10 x 50 500</v>
+        <v>Stock (Allocated 82.9%)</v>
       </c>
       <c r="F185">
-        <v>2395</v>
+        <v>9948</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>30/04/2026</v>
+      </c>
+      <c r="B186" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C186" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D186" t="str">
+        <v>Other</v>
+      </c>
+      <c r="E186" t="str">
+        <v>Pineapple</v>
+      </c>
+      <c r="F186">
+        <v>1500</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F185"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F186"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -11091,7 +11111,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z34"/>
+  <dimension ref="A1:Z35"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -11192,22 +11212,22 @@
         <v>6300</v>
       </c>
       <c r="E3">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>6180</v>
+        <v>6300</v>
       </c>
       <c r="G3">
-        <v>4180</v>
+        <v>4280</v>
       </c>
       <c r="H3">
         <v>92</v>
       </c>
       <c r="I3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="K3">
         <v>6</v>
@@ -11225,7 +11245,7 @@
         <v>0</v>
       </c>
       <c r="P3">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -11352,10 +11372,10 @@
         <v>9930</v>
       </c>
       <c r="E5">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>9750</v>
+        <v>9930</v>
       </c>
       <c r="G5">
         <v>4690</v>
@@ -11364,7 +11384,7 @@
         <v>81</v>
       </c>
       <c r="I5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J5">
         <v>48</v>
@@ -11379,7 +11399,7 @@
         <v>15</v>
       </c>
       <c r="N5">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O5">
         <v>0</v>
@@ -11394,7 +11414,7 @@
         <v>0</v>
       </c>
       <c r="S5">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="T5">
         <v>11</v>
@@ -11403,16 +11423,16 @@
         <v>0</v>
       </c>
       <c r="V5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -11512,10 +11532,10 @@
         <v>9540</v>
       </c>
       <c r="E7">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>9300</v>
+        <v>9540</v>
       </c>
       <c r="G7">
         <v>7560</v>
@@ -11524,7 +11544,7 @@
         <v>100</v>
       </c>
       <c r="I7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J7">
         <v>68</v>
@@ -11533,13 +11553,13 @@
         <v>17</v>
       </c>
       <c r="L7">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="M7">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="N7">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O7">
         <v>0</v>
@@ -11563,16 +11583,16 @@
         <v>34</v>
       </c>
       <c r="V7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z7">
         <v>28</v>
@@ -11592,10 +11612,10 @@
         <v>8510</v>
       </c>
       <c r="E8">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>8270</v>
+        <v>8510</v>
       </c>
       <c r="G8">
         <v>4100</v>
@@ -11604,7 +11624,7 @@
         <v>64</v>
       </c>
       <c r="I8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J8">
         <v>70</v>
@@ -11619,7 +11639,7 @@
         <v>8</v>
       </c>
       <c r="N8">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O8">
         <v>0</v>
@@ -11643,16 +11663,16 @@
         <v>32</v>
       </c>
       <c r="V8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z8">
         <v>16</v>
@@ -11672,10 +11692,10 @@
         <v>6420</v>
       </c>
       <c r="E9">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="F9">
-        <v>6240</v>
+        <v>6420</v>
       </c>
       <c r="G9">
         <v>3180</v>
@@ -11684,7 +11704,7 @@
         <v>56</v>
       </c>
       <c r="I9">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J9">
         <v>32</v>
@@ -11699,7 +11719,7 @@
         <v>9</v>
       </c>
       <c r="N9">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O9">
         <v>0</v>
@@ -11720,22 +11740,22 @@
         <v>11</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="V9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10">
@@ -11752,10 +11772,10 @@
         <v>6180</v>
       </c>
       <c r="E10">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="F10">
-        <v>6000</v>
+        <v>6180</v>
       </c>
       <c r="G10">
         <v>2880</v>
@@ -11764,7 +11784,7 @@
         <v>49</v>
       </c>
       <c r="I10">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J10">
         <v>55</v>
@@ -11779,7 +11799,7 @@
         <v>6</v>
       </c>
       <c r="N10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O10">
         <v>0</v>
@@ -11800,22 +11820,22 @@
         <v>17</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="V10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
@@ -11832,10 +11852,10 @@
         <v>5090</v>
       </c>
       <c r="E11">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="F11">
-        <v>4970</v>
+        <v>5090</v>
       </c>
       <c r="G11">
         <v>3130</v>
@@ -11844,7 +11864,7 @@
         <v>64</v>
       </c>
       <c r="I11">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J11">
         <v>37</v>
@@ -11859,7 +11879,7 @@
         <v>7</v>
       </c>
       <c r="N11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O11">
         <v>0</v>
@@ -11880,7 +11900,7 @@
         <v>9</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V11">
         <v>0</v>
@@ -11895,7 +11915,7 @@
         <v>0</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12">
@@ -11912,10 +11932,10 @@
         <v>9150</v>
       </c>
       <c r="E12">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="F12">
-        <v>8910</v>
+        <v>9150</v>
       </c>
       <c r="G12">
         <v>4890</v>
@@ -11924,7 +11944,7 @@
         <v>58</v>
       </c>
       <c r="I12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J12">
         <v>63</v>
@@ -11939,7 +11959,7 @@
         <v>22</v>
       </c>
       <c r="N12">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O12">
         <v>0</v>
@@ -11963,16 +11983,16 @@
         <v>0</v>
       </c>
       <c r="V12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -11992,10 +12012,10 @@
         <v>10880</v>
       </c>
       <c r="E13">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="F13">
-        <v>10700</v>
+        <v>10880</v>
       </c>
       <c r="G13">
         <v>5620</v>
@@ -12004,7 +12024,7 @@
         <v>60</v>
       </c>
       <c r="I13">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J13">
         <v>85</v>
@@ -12040,22 +12060,22 @@
         <v>21</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="V13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -12072,10 +12092,10 @@
         <v>9460</v>
       </c>
       <c r="E14">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="F14">
-        <v>9280</v>
+        <v>9460</v>
       </c>
       <c r="G14">
         <v>4680</v>
@@ -12084,7 +12104,7 @@
         <v>82</v>
       </c>
       <c r="I14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J14">
         <v>79</v>
@@ -12123,16 +12143,16 @@
         <v>18</v>
       </c>
       <c r="V14">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W14">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z14">
         <v>26</v>
@@ -12152,10 +12172,10 @@
         <v>7180</v>
       </c>
       <c r="E15">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="F15">
-        <v>7000</v>
+        <v>7180</v>
       </c>
       <c r="G15">
         <v>3630</v>
@@ -12164,7 +12184,7 @@
         <v>65</v>
       </c>
       <c r="I15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J15">
         <v>67</v>
@@ -12203,16 +12223,16 @@
         <v>0</v>
       </c>
       <c r="V15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -12232,10 +12252,10 @@
         <v>10980</v>
       </c>
       <c r="E16">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="F16">
-        <v>10800</v>
+        <v>10980</v>
       </c>
       <c r="G16">
         <v>4200</v>
@@ -12244,7 +12264,7 @@
         <v>100</v>
       </c>
       <c r="I16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J16">
         <v>62</v>
@@ -12283,16 +12303,16 @@
         <v>12</v>
       </c>
       <c r="V16">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W16">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -12472,10 +12492,10 @@
         <v>6560</v>
       </c>
       <c r="E19">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="F19">
-        <v>6380</v>
+        <v>6560</v>
       </c>
       <c r="G19">
         <v>3990</v>
@@ -12484,7 +12504,7 @@
         <v>78</v>
       </c>
       <c r="I19">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J19">
         <v>40</v>
@@ -12523,16 +12543,16 @@
         <v>14</v>
       </c>
       <c r="V19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -12552,10 +12572,10 @@
         <v>5920</v>
       </c>
       <c r="E20">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="F20">
-        <v>5800</v>
+        <v>5920</v>
       </c>
       <c r="G20">
         <v>5120</v>
@@ -12603,16 +12623,16 @@
         <v>10</v>
       </c>
       <c r="V20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z20">
         <v>22</v>
@@ -12632,10 +12652,10 @@
         <v>3870</v>
       </c>
       <c r="E21">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="F21">
-        <v>3750</v>
+        <v>3870</v>
       </c>
       <c r="G21">
         <v>2630</v>
@@ -12683,16 +12703,16 @@
         <v>0</v>
       </c>
       <c r="V21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z21">
         <v>8</v>
@@ -12712,10 +12732,10 @@
         <v>4670</v>
       </c>
       <c r="E22">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F22">
-        <v>4520</v>
+        <v>4670</v>
       </c>
       <c r="G22">
         <v>5220</v>
@@ -12763,16 +12783,16 @@
         <v>18</v>
       </c>
       <c r="V22">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W22">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="X22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z22">
         <v>16</v>
@@ -12792,10 +12812,10 @@
         <v>5470</v>
       </c>
       <c r="E23">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="F23">
-        <v>5350</v>
+        <v>5470</v>
       </c>
       <c r="G23">
         <v>3200</v>
@@ -12843,16 +12863,16 @@
         <v>10</v>
       </c>
       <c r="V23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z23">
         <v>34</v>
@@ -13352,10 +13372,10 @@
         <v>4980</v>
       </c>
       <c r="E30">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="F30">
-        <v>4860</v>
+        <v>4980</v>
       </c>
       <c r="G30">
         <v>3040</v>
@@ -13384,14 +13404,23 @@
       <c r="O30">
         <v>0</v>
       </c>
+      <c r="P30">
+        <v>130</v>
+      </c>
       <c r="Q30">
         <v>0</v>
       </c>
       <c r="R30">
         <v>0</v>
       </c>
+      <c r="S30">
+        <v>1</v>
+      </c>
+      <c r="T30">
+        <v>18</v>
+      </c>
       <c r="U30">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V30">
         <v>0</v>
@@ -13406,7 +13435,7 @@
         <v>0</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31">
@@ -13480,238 +13509,1357 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="str">
-        <v>TOTAL</v>
-      </c>
-      <c r="B33" t="str">
-        <v>29 days</v>
-      </c>
-      <c r="C33">
-        <v>303628</v>
-      </c>
-      <c r="D33">
-        <v>186770</v>
-      </c>
-      <c r="E33">
-        <v>4680</v>
-      </c>
-      <c r="F33">
-        <v>182090</v>
-      </c>
-      <c r="G33">
-        <v>116858</v>
-      </c>
-      <c r="H33">
-        <v>1845</v>
-      </c>
-      <c r="I33">
-        <v>67</v>
-      </c>
-      <c r="J33">
-        <v>1400</v>
-      </c>
-      <c r="K33">
-        <v>221</v>
-      </c>
-      <c r="L33">
-        <v>1325</v>
-      </c>
-      <c r="M33">
-        <v>258</v>
-      </c>
-      <c r="N33">
-        <v>57</v>
-      </c>
-      <c r="O33">
-        <v>0</v>
-      </c>
-      <c r="P33">
-        <v>4798</v>
-      </c>
-      <c r="Q33">
-        <v>0</v>
-      </c>
-      <c r="R33">
-        <v>0</v>
-      </c>
-      <c r="S33">
-        <v>72</v>
-      </c>
-      <c r="T33">
-        <v>349</v>
-      </c>
-      <c r="U33">
-        <v>282</v>
-      </c>
-      <c r="V33">
-        <v>52</v>
-      </c>
-      <c r="W33">
-        <v>54</v>
-      </c>
-      <c r="X33">
-        <v>32.5</v>
-      </c>
-      <c r="Y33">
-        <v>45</v>
-      </c>
-      <c r="Z33">
-        <v>316</v>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>30/04/2026</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Thu</v>
+      </c>
+      <c r="C32">
+        <v>10230</v>
+      </c>
+      <c r="D32">
+        <v>6250</v>
+      </c>
+      <c r="E32">
+        <v>210</v>
+      </c>
+      <c r="F32">
+        <v>6040</v>
+      </c>
+      <c r="G32">
+        <v>3980</v>
+      </c>
+      <c r="H32">
+        <v>48</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>60</v>
+      </c>
+      <c r="K32">
+        <v>5</v>
+      </c>
+      <c r="L32">
+        <v>51</v>
+      </c>
+      <c r="M32">
+        <v>14</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>178</v>
+      </c>
+      <c r="Q32">
+        <v>0</v>
+      </c>
+      <c r="R32">
+        <v>0</v>
+      </c>
+      <c r="U32">
+        <v>0</v>
+      </c>
+      <c r="V32">
+        <v>0</v>
+      </c>
+      <c r="W32">
+        <v>0</v>
+      </c>
+      <c r="X32">
+        <v>0</v>
+      </c>
+      <c r="Y32">
+        <v>0</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
+        <v>TOTAL</v>
+      </c>
+      <c r="B34" t="str">
+        <v>30 days</v>
+      </c>
+      <c r="C34">
+        <v>313858</v>
+      </c>
+      <c r="D34">
+        <v>193020</v>
+      </c>
+      <c r="E34">
+        <v>1860</v>
+      </c>
+      <c r="F34">
+        <v>191160</v>
+      </c>
+      <c r="G34">
+        <v>120938</v>
+      </c>
+      <c r="H34">
+        <v>1893</v>
+      </c>
+      <c r="I34">
+        <v>15</v>
+      </c>
+      <c r="J34">
+        <v>1454</v>
+      </c>
+      <c r="K34">
+        <v>226</v>
+      </c>
+      <c r="L34">
+        <v>1366</v>
+      </c>
+      <c r="M34">
+        <v>282</v>
+      </c>
+      <c r="N34">
+        <v>9</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>5100</v>
+      </c>
+      <c r="Q34">
+        <v>0</v>
+      </c>
+      <c r="R34">
+        <v>0</v>
+      </c>
+      <c r="S34">
+        <v>68</v>
+      </c>
+      <c r="T34">
+        <v>367</v>
+      </c>
+      <c r="U34">
+        <v>372</v>
+      </c>
+      <c r="V34">
+        <v>19</v>
+      </c>
+      <c r="W34">
+        <v>19</v>
+      </c>
+      <c r="X34">
+        <v>11.5</v>
+      </c>
+      <c r="Y34">
+        <v>19</v>
+      </c>
+      <c r="Z34">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
         <v>AVG/DAY</v>
       </c>
-      <c r="C34">
-        <v>10469.931034482759</v>
-      </c>
-      <c r="D34">
-        <v>6440.3448275862065</v>
-      </c>
-      <c r="E34">
-        <v>161.3793103448276</v>
-      </c>
-      <c r="F34">
-        <v>6278.9655172413795</v>
-      </c>
-      <c r="G34">
-        <v>4029.5862068965516</v>
-      </c>
-      <c r="H34">
-        <v>63.62068965517241</v>
-      </c>
-      <c r="I34">
-        <v>2.310344827586207</v>
-      </c>
-      <c r="J34">
-        <v>48.275862068965516</v>
-      </c>
-      <c r="K34">
-        <v>7.620689655172414</v>
-      </c>
-      <c r="L34">
-        <v>45.689655172413794</v>
-      </c>
-      <c r="M34">
-        <v>8.89655172413793</v>
-      </c>
-      <c r="N34">
-        <v>1.9655172413793103</v>
-      </c>
-      <c r="O34">
-        <v>0</v>
-      </c>
-      <c r="P34">
-        <v>165.44827586206895</v>
-      </c>
-      <c r="Q34">
-        <v>0</v>
-      </c>
-      <c r="R34">
-        <v>0</v>
-      </c>
-      <c r="S34">
-        <v>2.4827586206896552</v>
-      </c>
-      <c r="T34">
-        <v>12.03448275862069</v>
-      </c>
-      <c r="U34">
-        <v>9.724137931034482</v>
-      </c>
-      <c r="V34">
-        <v>1.793103448275862</v>
-      </c>
-      <c r="W34">
-        <v>1.8620689655172413</v>
-      </c>
-      <c r="X34">
-        <v>1.1206896551724137</v>
-      </c>
-      <c r="Y34">
-        <v>1.5517241379310345</v>
-      </c>
-      <c r="Z34">
-        <v>10.89655172413793</v>
+      <c r="C35">
+        <v>10461.933333333332</v>
+      </c>
+      <c r="D35">
+        <v>6434</v>
+      </c>
+      <c r="E35">
+        <v>62</v>
+      </c>
+      <c r="F35">
+        <v>6372</v>
+      </c>
+      <c r="G35">
+        <v>4031.266666666667</v>
+      </c>
+      <c r="H35">
+        <v>63.1</v>
+      </c>
+      <c r="I35">
+        <v>0.5</v>
+      </c>
+      <c r="J35">
+        <v>48.46666666666667</v>
+      </c>
+      <c r="K35">
+        <v>7.533333333333333</v>
+      </c>
+      <c r="L35">
+        <v>45.53333333333333</v>
+      </c>
+      <c r="M35">
+        <v>9.4</v>
+      </c>
+      <c r="N35">
+        <v>0.3</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>170</v>
+      </c>
+      <c r="Q35">
+        <v>0</v>
+      </c>
+      <c r="R35">
+        <v>0</v>
+      </c>
+      <c r="S35">
+        <v>2.2666666666666666</v>
+      </c>
+      <c r="T35">
+        <v>12.233333333333333</v>
+      </c>
+      <c r="U35">
+        <v>12.4</v>
+      </c>
+      <c r="V35">
+        <v>0.6333333333333333</v>
+      </c>
+      <c r="W35">
+        <v>0.6333333333333333</v>
+      </c>
+      <c r="X35">
+        <v>0.38333333333333336</v>
+      </c>
+      <c r="Y35">
+        <v>0.6333333333333333</v>
+      </c>
+      <c r="Z35">
+        <v>13.666666666666666</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Z34"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Z35"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:AD14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>Som Sai Jai Cold Press Bar - May 2026</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Date</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Day</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Revenue (฿)</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Cash (฿)</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Expenses (฿)</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Cash-Exp (฿)</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Scan/Transfer (฿)</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Orange</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Orange (100)</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Watermelon</v>
+      </c>
+      <c r="K2" t="str">
+        <v>Mango</v>
+      </c>
+      <c r="L2" t="str">
+        <v>Coconut</v>
+      </c>
+      <c r="M2" t="str">
+        <v>Apple</v>
+      </c>
+      <c r="N2" t="str">
+        <v>Young Coco</v>
+      </c>
+      <c r="O2" t="str">
+        <v>Guava</v>
+      </c>
+      <c r="P2" t="str">
+        <v>Pineapple</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>Total Cups</v>
+      </c>
+      <c r="R2" t="str">
+        <v>Bot Big</v>
+      </c>
+      <c r="S2" t="str">
+        <v>Bot Small</v>
+      </c>
+      <c r="T2" t="str">
+        <v>Used Orange (basket)</v>
+      </c>
+      <c r="U2" t="str">
+        <v>Used Watermelon (pcs)</v>
+      </c>
+      <c r="V2" t="str">
+        <v>Used Mango</v>
+      </c>
+      <c r="W2" t="str">
+        <v>Used Coco (Meat)</v>
+      </c>
+      <c r="X2" t="str">
+        <v>Used Coco (Water)</v>
+      </c>
+      <c r="Y2" t="str">
+        <v>Used Coco (Conden)</v>
+      </c>
+      <c r="Z2" t="str">
+        <v>Used Coco (Raw)</v>
+      </c>
+      <c r="AA2" t="str">
+        <v>Used Apple</v>
+      </c>
+      <c r="AB2" t="str">
+        <v>Used Guava</v>
+      </c>
+      <c r="AC2" t="str">
+        <v>Used Pineapple</v>
+      </c>
+      <c r="AD2" t="str">
+        <v>Used Young Coco</v>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Date</v>
+        <v>01/05/2026</v>
       </c>
       <c r="B3" t="str">
-        <v>Day</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Revenue (฿)</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Cash (฿)</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Expenses (฿)</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Cash-Exp (฿)</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Scan/Transfer (฿)</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Orange</v>
-      </c>
-      <c r="I3" t="str">
-        <v>Watermelon</v>
-      </c>
-      <c r="J3" t="str">
-        <v>Mango</v>
-      </c>
-      <c r="K3" t="str">
-        <v>Coconut</v>
-      </c>
-      <c r="L3" t="str">
-        <v>Apple</v>
-      </c>
-      <c r="M3" t="str">
-        <v>Young Coco</v>
-      </c>
-      <c r="N3" t="str">
-        <v>Total Cups</v>
-      </c>
-      <c r="O3" t="str">
-        <v>Bot Big</v>
-      </c>
-      <c r="P3" t="str">
-        <v>Bot Small</v>
-      </c>
-      <c r="Q3" t="str">
-        <v>Used Orange (basket)</v>
-      </c>
-      <c r="R3" t="str">
-        <v>Used Watermelon (pcs)</v>
+        <v>Fri</v>
+      </c>
+      <c r="C3">
+        <v>13950</v>
+      </c>
+      <c r="D3">
+        <v>8220</v>
+      </c>
+      <c r="E3">
+        <v>180</v>
+      </c>
+      <c r="F3">
+        <v>8040</v>
+      </c>
+      <c r="G3">
+        <v>5730</v>
+      </c>
+      <c r="H3">
+        <v>81</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>57</v>
+      </c>
+      <c r="K3">
+        <v>8</v>
+      </c>
+      <c r="L3">
+        <v>72</v>
+      </c>
+      <c r="M3">
+        <v>15</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>233</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>3.5</v>
+      </c>
+      <c r="U3">
+        <v>15</v>
+      </c>
+      <c r="V3">
+        <v>16</v>
+      </c>
+      <c r="W3">
+        <v>4</v>
+      </c>
+      <c r="X3">
+        <v>4</v>
+      </c>
+      <c r="Y3">
+        <v>2</v>
+      </c>
+      <c r="Z3">
+        <v>4</v>
+      </c>
+      <c r="AA3">
+        <v>30</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>02/05/2026</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Sat</v>
+      </c>
+      <c r="C4">
+        <v>17070</v>
+      </c>
+      <c r="D4">
+        <v>9780</v>
+      </c>
+      <c r="E4">
+        <v>240</v>
+      </c>
+      <c r="F4">
+        <v>9540</v>
+      </c>
+      <c r="G4">
+        <v>7290</v>
+      </c>
+      <c r="H4">
+        <v>84</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>126</v>
+      </c>
+      <c r="K4">
+        <v>7</v>
+      </c>
+      <c r="L4">
+        <v>70</v>
+      </c>
+      <c r="M4">
+        <v>15</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>302</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>3.5</v>
+      </c>
+      <c r="U4">
+        <v>33</v>
+      </c>
+      <c r="V4">
+        <v>14</v>
+      </c>
+      <c r="W4">
+        <v>4</v>
+      </c>
+      <c r="X4">
+        <v>4</v>
+      </c>
+      <c r="Y4">
+        <v>2</v>
+      </c>
+      <c r="Z4">
+        <v>5</v>
+      </c>
+      <c r="AA4">
+        <v>30</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>03/05/2026</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Sun</v>
+      </c>
+      <c r="C5">
+        <v>12530</v>
+      </c>
+      <c r="D5">
+        <v>7520</v>
+      </c>
+      <c r="E5">
+        <v>180</v>
+      </c>
+      <c r="F5">
+        <v>7340</v>
+      </c>
+      <c r="G5">
+        <v>5010</v>
+      </c>
+      <c r="H5">
+        <v>63</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>70</v>
+      </c>
+      <c r="K5">
+        <v>5</v>
+      </c>
+      <c r="L5">
+        <v>67</v>
+      </c>
+      <c r="M5">
+        <v>13</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>218</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>2</v>
+      </c>
+      <c r="U5">
+        <v>18</v>
+      </c>
+      <c r="V5">
+        <v>10</v>
+      </c>
+      <c r="W5">
+        <v>4</v>
+      </c>
+      <c r="X5">
+        <v>4</v>
+      </c>
+      <c r="Y5">
+        <v>2</v>
+      </c>
+      <c r="Z5">
+        <v>4</v>
+      </c>
+      <c r="AA5">
+        <v>26</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>04/05/2026</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Mon</v>
+      </c>
+      <c r="C6">
+        <v>10030</v>
+      </c>
+      <c r="D6">
+        <v>6400</v>
+      </c>
+      <c r="E6">
+        <v>180</v>
+      </c>
+      <c r="F6">
+        <v>6220</v>
+      </c>
+      <c r="G6">
+        <v>3630</v>
+      </c>
+      <c r="H6">
+        <v>43</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>68</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="L6">
+        <v>40</v>
+      </c>
+      <c r="M6">
+        <v>20</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>176</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>2</v>
+      </c>
+      <c r="U6">
+        <v>17</v>
+      </c>
+      <c r="V6">
+        <v>10</v>
+      </c>
+      <c r="W6">
+        <v>2</v>
+      </c>
+      <c r="X6">
+        <v>2</v>
+      </c>
+      <c r="Y6">
+        <v>1</v>
+      </c>
+      <c r="Z6">
+        <v>2</v>
+      </c>
+      <c r="AA6">
+        <v>40</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>05/05/2026</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Tue</v>
+      </c>
+      <c r="C7">
+        <v>7920</v>
+      </c>
+      <c r="D7">
+        <v>4400</v>
+      </c>
+      <c r="E7">
+        <v>120</v>
+      </c>
+      <c r="F7">
+        <v>4280</v>
+      </c>
+      <c r="G7">
+        <v>3520</v>
+      </c>
+      <c r="H7">
+        <v>28</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>60</v>
+      </c>
+      <c r="K7">
+        <v>4</v>
+      </c>
+      <c r="L7">
+        <v>39</v>
+      </c>
+      <c r="M7">
+        <v>9</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>140</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>1.5</v>
+      </c>
+      <c r="U7">
+        <v>15</v>
+      </c>
+      <c r="V7">
+        <v>8</v>
+      </c>
+      <c r="W7">
+        <v>2</v>
+      </c>
+      <c r="X7">
+        <v>2</v>
+      </c>
+      <c r="Y7">
+        <v>1</v>
+      </c>
+      <c r="Z7">
+        <v>2</v>
+      </c>
+      <c r="AA7">
+        <v>18</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>06/05/2026</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Wed</v>
+      </c>
+      <c r="C8">
+        <v>8830</v>
+      </c>
+      <c r="D8">
+        <v>4770</v>
+      </c>
+      <c r="E8">
+        <v>120</v>
+      </c>
+      <c r="F8">
+        <v>4650</v>
+      </c>
+      <c r="G8">
+        <v>4060</v>
+      </c>
+      <c r="H8">
+        <v>47</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>53</v>
+      </c>
+      <c r="K8">
+        <v>6</v>
+      </c>
+      <c r="L8">
+        <v>38</v>
+      </c>
+      <c r="M8">
+        <v>9</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>153</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>2.5</v>
+      </c>
+      <c r="U8">
+        <v>15</v>
+      </c>
+      <c r="V8">
+        <v>12</v>
+      </c>
+      <c r="W8">
+        <v>2</v>
+      </c>
+      <c r="X8">
+        <v>2</v>
+      </c>
+      <c r="Y8">
+        <v>1</v>
+      </c>
+      <c r="Z8">
+        <v>2</v>
+      </c>
+      <c r="AA8">
+        <v>18</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>07/05/2026</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Thu</v>
+      </c>
+      <c r="C9">
+        <v>5410</v>
+      </c>
+      <c r="D9">
+        <v>3010</v>
+      </c>
+      <c r="E9">
+        <v>120</v>
+      </c>
+      <c r="F9">
+        <v>2890</v>
+      </c>
+      <c r="G9">
+        <v>2400</v>
+      </c>
+      <c r="H9">
+        <v>37</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>26</v>
+      </c>
+      <c r="K9">
+        <v>3</v>
+      </c>
+      <c r="L9">
+        <v>20</v>
+      </c>
+      <c r="M9">
+        <v>7</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>93</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>2</v>
+      </c>
+      <c r="U9">
+        <v>8</v>
+      </c>
+      <c r="V9">
+        <v>6</v>
+      </c>
+      <c r="W9">
+        <v>1</v>
+      </c>
+      <c r="X9">
+        <v>1</v>
+      </c>
+      <c r="Y9">
+        <v>1</v>
+      </c>
+      <c r="Z9">
+        <v>1</v>
+      </c>
+      <c r="AA9">
+        <v>14</v>
+      </c>
+      <c r="AB9">
+        <v>0</v>
+      </c>
+      <c r="AC9">
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>08/05/2026</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Fri</v>
+      </c>
+      <c r="C10">
+        <v>6830</v>
+      </c>
+      <c r="D10">
+        <v>4350</v>
+      </c>
+      <c r="E10">
+        <v>120</v>
+      </c>
+      <c r="F10">
+        <v>4230</v>
+      </c>
+      <c r="G10">
+        <v>2480</v>
+      </c>
+      <c r="H10">
+        <v>52</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>31</v>
+      </c>
+      <c r="K10">
+        <v>6</v>
+      </c>
+      <c r="L10">
+        <v>20</v>
+      </c>
+      <c r="M10">
+        <v>7</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>116</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>2</v>
+      </c>
+      <c r="U10">
+        <v>7</v>
+      </c>
+      <c r="V10">
+        <v>12</v>
+      </c>
+      <c r="W10">
+        <v>1</v>
+      </c>
+      <c r="X10">
+        <v>1</v>
+      </c>
+      <c r="Y10">
+        <v>1</v>
+      </c>
+      <c r="Z10">
+        <v>1</v>
+      </c>
+      <c r="AA10">
+        <v>14</v>
+      </c>
+      <c r="AB10">
+        <v>0</v>
+      </c>
+      <c r="AC10">
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>09/05/2026</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Sat</v>
+      </c>
+      <c r="C11">
+        <v>9680</v>
+      </c>
+      <c r="D11">
+        <v>4350</v>
+      </c>
+      <c r="E11">
+        <v>120</v>
+      </c>
+      <c r="F11">
+        <v>4230</v>
+      </c>
+      <c r="G11">
+        <v>5330</v>
+      </c>
+      <c r="H11">
+        <v>62</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>55</v>
+      </c>
+      <c r="K11">
+        <v>5</v>
+      </c>
+      <c r="L11">
+        <v>38</v>
+      </c>
+      <c r="M11">
+        <v>6</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>166</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>3</v>
+      </c>
+      <c r="U11">
+        <v>13</v>
+      </c>
+      <c r="V11">
+        <v>10</v>
+      </c>
+      <c r="W11">
+        <v>2</v>
+      </c>
+      <c r="X11">
+        <v>2</v>
+      </c>
+      <c r="Y11">
+        <v>1</v>
+      </c>
+      <c r="Z11">
+        <v>2</v>
+      </c>
+      <c r="AA11">
+        <v>12</v>
+      </c>
+      <c r="AB11">
+        <v>0</v>
+      </c>
+      <c r="AC11">
+        <v>0</v>
+      </c>
+      <c r="AD11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>TOTAL</v>
+      </c>
+      <c r="B13" t="str">
+        <v>9 days</v>
+      </c>
+      <c r="C13">
+        <v>92250</v>
+      </c>
+      <c r="D13">
+        <v>52800</v>
+      </c>
+      <c r="E13">
+        <v>1380</v>
+      </c>
+      <c r="F13">
+        <v>51420</v>
+      </c>
+      <c r="G13">
+        <v>39450</v>
+      </c>
+      <c r="H13">
+        <v>497</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>546</v>
+      </c>
+      <c r="K13">
+        <v>49</v>
+      </c>
+      <c r="L13">
+        <v>404</v>
+      </c>
+      <c r="M13">
+        <v>101</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>1597</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>22</v>
+      </c>
+      <c r="U13">
+        <v>141</v>
+      </c>
+      <c r="V13">
+        <v>98</v>
+      </c>
+      <c r="W13">
+        <v>22</v>
+      </c>
+      <c r="X13">
+        <v>22</v>
+      </c>
+      <c r="Y13">
+        <v>12</v>
+      </c>
+      <c r="Z13">
+        <v>23</v>
+      </c>
+      <c r="AA13">
+        <v>202</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>AVG/DAY</v>
+      </c>
+      <c r="C14">
+        <v>10250</v>
+      </c>
+      <c r="D14">
+        <v>5866.666666666667</v>
+      </c>
+      <c r="E14">
+        <v>153.33333333333334</v>
+      </c>
+      <c r="F14">
+        <v>5713.333333333333</v>
+      </c>
+      <c r="G14">
+        <v>4383.333333333333</v>
+      </c>
+      <c r="H14">
+        <v>55.22222222222222</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>60.666666666666664</v>
+      </c>
+      <c r="K14">
+        <v>5.444444444444445</v>
+      </c>
+      <c r="L14">
+        <v>44.888888888888886</v>
+      </c>
+      <c r="M14">
+        <v>11.222222222222221</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>177.44444444444446</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>2.4444444444444446</v>
+      </c>
+      <c r="U14">
+        <v>15.666666666666666</v>
+      </c>
+      <c r="V14">
+        <v>10.88888888888889</v>
+      </c>
+      <c r="W14">
+        <v>2.4444444444444446</v>
+      </c>
+      <c r="X14">
+        <v>2.4444444444444446</v>
+      </c>
+      <c r="Y14">
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="Z14">
+        <v>2.5555555555555554</v>
+      </c>
+      <c r="AA14">
+        <v>22.444444444444443</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AD14"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/3_Automation_Dashboard/SomSaiJai_Dashboard_B1_2026.xlsx
+++ b/3_Automation_Dashboard/SomSaiJai_Dashboard_B1_2026.xlsx
@@ -13749,7 +13749,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AD14"/>
+  <dimension ref="A1:AD16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -13856,19 +13856,19 @@
         <v>Fri</v>
       </c>
       <c r="C3">
-        <v>13950</v>
+        <v>13770</v>
       </c>
       <c r="D3">
-        <v>8220</v>
+        <v>8040</v>
       </c>
       <c r="E3">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="F3">
-        <v>8040</v>
+        <v>7920</v>
       </c>
       <c r="G3">
-        <v>5730</v>
+        <v>5910</v>
       </c>
       <c r="H3">
         <v>81</v>
@@ -13963,13 +13963,13 @@
         <v>7290</v>
       </c>
       <c r="H4">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="K4">
         <v>7</v>
@@ -13990,7 +13990,7 @@
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>302</v>
+        <v>92</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -14020,7 +14020,7 @@
         <v>5</v>
       </c>
       <c r="AA4">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="AB4">
         <v>0</v>
@@ -14055,49 +14055,49 @@
         <v>5010</v>
       </c>
       <c r="H5">
+        <v>65</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>88</v>
+      </c>
+      <c r="K5">
+        <v>15</v>
+      </c>
+      <c r="L5">
+        <v>75</v>
+      </c>
+      <c r="M5">
+        <v>39</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>282</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
         <v>63</v>
       </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
+      <c r="U5">
         <v>70</v>
       </c>
-      <c r="K5">
+      <c r="V5">
         <v>5</v>
-      </c>
-      <c r="L5">
-        <v>67</v>
-      </c>
-      <c r="M5">
-        <v>13</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>0</v>
-      </c>
-      <c r="Q5">
-        <v>218</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>2</v>
-      </c>
-      <c r="U5">
-        <v>18</v>
-      </c>
-      <c r="V5">
-        <v>10</v>
       </c>
       <c r="W5">
         <v>4</v>
@@ -14112,7 +14112,7 @@
         <v>4</v>
       </c>
       <c r="AA5">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="AB5">
         <v>0</v>
@@ -14239,19 +14239,19 @@
         <v>3520</v>
       </c>
       <c r="H7">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
       <c r="J7">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L7">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="M7">
         <v>9</v>
@@ -14266,7 +14266,7 @@
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -14278,10 +14278,10 @@
         <v>1.5</v>
       </c>
       <c r="U7">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="V7">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="W7">
         <v>2</v>
@@ -14515,16 +14515,16 @@
         <v>2480</v>
       </c>
       <c r="H10">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
       <c r="J10">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K10">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L10">
         <v>20</v>
@@ -14542,7 +14542,7 @@
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -14607,22 +14607,22 @@
         <v>5330</v>
       </c>
       <c r="H11">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
       <c r="J11">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="K11">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L11">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="M11">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -14634,7 +14634,7 @@
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -14676,45 +14676,137 @@
         <v>0</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>10/05/2026</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Sun</v>
+      </c>
+      <c r="C12">
+        <v>10690</v>
+      </c>
+      <c r="D12">
+        <v>6590</v>
+      </c>
+      <c r="E12">
+        <v>180</v>
+      </c>
+      <c r="F12">
+        <v>6410</v>
+      </c>
+      <c r="G12">
+        <v>4100</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>45</v>
+      </c>
+      <c r="U12">
+        <v>56</v>
+      </c>
+      <c r="V12">
+        <v>9</v>
+      </c>
+      <c r="W12">
+        <v>3</v>
+      </c>
+      <c r="X12">
+        <v>3</v>
+      </c>
+      <c r="Y12">
+        <v>1.5</v>
+      </c>
+      <c r="Z12">
+        <v>3</v>
+      </c>
+      <c r="AA12">
+        <v>9</v>
+      </c>
+      <c r="AB12">
+        <v>0</v>
+      </c>
+      <c r="AC12">
+        <v>0</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+    </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>TOTAL</v>
+        <v>11/05/2026</v>
       </c>
       <c r="B13" t="str">
-        <v>9 days</v>
+        <v>Mon</v>
       </c>
       <c r="C13">
-        <v>92250</v>
+        <v>6455</v>
       </c>
       <c r="D13">
-        <v>52800</v>
+        <v>3660</v>
       </c>
       <c r="E13">
-        <v>1380</v>
+        <v>120</v>
       </c>
       <c r="F13">
-        <v>51420</v>
+        <v>3540</v>
       </c>
       <c r="G13">
-        <v>39450</v>
+        <v>2795</v>
       </c>
       <c r="H13">
-        <v>497</v>
+        <v>0</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
       <c r="J13">
-        <v>546</v>
+        <v>0</v>
       </c>
       <c r="K13">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="L13">
-        <v>404</v>
+        <v>0</v>
       </c>
       <c r="M13">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -14726,7 +14818,7 @@
         <v>0</v>
       </c>
       <c r="Q13">
-        <v>1597</v>
+        <v>0</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -14735,28 +14827,28 @@
         <v>0</v>
       </c>
       <c r="T13">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="U13">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="V13">
-        <v>98</v>
+        <v>3</v>
       </c>
       <c r="W13">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="X13">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="Y13">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="Z13">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="AA13">
-        <v>202</v>
+        <v>7</v>
       </c>
       <c r="AB13">
         <v>0</v>
@@ -14770,40 +14862,43 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>AVG/DAY</v>
+        <v>12/05/2026</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Tue</v>
       </c>
       <c r="C14">
-        <v>10250</v>
+        <v>4770</v>
       </c>
       <c r="D14">
-        <v>5866.666666666667</v>
+        <v>3110</v>
       </c>
       <c r="E14">
-        <v>153.33333333333334</v>
+        <v>120</v>
       </c>
       <c r="F14">
-        <v>5713.333333333333</v>
+        <v>2990</v>
       </c>
       <c r="G14">
-        <v>4383.333333333333</v>
+        <v>1660</v>
       </c>
       <c r="H14">
-        <v>55.22222222222222</v>
+        <v>0</v>
       </c>
       <c r="I14">
         <v>0</v>
       </c>
       <c r="J14">
-        <v>60.666666666666664</v>
+        <v>0</v>
       </c>
       <c r="K14">
-        <v>5.444444444444445</v>
+        <v>3</v>
       </c>
       <c r="L14">
-        <v>44.888888888888886</v>
+        <v>26</v>
       </c>
       <c r="M14">
-        <v>11.222222222222221</v>
+        <v>9</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -14815,7 +14910,7 @@
         <v>0</v>
       </c>
       <c r="Q14">
-        <v>177.44444444444446</v>
+        <v>38</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -14824,28 +14919,28 @@
         <v>0</v>
       </c>
       <c r="T14">
-        <v>2.4444444444444446</v>
+        <v>6</v>
       </c>
       <c r="U14">
-        <v>15.666666666666666</v>
+        <v>6</v>
       </c>
       <c r="V14">
-        <v>10.88888888888889</v>
+        <v>6</v>
       </c>
       <c r="W14">
-        <v>2.4444444444444446</v>
+        <v>0</v>
       </c>
       <c r="X14">
-        <v>2.4444444444444446</v>
+        <v>2</v>
       </c>
       <c r="Y14">
-        <v>1.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="Z14">
-        <v>2.5555555555555554</v>
+        <v>1</v>
       </c>
       <c r="AA14">
-        <v>22.444444444444443</v>
+        <v>18</v>
       </c>
       <c r="AB14">
         <v>0</v>
@@ -14854,12 +14949,196 @@
         <v>0</v>
       </c>
       <c r="AD14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>13/05/2026</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Wed</v>
+      </c>
+      <c r="C15">
+        <v>9380</v>
+      </c>
+      <c r="D15">
+        <v>5350</v>
+      </c>
+      <c r="E15">
+        <v>150</v>
+      </c>
+      <c r="F15">
+        <v>5200</v>
+      </c>
+      <c r="G15">
+        <v>4030</v>
+      </c>
+      <c r="H15">
+        <v>55</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>43</v>
+      </c>
+      <c r="K15">
+        <v>5</v>
+      </c>
+      <c r="L15">
+        <v>46</v>
+      </c>
+      <c r="M15">
+        <v>12</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>161</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>2</v>
+      </c>
+      <c r="U15">
+        <v>12</v>
+      </c>
+      <c r="V15">
+        <v>10</v>
+      </c>
+      <c r="W15">
+        <v>3</v>
+      </c>
+      <c r="X15">
+        <v>3</v>
+      </c>
+      <c r="Y15">
+        <v>1</v>
+      </c>
+      <c r="Z15">
+        <v>2</v>
+      </c>
+      <c r="AA15">
+        <v>24</v>
+      </c>
+      <c r="AB15">
+        <v>0</v>
+      </c>
+      <c r="AC15">
+        <v>0</v>
+      </c>
+      <c r="AD15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>14/05/2026</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Thu</v>
+      </c>
+      <c r="C16">
+        <v>7890</v>
+      </c>
+      <c r="D16">
+        <v>4330</v>
+      </c>
+      <c r="E16">
+        <v>120</v>
+      </c>
+      <c r="F16">
+        <v>4210</v>
+      </c>
+      <c r="G16">
+        <v>3560</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>2.5</v>
+      </c>
+      <c r="U16">
+        <v>9</v>
+      </c>
+      <c r="V16">
+        <v>5</v>
+      </c>
+      <c r="W16">
+        <v>2</v>
+      </c>
+      <c r="X16">
+        <v>2</v>
+      </c>
+      <c r="Y16">
+        <v>1</v>
+      </c>
+      <c r="Z16">
+        <v>2</v>
+      </c>
+      <c r="AA16">
+        <v>30</v>
+      </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <v>0</v>
+      </c>
+      <c r="AD16">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AD14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AD16"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/3_Automation_Dashboard/SomSaiJai_Dashboard_B1_2026.xlsx
+++ b/3_Automation_Dashboard/SomSaiJai_Dashboard_B1_2026.xlsx
@@ -1168,7 +1168,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F186"/>
+  <dimension ref="A1:F257"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1237,939 +1237,939 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>02/01/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B6" t="str">
-        <v>Jan26</v>
+        <v>May26</v>
       </c>
       <c r="C6" t="str">
         <v>COGS</v>
       </c>
       <c r="D6" t="str">
-        <v>Packaging</v>
+        <v>Ice</v>
       </c>
       <c r="E6" t="str">
-        <v>แก้ว หลอด</v>
+        <v>สับปะรด 18 ลูก</v>
       </c>
       <c r="F6">
-        <v>2165</v>
+        <v>576</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>02/01/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B7" t="str">
-        <v>Jan26</v>
+        <v>May26</v>
       </c>
       <c r="C7" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D7" t="str">
-        <v>Ice</v>
+        <v>Other</v>
       </c>
       <c r="E7" t="str">
-        <v>ส่วนแบ่ง60เปอ</v>
+        <v>สับปะรด 18 ลูก</v>
       </c>
       <c r="F7">
-        <v>47961</v>
+        <v>594</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>02/01/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B8" t="str">
-        <v>Jan26</v>
+        <v>May26</v>
       </c>
       <c r="C8" t="str">
         <v>COGS</v>
       </c>
       <c r="D8" t="str">
-        <v>Ice</v>
+        <v>Apple/Melon</v>
       </c>
       <c r="E8" t="str">
-        <v>ค่าส่วนแบ่งกำไรเมน 40เปอ</v>
+        <v>แอปเปิ้ล 3 ลังครับ</v>
       </c>
       <c r="F8">
-        <v>32000</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>02/01/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B9" t="str">
-        <v>Jan26</v>
+        <v>May26</v>
       </c>
       <c r="C9" t="str">
         <v>COGS</v>
       </c>
       <c r="D9" t="str">
-        <v>Transportation</v>
+        <v>Orange</v>
       </c>
       <c r="E9" t="str">
-        <v>Unknown</v>
+        <v>ค่าส่งส้ม Lalamove หักผ่านบัตร</v>
       </c>
       <c r="F9">
-        <v>400</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>03/01/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B10" t="str">
-        <v>Jan26</v>
+        <v>May26</v>
       </c>
       <c r="C10" t="str">
         <v>COGS</v>
       </c>
       <c r="D10" t="str">
-        <v>Watermelon</v>
+        <v>Orange</v>
       </c>
       <c r="E10" t="str">
-        <v>แตงโม 60 ลูก</v>
+        <v>24/05/69</v>
       </c>
       <c r="F10">
-        <v>4000</v>
+        <v>15015</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>04/01/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B11" t="str">
-        <v>Jan26</v>
+        <v>May26</v>
       </c>
       <c r="C11" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D11" t="str">
-        <v>Transportation</v>
+        <v>Salary</v>
       </c>
       <c r="E11" t="str">
-        <v>ค่าส่งแก้ว</v>
+        <v>เงินเดือนซี เดือนพ.ค.</v>
       </c>
       <c r="F11">
-        <v>198</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>06/01/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B12" t="str">
-        <v>Jan26</v>
+        <v>May26</v>
       </c>
       <c r="C12" t="str">
         <v>COGS</v>
       </c>
       <c r="D12" t="str">
-        <v>Orange</v>
+        <v>Packaging</v>
       </c>
       <c r="E12" t="str">
-        <v>ค่าส้ม 5720 ค่าส่งส้ม 960</v>
+        <v>แก้ว 3 ลัง</v>
       </c>
       <c r="F12">
-        <v>6680</v>
+        <v>4680</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>06/01/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B13" t="str">
-        <v>Jan26</v>
+        <v>May26</v>
       </c>
       <c r="C13" t="str">
         <v>COGS</v>
       </c>
       <c r="D13" t="str">
-        <v>Orange</v>
+        <v>Packaging</v>
       </c>
       <c r="E13" t="str">
-        <v>ค่าส่งส้มมาบทท</v>
+        <v>ฝา1 788</v>
       </c>
       <c r="F13">
-        <v>375</v>
+        <v>2902</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>07/01/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B14" t="str">
-        <v>Jan26</v>
+        <v>May26</v>
       </c>
       <c r="C14" t="str">
         <v>COGS</v>
       </c>
       <c r="D14" t="str">
-        <v>Transportation</v>
+        <v>Apple/Melon</v>
       </c>
       <c r="E14" t="str">
-        <v>Unknown</v>
+        <v>แอปเปิ้ล 2 ลัง</v>
       </c>
       <c r="F14">
-        <v>400</v>
+        <v>700</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>08/01/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B15" t="str">
-        <v>Jan26</v>
+        <v>May26</v>
       </c>
       <c r="C15" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D15" t="str">
-        <v>Ice</v>
+        <v>Other</v>
       </c>
       <c r="E15" t="str">
-        <v>ค่าเช่า12,000 น้ำไฟ324 รวม12,324</v>
+        <v>สับปะรด 18 ลูก</v>
       </c>
       <c r="F15">
-        <v>12324</v>
+        <v>522</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>08/01/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B16" t="str">
-        <v>Jan26</v>
+        <v>May26</v>
       </c>
       <c r="C16" t="str">
         <v>COGS</v>
       </c>
       <c r="D16" t="str">
-        <v>Transportation</v>
+        <v>Packaging</v>
       </c>
       <c r="E16" t="str">
-        <v>Unknown</v>
+        <v>หลอด20 แพค (767)</v>
       </c>
       <c r="F16">
-        <v>400</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>09/01/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B17" t="str">
-        <v>Jan26</v>
+        <v>May26</v>
       </c>
       <c r="C17" t="str">
         <v>COGS</v>
       </c>
       <c r="D17" t="str">
-        <v>Transportation</v>
+        <v>Mango</v>
       </c>
       <c r="E17" t="str">
-        <v>Unknown</v>
+        <v>มะม่วง 1 ตะกร้า</v>
       </c>
       <c r="F17">
-        <v>400</v>
+        <v>960</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>09/01/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B18" t="str">
-        <v>Jan26</v>
+        <v>May26</v>
       </c>
       <c r="C18" t="str">
         <v>COGS</v>
       </c>
       <c r="D18" t="str">
-        <v>Ice</v>
+        <v>Mango</v>
       </c>
       <c r="E18" t="str">
-        <v>ค่าขนตะกร้ากลับ</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F18">
-        <v>500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>11/01/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B19" t="str">
-        <v>Jan26</v>
+        <v>May26</v>
       </c>
       <c r="C19" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D19" t="str">
-        <v>Packaging</v>
+        <v>Other</v>
       </c>
       <c r="E19" t="str">
-        <v>ขวดใหญ่ 98 ใบ</v>
+        <v>16-5-2569ยอด 4,000฿</v>
       </c>
       <c r="F19">
-        <v>319</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>11/01/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B20" t="str">
-        <v>Jan26</v>
+        <v>May26</v>
       </c>
       <c r="C20" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D20" t="str">
-        <v>Orange</v>
+        <v>Other</v>
       </c>
       <c r="E20" t="str">
-        <v>ค่าส่งส้มไปบทท</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F20">
-        <v>461</v>
+        <v>600</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>11/01/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B21" t="str">
-        <v>Jan26</v>
+        <v>May26</v>
       </c>
       <c r="C21" t="str">
         <v>COGS</v>
       </c>
       <c r="D21" t="str">
-        <v>Orange</v>
+        <v>Transportation</v>
       </c>
       <c r="E21" t="str">
-        <v>ค่าส้ม20ลัง</v>
+        <v>ค่าขนส่ง</v>
       </c>
       <c r="F21">
-        <v>6680</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>11/01/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B22" t="str">
-        <v>Jan26</v>
+        <v>May26</v>
       </c>
       <c r="C22" t="str">
         <v>COGS</v>
       </c>
       <c r="D22" t="str">
-        <v>Transportation</v>
+        <v>Mango</v>
       </c>
       <c r="E22" t="str">
-        <v>Unknown</v>
+        <v>มะม่วง 1 ลัง (25 โล)</v>
       </c>
       <c r="F22">
-        <v>400</v>
+        <v>875</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>12/01/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B23" t="str">
-        <v>Jan26</v>
+        <v>May26</v>
       </c>
       <c r="C23" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D23" t="str">
-        <v>Packaging</v>
+        <v>Other</v>
       </c>
       <c r="E23" t="str">
-        <v>ถุงขยะ</v>
+        <v>ฝรั่ง 1 ลัง</v>
       </c>
       <c r="F23">
-        <v>548</v>
+        <v>600</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>14/01/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B24" t="str">
-        <v>Jan26</v>
+        <v>May26</v>
       </c>
       <c r="C24" t="str">
         <v>COGS</v>
       </c>
       <c r="D24" t="str">
-        <v>Packaging</v>
+        <v>Ice</v>
       </c>
       <c r="E24" t="str">
-        <v>Unknown</v>
+        <v>Police fees -2000 2 head</v>
       </c>
       <c r="F24">
-        <v>1625</v>
+        <v>4290</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>14/01/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B25" t="str">
-        <v>Jan26</v>
+        <v>May26</v>
       </c>
       <c r="C25" t="str">
         <v>COGS</v>
       </c>
       <c r="D25" t="str">
-        <v>Watermelon</v>
+        <v>Apple/Melon</v>
       </c>
       <c r="E25" t="str">
-        <v>แตงโม 40ลูก</v>
+        <v>แอปเปิ้ล 4 ลังครับ</v>
       </c>
       <c r="F25">
-        <v>3200</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>14/01/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B26" t="str">
-        <v>Jan26</v>
+        <v>May26</v>
       </c>
       <c r="C26" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D26" t="str">
-        <v>Orange</v>
+        <v>Other</v>
       </c>
       <c r="E26" t="str">
-        <v>ส้ม 20 ตะกร้า</v>
+        <v>36*18 648</v>
       </c>
       <c r="F26">
-        <v>6680</v>
+        <v>648</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>14/01/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B27" t="str">
-        <v>Jan26</v>
+        <v>May26</v>
       </c>
       <c r="C27" t="str">
         <v>COGS</v>
       </c>
       <c r="D27" t="str">
-        <v>Orange</v>
+        <v>Coconut</v>
       </c>
       <c r="E27" t="str">
-        <v>ค่าส่งส้มมาบทท</v>
+        <v>มะพร้าว 20 โล</v>
       </c>
       <c r="F27">
-        <v>675</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>17/01/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B28" t="str">
-        <v>Jan26</v>
+        <v>May26</v>
       </c>
       <c r="C28" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D28" t="str">
-        <v>Transportation</v>
+        <v>Other</v>
       </c>
       <c r="E28" t="str">
         <v>Unknown</v>
       </c>
       <c r="F28">
-        <v>400</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>17/01/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B29" t="str">
-        <v>Jan26</v>
+        <v>May26</v>
       </c>
       <c r="C29" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D29" t="str">
-        <v>Watermelon</v>
+        <v>Other</v>
       </c>
       <c r="E29" t="str">
-        <v>แตงโม 40 ลูก</v>
+        <v>14/05/26 18 ลูก 504 บาท 16/05/26 18 ลูก</v>
       </c>
       <c r="F29">
-        <v>3200</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>17/01/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B30" t="str">
-        <v>Jan26</v>
+        <v>May26</v>
       </c>
       <c r="C30" t="str">
         <v>COGS</v>
       </c>
       <c r="D30" t="str">
-        <v>Ice</v>
+        <v>Mango</v>
       </c>
       <c r="E30" t="str">
-        <v>Unknown</v>
+        <v>มะม่วง 1</v>
       </c>
       <c r="F30">
-        <v>60</v>
+        <v>875</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>19/01/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B31" t="str">
-        <v>Jan26</v>
+        <v>May26</v>
       </c>
       <c r="C31" t="str">
         <v>COGS</v>
       </c>
       <c r="D31" t="str">
-        <v>Transportation</v>
+        <v>Orange</v>
       </c>
       <c r="E31" t="str">
-        <v>ค่าขนส่ง</v>
+        <v>15/05/69</v>
       </c>
       <c r="F31">
-        <v>349</v>
+        <v>15730</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>20/01/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B32" t="str">
-        <v>Jan26</v>
+        <v>May26</v>
       </c>
       <c r="C32" t="str">
         <v>COGS</v>
       </c>
       <c r="D32" t="str">
-        <v>Transportation</v>
+        <v>Orange</v>
       </c>
       <c r="E32" t="str">
-        <v>Unknown</v>
+        <v>05/05/69 ส้ม 30x22กก 660กกx30</v>
       </c>
       <c r="F32">
-        <v>400</v>
+        <v>21450</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>20/01/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B33" t="str">
-        <v>Jan26</v>
+        <v>May26</v>
       </c>
       <c r="C33" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D33" t="str">
-        <v>Packaging</v>
+        <v>Other</v>
       </c>
       <c r="E33" t="str">
-        <v>แก้วฝา 2</v>
+        <v>11-5-2569 50 ลูก ยอด 4,000</v>
       </c>
       <c r="F33">
-        <v>2702</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>20/01/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B34" t="str">
-        <v>Jan26</v>
+        <v>May26</v>
       </c>
       <c r="C34" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D34" t="str">
-        <v>Watermelon</v>
+        <v>Fixed Costs</v>
       </c>
       <c r="E34" t="str">
-        <v>แตงโม 40</v>
+        <v>ค่าเช่า+สต๊อกร้าน 1</v>
       </c>
       <c r="F34">
-        <v>3200</v>
+        <v>47000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>21/01/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B35" t="str">
-        <v>Jan26</v>
+        <v>May26</v>
       </c>
       <c r="C35" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D35" t="str">
-        <v>Transportation</v>
+        <v>Other</v>
       </c>
       <c r="E35" t="str">
-        <v>ค่าขนส่ง</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F35">
-        <v>675</v>
+        <v>600</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>23/01/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B36" t="str">
-        <v>Jan26</v>
+        <v>May26</v>
       </c>
       <c r="C36" t="str">
         <v>COGS</v>
       </c>
       <c r="D36" t="str">
-        <v>Orange</v>
+        <v>Apple/Melon</v>
       </c>
       <c r="E36" t="str">
-        <v>ค่าส้ม20ตะกร้า</v>
+        <v>แอปเปิ้ล 3 ลัง</v>
       </c>
       <c r="F36">
-        <v>7120</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>23/01/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B37" t="str">
-        <v>Jan26</v>
+        <v>May26</v>
       </c>
       <c r="C37" t="str">
         <v>COGS</v>
       </c>
       <c r="D37" t="str">
-        <v>Transportation</v>
+        <v>Mango</v>
       </c>
       <c r="E37" t="str">
-        <v>Unknown</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F37">
-        <v>400</v>
+        <v>875</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>23/01/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B38" t="str">
-        <v>Jan26</v>
+        <v>May26</v>
       </c>
       <c r="C38" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D38" t="str">
-        <v>Transportation</v>
+        <v>Other</v>
       </c>
       <c r="E38" t="str">
-        <v>Unknown</v>
+        <v>ที่หนีบ 6ตัว 374 บาท</v>
       </c>
       <c r="F38">
-        <v>400</v>
+        <v>374</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>23/01/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B39" t="str">
-        <v>Jan26</v>
+        <v>May26</v>
       </c>
       <c r="C39" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D39" t="str">
-        <v>Watermelon</v>
+        <v>Other</v>
       </c>
       <c r="E39" t="str">
-        <v>แตงโม 40 ลูก</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F39">
-        <v>3200</v>
+        <v>600</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>25/01/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B40" t="str">
-        <v>Jan26</v>
+        <v>May26</v>
       </c>
       <c r="C40" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D40" t="str">
-        <v>Orange</v>
+        <v>Other</v>
       </c>
       <c r="E40" t="str">
-        <v>ส้ม5ตะกร้า แตงโม 40 ลูก</v>
+        <v>09/05/26 สับปะรด 2 ตะกร้า</v>
       </c>
       <c r="F40">
-        <v>5950</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>25/01/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B41" t="str">
-        <v>Jan26</v>
+        <v>May26</v>
       </c>
       <c r="C41" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D41" t="str">
-        <v>Transportation</v>
+        <v>Other</v>
       </c>
       <c r="E41" t="str">
-        <v>ค่าส่งฝา</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F41">
-        <v>114</v>
+        <v>600</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>26/01/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B42" t="str">
-        <v>Jan26</v>
+        <v>May26</v>
       </c>
       <c r="C42" t="str">
         <v>COGS</v>
       </c>
       <c r="D42" t="str">
-        <v>Orange</v>
+        <v>Coconut</v>
       </c>
       <c r="E42" t="str">
-        <v>ค่าส้ม 30 ตะกร้า</v>
+        <v>เนื้อมะพร้าว 1 ลัง</v>
       </c>
       <c r="F42">
-        <v>10680</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>26/01/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B43" t="str">
-        <v>Jan26</v>
+        <v>May26</v>
       </c>
       <c r="C43" t="str">
         <v>COGS</v>
       </c>
       <c r="D43" t="str">
-        <v>Transportation</v>
+        <v>Mango</v>
       </c>
       <c r="E43" t="str">
-        <v>Unknown</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F43">
-        <v>400</v>
+        <v>910</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>26/01/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B44" t="str">
-        <v>Jan26</v>
+        <v>May26</v>
       </c>
       <c r="C44" t="str">
         <v>COGS</v>
       </c>
       <c r="D44" t="str">
-        <v>Transportation</v>
+        <v>Watermelon</v>
       </c>
       <c r="E44" t="str">
-        <v>Unknown</v>
+        <v>แตงโม 4000 วันที่ 9-5-26</v>
       </c>
       <c r="F44">
-        <v>400</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>27/01/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B45" t="str">
-        <v>Jan26</v>
+        <v>May26</v>
       </c>
       <c r="C45" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D45" t="str">
-        <v>Packaging</v>
+        <v>Other</v>
       </c>
       <c r="E45" t="str">
-        <v>ถุงมือ - 5 กล่อง</v>
+        <v>ไฟ 2อัน 422</v>
       </c>
       <c r="F45">
-        <v>1077</v>
+        <v>838</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>28/01/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B46" t="str">
-        <v>Jan26</v>
+        <v>May26</v>
       </c>
       <c r="C46" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D46" t="str">
-        <v>Transportation</v>
+        <v>Other</v>
       </c>
       <c r="E46" t="str">
-        <v>ค่าส่ง</v>
+        <v>พรหมเช็ดเท้า 1 ผืน</v>
       </c>
       <c r="F46">
-        <v>486</v>
+        <v>372</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>28/01/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B47" t="str">
-        <v>Jan26</v>
+        <v>May26</v>
       </c>
       <c r="C47" t="str">
         <v>COGS</v>
       </c>
       <c r="D47" t="str">
-        <v>Transportation</v>
+        <v>Milk/Conden</v>
       </c>
       <c r="E47" t="str">
-        <v>Unknown</v>
+        <v>นมข้นจืด 1ลัง 636</v>
       </c>
       <c r="F47">
-        <v>400</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>28/01/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B48" t="str">
-        <v>Jan26</v>
+        <v>May26</v>
       </c>
       <c r="C48" t="str">
         <v>COGS</v>
       </c>
       <c r="D48" t="str">
-        <v>Watermelon</v>
+        <v>Packaging</v>
       </c>
       <c r="E48" t="str">
-        <v>ค่าแตงโม 50 ลูก</v>
+        <v>นมข้น 3 ลัง 2568</v>
       </c>
       <c r="F48">
-        <v>4000</v>
+        <v>4875</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>28/01/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B49" t="str">
-        <v>Jan26</v>
+        <v>May26</v>
       </c>
       <c r="C49" t="str">
-        <v>COGS</v>
+        <v>CAPEX</v>
       </c>
       <c r="D49" t="str">
-        <v>Transportation</v>
+        <v>Investment</v>
       </c>
       <c r="E49" t="str">
-        <v>Unknown</v>
+        <v>เครื่องสกัดเย็น 1</v>
       </c>
       <c r="F49">
-        <v>400</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>28/01/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B50" t="str">
-        <v>Jan26</v>
+        <v>May26</v>
       </c>
       <c r="C50" t="str">
         <v>COGS</v>
       </c>
       <c r="D50" t="str">
-        <v>Transportation</v>
+        <v>Packaging</v>
       </c>
       <c r="E50" t="str">
-        <v>ค่าส่ง</v>
+        <v>แก้ว3ลัง 5,301</v>
       </c>
       <c r="F50">
-        <v>486</v>
+        <v>6132</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>28/01/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B51" t="str">
-        <v>Jan26</v>
+        <v>May26</v>
       </c>
       <c r="C51" t="str">
         <v>COGS</v>
       </c>
       <c r="D51" t="str">
-        <v>Watermelon</v>
+        <v>Packaging</v>
       </c>
       <c r="E51" t="str">
-        <v>แตงโม 50 ลูก</v>
+        <v>ถุงมือ 20 กล่อง 2246 ฝา1ลัง 969</v>
       </c>
       <c r="F51">
-        <v>4000</v>
+        <v>4496</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>30/01/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B52" t="str">
-        <v>Jan26</v>
+        <v>May26</v>
       </c>
       <c r="C52" t="str">
         <v>COGS</v>
       </c>
       <c r="D52" t="str">
-        <v>Watermelon</v>
+        <v>Transportation</v>
       </c>
       <c r="E52" t="str">
-        <v>แตงโม 25 ลูก</v>
+        <v>Lalamove</v>
       </c>
       <c r="F52">
         <v>2000</v>
@@ -2177,170 +2177,170 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>30/01/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B53" t="str">
-        <v>Jan26</v>
+        <v>May26</v>
       </c>
       <c r="C53" t="str">
         <v>COGS</v>
       </c>
       <c r="D53" t="str">
-        <v>Apple/Melon</v>
+        <v>Transportation</v>
       </c>
       <c r="E53" t="str">
-        <v>แอปเปิ้ล เมล่อน</v>
+        <v>น้ำ 20 ขวด 900 ถอดเสื้อ 30 ลูก750 กล่องโฟม 3</v>
       </c>
       <c r="F53">
-        <v>851</v>
+        <v>4555</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>31/01/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B54" t="str">
-        <v>Jan26</v>
+        <v>May26</v>
       </c>
       <c r="C54" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D54" t="str">
-        <v>Salary</v>
+        <v>Water</v>
       </c>
       <c r="E54" t="str">
-        <v>เงินเดือนเมนมกราคม</v>
+        <v>น้ำมะร้าว 1 ลัง</v>
       </c>
       <c r="F54">
-        <v>19000</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>02/02/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B55" t="str">
-        <v>Feb26</v>
+        <v>May26</v>
       </c>
       <c r="C55" t="str">
         <v>COGS</v>
       </c>
       <c r="D55" t="str">
-        <v>Orange</v>
+        <v>Packaging</v>
       </c>
       <c r="E55" t="str">
-        <v>ส้ม 30 ตะกร้า</v>
+        <v>6 พ.ค. น้ำ 30 ขวด 1500 บาท เนื้อ 11 โล 1320 บาท</v>
       </c>
       <c r="F55">
-        <v>10680</v>
+        <v>2820</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>02/02/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B56" t="str">
-        <v>Feb26</v>
+        <v>May26</v>
       </c>
       <c r="C56" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D56" t="str">
-        <v>Watermelon</v>
+        <v>Other</v>
       </c>
       <c r="E56" t="str">
-        <v>แตงโม 50 ลูก</v>
+        <v>ค่าทำความสะอาดตึกชั้น 1</v>
       </c>
       <c r="F56">
-        <v>4000</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>02/02/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B57" t="str">
-        <v>Feb26</v>
+        <v>May26</v>
       </c>
       <c r="C57" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D57" t="str">
-        <v>Transportation</v>
+        <v>Other</v>
       </c>
       <c r="E57" t="str">
-        <v>Unknown</v>
+        <v>4-5-2569 เบอร์ 70฿ 60 ลูก ยอด 4,200</v>
       </c>
       <c r="F57">
-        <v>2000</v>
+        <v>8200</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>04/02/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B58" t="str">
-        <v>Feb26</v>
+        <v>May26</v>
       </c>
       <c r="C58" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D58" t="str">
-        <v>Packaging</v>
+        <v>Other</v>
       </c>
       <c r="E58" t="str">
-        <v>ฝา 690 1000 ชิ้น แก้ว 1196 1000 ชิ้น หลอด 421</v>
+        <v>ทิชชู่3แพค 36ห่อ</v>
       </c>
       <c r="F58">
-        <v>2023</v>
+        <v>451</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>05/02/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B59" t="str">
-        <v>Feb26</v>
+        <v>May26</v>
       </c>
       <c r="C59" t="str">
         <v>COGS</v>
       </c>
       <c r="D59" t="str">
-        <v>Watermelon</v>
+        <v>Coconut</v>
       </c>
       <c r="E59" t="str">
-        <v>แตงโม 50 ลูก</v>
+        <v>มะพร้าวถอดเสื้อ 23 ลูก *35 ราคา 805 ค่าส่ง 150</v>
       </c>
       <c r="F59">
-        <v>4000</v>
+        <v>955</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>05/02/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B60" t="str">
-        <v>Feb26</v>
+        <v>May26</v>
       </c>
       <c r="C60" t="str">
         <v>COGS</v>
       </c>
       <c r="D60" t="str">
-        <v>Packaging</v>
+        <v>Mango</v>
       </c>
       <c r="E60" t="str">
-        <v>แก้วสกรีน อย่างเดียวไม่รวมฝา 2280บาท</v>
+        <v>มะม่วง 2 ลัง</v>
       </c>
       <c r="F60">
-        <v>2280</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>08/02/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B61" t="str">
-        <v>Feb26</v>
+        <v>May26</v>
       </c>
       <c r="C61" t="str">
         <v>COGS</v>
@@ -2349,158 +2349,158 @@
         <v>Ice</v>
       </c>
       <c r="E61" t="str">
-        <v>Unknown</v>
+        <v>สับปะรด 18 ลูก</v>
       </c>
       <c r="F61">
-        <v>798</v>
+        <v>486</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>08/02/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B62" t="str">
-        <v>Feb26</v>
+        <v>May26</v>
       </c>
       <c r="C62" t="str">
         <v>COGS</v>
       </c>
       <c r="D62" t="str">
-        <v>Watermelon</v>
+        <v>Apple/Melon</v>
       </c>
       <c r="E62" t="str">
-        <v>แตงโม 50</v>
+        <v>แอปเปิ้ล 4 ลัง</v>
       </c>
       <c r="F62">
-        <v>4000</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>08/02/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B63" t="str">
-        <v>Feb26</v>
+        <v>May26</v>
       </c>
       <c r="C63" t="str">
         <v>COGS</v>
       </c>
       <c r="D63" t="str">
-        <v>Transportation</v>
+        <v>Packaging</v>
       </c>
       <c r="E63" t="str">
-        <v>Unknown</v>
+        <v>ถุงมือ4อัน</v>
       </c>
       <c r="F63">
-        <v>2000</v>
+        <v>499</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>09/02/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B64" t="str">
-        <v>Feb26</v>
+        <v>May26</v>
       </c>
       <c r="C64" t="str">
         <v>COGS</v>
       </c>
       <c r="D64" t="str">
-        <v>Orange</v>
+        <v>Apple/Melon</v>
       </c>
       <c r="E64" t="str">
-        <v>ส้ม 30 ตะกร้า</v>
+        <v>แอปเปิ้ล 4 ลัง</v>
       </c>
       <c r="F64">
-        <v>10680</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>09/02/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B65" t="str">
-        <v>Feb26</v>
+        <v>May26</v>
       </c>
       <c r="C65" t="str">
         <v>COGS</v>
       </c>
       <c r="D65" t="str">
-        <v>Orange</v>
+        <v>Mango</v>
       </c>
       <c r="E65" t="str">
-        <v>ค่าส่งส้ม</v>
+        <v>มะม่วง 2 ลัง</v>
       </c>
       <c r="F65">
-        <v>685</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>10/02/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B66" t="str">
-        <v>Feb26</v>
+        <v>May26</v>
       </c>
       <c r="C66" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D66" t="str">
-        <v>Ice</v>
+        <v>Other</v>
       </c>
       <c r="E66" t="str">
-        <v>ค่าไฟเดือนมค</v>
+        <v>30-4-2569 เบอร์ 70฿ 60 ลูก</v>
       </c>
       <c r="F66">
-        <v>389</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>11/02/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B67" t="str">
-        <v>Feb26</v>
+        <v>May26</v>
       </c>
       <c r="C67" t="str">
         <v>COGS</v>
       </c>
       <c r="D67" t="str">
-        <v>Watermelon</v>
+        <v>Mango</v>
       </c>
       <c r="E67" t="str">
-        <v>แตงโม 50 ลูก</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F67">
-        <v>4000</v>
+        <v>910</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>14/02/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B68" t="str">
-        <v>Feb26</v>
+        <v>May26</v>
       </c>
       <c r="C68" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D68" t="str">
-        <v>Other</v>
+        <v>Apple/Melon</v>
       </c>
       <c r="E68" t="str">
-        <v>Unknown</v>
+        <v>แอปเปิ้ล 4 ลัง</v>
       </c>
       <c r="F68">
-        <v>4000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>14/02/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B69" t="str">
-        <v>Feb26</v>
+        <v>May26</v>
       </c>
       <c r="C69" t="str">
         <v>COGS</v>
@@ -2509,278 +2509,278 @@
         <v>Ice</v>
       </c>
       <c r="E69" t="str">
-        <v>Unknown</v>
+        <v>สับปะรด 30 ลูก</v>
       </c>
       <c r="F69">
-        <v>350</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>16/02/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B70" t="str">
-        <v>Feb26</v>
+        <v>May26</v>
       </c>
       <c r="C70" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D70" t="str">
-        <v>Orange</v>
+        <v>Salary</v>
       </c>
       <c r="E70" t="str">
-        <v>ค่าส่งส้ม</v>
+        <v>เงินเดือนเมน 5/26</v>
       </c>
       <c r="F70">
-        <v>485</v>
+        <v>19000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>16/02/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B71" t="str">
-        <v>Feb26</v>
+        <v>May26</v>
       </c>
       <c r="C71" t="str">
         <v>COGS</v>
       </c>
       <c r="D71" t="str">
-        <v>Orange</v>
+        <v>Ice</v>
       </c>
       <c r="E71" t="str">
-        <v>ค่าส้ม 30 ตะกร้า 13/2/69</v>
+        <v>ค่าหาหมอเอ</v>
       </c>
       <c r="F71">
-        <v>10680</v>
+        <v>706</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>19/02/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B72" t="str">
-        <v>Feb26</v>
+        <v>May26</v>
       </c>
       <c r="C72" t="str">
         <v>COGS</v>
       </c>
       <c r="D72" t="str">
-        <v>Watermelon</v>
+        <v>Ice</v>
       </c>
       <c r="E72" t="str">
-        <v>แตงโม 50 ลูก วันที่ 1719</v>
+        <v>ค่าหมอเอ</v>
       </c>
       <c r="F72">
-        <v>8000</v>
+        <v>13</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>19/02/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B73" t="str">
-        <v>Feb26</v>
+        <v>May26</v>
       </c>
       <c r="C73" t="str">
         <v>COGS</v>
       </c>
       <c r="D73" t="str">
-        <v>Packaging</v>
+        <v>Water</v>
       </c>
       <c r="E73" t="str">
-        <v>แก้ว</v>
+        <v>ร่ม 1176 ร่ม 843 ฝรั่ง 300 นมข้นจืด 785 ที่ปั้ม 176</v>
       </c>
       <c r="F73">
-        <v>3315</v>
+        <v>7823</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>19/02/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B74" t="str">
-        <v>Feb26</v>
+        <v>May26</v>
       </c>
       <c r="C74" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D74" t="str">
-        <v>Transportation</v>
+        <v>Other</v>
       </c>
       <c r="E74" t="str">
-        <v>แก้วสกรีน2ลัง(รอบที่1นะ แบ่งสั่งจะได้ไม่มีค่า</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F74">
-        <v>6655</v>
+        <v>600</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>19/02/2026</v>
+        <v>01/01/2026</v>
       </c>
       <c r="B75" t="str">
-        <v>Feb26</v>
+        <v>May26</v>
       </c>
       <c r="C75" t="str">
         <v>COGS</v>
       </c>
       <c r="D75" t="str">
-        <v>Transportation</v>
+        <v>Mango</v>
       </c>
       <c r="E75" t="str">
-        <v>Unknown</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F75">
-        <v>2000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>20/02/2026</v>
+        <v>02/01/2026</v>
       </c>
       <c r="B76" t="str">
-        <v>Feb26</v>
+        <v>Jan26</v>
       </c>
       <c r="C76" t="str">
         <v>COGS</v>
       </c>
       <c r="D76" t="str">
-        <v>Ice</v>
+        <v>Packaging</v>
       </c>
       <c r="E76" t="str">
-        <v>ผ้าปิดร้าน 218 ค่ารถ 198</v>
+        <v>แก้ว หลอด</v>
       </c>
       <c r="F76">
-        <v>416</v>
+        <v>2165</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>23/02/2026</v>
+        <v>02/01/2026</v>
       </c>
       <c r="B77" t="str">
-        <v>Feb26</v>
+        <v>Jan26</v>
       </c>
       <c r="C77" t="str">
         <v>COGS</v>
       </c>
       <c r="D77" t="str">
-        <v>Watermelon</v>
+        <v>Ice</v>
       </c>
       <c r="E77" t="str">
-        <v>แตงโม 21 50 ลูก 23 50 ลูก</v>
+        <v>ส่วนแบ่ง60เปอ</v>
       </c>
       <c r="F77">
-        <v>8000</v>
+        <v>47961</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>24/02/2026</v>
+        <v>02/01/2026</v>
       </c>
       <c r="B78" t="str">
-        <v>Feb26</v>
+        <v>Jan26</v>
       </c>
       <c r="C78" t="str">
         <v>COGS</v>
       </c>
       <c r="D78" t="str">
-        <v>Transportation</v>
+        <v>Ice</v>
       </c>
       <c r="E78" t="str">
-        <v>Unknown</v>
+        <v>ค่าส่วนแบ่งกำไรเมน 40เปอ</v>
       </c>
       <c r="F78">
-        <v>209</v>
+        <v>32000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>24/02/2026</v>
+        <v>02/01/2026</v>
       </c>
       <c r="B79" t="str">
-        <v>Feb26</v>
+        <v>Jan26</v>
       </c>
       <c r="C79" t="str">
         <v>COGS</v>
       </c>
       <c r="D79" t="str">
-        <v>Orange</v>
+        <v>Transportation</v>
       </c>
       <c r="E79" t="str">
-        <v>ส้ม 30 18/2/69</v>
+        <v>Unknown</v>
       </c>
       <c r="F79">
-        <v>10680</v>
+        <v>400</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>24/02/2026</v>
+        <v>03/01/2026</v>
       </c>
       <c r="B80" t="str">
-        <v>Feb26</v>
+        <v>Jan26</v>
       </c>
       <c r="C80" t="str">
         <v>COGS</v>
       </c>
       <c r="D80" t="str">
-        <v>Packaging</v>
+        <v>Watermelon</v>
       </c>
       <c r="E80" t="str">
-        <v>แก้ว 2400 ฝา 1670</v>
+        <v>แตงโม 60 ลูก</v>
       </c>
       <c r="F80">
-        <v>4070</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>25/02/2026</v>
+        <v>04/01/2026</v>
       </c>
       <c r="B81" t="str">
-        <v>Feb26</v>
+        <v>Jan26</v>
       </c>
       <c r="C81" t="str">
         <v>COGS</v>
       </c>
       <c r="D81" t="str">
-        <v>Watermelon</v>
+        <v>Transportation</v>
       </c>
       <c r="E81" t="str">
-        <v>แตงโม 50</v>
+        <v>ค่าส่งแก้ว</v>
       </c>
       <c r="F81">
-        <v>4000</v>
+        <v>198</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>25/02/2026</v>
+        <v>06/01/2026</v>
       </c>
       <c r="B82" t="str">
-        <v>Feb26</v>
+        <v>Jan26</v>
       </c>
       <c r="C82" t="str">
         <v>COGS</v>
       </c>
       <c r="D82" t="str">
-        <v>Transportation</v>
+        <v>Orange</v>
       </c>
       <c r="E82" t="str">
-        <v>Unknown</v>
+        <v>ค่าส้ม 5720 ค่าส่งส้ม 960</v>
       </c>
       <c r="F82">
-        <v>2000</v>
+        <v>6680</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>25/02/2026</v>
+        <v>06/01/2026</v>
       </c>
       <c r="B83" t="str">
-        <v>Feb26</v>
+        <v>Jan26</v>
       </c>
       <c r="C83" t="str">
         <v>COGS</v>
@@ -2789,98 +2789,98 @@
         <v>Orange</v>
       </c>
       <c r="E83" t="str">
-        <v>ส้ม20 ตะกร้า</v>
+        <v>ค่าส่งส้มมาบทท</v>
       </c>
       <c r="F83">
-        <v>7312</v>
+        <v>375</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>25/02/2026</v>
+        <v>07/01/2026</v>
       </c>
       <c r="B84" t="str">
-        <v>Feb26</v>
+        <v>Jan26</v>
       </c>
       <c r="C84" t="str">
         <v>COGS</v>
       </c>
       <c r="D84" t="str">
-        <v>Orange</v>
+        <v>Transportation</v>
       </c>
       <c r="E84" t="str">
-        <v>ค่าส่งส้ม</v>
+        <v>Unknown</v>
       </c>
       <c r="F84">
-        <v>806</v>
+        <v>400</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>26/02/2026</v>
+        <v>08/01/2026</v>
       </c>
       <c r="B85" t="str">
-        <v>Feb26</v>
+        <v>Jan26</v>
       </c>
       <c r="C85" t="str">
         <v>COGS</v>
       </c>
       <c r="D85" t="str">
-        <v>Packaging</v>
+        <v>Ice</v>
       </c>
       <c r="E85" t="str">
-        <v>ค่าขวดใหญ่</v>
+        <v>ค่าเช่า12,000 น้ำไฟ324 รวม12,324</v>
       </c>
       <c r="F85">
-        <v>319</v>
+        <v>12324</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>28/02/2026</v>
+        <v>08/01/2026</v>
       </c>
       <c r="B86" t="str">
-        <v>Feb26</v>
+        <v>Jan26</v>
       </c>
       <c r="C86" t="str">
         <v>COGS</v>
       </c>
       <c r="D86" t="str">
-        <v>Orange</v>
+        <v>Transportation</v>
       </c>
       <c r="E86" t="str">
-        <v>ค่าส่งส้ม</v>
+        <v>Unknown</v>
       </c>
       <c r="F86">
-        <v>2237</v>
+        <v>400</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>28/02/2026</v>
+        <v>09/01/2026</v>
       </c>
       <c r="B87" t="str">
-        <v>Feb26</v>
+        <v>Jan26</v>
       </c>
       <c r="C87" t="str">
         <v>COGS</v>
       </c>
       <c r="D87" t="str">
-        <v>Orange</v>
+        <v>Transportation</v>
       </c>
       <c r="E87" t="str">
-        <v>ค่าส่งส้ม</v>
+        <v>Unknown</v>
       </c>
       <c r="F87">
-        <v>2237</v>
+        <v>400</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>28/02/2026</v>
+        <v>09/01/2026</v>
       </c>
       <c r="B88" t="str">
-        <v>Feb26</v>
+        <v>Jan26</v>
       </c>
       <c r="C88" t="str">
         <v>COGS</v>
@@ -2889,298 +2889,298 @@
         <v>Ice</v>
       </c>
       <c r="E88" t="str">
-        <v>ค่าเช่าสต็อคกพ</v>
+        <v>ค่าขนตะกร้ากลับ</v>
       </c>
       <c r="F88">
-        <v>12000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>28/02/2026</v>
+        <v>11/01/2026</v>
       </c>
       <c r="B89" t="str">
-        <v>Feb26</v>
+        <v>Jan26</v>
       </c>
       <c r="C89" t="str">
         <v>COGS</v>
       </c>
       <c r="D89" t="str">
-        <v>Watermelon</v>
+        <v>Packaging</v>
       </c>
       <c r="E89" t="str">
-        <v>แตงโม 50 ลูก</v>
+        <v>ขวดใหญ่ 98 ใบ</v>
       </c>
       <c r="F89">
-        <v>4000</v>
+        <v>319</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>04/03/2026</v>
+        <v>11/01/2026</v>
       </c>
       <c r="B90" t="str">
-        <v>Mar26</v>
+        <v>Jan26</v>
       </c>
       <c r="C90" t="str">
         <v>COGS</v>
       </c>
       <c r="D90" t="str">
-        <v>Watermelon</v>
+        <v>Orange</v>
       </c>
       <c r="E90" t="str">
-        <v>ค่าทางด่วนส่งแตงโม</v>
+        <v>ค่าส่งส้มไปบทท</v>
       </c>
       <c r="F90">
-        <v>140</v>
+        <v>461</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>04/03/2026</v>
+        <v>11/01/2026</v>
       </c>
       <c r="B91" t="str">
-        <v>Mar26</v>
+        <v>Jan26</v>
       </c>
       <c r="C91" t="str">
         <v>COGS</v>
       </c>
       <c r="D91" t="str">
-        <v>Mango</v>
+        <v>Orange</v>
       </c>
       <c r="E91" t="str">
-        <v>มะม่วง 16 โล</v>
+        <v>ค่าส้ม20ลัง</v>
       </c>
       <c r="F91">
-        <v>560</v>
+        <v>6680</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>05/03/2026</v>
+        <v>11/01/2026</v>
       </c>
       <c r="B92" t="str">
-        <v>Feb26</v>
+        <v>Jan26</v>
       </c>
       <c r="C92" t="str">
         <v>COGS</v>
       </c>
       <c r="D92" t="str">
-        <v>Mango</v>
+        <v>Transportation</v>
       </c>
       <c r="E92" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>Unknown</v>
       </c>
       <c r="F92">
-        <v>500</v>
+        <v>400</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>05/03/2026</v>
+        <v>12/01/2026</v>
       </c>
       <c r="B93" t="str">
-        <v>Feb26</v>
+        <v>Jan26</v>
       </c>
       <c r="C93" t="str">
         <v>COGS</v>
       </c>
       <c r="D93" t="str">
-        <v>Orange</v>
+        <v>Packaging</v>
       </c>
       <c r="E93" t="str">
-        <v>ค่าส้มวันที่ 27269</v>
+        <v>ถุงขยะ</v>
       </c>
       <c r="F93">
-        <v>7312</v>
+        <v>548</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>05/03/2026</v>
+        <v>14/01/2026</v>
       </c>
       <c r="B94" t="str">
-        <v>Mar26</v>
+        <v>Jan26</v>
       </c>
       <c r="C94" t="str">
         <v>COGS</v>
       </c>
       <c r="D94" t="str">
-        <v>Orange</v>
+        <v>Packaging</v>
       </c>
       <c r="E94" t="str">
-        <v>แตงโม 51 ยอด3,500</v>
+        <v>Unknown</v>
       </c>
       <c r="F94">
-        <v>7700</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>05/03/2026</v>
+        <v>14/01/2026</v>
       </c>
       <c r="B95" t="str">
-        <v>Mar26</v>
+        <v>Jan26</v>
       </c>
       <c r="C95" t="str">
         <v>COGS</v>
       </c>
       <c r="D95" t="str">
-        <v>Orange</v>
+        <v>Watermelon</v>
       </c>
       <c r="E95" t="str">
-        <v>ค่าส้ม 20 ตะกร้า</v>
+        <v>แตงโม 40ลูก</v>
       </c>
       <c r="F95">
-        <v>7312</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>05/03/2026</v>
+        <v>14/01/2026</v>
       </c>
       <c r="B96" t="str">
-        <v>Mar26</v>
+        <v>Jan26</v>
       </c>
       <c r="C96" t="str">
         <v>COGS</v>
       </c>
       <c r="D96" t="str">
-        <v>Ice</v>
+        <v>Orange</v>
       </c>
       <c r="E96" t="str">
-        <v>ค่าทางด่วน</v>
+        <v>ส้ม 20 ตะกร้า</v>
       </c>
       <c r="F96">
-        <v>105</v>
+        <v>6680</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>05/03/2026</v>
+        <v>14/01/2026</v>
       </c>
       <c r="B97" t="str">
-        <v>Mar26</v>
+        <v>Jan26</v>
       </c>
       <c r="C97" t="str">
         <v>COGS</v>
       </c>
       <c r="D97" t="str">
-        <v>Packaging</v>
+        <v>Orange</v>
       </c>
       <c r="E97" t="str">
-        <v>ถุงขยะ</v>
+        <v>ค่าส่งส้มมาบทท</v>
       </c>
       <c r="F97">
-        <v>909</v>
+        <v>675</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>05/03/2026</v>
+        <v>17/01/2026</v>
       </c>
       <c r="B98" t="str">
-        <v>Mar26</v>
+        <v>Jan26</v>
       </c>
       <c r="C98" t="str">
         <v>COGS</v>
       </c>
       <c r="D98" t="str">
-        <v>Mango</v>
+        <v>Transportation</v>
       </c>
       <c r="E98" t="str">
-        <v>มะม่วง 24 โล</v>
+        <v>Unknown</v>
       </c>
       <c r="F98">
-        <v>1560</v>
+        <v>400</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>07/03/2026</v>
+        <v>17/01/2026</v>
       </c>
       <c r="B99" t="str">
-        <v>Mar26</v>
+        <v>Jan26</v>
       </c>
       <c r="C99" t="str">
         <v>COGS</v>
       </c>
       <c r="D99" t="str">
-        <v>Transportation</v>
+        <v>Watermelon</v>
       </c>
       <c r="E99" t="str">
-        <v>Unknown</v>
+        <v>แตงโม 40 ลูก</v>
       </c>
       <c r="F99">
-        <v>2000</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>10/03/2026</v>
+        <v>17/01/2026</v>
       </c>
       <c r="B100" t="str">
-        <v>Mar26</v>
+        <v>Jan26</v>
       </c>
       <c r="C100" t="str">
         <v>COGS</v>
       </c>
       <c r="D100" t="str">
-        <v>Orange</v>
+        <v>Ice</v>
       </c>
       <c r="E100" t="str">
-        <v>09/03/69</v>
+        <v>Unknown</v>
       </c>
       <c r="F100">
-        <v>9804</v>
+        <v>60</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>10/03/2026</v>
+        <v>19/01/2026</v>
       </c>
       <c r="B101" t="str">
-        <v>Mar26</v>
+        <v>Jan26</v>
       </c>
       <c r="C101" t="str">
         <v>COGS</v>
       </c>
       <c r="D101" t="str">
-        <v>Watermelon</v>
+        <v>Transportation</v>
       </c>
       <c r="E101" t="str">
-        <v>แตงโม 50 วันที่ 7 แตงโม 50 วันที่ 10</v>
+        <v>ค่าขนส่ง</v>
       </c>
       <c r="F101">
-        <v>8000</v>
+        <v>349</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>10/03/2026</v>
+        <v>20/01/2026</v>
       </c>
       <c r="B102" t="str">
-        <v>Mar26</v>
+        <v>Jan26</v>
       </c>
       <c r="C102" t="str">
-        <v>CAPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D102" t="str">
-        <v>Investment</v>
+        <v>Transportation</v>
       </c>
       <c r="E102" t="str">
         <v>Unknown</v>
       </c>
       <c r="F102">
-        <v>6500</v>
+        <v>400</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>10/03/2026</v>
+        <v>20/01/2026</v>
       </c>
       <c r="B103" t="str">
-        <v>Mar26</v>
+        <v>Jan26</v>
       </c>
       <c r="C103" t="str">
         <v>COGS</v>
@@ -3189,118 +3189,118 @@
         <v>Packaging</v>
       </c>
       <c r="E103" t="str">
-        <v>แก้ว2ลัง ลังละ 1560</v>
+        <v>แก้วฝา 2</v>
       </c>
       <c r="F103">
-        <v>3120</v>
+        <v>2702</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>10/03/2026</v>
+        <v>20/01/2026</v>
       </c>
       <c r="B104" t="str">
-        <v>Mar26</v>
+        <v>Jan26</v>
       </c>
       <c r="C104" t="str">
         <v>COGS</v>
       </c>
       <c r="D104" t="str">
-        <v>Orange</v>
+        <v>Watermelon</v>
       </c>
       <c r="E104" t="str">
-        <v>แก้วร้านน้ำส้ม 2ลัง ลังละ1560</v>
+        <v>แตงโม 40</v>
       </c>
       <c r="F104">
-        <v>5667</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>13/03/2026</v>
+        <v>21/01/2026</v>
       </c>
       <c r="B105" t="str">
-        <v>Mar26</v>
+        <v>Jan26</v>
       </c>
       <c r="C105" t="str">
         <v>COGS</v>
       </c>
       <c r="D105" t="str">
-        <v>Packaging</v>
+        <v>Transportation</v>
       </c>
       <c r="E105" t="str">
-        <v>หลอด 20 แพค</v>
+        <v>ค่าขนส่ง</v>
       </c>
       <c r="F105">
-        <v>765</v>
+        <v>675</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>14/03/2026</v>
+        <v>23/01/2026</v>
       </c>
       <c r="B106" t="str">
-        <v>Mar26</v>
+        <v>Jan26</v>
       </c>
       <c r="C106" t="str">
         <v>COGS</v>
       </c>
       <c r="D106" t="str">
-        <v>Apple/Melon</v>
+        <v>Orange</v>
       </c>
       <c r="E106" t="str">
-        <v>แอปเปิ้ลฟูจิ 32</v>
+        <v>ค่าส้ม20ตะกร้า</v>
       </c>
       <c r="F106">
-        <v>350</v>
+        <v>7120</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>14/03/2026</v>
+        <v>23/01/2026</v>
       </c>
       <c r="B107" t="str">
-        <v>Mar26</v>
+        <v>Jan26</v>
       </c>
       <c r="C107" t="str">
         <v>COGS</v>
       </c>
       <c r="D107" t="str">
-        <v>Mango</v>
+        <v>Transportation</v>
       </c>
       <c r="E107" t="str">
-        <v>มะม่วง 2 ลัง 44</v>
+        <v>Unknown</v>
       </c>
       <c r="F107">
-        <v>2420</v>
+        <v>400</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>15/03/2026</v>
+        <v>23/01/2026</v>
       </c>
       <c r="B108" t="str">
-        <v>Mar26</v>
+        <v>Jan26</v>
       </c>
       <c r="C108" t="str">
         <v>COGS</v>
       </c>
       <c r="D108" t="str">
-        <v>Ice</v>
+        <v>Transportation</v>
       </c>
       <c r="E108" t="str">
-        <v>ค่าทางด่วน</v>
+        <v>Unknown</v>
       </c>
       <c r="F108">
-        <v>115</v>
+        <v>400</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>15/03/2026</v>
+        <v>23/01/2026</v>
       </c>
       <c r="B109" t="str">
-        <v>Mar26</v>
+        <v>Jan26</v>
       </c>
       <c r="C109" t="str">
         <v>COGS</v>
@@ -3309,178 +3309,178 @@
         <v>Watermelon</v>
       </c>
       <c r="E109" t="str">
-        <v>น้ำมะพร้าว 5ขวดเละ 50฿</v>
+        <v>แตงโม 40 ลูก</v>
       </c>
       <c r="F109">
-        <v>4800</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>17/03/2026</v>
+        <v>25/01/2026</v>
       </c>
       <c r="B110" t="str">
-        <v>Mar26</v>
+        <v>Jan26</v>
       </c>
       <c r="C110" t="str">
         <v>COGS</v>
       </c>
       <c r="D110" t="str">
-        <v>Ice</v>
+        <v>Orange</v>
       </c>
       <c r="E110" t="str">
-        <v>ค่าไฟเดือนกพ มีนา</v>
+        <v>ส้ม5ตะกร้า แตงโม 40 ลูก</v>
       </c>
       <c r="F110">
-        <v>2779.47</v>
+        <v>5950</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>19/03/2026</v>
+        <v>25/01/2026</v>
       </c>
       <c r="B111" t="str">
-        <v>Mar26</v>
+        <v>Jan26</v>
       </c>
       <c r="C111" t="str">
         <v>COGS</v>
       </c>
       <c r="D111" t="str">
-        <v>Watermelon</v>
+        <v>Transportation</v>
       </c>
       <c r="E111" t="str">
-        <v>ค่าแตงโม 18/3/67 51 ลูก 4000 บาท</v>
+        <v>ค่าส่งฝา</v>
       </c>
       <c r="F111">
-        <v>4000</v>
+        <v>114</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>21/03/2026</v>
+        <v>26/01/2026</v>
       </c>
       <c r="B112" t="str">
-        <v>Mar26</v>
+        <v>Jan26</v>
       </c>
       <c r="C112" t="str">
         <v>COGS</v>
       </c>
       <c r="D112" t="str">
-        <v>Ice</v>
+        <v>Orange</v>
       </c>
       <c r="E112" t="str">
-        <v>สกรู กาวตะปู</v>
+        <v>ค่าส้ม 30 ตะกร้า</v>
       </c>
       <c r="F112">
-        <v>117</v>
+        <v>10680</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>23/03/2026</v>
+        <v>26/01/2026</v>
       </c>
       <c r="B113" t="str">
-        <v>Mar26</v>
+        <v>Jan26</v>
       </c>
       <c r="C113" t="str">
         <v>COGS</v>
       </c>
       <c r="D113" t="str">
-        <v>Mango</v>
+        <v>Transportation</v>
       </c>
       <c r="E113" t="str">
-        <v>มะม่วง 44 โล</v>
+        <v>Unknown</v>
       </c>
       <c r="F113">
-        <v>2200</v>
+        <v>400</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>23/03/2026</v>
+        <v>26/01/2026</v>
       </c>
       <c r="B114" t="str">
-        <v>Mar26</v>
+        <v>Jan26</v>
       </c>
       <c r="C114" t="str">
         <v>COGS</v>
       </c>
       <c r="D114" t="str">
-        <v>Orange</v>
+        <v>Transportation</v>
       </c>
       <c r="E114" t="str">
-        <v>22-3-2569</v>
+        <v>Unknown</v>
       </c>
       <c r="F114">
-        <v>5890</v>
+        <v>400</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>24/03/2026</v>
+        <v>27/01/2026</v>
       </c>
       <c r="B115" t="str">
-        <v>Mar26</v>
+        <v>Jan26</v>
       </c>
       <c r="C115" t="str">
         <v>COGS</v>
       </c>
       <c r="D115" t="str">
-        <v>Ice</v>
+        <v>Packaging</v>
       </c>
       <c r="E115" t="str">
-        <v>รถเข็นของคันใหม่</v>
+        <v>ถุงมือ - 5 กล่อง</v>
       </c>
       <c r="F115">
-        <v>1752</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>28/03/2026</v>
+        <v>28/01/2026</v>
       </c>
       <c r="B116" t="str">
-        <v>Mar26</v>
+        <v>Jan26</v>
       </c>
       <c r="C116" t="str">
         <v>COGS</v>
       </c>
       <c r="D116" t="str">
-        <v>Coconut</v>
+        <v>Transportation</v>
       </c>
       <c r="E116" t="str">
-        <v>น้ำมะพร้าว 10 ขวด</v>
+        <v>ค่าส่ง</v>
       </c>
       <c r="F116">
-        <v>500</v>
+        <v>486</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>28/03/2026</v>
+        <v>28/01/2026</v>
       </c>
       <c r="B117" t="str">
-        <v>Mar26</v>
+        <v>Jan26</v>
       </c>
       <c r="C117" t="str">
         <v>COGS</v>
       </c>
       <c r="D117" t="str">
-        <v>Mango</v>
+        <v>Transportation</v>
       </c>
       <c r="E117" t="str">
-        <v>มะม่วง 23 โล</v>
+        <v>Unknown</v>
       </c>
       <c r="F117">
-        <v>1035</v>
+        <v>400</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>28/03/2026</v>
+        <v>28/01/2026</v>
       </c>
       <c r="B118" t="str">
-        <v>Mar26</v>
+        <v>Jan26</v>
       </c>
       <c r="C118" t="str">
         <v>COGS</v>
@@ -3489,7 +3489,7 @@
         <v>Watermelon</v>
       </c>
       <c r="E118" t="str">
-        <v>แตงโม 50 26/3/69</v>
+        <v>ค่าแตงโม 50 ลูก</v>
       </c>
       <c r="F118">
         <v>4000</v>
@@ -3497,50 +3497,50 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>30/03/2026</v>
+        <v>28/01/2026</v>
       </c>
       <c r="B119" t="str">
-        <v>Mar26</v>
+        <v>Jan26</v>
       </c>
       <c r="C119" t="str">
         <v>COGS</v>
       </c>
       <c r="D119" t="str">
-        <v>Packaging</v>
+        <v>Transportation</v>
       </c>
       <c r="E119" t="str">
-        <v>นมข้นจืดสามลังหนึ่งลังมี 12 กล่อง 36 กล่อง</v>
+        <v>Unknown</v>
       </c>
       <c r="F119">
-        <v>1720</v>
+        <v>400</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>30/03/2026</v>
+        <v>28/01/2026</v>
       </c>
       <c r="B120" t="str">
-        <v>Mar26</v>
+        <v>Jan26</v>
       </c>
       <c r="C120" t="str">
         <v>COGS</v>
       </c>
       <c r="D120" t="str">
-        <v>Packaging</v>
+        <v>Transportation</v>
       </c>
       <c r="E120" t="str">
-        <v>นมข้นหวาน 3 ลัง 24 ถุง</v>
+        <v>ค่าส่ง</v>
       </c>
       <c r="F120">
-        <v>2016</v>
+        <v>486</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>30/03/2026</v>
+        <v>28/01/2026</v>
       </c>
       <c r="B121" t="str">
-        <v>Mar26</v>
+        <v>Jan26</v>
       </c>
       <c r="C121" t="str">
         <v>COGS</v>
@@ -3549,27 +3549,27 @@
         <v>Watermelon</v>
       </c>
       <c r="E121" t="str">
-        <v>แตงโม 30 ลูก 2400 เนื้อมะพร้าว 10 โล 1100</v>
+        <v>แตงโม 50 ลูก</v>
       </c>
       <c r="F121">
-        <v>3500</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>30/03/2026</v>
+        <v>30/01/2026</v>
       </c>
       <c r="B122" t="str">
-        <v>Mar26</v>
+        <v>Jan26</v>
       </c>
       <c r="C122" t="str">
         <v>COGS</v>
       </c>
       <c r="D122" t="str">
-        <v>Transportation</v>
+        <v>Watermelon</v>
       </c>
       <c r="E122" t="str">
-        <v>ค่าส่ง lalamove</v>
+        <v>แตงโม 25 ลูก</v>
       </c>
       <c r="F122">
         <v>2000</v>
@@ -3577,110 +3577,110 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>31/03/2026</v>
+        <v>30/01/2026</v>
       </c>
       <c r="B123" t="str">
-        <v>Mar26</v>
+        <v>Jan26</v>
       </c>
       <c r="C123" t="str">
         <v>COGS</v>
       </c>
       <c r="D123" t="str">
-        <v>Transportation</v>
+        <v>Apple/Melon</v>
       </c>
       <c r="E123" t="str">
-        <v>Unknown</v>
+        <v>แอปเปิ้ล เมล่อน</v>
       </c>
       <c r="F123">
-        <v>2000</v>
+        <v>851</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>01/04/2026</v>
+        <v>31/01/2026</v>
       </c>
       <c r="B124" t="str">
-        <v>Apr26</v>
+        <v>Jan26</v>
       </c>
       <c r="C124" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D124" t="str">
-        <v>Apple/Melon</v>
+        <v>Salary</v>
       </c>
       <c r="E124" t="str">
-        <v>แอปเปิ้ล 3 ลัง</v>
+        <v>เงินเดือนเมนมกราคม</v>
       </c>
       <c r="F124">
-        <v>1050</v>
+        <v>19000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>01/04/2026</v>
+        <v>02/02/2026</v>
       </c>
       <c r="B125" t="str">
-        <v>Apr26</v>
+        <v>Feb26</v>
       </c>
       <c r="C125" t="str">
         <v>COGS</v>
       </c>
       <c r="D125" t="str">
-        <v>Mango</v>
+        <v>Orange</v>
       </c>
       <c r="E125" t="str">
-        <v>มะม่วง 2 ลัง</v>
+        <v>ส้ม 30 ตะกร้า</v>
       </c>
       <c r="F125">
-        <v>1920</v>
+        <v>10680</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>01/04/2026</v>
+        <v>02/02/2026</v>
       </c>
       <c r="B126" t="str">
-        <v>Apr26</v>
+        <v>Feb26</v>
       </c>
       <c r="C126" t="str">
         <v>COGS</v>
       </c>
       <c r="D126" t="str">
-        <v>Water</v>
+        <v>Watermelon</v>
       </c>
       <c r="E126" t="str">
-        <v>น้ำ500</v>
+        <v>แตงโม 50 ลูก</v>
       </c>
       <c r="F126">
-        <v>1700</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>02/04/2026</v>
+        <v>02/02/2026</v>
       </c>
       <c r="B127" t="str">
-        <v>Mar26</v>
+        <v>Feb26</v>
       </c>
       <c r="C127" t="str">
         <v>COGS</v>
       </c>
       <c r="D127" t="str">
-        <v>Ice</v>
+        <v>Transportation</v>
       </c>
       <c r="E127" t="str">
         <v>Unknown</v>
       </c>
       <c r="F127">
-        <v>49560</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>04/04/2026</v>
+        <v>04/02/2026</v>
       </c>
       <c r="B128" t="str">
-        <v>Apr26</v>
+        <v>Feb26</v>
       </c>
       <c r="C128" t="str">
         <v>COGS</v>
@@ -3689,58 +3689,58 @@
         <v>Packaging</v>
       </c>
       <c r="E128" t="str">
-        <v>แก้ว3ลัง 1539 3 4617</v>
+        <v>ฝา 690 1000 ชิ้น แก้ว 1196 1000 ชิ้น หลอด 421</v>
       </c>
       <c r="F128">
-        <v>7066</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>04/04/2026</v>
+        <v>05/02/2026</v>
       </c>
       <c r="B129" t="str">
-        <v>Apr26</v>
+        <v>Feb26</v>
       </c>
       <c r="C129" t="str">
         <v>COGS</v>
       </c>
       <c r="D129" t="str">
-        <v>Packaging</v>
+        <v>Watermelon</v>
       </c>
       <c r="E129" t="str">
-        <v>แก้ว1ลัง 1539</v>
+        <v>แตงโม 50 ลูก</v>
       </c>
       <c r="F129">
-        <v>1560</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>04/04/2026</v>
+        <v>05/02/2026</v>
       </c>
       <c r="B130" t="str">
-        <v>Apr26</v>
+        <v>Feb26</v>
       </c>
       <c r="C130" t="str">
         <v>COGS</v>
       </c>
       <c r="D130" t="str">
-        <v>Coconut</v>
+        <v>Packaging</v>
       </c>
       <c r="E130" t="str">
-        <v>ค่ามะพร้าว 26 60ลูก 1560</v>
+        <v>แก้วสกรีน อย่างเดียวไม่รวมฝา 2280บาท</v>
       </c>
       <c r="F130">
-        <v>1980</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>04/04/2026</v>
+        <v>08/02/2026</v>
       </c>
       <c r="B131" t="str">
-        <v>Apr26</v>
+        <v>Feb26</v>
       </c>
       <c r="C131" t="str">
         <v>COGS</v>
@@ -3749,158 +3749,158 @@
         <v>Ice</v>
       </c>
       <c r="E131" t="str">
-        <v>เนื้อ 1200 น้ำ 500</v>
+        <v>Unknown</v>
       </c>
       <c r="F131">
-        <v>1700</v>
+        <v>798</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>04/04/2026</v>
+        <v>08/02/2026</v>
       </c>
       <c r="B132" t="str">
-        <v>Apr26</v>
+        <v>Feb26</v>
       </c>
       <c r="C132" t="str">
         <v>COGS</v>
       </c>
       <c r="D132" t="str">
-        <v>Mango</v>
+        <v>Watermelon</v>
       </c>
       <c r="E132" t="str">
-        <v>มะม่วง1ลัง</v>
+        <v>แตงโม 50</v>
       </c>
       <c r="F132">
-        <v>1000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>04/04/2026</v>
+        <v>08/02/2026</v>
       </c>
       <c r="B133" t="str">
-        <v>Apr26</v>
+        <v>Feb26</v>
       </c>
       <c r="C133" t="str">
         <v>COGS</v>
       </c>
       <c r="D133" t="str">
-        <v>Orange</v>
+        <v>Transportation</v>
       </c>
       <c r="E133" t="str">
-        <v>ส้ม 4/4/69 20 ตะกร้า 30 บาท 13200 ค่าขนส่ง</v>
+        <v>Unknown</v>
       </c>
       <c r="F133">
-        <v>14160</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>04/04/2026</v>
+        <v>09/02/2026</v>
       </c>
       <c r="B134" t="str">
-        <v>Apr26</v>
+        <v>Feb26</v>
       </c>
       <c r="C134" t="str">
         <v>COGS</v>
       </c>
       <c r="D134" t="str">
-        <v>Ice</v>
+        <v>Orange</v>
       </c>
       <c r="E134" t="str">
-        <v>4/4/68 40 ลูก</v>
+        <v>ส้ม 30 ตะกร้า</v>
       </c>
       <c r="F134">
-        <v>3200</v>
+        <v>10680</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>04/04/2026</v>
+        <v>09/02/2026</v>
       </c>
       <c r="B135" t="str">
-        <v>Apr26</v>
+        <v>Feb26</v>
       </c>
       <c r="C135" t="str">
         <v>COGS</v>
       </c>
       <c r="D135" t="str">
-        <v>Watermelon</v>
+        <v>Orange</v>
       </c>
       <c r="E135" t="str">
-        <v>แตงโม 1/4/69 30 ลูก</v>
+        <v>ค่าส่งส้ม</v>
       </c>
       <c r="F135">
-        <v>2400</v>
+        <v>685</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>07/04/2026</v>
+        <v>10/02/2026</v>
       </c>
       <c r="B136" t="str">
-        <v>Apr26</v>
+        <v>Feb26</v>
       </c>
       <c r="C136" t="str">
         <v>COGS</v>
       </c>
       <c r="D136" t="str">
-        <v>Apple/Melon</v>
+        <v>Ice</v>
       </c>
       <c r="E136" t="str">
-        <v>แอปเปิ้ล 3 ลัง</v>
+        <v>ค่าไฟเดือนมค</v>
       </c>
       <c r="F136">
-        <v>1050</v>
+        <v>389</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>07/04/2026</v>
+        <v>11/02/2026</v>
       </c>
       <c r="B137" t="str">
-        <v>Apr26</v>
+        <v>Feb26</v>
       </c>
       <c r="C137" t="str">
         <v>COGS</v>
       </c>
       <c r="D137" t="str">
-        <v>Coconut</v>
+        <v>Watermelon</v>
       </c>
       <c r="E137" t="str">
-        <v>เนื้อมะพร้าว 10 - 1200 บาท น้ำมะพร้าว 10</v>
+        <v>แตงโม 50 ลูก</v>
       </c>
       <c r="F137">
-        <v>1700</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>07/04/2026</v>
+        <v>14/02/2026</v>
       </c>
       <c r="B138" t="str">
-        <v>Apr26</v>
+        <v>Feb26</v>
       </c>
       <c r="C138" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D138" t="str">
-        <v>Watermelon</v>
+        <v>Other</v>
       </c>
       <c r="E138" t="str">
-        <v>ค่าแตงโมวันที่ 4- 40 ลูก 3200 บาท วันที่ 7-40 ลูก</v>
+        <v>Unknown</v>
       </c>
       <c r="F138">
-        <v>6400</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>10/04/2026</v>
+        <v>14/02/2026</v>
       </c>
       <c r="B139" t="str">
-        <v>Apr26</v>
+        <v>Feb26</v>
       </c>
       <c r="C139" t="str">
         <v>COGS</v>
@@ -3909,158 +3909,158 @@
         <v>Ice</v>
       </c>
       <c r="E139" t="str">
-        <v>ค่านม</v>
+        <v>Unknown</v>
       </c>
       <c r="F139">
-        <v>180</v>
+        <v>350</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>11/04/2026</v>
+        <v>16/02/2026</v>
       </c>
       <c r="B140" t="str">
-        <v>Apr26</v>
+        <v>Feb26</v>
       </c>
       <c r="C140" t="str">
         <v>COGS</v>
       </c>
       <c r="D140" t="str">
-        <v>Transportation</v>
+        <v>Orange</v>
       </c>
       <c r="E140" t="str">
-        <v>ค่ารถ lalamove</v>
+        <v>ค่าส่งส้ม</v>
       </c>
       <c r="F140">
-        <v>2000</v>
+        <v>485</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>11/04/2026</v>
+        <v>16/02/2026</v>
       </c>
       <c r="B141" t="str">
-        <v>Apr26</v>
+        <v>Feb26</v>
       </c>
       <c r="C141" t="str">
         <v>COGS</v>
       </c>
       <c r="D141" t="str">
-        <v>Apple/Melon</v>
+        <v>Orange</v>
       </c>
       <c r="E141" t="str">
-        <v>แอปเปิ้ล 3 ลัง</v>
+        <v>ค่าส้ม 30 ตะกร้า 13/2/69</v>
       </c>
       <c r="F141">
-        <v>1050</v>
+        <v>10680</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>11/04/2026</v>
+        <v>19/02/2026</v>
       </c>
       <c r="B142" t="str">
-        <v>Apr26</v>
+        <v>Feb26</v>
       </c>
       <c r="C142" t="str">
         <v>COGS</v>
       </c>
       <c r="D142" t="str">
-        <v>Ice</v>
+        <v>Watermelon</v>
       </c>
       <c r="E142" t="str">
-        <v>น้ำ 500 เนื้อ 1200</v>
+        <v>แตงโม 50 ลูก วันที่ 1719</v>
       </c>
       <c r="F142">
-        <v>1700</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>11/04/2026</v>
+        <v>19/02/2026</v>
       </c>
       <c r="B143" t="str">
-        <v>Apr26</v>
+        <v>Feb26</v>
       </c>
       <c r="C143" t="str">
         <v>COGS</v>
       </c>
       <c r="D143" t="str">
-        <v>Mango</v>
+        <v>Packaging</v>
       </c>
       <c r="E143" t="str">
-        <v>มะม่วง 1 ลัง 23 โล</v>
+        <v>แก้ว</v>
       </c>
       <c r="F143">
-        <v>690</v>
+        <v>3315</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>13/04/2026</v>
+        <v>19/02/2026</v>
       </c>
       <c r="B144" t="str">
-        <v>Apr26</v>
+        <v>Feb26</v>
       </c>
       <c r="C144" t="str">
         <v>COGS</v>
       </c>
       <c r="D144" t="str">
-        <v>Coconut</v>
+        <v>Transportation</v>
       </c>
       <c r="E144" t="str">
-        <v>Unknown</v>
+        <v>แก้วสกรีน2ลัง(รอบที่1นะ แบ่งสั่งจะได้ไม่มีค่า</v>
       </c>
       <c r="F144">
-        <v>300</v>
+        <v>6655</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>13/04/2026</v>
+        <v>19/02/2026</v>
       </c>
       <c r="B145" t="str">
-        <v>Apr26</v>
+        <v>Feb26</v>
       </c>
       <c r="C145" t="str">
         <v>COGS</v>
       </c>
       <c r="D145" t="str">
-        <v>Coconut</v>
+        <v>Transportation</v>
       </c>
       <c r="E145" t="str">
-        <v>เนื้อมะพร้าว 1200 น้ำมะพร้าว 500</v>
+        <v>Unknown</v>
       </c>
       <c r="F145">
-        <v>1400</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>13/04/2026</v>
+        <v>20/02/2026</v>
       </c>
       <c r="B146" t="str">
-        <v>Apr26</v>
+        <v>Feb26</v>
       </c>
       <c r="C146" t="str">
         <v>COGS</v>
       </c>
       <c r="D146" t="str">
-        <v>Mango</v>
+        <v>Ice</v>
       </c>
       <c r="E146" t="str">
-        <v>Unknown</v>
+        <v>ผ้าปิดร้าน 218 ค่ารถ 198</v>
       </c>
       <c r="F146">
-        <v>750</v>
+        <v>416</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>13/04/2026</v>
+        <v>23/02/2026</v>
       </c>
       <c r="B147" t="str">
-        <v>Apr26</v>
+        <v>Feb26</v>
       </c>
       <c r="C147" t="str">
         <v>COGS</v>
@@ -4069,98 +4069,98 @@
         <v>Watermelon</v>
       </c>
       <c r="E147" t="str">
-        <v>Unknown</v>
+        <v>แตงโม 21 50 ลูก 23 50 ลูก</v>
       </c>
       <c r="F147">
-        <v>3200</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>18/04/2026</v>
+        <v>24/02/2026</v>
       </c>
       <c r="B148" t="str">
-        <v>Apr26</v>
+        <v>Feb26</v>
       </c>
       <c r="C148" t="str">
         <v>COGS</v>
       </c>
       <c r="D148" t="str">
-        <v>Apple/Melon</v>
+        <v>Transportation</v>
       </c>
       <c r="E148" t="str">
-        <v>แอปเปิ้ล 3 ลัง</v>
+        <v>Unknown</v>
       </c>
       <c r="F148">
-        <v>1050</v>
+        <v>209</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>18/04/2026</v>
+        <v>24/02/2026</v>
       </c>
       <c r="B149" t="str">
-        <v>Apr26</v>
+        <v>Feb26</v>
       </c>
       <c r="C149" t="str">
         <v>COGS</v>
       </c>
       <c r="D149" t="str">
-        <v>Mango</v>
+        <v>Orange</v>
       </c>
       <c r="E149" t="str">
-        <v>16/04/26 มะม่วง 1 ลัง</v>
+        <v>ส้ม 30 18/2/69</v>
       </c>
       <c r="F149">
-        <v>750</v>
+        <v>10680</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>18/04/2026</v>
+        <v>24/02/2026</v>
       </c>
       <c r="B150" t="str">
-        <v>Apr26</v>
+        <v>Feb26</v>
       </c>
       <c r="C150" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D150" t="str">
-        <v>Other</v>
+        <v>Packaging</v>
       </c>
       <c r="E150" t="str">
-        <v>16/4/2569</v>
+        <v>แก้ว 2400 ฝา 1670</v>
       </c>
       <c r="F150">
-        <v>4000</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>20/04/2026</v>
+        <v>25/02/2026</v>
       </c>
       <c r="B151" t="str">
-        <v>Apr26</v>
+        <v>Feb26</v>
       </c>
       <c r="C151" t="str">
         <v>COGS</v>
       </c>
       <c r="D151" t="str">
-        <v>Orange</v>
+        <v>Watermelon</v>
       </c>
       <c r="E151" t="str">
-        <v>ส้ม 40 ตะกร้า ตะกร้าละ 22 โล โลละ 30 บาท</v>
+        <v>แตงโม 50</v>
       </c>
       <c r="F151">
-        <v>28600</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>20/04/2026</v>
+        <v>25/02/2026</v>
       </c>
       <c r="B152" t="str">
-        <v>Apr26</v>
+        <v>Feb26</v>
       </c>
       <c r="C152" t="str">
         <v>COGS</v>
@@ -4169,298 +4169,298 @@
         <v>Transportation</v>
       </c>
       <c r="E152" t="str">
-        <v>ค่าส่งป้ายเมนูร้านใหม่</v>
+        <v>Unknown</v>
       </c>
       <c r="F152">
-        <v>335</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>20/04/2026</v>
+        <v>25/02/2026</v>
       </c>
       <c r="B153" t="str">
-        <v>Apr26</v>
+        <v>Feb26</v>
       </c>
       <c r="C153" t="str">
         <v>COGS</v>
       </c>
       <c r="D153" t="str">
-        <v>Packaging</v>
+        <v>Orange</v>
       </c>
       <c r="E153" t="str">
-        <v>ขวดใหญ่ 98 อัน</v>
+        <v>ส้ม20 ตะกร้า</v>
       </c>
       <c r="F153">
-        <v>338</v>
+        <v>7312</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>20/04/2026</v>
+        <v>25/02/2026</v>
       </c>
       <c r="B154" t="str">
-        <v>Apr26</v>
+        <v>Feb26</v>
       </c>
       <c r="C154" t="str">
         <v>COGS</v>
       </c>
       <c r="D154" t="str">
-        <v>Packaging</v>
+        <v>Orange</v>
       </c>
       <c r="E154" t="str">
-        <v>ถุงขยะ 10 แพค</v>
+        <v>ค่าส่งส้ม</v>
       </c>
       <c r="F154">
-        <v>520</v>
+        <v>806</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>20/04/2026</v>
+        <v>26/02/2026</v>
       </c>
       <c r="B155" t="str">
-        <v>Apr26</v>
+        <v>Feb26</v>
       </c>
       <c r="C155" t="str">
         <v>COGS</v>
       </c>
       <c r="D155" t="str">
-        <v>Watermelon</v>
+        <v>Packaging</v>
       </c>
       <c r="E155" t="str">
-        <v>18/4/26 แตงโม 30 ลูก</v>
+        <v>ค่าขวดใหญ่</v>
       </c>
       <c r="F155">
-        <v>2400</v>
+        <v>319</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>20/04/2026</v>
+        <v>28/02/2026</v>
       </c>
       <c r="B156" t="str">
-        <v>Apr26</v>
+        <v>Feb26</v>
       </c>
       <c r="C156" t="str">
         <v>COGS</v>
       </c>
       <c r="D156" t="str">
-        <v>Mango</v>
+        <v>Orange</v>
       </c>
       <c r="E156" t="str">
-        <v>18/4/26 มะม่วง 25 โล 750</v>
+        <v>ค่าส่งส้ม</v>
       </c>
       <c r="F156">
-        <v>750</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>21/04/2026</v>
+        <v>28/02/2026</v>
       </c>
       <c r="B157" t="str">
-        <v>Apr26</v>
+        <v>Feb26</v>
       </c>
       <c r="C157" t="str">
         <v>COGS</v>
       </c>
       <c r="D157" t="str">
-        <v>Watermelon</v>
+        <v>Orange</v>
       </c>
       <c r="E157" t="str">
-        <v>21/4/26 แตงโม60 ลูก</v>
+        <v>ค่าส่งส้ม</v>
       </c>
       <c r="F157">
-        <v>4800</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>21/04/2026</v>
+        <v>28/02/2026</v>
       </c>
       <c r="B158" t="str">
-        <v>Apr26</v>
+        <v>Feb26</v>
       </c>
       <c r="C158" t="str">
         <v>COGS</v>
       </c>
       <c r="D158" t="str">
-        <v>Transportation</v>
+        <v>Ice</v>
       </c>
       <c r="E158" t="str">
-        <v>Lalamove</v>
+        <v>ค่าเช่าสต็อคกพ</v>
       </c>
       <c r="F158">
-        <v>2000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>21/04/2026</v>
+        <v>28/02/2026</v>
       </c>
       <c r="B159" t="str">
-        <v>Apr26</v>
+        <v>Feb26</v>
       </c>
       <c r="C159" t="str">
         <v>COGS</v>
       </c>
       <c r="D159" t="str">
-        <v>Apple/Melon</v>
+        <v>Watermelon</v>
       </c>
       <c r="E159" t="str">
-        <v>แอปเปิ้ล 4 ลัง</v>
+        <v>แตงโม 50 ลูก</v>
       </c>
       <c r="F159">
-        <v>1400</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>23/04/2026</v>
+        <v>04/03/2026</v>
       </c>
       <c r="B160" t="str">
-        <v>Apr26</v>
+        <v>Mar26</v>
       </c>
       <c r="C160" t="str">
         <v>COGS</v>
       </c>
       <c r="D160" t="str">
-        <v>Mango</v>
+        <v>Watermelon</v>
       </c>
       <c r="E160" t="str">
-        <v>มะม่วง 2 ลัง</v>
+        <v>ค่าทางด่วนส่งแตงโม</v>
       </c>
       <c r="F160">
-        <v>1560</v>
+        <v>140</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>23/04/2026</v>
+        <v>04/03/2026</v>
       </c>
       <c r="B161" t="str">
-        <v>Apr26</v>
+        <v>Mar26</v>
       </c>
       <c r="C161" t="str">
         <v>COGS</v>
       </c>
       <c r="D161" t="str">
-        <v>Apple/Melon</v>
+        <v>Mango</v>
       </c>
       <c r="E161" t="str">
-        <v>แอปเปิ้ล 4 ลัง</v>
+        <v>มะม่วง 16 โล</v>
       </c>
       <c r="F161">
-        <v>1400</v>
+        <v>560</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>23/04/2026</v>
+        <v>05/03/2026</v>
       </c>
       <c r="B162" t="str">
-        <v>Apr26</v>
+        <v>Feb26</v>
       </c>
       <c r="C162" t="str">
         <v>COGS</v>
       </c>
       <c r="D162" t="str">
-        <v>Ice</v>
+        <v>Mango</v>
       </c>
       <c r="E162" t="str">
-        <v>16/4/26 เนื้อ 10 น้ำ 10 21/4/26 เนื้อ 10</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F162">
-        <v>2900</v>
+        <v>500</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>23/04/2026</v>
+        <v>05/03/2026</v>
       </c>
       <c r="B163" t="str">
-        <v>Apr26</v>
+        <v>Feb26</v>
       </c>
       <c r="C163" t="str">
         <v>COGS</v>
       </c>
       <c r="D163" t="str">
-        <v>Mango</v>
+        <v>Orange</v>
       </c>
       <c r="E163" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>ค่าส้มวันที่ 27269</v>
       </c>
       <c r="F163">
-        <v>780</v>
+        <v>7312</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>24/04/2026</v>
+        <v>05/03/2026</v>
       </c>
       <c r="B164" t="str">
-        <v>Apr26</v>
+        <v>Mar26</v>
       </c>
       <c r="C164" t="str">
         <v>COGS</v>
       </c>
       <c r="D164" t="str">
-        <v>Packaging</v>
+        <v>Orange</v>
       </c>
       <c r="E164" t="str">
-        <v>บาร์เลย 4 ถั่วแดง 3 ถุงละ 60</v>
+        <v>แตงโม 51 ยอด3,500</v>
       </c>
       <c r="F164">
-        <v>420</v>
+        <v>7700</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>24/04/2026</v>
+        <v>05/03/2026</v>
       </c>
       <c r="B165" t="str">
-        <v>Apr26</v>
+        <v>Mar26</v>
       </c>
       <c r="C165" t="str">
         <v>COGS</v>
       </c>
       <c r="D165" t="str">
-        <v>Watermelon</v>
+        <v>Orange</v>
       </c>
       <c r="E165" t="str">
-        <v>แตงโม 50 ลูก</v>
+        <v>ค่าส้ม 20 ตะกร้า</v>
       </c>
       <c r="F165">
-        <v>4000</v>
+        <v>7312</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>25/04/2026</v>
+        <v>05/03/2026</v>
       </c>
       <c r="B166" t="str">
-        <v>Apr26</v>
+        <v>Mar26</v>
       </c>
       <c r="C166" t="str">
         <v>COGS</v>
       </c>
       <c r="D166" t="str">
-        <v>Orange</v>
+        <v>Ice</v>
       </c>
       <c r="E166" t="str">
-        <v>22/04/69</v>
+        <v>ค่าทางด่วน</v>
       </c>
       <c r="F166">
-        <v>14400</v>
+        <v>105</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>26/04/2026</v>
+        <v>05/03/2026</v>
       </c>
       <c r="B167" t="str">
-        <v>Apr26</v>
+        <v>Mar26</v>
       </c>
       <c r="C167" t="str">
         <v>COGS</v>
@@ -4469,238 +4469,238 @@
         <v>Packaging</v>
       </c>
       <c r="E167" t="str">
-        <v>แก้ว 1 ลัง</v>
+        <v>ถุงขยะ</v>
       </c>
       <c r="F167">
-        <v>1539</v>
+        <v>909</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>26/04/2026</v>
+        <v>05/03/2026</v>
       </c>
       <c r="B168" t="str">
-        <v>Apr26</v>
+        <v>Mar26</v>
       </c>
       <c r="C168" t="str">
         <v>COGS</v>
       </c>
       <c r="D168" t="str">
-        <v>Packaging</v>
+        <v>Mango</v>
       </c>
       <c r="E168" t="str">
-        <v>แก้ว3ลัง</v>
+        <v>มะม่วง 24 โล</v>
       </c>
       <c r="F168">
-        <v>7090</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>26/04/2026</v>
+        <v>07/03/2026</v>
       </c>
       <c r="B169" t="str">
-        <v>Apr26</v>
+        <v>Mar26</v>
       </c>
       <c r="C169" t="str">
         <v>COGS</v>
       </c>
       <c r="D169" t="str">
-        <v>Mango</v>
+        <v>Transportation</v>
       </c>
       <c r="E169" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>Unknown</v>
       </c>
       <c r="F169">
-        <v>780</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>26/04/2026</v>
+        <v>10/03/2026</v>
       </c>
       <c r="B170" t="str">
-        <v>Apr26</v>
+        <v>Mar26</v>
       </c>
       <c r="C170" t="str">
         <v>COGS</v>
       </c>
       <c r="D170" t="str">
-        <v>Apple/Melon</v>
+        <v>Orange</v>
       </c>
       <c r="E170" t="str">
-        <v>แอปเปิ้ล 4</v>
+        <v>09/03/69</v>
       </c>
       <c r="F170">
-        <v>1400</v>
+        <v>9804</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>27/04/2026</v>
+        <v>10/03/2026</v>
       </c>
       <c r="B171" t="str">
-        <v>Apr26</v>
+        <v>Mar26</v>
       </c>
       <c r="C171" t="str">
         <v>COGS</v>
       </c>
       <c r="D171" t="str">
-        <v>Ice</v>
+        <v>Watermelon</v>
       </c>
       <c r="E171" t="str">
-        <v>26/4/26 50 ลูก</v>
+        <v>แตงโม 50 วันที่ 7 แตงโม 50 วันที่ 10</v>
       </c>
       <c r="F171">
-        <v>4000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>28/04/2026</v>
+        <v>10/03/2026</v>
       </c>
       <c r="B172" t="str">
-        <v>Apr26</v>
+        <v>Mar26</v>
       </c>
       <c r="C172" t="str">
-        <v>COGS</v>
+        <v>CAPEX</v>
       </c>
       <c r="D172" t="str">
-        <v>Packaging</v>
+        <v>Investment</v>
       </c>
       <c r="E172" t="str">
-        <v>หลอด 704(20ห่อ)</v>
+        <v>Unknown</v>
       </c>
       <c r="F172">
-        <v>2110</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>28/04/2026</v>
+        <v>10/03/2026</v>
       </c>
       <c r="B173" t="str">
-        <v>Apr26</v>
+        <v>Mar26</v>
       </c>
       <c r="C173" t="str">
         <v>COGS</v>
       </c>
       <c r="D173" t="str">
-        <v>Orange</v>
+        <v>Packaging</v>
       </c>
       <c r="E173" t="str">
-        <v>รอบ 27/04/69</v>
+        <v>แก้ว2ลัง ลังละ 1560</v>
       </c>
       <c r="F173">
-        <v>21600</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>28/04/2026</v>
+        <v>10/03/2026</v>
       </c>
       <c r="B174" t="str">
-        <v>Apr26</v>
+        <v>Mar26</v>
       </c>
       <c r="C174" t="str">
         <v>COGS</v>
       </c>
       <c r="D174" t="str">
-        <v>Coconut</v>
+        <v>Orange</v>
       </c>
       <c r="E174" t="str">
-        <v>ค่าส่งมะพร้าว</v>
+        <v>แก้วร้านน้ำส้ม 2ลัง ลังละ1560</v>
       </c>
       <c r="F174">
-        <v>100</v>
+        <v>5667</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>28/04/2026</v>
+        <v>13/03/2026</v>
       </c>
       <c r="B175" t="str">
-        <v>Apr26</v>
+        <v>Mar26</v>
       </c>
       <c r="C175" t="str">
         <v>COGS</v>
       </c>
       <c r="D175" t="str">
-        <v>Apple/Melon</v>
+        <v>Packaging</v>
       </c>
       <c r="E175" t="str">
-        <v>แอปเปิ้ล 4 ลัง</v>
+        <v>หลอด 20 แพค</v>
       </c>
       <c r="F175">
-        <v>1400</v>
+        <v>765</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>28/04/2026</v>
+        <v>14/03/2026</v>
       </c>
       <c r="B176" t="str">
-        <v>Apr26</v>
+        <v>Mar26</v>
       </c>
       <c r="C176" t="str">
         <v>COGS</v>
       </c>
       <c r="D176" t="str">
-        <v>Mango</v>
+        <v>Apple/Melon</v>
       </c>
       <c r="E176" t="str">
-        <v>มะม่วง 2 ลัง</v>
+        <v>แอปเปิ้ลฟูจิ 32</v>
       </c>
       <c r="F176">
-        <v>1560</v>
+        <v>350</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>29/04/2026</v>
+        <v>14/03/2026</v>
       </c>
       <c r="B177" t="str">
-        <v>Apr26</v>
+        <v>Mar26</v>
       </c>
       <c r="C177" t="str">
         <v>COGS</v>
       </c>
       <c r="D177" t="str">
-        <v>Milk/Conden</v>
+        <v>Mango</v>
       </c>
       <c r="E177" t="str">
-        <v>นมข้นหวาน1ลัง 836</v>
+        <v>มะม่วง 2 ลัง 44</v>
       </c>
       <c r="F177">
-        <v>2160</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>29/04/2026</v>
+        <v>15/03/2026</v>
       </c>
       <c r="B178" t="str">
-        <v>Apr26</v>
+        <v>Mar26</v>
       </c>
       <c r="C178" t="str">
         <v>COGS</v>
       </c>
       <c r="D178" t="str">
-        <v>Packaging</v>
+        <v>Ice</v>
       </c>
       <c r="E178" t="str">
-        <v>นมข้นหวาน2ลัง 1602</v>
+        <v>ค่าทางด่วน</v>
       </c>
       <c r="F178">
-        <v>3210</v>
+        <v>115</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>29/04/2026</v>
+        <v>15/03/2026</v>
       </c>
       <c r="B179" t="str">
-        <v>Apr26</v>
+        <v>Mar26</v>
       </c>
       <c r="C179" t="str">
         <v>COGS</v>
@@ -4709,155 +4709,1575 @@
         <v>Watermelon</v>
       </c>
       <c r="E179" t="str">
-        <v>แตงโม 60 ลูก</v>
+        <v>น้ำมะพร้าว 5ขวดเละ 50฿</v>
       </c>
       <c r="F179">
-        <v>4200</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>29/04/2026</v>
+        <v>17/03/2026</v>
       </c>
       <c r="B180" t="str">
-        <v>Apr26</v>
+        <v>Mar26</v>
       </c>
       <c r="C180" t="str">
         <v>COGS</v>
       </c>
       <c r="D180" t="str">
-        <v>Transportation</v>
+        <v>Ice</v>
       </c>
       <c r="E180" t="str">
-        <v>เนื้อ 10 x 50 500</v>
+        <v>ค่าไฟเดือนกพ มีนา</v>
       </c>
       <c r="F180">
-        <v>2395</v>
+        <v>2779.47</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>30/04/2026</v>
+        <v>19/03/2026</v>
       </c>
       <c r="B181" t="str">
-        <v>Apr26</v>
+        <v>Mar26</v>
       </c>
       <c r="C181" t="str">
         <v>COGS</v>
       </c>
       <c r="D181" t="str">
-        <v>Ice</v>
+        <v>Watermelon</v>
       </c>
       <c r="E181" t="str">
-        <v>สับปะรส 3 ตะกร้า</v>
+        <v>ค่าแตงโม 18/3/67 51 ลูก 4000 บาท</v>
       </c>
       <c r="F181">
-        <v>1500</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>30/04/2026</v>
+        <v>21/03/2026</v>
       </c>
       <c r="B182" t="str">
-        <v>Apr26</v>
+        <v>Mar26</v>
       </c>
       <c r="C182" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D182" t="str">
-        <v>Salary</v>
+        <v>Ice</v>
       </c>
       <c r="E182" t="str">
-        <v>Employee 1</v>
+        <v>สกรู กาวตะปู</v>
       </c>
       <c r="F182">
-        <v>19000</v>
+        <v>117</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>30/04/2026</v>
+        <v>23/03/2026</v>
       </c>
       <c r="B183" t="str">
-        <v>Apr26</v>
+        <v>Mar26</v>
       </c>
       <c r="C183" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D183" t="str">
-        <v>Salary</v>
+        <v>Mango</v>
       </c>
       <c r="E183" t="str">
-        <v>Employee 2</v>
+        <v>มะม่วง 44 โล</v>
       </c>
       <c r="F183">
-        <v>12000</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>30/04/2026</v>
+        <v>23/03/2026</v>
       </c>
       <c r="B184" t="str">
-        <v>Apr26</v>
+        <v>Mar26</v>
       </c>
       <c r="C184" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D184" t="str">
-        <v>Fixed Costs</v>
+        <v>Orange</v>
       </c>
       <c r="E184" t="str">
-        <v>Rent</v>
+        <v>22-3-2569</v>
       </c>
       <c r="F184">
-        <v>35000</v>
+        <v>5890</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>30/04/2026</v>
+        <v>24/03/2026</v>
       </c>
       <c r="B185" t="str">
-        <v>Apr26</v>
+        <v>Mar26</v>
       </c>
       <c r="C185" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D185" t="str">
-        <v>Investment</v>
+        <v>Ice</v>
       </c>
       <c r="E185" t="str">
-        <v>Stock (Allocated 82.9%)</v>
+        <v>รถเข็นของคันใหม่</v>
       </c>
       <c r="F185">
-        <v>9948</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
+        <v>28/03/2026</v>
+      </c>
+      <c r="B186" t="str">
+        <v>Mar26</v>
+      </c>
+      <c r="C186" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D186" t="str">
+        <v>Coconut</v>
+      </c>
+      <c r="E186" t="str">
+        <v>น้ำมะพร้าว 10 ขวด</v>
+      </c>
+      <c r="F186">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>28/03/2026</v>
+      </c>
+      <c r="B187" t="str">
+        <v>Mar26</v>
+      </c>
+      <c r="C187" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D187" t="str">
+        <v>Mango</v>
+      </c>
+      <c r="E187" t="str">
+        <v>มะม่วง 23 โล</v>
+      </c>
+      <c r="F187">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>28/03/2026</v>
+      </c>
+      <c r="B188" t="str">
+        <v>Mar26</v>
+      </c>
+      <c r="C188" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D188" t="str">
+        <v>Watermelon</v>
+      </c>
+      <c r="E188" t="str">
+        <v>แตงโม 50 26/3/69</v>
+      </c>
+      <c r="F188">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>30/03/2026</v>
+      </c>
+      <c r="B189" t="str">
+        <v>Mar26</v>
+      </c>
+      <c r="C189" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D189" t="str">
+        <v>Packaging</v>
+      </c>
+      <c r="E189" t="str">
+        <v>นมข้นจืดสามลังหนึ่งลังมี 12 กล่อง 36 กล่อง</v>
+      </c>
+      <c r="F189">
+        <v>1720</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>30/03/2026</v>
+      </c>
+      <c r="B190" t="str">
+        <v>Mar26</v>
+      </c>
+      <c r="C190" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D190" t="str">
+        <v>Packaging</v>
+      </c>
+      <c r="E190" t="str">
+        <v>นมข้นหวาน 3 ลัง 24 ถุง</v>
+      </c>
+      <c r="F190">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>30/03/2026</v>
+      </c>
+      <c r="B191" t="str">
+        <v>Mar26</v>
+      </c>
+      <c r="C191" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D191" t="str">
+        <v>Watermelon</v>
+      </c>
+      <c r="E191" t="str">
+        <v>แตงโม 30 ลูก 2400 เนื้อมะพร้าว 10 โล 1100</v>
+      </c>
+      <c r="F191">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>30/03/2026</v>
+      </c>
+      <c r="B192" t="str">
+        <v>Mar26</v>
+      </c>
+      <c r="C192" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D192" t="str">
+        <v>Transportation</v>
+      </c>
+      <c r="E192" t="str">
+        <v>ค่าส่ง lalamove</v>
+      </c>
+      <c r="F192">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>31/03/2026</v>
+      </c>
+      <c r="B193" t="str">
+        <v>Mar26</v>
+      </c>
+      <c r="C193" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D193" t="str">
+        <v>Transportation</v>
+      </c>
+      <c r="E193" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="F193">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>01/04/2026</v>
+      </c>
+      <c r="B194" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C194" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D194" t="str">
+        <v>Apple/Melon</v>
+      </c>
+      <c r="E194" t="str">
+        <v>แอปเปิ้ล 3 ลัง</v>
+      </c>
+      <c r="F194">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>01/04/2026</v>
+      </c>
+      <c r="B195" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C195" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D195" t="str">
+        <v>Mango</v>
+      </c>
+      <c r="E195" t="str">
+        <v>มะม่วง 2 ลัง</v>
+      </c>
+      <c r="F195">
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>01/04/2026</v>
+      </c>
+      <c r="B196" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C196" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D196" t="str">
+        <v>Water</v>
+      </c>
+      <c r="E196" t="str">
+        <v>น้ำ500</v>
+      </c>
+      <c r="F196">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>02/04/2026</v>
+      </c>
+      <c r="B197" t="str">
+        <v>Mar26</v>
+      </c>
+      <c r="C197" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D197" t="str">
+        <v>Ice</v>
+      </c>
+      <c r="E197" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="F197">
+        <v>49560</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>04/04/2026</v>
+      </c>
+      <c r="B198" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C198" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D198" t="str">
+        <v>Packaging</v>
+      </c>
+      <c r="E198" t="str">
+        <v>แก้ว3ลัง 1539 3 4617</v>
+      </c>
+      <c r="F198">
+        <v>7066</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>04/04/2026</v>
+      </c>
+      <c r="B199" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C199" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D199" t="str">
+        <v>Packaging</v>
+      </c>
+      <c r="E199" t="str">
+        <v>แก้ว1ลัง 1539</v>
+      </c>
+      <c r="F199">
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>04/04/2026</v>
+      </c>
+      <c r="B200" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C200" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D200" t="str">
+        <v>Coconut</v>
+      </c>
+      <c r="E200" t="str">
+        <v>ค่ามะพร้าว 26 60ลูก 1560</v>
+      </c>
+      <c r="F200">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>04/04/2026</v>
+      </c>
+      <c r="B201" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C201" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D201" t="str">
+        <v>Ice</v>
+      </c>
+      <c r="E201" t="str">
+        <v>เนื้อ 1200 น้ำ 500</v>
+      </c>
+      <c r="F201">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>04/04/2026</v>
+      </c>
+      <c r="B202" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C202" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D202" t="str">
+        <v>Mango</v>
+      </c>
+      <c r="E202" t="str">
+        <v>มะม่วง1ลัง</v>
+      </c>
+      <c r="F202">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>04/04/2026</v>
+      </c>
+      <c r="B203" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C203" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D203" t="str">
+        <v>Orange</v>
+      </c>
+      <c r="E203" t="str">
+        <v>ส้ม 4/4/69 20 ตะกร้า 30 บาท 13200 ค่าขนส่ง</v>
+      </c>
+      <c r="F203">
+        <v>14160</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>04/04/2026</v>
+      </c>
+      <c r="B204" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C204" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D204" t="str">
+        <v>Ice</v>
+      </c>
+      <c r="E204" t="str">
+        <v>4/4/68 40 ลูก</v>
+      </c>
+      <c r="F204">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>04/04/2026</v>
+      </c>
+      <c r="B205" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C205" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D205" t="str">
+        <v>Watermelon</v>
+      </c>
+      <c r="E205" t="str">
+        <v>แตงโม 1/4/69 30 ลูก</v>
+      </c>
+      <c r="F205">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>07/04/2026</v>
+      </c>
+      <c r="B206" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C206" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D206" t="str">
+        <v>Apple/Melon</v>
+      </c>
+      <c r="E206" t="str">
+        <v>แอปเปิ้ล 3 ลัง</v>
+      </c>
+      <c r="F206">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>07/04/2026</v>
+      </c>
+      <c r="B207" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C207" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D207" t="str">
+        <v>Coconut</v>
+      </c>
+      <c r="E207" t="str">
+        <v>เนื้อมะพร้าว 10 - 1200 บาท น้ำมะพร้าว 10</v>
+      </c>
+      <c r="F207">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>07/04/2026</v>
+      </c>
+      <c r="B208" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C208" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D208" t="str">
+        <v>Watermelon</v>
+      </c>
+      <c r="E208" t="str">
+        <v>ค่าแตงโมวันที่ 4- 40 ลูก 3200 บาท วันที่ 7-40 ลูก</v>
+      </c>
+      <c r="F208">
+        <v>6400</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>10/04/2026</v>
+      </c>
+      <c r="B209" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C209" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D209" t="str">
+        <v>Ice</v>
+      </c>
+      <c r="E209" t="str">
+        <v>ค่านม</v>
+      </c>
+      <c r="F209">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>11/04/2026</v>
+      </c>
+      <c r="B210" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C210" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D210" t="str">
+        <v>Transportation</v>
+      </c>
+      <c r="E210" t="str">
+        <v>ค่ารถ lalamove</v>
+      </c>
+      <c r="F210">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>11/04/2026</v>
+      </c>
+      <c r="B211" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C211" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D211" t="str">
+        <v>Apple/Melon</v>
+      </c>
+      <c r="E211" t="str">
+        <v>แอปเปิ้ล 3 ลัง</v>
+      </c>
+      <c r="F211">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>11/04/2026</v>
+      </c>
+      <c r="B212" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C212" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D212" t="str">
+        <v>Ice</v>
+      </c>
+      <c r="E212" t="str">
+        <v>น้ำ 500 เนื้อ 1200</v>
+      </c>
+      <c r="F212">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>11/04/2026</v>
+      </c>
+      <c r="B213" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C213" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D213" t="str">
+        <v>Mango</v>
+      </c>
+      <c r="E213" t="str">
+        <v>มะม่วง 1 ลัง 23 โล</v>
+      </c>
+      <c r="F213">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>13/04/2026</v>
+      </c>
+      <c r="B214" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C214" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D214" t="str">
+        <v>Coconut</v>
+      </c>
+      <c r="E214" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="F214">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>13/04/2026</v>
+      </c>
+      <c r="B215" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C215" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D215" t="str">
+        <v>Coconut</v>
+      </c>
+      <c r="E215" t="str">
+        <v>เนื้อมะพร้าว 1200 น้ำมะพร้าว 500</v>
+      </c>
+      <c r="F215">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>13/04/2026</v>
+      </c>
+      <c r="B216" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C216" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D216" t="str">
+        <v>Mango</v>
+      </c>
+      <c r="E216" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="F216">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>13/04/2026</v>
+      </c>
+      <c r="B217" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C217" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D217" t="str">
+        <v>Watermelon</v>
+      </c>
+      <c r="E217" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="F217">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>18/04/2026</v>
+      </c>
+      <c r="B218" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C218" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D218" t="str">
+        <v>Apple/Melon</v>
+      </c>
+      <c r="E218" t="str">
+        <v>แอปเปิ้ล 3 ลัง</v>
+      </c>
+      <c r="F218">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>18/04/2026</v>
+      </c>
+      <c r="B219" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C219" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D219" t="str">
+        <v>Mango</v>
+      </c>
+      <c r="E219" t="str">
+        <v>16/04/26 มะม่วง 1 ลัง</v>
+      </c>
+      <c r="F219">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>18/04/2026</v>
+      </c>
+      <c r="B220" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C220" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D220" t="str">
+        <v>Other</v>
+      </c>
+      <c r="E220" t="str">
+        <v>16/4/2569</v>
+      </c>
+      <c r="F220">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>20/04/2026</v>
+      </c>
+      <c r="B221" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C221" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D221" t="str">
+        <v>Orange</v>
+      </c>
+      <c r="E221" t="str">
+        <v>ส้ม 40 ตะกร้า ตะกร้าละ 22 โล โลละ 30 บาท</v>
+      </c>
+      <c r="F221">
+        <v>28600</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>20/04/2026</v>
+      </c>
+      <c r="B222" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C222" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D222" t="str">
+        <v>Transportation</v>
+      </c>
+      <c r="E222" t="str">
+        <v>ค่าส่งป้ายเมนูร้านใหม่</v>
+      </c>
+      <c r="F222">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
+        <v>20/04/2026</v>
+      </c>
+      <c r="B223" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C223" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D223" t="str">
+        <v>Packaging</v>
+      </c>
+      <c r="E223" t="str">
+        <v>ขวดใหญ่ 98 อัน</v>
+      </c>
+      <c r="F223">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>20/04/2026</v>
+      </c>
+      <c r="B224" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C224" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D224" t="str">
+        <v>Packaging</v>
+      </c>
+      <c r="E224" t="str">
+        <v>ถุงขยะ 10 แพค</v>
+      </c>
+      <c r="F224">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>20/04/2026</v>
+      </c>
+      <c r="B225" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C225" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D225" t="str">
+        <v>Watermelon</v>
+      </c>
+      <c r="E225" t="str">
+        <v>18/4/26 แตงโม 30 ลูก</v>
+      </c>
+      <c r="F225">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>20/04/2026</v>
+      </c>
+      <c r="B226" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C226" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D226" t="str">
+        <v>Mango</v>
+      </c>
+      <c r="E226" t="str">
+        <v>18/4/26 มะม่วง 25 โล 750</v>
+      </c>
+      <c r="F226">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
+        <v>21/04/2026</v>
+      </c>
+      <c r="B227" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C227" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D227" t="str">
+        <v>Watermelon</v>
+      </c>
+      <c r="E227" t="str">
+        <v>21/4/26 แตงโม60 ลูก</v>
+      </c>
+      <c r="F227">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>21/04/2026</v>
+      </c>
+      <c r="B228" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C228" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D228" t="str">
+        <v>Transportation</v>
+      </c>
+      <c r="E228" t="str">
+        <v>Lalamove</v>
+      </c>
+      <c r="F228">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>21/04/2026</v>
+      </c>
+      <c r="B229" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C229" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D229" t="str">
+        <v>Apple/Melon</v>
+      </c>
+      <c r="E229" t="str">
+        <v>แอปเปิ้ล 4 ลัง</v>
+      </c>
+      <c r="F229">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="str">
+        <v>23/04/2026</v>
+      </c>
+      <c r="B230" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C230" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D230" t="str">
+        <v>Mango</v>
+      </c>
+      <c r="E230" t="str">
+        <v>มะม่วง 2 ลัง</v>
+      </c>
+      <c r="F230">
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="str">
+        <v>23/04/2026</v>
+      </c>
+      <c r="B231" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C231" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D231" t="str">
+        <v>Apple/Melon</v>
+      </c>
+      <c r="E231" t="str">
+        <v>แอปเปิ้ล 4 ลัง</v>
+      </c>
+      <c r="F231">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="str">
+        <v>23/04/2026</v>
+      </c>
+      <c r="B232" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C232" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D232" t="str">
+        <v>Ice</v>
+      </c>
+      <c r="E232" t="str">
+        <v>16/4/26 เนื้อ 10 น้ำ 10 21/4/26 เนื้อ 10</v>
+      </c>
+      <c r="F232">
+        <v>2900</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="str">
+        <v>23/04/2026</v>
+      </c>
+      <c r="B233" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C233" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D233" t="str">
+        <v>Mango</v>
+      </c>
+      <c r="E233" t="str">
+        <v>มะม่วง 1 ลัง</v>
+      </c>
+      <c r="F233">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="str">
+        <v>24/04/2026</v>
+      </c>
+      <c r="B234" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C234" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D234" t="str">
+        <v>Packaging</v>
+      </c>
+      <c r="E234" t="str">
+        <v>บาร์เลย 4 ถั่วแดง 3 ถุงละ 60</v>
+      </c>
+      <c r="F234">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="str">
+        <v>24/04/2026</v>
+      </c>
+      <c r="B235" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C235" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D235" t="str">
+        <v>Watermelon</v>
+      </c>
+      <c r="E235" t="str">
+        <v>แตงโม 50 ลูก</v>
+      </c>
+      <c r="F235">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="str">
+        <v>25/04/2026</v>
+      </c>
+      <c r="B236" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C236" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D236" t="str">
+        <v>Orange</v>
+      </c>
+      <c r="E236" t="str">
+        <v>22/04/69</v>
+      </c>
+      <c r="F236">
+        <v>14400</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="str">
+        <v>26/04/2026</v>
+      </c>
+      <c r="B237" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C237" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D237" t="str">
+        <v>Packaging</v>
+      </c>
+      <c r="E237" t="str">
+        <v>แก้ว 1 ลัง</v>
+      </c>
+      <c r="F237">
+        <v>1539</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="str">
+        <v>26/04/2026</v>
+      </c>
+      <c r="B238" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C238" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D238" t="str">
+        <v>Packaging</v>
+      </c>
+      <c r="E238" t="str">
+        <v>แก้ว3ลัง</v>
+      </c>
+      <c r="F238">
+        <v>7090</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="str">
+        <v>26/04/2026</v>
+      </c>
+      <c r="B239" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C239" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D239" t="str">
+        <v>Mango</v>
+      </c>
+      <c r="E239" t="str">
+        <v>มะม่วง 1 ลัง</v>
+      </c>
+      <c r="F239">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="str">
+        <v>26/04/2026</v>
+      </c>
+      <c r="B240" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C240" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D240" t="str">
+        <v>Apple/Melon</v>
+      </c>
+      <c r="E240" t="str">
+        <v>แอปเปิ้ล 4</v>
+      </c>
+      <c r="F240">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="str">
+        <v>27/04/2026</v>
+      </c>
+      <c r="B241" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C241" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D241" t="str">
+        <v>Ice</v>
+      </c>
+      <c r="E241" t="str">
+        <v>26/4/26 50 ลูก</v>
+      </c>
+      <c r="F241">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="str">
+        <v>28/04/2026</v>
+      </c>
+      <c r="B242" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C242" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D242" t="str">
+        <v>Packaging</v>
+      </c>
+      <c r="E242" t="str">
+        <v>หลอด 704(20ห่อ)</v>
+      </c>
+      <c r="F242">
+        <v>2110</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="str">
+        <v>28/04/2026</v>
+      </c>
+      <c r="B243" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C243" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D243" t="str">
+        <v>Orange</v>
+      </c>
+      <c r="E243" t="str">
+        <v>รอบ 27/04/69</v>
+      </c>
+      <c r="F243">
+        <v>21600</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="str">
+        <v>28/04/2026</v>
+      </c>
+      <c r="B244" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C244" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D244" t="str">
+        <v>Coconut</v>
+      </c>
+      <c r="E244" t="str">
+        <v>ค่าส่งมะพร้าว</v>
+      </c>
+      <c r="F244">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="str">
+        <v>28/04/2026</v>
+      </c>
+      <c r="B245" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C245" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D245" t="str">
+        <v>Apple/Melon</v>
+      </c>
+      <c r="E245" t="str">
+        <v>แอปเปิ้ล 4 ลัง</v>
+      </c>
+      <c r="F245">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="str">
+        <v>28/04/2026</v>
+      </c>
+      <c r="B246" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C246" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D246" t="str">
+        <v>Mango</v>
+      </c>
+      <c r="E246" t="str">
+        <v>มะม่วง 2 ลัง</v>
+      </c>
+      <c r="F246">
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="str">
+        <v>29/04/2026</v>
+      </c>
+      <c r="B247" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C247" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D247" t="str">
+        <v>Milk/Conden</v>
+      </c>
+      <c r="E247" t="str">
+        <v>นมข้นหวาน1ลัง 836</v>
+      </c>
+      <c r="F247">
+        <v>2160</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="str">
+        <v>29/04/2026</v>
+      </c>
+      <c r="B248" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C248" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D248" t="str">
+        <v>Packaging</v>
+      </c>
+      <c r="E248" t="str">
+        <v>นมข้นหวาน2ลัง 1602</v>
+      </c>
+      <c r="F248">
+        <v>3210</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="str">
+        <v>29/04/2026</v>
+      </c>
+      <c r="B249" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C249" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D249" t="str">
+        <v>Watermelon</v>
+      </c>
+      <c r="E249" t="str">
+        <v>แตงโม 60 ลูก</v>
+      </c>
+      <c r="F249">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="str">
+        <v>29/04/2026</v>
+      </c>
+      <c r="B250" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C250" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D250" t="str">
+        <v>Transportation</v>
+      </c>
+      <c r="E250" t="str">
+        <v>เนื้อ 10 x 50 500</v>
+      </c>
+      <c r="F250">
+        <v>2395</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="str">
         <v>30/04/2026</v>
       </c>
-      <c r="B186" t="str">
+      <c r="B251" t="str">
         <v>Apr26</v>
       </c>
-      <c r="C186" t="str">
-        <v>COGS</v>
-      </c>
-      <c r="D186" t="str">
+      <c r="C251" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D251" t="str">
+        <v>Ice</v>
+      </c>
+      <c r="E251" t="str">
+        <v>สับปะรส 3 ตะกร้า</v>
+      </c>
+      <c r="F251">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="str">
+        <v>30/04/2026</v>
+      </c>
+      <c r="B252" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C252" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D252" t="str">
+        <v>Salary</v>
+      </c>
+      <c r="E252" t="str">
+        <v>Employee 1</v>
+      </c>
+      <c r="F252">
+        <v>19000</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="str">
+        <v>30/04/2026</v>
+      </c>
+      <c r="B253" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C253" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D253" t="str">
+        <v>Salary</v>
+      </c>
+      <c r="E253" t="str">
+        <v>Employee 2</v>
+      </c>
+      <c r="F253">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="str">
+        <v>30/04/2026</v>
+      </c>
+      <c r="B254" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C254" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D254" t="str">
+        <v>Fixed Costs</v>
+      </c>
+      <c r="E254" t="str">
+        <v>Rent</v>
+      </c>
+      <c r="F254">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="str">
+        <v>30/04/2026</v>
+      </c>
+      <c r="B255" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C255" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D255" t="str">
+        <v>Investment</v>
+      </c>
+      <c r="E255" t="str">
+        <v>Stock (Allocated 82.9%)</v>
+      </c>
+      <c r="F255">
+        <v>9948</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="str">
+        <v>30/04/2026</v>
+      </c>
+      <c r="B256" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C256" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D256" t="str">
         <v>Other</v>
       </c>
-      <c r="E186" t="str">
+      <c r="E256" t="str">
         <v>Pineapple</v>
       </c>
-      <c r="F186">
+      <c r="F256">
         <v>1500</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="str">
+        <v>31/05/2026</v>
+      </c>
+      <c r="B257" t="str">
+        <v>May26</v>
+      </c>
+      <c r="C257" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D257" t="str">
+        <v>Investment</v>
+      </c>
+      <c r="E257" t="str">
+        <v>Stock Adjustment (Allocated to B2)</v>
+      </c>
+      <c r="F257">
+        <v>-4830</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F186"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F257"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -13749,7 +15169,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AD16"/>
+  <dimension ref="A1:AD35"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -13856,7 +15276,7 @@
         <v>Fri</v>
       </c>
       <c r="C3">
-        <v>13770</v>
+        <v>13950</v>
       </c>
       <c r="D3">
         <v>8040</v>
@@ -13868,7 +15288,7 @@
         <v>7920</v>
       </c>
       <c r="G3">
-        <v>5910</v>
+        <v>5730</v>
       </c>
       <c r="H3">
         <v>81</v>
@@ -13963,13 +15383,13 @@
         <v>7290</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="K4">
         <v>7</v>
@@ -13990,7 +15410,7 @@
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>92</v>
+        <v>302</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -14020,7 +15440,7 @@
         <v>5</v>
       </c>
       <c r="AA4">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AB4">
         <v>0</v>
@@ -14055,22 +15475,22 @@
         <v>5010</v>
       </c>
       <c r="H5">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
       <c r="J5">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="K5">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="L5">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="M5">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -14082,7 +15502,7 @@
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>282</v>
+        <v>218</v>
       </c>
       <c r="R5">
         <v>0</v>
@@ -14091,13 +15511,13 @@
         <v>0</v>
       </c>
       <c r="T5">
-        <v>63</v>
+        <v>2</v>
       </c>
       <c r="U5">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="V5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="W5">
         <v>4</v>
@@ -14112,7 +15532,7 @@
         <v>4</v>
       </c>
       <c r="AA5">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="AB5">
         <v>0</v>
@@ -14239,19 +15659,19 @@
         <v>3520</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="K7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L7">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="M7">
         <v>9</v>
@@ -14266,7 +15686,7 @@
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>132</v>
+        <v>190</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -14278,10 +15698,10 @@
         <v>1.5</v>
       </c>
       <c r="U7">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="V7">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="W7">
         <v>2</v>
@@ -14515,16 +15935,16 @@
         <v>2480</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="K10">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L10">
         <v>20</v>
@@ -14542,7 +15962,7 @@
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -14607,22 +16027,22 @@
         <v>5330</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -14634,7 +16054,7 @@
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -14687,34 +16107,34 @@
         <v>10690</v>
       </c>
       <c r="D12">
-        <v>6590</v>
+        <v>6410</v>
       </c>
       <c r="E12">
         <v>180</v>
       </c>
       <c r="F12">
-        <v>6410</v>
+        <v>6230</v>
       </c>
       <c r="G12">
-        <v>4100</v>
+        <v>4280</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -14726,7 +16146,7 @@
         <v>0</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>183</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -14735,13 +16155,13 @@
         <v>0</v>
       </c>
       <c r="T12">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="U12">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="V12">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="W12">
         <v>3</v>
@@ -14756,7 +16176,7 @@
         <v>3</v>
       </c>
       <c r="AA12">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="AB12">
         <v>0</v>
@@ -14779,34 +16199,34 @@
         <v>6455</v>
       </c>
       <c r="D13">
-        <v>3660</v>
+        <v>3540</v>
       </c>
       <c r="E13">
         <v>120</v>
       </c>
       <c r="F13">
-        <v>3540</v>
+        <v>3420</v>
       </c>
       <c r="G13">
-        <v>2795</v>
+        <v>2915</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -14818,7 +16238,7 @@
         <v>0</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -14827,13 +16247,13 @@
         <v>0</v>
       </c>
       <c r="T13">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="U13">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="V13">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W13">
         <v>2</v>
@@ -14848,7 +16268,7 @@
         <v>2</v>
       </c>
       <c r="AA13">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AB13">
         <v>0</v>
@@ -14868,34 +16288,34 @@
         <v>Tue</v>
       </c>
       <c r="C14">
-        <v>4770</v>
+        <v>4890</v>
       </c>
       <c r="D14">
-        <v>3110</v>
+        <v>3230</v>
       </c>
       <c r="E14">
         <v>120</v>
       </c>
       <c r="F14">
-        <v>2990</v>
+        <v>3110</v>
       </c>
       <c r="G14">
         <v>1660</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="I14">
         <v>0</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="K14">
         <v>3</v>
       </c>
       <c r="L14">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="M14">
         <v>9</v>
@@ -14910,7 +16330,7 @@
         <v>0</v>
       </c>
       <c r="Q14">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -15014,7 +16434,7 @@
         <v>2</v>
       </c>
       <c r="U15">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="V15">
         <v>10</v>
@@ -15067,22 +16487,22 @@
         <v>3560</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="I16">
         <v>0</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -15094,7 +16514,7 @@
         <v>0</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="R16">
         <v>0</v>
@@ -15109,7 +16529,7 @@
         <v>9</v>
       </c>
       <c r="V16">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="W16">
         <v>2</v>
@@ -15136,9 +16556,1662 @@
         <v>0</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>15/05/2026</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Fri</v>
+      </c>
+      <c r="C17">
+        <v>11700</v>
+      </c>
+      <c r="D17">
+        <v>6590</v>
+      </c>
+      <c r="E17">
+        <v>120</v>
+      </c>
+      <c r="F17">
+        <v>6470</v>
+      </c>
+      <c r="G17">
+        <v>5110</v>
+      </c>
+      <c r="H17">
+        <v>100</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>60</v>
+      </c>
+      <c r="K17">
+        <v>8</v>
+      </c>
+      <c r="L17">
+        <v>20</v>
+      </c>
+      <c r="M17">
+        <v>13</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>201</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>4</v>
+      </c>
+      <c r="U17">
+        <v>5</v>
+      </c>
+      <c r="V17">
+        <v>16</v>
+      </c>
+      <c r="W17">
+        <v>2</v>
+      </c>
+      <c r="X17">
+        <v>2</v>
+      </c>
+      <c r="Y17">
+        <v>1</v>
+      </c>
+      <c r="Z17">
+        <v>1</v>
+      </c>
+      <c r="AA17">
+        <v>26</v>
+      </c>
+      <c r="AB17">
+        <v>0</v>
+      </c>
+      <c r="AC17">
+        <v>0</v>
+      </c>
+      <c r="AD17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>16/05/2026</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Sat</v>
+      </c>
+      <c r="C18">
+        <v>9730</v>
+      </c>
+      <c r="D18">
+        <v>4400</v>
+      </c>
+      <c r="E18">
+        <v>180</v>
+      </c>
+      <c r="F18">
+        <v>4220</v>
+      </c>
+      <c r="G18">
+        <v>5330</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>2</v>
+      </c>
+      <c r="U18">
+        <v>12</v>
+      </c>
+      <c r="V18">
+        <v>14</v>
+      </c>
+      <c r="W18">
+        <v>2</v>
+      </c>
+      <c r="X18">
+        <v>2</v>
+      </c>
+      <c r="Y18">
+        <v>1</v>
+      </c>
+      <c r="Z18">
+        <v>1</v>
+      </c>
+      <c r="AA18">
+        <v>26</v>
+      </c>
+      <c r="AB18">
+        <v>0</v>
+      </c>
+      <c r="AC18">
+        <v>0</v>
+      </c>
+      <c r="AD18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>17/05/2026</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Sun</v>
+      </c>
+      <c r="C19">
+        <v>6630</v>
+      </c>
+      <c r="D19">
+        <v>2530</v>
+      </c>
+      <c r="E19">
+        <v>120</v>
+      </c>
+      <c r="F19">
+        <v>2410</v>
+      </c>
+      <c r="G19">
+        <v>4100</v>
+      </c>
+      <c r="H19">
+        <v>44</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>48</v>
+      </c>
+      <c r="K19">
+        <v>3</v>
+      </c>
+      <c r="L19">
+        <v>8</v>
+      </c>
+      <c r="M19">
+        <v>12</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>115</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>2</v>
+      </c>
+      <c r="U19">
+        <v>10</v>
+      </c>
+      <c r="V19">
+        <v>6</v>
+      </c>
+      <c r="W19">
+        <v>1</v>
+      </c>
+      <c r="X19">
+        <v>1</v>
+      </c>
+      <c r="Y19">
+        <v>0.5</v>
+      </c>
+      <c r="Z19">
+        <v>2</v>
+      </c>
+      <c r="AA19">
+        <v>24</v>
+      </c>
+      <c r="AB19">
+        <v>0</v>
+      </c>
+      <c r="AC19">
+        <v>0</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>18/05/2026</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Mon</v>
+      </c>
+      <c r="C20">
+        <v>6790</v>
+      </c>
+      <c r="D20">
+        <v>3630</v>
+      </c>
+      <c r="E20">
+        <v>120</v>
+      </c>
+      <c r="F20">
+        <v>3510</v>
+      </c>
+      <c r="G20">
+        <v>3160</v>
+      </c>
+      <c r="H20">
+        <v>56</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>41</v>
+      </c>
+      <c r="K20">
+        <v>2</v>
+      </c>
+      <c r="L20">
+        <v>12</v>
+      </c>
+      <c r="M20">
+        <v>6</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>117</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>2</v>
+      </c>
+      <c r="U20">
+        <v>8</v>
+      </c>
+      <c r="V20">
+        <v>4</v>
+      </c>
+      <c r="W20">
+        <v>1</v>
+      </c>
+      <c r="X20">
+        <v>1</v>
+      </c>
+      <c r="Y20">
+        <v>1</v>
+      </c>
+      <c r="Z20">
+        <v>1</v>
+      </c>
+      <c r="AA20">
+        <v>12</v>
+      </c>
+      <c r="AB20">
+        <v>0</v>
+      </c>
+      <c r="AC20">
+        <v>0</v>
+      </c>
+      <c r="AD20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>19/05/2026</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Tue</v>
+      </c>
+      <c r="C21">
+        <v>3590</v>
+      </c>
+      <c r="D21">
+        <v>2660</v>
+      </c>
+      <c r="E21">
+        <v>60</v>
+      </c>
+      <c r="F21">
+        <v>2600</v>
+      </c>
+      <c r="G21">
+        <v>930</v>
+      </c>
+      <c r="H21">
+        <v>26</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>19</v>
+      </c>
+      <c r="K21">
+        <v>2</v>
+      </c>
+      <c r="L21">
+        <v>12</v>
+      </c>
+      <c r="M21">
+        <v>2</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>61</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>1</v>
+      </c>
+      <c r="U21">
+        <v>5</v>
+      </c>
+      <c r="V21">
+        <v>4</v>
+      </c>
+      <c r="W21">
+        <v>1</v>
+      </c>
+      <c r="X21">
+        <v>1</v>
+      </c>
+      <c r="Y21">
+        <v>1</v>
+      </c>
+      <c r="Z21">
+        <v>0.5</v>
+      </c>
+      <c r="AA21">
+        <v>4</v>
+      </c>
+      <c r="AB21">
+        <v>0</v>
+      </c>
+      <c r="AC21">
+        <v>0</v>
+      </c>
+      <c r="AD21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>20/05/2026</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Wed</v>
+      </c>
+      <c r="C22">
+        <v>2755</v>
+      </c>
+      <c r="D22">
+        <v>1700</v>
+      </c>
+      <c r="E22">
+        <v>60</v>
+      </c>
+      <c r="F22">
+        <v>1640</v>
+      </c>
+      <c r="G22">
+        <v>1055</v>
+      </c>
+      <c r="H22">
+        <v>3</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>20</v>
+      </c>
+      <c r="K22">
+        <v>3</v>
+      </c>
+      <c r="L22">
+        <v>3</v>
+      </c>
+      <c r="M22">
+        <v>5</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>34</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>1</v>
+      </c>
+      <c r="U22">
+        <v>5</v>
+      </c>
+      <c r="V22">
+        <v>6</v>
+      </c>
+      <c r="W22">
+        <v>0.5</v>
+      </c>
+      <c r="X22">
+        <v>0.5</v>
+      </c>
+      <c r="Y22">
+        <v>0.5</v>
+      </c>
+      <c r="Z22">
+        <v>0.5</v>
+      </c>
+      <c r="AA22">
+        <v>10</v>
+      </c>
+      <c r="AB22">
+        <v>0</v>
+      </c>
+      <c r="AC22">
+        <v>0</v>
+      </c>
+      <c r="AD22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>22/05/2026</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Fri</v>
+      </c>
+      <c r="C23">
+        <v>7490</v>
+      </c>
+      <c r="D23">
+        <v>5160</v>
+      </c>
+      <c r="E23">
+        <v>150</v>
+      </c>
+      <c r="F23">
+        <v>5010</v>
+      </c>
+      <c r="G23">
+        <v>2330</v>
+      </c>
+      <c r="H23">
+        <v>45</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>37</v>
+      </c>
+      <c r="K23">
+        <v>2</v>
+      </c>
+      <c r="L23">
+        <v>40</v>
+      </c>
+      <c r="M23">
+        <v>6</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>130</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>2</v>
+      </c>
+      <c r="U23">
+        <v>10</v>
+      </c>
+      <c r="V23">
+        <v>4</v>
+      </c>
+      <c r="W23">
+        <v>2</v>
+      </c>
+      <c r="X23">
+        <v>2</v>
+      </c>
+      <c r="Y23">
+        <v>1</v>
+      </c>
+      <c r="Z23">
+        <v>1</v>
+      </c>
+      <c r="AA23">
+        <v>12</v>
+      </c>
+      <c r="AB23">
+        <v>0</v>
+      </c>
+      <c r="AC23">
+        <v>0</v>
+      </c>
+      <c r="AD23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>23/05/2026</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Sat</v>
+      </c>
+      <c r="C24">
+        <v>9380</v>
+      </c>
+      <c r="D24">
+        <v>5350</v>
+      </c>
+      <c r="E24">
+        <v>150</v>
+      </c>
+      <c r="F24">
+        <v>5200</v>
+      </c>
+      <c r="G24">
+        <v>4030</v>
+      </c>
+      <c r="H24">
+        <v>55</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>43</v>
+      </c>
+      <c r="K24">
+        <v>5</v>
+      </c>
+      <c r="L24">
+        <v>46</v>
+      </c>
+      <c r="M24">
+        <v>12</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>161</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>2</v>
+      </c>
+      <c r="U24">
+        <v>18</v>
+      </c>
+      <c r="V24">
+        <v>10</v>
+      </c>
+      <c r="W24">
+        <v>3</v>
+      </c>
+      <c r="X24">
+        <v>3</v>
+      </c>
+      <c r="Y24">
+        <v>1</v>
+      </c>
+      <c r="Z24">
+        <v>2</v>
+      </c>
+      <c r="AA24">
+        <v>24</v>
+      </c>
+      <c r="AB24">
+        <v>0</v>
+      </c>
+      <c r="AC24">
+        <v>0</v>
+      </c>
+      <c r="AD24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>24/05/2026</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Sun</v>
+      </c>
+      <c r="C25">
+        <v>8550</v>
+      </c>
+      <c r="D25">
+        <v>4720</v>
+      </c>
+      <c r="E25">
+        <v>150</v>
+      </c>
+      <c r="F25">
+        <v>4570</v>
+      </c>
+      <c r="G25">
+        <v>3830</v>
+      </c>
+      <c r="H25">
+        <v>59</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>39</v>
+      </c>
+      <c r="K25">
+        <v>2</v>
+      </c>
+      <c r="L25">
+        <v>36</v>
+      </c>
+      <c r="M25">
+        <v>12</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>148</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>2</v>
+      </c>
+      <c r="U25">
+        <v>10</v>
+      </c>
+      <c r="V25">
+        <v>4</v>
+      </c>
+      <c r="W25">
+        <v>2</v>
+      </c>
+      <c r="X25">
+        <v>2</v>
+      </c>
+      <c r="Y25">
+        <v>1</v>
+      </c>
+      <c r="Z25">
+        <v>2</v>
+      </c>
+      <c r="AA25">
+        <v>24</v>
+      </c>
+      <c r="AB25">
+        <v>0</v>
+      </c>
+      <c r="AC25">
+        <v>0</v>
+      </c>
+      <c r="AD25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>25/05/2026</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Mon</v>
+      </c>
+      <c r="C26">
+        <v>8050</v>
+      </c>
+      <c r="D26">
+        <v>5680</v>
+      </c>
+      <c r="E26">
+        <v>150</v>
+      </c>
+      <c r="F26">
+        <v>5530</v>
+      </c>
+      <c r="G26">
+        <v>2370</v>
+      </c>
+      <c r="H26">
+        <v>53</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>56</v>
+      </c>
+      <c r="K26">
+        <v>6</v>
+      </c>
+      <c r="L26">
+        <v>19</v>
+      </c>
+      <c r="M26">
+        <v>4</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <v>138</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>3</v>
+      </c>
+      <c r="U26">
+        <v>9</v>
+      </c>
+      <c r="V26">
+        <v>12</v>
+      </c>
+      <c r="W26">
+        <v>2</v>
+      </c>
+      <c r="X26">
+        <v>2</v>
+      </c>
+      <c r="Y26">
+        <v>0.5</v>
+      </c>
+      <c r="Z26">
+        <v>1.5</v>
+      </c>
+      <c r="AA26">
+        <v>8</v>
+      </c>
+      <c r="AB26">
+        <v>0</v>
+      </c>
+      <c r="AC26">
+        <v>0</v>
+      </c>
+      <c r="AD26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>26/05/2026</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Tue</v>
+      </c>
+      <c r="C27">
+        <v>6560</v>
+      </c>
+      <c r="D27">
+        <v>3710</v>
+      </c>
+      <c r="E27">
+        <v>150</v>
+      </c>
+      <c r="F27">
+        <v>3560</v>
+      </c>
+      <c r="G27">
+        <v>2850</v>
+      </c>
+      <c r="H27">
+        <v>40</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>22</v>
+      </c>
+      <c r="K27">
+        <v>4</v>
+      </c>
+      <c r="L27">
+        <v>23</v>
+      </c>
+      <c r="M27">
+        <v>21</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>110</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>2</v>
+      </c>
+      <c r="U27">
+        <v>5</v>
+      </c>
+      <c r="V27">
+        <v>8</v>
+      </c>
+      <c r="W27">
+        <v>2</v>
+      </c>
+      <c r="X27">
+        <v>2</v>
+      </c>
+      <c r="Y27">
+        <v>1</v>
+      </c>
+      <c r="Z27">
+        <v>2</v>
+      </c>
+      <c r="AA27">
+        <v>4.5</v>
+      </c>
+      <c r="AB27">
+        <v>0</v>
+      </c>
+      <c r="AC27">
+        <v>0</v>
+      </c>
+      <c r="AD27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>27/05/2026</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Wed</v>
+      </c>
+      <c r="C28">
+        <v>6240</v>
+      </c>
+      <c r="D28">
+        <v>3200</v>
+      </c>
+      <c r="E28">
+        <v>120</v>
+      </c>
+      <c r="F28">
+        <v>3080</v>
+      </c>
+      <c r="G28">
+        <v>3040</v>
+      </c>
+      <c r="H28">
+        <v>35</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>21</v>
+      </c>
+      <c r="K28">
+        <v>5</v>
+      </c>
+      <c r="L28">
+        <v>38</v>
+      </c>
+      <c r="M28">
+        <v>6</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>105</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>1</v>
+      </c>
+      <c r="U28">
+        <v>5</v>
+      </c>
+      <c r="V28">
+        <v>10</v>
+      </c>
+      <c r="W28">
+        <v>2</v>
+      </c>
+      <c r="X28">
+        <v>2</v>
+      </c>
+      <c r="Y28">
+        <v>1</v>
+      </c>
+      <c r="Z28">
+        <v>2</v>
+      </c>
+      <c r="AA28">
+        <v>12</v>
+      </c>
+      <c r="AB28">
+        <v>0</v>
+      </c>
+      <c r="AC28">
+        <v>0</v>
+      </c>
+      <c r="AD28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>28/05/2026</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Thu</v>
+      </c>
+      <c r="C29">
+        <v>6390</v>
+      </c>
+      <c r="D29">
+        <v>3940</v>
+      </c>
+      <c r="E29">
+        <v>90</v>
+      </c>
+      <c r="F29">
+        <v>3850</v>
+      </c>
+      <c r="G29">
+        <v>2450</v>
+      </c>
+      <c r="H29">
+        <v>18</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>2</v>
+      </c>
+      <c r="L29">
+        <v>12</v>
+      </c>
+      <c r="M29">
+        <v>8</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <v>40</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>1</v>
+      </c>
+      <c r="U29">
+        <v>9</v>
+      </c>
+      <c r="V29">
+        <v>4</v>
+      </c>
+      <c r="W29">
+        <v>1</v>
+      </c>
+      <c r="X29">
+        <v>1</v>
+      </c>
+      <c r="Y29">
+        <v>1</v>
+      </c>
+      <c r="Z29">
+        <v>1</v>
+      </c>
+      <c r="AA29">
+        <v>20</v>
+      </c>
+      <c r="AB29">
+        <v>0</v>
+      </c>
+      <c r="AC29">
+        <v>0</v>
+      </c>
+      <c r="AD29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>29/05/2026</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Fri</v>
+      </c>
+      <c r="C30">
+        <v>8980</v>
+      </c>
+      <c r="D30">
+        <v>4280</v>
+      </c>
+      <c r="E30">
+        <v>150</v>
+      </c>
+      <c r="F30">
+        <v>4130</v>
+      </c>
+      <c r="G30">
+        <v>4700</v>
+      </c>
+      <c r="H30">
+        <v>50</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>47</v>
+      </c>
+      <c r="K30">
+        <v>5</v>
+      </c>
+      <c r="L30">
+        <v>39</v>
+      </c>
+      <c r="M30">
+        <v>13</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>0</v>
+      </c>
+      <c r="Q30">
+        <v>154</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <v>2.5</v>
+      </c>
+      <c r="U30">
+        <v>12</v>
+      </c>
+      <c r="V30">
+        <v>6</v>
+      </c>
+      <c r="W30">
+        <v>3</v>
+      </c>
+      <c r="X30">
+        <v>3</v>
+      </c>
+      <c r="Y30">
+        <v>1</v>
+      </c>
+      <c r="Z30">
+        <v>2</v>
+      </c>
+      <c r="AA30">
+        <v>26</v>
+      </c>
+      <c r="AB30">
+        <v>0</v>
+      </c>
+      <c r="AC30">
+        <v>0</v>
+      </c>
+      <c r="AD30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>30/05/2026</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Sat</v>
+      </c>
+      <c r="C31">
+        <v>7810</v>
+      </c>
+      <c r="D31">
+        <v>3910</v>
+      </c>
+      <c r="E31">
+        <v>220</v>
+      </c>
+      <c r="F31">
+        <v>3690</v>
+      </c>
+      <c r="G31">
+        <v>3900</v>
+      </c>
+      <c r="H31">
+        <v>45</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>28</v>
+      </c>
+      <c r="K31">
+        <v>6</v>
+      </c>
+      <c r="L31">
+        <v>43</v>
+      </c>
+      <c r="M31">
+        <v>10</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>0</v>
+      </c>
+      <c r="Q31">
+        <v>132</v>
+      </c>
+      <c r="R31">
+        <v>0</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="T31">
+        <v>2</v>
+      </c>
+      <c r="U31">
+        <v>7</v>
+      </c>
+      <c r="V31">
+        <v>12</v>
+      </c>
+      <c r="W31">
+        <v>2</v>
+      </c>
+      <c r="X31">
+        <v>2</v>
+      </c>
+      <c r="Y31">
+        <v>1</v>
+      </c>
+      <c r="Z31">
+        <v>2</v>
+      </c>
+      <c r="AA31">
+        <v>20</v>
+      </c>
+      <c r="AB31">
+        <v>0</v>
+      </c>
+      <c r="AC31">
+        <v>0</v>
+      </c>
+      <c r="AD31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>31/05/2026</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Sun</v>
+      </c>
+      <c r="C32">
+        <v>6280</v>
+      </c>
+      <c r="D32">
+        <v>3470</v>
+      </c>
+      <c r="E32">
+        <v>120</v>
+      </c>
+      <c r="F32">
+        <v>3350</v>
+      </c>
+      <c r="G32">
+        <v>2810</v>
+      </c>
+      <c r="H32">
+        <v>44</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>29</v>
+      </c>
+      <c r="K32">
+        <v>5</v>
+      </c>
+      <c r="L32">
+        <v>20</v>
+      </c>
+      <c r="M32">
+        <v>9</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>0</v>
+      </c>
+      <c r="Q32">
+        <v>107</v>
+      </c>
+      <c r="R32">
+        <v>0</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <v>2</v>
+      </c>
+      <c r="U32">
+        <v>7</v>
+      </c>
+      <c r="V32">
+        <v>10</v>
+      </c>
+      <c r="W32">
+        <v>2</v>
+      </c>
+      <c r="X32">
+        <v>2</v>
+      </c>
+      <c r="Y32">
+        <v>1</v>
+      </c>
+      <c r="Z32">
+        <v>1</v>
+      </c>
+      <c r="AA32">
+        <v>18</v>
+      </c>
+      <c r="AB32">
+        <v>0</v>
+      </c>
+      <c r="AC32">
+        <v>0</v>
+      </c>
+      <c r="AD32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>TOTAL</v>
+      </c>
+      <c r="B34" t="str">
+        <v>30 days</v>
+      </c>
+      <c r="C34">
+        <v>248480</v>
+      </c>
+      <c r="D34">
+        <v>140410</v>
+      </c>
+      <c r="E34">
+        <v>4120</v>
+      </c>
+      <c r="F34">
+        <v>136290</v>
+      </c>
+      <c r="G34">
+        <v>107890</v>
+      </c>
+      <c r="H34">
+        <v>1379</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>1263</v>
+      </c>
+      <c r="K34">
+        <v>134</v>
+      </c>
+      <c r="L34">
+        <v>1000</v>
+      </c>
+      <c r="M34">
+        <v>292</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>0</v>
+      </c>
+      <c r="Q34">
+        <v>4068</v>
+      </c>
+      <c r="R34">
+        <v>0</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+      <c r="T34">
+        <v>68</v>
+      </c>
+      <c r="U34">
+        <v>337</v>
+      </c>
+      <c r="V34">
+        <v>278</v>
+      </c>
+      <c r="W34">
+        <v>60.5</v>
+      </c>
+      <c r="X34">
+        <v>62.5</v>
+      </c>
+      <c r="Y34">
+        <v>32</v>
+      </c>
+      <c r="Z34">
+        <v>55.5</v>
+      </c>
+      <c r="AA34">
+        <v>626.5</v>
+      </c>
+      <c r="AB34">
+        <v>0</v>
+      </c>
+      <c r="AC34">
+        <v>0</v>
+      </c>
+      <c r="AD34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>AVG/DAY</v>
+      </c>
+      <c r="C35">
+        <v>8282.666666666666</v>
+      </c>
+      <c r="D35">
+        <v>4680.333333333333</v>
+      </c>
+      <c r="E35">
+        <v>137.33333333333334</v>
+      </c>
+      <c r="F35">
+        <v>4543</v>
+      </c>
+      <c r="G35">
+        <v>3596.3333333333335</v>
+      </c>
+      <c r="H35">
+        <v>45.96666666666667</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>42.1</v>
+      </c>
+      <c r="K35">
+        <v>4.466666666666667</v>
+      </c>
+      <c r="L35">
+        <v>33.333333333333336</v>
+      </c>
+      <c r="M35">
+        <v>9.733333333333333</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>0</v>
+      </c>
+      <c r="Q35">
+        <v>135.6</v>
+      </c>
+      <c r="R35">
+        <v>0</v>
+      </c>
+      <c r="S35">
+        <v>0</v>
+      </c>
+      <c r="T35">
+        <v>2.2666666666666666</v>
+      </c>
+      <c r="U35">
+        <v>11.233333333333333</v>
+      </c>
+      <c r="V35">
+        <v>9.266666666666667</v>
+      </c>
+      <c r="W35">
+        <v>2.0166666666666666</v>
+      </c>
+      <c r="X35">
+        <v>2.0833333333333335</v>
+      </c>
+      <c r="Y35">
+        <v>1.0666666666666667</v>
+      </c>
+      <c r="Z35">
+        <v>1.85</v>
+      </c>
+      <c r="AA35">
+        <v>20.883333333333333</v>
+      </c>
+      <c r="AB35">
+        <v>0</v>
+      </c>
+      <c r="AC35">
+        <v>0</v>
+      </c>
+      <c r="AD35">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AD16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AD35"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/3_Automation_Dashboard/SomSaiJai_Dashboard_B1_2026.xlsx
+++ b/3_Automation_Dashboard/SomSaiJai_Dashboard_B1_2026.xlsx
@@ -1168,7 +1168,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F257"/>
+  <dimension ref="A1:F288"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1223,10 +1223,10 @@
         <v>Mar26</v>
       </c>
       <c r="C5" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D5" t="str">
-        <v>Water</v>
+        <v>Rental</v>
       </c>
       <c r="E5" t="str">
         <v>Unknown</v>
@@ -1237,939 +1237,939 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>01/01/2026</v>
+        <v>02/01/2026</v>
       </c>
       <c r="B6" t="str">
-        <v>May26</v>
+        <v>Jan26</v>
       </c>
       <c r="C6" t="str">
         <v>COGS</v>
       </c>
       <c r="D6" t="str">
-        <v>Ice</v>
+        <v>Packaging</v>
       </c>
       <c r="E6" t="str">
-        <v>สับปะรด 18 ลูก</v>
+        <v>แก้ว หลอด</v>
       </c>
       <c r="F6">
-        <v>576</v>
+        <v>2165</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>01/01/2026</v>
+        <v>02/01/2026</v>
       </c>
       <c r="B7" t="str">
-        <v>May26</v>
+        <v>Jan26</v>
       </c>
       <c r="C7" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D7" t="str">
-        <v>Other</v>
+        <v>Ice</v>
       </c>
       <c r="E7" t="str">
-        <v>สับปะรด 18 ลูก</v>
+        <v>ส่วนแบ่ง60เปอ</v>
       </c>
       <c r="F7">
-        <v>594</v>
+        <v>47961</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>01/01/2026</v>
+        <v>02/01/2026</v>
       </c>
       <c r="B8" t="str">
-        <v>May26</v>
+        <v>Jan26</v>
       </c>
       <c r="C8" t="str">
         <v>COGS</v>
       </c>
       <c r="D8" t="str">
-        <v>Apple/Melon</v>
+        <v>Ice</v>
       </c>
       <c r="E8" t="str">
-        <v>แอปเปิ้ล 3 ลังครับ</v>
+        <v>ค่าส่วนแบ่งกำไรเมน 40เปอ</v>
       </c>
       <c r="F8">
-        <v>1050</v>
+        <v>32000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>01/01/2026</v>
+        <v>02/01/2026</v>
       </c>
       <c r="B9" t="str">
-        <v>May26</v>
+        <v>Jan26</v>
       </c>
       <c r="C9" t="str">
         <v>COGS</v>
       </c>
       <c r="D9" t="str">
-        <v>Orange</v>
+        <v>Transportation</v>
       </c>
       <c r="E9" t="str">
-        <v>ค่าส่งส้ม Lalamove หักผ่านบัตร</v>
+        <v>Unknown</v>
       </c>
       <c r="F9">
-        <v>1245</v>
+        <v>400</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>01/01/2026</v>
+        <v>03/01/2026</v>
       </c>
       <c r="B10" t="str">
-        <v>May26</v>
+        <v>Jan26</v>
       </c>
       <c r="C10" t="str">
         <v>COGS</v>
       </c>
       <c r="D10" t="str">
-        <v>Orange</v>
+        <v>Watermelon</v>
       </c>
       <c r="E10" t="str">
-        <v>24/05/69</v>
+        <v>แตงโม 60 ลูก</v>
       </c>
       <c r="F10">
-        <v>15015</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>01/01/2026</v>
+        <v>04/01/2026</v>
       </c>
       <c r="B11" t="str">
-        <v>May26</v>
+        <v>Jan26</v>
       </c>
       <c r="C11" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D11" t="str">
-        <v>Salary</v>
+        <v>Transportation</v>
       </c>
       <c r="E11" t="str">
-        <v>เงินเดือนซี เดือนพ.ค.</v>
+        <v>ค่าส่งแก้ว</v>
       </c>
       <c r="F11">
-        <v>7800</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>01/01/2026</v>
+        <v>06/01/2026</v>
       </c>
       <c r="B12" t="str">
-        <v>May26</v>
+        <v>Jan26</v>
       </c>
       <c r="C12" t="str">
         <v>COGS</v>
       </c>
       <c r="D12" t="str">
-        <v>Packaging</v>
+        <v>Orange</v>
       </c>
       <c r="E12" t="str">
-        <v>แก้ว 3 ลัง</v>
+        <v>ค่าส้ม 5720 ค่าส่งส้ม 960</v>
       </c>
       <c r="F12">
-        <v>4680</v>
+        <v>6680</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>01/01/2026</v>
+        <v>06/01/2026</v>
       </c>
       <c r="B13" t="str">
-        <v>May26</v>
+        <v>Jan26</v>
       </c>
       <c r="C13" t="str">
         <v>COGS</v>
       </c>
       <c r="D13" t="str">
-        <v>Packaging</v>
+        <v>Orange</v>
       </c>
       <c r="E13" t="str">
-        <v>ฝา1 788</v>
+        <v>ค่าส่งส้มมาบทท</v>
       </c>
       <c r="F13">
-        <v>2902</v>
+        <v>375</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>01/01/2026</v>
+        <v>07/01/2026</v>
       </c>
       <c r="B14" t="str">
-        <v>May26</v>
+        <v>Jan26</v>
       </c>
       <c r="C14" t="str">
         <v>COGS</v>
       </c>
       <c r="D14" t="str">
-        <v>Apple/Melon</v>
+        <v>Transportation</v>
       </c>
       <c r="E14" t="str">
-        <v>แอปเปิ้ล 2 ลัง</v>
+        <v>Unknown</v>
       </c>
       <c r="F14">
-        <v>700</v>
+        <v>400</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>01/01/2026</v>
+        <v>08/01/2026</v>
       </c>
       <c r="B15" t="str">
-        <v>May26</v>
+        <v>Jan26</v>
       </c>
       <c r="C15" t="str">
         <v>OPEX</v>
       </c>
       <c r="D15" t="str">
-        <v>Other</v>
+        <v>Rental</v>
       </c>
       <c r="E15" t="str">
-        <v>สับปะรด 18 ลูก</v>
+        <v>ค่าเช่า12,000 น้ำไฟ324 รวม12,324</v>
       </c>
       <c r="F15">
-        <v>522</v>
+        <v>12324</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>01/01/2026</v>
+        <v>08/01/2026</v>
       </c>
       <c r="B16" t="str">
-        <v>May26</v>
+        <v>Jan26</v>
       </c>
       <c r="C16" t="str">
         <v>COGS</v>
       </c>
       <c r="D16" t="str">
-        <v>Packaging</v>
+        <v>Transportation</v>
       </c>
       <c r="E16" t="str">
-        <v>หลอด20 แพค (767)</v>
+        <v>Unknown</v>
       </c>
       <c r="F16">
-        <v>1502</v>
+        <v>400</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>01/01/2026</v>
+        <v>09/01/2026</v>
       </c>
       <c r="B17" t="str">
-        <v>May26</v>
+        <v>Jan26</v>
       </c>
       <c r="C17" t="str">
         <v>COGS</v>
       </c>
       <c r="D17" t="str">
-        <v>Mango</v>
+        <v>Transportation</v>
       </c>
       <c r="E17" t="str">
-        <v>มะม่วง 1 ตะกร้า</v>
+        <v>Unknown</v>
       </c>
       <c r="F17">
-        <v>960</v>
+        <v>400</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>01/01/2026</v>
+        <v>09/01/2026</v>
       </c>
       <c r="B18" t="str">
-        <v>May26</v>
+        <v>Jan26</v>
       </c>
       <c r="C18" t="str">
         <v>COGS</v>
       </c>
       <c r="D18" t="str">
-        <v>Mango</v>
+        <v>Ice</v>
       </c>
       <c r="E18" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>ค่าขนตะกร้ากลับ</v>
       </c>
       <c r="F18">
-        <v>1000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>01/01/2026</v>
+        <v>11/01/2026</v>
       </c>
       <c r="B19" t="str">
-        <v>May26</v>
+        <v>Jan26</v>
       </c>
       <c r="C19" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D19" t="str">
-        <v>Other</v>
+        <v>Packaging</v>
       </c>
       <c r="E19" t="str">
-        <v>16-5-2569ยอด 4,000฿</v>
+        <v>ขวดใหญ่ 98 ใบ</v>
       </c>
       <c r="F19">
-        <v>12000</v>
+        <v>319</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>01/01/2026</v>
+        <v>11/01/2026</v>
       </c>
       <c r="B20" t="str">
-        <v>May26</v>
+        <v>Jan26</v>
       </c>
       <c r="C20" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D20" t="str">
-        <v>Other</v>
+        <v>Orange</v>
       </c>
       <c r="E20" t="str">
-        <v>ฝรั่ง 1 ตะกร้า</v>
+        <v>ค่าส่งส้มไปบทท</v>
       </c>
       <c r="F20">
-        <v>600</v>
+        <v>461</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>01/01/2026</v>
+        <v>11/01/2026</v>
       </c>
       <c r="B21" t="str">
-        <v>May26</v>
+        <v>Jan26</v>
       </c>
       <c r="C21" t="str">
         <v>COGS</v>
       </c>
       <c r="D21" t="str">
-        <v>Transportation</v>
+        <v>Orange</v>
       </c>
       <c r="E21" t="str">
-        <v>ค่าขนส่ง</v>
+        <v>ค่าส้ม20ลัง</v>
       </c>
       <c r="F21">
-        <v>2000</v>
+        <v>6680</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>01/01/2026</v>
+        <v>11/01/2026</v>
       </c>
       <c r="B22" t="str">
-        <v>May26</v>
+        <v>Jan26</v>
       </c>
       <c r="C22" t="str">
         <v>COGS</v>
       </c>
       <c r="D22" t="str">
-        <v>Mango</v>
+        <v>Transportation</v>
       </c>
       <c r="E22" t="str">
-        <v>มะม่วง 1 ลัง (25 โล)</v>
+        <v>Unknown</v>
       </c>
       <c r="F22">
-        <v>875</v>
+        <v>400</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>01/01/2026</v>
+        <v>12/01/2026</v>
       </c>
       <c r="B23" t="str">
-        <v>May26</v>
+        <v>Jan26</v>
       </c>
       <c r="C23" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D23" t="str">
-        <v>Other</v>
+        <v>Packaging</v>
       </c>
       <c r="E23" t="str">
-        <v>ฝรั่ง 1 ลัง</v>
+        <v>ถุงขยะ</v>
       </c>
       <c r="F23">
-        <v>600</v>
+        <v>548</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>01/01/2026</v>
+        <v>14/01/2026</v>
       </c>
       <c r="B24" t="str">
-        <v>May26</v>
+        <v>Jan26</v>
       </c>
       <c r="C24" t="str">
         <v>COGS</v>
       </c>
       <c r="D24" t="str">
-        <v>Ice</v>
+        <v>Packaging</v>
       </c>
       <c r="E24" t="str">
-        <v>Police fees -2000 2 head</v>
+        <v>Unknown</v>
       </c>
       <c r="F24">
-        <v>4290</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>01/01/2026</v>
+        <v>14/01/2026</v>
       </c>
       <c r="B25" t="str">
-        <v>May26</v>
+        <v>Jan26</v>
       </c>
       <c r="C25" t="str">
         <v>COGS</v>
       </c>
       <c r="D25" t="str">
-        <v>Apple/Melon</v>
+        <v>Watermelon</v>
       </c>
       <c r="E25" t="str">
-        <v>แอปเปิ้ล 4 ลังครับ</v>
+        <v>แตงโม 40ลูก</v>
       </c>
       <c r="F25">
-        <v>1400</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>01/01/2026</v>
+        <v>14/01/2026</v>
       </c>
       <c r="B26" t="str">
-        <v>May26</v>
+        <v>Jan26</v>
       </c>
       <c r="C26" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D26" t="str">
-        <v>Other</v>
+        <v>Orange</v>
       </c>
       <c r="E26" t="str">
-        <v>36*18 648</v>
+        <v>ส้ม 20 ตะกร้า</v>
       </c>
       <c r="F26">
-        <v>648</v>
+        <v>6680</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>01/01/2026</v>
+        <v>14/01/2026</v>
       </c>
       <c r="B27" t="str">
-        <v>May26</v>
+        <v>Jan26</v>
       </c>
       <c r="C27" t="str">
         <v>COGS</v>
       </c>
       <c r="D27" t="str">
-        <v>Coconut</v>
+        <v>Orange</v>
       </c>
       <c r="E27" t="str">
-        <v>มะพร้าว 20 โล</v>
+        <v>ค่าส่งส้มมาบทท</v>
       </c>
       <c r="F27">
-        <v>2400</v>
+        <v>675</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>01/01/2026</v>
+        <v>17/01/2026</v>
       </c>
       <c r="B28" t="str">
-        <v>May26</v>
+        <v>Jan26</v>
       </c>
       <c r="C28" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D28" t="str">
-        <v>Other</v>
+        <v>Transportation</v>
       </c>
       <c r="E28" t="str">
         <v>Unknown</v>
       </c>
       <c r="F28">
-        <v>1050</v>
+        <v>400</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>01/01/2026</v>
+        <v>17/01/2026</v>
       </c>
       <c r="B29" t="str">
-        <v>May26</v>
+        <v>Jan26</v>
       </c>
       <c r="C29" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D29" t="str">
-        <v>Other</v>
+        <v>Watermelon</v>
       </c>
       <c r="E29" t="str">
-        <v>14/05/26 18 ลูก 504 บาท 16/05/26 18 ลูก</v>
+        <v>แตงโม 40 ลูก</v>
       </c>
       <c r="F29">
-        <v>1008</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>01/01/2026</v>
+        <v>17/01/2026</v>
       </c>
       <c r="B30" t="str">
-        <v>May26</v>
+        <v>Jan26</v>
       </c>
       <c r="C30" t="str">
         <v>COGS</v>
       </c>
       <c r="D30" t="str">
-        <v>Mango</v>
+        <v>Ice</v>
       </c>
       <c r="E30" t="str">
-        <v>มะม่วง 1</v>
+        <v>Unknown</v>
       </c>
       <c r="F30">
-        <v>875</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>01/01/2026</v>
+        <v>19/01/2026</v>
       </c>
       <c r="B31" t="str">
-        <v>May26</v>
+        <v>Jan26</v>
       </c>
       <c r="C31" t="str">
         <v>COGS</v>
       </c>
       <c r="D31" t="str">
-        <v>Orange</v>
+        <v>Transportation</v>
       </c>
       <c r="E31" t="str">
-        <v>15/05/69</v>
+        <v>ค่าขนส่ง</v>
       </c>
       <c r="F31">
-        <v>15730</v>
+        <v>349</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>01/01/2026</v>
+        <v>20/01/2026</v>
       </c>
       <c r="B32" t="str">
-        <v>May26</v>
+        <v>Jan26</v>
       </c>
       <c r="C32" t="str">
         <v>COGS</v>
       </c>
       <c r="D32" t="str">
-        <v>Orange</v>
+        <v>Transportation</v>
       </c>
       <c r="E32" t="str">
-        <v>05/05/69 ส้ม 30x22กก 660กกx30</v>
+        <v>Unknown</v>
       </c>
       <c r="F32">
-        <v>21450</v>
+        <v>400</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>01/01/2026</v>
+        <v>20/01/2026</v>
       </c>
       <c r="B33" t="str">
-        <v>May26</v>
+        <v>Jan26</v>
       </c>
       <c r="C33" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D33" t="str">
-        <v>Other</v>
+        <v>Packaging</v>
       </c>
       <c r="E33" t="str">
-        <v>11-5-2569 50 ลูก ยอด 4,000</v>
+        <v>แก้วฝา 2</v>
       </c>
       <c r="F33">
-        <v>8000</v>
+        <v>2702</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>01/01/2026</v>
+        <v>20/01/2026</v>
       </c>
       <c r="B34" t="str">
-        <v>May26</v>
+        <v>Jan26</v>
       </c>
       <c r="C34" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D34" t="str">
-        <v>Fixed Costs</v>
+        <v>Watermelon</v>
       </c>
       <c r="E34" t="str">
-        <v>ค่าเช่า+สต๊อกร้าน 1</v>
+        <v>แตงโม 40</v>
       </c>
       <c r="F34">
-        <v>47000</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>01/01/2026</v>
+        <v>21/01/2026</v>
       </c>
       <c r="B35" t="str">
-        <v>May26</v>
+        <v>Jan26</v>
       </c>
       <c r="C35" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D35" t="str">
-        <v>Other</v>
+        <v>Transportation</v>
       </c>
       <c r="E35" t="str">
-        <v>ฝรั่ง 1 ตะกร้า</v>
+        <v>ค่าขนส่ง</v>
       </c>
       <c r="F35">
-        <v>600</v>
+        <v>675</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>01/01/2026</v>
+        <v>23/01/2026</v>
       </c>
       <c r="B36" t="str">
-        <v>May26</v>
+        <v>Jan26</v>
       </c>
       <c r="C36" t="str">
         <v>COGS</v>
       </c>
       <c r="D36" t="str">
-        <v>Apple/Melon</v>
+        <v>Orange</v>
       </c>
       <c r="E36" t="str">
-        <v>แอปเปิ้ล 3 ลัง</v>
+        <v>ค่าส้ม20ตะกร้า</v>
       </c>
       <c r="F36">
-        <v>1050</v>
+        <v>7120</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>01/01/2026</v>
+        <v>23/01/2026</v>
       </c>
       <c r="B37" t="str">
-        <v>May26</v>
+        <v>Jan26</v>
       </c>
       <c r="C37" t="str">
         <v>COGS</v>
       </c>
       <c r="D37" t="str">
-        <v>Mango</v>
+        <v>Transportation</v>
       </c>
       <c r="E37" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>Unknown</v>
       </c>
       <c r="F37">
-        <v>875</v>
+        <v>400</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>01/01/2026</v>
+        <v>23/01/2026</v>
       </c>
       <c r="B38" t="str">
-        <v>May26</v>
+        <v>Jan26</v>
       </c>
       <c r="C38" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D38" t="str">
-        <v>Other</v>
+        <v>Transportation</v>
       </c>
       <c r="E38" t="str">
-        <v>ที่หนีบ 6ตัว 374 บาท</v>
+        <v>Unknown</v>
       </c>
       <c r="F38">
-        <v>374</v>
+        <v>400</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>01/01/2026</v>
+        <v>23/01/2026</v>
       </c>
       <c r="B39" t="str">
-        <v>May26</v>
+        <v>Jan26</v>
       </c>
       <c r="C39" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D39" t="str">
-        <v>Other</v>
+        <v>Watermelon</v>
       </c>
       <c r="E39" t="str">
-        <v>ฝรั่ง 1 ตะกร้า</v>
+        <v>แตงโม 40 ลูก</v>
       </c>
       <c r="F39">
-        <v>600</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>01/01/2026</v>
+        <v>25/01/2026</v>
       </c>
       <c r="B40" t="str">
-        <v>May26</v>
+        <v>Jan26</v>
       </c>
       <c r="C40" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D40" t="str">
-        <v>Other</v>
+        <v>Orange</v>
       </c>
       <c r="E40" t="str">
-        <v>09/05/26 สับปะรด 2 ตะกร้า</v>
+        <v>ส้ม5ตะกร้า แตงโม 40 ลูก</v>
       </c>
       <c r="F40">
-        <v>1008</v>
+        <v>5950</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>01/01/2026</v>
+        <v>25/01/2026</v>
       </c>
       <c r="B41" t="str">
-        <v>May26</v>
+        <v>Jan26</v>
       </c>
       <c r="C41" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D41" t="str">
-        <v>Other</v>
+        <v>Transportation</v>
       </c>
       <c r="E41" t="str">
-        <v>ฝรั่ง 1 ตะกร้า</v>
+        <v>ค่าส่งฝา</v>
       </c>
       <c r="F41">
-        <v>600</v>
+        <v>114</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>01/01/2026</v>
+        <v>26/01/2026</v>
       </c>
       <c r="B42" t="str">
-        <v>May26</v>
+        <v>Jan26</v>
       </c>
       <c r="C42" t="str">
         <v>COGS</v>
       </c>
       <c r="D42" t="str">
-        <v>Coconut</v>
+        <v>Orange</v>
       </c>
       <c r="E42" t="str">
-        <v>เนื้อมะพร้าว 1 ลัง</v>
+        <v>ค่าส้ม 30 ตะกร้า</v>
       </c>
       <c r="F42">
-        <v>3500</v>
+        <v>10680</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>01/01/2026</v>
+        <v>26/01/2026</v>
       </c>
       <c r="B43" t="str">
-        <v>May26</v>
+        <v>Jan26</v>
       </c>
       <c r="C43" t="str">
         <v>COGS</v>
       </c>
       <c r="D43" t="str">
-        <v>Mango</v>
+        <v>Transportation</v>
       </c>
       <c r="E43" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>Unknown</v>
       </c>
       <c r="F43">
-        <v>910</v>
+        <v>400</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>01/01/2026</v>
+        <v>26/01/2026</v>
       </c>
       <c r="B44" t="str">
-        <v>May26</v>
+        <v>Jan26</v>
       </c>
       <c r="C44" t="str">
         <v>COGS</v>
       </c>
       <c r="D44" t="str">
-        <v>Watermelon</v>
+        <v>Transportation</v>
       </c>
       <c r="E44" t="str">
-        <v>แตงโม 4000 วันที่ 9-5-26</v>
+        <v>Unknown</v>
       </c>
       <c r="F44">
-        <v>4000</v>
+        <v>400</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>01/01/2026</v>
+        <v>27/01/2026</v>
       </c>
       <c r="B45" t="str">
-        <v>May26</v>
+        <v>Jan26</v>
       </c>
       <c r="C45" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D45" t="str">
-        <v>Other</v>
+        <v>Packaging</v>
       </c>
       <c r="E45" t="str">
-        <v>ไฟ 2อัน 422</v>
+        <v>ถุงมือ - 5 กล่อง</v>
       </c>
       <c r="F45">
-        <v>838</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>01/01/2026</v>
+        <v>28/01/2026</v>
       </c>
       <c r="B46" t="str">
-        <v>May26</v>
+        <v>Jan26</v>
       </c>
       <c r="C46" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D46" t="str">
-        <v>Other</v>
+        <v>Transportation</v>
       </c>
       <c r="E46" t="str">
-        <v>พรหมเช็ดเท้า 1 ผืน</v>
+        <v>ค่าส่ง</v>
       </c>
       <c r="F46">
-        <v>372</v>
+        <v>486</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>01/01/2026</v>
+        <v>28/01/2026</v>
       </c>
       <c r="B47" t="str">
-        <v>May26</v>
+        <v>Jan26</v>
       </c>
       <c r="C47" t="str">
         <v>COGS</v>
       </c>
       <c r="D47" t="str">
-        <v>Milk/Conden</v>
+        <v>Transportation</v>
       </c>
       <c r="E47" t="str">
-        <v>นมข้นจืด 1ลัง 636</v>
+        <v>Unknown</v>
       </c>
       <c r="F47">
-        <v>1122</v>
+        <v>400</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>01/01/2026</v>
+        <v>28/01/2026</v>
       </c>
       <c r="B48" t="str">
-        <v>May26</v>
+        <v>Jan26</v>
       </c>
       <c r="C48" t="str">
         <v>COGS</v>
       </c>
       <c r="D48" t="str">
-        <v>Packaging</v>
+        <v>Watermelon</v>
       </c>
       <c r="E48" t="str">
-        <v>นมข้น 3 ลัง 2568</v>
+        <v>ค่าแตงโม 50 ลูก</v>
       </c>
       <c r="F48">
-        <v>4875</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>01/01/2026</v>
+        <v>28/01/2026</v>
       </c>
       <c r="B49" t="str">
-        <v>May26</v>
+        <v>Jan26</v>
       </c>
       <c r="C49" t="str">
-        <v>CAPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D49" t="str">
-        <v>Investment</v>
+        <v>Transportation</v>
       </c>
       <c r="E49" t="str">
-        <v>เครื่องสกัดเย็น 1</v>
+        <v>Unknown</v>
       </c>
       <c r="F49">
-        <v>1065</v>
+        <v>400</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>01/01/2026</v>
+        <v>28/01/2026</v>
       </c>
       <c r="B50" t="str">
-        <v>May26</v>
+        <v>Jan26</v>
       </c>
       <c r="C50" t="str">
         <v>COGS</v>
       </c>
       <c r="D50" t="str">
-        <v>Packaging</v>
+        <v>Transportation</v>
       </c>
       <c r="E50" t="str">
-        <v>แก้ว3ลัง 5,301</v>
+        <v>ค่าส่ง</v>
       </c>
       <c r="F50">
-        <v>6132</v>
+        <v>486</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>01/01/2026</v>
+        <v>28/01/2026</v>
       </c>
       <c r="B51" t="str">
-        <v>May26</v>
+        <v>Jan26</v>
       </c>
       <c r="C51" t="str">
         <v>COGS</v>
       </c>
       <c r="D51" t="str">
-        <v>Packaging</v>
+        <v>Watermelon</v>
       </c>
       <c r="E51" t="str">
-        <v>ถุงมือ 20 กล่อง 2246 ฝา1ลัง 969</v>
+        <v>แตงโม 50 ลูก</v>
       </c>
       <c r="F51">
-        <v>4496</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>01/01/2026</v>
+        <v>30/01/2026</v>
       </c>
       <c r="B52" t="str">
-        <v>May26</v>
+        <v>Jan26</v>
       </c>
       <c r="C52" t="str">
         <v>COGS</v>
       </c>
       <c r="D52" t="str">
-        <v>Transportation</v>
+        <v>Watermelon</v>
       </c>
       <c r="E52" t="str">
-        <v>Lalamove</v>
+        <v>แตงโม 25 ลูก</v>
       </c>
       <c r="F52">
         <v>2000</v>
@@ -2177,170 +2177,170 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>01/01/2026</v>
+        <v>30/01/2026</v>
       </c>
       <c r="B53" t="str">
-        <v>May26</v>
+        <v>Jan26</v>
       </c>
       <c r="C53" t="str">
         <v>COGS</v>
       </c>
       <c r="D53" t="str">
-        <v>Transportation</v>
+        <v>Apple</v>
       </c>
       <c r="E53" t="str">
-        <v>น้ำ 20 ขวด 900 ถอดเสื้อ 30 ลูก750 กล่องโฟม 3</v>
+        <v>แอปเปิ้ล เมล่อน</v>
       </c>
       <c r="F53">
-        <v>4555</v>
+        <v>851</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>01/01/2026</v>
+        <v>31/01/2026</v>
       </c>
       <c r="B54" t="str">
-        <v>May26</v>
+        <v>Jan26</v>
       </c>
       <c r="C54" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D54" t="str">
-        <v>Water</v>
+        <v>Salary</v>
       </c>
       <c r="E54" t="str">
-        <v>น้ำมะร้าว 1 ลัง</v>
+        <v>เงินเดือนเมนมกราคม</v>
       </c>
       <c r="F54">
-        <v>1100</v>
+        <v>19000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>01/01/2026</v>
+        <v>02/02/2026</v>
       </c>
       <c r="B55" t="str">
-        <v>May26</v>
+        <v>Feb26</v>
       </c>
       <c r="C55" t="str">
         <v>COGS</v>
       </c>
       <c r="D55" t="str">
-        <v>Packaging</v>
+        <v>Orange</v>
       </c>
       <c r="E55" t="str">
-        <v>6 พ.ค. น้ำ 30 ขวด 1500 บาท เนื้อ 11 โล 1320 บาท</v>
+        <v>ส้ม 30 ตะกร้า</v>
       </c>
       <c r="F55">
-        <v>2820</v>
+        <v>10680</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>01/01/2026</v>
+        <v>02/02/2026</v>
       </c>
       <c r="B56" t="str">
-        <v>May26</v>
+        <v>Feb26</v>
       </c>
       <c r="C56" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D56" t="str">
-        <v>Other</v>
+        <v>Watermelon</v>
       </c>
       <c r="E56" t="str">
-        <v>ค่าทำความสะอาดตึกชั้น 1</v>
+        <v>แตงโม 50 ลูก</v>
       </c>
       <c r="F56">
-        <v>2700</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>01/01/2026</v>
+        <v>02/02/2026</v>
       </c>
       <c r="B57" t="str">
-        <v>May26</v>
+        <v>Feb26</v>
       </c>
       <c r="C57" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D57" t="str">
-        <v>Other</v>
+        <v>Transportation</v>
       </c>
       <c r="E57" t="str">
-        <v>4-5-2569 เบอร์ 70฿ 60 ลูก ยอด 4,200</v>
+        <v>Unknown</v>
       </c>
       <c r="F57">
-        <v>8200</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>01/01/2026</v>
+        <v>04/02/2026</v>
       </c>
       <c r="B58" t="str">
-        <v>May26</v>
+        <v>Feb26</v>
       </c>
       <c r="C58" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D58" t="str">
-        <v>Other</v>
+        <v>Packaging</v>
       </c>
       <c r="E58" t="str">
-        <v>ทิชชู่3แพค 36ห่อ</v>
+        <v>ฝา 690 1000 ชิ้น แก้ว 1196 1000 ชิ้น หลอด 421</v>
       </c>
       <c r="F58">
-        <v>451</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>01/01/2026</v>
+        <v>05/02/2026</v>
       </c>
       <c r="B59" t="str">
-        <v>May26</v>
+        <v>Feb26</v>
       </c>
       <c r="C59" t="str">
         <v>COGS</v>
       </c>
       <c r="D59" t="str">
-        <v>Coconut</v>
+        <v>Watermelon</v>
       </c>
       <c r="E59" t="str">
-        <v>มะพร้าวถอดเสื้อ 23 ลูก *35 ราคา 805 ค่าส่ง 150</v>
+        <v>แตงโม 50 ลูก</v>
       </c>
       <c r="F59">
-        <v>955</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>01/01/2026</v>
+        <v>05/02/2026</v>
       </c>
       <c r="B60" t="str">
-        <v>May26</v>
+        <v>Feb26</v>
       </c>
       <c r="C60" t="str">
         <v>COGS</v>
       </c>
       <c r="D60" t="str">
-        <v>Mango</v>
+        <v>Packaging</v>
       </c>
       <c r="E60" t="str">
-        <v>มะม่วง 2 ลัง</v>
+        <v>แก้วสกรีน อย่างเดียวไม่รวมฝา 2280บาท</v>
       </c>
       <c r="F60">
-        <v>1750</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>01/01/2026</v>
+        <v>08/02/2026</v>
       </c>
       <c r="B61" t="str">
-        <v>May26</v>
+        <v>Feb26</v>
       </c>
       <c r="C61" t="str">
         <v>COGS</v>
@@ -2349,158 +2349,158 @@
         <v>Ice</v>
       </c>
       <c r="E61" t="str">
-        <v>สับปะรด 18 ลูก</v>
+        <v>Unknown</v>
       </c>
       <c r="F61">
-        <v>486</v>
+        <v>798</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>01/01/2026</v>
+        <v>08/02/2026</v>
       </c>
       <c r="B62" t="str">
-        <v>May26</v>
+        <v>Feb26</v>
       </c>
       <c r="C62" t="str">
         <v>COGS</v>
       </c>
       <c r="D62" t="str">
-        <v>Apple/Melon</v>
+        <v>Watermelon</v>
       </c>
       <c r="E62" t="str">
-        <v>แอปเปิ้ล 4 ลัง</v>
+        <v>แตงโม 50</v>
       </c>
       <c r="F62">
-        <v>1400</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>01/01/2026</v>
+        <v>08/02/2026</v>
       </c>
       <c r="B63" t="str">
-        <v>May26</v>
+        <v>Feb26</v>
       </c>
       <c r="C63" t="str">
         <v>COGS</v>
       </c>
       <c r="D63" t="str">
-        <v>Packaging</v>
+        <v>Transportation</v>
       </c>
       <c r="E63" t="str">
-        <v>ถุงมือ4อัน</v>
+        <v>Unknown</v>
       </c>
       <c r="F63">
-        <v>499</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>01/01/2026</v>
+        <v>09/02/2026</v>
       </c>
       <c r="B64" t="str">
-        <v>May26</v>
+        <v>Feb26</v>
       </c>
       <c r="C64" t="str">
         <v>COGS</v>
       </c>
       <c r="D64" t="str">
-        <v>Apple/Melon</v>
+        <v>Orange</v>
       </c>
       <c r="E64" t="str">
-        <v>แอปเปิ้ล 4 ลัง</v>
+        <v>ส้ม 30 ตะกร้า</v>
       </c>
       <c r="F64">
-        <v>1400</v>
+        <v>10680</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>01/01/2026</v>
+        <v>09/02/2026</v>
       </c>
       <c r="B65" t="str">
-        <v>May26</v>
+        <v>Feb26</v>
       </c>
       <c r="C65" t="str">
         <v>COGS</v>
       </c>
       <c r="D65" t="str">
-        <v>Mango</v>
+        <v>Orange</v>
       </c>
       <c r="E65" t="str">
-        <v>มะม่วง 2 ลัง</v>
+        <v>ค่าส่งส้ม</v>
       </c>
       <c r="F65">
-        <v>1680</v>
+        <v>685</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>01/01/2026</v>
+        <v>10/02/2026</v>
       </c>
       <c r="B66" t="str">
-        <v>May26</v>
+        <v>Feb26</v>
       </c>
       <c r="C66" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D66" t="str">
-        <v>Other</v>
+        <v>Ice</v>
       </c>
       <c r="E66" t="str">
-        <v>30-4-2569 เบอร์ 70฿ 60 ลูก</v>
+        <v>ค่าไฟเดือนมค</v>
       </c>
       <c r="F66">
-        <v>7000</v>
+        <v>389</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>01/01/2026</v>
+        <v>11/02/2026</v>
       </c>
       <c r="B67" t="str">
-        <v>May26</v>
+        <v>Feb26</v>
       </c>
       <c r="C67" t="str">
         <v>COGS</v>
       </c>
       <c r="D67" t="str">
-        <v>Mango</v>
+        <v>Watermelon</v>
       </c>
       <c r="E67" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>แตงโม 50 ลูก</v>
       </c>
       <c r="F67">
-        <v>910</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>01/01/2026</v>
+        <v>14/02/2026</v>
       </c>
       <c r="B68" t="str">
-        <v>May26</v>
+        <v>Feb26</v>
       </c>
       <c r="C68" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D68" t="str">
-        <v>Apple/Melon</v>
+        <v>Other</v>
       </c>
       <c r="E68" t="str">
-        <v>แอปเปิ้ล 4 ลัง</v>
+        <v>Unknown</v>
       </c>
       <c r="F68">
-        <v>1500</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>01/01/2026</v>
+        <v>14/02/2026</v>
       </c>
       <c r="B69" t="str">
-        <v>May26</v>
+        <v>Feb26</v>
       </c>
       <c r="C69" t="str">
         <v>COGS</v>
@@ -2509,278 +2509,278 @@
         <v>Ice</v>
       </c>
       <c r="E69" t="str">
-        <v>สับปะรด 30 ลูก</v>
+        <v>Unknown</v>
       </c>
       <c r="F69">
-        <v>1116</v>
+        <v>350</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>01/01/2026</v>
+        <v>16/02/2026</v>
       </c>
       <c r="B70" t="str">
-        <v>May26</v>
+        <v>Feb26</v>
       </c>
       <c r="C70" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D70" t="str">
-        <v>Salary</v>
+        <v>Orange</v>
       </c>
       <c r="E70" t="str">
-        <v>เงินเดือนเมน 5/26</v>
+        <v>ค่าส่งส้ม</v>
       </c>
       <c r="F70">
-        <v>19000</v>
+        <v>485</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>01/01/2026</v>
+        <v>16/02/2026</v>
       </c>
       <c r="B71" t="str">
-        <v>May26</v>
+        <v>Feb26</v>
       </c>
       <c r="C71" t="str">
         <v>COGS</v>
       </c>
       <c r="D71" t="str">
-        <v>Ice</v>
+        <v>Orange</v>
       </c>
       <c r="E71" t="str">
-        <v>ค่าหาหมอเอ</v>
+        <v>ค่าส้ม 30 ตะกร้า 13/2/69</v>
       </c>
       <c r="F71">
-        <v>706</v>
+        <v>10680</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>01/01/2026</v>
+        <v>19/02/2026</v>
       </c>
       <c r="B72" t="str">
-        <v>May26</v>
+        <v>Feb26</v>
       </c>
       <c r="C72" t="str">
         <v>COGS</v>
       </c>
       <c r="D72" t="str">
-        <v>Ice</v>
+        <v>Watermelon</v>
       </c>
       <c r="E72" t="str">
-        <v>ค่าหมอเอ</v>
+        <v>แตงโม 50 ลูก วันที่ 1719</v>
       </c>
       <c r="F72">
-        <v>13</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>01/01/2026</v>
+        <v>19/02/2026</v>
       </c>
       <c r="B73" t="str">
-        <v>May26</v>
+        <v>Feb26</v>
       </c>
       <c r="C73" t="str">
         <v>COGS</v>
       </c>
       <c r="D73" t="str">
-        <v>Water</v>
+        <v>Packaging</v>
       </c>
       <c r="E73" t="str">
-        <v>ร่ม 1176 ร่ม 843 ฝรั่ง 300 นมข้นจืด 785 ที่ปั้ม 176</v>
+        <v>แก้ว</v>
       </c>
       <c r="F73">
-        <v>7823</v>
+        <v>3315</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>01/01/2026</v>
+        <v>19/02/2026</v>
       </c>
       <c r="B74" t="str">
-        <v>May26</v>
+        <v>Feb26</v>
       </c>
       <c r="C74" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D74" t="str">
-        <v>Other</v>
+        <v>Transportation</v>
       </c>
       <c r="E74" t="str">
-        <v>ฝรั่ง 1 ตะกร้า</v>
+        <v>แก้วสกรีน2ลัง(รอบที่1นะ แบ่งสั่งจะได้ไม่มีค่า</v>
       </c>
       <c r="F74">
-        <v>600</v>
+        <v>6655</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>01/01/2026</v>
+        <v>19/02/2026</v>
       </c>
       <c r="B75" t="str">
-        <v>May26</v>
+        <v>Feb26</v>
       </c>
       <c r="C75" t="str">
         <v>COGS</v>
       </c>
       <c r="D75" t="str">
-        <v>Mango</v>
+        <v>Transportation</v>
       </c>
       <c r="E75" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>Unknown</v>
       </c>
       <c r="F75">
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>02/01/2026</v>
+        <v>20/02/2026</v>
       </c>
       <c r="B76" t="str">
-        <v>Jan26</v>
+        <v>Feb26</v>
       </c>
       <c r="C76" t="str">
         <v>COGS</v>
       </c>
       <c r="D76" t="str">
-        <v>Packaging</v>
+        <v>Ice</v>
       </c>
       <c r="E76" t="str">
-        <v>แก้ว หลอด</v>
+        <v>ผ้าปิดร้าน 218 ค่ารถ 198</v>
       </c>
       <c r="F76">
-        <v>2165</v>
+        <v>416</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>02/01/2026</v>
+        <v>23/02/2026</v>
       </c>
       <c r="B77" t="str">
-        <v>Jan26</v>
+        <v>Feb26</v>
       </c>
       <c r="C77" t="str">
         <v>COGS</v>
       </c>
       <c r="D77" t="str">
-        <v>Ice</v>
+        <v>Watermelon</v>
       </c>
       <c r="E77" t="str">
-        <v>ส่วนแบ่ง60เปอ</v>
+        <v>แตงโม 21 50 ลูก 23 50 ลูก</v>
       </c>
       <c r="F77">
-        <v>47961</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>02/01/2026</v>
+        <v>24/02/2026</v>
       </c>
       <c r="B78" t="str">
-        <v>Jan26</v>
+        <v>Feb26</v>
       </c>
       <c r="C78" t="str">
         <v>COGS</v>
       </c>
       <c r="D78" t="str">
-        <v>Ice</v>
+        <v>Transportation</v>
       </c>
       <c r="E78" t="str">
-        <v>ค่าส่วนแบ่งกำไรเมน 40เปอ</v>
+        <v>Unknown</v>
       </c>
       <c r="F78">
-        <v>32000</v>
+        <v>209</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>02/01/2026</v>
+        <v>24/02/2026</v>
       </c>
       <c r="B79" t="str">
-        <v>Jan26</v>
+        <v>Feb26</v>
       </c>
       <c r="C79" t="str">
         <v>COGS</v>
       </c>
       <c r="D79" t="str">
-        <v>Transportation</v>
+        <v>Orange</v>
       </c>
       <c r="E79" t="str">
-        <v>Unknown</v>
+        <v>ส้ม 30 18/2/69</v>
       </c>
       <c r="F79">
-        <v>400</v>
+        <v>10680</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>03/01/2026</v>
+        <v>24/02/2026</v>
       </c>
       <c r="B80" t="str">
-        <v>Jan26</v>
+        <v>Feb26</v>
       </c>
       <c r="C80" t="str">
         <v>COGS</v>
       </c>
       <c r="D80" t="str">
-        <v>Watermelon</v>
+        <v>Packaging</v>
       </c>
       <c r="E80" t="str">
-        <v>แตงโม 60 ลูก</v>
+        <v>แก้ว 2400 ฝา 1670</v>
       </c>
       <c r="F80">
-        <v>4000</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>04/01/2026</v>
+        <v>25/02/2026</v>
       </c>
       <c r="B81" t="str">
-        <v>Jan26</v>
+        <v>Feb26</v>
       </c>
       <c r="C81" t="str">
         <v>COGS</v>
       </c>
       <c r="D81" t="str">
-        <v>Transportation</v>
+        <v>Watermelon</v>
       </c>
       <c r="E81" t="str">
-        <v>ค่าส่งแก้ว</v>
+        <v>แตงโม 50</v>
       </c>
       <c r="F81">
-        <v>198</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>06/01/2026</v>
+        <v>25/02/2026</v>
       </c>
       <c r="B82" t="str">
-        <v>Jan26</v>
+        <v>Feb26</v>
       </c>
       <c r="C82" t="str">
         <v>COGS</v>
       </c>
       <c r="D82" t="str">
-        <v>Orange</v>
+        <v>Transportation</v>
       </c>
       <c r="E82" t="str">
-        <v>ค่าส้ม 5720 ค่าส่งส้ม 960</v>
+        <v>Unknown</v>
       </c>
       <c r="F82">
-        <v>6680</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>06/01/2026</v>
+        <v>25/02/2026</v>
       </c>
       <c r="B83" t="str">
-        <v>Jan26</v>
+        <v>Feb26</v>
       </c>
       <c r="C83" t="str">
         <v>COGS</v>
@@ -2789,398 +2789,398 @@
         <v>Orange</v>
       </c>
       <c r="E83" t="str">
-        <v>ค่าส่งส้มมาบทท</v>
+        <v>ส้ม20 ตะกร้า</v>
       </c>
       <c r="F83">
-        <v>375</v>
+        <v>7312</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>07/01/2026</v>
+        <v>25/02/2026</v>
       </c>
       <c r="B84" t="str">
-        <v>Jan26</v>
+        <v>Feb26</v>
       </c>
       <c r="C84" t="str">
         <v>COGS</v>
       </c>
       <c r="D84" t="str">
-        <v>Transportation</v>
+        <v>Orange</v>
       </c>
       <c r="E84" t="str">
-        <v>Unknown</v>
+        <v>ค่าส่งส้ม</v>
       </c>
       <c r="F84">
-        <v>400</v>
+        <v>806</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>08/01/2026</v>
+        <v>26/02/2026</v>
       </c>
       <c r="B85" t="str">
-        <v>Jan26</v>
+        <v>Feb26</v>
       </c>
       <c r="C85" t="str">
         <v>COGS</v>
       </c>
       <c r="D85" t="str">
-        <v>Ice</v>
+        <v>Packaging</v>
       </c>
       <c r="E85" t="str">
-        <v>ค่าเช่า12,000 น้ำไฟ324 รวม12,324</v>
+        <v>ค่าขวดใหญ่</v>
       </c>
       <c r="F85">
-        <v>12324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>08/01/2026</v>
+        <v>28/02/2026</v>
       </c>
       <c r="B86" t="str">
-        <v>Jan26</v>
+        <v>Feb26</v>
       </c>
       <c r="C86" t="str">
         <v>COGS</v>
       </c>
       <c r="D86" t="str">
-        <v>Transportation</v>
+        <v>Orange</v>
       </c>
       <c r="E86" t="str">
-        <v>Unknown</v>
+        <v>ค่าส่งส้ม</v>
       </c>
       <c r="F86">
-        <v>400</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>09/01/2026</v>
+        <v>28/02/2026</v>
       </c>
       <c r="B87" t="str">
-        <v>Jan26</v>
+        <v>Feb26</v>
       </c>
       <c r="C87" t="str">
         <v>COGS</v>
       </c>
       <c r="D87" t="str">
-        <v>Transportation</v>
+        <v>Orange</v>
       </c>
       <c r="E87" t="str">
-        <v>Unknown</v>
+        <v>ค่าส่งส้ม</v>
       </c>
       <c r="F87">
-        <v>400</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>09/01/2026</v>
+        <v>28/02/2026</v>
       </c>
       <c r="B88" t="str">
-        <v>Jan26</v>
+        <v>Feb26</v>
       </c>
       <c r="C88" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D88" t="str">
-        <v>Ice</v>
+        <v>Rental</v>
       </c>
       <c r="E88" t="str">
-        <v>ค่าขนตะกร้ากลับ</v>
+        <v>ค่าเช่าสต็อคกพ</v>
       </c>
       <c r="F88">
-        <v>500</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>11/01/2026</v>
+        <v>28/02/2026</v>
       </c>
       <c r="B89" t="str">
-        <v>Jan26</v>
+        <v>Feb26</v>
       </c>
       <c r="C89" t="str">
         <v>COGS</v>
       </c>
       <c r="D89" t="str">
-        <v>Packaging</v>
+        <v>Watermelon</v>
       </c>
       <c r="E89" t="str">
-        <v>ขวดใหญ่ 98 ใบ</v>
+        <v>แตงโม 50 ลูก</v>
       </c>
       <c r="F89">
-        <v>319</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>11/01/2026</v>
+        <v>04/03/2026</v>
       </c>
       <c r="B90" t="str">
-        <v>Jan26</v>
+        <v>Mar26</v>
       </c>
       <c r="C90" t="str">
         <v>COGS</v>
       </c>
       <c r="D90" t="str">
-        <v>Orange</v>
+        <v>Watermelon</v>
       </c>
       <c r="E90" t="str">
-        <v>ค่าส่งส้มไปบทท</v>
+        <v>ค่าทางด่วนส่งแตงโม</v>
       </c>
       <c r="F90">
-        <v>461</v>
+        <v>140</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>11/01/2026</v>
+        <v>04/03/2026</v>
       </c>
       <c r="B91" t="str">
-        <v>Jan26</v>
+        <v>Mar26</v>
       </c>
       <c r="C91" t="str">
         <v>COGS</v>
       </c>
       <c r="D91" t="str">
-        <v>Orange</v>
+        <v>Mango</v>
       </c>
       <c r="E91" t="str">
-        <v>ค่าส้ม20ลัง</v>
+        <v>มะม่วง 16 โล</v>
       </c>
       <c r="F91">
-        <v>6680</v>
+        <v>560</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>11/01/2026</v>
+        <v>05/03/2026</v>
       </c>
       <c r="B92" t="str">
-        <v>Jan26</v>
+        <v>Feb26</v>
       </c>
       <c r="C92" t="str">
         <v>COGS</v>
       </c>
       <c r="D92" t="str">
-        <v>Transportation</v>
+        <v>Mango</v>
       </c>
       <c r="E92" t="str">
-        <v>Unknown</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F92">
-        <v>400</v>
+        <v>500</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>12/01/2026</v>
+        <v>05/03/2026</v>
       </c>
       <c r="B93" t="str">
-        <v>Jan26</v>
+        <v>Feb26</v>
       </c>
       <c r="C93" t="str">
         <v>COGS</v>
       </c>
       <c r="D93" t="str">
-        <v>Packaging</v>
+        <v>Orange</v>
       </c>
       <c r="E93" t="str">
-        <v>ถุงขยะ</v>
+        <v>ค่าส้มวันที่ 27269</v>
       </c>
       <c r="F93">
-        <v>548</v>
+        <v>7312</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>14/01/2026</v>
+        <v>05/03/2026</v>
       </c>
       <c r="B94" t="str">
-        <v>Jan26</v>
+        <v>Mar26</v>
       </c>
       <c r="C94" t="str">
         <v>COGS</v>
       </c>
       <c r="D94" t="str">
-        <v>Packaging</v>
+        <v>Orange</v>
       </c>
       <c r="E94" t="str">
-        <v>Unknown</v>
+        <v>แตงโม 51 ยอด3,500</v>
       </c>
       <c r="F94">
-        <v>1625</v>
+        <v>7700</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>14/01/2026</v>
+        <v>05/03/2026</v>
       </c>
       <c r="B95" t="str">
-        <v>Jan26</v>
+        <v>Mar26</v>
       </c>
       <c r="C95" t="str">
         <v>COGS</v>
       </c>
       <c r="D95" t="str">
-        <v>Watermelon</v>
+        <v>Orange</v>
       </c>
       <c r="E95" t="str">
-        <v>แตงโม 40ลูก</v>
+        <v>ค่าส้ม 20 ตะกร้า</v>
       </c>
       <c r="F95">
-        <v>3200</v>
+        <v>7312</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>14/01/2026</v>
+        <v>05/03/2026</v>
       </c>
       <c r="B96" t="str">
-        <v>Jan26</v>
+        <v>Mar26</v>
       </c>
       <c r="C96" t="str">
         <v>COGS</v>
       </c>
       <c r="D96" t="str">
-        <v>Orange</v>
+        <v>Ice</v>
       </c>
       <c r="E96" t="str">
-        <v>ส้ม 20 ตะกร้า</v>
+        <v>ค่าทางด่วน</v>
       </c>
       <c r="F96">
-        <v>6680</v>
+        <v>105</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>14/01/2026</v>
+        <v>05/03/2026</v>
       </c>
       <c r="B97" t="str">
-        <v>Jan26</v>
+        <v>Mar26</v>
       </c>
       <c r="C97" t="str">
         <v>COGS</v>
       </c>
       <c r="D97" t="str">
-        <v>Orange</v>
+        <v>Packaging</v>
       </c>
       <c r="E97" t="str">
-        <v>ค่าส่งส้มมาบทท</v>
+        <v>ถุงขยะ</v>
       </c>
       <c r="F97">
-        <v>675</v>
+        <v>909</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>17/01/2026</v>
+        <v>05/03/2026</v>
       </c>
       <c r="B98" t="str">
-        <v>Jan26</v>
+        <v>Mar26</v>
       </c>
       <c r="C98" t="str">
         <v>COGS</v>
       </c>
       <c r="D98" t="str">
-        <v>Transportation</v>
+        <v>Mango</v>
       </c>
       <c r="E98" t="str">
-        <v>Unknown</v>
+        <v>มะม่วง 24 โล</v>
       </c>
       <c r="F98">
-        <v>400</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>17/01/2026</v>
+        <v>07/03/2026</v>
       </c>
       <c r="B99" t="str">
-        <v>Jan26</v>
+        <v>Mar26</v>
       </c>
       <c r="C99" t="str">
         <v>COGS</v>
       </c>
       <c r="D99" t="str">
-        <v>Watermelon</v>
+        <v>Transportation</v>
       </c>
       <c r="E99" t="str">
-        <v>แตงโม 40 ลูก</v>
+        <v>Unknown</v>
       </c>
       <c r="F99">
-        <v>3200</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>17/01/2026</v>
+        <v>10/03/2026</v>
       </c>
       <c r="B100" t="str">
-        <v>Jan26</v>
+        <v>Mar26</v>
       </c>
       <c r="C100" t="str">
         <v>COGS</v>
       </c>
       <c r="D100" t="str">
-        <v>Ice</v>
+        <v>Orange</v>
       </c>
       <c r="E100" t="str">
-        <v>Unknown</v>
+        <v>09/03/69</v>
       </c>
       <c r="F100">
-        <v>60</v>
+        <v>9804</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>19/01/2026</v>
+        <v>10/03/2026</v>
       </c>
       <c r="B101" t="str">
-        <v>Jan26</v>
+        <v>Mar26</v>
       </c>
       <c r="C101" t="str">
         <v>COGS</v>
       </c>
       <c r="D101" t="str">
-        <v>Transportation</v>
+        <v>Watermelon</v>
       </c>
       <c r="E101" t="str">
-        <v>ค่าขนส่ง</v>
+        <v>แตงโม 50 วันที่ 7 แตงโม 50 วันที่ 10</v>
       </c>
       <c r="F101">
-        <v>349</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>20/01/2026</v>
+        <v>10/03/2026</v>
       </c>
       <c r="B102" t="str">
-        <v>Jan26</v>
+        <v>Mar26</v>
       </c>
       <c r="C102" t="str">
-        <v>COGS</v>
+        <v>CAPEX</v>
       </c>
       <c r="D102" t="str">
-        <v>Transportation</v>
+        <v>Investment</v>
       </c>
       <c r="E102" t="str">
         <v>Unknown</v>
       </c>
       <c r="F102">
-        <v>400</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>20/01/2026</v>
+        <v>10/03/2026</v>
       </c>
       <c r="B103" t="str">
-        <v>Jan26</v>
+        <v>Mar26</v>
       </c>
       <c r="C103" t="str">
         <v>COGS</v>
@@ -3189,118 +3189,118 @@
         <v>Packaging</v>
       </c>
       <c r="E103" t="str">
-        <v>แก้วฝา 2</v>
+        <v>แก้ว2ลัง ลังละ 1560</v>
       </c>
       <c r="F103">
-        <v>2702</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>20/01/2026</v>
+        <v>10/03/2026</v>
       </c>
       <c r="B104" t="str">
-        <v>Jan26</v>
+        <v>Mar26</v>
       </c>
       <c r="C104" t="str">
         <v>COGS</v>
       </c>
       <c r="D104" t="str">
-        <v>Watermelon</v>
+        <v>Orange</v>
       </c>
       <c r="E104" t="str">
-        <v>แตงโม 40</v>
+        <v>แก้วร้านน้ำส้ม 2ลัง ลังละ1560</v>
       </c>
       <c r="F104">
-        <v>3200</v>
+        <v>5667</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>21/01/2026</v>
+        <v>13/03/2026</v>
       </c>
       <c r="B105" t="str">
-        <v>Jan26</v>
+        <v>Mar26</v>
       </c>
       <c r="C105" t="str">
         <v>COGS</v>
       </c>
       <c r="D105" t="str">
-        <v>Transportation</v>
+        <v>Packaging</v>
       </c>
       <c r="E105" t="str">
-        <v>ค่าขนส่ง</v>
+        <v>หลอด 20 แพค</v>
       </c>
       <c r="F105">
-        <v>675</v>
+        <v>765</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>23/01/2026</v>
+        <v>14/03/2026</v>
       </c>
       <c r="B106" t="str">
-        <v>Jan26</v>
+        <v>Mar26</v>
       </c>
       <c r="C106" t="str">
         <v>COGS</v>
       </c>
       <c r="D106" t="str">
-        <v>Orange</v>
+        <v>Apple</v>
       </c>
       <c r="E106" t="str">
-        <v>ค่าส้ม20ตะกร้า</v>
+        <v>แอปเปิ้ลฟูจิ 32</v>
       </c>
       <c r="F106">
-        <v>7120</v>
+        <v>350</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>23/01/2026</v>
+        <v>14/03/2026</v>
       </c>
       <c r="B107" t="str">
-        <v>Jan26</v>
+        <v>Mar26</v>
       </c>
       <c r="C107" t="str">
         <v>COGS</v>
       </c>
       <c r="D107" t="str">
-        <v>Transportation</v>
+        <v>Mango</v>
       </c>
       <c r="E107" t="str">
-        <v>Unknown</v>
+        <v>มะม่วง 2 ลัง 44</v>
       </c>
       <c r="F107">
-        <v>400</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>23/01/2026</v>
+        <v>15/03/2026</v>
       </c>
       <c r="B108" t="str">
-        <v>Jan26</v>
+        <v>Mar26</v>
       </c>
       <c r="C108" t="str">
         <v>COGS</v>
       </c>
       <c r="D108" t="str">
-        <v>Transportation</v>
+        <v>Ice</v>
       </c>
       <c r="E108" t="str">
-        <v>Unknown</v>
+        <v>ค่าทางด่วน</v>
       </c>
       <c r="F108">
-        <v>400</v>
+        <v>115</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>23/01/2026</v>
+        <v>15/03/2026</v>
       </c>
       <c r="B109" t="str">
-        <v>Jan26</v>
+        <v>Mar26</v>
       </c>
       <c r="C109" t="str">
         <v>COGS</v>
@@ -3309,178 +3309,178 @@
         <v>Watermelon</v>
       </c>
       <c r="E109" t="str">
-        <v>แตงโม 40 ลูก</v>
+        <v>น้ำมะพร้าว 5ขวดเละ 50฿</v>
       </c>
       <c r="F109">
-        <v>3200</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>25/01/2026</v>
+        <v>17/03/2026</v>
       </c>
       <c r="B110" t="str">
-        <v>Jan26</v>
+        <v>Mar26</v>
       </c>
       <c r="C110" t="str">
         <v>COGS</v>
       </c>
       <c r="D110" t="str">
-        <v>Orange</v>
+        <v>Ice</v>
       </c>
       <c r="E110" t="str">
-        <v>ส้ม5ตะกร้า แตงโม 40 ลูก</v>
+        <v>ค่าไฟเดือนกพ มีนา</v>
       </c>
       <c r="F110">
-        <v>5950</v>
+        <v>2779.47</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>25/01/2026</v>
+        <v>19/03/2026</v>
       </c>
       <c r="B111" t="str">
-        <v>Jan26</v>
+        <v>Mar26</v>
       </c>
       <c r="C111" t="str">
         <v>COGS</v>
       </c>
       <c r="D111" t="str">
-        <v>Transportation</v>
+        <v>Watermelon</v>
       </c>
       <c r="E111" t="str">
-        <v>ค่าส่งฝา</v>
+        <v>ค่าแตงโม 18/3/67 51 ลูก 4000 บาท</v>
       </c>
       <c r="F111">
-        <v>114</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>26/01/2026</v>
+        <v>21/03/2026</v>
       </c>
       <c r="B112" t="str">
-        <v>Jan26</v>
+        <v>Mar26</v>
       </c>
       <c r="C112" t="str">
         <v>COGS</v>
       </c>
       <c r="D112" t="str">
-        <v>Orange</v>
+        <v>Ice</v>
       </c>
       <c r="E112" t="str">
-        <v>ค่าส้ม 30 ตะกร้า</v>
+        <v>สกรู กาวตะปู</v>
       </c>
       <c r="F112">
-        <v>10680</v>
+        <v>117</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>26/01/2026</v>
+        <v>23/03/2026</v>
       </c>
       <c r="B113" t="str">
-        <v>Jan26</v>
+        <v>Mar26</v>
       </c>
       <c r="C113" t="str">
         <v>COGS</v>
       </c>
       <c r="D113" t="str">
-        <v>Transportation</v>
+        <v>Mango</v>
       </c>
       <c r="E113" t="str">
-        <v>Unknown</v>
+        <v>มะม่วง 44 โล</v>
       </c>
       <c r="F113">
-        <v>400</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>26/01/2026</v>
+        <v>23/03/2026</v>
       </c>
       <c r="B114" t="str">
-        <v>Jan26</v>
+        <v>Mar26</v>
       </c>
       <c r="C114" t="str">
         <v>COGS</v>
       </c>
       <c r="D114" t="str">
-        <v>Transportation</v>
+        <v>Orange</v>
       </c>
       <c r="E114" t="str">
-        <v>Unknown</v>
+        <v>22-3-2569</v>
       </c>
       <c r="F114">
-        <v>400</v>
+        <v>5890</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>27/01/2026</v>
+        <v>24/03/2026</v>
       </c>
       <c r="B115" t="str">
-        <v>Jan26</v>
+        <v>Mar26</v>
       </c>
       <c r="C115" t="str">
         <v>COGS</v>
       </c>
       <c r="D115" t="str">
-        <v>Packaging</v>
+        <v>Ice</v>
       </c>
       <c r="E115" t="str">
-        <v>ถุงมือ - 5 กล่อง</v>
+        <v>รถเข็นของคันใหม่</v>
       </c>
       <c r="F115">
-        <v>1077</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>28/01/2026</v>
+        <v>28/03/2026</v>
       </c>
       <c r="B116" t="str">
-        <v>Jan26</v>
+        <v>Mar26</v>
       </c>
       <c r="C116" t="str">
         <v>COGS</v>
       </c>
       <c r="D116" t="str">
-        <v>Transportation</v>
+        <v>Coconut Water</v>
       </c>
       <c r="E116" t="str">
-        <v>ค่าส่ง</v>
+        <v>น้ำมะพร้าว 10 ขวด</v>
       </c>
       <c r="F116">
-        <v>486</v>
+        <v>500</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>28/01/2026</v>
+        <v>28/03/2026</v>
       </c>
       <c r="B117" t="str">
-        <v>Jan26</v>
+        <v>Mar26</v>
       </c>
       <c r="C117" t="str">
         <v>COGS</v>
       </c>
       <c r="D117" t="str">
-        <v>Transportation</v>
+        <v>Mango</v>
       </c>
       <c r="E117" t="str">
-        <v>Unknown</v>
+        <v>มะม่วง 23 โล</v>
       </c>
       <c r="F117">
-        <v>400</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>28/01/2026</v>
+        <v>28/03/2026</v>
       </c>
       <c r="B118" t="str">
-        <v>Jan26</v>
+        <v>Mar26</v>
       </c>
       <c r="C118" t="str">
         <v>COGS</v>
@@ -3489,7 +3489,7 @@
         <v>Watermelon</v>
       </c>
       <c r="E118" t="str">
-        <v>ค่าแตงโม 50 ลูก</v>
+        <v>แตงโม 50 26/3/69</v>
       </c>
       <c r="F118">
         <v>4000</v>
@@ -3497,50 +3497,50 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>28/01/2026</v>
+        <v>30/03/2026</v>
       </c>
       <c r="B119" t="str">
-        <v>Jan26</v>
+        <v>Mar26</v>
       </c>
       <c r="C119" t="str">
         <v>COGS</v>
       </c>
       <c r="D119" t="str">
-        <v>Transportation</v>
+        <v>Packaging</v>
       </c>
       <c r="E119" t="str">
-        <v>Unknown</v>
+        <v>นมข้นจืดสามลังหนึ่งลังมี 12 กล่อง 36 กล่อง</v>
       </c>
       <c r="F119">
-        <v>400</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>28/01/2026</v>
+        <v>30/03/2026</v>
       </c>
       <c r="B120" t="str">
-        <v>Jan26</v>
+        <v>Mar26</v>
       </c>
       <c r="C120" t="str">
         <v>COGS</v>
       </c>
       <c r="D120" t="str">
-        <v>Transportation</v>
+        <v>Packaging</v>
       </c>
       <c r="E120" t="str">
-        <v>ค่าส่ง</v>
+        <v>นมข้นหวาน 3 ลัง 24 ถุง</v>
       </c>
       <c r="F120">
-        <v>486</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>28/01/2026</v>
+        <v>30/03/2026</v>
       </c>
       <c r="B121" t="str">
-        <v>Jan26</v>
+        <v>Mar26</v>
       </c>
       <c r="C121" t="str">
         <v>COGS</v>
@@ -3549,27 +3549,27 @@
         <v>Watermelon</v>
       </c>
       <c r="E121" t="str">
-        <v>แตงโม 50 ลูก</v>
+        <v>แตงโม 30 ลูก 2400 เนื้อมะพร้าว 10 โล 1100</v>
       </c>
       <c r="F121">
-        <v>4000</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>30/01/2026</v>
+        <v>30/03/2026</v>
       </c>
       <c r="B122" t="str">
-        <v>Jan26</v>
+        <v>Mar26</v>
       </c>
       <c r="C122" t="str">
         <v>COGS</v>
       </c>
       <c r="D122" t="str">
-        <v>Watermelon</v>
+        <v>Transportation</v>
       </c>
       <c r="E122" t="str">
-        <v>แตงโม 25 ลูก</v>
+        <v>ค่าส่ง lalamove</v>
       </c>
       <c r="F122">
         <v>2000</v>
@@ -3577,110 +3577,110 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>30/01/2026</v>
+        <v>31/03/2026</v>
       </c>
       <c r="B123" t="str">
-        <v>Jan26</v>
+        <v>Mar26</v>
       </c>
       <c r="C123" t="str">
         <v>COGS</v>
       </c>
       <c r="D123" t="str">
-        <v>Apple/Melon</v>
+        <v>Transportation</v>
       </c>
       <c r="E123" t="str">
-        <v>แอปเปิ้ล เมล่อน</v>
+        <v>Unknown</v>
       </c>
       <c r="F123">
-        <v>851</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>31/01/2026</v>
+        <v>01/04/2026</v>
       </c>
       <c r="B124" t="str">
-        <v>Jan26</v>
+        <v>Apr26</v>
       </c>
       <c r="C124" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D124" t="str">
-        <v>Salary</v>
+        <v>Apple</v>
       </c>
       <c r="E124" t="str">
-        <v>เงินเดือนเมนมกราคม</v>
+        <v>แอปเปิ้ล 3 ลัง</v>
       </c>
       <c r="F124">
-        <v>19000</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>02/02/2026</v>
+        <v>01/04/2026</v>
       </c>
       <c r="B125" t="str">
-        <v>Feb26</v>
+        <v>Apr26</v>
       </c>
       <c r="C125" t="str">
         <v>COGS</v>
       </c>
       <c r="D125" t="str">
-        <v>Orange</v>
+        <v>Mango</v>
       </c>
       <c r="E125" t="str">
-        <v>ส้ม 30 ตะกร้า</v>
+        <v>มะม่วง 2 ลัง</v>
       </c>
       <c r="F125">
-        <v>10680</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>02/02/2026</v>
+        <v>01/04/2026</v>
       </c>
       <c r="B126" t="str">
-        <v>Feb26</v>
+        <v>Apr26</v>
       </c>
       <c r="C126" t="str">
         <v>COGS</v>
       </c>
       <c r="D126" t="str">
-        <v>Watermelon</v>
+        <v>Water</v>
       </c>
       <c r="E126" t="str">
-        <v>แตงโม 50 ลูก</v>
+        <v>น้ำ500</v>
       </c>
       <c r="F126">
-        <v>4000</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>02/02/2026</v>
+        <v>02/04/2026</v>
       </c>
       <c r="B127" t="str">
-        <v>Feb26</v>
+        <v>Mar26</v>
       </c>
       <c r="C127" t="str">
         <v>COGS</v>
       </c>
       <c r="D127" t="str">
-        <v>Transportation</v>
+        <v>Ice</v>
       </c>
       <c r="E127" t="str">
         <v>Unknown</v>
       </c>
       <c r="F127">
-        <v>2000</v>
+        <v>49560</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>04/02/2026</v>
+        <v>04/04/2026</v>
       </c>
       <c r="B128" t="str">
-        <v>Feb26</v>
+        <v>Apr26</v>
       </c>
       <c r="C128" t="str">
         <v>COGS</v>
@@ -3689,58 +3689,58 @@
         <v>Packaging</v>
       </c>
       <c r="E128" t="str">
-        <v>ฝา 690 1000 ชิ้น แก้ว 1196 1000 ชิ้น หลอด 421</v>
+        <v>แก้ว3ลัง 1539 3 4617</v>
       </c>
       <c r="F128">
-        <v>2023</v>
+        <v>7066</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>05/02/2026</v>
+        <v>04/04/2026</v>
       </c>
       <c r="B129" t="str">
-        <v>Feb26</v>
+        <v>Apr26</v>
       </c>
       <c r="C129" t="str">
         <v>COGS</v>
       </c>
       <c r="D129" t="str">
-        <v>Watermelon</v>
+        <v>Packaging</v>
       </c>
       <c r="E129" t="str">
-        <v>แตงโม 50 ลูก</v>
+        <v>แก้ว1ลัง 1539</v>
       </c>
       <c r="F129">
-        <v>4000</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>05/02/2026</v>
+        <v>04/04/2026</v>
       </c>
       <c r="B130" t="str">
-        <v>Feb26</v>
+        <v>Apr26</v>
       </c>
       <c r="C130" t="str">
         <v>COGS</v>
       </c>
       <c r="D130" t="str">
-        <v>Packaging</v>
+        <v>Coconut</v>
       </c>
       <c r="E130" t="str">
-        <v>แก้วสกรีน อย่างเดียวไม่รวมฝา 2280บาท</v>
+        <v>ค่ามะพร้าว 26 60ลูก 1560</v>
       </c>
       <c r="F130">
-        <v>2280</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>08/02/2026</v>
+        <v>04/04/2026</v>
       </c>
       <c r="B131" t="str">
-        <v>Feb26</v>
+        <v>Apr26</v>
       </c>
       <c r="C131" t="str">
         <v>COGS</v>
@@ -3749,158 +3749,158 @@
         <v>Ice</v>
       </c>
       <c r="E131" t="str">
-        <v>Unknown</v>
+        <v>เนื้อ 1200 น้ำ 500</v>
       </c>
       <c r="F131">
-        <v>798</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>08/02/2026</v>
+        <v>04/04/2026</v>
       </c>
       <c r="B132" t="str">
-        <v>Feb26</v>
+        <v>Apr26</v>
       </c>
       <c r="C132" t="str">
         <v>COGS</v>
       </c>
       <c r="D132" t="str">
-        <v>Watermelon</v>
+        <v>Mango</v>
       </c>
       <c r="E132" t="str">
-        <v>แตงโม 50</v>
+        <v>มะม่วง1ลัง</v>
       </c>
       <c r="F132">
-        <v>4000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>08/02/2026</v>
+        <v>04/04/2026</v>
       </c>
       <c r="B133" t="str">
-        <v>Feb26</v>
+        <v>Apr26</v>
       </c>
       <c r="C133" t="str">
         <v>COGS</v>
       </c>
       <c r="D133" t="str">
-        <v>Transportation</v>
+        <v>Orange</v>
       </c>
       <c r="E133" t="str">
-        <v>Unknown</v>
+        <v>ส้ม 4/4/69 20 ตะกร้า 30 บาท 13200 ค่าขนส่ง</v>
       </c>
       <c r="F133">
-        <v>2000</v>
+        <v>14160</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>09/02/2026</v>
+        <v>04/04/2026</v>
       </c>
       <c r="B134" t="str">
-        <v>Feb26</v>
+        <v>Apr26</v>
       </c>
       <c r="C134" t="str">
         <v>COGS</v>
       </c>
       <c r="D134" t="str">
-        <v>Orange</v>
+        <v>Ice</v>
       </c>
       <c r="E134" t="str">
-        <v>ส้ม 30 ตะกร้า</v>
+        <v>4/4/68 40 ลูก</v>
       </c>
       <c r="F134">
-        <v>10680</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>09/02/2026</v>
+        <v>04/04/2026</v>
       </c>
       <c r="B135" t="str">
-        <v>Feb26</v>
+        <v>Apr26</v>
       </c>
       <c r="C135" t="str">
         <v>COGS</v>
       </c>
       <c r="D135" t="str">
-        <v>Orange</v>
+        <v>Watermelon</v>
       </c>
       <c r="E135" t="str">
-        <v>ค่าส่งส้ม</v>
+        <v>แตงโม 1/4/69 30 ลูก</v>
       </c>
       <c r="F135">
-        <v>685</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>10/02/2026</v>
+        <v>07/04/2026</v>
       </c>
       <c r="B136" t="str">
-        <v>Feb26</v>
+        <v>Apr26</v>
       </c>
       <c r="C136" t="str">
         <v>COGS</v>
       </c>
       <c r="D136" t="str">
-        <v>Ice</v>
+        <v>Apple</v>
       </c>
       <c r="E136" t="str">
-        <v>ค่าไฟเดือนมค</v>
+        <v>แอปเปิ้ล 3 ลัง</v>
       </c>
       <c r="F136">
-        <v>389</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>11/02/2026</v>
+        <v>07/04/2026</v>
       </c>
       <c r="B137" t="str">
-        <v>Feb26</v>
+        <v>Apr26</v>
       </c>
       <c r="C137" t="str">
         <v>COGS</v>
       </c>
       <c r="D137" t="str">
-        <v>Watermelon</v>
+        <v>Coconut Water</v>
       </c>
       <c r="E137" t="str">
-        <v>แตงโม 50 ลูก</v>
+        <v>เนื้อมะพร้าว 10 - 1200 บาท น้ำมะพร้าว 10</v>
       </c>
       <c r="F137">
-        <v>4000</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>14/02/2026</v>
+        <v>07/04/2026</v>
       </c>
       <c r="B138" t="str">
-        <v>Feb26</v>
+        <v>Apr26</v>
       </c>
       <c r="C138" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D138" t="str">
-        <v>Other</v>
+        <v>Watermelon</v>
       </c>
       <c r="E138" t="str">
-        <v>Unknown</v>
+        <v>ค่าแตงโมวันที่ 4- 40 ลูก 3200 บาท วันที่ 7-40 ลูก</v>
       </c>
       <c r="F138">
-        <v>4000</v>
+        <v>6400</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>14/02/2026</v>
+        <v>10/04/2026</v>
       </c>
       <c r="B139" t="str">
-        <v>Feb26</v>
+        <v>Apr26</v>
       </c>
       <c r="C139" t="str">
         <v>COGS</v>
@@ -3909,158 +3909,158 @@
         <v>Ice</v>
       </c>
       <c r="E139" t="str">
-        <v>Unknown</v>
+        <v>ค่านม</v>
       </c>
       <c r="F139">
-        <v>350</v>
+        <v>180</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>16/02/2026</v>
+        <v>11/04/2026</v>
       </c>
       <c r="B140" t="str">
-        <v>Feb26</v>
+        <v>Apr26</v>
       </c>
       <c r="C140" t="str">
         <v>COGS</v>
       </c>
       <c r="D140" t="str">
-        <v>Orange</v>
+        <v>Transportation</v>
       </c>
       <c r="E140" t="str">
-        <v>ค่าส่งส้ม</v>
+        <v>ค่ารถ lalamove</v>
       </c>
       <c r="F140">
-        <v>485</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>16/02/2026</v>
+        <v>11/04/2026</v>
       </c>
       <c r="B141" t="str">
-        <v>Feb26</v>
+        <v>Apr26</v>
       </c>
       <c r="C141" t="str">
         <v>COGS</v>
       </c>
       <c r="D141" t="str">
-        <v>Orange</v>
+        <v>Apple</v>
       </c>
       <c r="E141" t="str">
-        <v>ค่าส้ม 30 ตะกร้า 13/2/69</v>
+        <v>แอปเปิ้ล 3 ลัง</v>
       </c>
       <c r="F141">
-        <v>10680</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>19/02/2026</v>
+        <v>11/04/2026</v>
       </c>
       <c r="B142" t="str">
-        <v>Feb26</v>
+        <v>Apr26</v>
       </c>
       <c r="C142" t="str">
         <v>COGS</v>
       </c>
       <c r="D142" t="str">
-        <v>Watermelon</v>
+        <v>Ice</v>
       </c>
       <c r="E142" t="str">
-        <v>แตงโม 50 ลูก วันที่ 1719</v>
+        <v>น้ำ 500 เนื้อ 1200</v>
       </c>
       <c r="F142">
-        <v>8000</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>19/02/2026</v>
+        <v>11/04/2026</v>
       </c>
       <c r="B143" t="str">
-        <v>Feb26</v>
+        <v>Apr26</v>
       </c>
       <c r="C143" t="str">
         <v>COGS</v>
       </c>
       <c r="D143" t="str">
-        <v>Packaging</v>
+        <v>Mango</v>
       </c>
       <c r="E143" t="str">
-        <v>แก้ว</v>
+        <v>มะม่วง 1 ลัง 23 โล</v>
       </c>
       <c r="F143">
-        <v>3315</v>
+        <v>690</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>19/02/2026</v>
+        <v>13/04/2026</v>
       </c>
       <c r="B144" t="str">
-        <v>Feb26</v>
+        <v>Apr26</v>
       </c>
       <c r="C144" t="str">
         <v>COGS</v>
       </c>
       <c r="D144" t="str">
-        <v>Transportation</v>
+        <v>Coconut Water</v>
       </c>
       <c r="E144" t="str">
-        <v>แก้วสกรีน2ลัง(รอบที่1นะ แบ่งสั่งจะได้ไม่มีค่า</v>
+        <v>Unknown</v>
       </c>
       <c r="F144">
-        <v>6655</v>
+        <v>300</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>19/02/2026</v>
+        <v>13/04/2026</v>
       </c>
       <c r="B145" t="str">
-        <v>Feb26</v>
+        <v>Apr26</v>
       </c>
       <c r="C145" t="str">
         <v>COGS</v>
       </c>
       <c r="D145" t="str">
-        <v>Transportation</v>
+        <v>Coconut Water</v>
       </c>
       <c r="E145" t="str">
-        <v>Unknown</v>
+        <v>เนื้อมะพร้าว 1200 น้ำมะพร้าว 500</v>
       </c>
       <c r="F145">
-        <v>2000</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>20/02/2026</v>
+        <v>13/04/2026</v>
       </c>
       <c r="B146" t="str">
-        <v>Feb26</v>
+        <v>Apr26</v>
       </c>
       <c r="C146" t="str">
         <v>COGS</v>
       </c>
       <c r="D146" t="str">
-        <v>Ice</v>
+        <v>Mango</v>
       </c>
       <c r="E146" t="str">
-        <v>ผ้าปิดร้าน 218 ค่ารถ 198</v>
+        <v>Unknown</v>
       </c>
       <c r="F146">
-        <v>416</v>
+        <v>750</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>23/02/2026</v>
+        <v>13/04/2026</v>
       </c>
       <c r="B147" t="str">
-        <v>Feb26</v>
+        <v>Apr26</v>
       </c>
       <c r="C147" t="str">
         <v>COGS</v>
@@ -4069,98 +4069,98 @@
         <v>Watermelon</v>
       </c>
       <c r="E147" t="str">
-        <v>แตงโม 21 50 ลูก 23 50 ลูก</v>
+        <v>Unknown</v>
       </c>
       <c r="F147">
-        <v>8000</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>24/02/2026</v>
+        <v>18/04/2026</v>
       </c>
       <c r="B148" t="str">
-        <v>Feb26</v>
+        <v>Apr26</v>
       </c>
       <c r="C148" t="str">
         <v>COGS</v>
       </c>
       <c r="D148" t="str">
-        <v>Transportation</v>
+        <v>Apple</v>
       </c>
       <c r="E148" t="str">
-        <v>Unknown</v>
+        <v>แอปเปิ้ล 3 ลัง</v>
       </c>
       <c r="F148">
-        <v>209</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>24/02/2026</v>
+        <v>18/04/2026</v>
       </c>
       <c r="B149" t="str">
-        <v>Feb26</v>
+        <v>Apr26</v>
       </c>
       <c r="C149" t="str">
         <v>COGS</v>
       </c>
       <c r="D149" t="str">
-        <v>Orange</v>
+        <v>Mango</v>
       </c>
       <c r="E149" t="str">
-        <v>ส้ม 30 18/2/69</v>
+        <v>16/04/26 มะม่วง 1 ลัง</v>
       </c>
       <c r="F149">
-        <v>10680</v>
+        <v>750</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>24/02/2026</v>
+        <v>18/04/2026</v>
       </c>
       <c r="B150" t="str">
-        <v>Feb26</v>
+        <v>Apr26</v>
       </c>
       <c r="C150" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D150" t="str">
-        <v>Packaging</v>
+        <v>Other</v>
       </c>
       <c r="E150" t="str">
-        <v>แก้ว 2400 ฝา 1670</v>
+        <v>16/4/2569</v>
       </c>
       <c r="F150">
-        <v>4070</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>25/02/2026</v>
+        <v>20/04/2026</v>
       </c>
       <c r="B151" t="str">
-        <v>Feb26</v>
+        <v>Apr26</v>
       </c>
       <c r="C151" t="str">
         <v>COGS</v>
       </c>
       <c r="D151" t="str">
-        <v>Watermelon</v>
+        <v>Orange</v>
       </c>
       <c r="E151" t="str">
-        <v>แตงโม 50</v>
+        <v>ส้ม 40 ตะกร้า ตะกร้าละ 22 โล โลละ 30 บาท</v>
       </c>
       <c r="F151">
-        <v>4000</v>
+        <v>28600</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>25/02/2026</v>
+        <v>20/04/2026</v>
       </c>
       <c r="B152" t="str">
-        <v>Feb26</v>
+        <v>Apr26</v>
       </c>
       <c r="C152" t="str">
         <v>COGS</v>
@@ -4169,298 +4169,298 @@
         <v>Transportation</v>
       </c>
       <c r="E152" t="str">
-        <v>Unknown</v>
+        <v>ค่าส่งป้ายเมนูร้านใหม่</v>
       </c>
       <c r="F152">
-        <v>2000</v>
+        <v>335</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>25/02/2026</v>
+        <v>20/04/2026</v>
       </c>
       <c r="B153" t="str">
-        <v>Feb26</v>
+        <v>Apr26</v>
       </c>
       <c r="C153" t="str">
         <v>COGS</v>
       </c>
       <c r="D153" t="str">
-        <v>Orange</v>
+        <v>Packaging</v>
       </c>
       <c r="E153" t="str">
-        <v>ส้ม20 ตะกร้า</v>
+        <v>ขวดใหญ่ 98 อัน</v>
       </c>
       <c r="F153">
-        <v>7312</v>
+        <v>338</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>25/02/2026</v>
+        <v>20/04/2026</v>
       </c>
       <c r="B154" t="str">
-        <v>Feb26</v>
+        <v>Apr26</v>
       </c>
       <c r="C154" t="str">
         <v>COGS</v>
       </c>
       <c r="D154" t="str">
-        <v>Orange</v>
+        <v>Packaging</v>
       </c>
       <c r="E154" t="str">
-        <v>ค่าส่งส้ม</v>
+        <v>ถุงขยะ 10 แพค</v>
       </c>
       <c r="F154">
-        <v>806</v>
+        <v>520</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>26/02/2026</v>
+        <v>20/04/2026</v>
       </c>
       <c r="B155" t="str">
-        <v>Feb26</v>
+        <v>Apr26</v>
       </c>
       <c r="C155" t="str">
         <v>COGS</v>
       </c>
       <c r="D155" t="str">
-        <v>Packaging</v>
+        <v>Watermelon</v>
       </c>
       <c r="E155" t="str">
-        <v>ค่าขวดใหญ่</v>
+        <v>18/4/26 แตงโม 30 ลูก</v>
       </c>
       <c r="F155">
-        <v>319</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>28/02/2026</v>
+        <v>20/04/2026</v>
       </c>
       <c r="B156" t="str">
-        <v>Feb26</v>
+        <v>Apr26</v>
       </c>
       <c r="C156" t="str">
         <v>COGS</v>
       </c>
       <c r="D156" t="str">
-        <v>Orange</v>
+        <v>Mango</v>
       </c>
       <c r="E156" t="str">
-        <v>ค่าส่งส้ม</v>
+        <v>18/4/26 มะม่วง 25 โล 750</v>
       </c>
       <c r="F156">
-        <v>2237</v>
+        <v>750</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>28/02/2026</v>
+        <v>21/04/2026</v>
       </c>
       <c r="B157" t="str">
-        <v>Feb26</v>
+        <v>Apr26</v>
       </c>
       <c r="C157" t="str">
         <v>COGS</v>
       </c>
       <c r="D157" t="str">
-        <v>Orange</v>
+        <v>Watermelon</v>
       </c>
       <c r="E157" t="str">
-        <v>ค่าส่งส้ม</v>
+        <v>21/4/26 แตงโม60 ลูก</v>
       </c>
       <c r="F157">
-        <v>2237</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>28/02/2026</v>
+        <v>21/04/2026</v>
       </c>
       <c r="B158" t="str">
-        <v>Feb26</v>
+        <v>Apr26</v>
       </c>
       <c r="C158" t="str">
         <v>COGS</v>
       </c>
       <c r="D158" t="str">
-        <v>Ice</v>
+        <v>Transportation</v>
       </c>
       <c r="E158" t="str">
-        <v>ค่าเช่าสต็อคกพ</v>
+        <v>Lalamove</v>
       </c>
       <c r="F158">
-        <v>12000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>28/02/2026</v>
+        <v>21/04/2026</v>
       </c>
       <c r="B159" t="str">
-        <v>Feb26</v>
+        <v>Apr26</v>
       </c>
       <c r="C159" t="str">
         <v>COGS</v>
       </c>
       <c r="D159" t="str">
-        <v>Watermelon</v>
+        <v>Apple</v>
       </c>
       <c r="E159" t="str">
-        <v>แตงโม 50 ลูก</v>
+        <v>แอปเปิ้ล 4 ลัง</v>
       </c>
       <c r="F159">
-        <v>4000</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>04/03/2026</v>
+        <v>23/04/2026</v>
       </c>
       <c r="B160" t="str">
-        <v>Mar26</v>
+        <v>Apr26</v>
       </c>
       <c r="C160" t="str">
         <v>COGS</v>
       </c>
       <c r="D160" t="str">
-        <v>Watermelon</v>
+        <v>Mango</v>
       </c>
       <c r="E160" t="str">
-        <v>ค่าทางด่วนส่งแตงโม</v>
+        <v>มะม่วง 2 ลัง</v>
       </c>
       <c r="F160">
-        <v>140</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>04/03/2026</v>
+        <v>23/04/2026</v>
       </c>
       <c r="B161" t="str">
-        <v>Mar26</v>
+        <v>Apr26</v>
       </c>
       <c r="C161" t="str">
         <v>COGS</v>
       </c>
       <c r="D161" t="str">
-        <v>Mango</v>
+        <v>Apple</v>
       </c>
       <c r="E161" t="str">
-        <v>มะม่วง 16 โล</v>
+        <v>แอปเปิ้ล 4 ลัง</v>
       </c>
       <c r="F161">
-        <v>560</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>05/03/2026</v>
+        <v>23/04/2026</v>
       </c>
       <c r="B162" t="str">
-        <v>Feb26</v>
+        <v>Apr26</v>
       </c>
       <c r="C162" t="str">
         <v>COGS</v>
       </c>
       <c r="D162" t="str">
-        <v>Mango</v>
+        <v>Ice</v>
       </c>
       <c r="E162" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>16/4/26 เนื้อ 10 น้ำ 10 21/4/26 เนื้อ 10</v>
       </c>
       <c r="F162">
-        <v>500</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>05/03/2026</v>
+        <v>23/04/2026</v>
       </c>
       <c r="B163" t="str">
-        <v>Feb26</v>
+        <v>Apr26</v>
       </c>
       <c r="C163" t="str">
         <v>COGS</v>
       </c>
       <c r="D163" t="str">
-        <v>Orange</v>
+        <v>Mango</v>
       </c>
       <c r="E163" t="str">
-        <v>ค่าส้มวันที่ 27269</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F163">
-        <v>7312</v>
+        <v>780</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>05/03/2026</v>
+        <v>24/04/2026</v>
       </c>
       <c r="B164" t="str">
-        <v>Mar26</v>
+        <v>Apr26</v>
       </c>
       <c r="C164" t="str">
         <v>COGS</v>
       </c>
       <c r="D164" t="str">
-        <v>Orange</v>
+        <v>Packaging</v>
       </c>
       <c r="E164" t="str">
-        <v>แตงโม 51 ยอด3,500</v>
+        <v>บาร์เลย 4 ถั่วแดง 3 ถุงละ 60</v>
       </c>
       <c r="F164">
-        <v>7700</v>
+        <v>420</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>05/03/2026</v>
+        <v>24/04/2026</v>
       </c>
       <c r="B165" t="str">
-        <v>Mar26</v>
+        <v>Apr26</v>
       </c>
       <c r="C165" t="str">
         <v>COGS</v>
       </c>
       <c r="D165" t="str">
-        <v>Orange</v>
+        <v>Watermelon</v>
       </c>
       <c r="E165" t="str">
-        <v>ค่าส้ม 20 ตะกร้า</v>
+        <v>แตงโม 50 ลูก</v>
       </c>
       <c r="F165">
-        <v>7312</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>05/03/2026</v>
+        <v>25/04/2026</v>
       </c>
       <c r="B166" t="str">
-        <v>Mar26</v>
+        <v>Apr26</v>
       </c>
       <c r="C166" t="str">
         <v>COGS</v>
       </c>
       <c r="D166" t="str">
-        <v>Ice</v>
+        <v>Orange</v>
       </c>
       <c r="E166" t="str">
-        <v>ค่าทางด่วน</v>
+        <v>22/04/69</v>
       </c>
       <c r="F166">
-        <v>105</v>
+        <v>14400</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>05/03/2026</v>
+        <v>26/04/2026</v>
       </c>
       <c r="B167" t="str">
-        <v>Mar26</v>
+        <v>Apr26</v>
       </c>
       <c r="C167" t="str">
         <v>COGS</v>
@@ -4469,238 +4469,238 @@
         <v>Packaging</v>
       </c>
       <c r="E167" t="str">
-        <v>ถุงขยะ</v>
+        <v>แก้ว 1 ลัง</v>
       </c>
       <c r="F167">
-        <v>909</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>05/03/2026</v>
+        <v>26/04/2026</v>
       </c>
       <c r="B168" t="str">
-        <v>Mar26</v>
+        <v>Apr26</v>
       </c>
       <c r="C168" t="str">
         <v>COGS</v>
       </c>
       <c r="D168" t="str">
-        <v>Mango</v>
+        <v>Packaging</v>
       </c>
       <c r="E168" t="str">
-        <v>มะม่วง 24 โล</v>
+        <v>แก้ว3ลัง</v>
       </c>
       <c r="F168">
-        <v>1560</v>
+        <v>7090</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>07/03/2026</v>
+        <v>26/04/2026</v>
       </c>
       <c r="B169" t="str">
-        <v>Mar26</v>
+        <v>Apr26</v>
       </c>
       <c r="C169" t="str">
         <v>COGS</v>
       </c>
       <c r="D169" t="str">
-        <v>Transportation</v>
+        <v>Mango</v>
       </c>
       <c r="E169" t="str">
-        <v>Unknown</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F169">
-        <v>2000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>10/03/2026</v>
+        <v>26/04/2026</v>
       </c>
       <c r="B170" t="str">
-        <v>Mar26</v>
+        <v>Apr26</v>
       </c>
       <c r="C170" t="str">
         <v>COGS</v>
       </c>
       <c r="D170" t="str">
-        <v>Orange</v>
+        <v>Apple</v>
       </c>
       <c r="E170" t="str">
-        <v>09/03/69</v>
+        <v>แอปเปิ้ล 4</v>
       </c>
       <c r="F170">
-        <v>9804</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>10/03/2026</v>
+        <v>27/04/2026</v>
       </c>
       <c r="B171" t="str">
-        <v>Mar26</v>
+        <v>Apr26</v>
       </c>
       <c r="C171" t="str">
         <v>COGS</v>
       </c>
       <c r="D171" t="str">
-        <v>Watermelon</v>
+        <v>Ice</v>
       </c>
       <c r="E171" t="str">
-        <v>แตงโม 50 วันที่ 7 แตงโม 50 วันที่ 10</v>
+        <v>26/4/26 50 ลูก</v>
       </c>
       <c r="F171">
-        <v>8000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>10/03/2026</v>
+        <v>28/04/2026</v>
       </c>
       <c r="B172" t="str">
-        <v>Mar26</v>
+        <v>Apr26</v>
       </c>
       <c r="C172" t="str">
-        <v>CAPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D172" t="str">
-        <v>Investment</v>
+        <v>Packaging</v>
       </c>
       <c r="E172" t="str">
-        <v>Unknown</v>
+        <v>หลอด 704(20ห่อ)</v>
       </c>
       <c r="F172">
-        <v>6500</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>10/03/2026</v>
+        <v>28/04/2026</v>
       </c>
       <c r="B173" t="str">
-        <v>Mar26</v>
+        <v>Apr26</v>
       </c>
       <c r="C173" t="str">
         <v>COGS</v>
       </c>
       <c r="D173" t="str">
-        <v>Packaging</v>
+        <v>Orange</v>
       </c>
       <c r="E173" t="str">
-        <v>แก้ว2ลัง ลังละ 1560</v>
+        <v>รอบ 27/04/69</v>
       </c>
       <c r="F173">
-        <v>3120</v>
+        <v>21600</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>10/03/2026</v>
+        <v>28/04/2026</v>
       </c>
       <c r="B174" t="str">
-        <v>Mar26</v>
+        <v>Apr26</v>
       </c>
       <c r="C174" t="str">
         <v>COGS</v>
       </c>
       <c r="D174" t="str">
-        <v>Orange</v>
+        <v>Coconut</v>
       </c>
       <c r="E174" t="str">
-        <v>แก้วร้านน้ำส้ม 2ลัง ลังละ1560</v>
+        <v>ค่าส่งมะพร้าว</v>
       </c>
       <c r="F174">
-        <v>5667</v>
+        <v>100</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>13/03/2026</v>
+        <v>28/04/2026</v>
       </c>
       <c r="B175" t="str">
-        <v>Mar26</v>
+        <v>Apr26</v>
       </c>
       <c r="C175" t="str">
         <v>COGS</v>
       </c>
       <c r="D175" t="str">
-        <v>Packaging</v>
+        <v>Apple</v>
       </c>
       <c r="E175" t="str">
-        <v>หลอด 20 แพค</v>
+        <v>แอปเปิ้ล 4 ลัง</v>
       </c>
       <c r="F175">
-        <v>765</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>14/03/2026</v>
+        <v>28/04/2026</v>
       </c>
       <c r="B176" t="str">
-        <v>Mar26</v>
+        <v>Apr26</v>
       </c>
       <c r="C176" t="str">
         <v>COGS</v>
       </c>
       <c r="D176" t="str">
-        <v>Apple/Melon</v>
+        <v>Mango</v>
       </c>
       <c r="E176" t="str">
-        <v>แอปเปิ้ลฟูจิ 32</v>
+        <v>มะม่วง 2 ลัง</v>
       </c>
       <c r="F176">
-        <v>350</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>14/03/2026</v>
+        <v>29/04/2026</v>
       </c>
       <c r="B177" t="str">
-        <v>Mar26</v>
+        <v>Apr26</v>
       </c>
       <c r="C177" t="str">
         <v>COGS</v>
       </c>
       <c r="D177" t="str">
-        <v>Mango</v>
+        <v>Milk/Conden</v>
       </c>
       <c r="E177" t="str">
-        <v>มะม่วง 2 ลัง 44</v>
+        <v>นมข้นหวาน1ลัง 836</v>
       </c>
       <c r="F177">
-        <v>2420</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>15/03/2026</v>
+        <v>29/04/2026</v>
       </c>
       <c r="B178" t="str">
-        <v>Mar26</v>
+        <v>Apr26</v>
       </c>
       <c r="C178" t="str">
         <v>COGS</v>
       </c>
       <c r="D178" t="str">
-        <v>Ice</v>
+        <v>Packaging</v>
       </c>
       <c r="E178" t="str">
-        <v>ค่าทางด่วน</v>
+        <v>นมข้นหวาน2ลัง 1602</v>
       </c>
       <c r="F178">
-        <v>115</v>
+        <v>3210</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>15/03/2026</v>
+        <v>29/04/2026</v>
       </c>
       <c r="B179" t="str">
-        <v>Mar26</v>
+        <v>Apr26</v>
       </c>
       <c r="C179" t="str">
         <v>COGS</v>
@@ -4709,318 +4709,318 @@
         <v>Watermelon</v>
       </c>
       <c r="E179" t="str">
-        <v>น้ำมะพร้าว 5ขวดเละ 50฿</v>
+        <v>แตงโม 60 ลูก</v>
       </c>
       <c r="F179">
-        <v>4800</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>17/03/2026</v>
+        <v>29/04/2026</v>
       </c>
       <c r="B180" t="str">
-        <v>Mar26</v>
+        <v>Apr26</v>
       </c>
       <c r="C180" t="str">
         <v>COGS</v>
       </c>
       <c r="D180" t="str">
-        <v>Ice</v>
+        <v>Transportation</v>
       </c>
       <c r="E180" t="str">
-        <v>ค่าไฟเดือนกพ มีนา</v>
+        <v>เนื้อ 10 x 50 500</v>
       </c>
       <c r="F180">
-        <v>2779.47</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>19/03/2026</v>
+        <v>30/04/2026</v>
       </c>
       <c r="B181" t="str">
-        <v>Mar26</v>
+        <v>Apr26</v>
       </c>
       <c r="C181" t="str">
         <v>COGS</v>
       </c>
       <c r="D181" t="str">
-        <v>Watermelon</v>
+        <v>Ice</v>
       </c>
       <c r="E181" t="str">
-        <v>ค่าแตงโม 18/3/67 51 ลูก 4000 บาท</v>
+        <v>สับปะรส 3 ตะกร้า</v>
       </c>
       <c r="F181">
-        <v>4000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>21/03/2026</v>
+        <v>30/04/2026</v>
       </c>
       <c r="B182" t="str">
-        <v>Mar26</v>
+        <v>Apr26</v>
       </c>
       <c r="C182" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D182" t="str">
-        <v>Ice</v>
+        <v>Salary</v>
       </c>
       <c r="E182" t="str">
-        <v>สกรู กาวตะปู</v>
+        <v>Employee 1</v>
       </c>
       <c r="F182">
-        <v>117</v>
+        <v>19000</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>23/03/2026</v>
+        <v>30/04/2026</v>
       </c>
       <c r="B183" t="str">
-        <v>Mar26</v>
+        <v>Apr26</v>
       </c>
       <c r="C183" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D183" t="str">
-        <v>Mango</v>
+        <v>Salary</v>
       </c>
       <c r="E183" t="str">
-        <v>มะม่วง 44 โล</v>
+        <v>Employee 2</v>
       </c>
       <c r="F183">
-        <v>2200</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>23/03/2026</v>
+        <v>30/04/2026</v>
       </c>
       <c r="B184" t="str">
-        <v>Mar26</v>
+        <v>Apr26</v>
       </c>
       <c r="C184" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D184" t="str">
-        <v>Orange</v>
+        <v>Fixed Costs</v>
       </c>
       <c r="E184" t="str">
-        <v>22-3-2569</v>
+        <v>Rent</v>
       </c>
       <c r="F184">
-        <v>5890</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>24/03/2026</v>
+        <v>30/04/2026</v>
       </c>
       <c r="B185" t="str">
-        <v>Mar26</v>
+        <v>Apr26</v>
       </c>
       <c r="C185" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D185" t="str">
-        <v>Ice</v>
+        <v>Investment</v>
       </c>
       <c r="E185" t="str">
-        <v>รถเข็นของคันใหม่</v>
+        <v>Stock (Allocated 82.9%)</v>
       </c>
       <c r="F185">
-        <v>1752</v>
+        <v>9948</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>28/03/2026</v>
+        <v>30/04/2026</v>
       </c>
       <c r="B186" t="str">
-        <v>Mar26</v>
+        <v>Apr26</v>
       </c>
       <c r="C186" t="str">
         <v>COGS</v>
       </c>
       <c r="D186" t="str">
-        <v>Coconut</v>
+        <v>Other</v>
       </c>
       <c r="E186" t="str">
-        <v>น้ำมะพร้าว 10 ขวด</v>
+        <v>Pineapple</v>
       </c>
       <c r="F186">
-        <v>500</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>28/03/2026</v>
+        <v>01/05/2026</v>
       </c>
       <c r="B187" t="str">
-        <v>Mar26</v>
+        <v>May26</v>
       </c>
       <c r="C187" t="str">
         <v>COGS</v>
       </c>
       <c r="D187" t="str">
-        <v>Mango</v>
+        <v>Guava</v>
       </c>
       <c r="E187" t="str">
-        <v>มะม่วง 23 โล</v>
+        <v>ร่ม 1176 ร่ม 843 ฝรั่ง 300 นมข้นจืด 785 ที่ปั้ม 176</v>
       </c>
       <c r="F187">
-        <v>1035</v>
+        <v>7823</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>28/03/2026</v>
+        <v>02/05/2026</v>
       </c>
       <c r="B188" t="str">
-        <v>Mar26</v>
+        <v>May26</v>
       </c>
       <c r="C188" t="str">
         <v>COGS</v>
       </c>
       <c r="D188" t="str">
-        <v>Watermelon</v>
+        <v>Mango</v>
       </c>
       <c r="E188" t="str">
-        <v>แตงโม 50 26/3/69</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F188">
-        <v>4000</v>
+        <v>910</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>30/03/2026</v>
+        <v>02/05/2026</v>
       </c>
       <c r="B189" t="str">
-        <v>Mar26</v>
+        <v>May26</v>
       </c>
       <c r="C189" t="str">
         <v>COGS</v>
       </c>
       <c r="D189" t="str">
-        <v>Packaging</v>
+        <v>Apple</v>
       </c>
       <c r="E189" t="str">
-        <v>นมข้นจืดสามลังหนึ่งลังมี 12 กล่อง 36 กล่อง</v>
+        <v>แอปเปิ้ล 4 ลัง</v>
       </c>
       <c r="F189">
-        <v>1720</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>30/03/2026</v>
+        <v>02/05/2026</v>
       </c>
       <c r="B190" t="str">
-        <v>Mar26</v>
+        <v>May26</v>
       </c>
       <c r="C190" t="str">
         <v>COGS</v>
       </c>
       <c r="D190" t="str">
-        <v>Packaging</v>
+        <v>Pineapple</v>
       </c>
       <c r="E190" t="str">
-        <v>นมข้นหวาน 3 ลัง 24 ถุง</v>
+        <v>สับปะรด 30 ลูก</v>
       </c>
       <c r="F190">
-        <v>2016</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>30/03/2026</v>
+        <v>02/05/2026</v>
       </c>
       <c r="B191" t="str">
-        <v>Mar26</v>
+        <v>May26</v>
       </c>
       <c r="C191" t="str">
         <v>COGS</v>
       </c>
       <c r="D191" t="str">
-        <v>Watermelon</v>
+        <v>Ice</v>
       </c>
       <c r="E191" t="str">
-        <v>แตงโม 30 ลูก 2400 เนื้อมะพร้าว 10 โล 1100</v>
+        <v>ค่าหาหมอเอ</v>
       </c>
       <c r="F191">
-        <v>3500</v>
+        <v>706</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>30/03/2026</v>
+        <v>02/05/2026</v>
       </c>
       <c r="B192" t="str">
-        <v>Mar26</v>
+        <v>May26</v>
       </c>
       <c r="C192" t="str">
         <v>COGS</v>
       </c>
       <c r="D192" t="str">
-        <v>Transportation</v>
+        <v>Ice</v>
       </c>
       <c r="E192" t="str">
-        <v>ค่าส่ง lalamove</v>
+        <v>ค่าหมอเอ</v>
       </c>
       <c r="F192">
-        <v>2000</v>
+        <v>13</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>31/03/2026</v>
+        <v>04/05/2026</v>
       </c>
       <c r="B193" t="str">
-        <v>Mar26</v>
+        <v>May26</v>
       </c>
       <c r="C193" t="str">
         <v>COGS</v>
       </c>
       <c r="D193" t="str">
-        <v>Transportation</v>
+        <v>Packaging</v>
       </c>
       <c r="E193" t="str">
-        <v>Unknown</v>
+        <v>ถุงมือ4อัน</v>
       </c>
       <c r="F193">
-        <v>2000</v>
+        <v>499</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>01/04/2026</v>
+        <v>04/05/2026</v>
       </c>
       <c r="B194" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C194" t="str">
         <v>COGS</v>
       </c>
       <c r="D194" t="str">
-        <v>Apple/Melon</v>
+        <v>Apple</v>
       </c>
       <c r="E194" t="str">
-        <v>แอปเปิ้ล 3 ลัง</v>
+        <v>แอปเปิ้ล 4 ลัง</v>
       </c>
       <c r="F194">
-        <v>1050</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>01/04/2026</v>
+        <v>04/05/2026</v>
       </c>
       <c r="B195" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C195" t="str">
         <v>COGS</v>
@@ -5032,695 +5032,695 @@
         <v>มะม่วง 2 ลัง</v>
       </c>
       <c r="F195">
-        <v>1920</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>01/04/2026</v>
+        <v>04/05/2026</v>
       </c>
       <c r="B196" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C196" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D196" t="str">
-        <v>Water</v>
+        <v>Other</v>
       </c>
       <c r="E196" t="str">
-        <v>น้ำ500</v>
+        <v>30-4-2569 เบอร์ 70฿ 60 ลูก</v>
       </c>
       <c r="F196">
-        <v>1700</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>02/04/2026</v>
+        <v>06/05/2026</v>
       </c>
       <c r="B197" t="str">
-        <v>Mar26</v>
+        <v>May26</v>
       </c>
       <c r="C197" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D197" t="str">
-        <v>Ice</v>
+        <v>Other</v>
       </c>
       <c r="E197" t="str">
-        <v>Unknown</v>
+        <v>ทิชชู่3แพค 36ห่อ</v>
       </c>
       <c r="F197">
-        <v>49560</v>
+        <v>451</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>04/04/2026</v>
+        <v>06/05/2026</v>
       </c>
       <c r="B198" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C198" t="str">
         <v>COGS</v>
       </c>
       <c r="D198" t="str">
-        <v>Packaging</v>
+        <v>Mango</v>
       </c>
       <c r="E198" t="str">
-        <v>แก้ว3ลัง 1539 3 4617</v>
+        <v>มะม่วง 2 ลัง</v>
       </c>
       <c r="F198">
-        <v>7066</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>04/04/2026</v>
+        <v>06/05/2026</v>
       </c>
       <c r="B199" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C199" t="str">
         <v>COGS</v>
       </c>
       <c r="D199" t="str">
-        <v>Packaging</v>
+        <v>Pineapple</v>
       </c>
       <c r="E199" t="str">
-        <v>แก้ว1ลัง 1539</v>
+        <v>สับปะรด 18 ลูก</v>
       </c>
       <c r="F199">
-        <v>1560</v>
+        <v>486</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>04/04/2026</v>
+        <v>06/05/2026</v>
       </c>
       <c r="B200" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C200" t="str">
         <v>COGS</v>
       </c>
       <c r="D200" t="str">
-        <v>Coconut</v>
+        <v>Apple</v>
       </c>
       <c r="E200" t="str">
-        <v>ค่ามะพร้าว 26 60ลูก 1560</v>
+        <v>แอปเปิ้ล 4 ลัง</v>
       </c>
       <c r="F200">
-        <v>1980</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>04/04/2026</v>
+        <v>08/05/2026</v>
       </c>
       <c r="B201" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C201" t="str">
         <v>COGS</v>
       </c>
       <c r="D201" t="str">
-        <v>Ice</v>
+        <v>Transportation</v>
       </c>
       <c r="E201" t="str">
-        <v>เนื้อ 1200 น้ำ 500</v>
+        <v>น้ำ 20 ขวด 900 ถอดเสื้อ 30 ลูก750 กล่องโฟม 3</v>
       </c>
       <c r="F201">
-        <v>1700</v>
+        <v>4555</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>04/04/2026</v>
+        <v>08/05/2026</v>
       </c>
       <c r="B202" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C202" t="str">
         <v>COGS</v>
       </c>
       <c r="D202" t="str">
-        <v>Mango</v>
+        <v>Water</v>
       </c>
       <c r="E202" t="str">
-        <v>มะม่วง1ลัง</v>
+        <v>น้ำมะร้าว 1 ลัง</v>
       </c>
       <c r="F202">
-        <v>1000</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>04/04/2026</v>
+        <v>08/05/2026</v>
       </c>
       <c r="B203" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C203" t="str">
         <v>COGS</v>
       </c>
       <c r="D203" t="str">
-        <v>Orange</v>
+        <v>Packaging</v>
       </c>
       <c r="E203" t="str">
-        <v>ส้ม 4/4/69 20 ตะกร้า 30 บาท 13200 ค่าขนส่ง</v>
+        <v>6 พ.ค. น้ำ 30 ขวด 1500 บาท เนื้อ 11 โล 1320 บาท</v>
       </c>
       <c r="F203">
-        <v>14160</v>
+        <v>2820</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>04/04/2026</v>
+        <v>08/05/2026</v>
       </c>
       <c r="B204" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C204" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D204" t="str">
-        <v>Ice</v>
+        <v>Other</v>
       </c>
       <c r="E204" t="str">
-        <v>4/4/68 40 ลูก</v>
+        <v>ค่าทำความสะอาดตึกชั้น 1</v>
       </c>
       <c r="F204">
-        <v>3200</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>04/04/2026</v>
+        <v>08/05/2026</v>
       </c>
       <c r="B205" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C205" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D205" t="str">
-        <v>Watermelon</v>
+        <v>Other</v>
       </c>
       <c r="E205" t="str">
-        <v>แตงโม 1/4/69 30 ลูก</v>
+        <v>4-5-2569 เบอร์ 70฿ 60 ลูก ยอด 4,200</v>
       </c>
       <c r="F205">
-        <v>2400</v>
+        <v>8200</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>07/04/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="B206" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C206" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D206" t="str">
-        <v>Apple/Melon</v>
+        <v>Other</v>
       </c>
       <c r="E206" t="str">
-        <v>แอปเปิ้ล 3 ลัง</v>
+        <v>พรหมเช็ดเท้า 1 ผืน</v>
       </c>
       <c r="F206">
-        <v>1050</v>
+        <v>372</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>07/04/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="B207" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C207" t="str">
         <v>COGS</v>
       </c>
       <c r="D207" t="str">
-        <v>Coconut</v>
+        <v>Milk/Conden</v>
       </c>
       <c r="E207" t="str">
-        <v>เนื้อมะพร้าว 10 - 1200 บาท น้ำมะพร้าว 10</v>
+        <v>นมข้นจืด 1ลัง 636</v>
       </c>
       <c r="F207">
-        <v>1700</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>07/04/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="B208" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C208" t="str">
         <v>COGS</v>
       </c>
       <c r="D208" t="str">
-        <v>Watermelon</v>
+        <v>Packaging</v>
       </c>
       <c r="E208" t="str">
-        <v>ค่าแตงโมวันที่ 4- 40 ลูก 3200 บาท วันที่ 7-40 ลูก</v>
+        <v>นมข้น 3 ลัง 2568</v>
       </c>
       <c r="F208">
-        <v>6400</v>
+        <v>4875</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>10/04/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="B209" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C209" t="str">
         <v>COGS</v>
       </c>
       <c r="D209" t="str">
-        <v>Ice</v>
+        <v>Packaging</v>
       </c>
       <c r="E209" t="str">
-        <v>ค่านม</v>
+        <v>แก้ว3ลัง 5,301</v>
       </c>
       <c r="F209">
-        <v>180</v>
+        <v>6132</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>11/04/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="B210" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C210" t="str">
         <v>COGS</v>
       </c>
       <c r="D210" t="str">
-        <v>Transportation</v>
+        <v>Packaging</v>
       </c>
       <c r="E210" t="str">
-        <v>ค่ารถ lalamove</v>
+        <v>ถุงมือ 20 กล่อง 2246 ฝา1ลัง 969</v>
       </c>
       <c r="F210">
-        <v>2000</v>
+        <v>4496</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>11/04/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="B211" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C211" t="str">
         <v>COGS</v>
       </c>
       <c r="D211" t="str">
-        <v>Apple/Melon</v>
+        <v>Transportation</v>
       </c>
       <c r="E211" t="str">
-        <v>แอปเปิ้ล 3 ลัง</v>
+        <v>Lalamove</v>
       </c>
       <c r="F211">
-        <v>1050</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>11/04/2026</v>
+        <v>10/05/2026</v>
       </c>
       <c r="B212" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C212" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D212" t="str">
-        <v>Ice</v>
+        <v>Other</v>
       </c>
       <c r="E212" t="str">
-        <v>น้ำ 500 เนื้อ 1200</v>
+        <v>ไฟ 2อัน 422</v>
       </c>
       <c r="F212">
-        <v>1700</v>
+        <v>838</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>11/04/2026</v>
+        <v>11/05/2026</v>
       </c>
       <c r="B213" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C213" t="str">
         <v>COGS</v>
       </c>
       <c r="D213" t="str">
-        <v>Mango</v>
+        <v>Guava</v>
       </c>
       <c r="E213" t="str">
-        <v>มะม่วง 1 ลัง 23 โล</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F213">
-        <v>690</v>
+        <v>600</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>13/04/2026</v>
+        <v>11/05/2026</v>
       </c>
       <c r="B214" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C214" t="str">
         <v>COGS</v>
       </c>
       <c r="D214" t="str">
-        <v>Coconut</v>
+        <v>Mango</v>
       </c>
       <c r="E214" t="str">
-        <v>Unknown</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F214">
-        <v>300</v>
+        <v>910</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>13/04/2026</v>
+        <v>11/05/2026</v>
       </c>
       <c r="B215" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C215" t="str">
         <v>COGS</v>
       </c>
       <c r="D215" t="str">
-        <v>Coconut</v>
+        <v>Watermelon</v>
       </c>
       <c r="E215" t="str">
-        <v>เนื้อมะพร้าว 1200 น้ำมะพร้าว 500</v>
+        <v>แตงโม 4000 วันที่ 9-5-26</v>
       </c>
       <c r="F215">
-        <v>1400</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>13/04/2026</v>
+        <v>12/05/2026</v>
       </c>
       <c r="B216" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C216" t="str">
         <v>COGS</v>
       </c>
       <c r="D216" t="str">
-        <v>Mango</v>
+        <v>Coconut Meat</v>
       </c>
       <c r="E216" t="str">
-        <v>Unknown</v>
+        <v>เนื้อมะพร้าว 1 ลัง</v>
       </c>
       <c r="F216">
-        <v>750</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>13/04/2026</v>
+        <v>13/05/2026</v>
       </c>
       <c r="B217" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C217" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D217" t="str">
-        <v>Watermelon</v>
+        <v>Other</v>
       </c>
       <c r="E217" t="str">
-        <v>Unknown</v>
+        <v>ที่หนีบ 6ตัว 374 บาท</v>
       </c>
       <c r="F217">
-        <v>3200</v>
+        <v>374</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>18/04/2026</v>
+        <v>13/05/2026</v>
       </c>
       <c r="B218" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C218" t="str">
         <v>COGS</v>
       </c>
       <c r="D218" t="str">
-        <v>Apple/Melon</v>
+        <v>Pineapple</v>
       </c>
       <c r="E218" t="str">
-        <v>แอปเปิ้ล 3 ลัง</v>
+        <v>09/05/26 สับปะรด 2 ตะกร้า</v>
       </c>
       <c r="F218">
-        <v>1050</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>18/04/2026</v>
+        <v>14/05/2026</v>
       </c>
       <c r="B219" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C219" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D219" t="str">
-        <v>Mango</v>
+        <v>Other</v>
       </c>
       <c r="E219" t="str">
-        <v>16/04/26 มะม่วง 1 ลัง</v>
+        <v>11-5-2569 50 ลูก ยอด 4,000</v>
       </c>
       <c r="F219">
-        <v>750</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>18/04/2026</v>
+        <v>14/05/2026</v>
       </c>
       <c r="B220" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C220" t="str">
         <v>OPEX</v>
       </c>
       <c r="D220" t="str">
-        <v>Other</v>
+        <v>Rental</v>
       </c>
       <c r="E220" t="str">
-        <v>16/4/2569</v>
+        <v>ค่าเช่า+สต๊อกร้าน 1</v>
       </c>
       <c r="F220">
-        <v>4000</v>
+        <v>47000</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>20/04/2026</v>
+        <v>14/05/2026</v>
       </c>
       <c r="B221" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C221" t="str">
         <v>COGS</v>
       </c>
       <c r="D221" t="str">
-        <v>Orange</v>
+        <v>Guava</v>
       </c>
       <c r="E221" t="str">
-        <v>ส้ม 40 ตะกร้า ตะกร้าละ 22 โล โลละ 30 บาท</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F221">
-        <v>28600</v>
+        <v>600</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>20/04/2026</v>
+        <v>14/05/2026</v>
       </c>
       <c r="B222" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C222" t="str">
         <v>COGS</v>
       </c>
       <c r="D222" t="str">
-        <v>Transportation</v>
+        <v>Apple</v>
       </c>
       <c r="E222" t="str">
-        <v>ค่าส่งป้ายเมนูร้านใหม่</v>
+        <v>แอปเปิ้ล 3 ลัง</v>
       </c>
       <c r="F222">
-        <v>335</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>20/04/2026</v>
+        <v>14/05/2026</v>
       </c>
       <c r="B223" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C223" t="str">
         <v>COGS</v>
       </c>
       <c r="D223" t="str">
-        <v>Packaging</v>
+        <v>Mango</v>
       </c>
       <c r="E223" t="str">
-        <v>ขวดใหญ่ 98 อัน</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F223">
-        <v>338</v>
+        <v>875</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>20/04/2026</v>
+        <v>15/05/2026</v>
       </c>
       <c r="B224" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C224" t="str">
         <v>COGS</v>
       </c>
       <c r="D224" t="str">
-        <v>Packaging</v>
+        <v>Orange</v>
       </c>
       <c r="E224" t="str">
-        <v>ถุงขยะ 10 แพค</v>
+        <v>15/05/69</v>
       </c>
       <c r="F224">
-        <v>520</v>
+        <v>15730</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>20/04/2026</v>
+        <v>15/05/2026</v>
       </c>
       <c r="B225" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C225" t="str">
         <v>COGS</v>
       </c>
       <c r="D225" t="str">
-        <v>Watermelon</v>
+        <v>Orange</v>
       </c>
       <c r="E225" t="str">
-        <v>18/4/26 แตงโม 30 ลูก</v>
+        <v>05/05/69 ส้ม 30x22กก 660กกx30</v>
       </c>
       <c r="F225">
-        <v>2400</v>
+        <v>21450</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>20/04/2026</v>
+        <v>16/05/2026</v>
       </c>
       <c r="B226" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C226" t="str">
         <v>COGS</v>
       </c>
       <c r="D226" t="str">
-        <v>Mango</v>
+        <v>Ice</v>
       </c>
       <c r="E226" t="str">
-        <v>18/4/26 มะม่วง 25 โล 750</v>
+        <v>Police fees -2000 2 head</v>
       </c>
       <c r="F226">
-        <v>750</v>
+        <v>4290</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>21/04/2026</v>
+        <v>16/05/2026</v>
       </c>
       <c r="B227" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C227" t="str">
         <v>COGS</v>
       </c>
       <c r="D227" t="str">
-        <v>Watermelon</v>
+        <v>Coconut</v>
       </c>
       <c r="E227" t="str">
-        <v>21/4/26 แตงโม60 ลูก</v>
+        <v>มะพร้าว 20 โล</v>
       </c>
       <c r="F227">
-        <v>4800</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>21/04/2026</v>
+        <v>16/05/2026</v>
       </c>
       <c r="B228" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C228" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D228" t="str">
-        <v>Transportation</v>
+        <v>Other</v>
       </c>
       <c r="E228" t="str">
-        <v>Lalamove</v>
+        <v>14/05/26 18 ลูก 504 บาท 16/05/26 18 ลูก</v>
       </c>
       <c r="F228">
-        <v>2000</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>21/04/2026</v>
+        <v>16/05/2026</v>
       </c>
       <c r="B229" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C229" t="str">
         <v>COGS</v>
       </c>
       <c r="D229" t="str">
-        <v>Apple/Melon</v>
+        <v>Mango</v>
       </c>
       <c r="E229" t="str">
-        <v>แอปเปิ้ล 4 ลัง</v>
+        <v>มะม่วง 1</v>
       </c>
       <c r="F229">
-        <v>1400</v>
+        <v>875</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>23/04/2026</v>
+        <v>19/05/2026</v>
       </c>
       <c r="B230" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C230" t="str">
         <v>COGS</v>
@@ -5729,238 +5729,238 @@
         <v>Mango</v>
       </c>
       <c r="E230" t="str">
-        <v>มะม่วง 2 ลัง</v>
+        <v>มะม่วง 1 ลัง (25 โล)</v>
       </c>
       <c r="F230">
-        <v>1560</v>
+        <v>875</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>23/04/2026</v>
+        <v>19/05/2026</v>
       </c>
       <c r="B231" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C231" t="str">
         <v>COGS</v>
       </c>
       <c r="D231" t="str">
-        <v>Apple/Melon</v>
+        <v>Guava</v>
       </c>
       <c r="E231" t="str">
-        <v>แอปเปิ้ล 4 ลัง</v>
+        <v>ฝรั่ง 1 ลัง</v>
       </c>
       <c r="F231">
-        <v>1400</v>
+        <v>600</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>23/04/2026</v>
+        <v>19/05/2026</v>
       </c>
       <c r="B232" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C232" t="str">
         <v>COGS</v>
       </c>
       <c r="D232" t="str">
-        <v>Ice</v>
+        <v>Apple</v>
       </c>
       <c r="E232" t="str">
-        <v>16/4/26 เนื้อ 10 น้ำ 10 21/4/26 เนื้อ 10</v>
+        <v>แอปเปิ้ล 4 ลังครับ</v>
       </c>
       <c r="F232">
-        <v>2900</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>23/04/2026</v>
+        <v>19/05/2026</v>
       </c>
       <c r="B233" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C233" t="str">
         <v>COGS</v>
       </c>
       <c r="D233" t="str">
-        <v>Mango</v>
+        <v>Pineapple</v>
       </c>
       <c r="E233" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>36*18 648</v>
       </c>
       <c r="F233">
-        <v>780</v>
+        <v>648</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>24/04/2026</v>
+        <v>22/05/2026</v>
       </c>
       <c r="B234" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C234" t="str">
         <v>COGS</v>
       </c>
       <c r="D234" t="str">
-        <v>Packaging</v>
+        <v>Apple</v>
       </c>
       <c r="E234" t="str">
-        <v>บาร์เลย 4 ถั่วแดง 3 ถุงละ 60</v>
+        <v>แอปเปิ้ล 2 ลัง</v>
       </c>
       <c r="F234">
-        <v>420</v>
+        <v>700</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>24/04/2026</v>
+        <v>22/05/2026</v>
       </c>
       <c r="B235" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C235" t="str">
         <v>COGS</v>
       </c>
       <c r="D235" t="str">
-        <v>Watermelon</v>
+        <v>Pineapple</v>
       </c>
       <c r="E235" t="str">
-        <v>แตงโม 50 ลูก</v>
+        <v>สับปะรด 18 ลูก</v>
       </c>
       <c r="F235">
-        <v>4000</v>
+        <v>522</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>25/04/2026</v>
+        <v>22/05/2026</v>
       </c>
       <c r="B236" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C236" t="str">
         <v>COGS</v>
       </c>
       <c r="D236" t="str">
-        <v>Orange</v>
+        <v>Mango</v>
       </c>
       <c r="E236" t="str">
-        <v>22/04/69</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F236">
-        <v>14400</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>26/04/2026</v>
+        <v>22/05/2026</v>
       </c>
       <c r="B237" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C237" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D237" t="str">
-        <v>Packaging</v>
+        <v>Other</v>
       </c>
       <c r="E237" t="str">
-        <v>แก้ว 1 ลัง</v>
+        <v>16-5-2569ยอด 4,000฿</v>
       </c>
       <c r="F237">
-        <v>1539</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>26/04/2026</v>
+        <v>22/05/2026</v>
       </c>
       <c r="B238" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C238" t="str">
         <v>COGS</v>
       </c>
       <c r="D238" t="str">
-        <v>Packaging</v>
+        <v>Guava</v>
       </c>
       <c r="E238" t="str">
-        <v>แก้ว3ลัง</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F238">
-        <v>7090</v>
+        <v>600</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>26/04/2026</v>
+        <v>22/05/2026</v>
       </c>
       <c r="B239" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C239" t="str">
         <v>COGS</v>
       </c>
       <c r="D239" t="str">
-        <v>Mango</v>
+        <v>Transportation</v>
       </c>
       <c r="E239" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>ค่าขนส่ง</v>
       </c>
       <c r="F239">
-        <v>780</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>26/04/2026</v>
+        <v>23/05/2026</v>
       </c>
       <c r="B240" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C240" t="str">
         <v>COGS</v>
       </c>
       <c r="D240" t="str">
-        <v>Apple/Melon</v>
+        <v>Packaging</v>
       </c>
       <c r="E240" t="str">
-        <v>แอปเปิ้ล 4</v>
+        <v>แก้ว 3 ลัง</v>
       </c>
       <c r="F240">
-        <v>1400</v>
+        <v>4680</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>27/04/2026</v>
+        <v>23/05/2026</v>
       </c>
       <c r="B241" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C241" t="str">
         <v>COGS</v>
       </c>
       <c r="D241" t="str">
-        <v>Ice</v>
+        <v>Packaging</v>
       </c>
       <c r="E241" t="str">
-        <v>26/4/26 50 ลูก</v>
+        <v>ฝา1 788</v>
       </c>
       <c r="F241">
-        <v>4000</v>
+        <v>2902</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>28/04/2026</v>
+        <v>23/05/2026</v>
       </c>
       <c r="B242" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C242" t="str">
         <v>COGS</v>
@@ -5969,290 +5969,290 @@
         <v>Packaging</v>
       </c>
       <c r="E242" t="str">
-        <v>หลอด 704(20ห่อ)</v>
+        <v>หลอด20 แพค (767)</v>
       </c>
       <c r="F242">
-        <v>2110</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>28/04/2026</v>
+        <v>25/05/2026</v>
       </c>
       <c r="B243" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C243" t="str">
         <v>COGS</v>
       </c>
       <c r="D243" t="str">
-        <v>Orange</v>
+        <v>Pineapple</v>
       </c>
       <c r="E243" t="str">
-        <v>รอบ 27/04/69</v>
+        <v>สับปะรด 18 ลูก</v>
       </c>
       <c r="F243">
-        <v>21600</v>
+        <v>594</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>28/04/2026</v>
+        <v>25/05/2026</v>
       </c>
       <c r="B244" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C244" t="str">
         <v>COGS</v>
       </c>
       <c r="D244" t="str">
-        <v>Coconut</v>
+        <v>Apple</v>
       </c>
       <c r="E244" t="str">
-        <v>ค่าส่งมะพร้าว</v>
+        <v>แอปเปิ้ล 3 ลังครับ</v>
       </c>
       <c r="F244">
-        <v>100</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>28/04/2026</v>
+        <v>25/05/2026</v>
       </c>
       <c r="B245" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C245" t="str">
         <v>COGS</v>
       </c>
       <c r="D245" t="str">
-        <v>Apple/Melon</v>
+        <v>Orange</v>
       </c>
       <c r="E245" t="str">
-        <v>แอปเปิ้ล 4 ลัง</v>
+        <v>ค่าส่งส้ม Lalamove หักผ่านบัตร</v>
       </c>
       <c r="F245">
-        <v>1400</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>28/04/2026</v>
+        <v>25/05/2026</v>
       </c>
       <c r="B246" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C246" t="str">
         <v>COGS</v>
       </c>
       <c r="D246" t="str">
-        <v>Mango</v>
+        <v>Orange</v>
       </c>
       <c r="E246" t="str">
-        <v>มะม่วง 2 ลัง</v>
+        <v>24/05/69</v>
       </c>
       <c r="F246">
-        <v>1560</v>
+        <v>15015</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>29/04/2026</v>
+        <v>25/05/2026</v>
       </c>
       <c r="B247" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C247" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D247" t="str">
-        <v>Milk/Conden</v>
+        <v>Salary</v>
       </c>
       <c r="E247" t="str">
-        <v>นมข้นหวาน1ลัง 836</v>
+        <v>เงินเดือนซี เดือนพ.ค.</v>
       </c>
       <c r="F247">
-        <v>2160</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>29/04/2026</v>
+        <v>25/05/2026</v>
       </c>
       <c r="B248" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C248" t="str">
         <v>COGS</v>
       </c>
       <c r="D248" t="str">
-        <v>Packaging</v>
+        <v>Guava</v>
       </c>
       <c r="E248" t="str">
-        <v>นมข้นหวาน2ลัง 1602</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F248">
-        <v>3210</v>
+        <v>600</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>29/04/2026</v>
+        <v>25/05/2026</v>
       </c>
       <c r="B249" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C249" t="str">
         <v>COGS</v>
       </c>
       <c r="D249" t="str">
-        <v>Watermelon</v>
+        <v>Mango</v>
       </c>
       <c r="E249" t="str">
-        <v>แตงโม 60 ลูก</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F249">
-        <v>4200</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>29/04/2026</v>
+        <v>27/05/2026</v>
       </c>
       <c r="B250" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C250" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D250" t="str">
-        <v>Transportation</v>
+        <v>Salary</v>
       </c>
       <c r="E250" t="str">
-        <v>เนื้อ 10 x 50 500</v>
+        <v>เงินเดือนเมน 5/26</v>
       </c>
       <c r="F250">
-        <v>2395</v>
+        <v>19000</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>30/04/2026</v>
+        <v>28/05/2026</v>
       </c>
       <c r="B251" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C251" t="str">
-        <v>COGS</v>
+        <v>CAPEX</v>
       </c>
       <c r="D251" t="str">
-        <v>Ice</v>
+        <v>Investment</v>
       </c>
       <c r="E251" t="str">
-        <v>สับปะรส 3 ตะกร้า</v>
+        <v>เครื่องสกัดเย็น 1</v>
       </c>
       <c r="F251">
-        <v>1500</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>30/04/2026</v>
+        <v>28/05/2026</v>
       </c>
       <c r="B252" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C252" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D252" t="str">
-        <v>Salary</v>
+        <v>Coconut</v>
       </c>
       <c r="E252" t="str">
-        <v>Employee 1</v>
+        <v>มะพร้าวถอดเสื้อ 23 ลูก *35 ราคา 805 ค่าส่ง 150</v>
       </c>
       <c r="F252">
-        <v>19000</v>
+        <v>955</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>30/04/2026</v>
+        <v>30/05/2026</v>
       </c>
       <c r="B253" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C253" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D253" t="str">
-        <v>Salary</v>
+        <v>Pineapple</v>
       </c>
       <c r="E253" t="str">
-        <v>Employee 2</v>
+        <v>สับปะรด 18 ลูก</v>
       </c>
       <c r="F253">
-        <v>12000</v>
+        <v>576</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>30/04/2026</v>
+        <v>30/05/2026</v>
       </c>
       <c r="B254" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C254" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D254" t="str">
-        <v>Fixed Costs</v>
+        <v>Mango</v>
       </c>
       <c r="E254" t="str">
-        <v>Rent</v>
+        <v>มะม่วง 1 ตะกร้า</v>
       </c>
       <c r="F254">
-        <v>35000</v>
+        <v>960</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>30/04/2026</v>
+        <v>30/05/2026</v>
       </c>
       <c r="B255" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C255" t="str">
         <v>OPEX</v>
       </c>
       <c r="D255" t="str">
-        <v>Investment</v>
+        <v>Other</v>
       </c>
       <c r="E255" t="str">
-        <v>Stock (Allocated 82.9%)</v>
+        <v>Unknown</v>
       </c>
       <c r="F255">
-        <v>9948</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>30/04/2026</v>
+        <v>30/05/2026</v>
       </c>
       <c r="B256" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C256" t="str">
         <v>COGS</v>
       </c>
       <c r="D256" t="str">
-        <v>Other</v>
+        <v>Guava</v>
       </c>
       <c r="E256" t="str">
-        <v>Pineapple</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F256">
-        <v>1500</v>
+        <v>600</v>
       </c>
     </row>
     <row r="257">
@@ -6275,9 +6275,629 @@
         <v>-4830</v>
       </c>
     </row>
+    <row r="258">
+      <c r="A258" t="str">
+        <v>01/06/2026</v>
+      </c>
+      <c r="B258" t="str">
+        <v>May26</v>
+      </c>
+      <c r="C258" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D258" t="str">
+        <v>Salary</v>
+      </c>
+      <c r="E258" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="F258">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="str">
+        <v>02/06/2026</v>
+      </c>
+      <c r="B259" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C259" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D259" t="str">
+        <v>Pineapple</v>
+      </c>
+      <c r="E259" t="str">
+        <v>สับปะรด ราคา 31*18 ลูก 558</v>
+      </c>
+      <c r="F259">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="str">
+        <v>02/06/2026</v>
+      </c>
+      <c r="B260" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C260" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D260" t="str">
+        <v>Guava</v>
+      </c>
+      <c r="E260" t="str">
+        <v>ฝรั่ง 1 ตะกร้า</v>
+      </c>
+      <c r="F260">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="str">
+        <v>02/06/2026</v>
+      </c>
+      <c r="B261" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C261" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D261" t="str">
+        <v>Watermelon</v>
+      </c>
+      <c r="E261" t="str">
+        <v>แตงโม 160 ลูก (25-5-2569: 80 ลูก, 30-5-2569: 80 ลูก)</v>
+      </c>
+      <c r="F261">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="str">
+        <v>04/06/2026</v>
+      </c>
+      <c r="B262" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C262" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D262" t="str">
+        <v>Pineapple</v>
+      </c>
+      <c r="E262" t="str">
+        <v>Watermelon 750+pineapple - 750</v>
+      </c>
+      <c r="F262">
+        <v>5750</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="str">
+        <v>04/06/2026</v>
+      </c>
+      <c r="B263" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C263" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D263" t="str">
+        <v>Guava</v>
+      </c>
+      <c r="E263" t="str">
+        <v>ฝรั่ง 1 ตะกร้า</v>
+      </c>
+      <c r="F263">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="str">
+        <v>04/06/2026</v>
+      </c>
+      <c r="B264" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C264" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D264" t="str">
+        <v>Mango</v>
+      </c>
+      <c r="E264" t="str">
+        <v>มะม่วง 1 ลัง</v>
+      </c>
+      <c r="F264">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="str">
+        <v>04/06/2026</v>
+      </c>
+      <c r="B265" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C265" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D265" t="str">
+        <v>Apple</v>
+      </c>
+      <c r="E265" t="str">
+        <v>แอพเปิ้ล 4 ลัง</v>
+      </c>
+      <c r="F265">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="str">
+        <v>04/06/2026</v>
+      </c>
+      <c r="B266" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C266" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D266" t="str">
+        <v>Pineapple</v>
+      </c>
+      <c r="E266" t="str">
+        <v>สับปะรด 2 ลูก</v>
+      </c>
+      <c r="F266">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="str">
+        <v>04/06/2026</v>
+      </c>
+      <c r="B267" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C267" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D267" t="str">
+        <v>Packaging</v>
+      </c>
+      <c r="E267" t="str">
+        <v>ขวดใหญ่ 1000ml 98 ใบ 364 ถุงเล็ก 20</v>
+      </c>
+      <c r="F267">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="str">
+        <v>05/06/2026</v>
+      </c>
+      <c r="B268" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C268" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D268" t="str">
+        <v>Pineapple</v>
+      </c>
+      <c r="E268" t="str">
+        <v>สับปะรด 33*18 รวม 594</v>
+      </c>
+      <c r="F268">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="str">
+        <v>05/06/2026</v>
+      </c>
+      <c r="B269" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C269" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D269" t="str">
+        <v>Watermelon</v>
+      </c>
+      <c r="E269" t="str">
+        <v>แตงโม 100 ลูก (2-6-2569: 50 ลูก, 4-6-2569: 50 ลูก)</v>
+      </c>
+      <c r="F269">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="str">
+        <v>07/06/2026</v>
+      </c>
+      <c r="B270" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C270" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D270" t="str">
+        <v>Orange</v>
+      </c>
+      <c r="E270" t="str">
+        <v>ส้ม 20x22กก 440กกx30 13,200บาท</v>
+      </c>
+      <c r="F270">
+        <v>14300</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="str">
+        <v>08/06/2026</v>
+      </c>
+      <c r="B271" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C271" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D271" t="str">
+        <v>Transportation</v>
+      </c>
+      <c r="E271" t="str">
+        <v>Lalamove</v>
+      </c>
+      <c r="F271">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="str">
+        <v>08/06/2026</v>
+      </c>
+      <c r="B272" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C272" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D272" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="E272" t="str">
+        <v>Stock June 2026 (split from rent slip)</v>
+      </c>
+      <c r="F272">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="str">
+        <v>08/06/2026</v>
+      </c>
+      <c r="B273" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C273" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D273" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="E273" t="str">
+        <v>ค่าเช่าร้านเดือน June (06) b1 35000</v>
+      </c>
+      <c r="F273">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="str">
+        <v>08/06/2026</v>
+      </c>
+      <c r="B274" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C274" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D274" t="str">
+        <v>Pineapple</v>
+      </c>
+      <c r="E274" t="str">
+        <v>สับปะรด 15 ลูก</v>
+      </c>
+      <c r="F274">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="str">
+        <v>08/06/2026</v>
+      </c>
+      <c r="B275" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C275" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D275" t="str">
+        <v>Mango</v>
+      </c>
+      <c r="E275" t="str">
+        <v>มะม่วง 1 ลัง</v>
+      </c>
+      <c r="F275">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="str">
+        <v>08/06/2026</v>
+      </c>
+      <c r="B276" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C276" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D276" t="str">
+        <v>Apple</v>
+      </c>
+      <c r="E276" t="str">
+        <v>แอปเปิ้ล 5 ลัง</v>
+      </c>
+      <c r="F276">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="str">
+        <v>08/06/2026</v>
+      </c>
+      <c r="B277" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C277" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D277" t="str">
+        <v>Guava</v>
+      </c>
+      <c r="E277" t="str">
+        <v>ฝรั่ง 1 ตะกร้า</v>
+      </c>
+      <c r="F277">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="str">
+        <v>09/06/2026</v>
+      </c>
+      <c r="B278" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C278" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D278" t="str">
+        <v>Packaging</v>
+      </c>
+      <c r="E278" t="str">
+        <v>แก้ว 1937*3 รวม 5,811</v>
+      </c>
+      <c r="F278">
+        <v>6659</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="str">
+        <v>09/06/2026</v>
+      </c>
+      <c r="B279" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C279" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D279" t="str">
+        <v>Packaging</v>
+      </c>
+      <c r="E279" t="str">
+        <v>หลอด 20 แพ็ก 671</v>
+      </c>
+      <c r="F279">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="str">
+        <v>09/06/2026</v>
+      </c>
+      <c r="B280" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C280" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D280" t="str">
+        <v>Packaging</v>
+      </c>
+      <c r="E280" t="str">
+        <v>ฝา1 714</v>
+      </c>
+      <c r="F280">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="str">
+        <v>09/06/2026</v>
+      </c>
+      <c r="B281" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C281" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D281" t="str">
+        <v>Packaging</v>
+      </c>
+      <c r="E281" t="str">
+        <v>ถุงขยะ 4แพคใหญ่ 1019</v>
+      </c>
+      <c r="F281">
+        <v>1830</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="str">
+        <v>11/06/2026</v>
+      </c>
+      <c r="B282" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C282" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D282" t="str">
+        <v>Guava</v>
+      </c>
+      <c r="E282" t="str">
+        <v>ฝรั่ง 1 ลัง</v>
+      </c>
+      <c r="F282">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="str">
+        <v>12/06/2026</v>
+      </c>
+      <c r="B283" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C283" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D283" t="str">
+        <v>Coconut Water</v>
+      </c>
+      <c r="E283" t="str">
+        <v>น้ำมะพร้าว50*20 1,000</v>
+      </c>
+      <c r="F283">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="str">
+        <v>12/06/2026</v>
+      </c>
+      <c r="B284" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C284" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D284" t="str">
+        <v>Mango</v>
+      </c>
+      <c r="E284" t="str">
+        <v>มะม่วง 1 ลัง</v>
+      </c>
+      <c r="F284">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="str">
+        <v>12/06/2026</v>
+      </c>
+      <c r="B285" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C285" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D285" t="str">
+        <v>Apple</v>
+      </c>
+      <c r="E285" t="str">
+        <v>แอปเปิ้ล 5 ลัง</v>
+      </c>
+      <c r="F285">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="str">
+        <v>12/06/2026</v>
+      </c>
+      <c r="B286" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C286" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D286" t="str">
+        <v>Pineapple</v>
+      </c>
+      <c r="E286" t="str">
+        <v>สับปะรด 19 ลูก</v>
+      </c>
+      <c r="F286">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="str">
+        <v>14/06/2026</v>
+      </c>
+      <c r="B287" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C287" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D287" t="str">
+        <v>Watermelon</v>
+      </c>
+      <c r="E287" t="str">
+        <v>แตงโม 90 ลูก (7-6-2569: 45 ลูก, 12-6-2569: 45 ลูก)</v>
+      </c>
+      <c r="F287">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="str">
+        <v>15/06/2026</v>
+      </c>
+      <c r="B288" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C288" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D288" t="str">
+        <v>Pineapple</v>
+      </c>
+      <c r="E288" t="str">
+        <v>สับปะรด 1 ลูก</v>
+      </c>
+      <c r="F288">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F257"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F288"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -15671,7 +16291,7 @@
         <v>4</v>
       </c>
       <c r="L7">
-        <v>89</v>
+        <v>39</v>
       </c>
       <c r="M7">
         <v>9</v>
@@ -15686,7 +16306,7 @@
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>190</v>
+        <v>140</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -16303,7 +16923,7 @@
         <v>1660</v>
       </c>
       <c r="H14">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -16315,10 +16935,10 @@
         <v>3</v>
       </c>
       <c r="L14">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="M14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -16330,7 +16950,7 @@
         <v>0</v>
       </c>
       <c r="Q14">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -16671,22 +17291,22 @@
         <v>5330</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="I18">
         <v>0</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="N18">
         <v>0</v>
@@ -16698,7 +17318,7 @@
         <v>0</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -17039,13 +17659,13 @@
         <v>1055</v>
       </c>
       <c r="H22">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="I22">
         <v>0</v>
       </c>
       <c r="J22">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K22">
         <v>3</v>
@@ -17066,7 +17686,7 @@
         <v>0</v>
       </c>
       <c r="Q22">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="R22">
         <v>0</v>
@@ -17683,13 +18303,13 @@
         <v>2450</v>
       </c>
       <c r="H29">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="I29">
         <v>0</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="K29">
         <v>2</v>
@@ -17698,7 +18318,7 @@
         <v>12</v>
       </c>
       <c r="M29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N29">
         <v>0</v>
@@ -17710,7 +18330,7 @@
         <v>0</v>
       </c>
       <c r="Q29">
-        <v>40</v>
+        <v>114</v>
       </c>
       <c r="R29">
         <v>0</v>
@@ -18218,72 +18838,1577 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:AD19"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>Som Sai Jai Cold Press Bar - June 2026</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Date</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Day</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Revenue (฿)</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Cash (฿)</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Expenses (฿)</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Cash-Exp (฿)</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Scan/Transfer (฿)</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Orange</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Orange (100)</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Watermelon</v>
+      </c>
+      <c r="K2" t="str">
+        <v>Mango</v>
+      </c>
+      <c r="L2" t="str">
+        <v>Coconut</v>
+      </c>
+      <c r="M2" t="str">
+        <v>Apple</v>
+      </c>
+      <c r="N2" t="str">
+        <v>Young Coco</v>
+      </c>
+      <c r="O2" t="str">
+        <v>Guava</v>
+      </c>
+      <c r="P2" t="str">
+        <v>Pineapple</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>Total Cups</v>
+      </c>
+      <c r="R2" t="str">
+        <v>Bot Big</v>
+      </c>
+      <c r="S2" t="str">
+        <v>Bot Small</v>
+      </c>
+      <c r="T2" t="str">
+        <v>Used Orange (basket)</v>
+      </c>
+      <c r="U2" t="str">
+        <v>Used Watermelon (pcs)</v>
+      </c>
+      <c r="V2" t="str">
+        <v>Used Mango</v>
+      </c>
+      <c r="W2" t="str">
+        <v>Used Coco (Meat)</v>
+      </c>
+      <c r="X2" t="str">
+        <v>Used Coco (Water)</v>
+      </c>
+      <c r="Y2" t="str">
+        <v>Used Coco (Conden)</v>
+      </c>
+      <c r="Z2" t="str">
+        <v>Used Coco (Raw)</v>
+      </c>
+      <c r="AA2" t="str">
+        <v>Used Apple</v>
+      </c>
+      <c r="AB2" t="str">
+        <v>Used Guava</v>
+      </c>
+      <c r="AC2" t="str">
+        <v>Used Pineapple</v>
+      </c>
+      <c r="AD2" t="str">
+        <v>Used Young Coco</v>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Date</v>
+        <v>01/06/2026</v>
       </c>
       <c r="B3" t="str">
-        <v>Day</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Revenue (฿)</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Cash (฿)</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Expenses (฿)</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Cash-Exp (฿)</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Scan/Transfer (฿)</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Orange</v>
-      </c>
-      <c r="I3" t="str">
-        <v>Watermelon</v>
-      </c>
-      <c r="J3" t="str">
-        <v>Mango</v>
-      </c>
-      <c r="K3" t="str">
-        <v>Coconut</v>
-      </c>
-      <c r="L3" t="str">
-        <v>Apple</v>
-      </c>
-      <c r="M3" t="str">
-        <v>Young Coco</v>
-      </c>
-      <c r="N3" t="str">
-        <v>Total Cups</v>
-      </c>
-      <c r="O3" t="str">
-        <v>Bot Big</v>
-      </c>
-      <c r="P3" t="str">
-        <v>Bot Small</v>
-      </c>
-      <c r="Q3" t="str">
-        <v>Used Orange (basket)</v>
-      </c>
-      <c r="R3" t="str">
-        <v>Used Watermelon (pcs)</v>
+        <v>Mon</v>
+      </c>
+      <c r="C3">
+        <v>6520</v>
+      </c>
+      <c r="D3">
+        <v>2020</v>
+      </c>
+      <c r="E3">
+        <v>120</v>
+      </c>
+      <c r="F3">
+        <v>1900</v>
+      </c>
+      <c r="G3">
+        <v>4500</v>
+      </c>
+      <c r="H3">
+        <v>39</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>53</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>14</v>
+      </c>
+      <c r="M3">
+        <v>8</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>115</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>1.5</v>
+      </c>
+      <c r="U3">
+        <v>9</v>
+      </c>
+      <c r="V3">
+        <v>2</v>
+      </c>
+      <c r="W3">
+        <v>1.5</v>
+      </c>
+      <c r="X3">
+        <v>1.5</v>
+      </c>
+      <c r="Y3">
+        <v>1</v>
+      </c>
+      <c r="Z3">
+        <v>1</v>
+      </c>
+      <c r="AA3">
+        <v>16</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>02/06/2026</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Tue</v>
+      </c>
+      <c r="C4">
+        <v>7350</v>
+      </c>
+      <c r="D4">
+        <v>4410</v>
+      </c>
+      <c r="E4">
+        <v>150</v>
+      </c>
+      <c r="F4">
+        <v>4260</v>
+      </c>
+      <c r="G4">
+        <v>2940</v>
+      </c>
+      <c r="H4">
+        <v>52</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>36</v>
+      </c>
+      <c r="K4">
+        <v>7</v>
+      </c>
+      <c r="L4">
+        <v>20</v>
+      </c>
+      <c r="M4">
+        <v>10</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>125</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>2</v>
+      </c>
+      <c r="U4">
+        <v>9</v>
+      </c>
+      <c r="V4">
+        <v>14</v>
+      </c>
+      <c r="W4">
+        <v>2</v>
+      </c>
+      <c r="X4">
+        <v>2</v>
+      </c>
+      <c r="Y4">
+        <v>1</v>
+      </c>
+      <c r="Z4">
+        <v>1</v>
+      </c>
+      <c r="AA4">
+        <v>20</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>03/06/2026</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Wed</v>
+      </c>
+      <c r="C5">
+        <v>5020</v>
+      </c>
+      <c r="D5">
+        <v>2550</v>
+      </c>
+      <c r="E5">
+        <v>120</v>
+      </c>
+      <c r="F5">
+        <v>2430</v>
+      </c>
+      <c r="G5">
+        <v>2470</v>
+      </c>
+      <c r="H5">
+        <v>33</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>25</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>22</v>
+      </c>
+      <c r="M5">
+        <v>5</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>88</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>1</v>
+      </c>
+      <c r="U5">
+        <v>6</v>
+      </c>
+      <c r="V5">
+        <v>6</v>
+      </c>
+      <c r="W5">
+        <v>2</v>
+      </c>
+      <c r="X5">
+        <v>2</v>
+      </c>
+      <c r="Y5">
+        <v>1</v>
+      </c>
+      <c r="Z5">
+        <v>1</v>
+      </c>
+      <c r="AA5">
+        <v>10</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>04/06/2026</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Thu</v>
+      </c>
+      <c r="C6">
+        <v>4680</v>
+      </c>
+      <c r="D6">
+        <v>3020</v>
+      </c>
+      <c r="E6">
+        <v>180</v>
+      </c>
+      <c r="F6">
+        <v>2840</v>
+      </c>
+      <c r="G6">
+        <v>1660</v>
+      </c>
+      <c r="H6">
+        <v>36</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>35</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>2</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>78</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>8</v>
+      </c>
+      <c r="T6">
+        <v>1.5</v>
+      </c>
+      <c r="U6">
+        <v>6</v>
+      </c>
+      <c r="V6">
+        <v>2</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>8</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>05/06/2026</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Fri</v>
+      </c>
+      <c r="C7">
+        <v>8520</v>
+      </c>
+      <c r="D7">
+        <v>5930</v>
+      </c>
+      <c r="E7">
+        <v>160</v>
+      </c>
+      <c r="F7">
+        <v>5770</v>
+      </c>
+      <c r="G7">
+        <v>2590</v>
+      </c>
+      <c r="H7">
+        <v>46</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>42</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>46</v>
+      </c>
+      <c r="M7">
+        <v>13</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>147</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>1.5</v>
+      </c>
+      <c r="U7">
+        <v>7</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>2.5</v>
+      </c>
+      <c r="X7">
+        <v>2.5</v>
+      </c>
+      <c r="Y7">
+        <v>1</v>
+      </c>
+      <c r="Z7">
+        <v>1</v>
+      </c>
+      <c r="AA7">
+        <v>26</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>06/06/2026</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Sat</v>
+      </c>
+      <c r="C8">
+        <v>8190</v>
+      </c>
+      <c r="D8">
+        <v>4240</v>
+      </c>
+      <c r="E8">
+        <v>120</v>
+      </c>
+      <c r="F8">
+        <v>4120</v>
+      </c>
+      <c r="G8">
+        <v>3950</v>
+      </c>
+      <c r="H8">
+        <v>63</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>57</v>
+      </c>
+      <c r="K8">
+        <v>2</v>
+      </c>
+      <c r="L8">
+        <v>11</v>
+      </c>
+      <c r="M8">
+        <v>10</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>143</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>3</v>
+      </c>
+      <c r="U8">
+        <v>7</v>
+      </c>
+      <c r="V8">
+        <v>4</v>
+      </c>
+      <c r="W8">
+        <v>1</v>
+      </c>
+      <c r="X8">
+        <v>1</v>
+      </c>
+      <c r="Y8">
+        <v>1</v>
+      </c>
+      <c r="Z8">
+        <v>1</v>
+      </c>
+      <c r="AA8">
+        <v>20</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>07/06/2026</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Sun</v>
+      </c>
+      <c r="C9">
+        <v>7330</v>
+      </c>
+      <c r="D9">
+        <v>3880</v>
+      </c>
+      <c r="E9">
+        <v>120</v>
+      </c>
+      <c r="F9">
+        <v>3760</v>
+      </c>
+      <c r="G9">
+        <v>3450</v>
+      </c>
+      <c r="H9">
+        <v>38</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>59</v>
+      </c>
+      <c r="K9">
+        <v>8</v>
+      </c>
+      <c r="L9">
+        <v>23</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>128</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>2.5</v>
+      </c>
+      <c r="U9">
+        <v>10</v>
+      </c>
+      <c r="V9">
+        <v>4</v>
+      </c>
+      <c r="W9">
+        <v>2</v>
+      </c>
+      <c r="X9">
+        <v>2</v>
+      </c>
+      <c r="Y9">
+        <v>1</v>
+      </c>
+      <c r="Z9">
+        <v>1</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0</v>
+      </c>
+      <c r="AC9">
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>08/06/2026</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Mon</v>
+      </c>
+      <c r="C10">
+        <v>5470</v>
+      </c>
+      <c r="D10">
+        <v>2730</v>
+      </c>
+      <c r="E10">
+        <v>90</v>
+      </c>
+      <c r="F10">
+        <v>2640</v>
+      </c>
+      <c r="G10">
+        <v>2740</v>
+      </c>
+      <c r="H10">
+        <v>31</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>20</v>
+      </c>
+      <c r="K10">
+        <v>13</v>
+      </c>
+      <c r="L10">
+        <v>12</v>
+      </c>
+      <c r="M10">
+        <v>12</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>88</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>1.5</v>
+      </c>
+      <c r="U10">
+        <v>5</v>
+      </c>
+      <c r="V10">
+        <v>8</v>
+      </c>
+      <c r="W10">
+        <v>1</v>
+      </c>
+      <c r="X10">
+        <v>1.5</v>
+      </c>
+      <c r="Y10">
+        <v>1</v>
+      </c>
+      <c r="Z10">
+        <v>1</v>
+      </c>
+      <c r="AA10">
+        <v>19</v>
+      </c>
+      <c r="AB10">
+        <v>0</v>
+      </c>
+      <c r="AC10">
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>09/06/2026</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Tue</v>
+      </c>
+      <c r="C11">
+        <v>5010</v>
+      </c>
+      <c r="D11">
+        <v>2250</v>
+      </c>
+      <c r="E11">
+        <v>120</v>
+      </c>
+      <c r="F11">
+        <v>2130</v>
+      </c>
+      <c r="G11">
+        <v>2760</v>
+      </c>
+      <c r="H11">
+        <v>44</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>21</v>
+      </c>
+      <c r="K11">
+        <v>2</v>
+      </c>
+      <c r="L11">
+        <v>12</v>
+      </c>
+      <c r="M11">
+        <v>7</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>86</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>1.5</v>
+      </c>
+      <c r="U11">
+        <v>4</v>
+      </c>
+      <c r="V11">
+        <v>4</v>
+      </c>
+      <c r="W11">
+        <v>1</v>
+      </c>
+      <c r="X11">
+        <v>1</v>
+      </c>
+      <c r="Y11">
+        <v>1</v>
+      </c>
+      <c r="Z11">
+        <v>1</v>
+      </c>
+      <c r="AA11">
+        <v>14</v>
+      </c>
+      <c r="AB11">
+        <v>0</v>
+      </c>
+      <c r="AC11">
+        <v>0</v>
+      </c>
+      <c r="AD11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>10/06/2026</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Wed</v>
+      </c>
+      <c r="C12">
+        <v>4520</v>
+      </c>
+      <c r="D12">
+        <v>2250</v>
+      </c>
+      <c r="E12">
+        <v>120</v>
+      </c>
+      <c r="F12">
+        <v>2130</v>
+      </c>
+      <c r="G12">
+        <v>2270</v>
+      </c>
+      <c r="H12">
+        <v>33</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>22</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>12</v>
+      </c>
+      <c r="M12">
+        <v>12</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>79</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>1</v>
+      </c>
+      <c r="U12">
+        <v>5</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>1</v>
+      </c>
+      <c r="X12">
+        <v>1</v>
+      </c>
+      <c r="Y12">
+        <v>0.5</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>10</v>
+      </c>
+      <c r="AB12">
+        <v>0</v>
+      </c>
+      <c r="AC12">
+        <v>0</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>11/06/2026</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Thu</v>
+      </c>
+      <c r="C13">
+        <v>4040</v>
+      </c>
+      <c r="D13">
+        <v>2600</v>
+      </c>
+      <c r="E13">
+        <v>60</v>
+      </c>
+      <c r="F13">
+        <v>2540</v>
+      </c>
+      <c r="G13">
+        <v>1440</v>
+      </c>
+      <c r="H13">
+        <v>23</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>28</v>
+      </c>
+      <c r="K13">
+        <v>2</v>
+      </c>
+      <c r="L13">
+        <v>9</v>
+      </c>
+      <c r="M13">
+        <v>9</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>71</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>1</v>
+      </c>
+      <c r="U13">
+        <v>4</v>
+      </c>
+      <c r="V13">
+        <v>4</v>
+      </c>
+      <c r="W13">
+        <v>1</v>
+      </c>
+      <c r="X13">
+        <v>1</v>
+      </c>
+      <c r="Y13">
+        <v>1</v>
+      </c>
+      <c r="Z13">
+        <v>1</v>
+      </c>
+      <c r="AA13">
+        <v>18</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>12/06/2026</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Fri</v>
+      </c>
+      <c r="C14">
+        <v>3070</v>
+      </c>
+      <c r="D14">
+        <v>1530</v>
+      </c>
+      <c r="E14">
+        <v>60</v>
+      </c>
+      <c r="F14">
+        <v>1470</v>
+      </c>
+      <c r="G14">
+        <v>1540</v>
+      </c>
+      <c r="H14">
+        <v>17</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>14</v>
+      </c>
+      <c r="K14">
+        <v>5</v>
+      </c>
+      <c r="L14">
+        <v>7</v>
+      </c>
+      <c r="M14">
+        <v>8</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>51</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>1</v>
+      </c>
+      <c r="U14">
+        <v>5</v>
+      </c>
+      <c r="V14">
+        <v>3</v>
+      </c>
+      <c r="W14">
+        <v>1</v>
+      </c>
+      <c r="X14">
+        <v>1</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>13</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>13/06/2026</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Sat</v>
+      </c>
+      <c r="C15">
+        <v>9220</v>
+      </c>
+      <c r="D15">
+        <v>4950</v>
+      </c>
+      <c r="E15">
+        <v>120</v>
+      </c>
+      <c r="F15">
+        <v>4830</v>
+      </c>
+      <c r="G15">
+        <v>4270</v>
+      </c>
+      <c r="H15">
+        <v>46</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>31</v>
+      </c>
+      <c r="K15">
+        <v>4</v>
+      </c>
+      <c r="L15">
+        <v>38</v>
+      </c>
+      <c r="M15">
+        <v>32</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>151</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>3.5</v>
+      </c>
+      <c r="U15">
+        <v>10</v>
+      </c>
+      <c r="V15">
+        <v>6</v>
+      </c>
+      <c r="W15">
+        <v>2</v>
+      </c>
+      <c r="X15">
+        <v>2</v>
+      </c>
+      <c r="Y15">
+        <v>1</v>
+      </c>
+      <c r="Z15">
+        <v>1</v>
+      </c>
+      <c r="AA15">
+        <v>38</v>
+      </c>
+      <c r="AB15">
+        <v>0</v>
+      </c>
+      <c r="AC15">
+        <v>0</v>
+      </c>
+      <c r="AD15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>14/06/2026</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Sun</v>
+      </c>
+      <c r="C16">
+        <v>6020</v>
+      </c>
+      <c r="D16">
+        <v>3050</v>
+      </c>
+      <c r="E16">
+        <v>120</v>
+      </c>
+      <c r="F16">
+        <v>2930</v>
+      </c>
+      <c r="G16">
+        <v>2970</v>
+      </c>
+      <c r="H16">
+        <v>33</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>28</v>
+      </c>
+      <c r="K16">
+        <v>4</v>
+      </c>
+      <c r="L16">
+        <v>19</v>
+      </c>
+      <c r="M16">
+        <v>19</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>103</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>1</v>
+      </c>
+      <c r="U16">
+        <v>7</v>
+      </c>
+      <c r="V16">
+        <v>3</v>
+      </c>
+      <c r="W16">
+        <v>2</v>
+      </c>
+      <c r="X16">
+        <v>2</v>
+      </c>
+      <c r="Y16">
+        <v>1</v>
+      </c>
+      <c r="Z16">
+        <v>1</v>
+      </c>
+      <c r="AA16">
+        <v>23</v>
+      </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>TOTAL</v>
+      </c>
+      <c r="B18" t="str">
+        <v>13 days</v>
+      </c>
+      <c r="C18">
+        <v>78440</v>
+      </c>
+      <c r="D18">
+        <v>43390</v>
+      </c>
+      <c r="E18">
+        <v>1540</v>
+      </c>
+      <c r="F18">
+        <v>41850</v>
+      </c>
+      <c r="G18">
+        <v>35050</v>
+      </c>
+      <c r="H18">
+        <v>419</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>319</v>
+      </c>
+      <c r="K18">
+        <v>51</v>
+      </c>
+      <c r="L18">
+        <v>233</v>
+      </c>
+      <c r="M18">
+        <v>141</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>1163</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>103.2</v>
+      </c>
+      <c r="U18">
+        <v>119.4</v>
+      </c>
+      <c r="V18">
+        <v>58</v>
+      </c>
+      <c r="W18">
+        <v>18.5</v>
+      </c>
+      <c r="X18">
+        <v>19</v>
+      </c>
+      <c r="Y18">
+        <v>10.5</v>
+      </c>
+      <c r="Z18">
+        <v>10</v>
+      </c>
+      <c r="AA18">
+        <v>209</v>
+      </c>
+      <c r="AB18">
+        <v>0</v>
+      </c>
+      <c r="AC18">
+        <v>0</v>
+      </c>
+      <c r="AD18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>AVG/DAY</v>
+      </c>
+      <c r="C19">
+        <v>6033.846153846154</v>
+      </c>
+      <c r="D19">
+        <v>3337.6923076923076</v>
+      </c>
+      <c r="E19">
+        <v>118.46153846153847</v>
+      </c>
+      <c r="F19">
+        <v>3219.230769230769</v>
+      </c>
+      <c r="G19">
+        <v>2696.153846153846</v>
+      </c>
+      <c r="H19">
+        <v>32.23076923076923</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>24.53846153846154</v>
+      </c>
+      <c r="K19">
+        <v>3.923076923076923</v>
+      </c>
+      <c r="L19">
+        <v>17.923076923076923</v>
+      </c>
+      <c r="M19">
+        <v>10.846153846153847</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>89.46153846153847</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>7.938461538461539</v>
+      </c>
+      <c r="U19">
+        <v>9.184615384615386</v>
+      </c>
+      <c r="V19">
+        <v>4.461538461538462</v>
+      </c>
+      <c r="W19">
+        <v>1.4230769230769231</v>
+      </c>
+      <c r="X19">
+        <v>1.4615384615384615</v>
+      </c>
+      <c r="Y19">
+        <v>0.8076923076923077</v>
+      </c>
+      <c r="Z19">
+        <v>0.7692307692307693</v>
+      </c>
+      <c r="AA19">
+        <v>16.076923076923077</v>
+      </c>
+      <c r="AB19">
+        <v>0</v>
+      </c>
+      <c r="AC19">
+        <v>0</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AD19"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/3_Automation_Dashboard/SomSaiJai_Dashboard_B1_2026.xlsx
+++ b/3_Automation_Dashboard/SomSaiJai_Dashboard_B1_2026.xlsx
@@ -1168,7 +1168,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F288"/>
+  <dimension ref="A1:F304"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6895,9 +6895,329 @@
         <v>50</v>
       </c>
     </row>
+    <row r="289">
+      <c r="A289" t="str">
+        <v>15/06/2026</v>
+      </c>
+      <c r="B289" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C289" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D289" t="str">
+        <v>Ice</v>
+      </c>
+      <c r="E289" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="F289">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="str">
+        <v>15/06/2026</v>
+      </c>
+      <c r="B290" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C290" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D290" t="str">
+        <v>Pineapple</v>
+      </c>
+      <c r="E290" t="str">
+        <v>สับปะรด 12 ลูก</v>
+      </c>
+      <c r="F290">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="str">
+        <v>15/06/2026</v>
+      </c>
+      <c r="B291" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C291" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D291" t="str">
+        <v>Guava</v>
+      </c>
+      <c r="E291" t="str">
+        <v>ฝรั่ง 1 ตะกร้า</v>
+      </c>
+      <c r="F291">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="str">
+        <v>17/06/2026</v>
+      </c>
+      <c r="B292" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C292" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D292" t="str">
+        <v>Orange</v>
+      </c>
+      <c r="E292" t="str">
+        <v>รอบ 09/06/69</v>
+      </c>
+      <c r="F292">
+        <v>16445</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="str">
+        <v>18/06/2026</v>
+      </c>
+      <c r="B293" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C293" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D293" t="str">
+        <v>Mango</v>
+      </c>
+      <c r="E293" t="str">
+        <v>มะม่วง 1 ลัง</v>
+      </c>
+      <c r="F293">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="str">
+        <v>18/06/2026</v>
+      </c>
+      <c r="B294" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C294" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D294" t="str">
+        <v>Coconut Water</v>
+      </c>
+      <c r="E294" t="str">
+        <v>เนื้อมะพร้าว 20 * 120 2400 น้ำมะพร้าว 20 *</v>
+      </c>
+      <c r="F294">
+        <v>3400</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="str">
+        <v>18/06/2026</v>
+      </c>
+      <c r="B295" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C295" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D295" t="str">
+        <v>Guava</v>
+      </c>
+      <c r="E295" t="str">
+        <v>ฝรั่ง 1 ตะกร้า</v>
+      </c>
+      <c r="F295">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="str">
+        <v>19/06/2026</v>
+      </c>
+      <c r="B296" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C296" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D296" t="str">
+        <v>Coconut Water</v>
+      </c>
+      <c r="E296" t="str">
+        <v>น้ำมะพร้าว40ลิตร ลิตรละ45บาท</v>
+      </c>
+      <c r="F296">
+        <v>5700</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="str">
+        <v>19/06/2026</v>
+      </c>
+      <c r="B297" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C297" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D297" t="str">
+        <v>Packaging</v>
+      </c>
+      <c r="E297" t="str">
+        <v>น้ำยาล้างจาน 7 ถุง ผงซักฟอก 1</v>
+      </c>
+      <c r="F297">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="str">
+        <v>21/06/2026</v>
+      </c>
+      <c r="B298" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C298" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D298" t="str">
+        <v>Watermelon</v>
+      </c>
+      <c r="E298" t="str">
+        <v>15-6-2569 แตงโม 50บาท 50 ลูก ยอด 2,500</v>
+      </c>
+      <c r="F298">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="str">
+        <v>22/06/2026</v>
+      </c>
+      <c r="B299" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C299" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D299" t="str">
+        <v>Pineapple</v>
+      </c>
+      <c r="E299" t="str">
+        <v>สับปะรด 15 ลูก</v>
+      </c>
+      <c r="F299">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="str">
+        <v>22/06/2026</v>
+      </c>
+      <c r="B300" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C300" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D300" t="str">
+        <v>Mango</v>
+      </c>
+      <c r="E300" t="str">
+        <v>มะม่วง 2 ลัง</v>
+      </c>
+      <c r="F300">
+        <v>1632</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="str">
+        <v>22/06/2026</v>
+      </c>
+      <c r="B301" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C301" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D301" t="str">
+        <v>Transportation</v>
+      </c>
+      <c r="E301" t="str">
+        <v>Lalamove</v>
+      </c>
+      <c r="F301">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="str">
+        <v>22/06/2026</v>
+      </c>
+      <c r="B302" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C302" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D302" t="str">
+        <v>Apple</v>
+      </c>
+      <c r="E302" t="str">
+        <v>แอพเปิ้ล 5 ลัง</v>
+      </c>
+      <c r="F302">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="str">
+        <v>22/06/2026</v>
+      </c>
+      <c r="B303" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C303" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D303" t="str">
+        <v>Pineapple</v>
+      </c>
+      <c r="E303" t="str">
+        <v>สับปะรด 15 ลูก</v>
+      </c>
+      <c r="F303">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="str">
+        <v>22/06/2026</v>
+      </c>
+      <c r="B304" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C304" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D304" t="str">
+        <v>Guava</v>
+      </c>
+      <c r="E304" t="str">
+        <v>ฝรั่ง 1 ลัง</v>
+      </c>
+      <c r="F304">
+        <v>700</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F288"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F304"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -18671,22 +18991,22 @@
         <v>107890</v>
       </c>
       <c r="H34">
-        <v>1379</v>
+        <v>1468</v>
       </c>
       <c r="I34">
         <v>0</v>
       </c>
       <c r="J34">
-        <v>1263</v>
+        <v>1383</v>
       </c>
       <c r="K34">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="L34">
-        <v>1000</v>
+        <v>988</v>
       </c>
       <c r="M34">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="N34">
         <v>0</v>
@@ -18698,7 +19018,7 @@
         <v>0</v>
       </c>
       <c r="Q34">
-        <v>4068</v>
+        <v>4286</v>
       </c>
       <c r="R34">
         <v>0</v>
@@ -18760,22 +19080,22 @@
         <v>3596.3333333333335</v>
       </c>
       <c r="H35">
-        <v>45.96666666666667</v>
+        <v>48.93333333333333</v>
       </c>
       <c r="I35">
         <v>0</v>
       </c>
       <c r="J35">
-        <v>42.1</v>
+        <v>46.1</v>
       </c>
       <c r="K35">
-        <v>4.466666666666667</v>
+        <v>4.7</v>
       </c>
       <c r="L35">
-        <v>33.333333333333336</v>
+        <v>32.93333333333333</v>
       </c>
       <c r="M35">
-        <v>9.733333333333333</v>
+        <v>10.2</v>
       </c>
       <c r="N35">
         <v>0</v>
@@ -18787,7 +19107,7 @@
         <v>0</v>
       </c>
       <c r="Q35">
-        <v>135.6</v>
+        <v>142.86666666666667</v>
       </c>
       <c r="R35">
         <v>0</v>
@@ -18838,7 +19158,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AD19"/>
+  <dimension ref="A1:AD25"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -20225,45 +20545,137 @@
         <v>0</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>15/06/2026</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Mon</v>
+      </c>
+      <c r="C17">
+        <v>7080</v>
+      </c>
+      <c r="D17">
+        <v>4290</v>
+      </c>
+      <c r="E17">
+        <v>120</v>
+      </c>
+      <c r="F17">
+        <v>4170</v>
+      </c>
+      <c r="G17">
+        <v>2790</v>
+      </c>
+      <c r="H17">
+        <v>34</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>63</v>
+      </c>
+      <c r="K17">
+        <v>5</v>
+      </c>
+      <c r="L17">
+        <v>16</v>
+      </c>
+      <c r="M17">
+        <v>8</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>126</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>1.5</v>
+      </c>
+      <c r="U17">
+        <v>12</v>
+      </c>
+      <c r="V17">
+        <v>10</v>
+      </c>
+      <c r="W17">
+        <v>2</v>
+      </c>
+      <c r="X17">
+        <v>2</v>
+      </c>
+      <c r="Y17">
+        <v>1</v>
+      </c>
+      <c r="Z17">
+        <v>2</v>
+      </c>
+      <c r="AA17">
+        <v>16</v>
+      </c>
+      <c r="AB17">
+        <v>0</v>
+      </c>
+      <c r="AC17">
+        <v>0</v>
+      </c>
+      <c r="AD17">
+        <v>0</v>
+      </c>
+    </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>TOTAL</v>
+        <v>16/06/2026</v>
       </c>
       <c r="B18" t="str">
-        <v>13 days</v>
+        <v>Tue</v>
       </c>
       <c r="C18">
-        <v>78440</v>
+        <v>4190</v>
       </c>
       <c r="D18">
-        <v>43390</v>
+        <v>1200</v>
       </c>
       <c r="E18">
-        <v>1540</v>
+        <v>60</v>
       </c>
       <c r="F18">
-        <v>41850</v>
+        <v>1140</v>
       </c>
       <c r="G18">
-        <v>35050</v>
+        <v>2990</v>
       </c>
       <c r="H18">
-        <v>419</v>
+        <v>24</v>
       </c>
       <c r="I18">
         <v>0</v>
       </c>
       <c r="J18">
-        <v>319</v>
+        <v>40</v>
       </c>
       <c r="K18">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="L18">
-        <v>233</v>
+        <v>5</v>
       </c>
       <c r="M18">
-        <v>141</v>
+        <v>5</v>
       </c>
       <c r="N18">
         <v>0</v>
@@ -20275,7 +20687,7 @@
         <v>0</v>
       </c>
       <c r="Q18">
-        <v>1163</v>
+        <v>75</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -20284,28 +20696,28 @@
         <v>0</v>
       </c>
       <c r="T18">
-        <v>103.2</v>
+        <v>1</v>
       </c>
       <c r="U18">
-        <v>119.4</v>
+        <v>8</v>
       </c>
       <c r="V18">
-        <v>58</v>
+        <v>2</v>
       </c>
       <c r="W18">
-        <v>18.5</v>
+        <v>1</v>
       </c>
       <c r="X18">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="Y18">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="Z18">
+        <v>1</v>
+      </c>
+      <c r="AA18">
         <v>10</v>
-      </c>
-      <c r="AA18">
-        <v>209</v>
       </c>
       <c r="AB18">
         <v>0</v>
@@ -20319,96 +20731,556 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
+        <v>17/06/2026</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Wed</v>
+      </c>
+      <c r="C19">
+        <v>8450</v>
+      </c>
+      <c r="D19">
+        <v>5530</v>
+      </c>
+      <c r="E19">
+        <v>120</v>
+      </c>
+      <c r="F19">
+        <v>5410</v>
+      </c>
+      <c r="G19">
+        <v>2920</v>
+      </c>
+      <c r="H19">
+        <v>47</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>52</v>
+      </c>
+      <c r="K19">
+        <v>11</v>
+      </c>
+      <c r="L19">
+        <v>27</v>
+      </c>
+      <c r="M19">
+        <v>17</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>154</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>2</v>
+      </c>
+      <c r="U19">
+        <v>10</v>
+      </c>
+      <c r="V19">
+        <v>22</v>
+      </c>
+      <c r="W19">
+        <v>3</v>
+      </c>
+      <c r="X19">
+        <v>3</v>
+      </c>
+      <c r="Y19">
+        <v>1</v>
+      </c>
+      <c r="Z19">
+        <v>3</v>
+      </c>
+      <c r="AA19">
+        <v>34</v>
+      </c>
+      <c r="AB19">
+        <v>0</v>
+      </c>
+      <c r="AC19">
+        <v>0</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>18/06/2026</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Thu</v>
+      </c>
+      <c r="C20">
+        <v>4960</v>
+      </c>
+      <c r="D20">
+        <v>3960</v>
+      </c>
+      <c r="E20">
+        <v>90</v>
+      </c>
+      <c r="F20">
+        <v>3870</v>
+      </c>
+      <c r="G20">
+        <v>1000</v>
+      </c>
+      <c r="H20">
+        <v>17</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>53</v>
+      </c>
+      <c r="K20">
+        <v>3</v>
+      </c>
+      <c r="L20">
+        <v>6</v>
+      </c>
+      <c r="M20">
+        <v>8</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>87</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>1</v>
+      </c>
+      <c r="U20">
+        <v>9</v>
+      </c>
+      <c r="V20">
+        <v>6</v>
+      </c>
+      <c r="W20">
+        <v>1</v>
+      </c>
+      <c r="X20">
+        <v>1</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
+      </c>
+      <c r="Z20">
+        <v>1</v>
+      </c>
+      <c r="AA20">
+        <v>16</v>
+      </c>
+      <c r="AB20">
+        <v>0</v>
+      </c>
+      <c r="AC20">
+        <v>0</v>
+      </c>
+      <c r="AD20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>19/06/2026</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Fri</v>
+      </c>
+      <c r="C21">
+        <v>2880</v>
+      </c>
+      <c r="D21">
+        <v>840</v>
+      </c>
+      <c r="E21">
+        <v>60</v>
+      </c>
+      <c r="F21">
+        <v>780</v>
+      </c>
+      <c r="G21">
+        <v>2040</v>
+      </c>
+      <c r="H21">
+        <v>12</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>21</v>
+      </c>
+      <c r="K21">
+        <v>5</v>
+      </c>
+      <c r="L21">
+        <v>7</v>
+      </c>
+      <c r="M21">
+        <v>2</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>47</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>1</v>
+      </c>
+      <c r="U21">
+        <v>5</v>
+      </c>
+      <c r="V21">
+        <v>10</v>
+      </c>
+      <c r="W21">
+        <v>1.5</v>
+      </c>
+      <c r="X21">
+        <v>1</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+      <c r="Z21">
+        <v>1</v>
+      </c>
+      <c r="AA21">
+        <v>4</v>
+      </c>
+      <c r="AB21">
+        <v>0</v>
+      </c>
+      <c r="AC21">
+        <v>0</v>
+      </c>
+      <c r="AD21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>20/06/2026</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Sat</v>
+      </c>
+      <c r="C22">
+        <v>11630</v>
+      </c>
+      <c r="D22">
+        <v>6190</v>
+      </c>
+      <c r="E22">
+        <v>180</v>
+      </c>
+      <c r="F22">
+        <v>6010</v>
+      </c>
+      <c r="G22">
+        <v>5440</v>
+      </c>
+      <c r="H22">
+        <v>63</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>79</v>
+      </c>
+      <c r="K22">
+        <v>19</v>
+      </c>
+      <c r="L22">
+        <v>31</v>
+      </c>
+      <c r="M22">
+        <v>16</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>208</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>2.5</v>
+      </c>
+      <c r="U22">
+        <v>12</v>
+      </c>
+      <c r="V22">
+        <v>38</v>
+      </c>
+      <c r="W22">
+        <v>4</v>
+      </c>
+      <c r="X22">
+        <v>4</v>
+      </c>
+      <c r="Y22">
+        <v>1</v>
+      </c>
+      <c r="Z22">
+        <v>4</v>
+      </c>
+      <c r="AA22">
+        <v>32</v>
+      </c>
+      <c r="AB22">
+        <v>0</v>
+      </c>
+      <c r="AC22">
+        <v>0</v>
+      </c>
+      <c r="AD22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>TOTAL</v>
+      </c>
+      <c r="B24" t="str">
+        <v>20 days</v>
+      </c>
+      <c r="C24">
+        <v>124150</v>
+      </c>
+      <c r="D24">
+        <v>67420</v>
+      </c>
+      <c r="E24">
+        <v>2290</v>
+      </c>
+      <c r="F24">
+        <v>65130</v>
+      </c>
+      <c r="G24">
+        <v>56730</v>
+      </c>
+      <c r="H24">
+        <v>731</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>779</v>
+      </c>
+      <c r="K24">
+        <v>96</v>
+      </c>
+      <c r="L24">
+        <v>339</v>
+      </c>
+      <c r="M24">
+        <v>205</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>2150</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>8</v>
+      </c>
+      <c r="T24">
+        <v>32.5</v>
+      </c>
+      <c r="U24">
+        <v>150</v>
+      </c>
+      <c r="V24">
+        <v>148</v>
+      </c>
+      <c r="W24">
+        <v>32.5</v>
+      </c>
+      <c r="X24">
+        <v>32.5</v>
+      </c>
+      <c r="Y24">
+        <v>14.5</v>
+      </c>
+      <c r="Z24">
+        <v>23</v>
+      </c>
+      <c r="AA24">
+        <v>347</v>
+      </c>
+      <c r="AB24">
+        <v>0</v>
+      </c>
+      <c r="AC24">
+        <v>0</v>
+      </c>
+      <c r="AD24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
         <v>AVG/DAY</v>
       </c>
-      <c r="C19">
-        <v>6033.846153846154</v>
-      </c>
-      <c r="D19">
-        <v>3337.6923076923076</v>
-      </c>
-      <c r="E19">
-        <v>118.46153846153847</v>
-      </c>
-      <c r="F19">
-        <v>3219.230769230769</v>
-      </c>
-      <c r="G19">
-        <v>2696.153846153846</v>
-      </c>
-      <c r="H19">
-        <v>32.23076923076923</v>
-      </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19">
-        <v>24.53846153846154</v>
-      </c>
-      <c r="K19">
-        <v>3.923076923076923</v>
-      </c>
-      <c r="L19">
-        <v>17.923076923076923</v>
-      </c>
-      <c r="M19">
-        <v>10.846153846153847</v>
-      </c>
-      <c r="N19">
-        <v>0</v>
-      </c>
-      <c r="O19">
-        <v>0</v>
-      </c>
-      <c r="P19">
-        <v>0</v>
-      </c>
-      <c r="Q19">
-        <v>89.46153846153847</v>
-      </c>
-      <c r="R19">
-        <v>0</v>
-      </c>
-      <c r="S19">
-        <v>0</v>
-      </c>
-      <c r="T19">
-        <v>7.938461538461539</v>
-      </c>
-      <c r="U19">
-        <v>9.184615384615386</v>
-      </c>
-      <c r="V19">
-        <v>4.461538461538462</v>
-      </c>
-      <c r="W19">
-        <v>1.4230769230769231</v>
-      </c>
-      <c r="X19">
-        <v>1.4615384615384615</v>
-      </c>
-      <c r="Y19">
-        <v>0.8076923076923077</v>
-      </c>
-      <c r="Z19">
-        <v>0.7692307692307693</v>
-      </c>
-      <c r="AA19">
-        <v>16.076923076923077</v>
-      </c>
-      <c r="AB19">
-        <v>0</v>
-      </c>
-      <c r="AC19">
-        <v>0</v>
-      </c>
-      <c r="AD19">
+      <c r="C25">
+        <v>6207.5</v>
+      </c>
+      <c r="D25">
+        <v>3371</v>
+      </c>
+      <c r="E25">
+        <v>114.5</v>
+      </c>
+      <c r="F25">
+        <v>3256.5</v>
+      </c>
+      <c r="G25">
+        <v>2836.5</v>
+      </c>
+      <c r="H25">
+        <v>36.55</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>38.95</v>
+      </c>
+      <c r="K25">
+        <v>4.8</v>
+      </c>
+      <c r="L25">
+        <v>16.95</v>
+      </c>
+      <c r="M25">
+        <v>10.25</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>107.5</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0.4</v>
+      </c>
+      <c r="T25">
+        <v>1.625</v>
+      </c>
+      <c r="U25">
+        <v>7.5</v>
+      </c>
+      <c r="V25">
+        <v>7.4</v>
+      </c>
+      <c r="W25">
+        <v>1.625</v>
+      </c>
+      <c r="X25">
+        <v>1.625</v>
+      </c>
+      <c r="Y25">
+        <v>0.725</v>
+      </c>
+      <c r="Z25">
+        <v>1.15</v>
+      </c>
+      <c r="AA25">
+        <v>17.35</v>
+      </c>
+      <c r="AB25">
+        <v>0</v>
+      </c>
+      <c r="AC25">
+        <v>0</v>
+      </c>
+      <c r="AD25">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AD19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AD25"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/3_Automation_Dashboard/SomSaiJai_Dashboard_B1_2026.xlsx
+++ b/3_Automation_Dashboard/SomSaiJai_Dashboard_B1_2026.xlsx
@@ -1168,7 +1168,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F304"/>
+  <dimension ref="A1:F319"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1886,18 +1886,18 @@
         <v>COGS</v>
       </c>
       <c r="D38" t="str">
-        <v>Transportation</v>
+        <v>Watermelon</v>
       </c>
       <c r="E38" t="str">
-        <v>Unknown</v>
+        <v>แตงโม 40 ลูก</v>
       </c>
       <c r="F38">
-        <v>400</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>23/01/2026</v>
+        <v>25/01/2026</v>
       </c>
       <c r="B39" t="str">
         <v>Jan26</v>
@@ -1906,13 +1906,13 @@
         <v>COGS</v>
       </c>
       <c r="D39" t="str">
-        <v>Watermelon</v>
+        <v>Orange</v>
       </c>
       <c r="E39" t="str">
-        <v>แตงโม 40 ลูก</v>
+        <v>ส้ม5ตะกร้า แตงโม 40 ลูก</v>
       </c>
       <c r="F39">
-        <v>3200</v>
+        <v>5950</v>
       </c>
     </row>
     <row r="40">
@@ -1926,18 +1926,18 @@
         <v>COGS</v>
       </c>
       <c r="D40" t="str">
-        <v>Orange</v>
+        <v>Transportation</v>
       </c>
       <c r="E40" t="str">
-        <v>ส้ม5ตะกร้า แตงโม 40 ลูก</v>
+        <v>ค่าส่งฝา</v>
       </c>
       <c r="F40">
-        <v>5950</v>
+        <v>114</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>25/01/2026</v>
+        <v>26/01/2026</v>
       </c>
       <c r="B41" t="str">
         <v>Jan26</v>
@@ -1946,13 +1946,13 @@
         <v>COGS</v>
       </c>
       <c r="D41" t="str">
-        <v>Transportation</v>
+        <v>Orange</v>
       </c>
       <c r="E41" t="str">
-        <v>ค่าส่งฝา</v>
+        <v>ค่าส้ม 30 ตะกร้า</v>
       </c>
       <c r="F41">
-        <v>114</v>
+        <v>10680</v>
       </c>
     </row>
     <row r="42">
@@ -1966,18 +1966,18 @@
         <v>COGS</v>
       </c>
       <c r="D42" t="str">
-        <v>Orange</v>
+        <v>Transportation</v>
       </c>
       <c r="E42" t="str">
-        <v>ค่าส้ม 30 ตะกร้า</v>
+        <v>Unknown</v>
       </c>
       <c r="F42">
-        <v>10680</v>
+        <v>400</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>26/01/2026</v>
+        <v>27/01/2026</v>
       </c>
       <c r="B43" t="str">
         <v>Jan26</v>
@@ -1986,18 +1986,18 @@
         <v>COGS</v>
       </c>
       <c r="D43" t="str">
-        <v>Transportation</v>
+        <v>Packaging</v>
       </c>
       <c r="E43" t="str">
-        <v>Unknown</v>
+        <v>ถุงมือ - 5 กล่อง</v>
       </c>
       <c r="F43">
-        <v>400</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>26/01/2026</v>
+        <v>28/01/2026</v>
       </c>
       <c r="B44" t="str">
         <v>Jan26</v>
@@ -2009,15 +2009,15 @@
         <v>Transportation</v>
       </c>
       <c r="E44" t="str">
-        <v>Unknown</v>
+        <v>ค่าส่ง</v>
       </c>
       <c r="F44">
-        <v>400</v>
+        <v>486</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>27/01/2026</v>
+        <v>28/01/2026</v>
       </c>
       <c r="B45" t="str">
         <v>Jan26</v>
@@ -2026,13 +2026,13 @@
         <v>COGS</v>
       </c>
       <c r="D45" t="str">
-        <v>Packaging</v>
+        <v>Transportation</v>
       </c>
       <c r="E45" t="str">
-        <v>ถุงมือ - 5 กล่อง</v>
+        <v>Unknown</v>
       </c>
       <c r="F45">
-        <v>1077</v>
+        <v>400</v>
       </c>
     </row>
     <row r="46">
@@ -2046,18 +2046,18 @@
         <v>COGS</v>
       </c>
       <c r="D46" t="str">
-        <v>Transportation</v>
+        <v>Watermelon</v>
       </c>
       <c r="E46" t="str">
-        <v>ค่าส่ง</v>
+        <v>ค่าแตงโม 50 ลูก</v>
       </c>
       <c r="F46">
-        <v>486</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>28/01/2026</v>
+        <v>30/01/2026</v>
       </c>
       <c r="B47" t="str">
         <v>Jan26</v>
@@ -2066,18 +2066,18 @@
         <v>COGS</v>
       </c>
       <c r="D47" t="str">
-        <v>Transportation</v>
+        <v>Watermelon</v>
       </c>
       <c r="E47" t="str">
-        <v>Unknown</v>
+        <v>แตงโม 25 ลูก</v>
       </c>
       <c r="F47">
-        <v>400</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>28/01/2026</v>
+        <v>30/01/2026</v>
       </c>
       <c r="B48" t="str">
         <v>Jan26</v>
@@ -2086,61 +2086,61 @@
         <v>COGS</v>
       </c>
       <c r="D48" t="str">
-        <v>Watermelon</v>
+        <v>Apple</v>
       </c>
       <c r="E48" t="str">
-        <v>ค่าแตงโม 50 ลูก</v>
+        <v>แอปเปิ้ล เมล่อน</v>
       </c>
       <c r="F48">
-        <v>4000</v>
+        <v>851</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>28/01/2026</v>
+        <v>31/01/2026</v>
       </c>
       <c r="B49" t="str">
         <v>Jan26</v>
       </c>
       <c r="C49" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D49" t="str">
-        <v>Transportation</v>
+        <v>Salary</v>
       </c>
       <c r="E49" t="str">
-        <v>Unknown</v>
+        <v>เงินเดือนเมนมกราคม</v>
       </c>
       <c r="F49">
-        <v>400</v>
+        <v>19000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>28/01/2026</v>
+        <v>02/02/2026</v>
       </c>
       <c r="B50" t="str">
-        <v>Jan26</v>
+        <v>Feb26</v>
       </c>
       <c r="C50" t="str">
         <v>COGS</v>
       </c>
       <c r="D50" t="str">
-        <v>Transportation</v>
+        <v>Orange</v>
       </c>
       <c r="E50" t="str">
-        <v>ค่าส่ง</v>
+        <v>ส้ม 30 ตะกร้า</v>
       </c>
       <c r="F50">
-        <v>486</v>
+        <v>10680</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>28/01/2026</v>
+        <v>02/02/2026</v>
       </c>
       <c r="B51" t="str">
-        <v>Jan26</v>
+        <v>Feb26</v>
       </c>
       <c r="C51" t="str">
         <v>COGS</v>
@@ -2157,19 +2157,19 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>30/01/2026</v>
+        <v>02/02/2026</v>
       </c>
       <c r="B52" t="str">
-        <v>Jan26</v>
+        <v>Feb26</v>
       </c>
       <c r="C52" t="str">
         <v>COGS</v>
       </c>
       <c r="D52" t="str">
-        <v>Watermelon</v>
+        <v>Transportation</v>
       </c>
       <c r="E52" t="str">
-        <v>แตงโม 25 ลูก</v>
+        <v>Unknown</v>
       </c>
       <c r="F52">
         <v>2000</v>
@@ -2177,47 +2177,47 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>30/01/2026</v>
+        <v>04/02/2026</v>
       </c>
       <c r="B53" t="str">
-        <v>Jan26</v>
+        <v>Feb26</v>
       </c>
       <c r="C53" t="str">
         <v>COGS</v>
       </c>
       <c r="D53" t="str">
-        <v>Apple</v>
+        <v>Packaging</v>
       </c>
       <c r="E53" t="str">
-        <v>แอปเปิ้ล เมล่อน</v>
+        <v>ฝา 690 1000 ชิ้น แก้ว 1196 1000 ชิ้น หลอด 421</v>
       </c>
       <c r="F53">
-        <v>851</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>31/01/2026</v>
+        <v>05/02/2026</v>
       </c>
       <c r="B54" t="str">
-        <v>Jan26</v>
+        <v>Feb26</v>
       </c>
       <c r="C54" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D54" t="str">
-        <v>Salary</v>
+        <v>Watermelon</v>
       </c>
       <c r="E54" t="str">
-        <v>เงินเดือนเมนมกราคม</v>
+        <v>แตงโม 50 ลูก</v>
       </c>
       <c r="F54">
-        <v>19000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>02/02/2026</v>
+        <v>05/02/2026</v>
       </c>
       <c r="B55" t="str">
         <v>Feb26</v>
@@ -2226,18 +2226,18 @@
         <v>COGS</v>
       </c>
       <c r="D55" t="str">
-        <v>Orange</v>
+        <v>Packaging</v>
       </c>
       <c r="E55" t="str">
-        <v>ส้ม 30 ตะกร้า</v>
+        <v>แก้วสกรีน อย่างเดียวไม่รวมฝา 2280บาท</v>
       </c>
       <c r="F55">
-        <v>10680</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>02/02/2026</v>
+        <v>08/02/2026</v>
       </c>
       <c r="B56" t="str">
         <v>Feb26</v>
@@ -2246,18 +2246,18 @@
         <v>COGS</v>
       </c>
       <c r="D56" t="str">
-        <v>Watermelon</v>
+        <v>Ice</v>
       </c>
       <c r="E56" t="str">
-        <v>แตงโม 50 ลูก</v>
+        <v>Unknown</v>
       </c>
       <c r="F56">
-        <v>4000</v>
+        <v>798</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>02/02/2026</v>
+        <v>08/02/2026</v>
       </c>
       <c r="B57" t="str">
         <v>Feb26</v>
@@ -2266,18 +2266,18 @@
         <v>COGS</v>
       </c>
       <c r="D57" t="str">
-        <v>Transportation</v>
+        <v>Watermelon</v>
       </c>
       <c r="E57" t="str">
-        <v>Unknown</v>
+        <v>แตงโม 50</v>
       </c>
       <c r="F57">
-        <v>2000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>04/02/2026</v>
+        <v>08/02/2026</v>
       </c>
       <c r="B58" t="str">
         <v>Feb26</v>
@@ -2286,18 +2286,18 @@
         <v>COGS</v>
       </c>
       <c r="D58" t="str">
-        <v>Packaging</v>
+        <v>Transportation</v>
       </c>
       <c r="E58" t="str">
-        <v>ฝา 690 1000 ชิ้น แก้ว 1196 1000 ชิ้น หลอด 421</v>
+        <v>Unknown</v>
       </c>
       <c r="F58">
-        <v>2023</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>05/02/2026</v>
+        <v>09/02/2026</v>
       </c>
       <c r="B59" t="str">
         <v>Feb26</v>
@@ -2306,18 +2306,18 @@
         <v>COGS</v>
       </c>
       <c r="D59" t="str">
-        <v>Watermelon</v>
+        <v>Orange</v>
       </c>
       <c r="E59" t="str">
-        <v>แตงโม 50 ลูก</v>
+        <v>ส้ม 30 ตะกร้า</v>
       </c>
       <c r="F59">
-        <v>4000</v>
+        <v>10680</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>05/02/2026</v>
+        <v>09/02/2026</v>
       </c>
       <c r="B60" t="str">
         <v>Feb26</v>
@@ -2326,18 +2326,18 @@
         <v>COGS</v>
       </c>
       <c r="D60" t="str">
-        <v>Packaging</v>
+        <v>Orange</v>
       </c>
       <c r="E60" t="str">
-        <v>แก้วสกรีน อย่างเดียวไม่รวมฝา 2280บาท</v>
+        <v>ค่าส่งส้ม</v>
       </c>
       <c r="F60">
-        <v>2280</v>
+        <v>685</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>08/02/2026</v>
+        <v>10/02/2026</v>
       </c>
       <c r="B61" t="str">
         <v>Feb26</v>
@@ -2349,15 +2349,15 @@
         <v>Ice</v>
       </c>
       <c r="E61" t="str">
-        <v>Unknown</v>
+        <v>ค่าไฟเดือนมค</v>
       </c>
       <c r="F61">
-        <v>798</v>
+        <v>389</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>08/02/2026</v>
+        <v>11/02/2026</v>
       </c>
       <c r="B62" t="str">
         <v>Feb26</v>
@@ -2369,7 +2369,7 @@
         <v>Watermelon</v>
       </c>
       <c r="E62" t="str">
-        <v>แตงโม 50</v>
+        <v>แตงโม 50 ลูก</v>
       </c>
       <c r="F62">
         <v>4000</v>
@@ -2377,27 +2377,27 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>08/02/2026</v>
+        <v>14/02/2026</v>
       </c>
       <c r="B63" t="str">
         <v>Feb26</v>
       </c>
       <c r="C63" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D63" t="str">
-        <v>Transportation</v>
+        <v>Other</v>
       </c>
       <c r="E63" t="str">
         <v>Unknown</v>
       </c>
       <c r="F63">
-        <v>2000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>09/02/2026</v>
+        <v>14/02/2026</v>
       </c>
       <c r="B64" t="str">
         <v>Feb26</v>
@@ -2406,18 +2406,18 @@
         <v>COGS</v>
       </c>
       <c r="D64" t="str">
-        <v>Orange</v>
+        <v>Ice</v>
       </c>
       <c r="E64" t="str">
-        <v>ส้ม 30 ตะกร้า</v>
+        <v>Unknown</v>
       </c>
       <c r="F64">
-        <v>10680</v>
+        <v>350</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>09/02/2026</v>
+        <v>16/02/2026</v>
       </c>
       <c r="B65" t="str">
         <v>Feb26</v>
@@ -2432,12 +2432,12 @@
         <v>ค่าส่งส้ม</v>
       </c>
       <c r="F65">
-        <v>685</v>
+        <v>485</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>10/02/2026</v>
+        <v>16/02/2026</v>
       </c>
       <c r="B66" t="str">
         <v>Feb26</v>
@@ -2446,18 +2446,18 @@
         <v>COGS</v>
       </c>
       <c r="D66" t="str">
-        <v>Ice</v>
+        <v>Orange</v>
       </c>
       <c r="E66" t="str">
-        <v>ค่าไฟเดือนมค</v>
+        <v>ค่าส้ม 30 ตะกร้า 13/2/69</v>
       </c>
       <c r="F66">
-        <v>389</v>
+        <v>10680</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>11/02/2026</v>
+        <v>19/02/2026</v>
       </c>
       <c r="B67" t="str">
         <v>Feb26</v>
@@ -2469,35 +2469,35 @@
         <v>Watermelon</v>
       </c>
       <c r="E67" t="str">
-        <v>แตงโม 50 ลูก</v>
+        <v>แตงโม 50 ลูก วันที่ 1719</v>
       </c>
       <c r="F67">
-        <v>4000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>14/02/2026</v>
+        <v>19/02/2026</v>
       </c>
       <c r="B68" t="str">
         <v>Feb26</v>
       </c>
       <c r="C68" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D68" t="str">
-        <v>Other</v>
+        <v>Packaging</v>
       </c>
       <c r="E68" t="str">
-        <v>Unknown</v>
+        <v>แก้ว</v>
       </c>
       <c r="F68">
-        <v>4000</v>
+        <v>3315</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>14/02/2026</v>
+        <v>19/02/2026</v>
       </c>
       <c r="B69" t="str">
         <v>Feb26</v>
@@ -2506,18 +2506,18 @@
         <v>COGS</v>
       </c>
       <c r="D69" t="str">
-        <v>Ice</v>
+        <v>Transportation</v>
       </c>
       <c r="E69" t="str">
-        <v>Unknown</v>
+        <v>แก้วสกรีน2ลัง(รอบที่1นะ แบ่งสั่งจะได้ไม่มีค่า</v>
       </c>
       <c r="F69">
-        <v>350</v>
+        <v>6655</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>16/02/2026</v>
+        <v>19/02/2026</v>
       </c>
       <c r="B70" t="str">
         <v>Feb26</v>
@@ -2526,18 +2526,18 @@
         <v>COGS</v>
       </c>
       <c r="D70" t="str">
-        <v>Orange</v>
+        <v>Transportation</v>
       </c>
       <c r="E70" t="str">
-        <v>ค่าส่งส้ม</v>
+        <v>Unknown</v>
       </c>
       <c r="F70">
-        <v>485</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>16/02/2026</v>
+        <v>20/02/2026</v>
       </c>
       <c r="B71" t="str">
         <v>Feb26</v>
@@ -2546,18 +2546,18 @@
         <v>COGS</v>
       </c>
       <c r="D71" t="str">
-        <v>Orange</v>
+        <v>Ice</v>
       </c>
       <c r="E71" t="str">
-        <v>ค่าส้ม 30 ตะกร้า 13/2/69</v>
+        <v>ผ้าปิดร้าน 218 ค่ารถ 198</v>
       </c>
       <c r="F71">
-        <v>10680</v>
+        <v>416</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>19/02/2026</v>
+        <v>23/02/2026</v>
       </c>
       <c r="B72" t="str">
         <v>Feb26</v>
@@ -2569,7 +2569,7 @@
         <v>Watermelon</v>
       </c>
       <c r="E72" t="str">
-        <v>แตงโม 50 ลูก วันที่ 1719</v>
+        <v>แตงโม 21 50 ลูก 23 50 ลูก</v>
       </c>
       <c r="F72">
         <v>8000</v>
@@ -2577,7 +2577,7 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>19/02/2026</v>
+        <v>24/02/2026</v>
       </c>
       <c r="B73" t="str">
         <v>Feb26</v>
@@ -2586,18 +2586,18 @@
         <v>COGS</v>
       </c>
       <c r="D73" t="str">
-        <v>Packaging</v>
+        <v>Transportation</v>
       </c>
       <c r="E73" t="str">
-        <v>แก้ว</v>
+        <v>Unknown</v>
       </c>
       <c r="F73">
-        <v>3315</v>
+        <v>209</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>19/02/2026</v>
+        <v>24/02/2026</v>
       </c>
       <c r="B74" t="str">
         <v>Feb26</v>
@@ -2606,18 +2606,18 @@
         <v>COGS</v>
       </c>
       <c r="D74" t="str">
-        <v>Transportation</v>
+        <v>Orange</v>
       </c>
       <c r="E74" t="str">
-        <v>แก้วสกรีน2ลัง(รอบที่1นะ แบ่งสั่งจะได้ไม่มีค่า</v>
+        <v>ส้ม 30 18/2/69</v>
       </c>
       <c r="F74">
-        <v>6655</v>
+        <v>10680</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>19/02/2026</v>
+        <v>24/02/2026</v>
       </c>
       <c r="B75" t="str">
         <v>Feb26</v>
@@ -2626,18 +2626,18 @@
         <v>COGS</v>
       </c>
       <c r="D75" t="str">
-        <v>Transportation</v>
+        <v>Packaging</v>
       </c>
       <c r="E75" t="str">
-        <v>Unknown</v>
+        <v>แก้ว 2400 ฝา 1670</v>
       </c>
       <c r="F75">
-        <v>2000</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>20/02/2026</v>
+        <v>25/02/2026</v>
       </c>
       <c r="B76" t="str">
         <v>Feb26</v>
@@ -2646,18 +2646,18 @@
         <v>COGS</v>
       </c>
       <c r="D76" t="str">
-        <v>Ice</v>
+        <v>Watermelon</v>
       </c>
       <c r="E76" t="str">
-        <v>ผ้าปิดร้าน 218 ค่ารถ 198</v>
+        <v>แตงโม 50</v>
       </c>
       <c r="F76">
-        <v>416</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>23/02/2026</v>
+        <v>25/02/2026</v>
       </c>
       <c r="B77" t="str">
         <v>Feb26</v>
@@ -2666,18 +2666,18 @@
         <v>COGS</v>
       </c>
       <c r="D77" t="str">
-        <v>Watermelon</v>
+        <v>Transportation</v>
       </c>
       <c r="E77" t="str">
-        <v>แตงโม 21 50 ลูก 23 50 ลูก</v>
+        <v>Unknown</v>
       </c>
       <c r="F77">
-        <v>8000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>24/02/2026</v>
+        <v>25/02/2026</v>
       </c>
       <c r="B78" t="str">
         <v>Feb26</v>
@@ -2686,18 +2686,18 @@
         <v>COGS</v>
       </c>
       <c r="D78" t="str">
-        <v>Transportation</v>
+        <v>Orange</v>
       </c>
       <c r="E78" t="str">
-        <v>Unknown</v>
+        <v>ส้ม20 ตะกร้า</v>
       </c>
       <c r="F78">
-        <v>209</v>
+        <v>7312</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>24/02/2026</v>
+        <v>25/02/2026</v>
       </c>
       <c r="B79" t="str">
         <v>Feb26</v>
@@ -2709,15 +2709,15 @@
         <v>Orange</v>
       </c>
       <c r="E79" t="str">
-        <v>ส้ม 30 18/2/69</v>
+        <v>ค่าส่งส้ม</v>
       </c>
       <c r="F79">
-        <v>10680</v>
+        <v>806</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>24/02/2026</v>
+        <v>26/02/2026</v>
       </c>
       <c r="B80" t="str">
         <v>Feb26</v>
@@ -2729,15 +2729,15 @@
         <v>Packaging</v>
       </c>
       <c r="E80" t="str">
-        <v>แก้ว 2400 ฝา 1670</v>
+        <v>ค่าขวดใหญ่</v>
       </c>
       <c r="F80">
-        <v>4070</v>
+        <v>319</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>25/02/2026</v>
+        <v>28/02/2026</v>
       </c>
       <c r="B81" t="str">
         <v>Feb26</v>
@@ -2746,38 +2746,38 @@
         <v>COGS</v>
       </c>
       <c r="D81" t="str">
-        <v>Watermelon</v>
+        <v>Orange</v>
       </c>
       <c r="E81" t="str">
-        <v>แตงโม 50</v>
+        <v>ค่าส่งส้ม</v>
       </c>
       <c r="F81">
-        <v>4000</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>25/02/2026</v>
+        <v>28/02/2026</v>
       </c>
       <c r="B82" t="str">
         <v>Feb26</v>
       </c>
       <c r="C82" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D82" t="str">
-        <v>Transportation</v>
+        <v>Rental</v>
       </c>
       <c r="E82" t="str">
-        <v>Unknown</v>
+        <v>ค่าเช่าสต็อคกพ</v>
       </c>
       <c r="F82">
-        <v>2000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>25/02/2026</v>
+        <v>28/02/2026</v>
       </c>
       <c r="B83" t="str">
         <v>Feb26</v>
@@ -2786,58 +2786,58 @@
         <v>COGS</v>
       </c>
       <c r="D83" t="str">
-        <v>Orange</v>
+        <v>Watermelon</v>
       </c>
       <c r="E83" t="str">
-        <v>ส้ม20 ตะกร้า</v>
+        <v>แตงโม 50 ลูก</v>
       </c>
       <c r="F83">
-        <v>7312</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>25/02/2026</v>
+        <v>04/03/2026</v>
       </c>
       <c r="B84" t="str">
-        <v>Feb26</v>
+        <v>Mar26</v>
       </c>
       <c r="C84" t="str">
         <v>COGS</v>
       </c>
       <c r="D84" t="str">
-        <v>Orange</v>
+        <v>Watermelon</v>
       </c>
       <c r="E84" t="str">
-        <v>ค่าส่งส้ม</v>
+        <v>ค่าทางด่วนส่งแตงโม</v>
       </c>
       <c r="F84">
-        <v>806</v>
+        <v>140</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>26/02/2026</v>
+        <v>04/03/2026</v>
       </c>
       <c r="B85" t="str">
-        <v>Feb26</v>
+        <v>Mar26</v>
       </c>
       <c r="C85" t="str">
         <v>COGS</v>
       </c>
       <c r="D85" t="str">
-        <v>Packaging</v>
+        <v>Mango</v>
       </c>
       <c r="E85" t="str">
-        <v>ค่าขวดใหญ่</v>
+        <v>มะม่วง 16 โล</v>
       </c>
       <c r="F85">
-        <v>319</v>
+        <v>560</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>28/02/2026</v>
+        <v>05/03/2026</v>
       </c>
       <c r="B86" t="str">
         <v>Feb26</v>
@@ -2846,18 +2846,18 @@
         <v>COGS</v>
       </c>
       <c r="D86" t="str">
-        <v>Orange</v>
+        <v>Mango</v>
       </c>
       <c r="E86" t="str">
-        <v>ค่าส่งส้ม</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F86">
-        <v>2237</v>
+        <v>500</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>28/02/2026</v>
+        <v>05/03/2026</v>
       </c>
       <c r="B87" t="str">
         <v>Feb26</v>
@@ -2869,55 +2869,55 @@
         <v>Orange</v>
       </c>
       <c r="E87" t="str">
-        <v>ค่าส่งส้ม</v>
+        <v>ค่าส้มวันที่ 27269</v>
       </c>
       <c r="F87">
-        <v>2237</v>
+        <v>7312</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>28/02/2026</v>
+        <v>05/03/2026</v>
       </c>
       <c r="B88" t="str">
-        <v>Feb26</v>
+        <v>Mar26</v>
       </c>
       <c r="C88" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D88" t="str">
-        <v>Rental</v>
+        <v>Orange</v>
       </c>
       <c r="E88" t="str">
-        <v>ค่าเช่าสต็อคกพ</v>
+        <v>แตงโม 51 ยอด3,500</v>
       </c>
       <c r="F88">
-        <v>12000</v>
+        <v>7700</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>28/02/2026</v>
+        <v>05/03/2026</v>
       </c>
       <c r="B89" t="str">
-        <v>Feb26</v>
+        <v>Mar26</v>
       </c>
       <c r="C89" t="str">
         <v>COGS</v>
       </c>
       <c r="D89" t="str">
-        <v>Watermelon</v>
+        <v>Orange</v>
       </c>
       <c r="E89" t="str">
-        <v>แตงโม 50 ลูก</v>
+        <v>ค่าส้ม 20 ตะกร้า</v>
       </c>
       <c r="F89">
-        <v>4000</v>
+        <v>7312</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>04/03/2026</v>
+        <v>05/03/2026</v>
       </c>
       <c r="B90" t="str">
         <v>Mar26</v>
@@ -2926,18 +2926,18 @@
         <v>COGS</v>
       </c>
       <c r="D90" t="str">
-        <v>Watermelon</v>
+        <v>Ice</v>
       </c>
       <c r="E90" t="str">
-        <v>ค่าทางด่วนส่งแตงโม</v>
+        <v>ค่าทางด่วน</v>
       </c>
       <c r="F90">
-        <v>140</v>
+        <v>105</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>04/03/2026</v>
+        <v>05/03/2026</v>
       </c>
       <c r="B91" t="str">
         <v>Mar26</v>
@@ -2946,13 +2946,13 @@
         <v>COGS</v>
       </c>
       <c r="D91" t="str">
-        <v>Mango</v>
+        <v>Packaging</v>
       </c>
       <c r="E91" t="str">
-        <v>มะม่วง 16 โล</v>
+        <v>ถุงขยะ</v>
       </c>
       <c r="F91">
-        <v>560</v>
+        <v>909</v>
       </c>
     </row>
     <row r="92">
@@ -2960,7 +2960,7 @@
         <v>05/03/2026</v>
       </c>
       <c r="B92" t="str">
-        <v>Feb26</v>
+        <v>Mar26</v>
       </c>
       <c r="C92" t="str">
         <v>COGS</v>
@@ -2969,35 +2969,35 @@
         <v>Mango</v>
       </c>
       <c r="E92" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>มะม่วง 24 โล</v>
       </c>
       <c r="F92">
-        <v>500</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>05/03/2026</v>
+        <v>07/03/2026</v>
       </c>
       <c r="B93" t="str">
-        <v>Feb26</v>
+        <v>Mar26</v>
       </c>
       <c r="C93" t="str">
         <v>COGS</v>
       </c>
       <c r="D93" t="str">
-        <v>Orange</v>
+        <v>Transportation</v>
       </c>
       <c r="E93" t="str">
-        <v>ค่าส้มวันที่ 27269</v>
+        <v>Unknown</v>
       </c>
       <c r="F93">
-        <v>7312</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>05/03/2026</v>
+        <v>10/03/2026</v>
       </c>
       <c r="B94" t="str">
         <v>Mar26</v>
@@ -3009,15 +3009,15 @@
         <v>Orange</v>
       </c>
       <c r="E94" t="str">
-        <v>แตงโม 51 ยอด3,500</v>
+        <v>09/03/69</v>
       </c>
       <c r="F94">
-        <v>7700</v>
+        <v>9804</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>05/03/2026</v>
+        <v>10/03/2026</v>
       </c>
       <c r="B95" t="str">
         <v>Mar26</v>
@@ -3026,38 +3026,38 @@
         <v>COGS</v>
       </c>
       <c r="D95" t="str">
-        <v>Orange</v>
+        <v>Watermelon</v>
       </c>
       <c r="E95" t="str">
-        <v>ค่าส้ม 20 ตะกร้า</v>
+        <v>แตงโม 50 วันที่ 7 แตงโม 50 วันที่ 10</v>
       </c>
       <c r="F95">
-        <v>7312</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>05/03/2026</v>
+        <v>10/03/2026</v>
       </c>
       <c r="B96" t="str">
         <v>Mar26</v>
       </c>
       <c r="C96" t="str">
-        <v>COGS</v>
+        <v>CAPEX</v>
       </c>
       <c r="D96" t="str">
-        <v>Ice</v>
+        <v>Investment</v>
       </c>
       <c r="E96" t="str">
-        <v>ค่าทางด่วน</v>
+        <v>Unknown</v>
       </c>
       <c r="F96">
-        <v>105</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>05/03/2026</v>
+        <v>10/03/2026</v>
       </c>
       <c r="B97" t="str">
         <v>Mar26</v>
@@ -3069,15 +3069,15 @@
         <v>Packaging</v>
       </c>
       <c r="E97" t="str">
-        <v>ถุงขยะ</v>
+        <v>แก้ว2ลัง ลังละ 1560</v>
       </c>
       <c r="F97">
-        <v>909</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>05/03/2026</v>
+        <v>10/03/2026</v>
       </c>
       <c r="B98" t="str">
         <v>Mar26</v>
@@ -3086,18 +3086,18 @@
         <v>COGS</v>
       </c>
       <c r="D98" t="str">
-        <v>Mango</v>
+        <v>Orange</v>
       </c>
       <c r="E98" t="str">
-        <v>มะม่วง 24 โล</v>
+        <v>แก้วร้านน้ำส้ม 2ลัง ลังละ1560</v>
       </c>
       <c r="F98">
-        <v>1560</v>
+        <v>5667</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>07/03/2026</v>
+        <v>13/03/2026</v>
       </c>
       <c r="B99" t="str">
         <v>Mar26</v>
@@ -3106,18 +3106,18 @@
         <v>COGS</v>
       </c>
       <c r="D99" t="str">
-        <v>Transportation</v>
+        <v>Packaging</v>
       </c>
       <c r="E99" t="str">
-        <v>Unknown</v>
+        <v>หลอด 20 แพค</v>
       </c>
       <c r="F99">
-        <v>2000</v>
+        <v>765</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>10/03/2026</v>
+        <v>14/03/2026</v>
       </c>
       <c r="B100" t="str">
         <v>Mar26</v>
@@ -3126,18 +3126,18 @@
         <v>COGS</v>
       </c>
       <c r="D100" t="str">
-        <v>Orange</v>
+        <v>Apple</v>
       </c>
       <c r="E100" t="str">
-        <v>09/03/69</v>
+        <v>แอปเปิ้ลฟูจิ 32</v>
       </c>
       <c r="F100">
-        <v>9804</v>
+        <v>350</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>10/03/2026</v>
+        <v>14/03/2026</v>
       </c>
       <c r="B101" t="str">
         <v>Mar26</v>
@@ -3146,38 +3146,38 @@
         <v>COGS</v>
       </c>
       <c r="D101" t="str">
-        <v>Watermelon</v>
+        <v>Mango</v>
       </c>
       <c r="E101" t="str">
-        <v>แตงโม 50 วันที่ 7 แตงโม 50 วันที่ 10</v>
+        <v>มะม่วง 2 ลัง 44</v>
       </c>
       <c r="F101">
-        <v>8000</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>10/03/2026</v>
+        <v>15/03/2026</v>
       </c>
       <c r="B102" t="str">
         <v>Mar26</v>
       </c>
       <c r="C102" t="str">
-        <v>CAPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D102" t="str">
-        <v>Investment</v>
+        <v>Ice</v>
       </c>
       <c r="E102" t="str">
-        <v>Unknown</v>
+        <v>ค่าทางด่วน</v>
       </c>
       <c r="F102">
-        <v>6500</v>
+        <v>115</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>10/03/2026</v>
+        <v>15/03/2026</v>
       </c>
       <c r="B103" t="str">
         <v>Mar26</v>
@@ -3186,18 +3186,18 @@
         <v>COGS</v>
       </c>
       <c r="D103" t="str">
-        <v>Packaging</v>
+        <v>Watermelon</v>
       </c>
       <c r="E103" t="str">
-        <v>แก้ว2ลัง ลังละ 1560</v>
+        <v>น้ำมะพร้าว 5ขวดเละ 50฿</v>
       </c>
       <c r="F103">
-        <v>3120</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>10/03/2026</v>
+        <v>17/03/2026</v>
       </c>
       <c r="B104" t="str">
         <v>Mar26</v>
@@ -3206,18 +3206,18 @@
         <v>COGS</v>
       </c>
       <c r="D104" t="str">
-        <v>Orange</v>
+        <v>Ice</v>
       </c>
       <c r="E104" t="str">
-        <v>แก้วร้านน้ำส้ม 2ลัง ลังละ1560</v>
+        <v>ค่าไฟเดือนกพ มีนา</v>
       </c>
       <c r="F104">
-        <v>5667</v>
+        <v>2779.47</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>13/03/2026</v>
+        <v>19/03/2026</v>
       </c>
       <c r="B105" t="str">
         <v>Mar26</v>
@@ -3226,18 +3226,18 @@
         <v>COGS</v>
       </c>
       <c r="D105" t="str">
-        <v>Packaging</v>
+        <v>Watermelon</v>
       </c>
       <c r="E105" t="str">
-        <v>หลอด 20 แพค</v>
+        <v>ค่าแตงโม 18/3/67 51 ลูก 4000 บาท</v>
       </c>
       <c r="F105">
-        <v>765</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>14/03/2026</v>
+        <v>21/03/2026</v>
       </c>
       <c r="B106" t="str">
         <v>Mar26</v>
@@ -3246,18 +3246,18 @@
         <v>COGS</v>
       </c>
       <c r="D106" t="str">
-        <v>Apple</v>
+        <v>Ice</v>
       </c>
       <c r="E106" t="str">
-        <v>แอปเปิ้ลฟูจิ 32</v>
+        <v>สกรู กาวตะปู</v>
       </c>
       <c r="F106">
-        <v>350</v>
+        <v>117</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>14/03/2026</v>
+        <v>23/03/2026</v>
       </c>
       <c r="B107" t="str">
         <v>Mar26</v>
@@ -3269,15 +3269,15 @@
         <v>Mango</v>
       </c>
       <c r="E107" t="str">
-        <v>มะม่วง 2 ลัง 44</v>
+        <v>มะม่วง 44 โล</v>
       </c>
       <c r="F107">
-        <v>2420</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>15/03/2026</v>
+        <v>23/03/2026</v>
       </c>
       <c r="B108" t="str">
         <v>Mar26</v>
@@ -3286,18 +3286,18 @@
         <v>COGS</v>
       </c>
       <c r="D108" t="str">
-        <v>Ice</v>
+        <v>Orange</v>
       </c>
       <c r="E108" t="str">
-        <v>ค่าทางด่วน</v>
+        <v>22-3-2569</v>
       </c>
       <c r="F108">
-        <v>115</v>
+        <v>5890</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>15/03/2026</v>
+        <v>24/03/2026</v>
       </c>
       <c r="B109" t="str">
         <v>Mar26</v>
@@ -3306,18 +3306,18 @@
         <v>COGS</v>
       </c>
       <c r="D109" t="str">
-        <v>Watermelon</v>
+        <v>Ice</v>
       </c>
       <c r="E109" t="str">
-        <v>น้ำมะพร้าว 5ขวดเละ 50฿</v>
+        <v>รถเข็นของคันใหม่</v>
       </c>
       <c r="F109">
-        <v>4800</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>17/03/2026</v>
+        <v>28/03/2026</v>
       </c>
       <c r="B110" t="str">
         <v>Mar26</v>
@@ -3326,18 +3326,18 @@
         <v>COGS</v>
       </c>
       <c r="D110" t="str">
-        <v>Ice</v>
+        <v>Coconut Water</v>
       </c>
       <c r="E110" t="str">
-        <v>ค่าไฟเดือนกพ มีนา</v>
+        <v>น้ำมะพร้าว 10 ขวด</v>
       </c>
       <c r="F110">
-        <v>2779.47</v>
+        <v>500</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>19/03/2026</v>
+        <v>28/03/2026</v>
       </c>
       <c r="B111" t="str">
         <v>Mar26</v>
@@ -3346,18 +3346,18 @@
         <v>COGS</v>
       </c>
       <c r="D111" t="str">
-        <v>Watermelon</v>
+        <v>Mango</v>
       </c>
       <c r="E111" t="str">
-        <v>ค่าแตงโม 18/3/67 51 ลูก 4000 บาท</v>
+        <v>มะม่วง 23 โล</v>
       </c>
       <c r="F111">
-        <v>4000</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>21/03/2026</v>
+        <v>28/03/2026</v>
       </c>
       <c r="B112" t="str">
         <v>Mar26</v>
@@ -3366,18 +3366,18 @@
         <v>COGS</v>
       </c>
       <c r="D112" t="str">
-        <v>Ice</v>
+        <v>Watermelon</v>
       </c>
       <c r="E112" t="str">
-        <v>สกรู กาวตะปู</v>
+        <v>แตงโม 50 26/3/69</v>
       </c>
       <c r="F112">
-        <v>117</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>23/03/2026</v>
+        <v>30/03/2026</v>
       </c>
       <c r="B113" t="str">
         <v>Mar26</v>
@@ -3386,18 +3386,18 @@
         <v>COGS</v>
       </c>
       <c r="D113" t="str">
-        <v>Mango</v>
+        <v>Packaging</v>
       </c>
       <c r="E113" t="str">
-        <v>มะม่วง 44 โล</v>
+        <v>นมข้นจืดสามลังหนึ่งลังมี 12 กล่อง 36 กล่อง</v>
       </c>
       <c r="F113">
-        <v>2200</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>23/03/2026</v>
+        <v>30/03/2026</v>
       </c>
       <c r="B114" t="str">
         <v>Mar26</v>
@@ -3406,18 +3406,18 @@
         <v>COGS</v>
       </c>
       <c r="D114" t="str">
-        <v>Orange</v>
+        <v>Packaging</v>
       </c>
       <c r="E114" t="str">
-        <v>22-3-2569</v>
+        <v>นมข้นหวาน 3 ลัง 24 ถุง</v>
       </c>
       <c r="F114">
-        <v>5890</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>24/03/2026</v>
+        <v>30/03/2026</v>
       </c>
       <c r="B115" t="str">
         <v>Mar26</v>
@@ -3426,18 +3426,18 @@
         <v>COGS</v>
       </c>
       <c r="D115" t="str">
-        <v>Ice</v>
+        <v>Watermelon</v>
       </c>
       <c r="E115" t="str">
-        <v>รถเข็นของคันใหม่</v>
+        <v>แตงโม 30 ลูก 2400 เนื้อมะพร้าว 10 โล 1100</v>
       </c>
       <c r="F115">
-        <v>1752</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>28/03/2026</v>
+        <v>30/03/2026</v>
       </c>
       <c r="B116" t="str">
         <v>Mar26</v>
@@ -3446,18 +3446,18 @@
         <v>COGS</v>
       </c>
       <c r="D116" t="str">
-        <v>Coconut Water</v>
+        <v>Transportation</v>
       </c>
       <c r="E116" t="str">
-        <v>น้ำมะพร้าว 10 ขวด</v>
+        <v>ค่าส่ง lalamove</v>
       </c>
       <c r="F116">
-        <v>500</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>28/03/2026</v>
+        <v>31/03/2026</v>
       </c>
       <c r="B117" t="str">
         <v>Mar26</v>
@@ -3466,78 +3466,78 @@
         <v>COGS</v>
       </c>
       <c r="D117" t="str">
-        <v>Mango</v>
+        <v>Transportation</v>
       </c>
       <c r="E117" t="str">
-        <v>มะม่วง 23 โล</v>
+        <v>Unknown</v>
       </c>
       <c r="F117">
-        <v>1035</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>28/03/2026</v>
+        <v>01/04/2026</v>
       </c>
       <c r="B118" t="str">
-        <v>Mar26</v>
+        <v>Apr26</v>
       </c>
       <c r="C118" t="str">
         <v>COGS</v>
       </c>
       <c r="D118" t="str">
-        <v>Watermelon</v>
+        <v>Apple</v>
       </c>
       <c r="E118" t="str">
-        <v>แตงโม 50 26/3/69</v>
+        <v>แอปเปิ้ล 3 ลัง</v>
       </c>
       <c r="F118">
-        <v>4000</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>30/03/2026</v>
+        <v>01/04/2026</v>
       </c>
       <c r="B119" t="str">
-        <v>Mar26</v>
+        <v>Apr26</v>
       </c>
       <c r="C119" t="str">
         <v>COGS</v>
       </c>
       <c r="D119" t="str">
-        <v>Packaging</v>
+        <v>Mango</v>
       </c>
       <c r="E119" t="str">
-        <v>นมข้นจืดสามลังหนึ่งลังมี 12 กล่อง 36 กล่อง</v>
+        <v>มะม่วง 2 ลัง</v>
       </c>
       <c r="F119">
-        <v>1720</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>30/03/2026</v>
+        <v>01/04/2026</v>
       </c>
       <c r="B120" t="str">
-        <v>Mar26</v>
+        <v>Apr26</v>
       </c>
       <c r="C120" t="str">
         <v>COGS</v>
       </c>
       <c r="D120" t="str">
-        <v>Packaging</v>
+        <v>Water</v>
       </c>
       <c r="E120" t="str">
-        <v>นมข้นหวาน 3 ลัง 24 ถุง</v>
+        <v>น้ำ500</v>
       </c>
       <c r="F120">
-        <v>2016</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>30/03/2026</v>
+        <v>02/04/2026</v>
       </c>
       <c r="B121" t="str">
         <v>Mar26</v>
@@ -3546,58 +3546,58 @@
         <v>COGS</v>
       </c>
       <c r="D121" t="str">
-        <v>Watermelon</v>
+        <v>Ice</v>
       </c>
       <c r="E121" t="str">
-        <v>แตงโม 30 ลูก 2400 เนื้อมะพร้าว 10 โล 1100</v>
+        <v>Unknown</v>
       </c>
       <c r="F121">
-        <v>3500</v>
+        <v>49560</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>30/03/2026</v>
+        <v>04/04/2026</v>
       </c>
       <c r="B122" t="str">
-        <v>Mar26</v>
+        <v>Apr26</v>
       </c>
       <c r="C122" t="str">
         <v>COGS</v>
       </c>
       <c r="D122" t="str">
-        <v>Transportation</v>
+        <v>Packaging</v>
       </c>
       <c r="E122" t="str">
-        <v>ค่าส่ง lalamove</v>
+        <v>แก้ว3ลัง 1539 3 4617</v>
       </c>
       <c r="F122">
-        <v>2000</v>
+        <v>7066</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>31/03/2026</v>
+        <v>04/04/2026</v>
       </c>
       <c r="B123" t="str">
-        <v>Mar26</v>
+        <v>Apr26</v>
       </c>
       <c r="C123" t="str">
         <v>COGS</v>
       </c>
       <c r="D123" t="str">
-        <v>Transportation</v>
+        <v>Packaging</v>
       </c>
       <c r="E123" t="str">
-        <v>Unknown</v>
+        <v>แก้ว1ลัง 1539</v>
       </c>
       <c r="F123">
-        <v>2000</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>01/04/2026</v>
+        <v>04/04/2026</v>
       </c>
       <c r="B124" t="str">
         <v>Apr26</v>
@@ -3606,18 +3606,18 @@
         <v>COGS</v>
       </c>
       <c r="D124" t="str">
-        <v>Apple</v>
+        <v>Coconut</v>
       </c>
       <c r="E124" t="str">
-        <v>แอปเปิ้ล 3 ลัง</v>
+        <v>ค่ามะพร้าว 26 60ลูก 1560</v>
       </c>
       <c r="F124">
-        <v>1050</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>01/04/2026</v>
+        <v>04/04/2026</v>
       </c>
       <c r="B125" t="str">
         <v>Apr26</v>
@@ -3626,18 +3626,18 @@
         <v>COGS</v>
       </c>
       <c r="D125" t="str">
-        <v>Mango</v>
+        <v>Ice</v>
       </c>
       <c r="E125" t="str">
-        <v>มะม่วง 2 ลัง</v>
+        <v>เนื้อ 1200 น้ำ 500</v>
       </c>
       <c r="F125">
-        <v>1920</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>01/04/2026</v>
+        <v>04/04/2026</v>
       </c>
       <c r="B126" t="str">
         <v>Apr26</v>
@@ -3646,33 +3646,33 @@
         <v>COGS</v>
       </c>
       <c r="D126" t="str">
-        <v>Water</v>
+        <v>Mango</v>
       </c>
       <c r="E126" t="str">
-        <v>น้ำ500</v>
+        <v>มะม่วง1ลัง</v>
       </c>
       <c r="F126">
-        <v>1700</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>02/04/2026</v>
+        <v>04/04/2026</v>
       </c>
       <c r="B127" t="str">
-        <v>Mar26</v>
+        <v>Apr26</v>
       </c>
       <c r="C127" t="str">
         <v>COGS</v>
       </c>
       <c r="D127" t="str">
-        <v>Ice</v>
+        <v>Orange</v>
       </c>
       <c r="E127" t="str">
-        <v>Unknown</v>
+        <v>ส้ม 4/4/69 20 ตะกร้า 30 บาท 13200 ค่าขนส่ง</v>
       </c>
       <c r="F127">
-        <v>49560</v>
+        <v>14160</v>
       </c>
     </row>
     <row r="128">
@@ -3686,13 +3686,13 @@
         <v>COGS</v>
       </c>
       <c r="D128" t="str">
-        <v>Packaging</v>
+        <v>Ice</v>
       </c>
       <c r="E128" t="str">
-        <v>แก้ว3ลัง 1539 3 4617</v>
+        <v>4/4/68 40 ลูก</v>
       </c>
       <c r="F128">
-        <v>7066</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="129">
@@ -3706,18 +3706,18 @@
         <v>COGS</v>
       </c>
       <c r="D129" t="str">
-        <v>Packaging</v>
+        <v>Watermelon</v>
       </c>
       <c r="E129" t="str">
-        <v>แก้ว1ลัง 1539</v>
+        <v>แตงโม 1/4/69 30 ลูก</v>
       </c>
       <c r="F129">
-        <v>1560</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>04/04/2026</v>
+        <v>07/04/2026</v>
       </c>
       <c r="B130" t="str">
         <v>Apr26</v>
@@ -3726,18 +3726,18 @@
         <v>COGS</v>
       </c>
       <c r="D130" t="str">
-        <v>Coconut</v>
+        <v>Apple</v>
       </c>
       <c r="E130" t="str">
-        <v>ค่ามะพร้าว 26 60ลูก 1560</v>
+        <v>แอปเปิ้ล 3 ลัง</v>
       </c>
       <c r="F130">
-        <v>1980</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>04/04/2026</v>
+        <v>07/04/2026</v>
       </c>
       <c r="B131" t="str">
         <v>Apr26</v>
@@ -3746,10 +3746,10 @@
         <v>COGS</v>
       </c>
       <c r="D131" t="str">
-        <v>Ice</v>
+        <v>Coconut Water</v>
       </c>
       <c r="E131" t="str">
-        <v>เนื้อ 1200 น้ำ 500</v>
+        <v>เนื้อมะพร้าว 10 - 1200 บาท น้ำมะพร้าว 10</v>
       </c>
       <c r="F131">
         <v>1700</v>
@@ -3757,7 +3757,7 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>04/04/2026</v>
+        <v>07/04/2026</v>
       </c>
       <c r="B132" t="str">
         <v>Apr26</v>
@@ -3766,18 +3766,18 @@
         <v>COGS</v>
       </c>
       <c r="D132" t="str">
-        <v>Mango</v>
+        <v>Watermelon</v>
       </c>
       <c r="E132" t="str">
-        <v>มะม่วง1ลัง</v>
+        <v>ค่าแตงโมวันที่ 4- 40 ลูก 3200 บาท วันที่ 7-40 ลูก</v>
       </c>
       <c r="F132">
-        <v>1000</v>
+        <v>6400</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>04/04/2026</v>
+        <v>10/04/2026</v>
       </c>
       <c r="B133" t="str">
         <v>Apr26</v>
@@ -3786,18 +3786,18 @@
         <v>COGS</v>
       </c>
       <c r="D133" t="str">
-        <v>Orange</v>
+        <v>Ice</v>
       </c>
       <c r="E133" t="str">
-        <v>ส้ม 4/4/69 20 ตะกร้า 30 บาท 13200 ค่าขนส่ง</v>
+        <v>ค่านม</v>
       </c>
       <c r="F133">
-        <v>14160</v>
+        <v>180</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>04/04/2026</v>
+        <v>11/04/2026</v>
       </c>
       <c r="B134" t="str">
         <v>Apr26</v>
@@ -3806,18 +3806,18 @@
         <v>COGS</v>
       </c>
       <c r="D134" t="str">
-        <v>Ice</v>
+        <v>Transportation</v>
       </c>
       <c r="E134" t="str">
-        <v>4/4/68 40 ลูก</v>
+        <v>ค่ารถ lalamove</v>
       </c>
       <c r="F134">
-        <v>3200</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>04/04/2026</v>
+        <v>11/04/2026</v>
       </c>
       <c r="B135" t="str">
         <v>Apr26</v>
@@ -3826,18 +3826,18 @@
         <v>COGS</v>
       </c>
       <c r="D135" t="str">
-        <v>Watermelon</v>
+        <v>Apple</v>
       </c>
       <c r="E135" t="str">
-        <v>แตงโม 1/4/69 30 ลูก</v>
+        <v>แอปเปิ้ล 3 ลัง</v>
       </c>
       <c r="F135">
-        <v>2400</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>07/04/2026</v>
+        <v>11/04/2026</v>
       </c>
       <c r="B136" t="str">
         <v>Apr26</v>
@@ -3846,18 +3846,18 @@
         <v>COGS</v>
       </c>
       <c r="D136" t="str">
-        <v>Apple</v>
+        <v>Ice</v>
       </c>
       <c r="E136" t="str">
-        <v>แอปเปิ้ล 3 ลัง</v>
+        <v>น้ำ 500 เนื้อ 1200</v>
       </c>
       <c r="F136">
-        <v>1050</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>07/04/2026</v>
+        <v>11/04/2026</v>
       </c>
       <c r="B137" t="str">
         <v>Apr26</v>
@@ -3866,18 +3866,18 @@
         <v>COGS</v>
       </c>
       <c r="D137" t="str">
-        <v>Coconut Water</v>
+        <v>Mango</v>
       </c>
       <c r="E137" t="str">
-        <v>เนื้อมะพร้าว 10 - 1200 บาท น้ำมะพร้าว 10</v>
+        <v>มะม่วง 1 ลัง 23 โล</v>
       </c>
       <c r="F137">
-        <v>1700</v>
+        <v>690</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>07/04/2026</v>
+        <v>13/04/2026</v>
       </c>
       <c r="B138" t="str">
         <v>Apr26</v>
@@ -3886,18 +3886,18 @@
         <v>COGS</v>
       </c>
       <c r="D138" t="str">
-        <v>Watermelon</v>
+        <v>Coconut Water</v>
       </c>
       <c r="E138" t="str">
-        <v>ค่าแตงโมวันที่ 4- 40 ลูก 3200 บาท วันที่ 7-40 ลูก</v>
+        <v>Unknown</v>
       </c>
       <c r="F138">
-        <v>6400</v>
+        <v>300</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>10/04/2026</v>
+        <v>13/04/2026</v>
       </c>
       <c r="B139" t="str">
         <v>Apr26</v>
@@ -3906,18 +3906,18 @@
         <v>COGS</v>
       </c>
       <c r="D139" t="str">
-        <v>Ice</v>
+        <v>Coconut Water</v>
       </c>
       <c r="E139" t="str">
-        <v>ค่านม</v>
+        <v>เนื้อมะพร้าว 1200 น้ำมะพร้าว 500</v>
       </c>
       <c r="F139">
-        <v>180</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>11/04/2026</v>
+        <v>13/04/2026</v>
       </c>
       <c r="B140" t="str">
         <v>Apr26</v>
@@ -3926,18 +3926,18 @@
         <v>COGS</v>
       </c>
       <c r="D140" t="str">
-        <v>Transportation</v>
+        <v>Mango</v>
       </c>
       <c r="E140" t="str">
-        <v>ค่ารถ lalamove</v>
+        <v>Unknown</v>
       </c>
       <c r="F140">
-        <v>2000</v>
+        <v>750</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>11/04/2026</v>
+        <v>13/04/2026</v>
       </c>
       <c r="B141" t="str">
         <v>Apr26</v>
@@ -3946,18 +3946,18 @@
         <v>COGS</v>
       </c>
       <c r="D141" t="str">
-        <v>Apple</v>
+        <v>Watermelon</v>
       </c>
       <c r="E141" t="str">
-        <v>แอปเปิ้ล 3 ลัง</v>
+        <v>Unknown</v>
       </c>
       <c r="F141">
-        <v>1050</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>11/04/2026</v>
+        <v>18/04/2026</v>
       </c>
       <c r="B142" t="str">
         <v>Apr26</v>
@@ -3966,18 +3966,18 @@
         <v>COGS</v>
       </c>
       <c r="D142" t="str">
-        <v>Ice</v>
+        <v>Apple</v>
       </c>
       <c r="E142" t="str">
-        <v>น้ำ 500 เนื้อ 1200</v>
+        <v>แอปเปิ้ล 3 ลัง</v>
       </c>
       <c r="F142">
-        <v>1700</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>11/04/2026</v>
+        <v>18/04/2026</v>
       </c>
       <c r="B143" t="str">
         <v>Apr26</v>
@@ -3989,35 +3989,35 @@
         <v>Mango</v>
       </c>
       <c r="E143" t="str">
-        <v>มะม่วง 1 ลัง 23 โล</v>
+        <v>16/04/26 มะม่วง 1 ลัง</v>
       </c>
       <c r="F143">
-        <v>690</v>
+        <v>750</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>13/04/2026</v>
+        <v>18/04/2026</v>
       </c>
       <c r="B144" t="str">
         <v>Apr26</v>
       </c>
       <c r="C144" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D144" t="str">
-        <v>Coconut Water</v>
+        <v>Other</v>
       </c>
       <c r="E144" t="str">
-        <v>Unknown</v>
+        <v>16/4/2569</v>
       </c>
       <c r="F144">
-        <v>300</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>13/04/2026</v>
+        <v>20/04/2026</v>
       </c>
       <c r="B145" t="str">
         <v>Apr26</v>
@@ -4026,18 +4026,18 @@
         <v>COGS</v>
       </c>
       <c r="D145" t="str">
-        <v>Coconut Water</v>
+        <v>Orange</v>
       </c>
       <c r="E145" t="str">
-        <v>เนื้อมะพร้าว 1200 น้ำมะพร้าว 500</v>
+        <v>ส้ม 40 ตะกร้า ตะกร้าละ 22 โล โลละ 30 บาท</v>
       </c>
       <c r="F145">
-        <v>1400</v>
+        <v>28600</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>13/04/2026</v>
+        <v>20/04/2026</v>
       </c>
       <c r="B146" t="str">
         <v>Apr26</v>
@@ -4046,18 +4046,18 @@
         <v>COGS</v>
       </c>
       <c r="D146" t="str">
-        <v>Mango</v>
+        <v>Transportation</v>
       </c>
       <c r="E146" t="str">
-        <v>Unknown</v>
+        <v>ค่าส่งป้ายเมนูร้านใหม่</v>
       </c>
       <c r="F146">
-        <v>750</v>
+        <v>335</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>13/04/2026</v>
+        <v>20/04/2026</v>
       </c>
       <c r="B147" t="str">
         <v>Apr26</v>
@@ -4066,18 +4066,18 @@
         <v>COGS</v>
       </c>
       <c r="D147" t="str">
-        <v>Watermelon</v>
+        <v>Packaging</v>
       </c>
       <c r="E147" t="str">
-        <v>Unknown</v>
+        <v>ขวดใหญ่ 98 อัน</v>
       </c>
       <c r="F147">
-        <v>3200</v>
+        <v>338</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>18/04/2026</v>
+        <v>20/04/2026</v>
       </c>
       <c r="B148" t="str">
         <v>Apr26</v>
@@ -4086,18 +4086,18 @@
         <v>COGS</v>
       </c>
       <c r="D148" t="str">
-        <v>Apple</v>
+        <v>Packaging</v>
       </c>
       <c r="E148" t="str">
-        <v>แอปเปิ้ล 3 ลัง</v>
+        <v>ถุงขยะ 10 แพค</v>
       </c>
       <c r="F148">
-        <v>1050</v>
+        <v>520</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>18/04/2026</v>
+        <v>20/04/2026</v>
       </c>
       <c r="B149" t="str">
         <v>Apr26</v>
@@ -4106,38 +4106,38 @@
         <v>COGS</v>
       </c>
       <c r="D149" t="str">
-        <v>Mango</v>
+        <v>Watermelon</v>
       </c>
       <c r="E149" t="str">
-        <v>16/04/26 มะม่วง 1 ลัง</v>
+        <v>18/4/26 แตงโม 30 ลูก</v>
       </c>
       <c r="F149">
-        <v>750</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>18/04/2026</v>
+        <v>20/04/2026</v>
       </c>
       <c r="B150" t="str">
         <v>Apr26</v>
       </c>
       <c r="C150" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D150" t="str">
-        <v>Other</v>
+        <v>Mango</v>
       </c>
       <c r="E150" t="str">
-        <v>16/4/2569</v>
+        <v>18/4/26 มะม่วง 25 โล 750</v>
       </c>
       <c r="F150">
-        <v>4000</v>
+        <v>750</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>20/04/2026</v>
+        <v>21/04/2026</v>
       </c>
       <c r="B151" t="str">
         <v>Apr26</v>
@@ -4146,18 +4146,18 @@
         <v>COGS</v>
       </c>
       <c r="D151" t="str">
-        <v>Orange</v>
+        <v>Watermelon</v>
       </c>
       <c r="E151" t="str">
-        <v>ส้ม 40 ตะกร้า ตะกร้าละ 22 โล โลละ 30 บาท</v>
+        <v>21/4/26 แตงโม60 ลูก</v>
       </c>
       <c r="F151">
-        <v>28600</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>20/04/2026</v>
+        <v>21/04/2026</v>
       </c>
       <c r="B152" t="str">
         <v>Apr26</v>
@@ -4169,15 +4169,15 @@
         <v>Transportation</v>
       </c>
       <c r="E152" t="str">
-        <v>ค่าส่งป้ายเมนูร้านใหม่</v>
+        <v>Lalamove</v>
       </c>
       <c r="F152">
-        <v>335</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>20/04/2026</v>
+        <v>21/04/2026</v>
       </c>
       <c r="B153" t="str">
         <v>Apr26</v>
@@ -4186,18 +4186,18 @@
         <v>COGS</v>
       </c>
       <c r="D153" t="str">
-        <v>Packaging</v>
+        <v>Apple</v>
       </c>
       <c r="E153" t="str">
-        <v>ขวดใหญ่ 98 อัน</v>
+        <v>แอปเปิ้ล 4 ลัง</v>
       </c>
       <c r="F153">
-        <v>338</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>20/04/2026</v>
+        <v>23/04/2026</v>
       </c>
       <c r="B154" t="str">
         <v>Apr26</v>
@@ -4206,18 +4206,18 @@
         <v>COGS</v>
       </c>
       <c r="D154" t="str">
-        <v>Packaging</v>
+        <v>Mango</v>
       </c>
       <c r="E154" t="str">
-        <v>ถุงขยะ 10 แพค</v>
+        <v>มะม่วง 2 ลัง</v>
       </c>
       <c r="F154">
-        <v>520</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>20/04/2026</v>
+        <v>23/04/2026</v>
       </c>
       <c r="B155" t="str">
         <v>Apr26</v>
@@ -4226,18 +4226,18 @@
         <v>COGS</v>
       </c>
       <c r="D155" t="str">
-        <v>Watermelon</v>
+        <v>Apple</v>
       </c>
       <c r="E155" t="str">
-        <v>18/4/26 แตงโม 30 ลูก</v>
+        <v>แอปเปิ้ล 4 ลัง</v>
       </c>
       <c r="F155">
-        <v>2400</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>20/04/2026</v>
+        <v>23/04/2026</v>
       </c>
       <c r="B156" t="str">
         <v>Apr26</v>
@@ -4246,18 +4246,18 @@
         <v>COGS</v>
       </c>
       <c r="D156" t="str">
-        <v>Mango</v>
+        <v>Ice</v>
       </c>
       <c r="E156" t="str">
-        <v>18/4/26 มะม่วง 25 โล 750</v>
+        <v>16/4/26 เนื้อ 10 น้ำ 10 21/4/26 เนื้อ 10</v>
       </c>
       <c r="F156">
-        <v>750</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>21/04/2026</v>
+        <v>23/04/2026</v>
       </c>
       <c r="B157" t="str">
         <v>Apr26</v>
@@ -4266,18 +4266,18 @@
         <v>COGS</v>
       </c>
       <c r="D157" t="str">
-        <v>Watermelon</v>
+        <v>Mango</v>
       </c>
       <c r="E157" t="str">
-        <v>21/4/26 แตงโม60 ลูก</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F157">
-        <v>4800</v>
+        <v>780</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>21/04/2026</v>
+        <v>24/04/2026</v>
       </c>
       <c r="B158" t="str">
         <v>Apr26</v>
@@ -4286,18 +4286,18 @@
         <v>COGS</v>
       </c>
       <c r="D158" t="str">
-        <v>Transportation</v>
+        <v>Packaging</v>
       </c>
       <c r="E158" t="str">
-        <v>Lalamove</v>
+        <v>บาร์เลย 4 ถั่วแดง 3 ถุงละ 60</v>
       </c>
       <c r="F158">
-        <v>2000</v>
+        <v>420</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>21/04/2026</v>
+        <v>24/04/2026</v>
       </c>
       <c r="B159" t="str">
         <v>Apr26</v>
@@ -4306,18 +4306,18 @@
         <v>COGS</v>
       </c>
       <c r="D159" t="str">
-        <v>Apple</v>
+        <v>Watermelon</v>
       </c>
       <c r="E159" t="str">
-        <v>แอปเปิ้ล 4 ลัง</v>
+        <v>แตงโม 50 ลูก</v>
       </c>
       <c r="F159">
-        <v>1400</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>23/04/2026</v>
+        <v>25/04/2026</v>
       </c>
       <c r="B160" t="str">
         <v>Apr26</v>
@@ -4326,18 +4326,18 @@
         <v>COGS</v>
       </c>
       <c r="D160" t="str">
-        <v>Mango</v>
+        <v>Orange</v>
       </c>
       <c r="E160" t="str">
-        <v>มะม่วง 2 ลัง</v>
+        <v>22/04/69</v>
       </c>
       <c r="F160">
-        <v>1560</v>
+        <v>14400</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>23/04/2026</v>
+        <v>26/04/2026</v>
       </c>
       <c r="B161" t="str">
         <v>Apr26</v>
@@ -4346,18 +4346,18 @@
         <v>COGS</v>
       </c>
       <c r="D161" t="str">
-        <v>Apple</v>
+        <v>Packaging</v>
       </c>
       <c r="E161" t="str">
-        <v>แอปเปิ้ล 4 ลัง</v>
+        <v>แก้ว 1 ลัง</v>
       </c>
       <c r="F161">
-        <v>1400</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>23/04/2026</v>
+        <v>26/04/2026</v>
       </c>
       <c r="B162" t="str">
         <v>Apr26</v>
@@ -4366,18 +4366,18 @@
         <v>COGS</v>
       </c>
       <c r="D162" t="str">
-        <v>Ice</v>
+        <v>Packaging</v>
       </c>
       <c r="E162" t="str">
-        <v>16/4/26 เนื้อ 10 น้ำ 10 21/4/26 เนื้อ 10</v>
+        <v>แก้ว3ลัง</v>
       </c>
       <c r="F162">
-        <v>2900</v>
+        <v>7090</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>23/04/2026</v>
+        <v>26/04/2026</v>
       </c>
       <c r="B163" t="str">
         <v>Apr26</v>
@@ -4397,7 +4397,7 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>24/04/2026</v>
+        <v>26/04/2026</v>
       </c>
       <c r="B164" t="str">
         <v>Apr26</v>
@@ -4406,18 +4406,18 @@
         <v>COGS</v>
       </c>
       <c r="D164" t="str">
-        <v>Packaging</v>
+        <v>Apple</v>
       </c>
       <c r="E164" t="str">
-        <v>บาร์เลย 4 ถั่วแดง 3 ถุงละ 60</v>
+        <v>แอปเปิ้ล 4</v>
       </c>
       <c r="F164">
-        <v>420</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>24/04/2026</v>
+        <v>27/04/2026</v>
       </c>
       <c r="B165" t="str">
         <v>Apr26</v>
@@ -4426,10 +4426,10 @@
         <v>COGS</v>
       </c>
       <c r="D165" t="str">
-        <v>Watermelon</v>
+        <v>Ice</v>
       </c>
       <c r="E165" t="str">
-        <v>แตงโม 50 ลูก</v>
+        <v>26/4/26 50 ลูก</v>
       </c>
       <c r="F165">
         <v>4000</v>
@@ -4437,7 +4437,7 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>25/04/2026</v>
+        <v>28/04/2026</v>
       </c>
       <c r="B166" t="str">
         <v>Apr26</v>
@@ -4446,18 +4446,18 @@
         <v>COGS</v>
       </c>
       <c r="D166" t="str">
-        <v>Orange</v>
+        <v>Packaging</v>
       </c>
       <c r="E166" t="str">
-        <v>22/04/69</v>
+        <v>หลอด 704(20ห่อ)</v>
       </c>
       <c r="F166">
-        <v>14400</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>26/04/2026</v>
+        <v>28/04/2026</v>
       </c>
       <c r="B167" t="str">
         <v>Apr26</v>
@@ -4466,18 +4466,18 @@
         <v>COGS</v>
       </c>
       <c r="D167" t="str">
-        <v>Packaging</v>
+        <v>Orange</v>
       </c>
       <c r="E167" t="str">
-        <v>แก้ว 1 ลัง</v>
+        <v>รอบ 27/04/69</v>
       </c>
       <c r="F167">
-        <v>1539</v>
+        <v>21600</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>26/04/2026</v>
+        <v>28/04/2026</v>
       </c>
       <c r="B168" t="str">
         <v>Apr26</v>
@@ -4486,18 +4486,18 @@
         <v>COGS</v>
       </c>
       <c r="D168" t="str">
-        <v>Packaging</v>
+        <v>Coconut</v>
       </c>
       <c r="E168" t="str">
-        <v>แก้ว3ลัง</v>
+        <v>ค่าส่งมะพร้าว</v>
       </c>
       <c r="F168">
-        <v>7090</v>
+        <v>100</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>26/04/2026</v>
+        <v>28/04/2026</v>
       </c>
       <c r="B169" t="str">
         <v>Apr26</v>
@@ -4506,18 +4506,18 @@
         <v>COGS</v>
       </c>
       <c r="D169" t="str">
-        <v>Mango</v>
+        <v>Apple</v>
       </c>
       <c r="E169" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>แอปเปิ้ล 4 ลัง</v>
       </c>
       <c r="F169">
-        <v>780</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>26/04/2026</v>
+        <v>28/04/2026</v>
       </c>
       <c r="B170" t="str">
         <v>Apr26</v>
@@ -4526,18 +4526,18 @@
         <v>COGS</v>
       </c>
       <c r="D170" t="str">
-        <v>Apple</v>
+        <v>Mango</v>
       </c>
       <c r="E170" t="str">
-        <v>แอปเปิ้ล 4</v>
+        <v>มะม่วง 2 ลัง</v>
       </c>
       <c r="F170">
-        <v>1400</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>27/04/2026</v>
+        <v>29/04/2026</v>
       </c>
       <c r="B171" t="str">
         <v>Apr26</v>
@@ -4546,18 +4546,18 @@
         <v>COGS</v>
       </c>
       <c r="D171" t="str">
-        <v>Ice</v>
+        <v>Milk/Conden</v>
       </c>
       <c r="E171" t="str">
-        <v>26/4/26 50 ลูก</v>
+        <v>นมข้นหวาน1ลัง 836</v>
       </c>
       <c r="F171">
-        <v>4000</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>28/04/2026</v>
+        <v>29/04/2026</v>
       </c>
       <c r="B172" t="str">
         <v>Apr26</v>
@@ -4569,15 +4569,15 @@
         <v>Packaging</v>
       </c>
       <c r="E172" t="str">
-        <v>หลอด 704(20ห่อ)</v>
+        <v>นมข้นหวาน2ลัง 1602</v>
       </c>
       <c r="F172">
-        <v>2110</v>
+        <v>3210</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>28/04/2026</v>
+        <v>29/04/2026</v>
       </c>
       <c r="B173" t="str">
         <v>Apr26</v>
@@ -4586,18 +4586,18 @@
         <v>COGS</v>
       </c>
       <c r="D173" t="str">
-        <v>Orange</v>
+        <v>Watermelon</v>
       </c>
       <c r="E173" t="str">
-        <v>รอบ 27/04/69</v>
+        <v>แตงโม 60 ลูก</v>
       </c>
       <c r="F173">
-        <v>21600</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>28/04/2026</v>
+        <v>29/04/2026</v>
       </c>
       <c r="B174" t="str">
         <v>Apr26</v>
@@ -4606,18 +4606,18 @@
         <v>COGS</v>
       </c>
       <c r="D174" t="str">
-        <v>Coconut</v>
+        <v>Transportation</v>
       </c>
       <c r="E174" t="str">
-        <v>ค่าส่งมะพร้าว</v>
+        <v>เนื้อ 10 x 50 500</v>
       </c>
       <c r="F174">
-        <v>100</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>28/04/2026</v>
+        <v>30/04/2026</v>
       </c>
       <c r="B175" t="str">
         <v>Apr26</v>
@@ -4626,98 +4626,98 @@
         <v>COGS</v>
       </c>
       <c r="D175" t="str">
-        <v>Apple</v>
+        <v>Ice</v>
       </c>
       <c r="E175" t="str">
-        <v>แอปเปิ้ล 4 ลัง</v>
+        <v>สับปะรส 3 ตะกร้า</v>
       </c>
       <c r="F175">
-        <v>1400</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>28/04/2026</v>
+        <v>30/04/2026</v>
       </c>
       <c r="B176" t="str">
         <v>Apr26</v>
       </c>
       <c r="C176" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D176" t="str">
-        <v>Mango</v>
+        <v>Salary</v>
       </c>
       <c r="E176" t="str">
-        <v>มะม่วง 2 ลัง</v>
+        <v>Employee 1</v>
       </c>
       <c r="F176">
-        <v>1560</v>
+        <v>19000</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>29/04/2026</v>
+        <v>30/04/2026</v>
       </c>
       <c r="B177" t="str">
         <v>Apr26</v>
       </c>
       <c r="C177" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D177" t="str">
-        <v>Milk/Conden</v>
+        <v>Salary</v>
       </c>
       <c r="E177" t="str">
-        <v>นมข้นหวาน1ลัง 836</v>
+        <v>Employee 2</v>
       </c>
       <c r="F177">
-        <v>2160</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>29/04/2026</v>
+        <v>30/04/2026</v>
       </c>
       <c r="B178" t="str">
         <v>Apr26</v>
       </c>
       <c r="C178" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D178" t="str">
-        <v>Packaging</v>
+        <v>Fixed Costs</v>
       </c>
       <c r="E178" t="str">
-        <v>นมข้นหวาน2ลัง 1602</v>
+        <v>Rent</v>
       </c>
       <c r="F178">
-        <v>3210</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>29/04/2026</v>
+        <v>30/04/2026</v>
       </c>
       <c r="B179" t="str">
         <v>Apr26</v>
       </c>
       <c r="C179" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D179" t="str">
-        <v>Watermelon</v>
+        <v>Investment</v>
       </c>
       <c r="E179" t="str">
-        <v>แตงโม 60 ลูก</v>
+        <v>Stock (Allocated 82.9%)</v>
       </c>
       <c r="F179">
-        <v>4200</v>
+        <v>9948</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>29/04/2026</v>
+        <v>30/04/2026</v>
       </c>
       <c r="B180" t="str">
         <v>Apr26</v>
@@ -4726,138 +4726,138 @@
         <v>COGS</v>
       </c>
       <c r="D180" t="str">
-        <v>Transportation</v>
+        <v>Other</v>
       </c>
       <c r="E180" t="str">
-        <v>เนื้อ 10 x 50 500</v>
+        <v>Pineapple</v>
       </c>
       <c r="F180">
-        <v>2395</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>30/04/2026</v>
+        <v>01/05/2026</v>
       </c>
       <c r="B181" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C181" t="str">
         <v>COGS</v>
       </c>
       <c r="D181" t="str">
-        <v>Ice</v>
+        <v>Guava</v>
       </c>
       <c r="E181" t="str">
-        <v>สับปะรส 3 ตะกร้า</v>
+        <v>ร่ม 1176 ร่ม 843 ฝรั่ง 300 นมข้นจืด 785 ที่ปั้ม 176</v>
       </c>
       <c r="F181">
-        <v>1500</v>
+        <v>7823</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>30/04/2026</v>
+        <v>02/05/2026</v>
       </c>
       <c r="B182" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C182" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D182" t="str">
-        <v>Salary</v>
+        <v>Mango</v>
       </c>
       <c r="E182" t="str">
-        <v>Employee 1</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F182">
-        <v>19000</v>
+        <v>910</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>30/04/2026</v>
+        <v>02/05/2026</v>
       </c>
       <c r="B183" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C183" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D183" t="str">
-        <v>Salary</v>
+        <v>Apple</v>
       </c>
       <c r="E183" t="str">
-        <v>Employee 2</v>
+        <v>แอปเปิ้ล 4 ลัง</v>
       </c>
       <c r="F183">
-        <v>12000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>30/04/2026</v>
+        <v>02/05/2026</v>
       </c>
       <c r="B184" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C184" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D184" t="str">
-        <v>Fixed Costs</v>
+        <v>Pineapple</v>
       </c>
       <c r="E184" t="str">
-        <v>Rent</v>
+        <v>สับปะรด 30 ลูก</v>
       </c>
       <c r="F184">
-        <v>35000</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>30/04/2026</v>
+        <v>02/05/2026</v>
       </c>
       <c r="B185" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C185" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D185" t="str">
-        <v>Investment</v>
+        <v>Ice</v>
       </c>
       <c r="E185" t="str">
-        <v>Stock (Allocated 82.9%)</v>
+        <v>ค่าหาหมอเอ</v>
       </c>
       <c r="F185">
-        <v>9948</v>
+        <v>706</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>30/04/2026</v>
+        <v>02/05/2026</v>
       </c>
       <c r="B186" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C186" t="str">
         <v>COGS</v>
       </c>
       <c r="D186" t="str">
-        <v>Other</v>
+        <v>Ice</v>
       </c>
       <c r="E186" t="str">
-        <v>Pineapple</v>
+        <v>ค่าหมอเอ</v>
       </c>
       <c r="F186">
-        <v>1500</v>
+        <v>13</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>01/05/2026</v>
+        <v>04/05/2026</v>
       </c>
       <c r="B187" t="str">
         <v>May26</v>
@@ -4866,18 +4866,18 @@
         <v>COGS</v>
       </c>
       <c r="D187" t="str">
-        <v>Guava</v>
+        <v>Packaging</v>
       </c>
       <c r="E187" t="str">
-        <v>ร่ม 1176 ร่ม 843 ฝรั่ง 300 นมข้นจืด 785 ที่ปั้ม 176</v>
+        <v>ถุงมือ4อัน</v>
       </c>
       <c r="F187">
-        <v>7823</v>
+        <v>499</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>02/05/2026</v>
+        <v>04/05/2026</v>
       </c>
       <c r="B188" t="str">
         <v>May26</v>
@@ -4886,18 +4886,18 @@
         <v>COGS</v>
       </c>
       <c r="D188" t="str">
-        <v>Mango</v>
+        <v>Apple</v>
       </c>
       <c r="E188" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>แอปเปิ้ล 4 ลัง</v>
       </c>
       <c r="F188">
-        <v>910</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>02/05/2026</v>
+        <v>04/05/2026</v>
       </c>
       <c r="B189" t="str">
         <v>May26</v>
@@ -4906,58 +4906,58 @@
         <v>COGS</v>
       </c>
       <c r="D189" t="str">
-        <v>Apple</v>
+        <v>Mango</v>
       </c>
       <c r="E189" t="str">
-        <v>แอปเปิ้ล 4 ลัง</v>
+        <v>มะม่วง 2 ลัง</v>
       </c>
       <c r="F189">
-        <v>1500</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>02/05/2026</v>
+        <v>04/05/2026</v>
       </c>
       <c r="B190" t="str">
         <v>May26</v>
       </c>
       <c r="C190" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D190" t="str">
-        <v>Pineapple</v>
+        <v>Other</v>
       </c>
       <c r="E190" t="str">
-        <v>สับปะรด 30 ลูก</v>
+        <v>30-4-2569 เบอร์ 70฿ 60 ลูก</v>
       </c>
       <c r="F190">
-        <v>1116</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>02/05/2026</v>
+        <v>06/05/2026</v>
       </c>
       <c r="B191" t="str">
         <v>May26</v>
       </c>
       <c r="C191" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D191" t="str">
-        <v>Ice</v>
+        <v>Other</v>
       </c>
       <c r="E191" t="str">
-        <v>ค่าหาหมอเอ</v>
+        <v>ทิชชู่3แพค 36ห่อ</v>
       </c>
       <c r="F191">
-        <v>706</v>
+        <v>451</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>02/05/2026</v>
+        <v>06/05/2026</v>
       </c>
       <c r="B192" t="str">
         <v>May26</v>
@@ -4966,18 +4966,18 @@
         <v>COGS</v>
       </c>
       <c r="D192" t="str">
-        <v>Ice</v>
+        <v>Mango</v>
       </c>
       <c r="E192" t="str">
-        <v>ค่าหมอเอ</v>
+        <v>มะม่วง 2 ลัง</v>
       </c>
       <c r="F192">
-        <v>13</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>04/05/2026</v>
+        <v>06/05/2026</v>
       </c>
       <c r="B193" t="str">
         <v>May26</v>
@@ -4986,18 +4986,18 @@
         <v>COGS</v>
       </c>
       <c r="D193" t="str">
-        <v>Packaging</v>
+        <v>Pineapple</v>
       </c>
       <c r="E193" t="str">
-        <v>ถุงมือ4อัน</v>
+        <v>สับปะรด 18 ลูก</v>
       </c>
       <c r="F193">
-        <v>499</v>
+        <v>486</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>04/05/2026</v>
+        <v>06/05/2026</v>
       </c>
       <c r="B194" t="str">
         <v>May26</v>
@@ -5017,7 +5017,7 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>04/05/2026</v>
+        <v>08/05/2026</v>
       </c>
       <c r="B195" t="str">
         <v>May26</v>
@@ -5026,118 +5026,118 @@
         <v>COGS</v>
       </c>
       <c r="D195" t="str">
-        <v>Mango</v>
+        <v>Transportation</v>
       </c>
       <c r="E195" t="str">
-        <v>มะม่วง 2 ลัง</v>
+        <v>น้ำ 20 ขวด 900 ถอดเสื้อ 30 ลูก750 กล่องโฟม 3</v>
       </c>
       <c r="F195">
-        <v>1680</v>
+        <v>4555</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>04/05/2026</v>
+        <v>08/05/2026</v>
       </c>
       <c r="B196" t="str">
         <v>May26</v>
       </c>
       <c r="C196" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D196" t="str">
-        <v>Other</v>
+        <v>Water</v>
       </c>
       <c r="E196" t="str">
-        <v>30-4-2569 เบอร์ 70฿ 60 ลูก</v>
+        <v>น้ำมะร้าว 1 ลัง</v>
       </c>
       <c r="F196">
-        <v>7000</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>06/05/2026</v>
+        <v>08/05/2026</v>
       </c>
       <c r="B197" t="str">
         <v>May26</v>
       </c>
       <c r="C197" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D197" t="str">
-        <v>Other</v>
+        <v>Packaging</v>
       </c>
       <c r="E197" t="str">
-        <v>ทิชชู่3แพค 36ห่อ</v>
+        <v>6 พ.ค. น้ำ 30 ขวด 1500 บาท เนื้อ 11 โล 1320 บาท</v>
       </c>
       <c r="F197">
-        <v>451</v>
+        <v>2820</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>06/05/2026</v>
+        <v>08/05/2026</v>
       </c>
       <c r="B198" t="str">
         <v>May26</v>
       </c>
       <c r="C198" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D198" t="str">
-        <v>Mango</v>
+        <v>Other</v>
       </c>
       <c r="E198" t="str">
-        <v>มะม่วง 2 ลัง</v>
+        <v>ค่าทำความสะอาดตึกชั้น 1</v>
       </c>
       <c r="F198">
-        <v>1750</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>06/05/2026</v>
+        <v>08/05/2026</v>
       </c>
       <c r="B199" t="str">
         <v>May26</v>
       </c>
       <c r="C199" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D199" t="str">
-        <v>Pineapple</v>
+        <v>Other</v>
       </c>
       <c r="E199" t="str">
-        <v>สับปะรด 18 ลูก</v>
+        <v>4-5-2569 เบอร์ 70฿ 60 ลูก ยอด 4,200</v>
       </c>
       <c r="F199">
-        <v>486</v>
+        <v>8200</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>06/05/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="B200" t="str">
         <v>May26</v>
       </c>
       <c r="C200" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D200" t="str">
-        <v>Apple</v>
+        <v>Other</v>
       </c>
       <c r="E200" t="str">
-        <v>แอปเปิ้ล 4 ลัง</v>
+        <v>พรหมเช็ดเท้า 1 ผืน</v>
       </c>
       <c r="F200">
-        <v>1400</v>
+        <v>372</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>08/05/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="B201" t="str">
         <v>May26</v>
@@ -5146,18 +5146,18 @@
         <v>COGS</v>
       </c>
       <c r="D201" t="str">
-        <v>Transportation</v>
+        <v>Milk/Conden</v>
       </c>
       <c r="E201" t="str">
-        <v>น้ำ 20 ขวด 900 ถอดเสื้อ 30 ลูก750 กล่องโฟม 3</v>
+        <v>นมข้นจืด 1ลัง 636</v>
       </c>
       <c r="F201">
-        <v>4555</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>08/05/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="B202" t="str">
         <v>May26</v>
@@ -5166,18 +5166,18 @@
         <v>COGS</v>
       </c>
       <c r="D202" t="str">
-        <v>Water</v>
+        <v>Packaging</v>
       </c>
       <c r="E202" t="str">
-        <v>น้ำมะร้าว 1 ลัง</v>
+        <v>นมข้น 3 ลัง 2568</v>
       </c>
       <c r="F202">
-        <v>1100</v>
+        <v>4875</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>08/05/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="B203" t="str">
         <v>May26</v>
@@ -5189,55 +5189,55 @@
         <v>Packaging</v>
       </c>
       <c r="E203" t="str">
-        <v>6 พ.ค. น้ำ 30 ขวด 1500 บาท เนื้อ 11 โล 1320 บาท</v>
+        <v>แก้ว3ลัง 5,301</v>
       </c>
       <c r="F203">
-        <v>2820</v>
+        <v>6132</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>08/05/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="B204" t="str">
         <v>May26</v>
       </c>
       <c r="C204" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D204" t="str">
-        <v>Other</v>
+        <v>Packaging</v>
       </c>
       <c r="E204" t="str">
-        <v>ค่าทำความสะอาดตึกชั้น 1</v>
+        <v>ถุงมือ 20 กล่อง 2246 ฝา1ลัง 969</v>
       </c>
       <c r="F204">
-        <v>2700</v>
+        <v>4496</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>08/05/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="B205" t="str">
         <v>May26</v>
       </c>
       <c r="C205" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D205" t="str">
-        <v>Other</v>
+        <v>Transportation</v>
       </c>
       <c r="E205" t="str">
-        <v>4-5-2569 เบอร์ 70฿ 60 ลูก ยอด 4,200</v>
+        <v>Lalamove</v>
       </c>
       <c r="F205">
-        <v>8200</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>09/05/2026</v>
+        <v>10/05/2026</v>
       </c>
       <c r="B206" t="str">
         <v>May26</v>
@@ -5249,15 +5249,15 @@
         <v>Other</v>
       </c>
       <c r="E206" t="str">
-        <v>พรหมเช็ดเท้า 1 ผืน</v>
+        <v>ไฟ 2อัน 422</v>
       </c>
       <c r="F206">
-        <v>372</v>
+        <v>838</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>09/05/2026</v>
+        <v>11/05/2026</v>
       </c>
       <c r="B207" t="str">
         <v>May26</v>
@@ -5266,18 +5266,18 @@
         <v>COGS</v>
       </c>
       <c r="D207" t="str">
-        <v>Milk/Conden</v>
+        <v>Guava</v>
       </c>
       <c r="E207" t="str">
-        <v>นมข้นจืด 1ลัง 636</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F207">
-        <v>1122</v>
+        <v>600</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>09/05/2026</v>
+        <v>11/05/2026</v>
       </c>
       <c r="B208" t="str">
         <v>May26</v>
@@ -5286,13 +5286,13 @@
         <v>COGS</v>
       </c>
       <c r="D208" t="str">
-        <v>Packaging</v>
+        <v>Mango</v>
       </c>
       <c r="E208" t="str">
-        <v>นมข้น 3 ลัง 2568</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F208">
-        <v>4875</v>
+        <v>910</v>
       </c>
     </row>
     <row r="209">
@@ -5306,18 +5306,18 @@
         <v>COGS</v>
       </c>
       <c r="D209" t="str">
-        <v>Packaging</v>
+        <v>Watermelon</v>
       </c>
       <c r="E209" t="str">
-        <v>แก้ว3ลัง 5,301</v>
+        <v>แตงโม 4000 วันที่ 9-5-26</v>
       </c>
       <c r="F209">
-        <v>6132</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>09/05/2026</v>
+        <v>12/05/2026</v>
       </c>
       <c r="B210" t="str">
         <v>May26</v>
@@ -5326,98 +5326,98 @@
         <v>COGS</v>
       </c>
       <c r="D210" t="str">
-        <v>Packaging</v>
+        <v>Coconut Meat</v>
       </c>
       <c r="E210" t="str">
-        <v>ถุงมือ 20 กล่อง 2246 ฝา1ลัง 969</v>
+        <v>เนื้อมะพร้าว 1 ลัง</v>
       </c>
       <c r="F210">
-        <v>4496</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>09/05/2026</v>
+        <v>13/05/2026</v>
       </c>
       <c r="B211" t="str">
         <v>May26</v>
       </c>
       <c r="C211" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D211" t="str">
-        <v>Transportation</v>
+        <v>Other</v>
       </c>
       <c r="E211" t="str">
-        <v>Lalamove</v>
+        <v>ที่หนีบ 6ตัว 374 บาท</v>
       </c>
       <c r="F211">
-        <v>2000</v>
+        <v>374</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>10/05/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="B212" t="str">
         <v>May26</v>
       </c>
       <c r="C212" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D212" t="str">
-        <v>Other</v>
+        <v>Pineapple</v>
       </c>
       <c r="E212" t="str">
-        <v>ไฟ 2อัน 422</v>
+        <v>09/05/26 สับปะรด 2 ตะกร้า</v>
       </c>
       <c r="F212">
-        <v>838</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>11/05/2026</v>
+        <v>14/05/2026</v>
       </c>
       <c r="B213" t="str">
         <v>May26</v>
       </c>
       <c r="C213" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D213" t="str">
-        <v>Guava</v>
+        <v>Other</v>
       </c>
       <c r="E213" t="str">
-        <v>ฝรั่ง 1 ตะกร้า</v>
+        <v>11-5-2569 50 ลูก ยอด 4,000</v>
       </c>
       <c r="F213">
-        <v>600</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>11/05/2026</v>
+        <v>14/05/2026</v>
       </c>
       <c r="B214" t="str">
         <v>May26</v>
       </c>
       <c r="C214" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D214" t="str">
-        <v>Mango</v>
+        <v>Rental</v>
       </c>
       <c r="E214" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>ค่าเช่า+สต๊อกร้าน 1</v>
       </c>
       <c r="F214">
-        <v>910</v>
+        <v>47000</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>11/05/2026</v>
+        <v>14/05/2026</v>
       </c>
       <c r="B215" t="str">
         <v>May26</v>
@@ -5426,18 +5426,18 @@
         <v>COGS</v>
       </c>
       <c r="D215" t="str">
-        <v>Watermelon</v>
+        <v>Guava</v>
       </c>
       <c r="E215" t="str">
-        <v>แตงโม 4000 วันที่ 9-5-26</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F215">
-        <v>4000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>12/05/2026</v>
+        <v>14/05/2026</v>
       </c>
       <c r="B216" t="str">
         <v>May26</v>
@@ -5446,38 +5446,38 @@
         <v>COGS</v>
       </c>
       <c r="D216" t="str">
-        <v>Coconut Meat</v>
+        <v>Apple</v>
       </c>
       <c r="E216" t="str">
-        <v>เนื้อมะพร้าว 1 ลัง</v>
+        <v>แอปเปิ้ล 3 ลัง</v>
       </c>
       <c r="F216">
-        <v>3500</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>13/05/2026</v>
+        <v>14/05/2026</v>
       </c>
       <c r="B217" t="str">
         <v>May26</v>
       </c>
       <c r="C217" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D217" t="str">
-        <v>Other</v>
+        <v>Mango</v>
       </c>
       <c r="E217" t="str">
-        <v>ที่หนีบ 6ตัว 374 บาท</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F217">
-        <v>374</v>
+        <v>875</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>13/05/2026</v>
+        <v>15/05/2026</v>
       </c>
       <c r="B218" t="str">
         <v>May26</v>
@@ -5486,58 +5486,58 @@
         <v>COGS</v>
       </c>
       <c r="D218" t="str">
-        <v>Pineapple</v>
+        <v>Orange</v>
       </c>
       <c r="E218" t="str">
-        <v>09/05/26 สับปะรด 2 ตะกร้า</v>
+        <v>15/05/69</v>
       </c>
       <c r="F218">
-        <v>1008</v>
+        <v>15730</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>14/05/2026</v>
+        <v>05/05/2026</v>
       </c>
       <c r="B219" t="str">
         <v>May26</v>
       </c>
       <c r="C219" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D219" t="str">
-        <v>Other</v>
+        <v>Orange</v>
       </c>
       <c r="E219" t="str">
-        <v>11-5-2569 50 ลูก ยอด 4,000</v>
+        <v>05/05/69 ส้ม 30x22กก 660กกx30</v>
       </c>
       <c r="F219">
-        <v>8000</v>
+        <v>21450</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>14/05/2026</v>
+        <v>16/05/2026</v>
       </c>
       <c r="B220" t="str">
         <v>May26</v>
       </c>
       <c r="C220" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D220" t="str">
-        <v>Rental</v>
+        <v>Ice</v>
       </c>
       <c r="E220" t="str">
-        <v>ค่าเช่า+สต๊อกร้าน 1</v>
+        <v>Police fees -2000 2 head</v>
       </c>
       <c r="F220">
-        <v>47000</v>
+        <v>4290</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>14/05/2026</v>
+        <v>16/05/2026</v>
       </c>
       <c r="B221" t="str">
         <v>May26</v>
@@ -5546,38 +5546,38 @@
         <v>COGS</v>
       </c>
       <c r="D221" t="str">
-        <v>Guava</v>
+        <v>Coconut</v>
       </c>
       <c r="E221" t="str">
-        <v>ฝรั่ง 1 ตะกร้า</v>
+        <v>มะพร้าว 20 โล</v>
       </c>
       <c r="F221">
-        <v>600</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>14/05/2026</v>
+        <v>16/05/2026</v>
       </c>
       <c r="B222" t="str">
         <v>May26</v>
       </c>
       <c r="C222" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D222" t="str">
-        <v>Apple</v>
+        <v>Other</v>
       </c>
       <c r="E222" t="str">
-        <v>แอปเปิ้ล 3 ลัง</v>
+        <v>14/05/26 18 ลูก 504 บาท 16/05/26 18 ลูก</v>
       </c>
       <c r="F222">
-        <v>1050</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>14/05/2026</v>
+        <v>16/05/2026</v>
       </c>
       <c r="B223" t="str">
         <v>May26</v>
@@ -5589,7 +5589,7 @@
         <v>Mango</v>
       </c>
       <c r="E223" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>มะม่วง 1</v>
       </c>
       <c r="F223">
         <v>875</v>
@@ -5597,7 +5597,7 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>15/05/2026</v>
+        <v>19/05/2026</v>
       </c>
       <c r="B224" t="str">
         <v>May26</v>
@@ -5606,18 +5606,18 @@
         <v>COGS</v>
       </c>
       <c r="D224" t="str">
-        <v>Orange</v>
+        <v>Mango</v>
       </c>
       <c r="E224" t="str">
-        <v>15/05/69</v>
+        <v>มะม่วง 1 ลัง (25 โล)</v>
       </c>
       <c r="F224">
-        <v>15730</v>
+        <v>875</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>15/05/2026</v>
+        <v>19/05/2026</v>
       </c>
       <c r="B225" t="str">
         <v>May26</v>
@@ -5626,18 +5626,18 @@
         <v>COGS</v>
       </c>
       <c r="D225" t="str">
-        <v>Orange</v>
+        <v>Guava</v>
       </c>
       <c r="E225" t="str">
-        <v>05/05/69 ส้ม 30x22กก 660กกx30</v>
+        <v>ฝรั่ง 1 ลัง</v>
       </c>
       <c r="F225">
-        <v>21450</v>
+        <v>600</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>16/05/2026</v>
+        <v>19/05/2026</v>
       </c>
       <c r="B226" t="str">
         <v>May26</v>
@@ -5646,18 +5646,18 @@
         <v>COGS</v>
       </c>
       <c r="D226" t="str">
-        <v>Ice</v>
+        <v>Apple</v>
       </c>
       <c r="E226" t="str">
-        <v>Police fees -2000 2 head</v>
+        <v>แอปเปิ้ล 4 ลังครับ</v>
       </c>
       <c r="F226">
-        <v>4290</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>16/05/2026</v>
+        <v>19/05/2026</v>
       </c>
       <c r="B227" t="str">
         <v>May26</v>
@@ -5666,38 +5666,38 @@
         <v>COGS</v>
       </c>
       <c r="D227" t="str">
-        <v>Coconut</v>
+        <v>Pineapple</v>
       </c>
       <c r="E227" t="str">
-        <v>มะพร้าว 20 โล</v>
+        <v>36*18 648</v>
       </c>
       <c r="F227">
-        <v>2400</v>
+        <v>648</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>16/05/2026</v>
+        <v>22/05/2026</v>
       </c>
       <c r="B228" t="str">
         <v>May26</v>
       </c>
       <c r="C228" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D228" t="str">
-        <v>Other</v>
+        <v>Apple</v>
       </c>
       <c r="E228" t="str">
-        <v>14/05/26 18 ลูก 504 บาท 16/05/26 18 ลูก</v>
+        <v>แอปเปิ้ล 2 ลัง</v>
       </c>
       <c r="F228">
-        <v>1008</v>
+        <v>700</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>16/05/2026</v>
+        <v>22/05/2026</v>
       </c>
       <c r="B229" t="str">
         <v>May26</v>
@@ -5706,18 +5706,18 @@
         <v>COGS</v>
       </c>
       <c r="D229" t="str">
-        <v>Mango</v>
+        <v>Pineapple</v>
       </c>
       <c r="E229" t="str">
-        <v>มะม่วง 1</v>
+        <v>สับปะรด 18 ลูก</v>
       </c>
       <c r="F229">
-        <v>875</v>
+        <v>522</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>19/05/2026</v>
+        <v>22/05/2026</v>
       </c>
       <c r="B230" t="str">
         <v>May26</v>
@@ -5729,35 +5729,35 @@
         <v>Mango</v>
       </c>
       <c r="E230" t="str">
-        <v>มะม่วง 1 ลัง (25 โล)</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F230">
-        <v>875</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>19/05/2026</v>
+        <v>22/05/2026</v>
       </c>
       <c r="B231" t="str">
         <v>May26</v>
       </c>
       <c r="C231" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D231" t="str">
-        <v>Guava</v>
+        <v>Other</v>
       </c>
       <c r="E231" t="str">
-        <v>ฝรั่ง 1 ลัง</v>
+        <v>16-5-2569ยอด 4,000฿</v>
       </c>
       <c r="F231">
-        <v>600</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>19/05/2026</v>
+        <v>22/05/2026</v>
       </c>
       <c r="B232" t="str">
         <v>May26</v>
@@ -5766,18 +5766,18 @@
         <v>COGS</v>
       </c>
       <c r="D232" t="str">
-        <v>Apple</v>
+        <v>Guava</v>
       </c>
       <c r="E232" t="str">
-        <v>แอปเปิ้ล 4 ลังครับ</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F232">
-        <v>1400</v>
+        <v>600</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>19/05/2026</v>
+        <v>22/05/2026</v>
       </c>
       <c r="B233" t="str">
         <v>May26</v>
@@ -5786,18 +5786,18 @@
         <v>COGS</v>
       </c>
       <c r="D233" t="str">
-        <v>Pineapple</v>
+        <v>Transportation</v>
       </c>
       <c r="E233" t="str">
-        <v>36*18 648</v>
+        <v>ค่าขนส่ง</v>
       </c>
       <c r="F233">
-        <v>648</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>22/05/2026</v>
+        <v>23/05/2026</v>
       </c>
       <c r="B234" t="str">
         <v>May26</v>
@@ -5806,18 +5806,18 @@
         <v>COGS</v>
       </c>
       <c r="D234" t="str">
-        <v>Apple</v>
+        <v>Packaging</v>
       </c>
       <c r="E234" t="str">
-        <v>แอปเปิ้ล 2 ลัง</v>
+        <v>แก้ว 3 ลัง</v>
       </c>
       <c r="F234">
-        <v>700</v>
+        <v>4680</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>22/05/2026</v>
+        <v>23/05/2026</v>
       </c>
       <c r="B235" t="str">
         <v>May26</v>
@@ -5826,18 +5826,18 @@
         <v>COGS</v>
       </c>
       <c r="D235" t="str">
-        <v>Pineapple</v>
+        <v>Packaging</v>
       </c>
       <c r="E235" t="str">
-        <v>สับปะรด 18 ลูก</v>
+        <v>ฝา1 788</v>
       </c>
       <c r="F235">
-        <v>522</v>
+        <v>2902</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>22/05/2026</v>
+        <v>23/05/2026</v>
       </c>
       <c r="B236" t="str">
         <v>May26</v>
@@ -5846,38 +5846,38 @@
         <v>COGS</v>
       </c>
       <c r="D236" t="str">
-        <v>Mango</v>
+        <v>Packaging</v>
       </c>
       <c r="E236" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>หลอด20 แพค (767)</v>
       </c>
       <c r="F236">
-        <v>1000</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>22/05/2026</v>
+        <v>25/05/2026</v>
       </c>
       <c r="B237" t="str">
         <v>May26</v>
       </c>
       <c r="C237" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D237" t="str">
-        <v>Other</v>
+        <v>Pineapple</v>
       </c>
       <c r="E237" t="str">
-        <v>16-5-2569ยอด 4,000฿</v>
+        <v>สับปะรด 18 ลูก</v>
       </c>
       <c r="F237">
-        <v>12000</v>
+        <v>594</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>22/05/2026</v>
+        <v>25/05/2026</v>
       </c>
       <c r="B238" t="str">
         <v>May26</v>
@@ -5886,18 +5886,18 @@
         <v>COGS</v>
       </c>
       <c r="D238" t="str">
-        <v>Guava</v>
+        <v>Apple</v>
       </c>
       <c r="E238" t="str">
-        <v>ฝรั่ง 1 ตะกร้า</v>
+        <v>แอปเปิ้ล 3 ลังครับ</v>
       </c>
       <c r="F238">
-        <v>600</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>22/05/2026</v>
+        <v>25/05/2026</v>
       </c>
       <c r="B239" t="str">
         <v>May26</v>
@@ -5906,18 +5906,18 @@
         <v>COGS</v>
       </c>
       <c r="D239" t="str">
-        <v>Transportation</v>
+        <v>Orange</v>
       </c>
       <c r="E239" t="str">
-        <v>ค่าขนส่ง</v>
+        <v>ค่าส่งส้ม Lalamove หักผ่านบัตร</v>
       </c>
       <c r="F239">
-        <v>2000</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>23/05/2026</v>
+        <v>24/05/2026</v>
       </c>
       <c r="B240" t="str">
         <v>May26</v>
@@ -5926,38 +5926,38 @@
         <v>COGS</v>
       </c>
       <c r="D240" t="str">
-        <v>Packaging</v>
+        <v>Orange</v>
       </c>
       <c r="E240" t="str">
-        <v>แก้ว 3 ลัง</v>
+        <v>24/05/69</v>
       </c>
       <c r="F240">
-        <v>4680</v>
+        <v>15015</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>23/05/2026</v>
+        <v>25/05/2026</v>
       </c>
       <c r="B241" t="str">
         <v>May26</v>
       </c>
       <c r="C241" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D241" t="str">
-        <v>Packaging</v>
+        <v>Salary</v>
       </c>
       <c r="E241" t="str">
-        <v>ฝา1 788</v>
+        <v>เงินเดือนซี เดือนพ.ค.</v>
       </c>
       <c r="F241">
-        <v>2902</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>23/05/2026</v>
+        <v>25/05/2026</v>
       </c>
       <c r="B242" t="str">
         <v>May26</v>
@@ -5966,13 +5966,13 @@
         <v>COGS</v>
       </c>
       <c r="D242" t="str">
-        <v>Packaging</v>
+        <v>Guava</v>
       </c>
       <c r="E242" t="str">
-        <v>หลอด20 แพค (767)</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F242">
-        <v>1502</v>
+        <v>600</v>
       </c>
     </row>
     <row r="243">
@@ -5986,58 +5986,58 @@
         <v>COGS</v>
       </c>
       <c r="D243" t="str">
-        <v>Pineapple</v>
+        <v>Mango</v>
       </c>
       <c r="E243" t="str">
-        <v>สับปะรด 18 ลูก</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F243">
-        <v>594</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>25/05/2026</v>
+        <v>27/05/2026</v>
       </c>
       <c r="B244" t="str">
         <v>May26</v>
       </c>
       <c r="C244" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D244" t="str">
-        <v>Apple</v>
+        <v>Salary</v>
       </c>
       <c r="E244" t="str">
-        <v>แอปเปิ้ล 3 ลังครับ</v>
+        <v>เงินเดือนเมน 5/26</v>
       </c>
       <c r="F244">
-        <v>1050</v>
+        <v>19000</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>25/05/2026</v>
+        <v>28/05/2026</v>
       </c>
       <c r="B245" t="str">
         <v>May26</v>
       </c>
       <c r="C245" t="str">
-        <v>COGS</v>
+        <v>CAPEX</v>
       </c>
       <c r="D245" t="str">
-        <v>Orange</v>
+        <v>Investment</v>
       </c>
       <c r="E245" t="str">
-        <v>ค่าส่งส้ม Lalamove หักผ่านบัตร</v>
+        <v>เครื่องสกัดเย็น 1</v>
       </c>
       <c r="F245">
-        <v>1245</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>25/05/2026</v>
+        <v>28/05/2026</v>
       </c>
       <c r="B246" t="str">
         <v>May26</v>
@@ -6046,38 +6046,38 @@
         <v>COGS</v>
       </c>
       <c r="D246" t="str">
-        <v>Orange</v>
+        <v>Coconut</v>
       </c>
       <c r="E246" t="str">
-        <v>24/05/69</v>
+        <v>มะพร้าวถอดเสื้อ 23 ลูก *35 ราคา 805 ค่าส่ง 150</v>
       </c>
       <c r="F246">
-        <v>15015</v>
+        <v>955</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>25/05/2026</v>
+        <v>30/05/2026</v>
       </c>
       <c r="B247" t="str">
         <v>May26</v>
       </c>
       <c r="C247" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D247" t="str">
-        <v>Salary</v>
+        <v>Pineapple</v>
       </c>
       <c r="E247" t="str">
-        <v>เงินเดือนซี เดือนพ.ค.</v>
+        <v>สับปะรด 18 ลูก</v>
       </c>
       <c r="F247">
-        <v>7800</v>
+        <v>576</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>25/05/2026</v>
+        <v>30/05/2026</v>
       </c>
       <c r="B248" t="str">
         <v>May26</v>
@@ -6086,101 +6086,101 @@
         <v>COGS</v>
       </c>
       <c r="D248" t="str">
-        <v>Guava</v>
+        <v>Mango</v>
       </c>
       <c r="E248" t="str">
-        <v>ฝรั่ง 1 ตะกร้า</v>
+        <v>มะม่วง 1 ตะกร้า</v>
       </c>
       <c r="F248">
-        <v>600</v>
+        <v>960</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>25/05/2026</v>
+        <v>30/05/2026</v>
       </c>
       <c r="B249" t="str">
         <v>May26</v>
       </c>
       <c r="C249" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D249" t="str">
-        <v>Mango</v>
+        <v>Other</v>
       </c>
       <c r="E249" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>Unknown</v>
       </c>
       <c r="F249">
-        <v>1000</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>27/05/2026</v>
+        <v>30/05/2026</v>
       </c>
       <c r="B250" t="str">
         <v>May26</v>
       </c>
       <c r="C250" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D250" t="str">
-        <v>Salary</v>
+        <v>Guava</v>
       </c>
       <c r="E250" t="str">
-        <v>เงินเดือนเมน 5/26</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F250">
-        <v>19000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>28/05/2026</v>
+        <v>31/05/2026</v>
       </c>
       <c r="B251" t="str">
         <v>May26</v>
       </c>
       <c r="C251" t="str">
-        <v>CAPEX</v>
+        <v>OPEX</v>
       </c>
       <c r="D251" t="str">
         <v>Investment</v>
       </c>
       <c r="E251" t="str">
-        <v>เครื่องสกัดเย็น 1</v>
+        <v>Stock Adjustment (Allocated to B2)</v>
       </c>
       <c r="F251">
-        <v>1065</v>
+        <v>-4830</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>28/05/2026</v>
+        <v>01/06/2026</v>
       </c>
       <c r="B252" t="str">
         <v>May26</v>
       </c>
       <c r="C252" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D252" t="str">
-        <v>Coconut</v>
+        <v>Salary</v>
       </c>
       <c r="E252" t="str">
-        <v>มะพร้าวถอดเสื้อ 23 ลูก *35 ราคา 805 ค่าส่ง 150</v>
+        <v>Unknown</v>
       </c>
       <c r="F252">
-        <v>955</v>
+        <v>0</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>30/05/2026</v>
+        <v>02/06/2026</v>
       </c>
       <c r="B253" t="str">
-        <v>May26</v>
+        <v>Jun26</v>
       </c>
       <c r="C253" t="str">
         <v>COGS</v>
@@ -6189,58 +6189,58 @@
         <v>Pineapple</v>
       </c>
       <c r="E253" t="str">
-        <v>สับปะรด 18 ลูก</v>
+        <v>สับปะรด ราคา 31*18 ลูก 558</v>
       </c>
       <c r="F253">
-        <v>576</v>
+        <v>558</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>30/05/2026</v>
+        <v>02/06/2026</v>
       </c>
       <c r="B254" t="str">
-        <v>May26</v>
+        <v>Jun26</v>
       </c>
       <c r="C254" t="str">
         <v>COGS</v>
       </c>
       <c r="D254" t="str">
-        <v>Mango</v>
+        <v>Guava</v>
       </c>
       <c r="E254" t="str">
-        <v>มะม่วง 1 ตะกร้า</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F254">
-        <v>960</v>
+        <v>600</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>30/05/2026</v>
+        <v>04/06/2026</v>
       </c>
       <c r="B255" t="str">
-        <v>May26</v>
+        <v>Jun26</v>
       </c>
       <c r="C255" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D255" t="str">
-        <v>Other</v>
+        <v>Pineapple</v>
       </c>
       <c r="E255" t="str">
-        <v>Unknown</v>
+        <v>Watermelon 750+pineapple - 750</v>
       </c>
       <c r="F255">
-        <v>1050</v>
+        <v>5750</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>30/05/2026</v>
+        <v>04/06/2026</v>
       </c>
       <c r="B256" t="str">
-        <v>May26</v>
+        <v>Jun26</v>
       </c>
       <c r="C256" t="str">
         <v>COGS</v>
@@ -6252,52 +6252,52 @@
         <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F256">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>31/05/2026</v>
+        <v>04/06/2026</v>
       </c>
       <c r="B257" t="str">
-        <v>May26</v>
+        <v>Jun26</v>
       </c>
       <c r="C257" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D257" t="str">
-        <v>Investment</v>
+        <v>Mango</v>
       </c>
       <c r="E257" t="str">
-        <v>Stock Adjustment (Allocated to B2)</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F257">
-        <v>-4830</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>01/06/2026</v>
+        <v>04/06/2026</v>
       </c>
       <c r="B258" t="str">
-        <v>May26</v>
+        <v>Jun26</v>
       </c>
       <c r="C258" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D258" t="str">
-        <v>Salary</v>
+        <v>Apple</v>
       </c>
       <c r="E258" t="str">
-        <v>Unknown</v>
+        <v>แอพเปิ้ล 4 ลัง</v>
       </c>
       <c r="F258">
-        <v>0</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>02/06/2026</v>
+        <v>04/06/2026</v>
       </c>
       <c r="B259" t="str">
         <v>Jun26</v>
@@ -6309,15 +6309,15 @@
         <v>Pineapple</v>
       </c>
       <c r="E259" t="str">
-        <v>สับปะรด ราคา 31*18 ลูก 558</v>
+        <v>สับปะรด 2 ลูก</v>
       </c>
       <c r="F259">
-        <v>558</v>
+        <v>36</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>02/06/2026</v>
+        <v>04/06/2026</v>
       </c>
       <c r="B260" t="str">
         <v>Jun26</v>
@@ -6326,18 +6326,18 @@
         <v>COGS</v>
       </c>
       <c r="D260" t="str">
-        <v>Guava</v>
+        <v>Packaging</v>
       </c>
       <c r="E260" t="str">
-        <v>ฝรั่ง 1 ตะกร้า</v>
+        <v>ขวดใหญ่ 1000ml 98 ใบ 364 ถุงเล็ก 20</v>
       </c>
       <c r="F260">
-        <v>600</v>
+        <v>764</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>02/06/2026</v>
+        <v>05/06/2026</v>
       </c>
       <c r="B261" t="str">
         <v>Jun26</v>
@@ -6346,18 +6346,18 @@
         <v>COGS</v>
       </c>
       <c r="D261" t="str">
-        <v>Watermelon</v>
+        <v>Pineapple</v>
       </c>
       <c r="E261" t="str">
-        <v>แตงโม 160 ลูก (25-5-2569: 80 ลูก, 30-5-2569: 80 ลูก)</v>
+        <v>สับปะรด 33*18 รวม 594</v>
       </c>
       <c r="F261">
-        <v>8000</v>
+        <v>594</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>04/06/2026</v>
+        <v>07/06/2026</v>
       </c>
       <c r="B262" t="str">
         <v>Jun26</v>
@@ -6366,18 +6366,18 @@
         <v>COGS</v>
       </c>
       <c r="D262" t="str">
-        <v>Pineapple</v>
+        <v>Orange</v>
       </c>
       <c r="E262" t="str">
-        <v>Watermelon 750+pineapple - 750</v>
+        <v>ส้ม 20x22กก 440กกx30 13,200บาท</v>
       </c>
       <c r="F262">
-        <v>5750</v>
+        <v>14300</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>04/06/2026</v>
+        <v>08/06/2026</v>
       </c>
       <c r="B263" t="str">
         <v>Jun26</v>
@@ -6386,58 +6386,58 @@
         <v>COGS</v>
       </c>
       <c r="D263" t="str">
-        <v>Guava</v>
+        <v>Transportation</v>
       </c>
       <c r="E263" t="str">
-        <v>ฝรั่ง 1 ตะกร้า</v>
+        <v>Lalamove</v>
       </c>
       <c r="F263">
-        <v>700</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>04/06/2026</v>
+        <v>08/06/2026</v>
       </c>
       <c r="B264" t="str">
         <v>Jun26</v>
       </c>
       <c r="C264" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D264" t="str">
-        <v>Mango</v>
+        <v>Rental</v>
       </c>
       <c r="E264" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>ค่าเช่าสต็อค เดือน June (B1 portion, split from joint 12,000 - see B2 for other half)</v>
       </c>
       <c r="F264">
-        <v>1040</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>04/06/2026</v>
+        <v>08/06/2026</v>
       </c>
       <c r="B265" t="str">
         <v>Jun26</v>
       </c>
       <c r="C265" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D265" t="str">
-        <v>Apple</v>
+        <v>Rental</v>
       </c>
       <c r="E265" t="str">
-        <v>แอพเปิ้ล 4 ลัง</v>
+        <v>ค่าเช่าร้านเดือน June (06) b1 35000</v>
       </c>
       <c r="F265">
-        <v>1400</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>04/06/2026</v>
+        <v>08/06/2026</v>
       </c>
       <c r="B266" t="str">
         <v>Jun26</v>
@@ -6449,15 +6449,15 @@
         <v>Pineapple</v>
       </c>
       <c r="E266" t="str">
-        <v>สับปะรด 2 ลูก</v>
+        <v>สับปะรด 15 ลูก</v>
       </c>
       <c r="F266">
-        <v>36</v>
+        <v>504</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>04/06/2026</v>
+        <v>08/06/2026</v>
       </c>
       <c r="B267" t="str">
         <v>Jun26</v>
@@ -6466,18 +6466,18 @@
         <v>COGS</v>
       </c>
       <c r="D267" t="str">
-        <v>Packaging</v>
+        <v>Mango</v>
       </c>
       <c r="E267" t="str">
-        <v>ขวดใหญ่ 1000ml 98 ใบ 364 ถุงเล็ก 20</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F267">
-        <v>764</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>05/06/2026</v>
+        <v>08/06/2026</v>
       </c>
       <c r="B268" t="str">
         <v>Jun26</v>
@@ -6486,18 +6486,18 @@
         <v>COGS</v>
       </c>
       <c r="D268" t="str">
-        <v>Pineapple</v>
+        <v>Apple</v>
       </c>
       <c r="E268" t="str">
-        <v>สับปะรด 33*18 รวม 594</v>
+        <v>แอปเปิ้ล 5 ลัง</v>
       </c>
       <c r="F268">
-        <v>594</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>05/06/2026</v>
+        <v>08/06/2026</v>
       </c>
       <c r="B269" t="str">
         <v>Jun26</v>
@@ -6506,18 +6506,18 @@
         <v>COGS</v>
       </c>
       <c r="D269" t="str">
-        <v>Watermelon</v>
+        <v>Guava</v>
       </c>
       <c r="E269" t="str">
-        <v>แตงโม 100 ลูก (2-6-2569: 50 ลูก, 4-6-2569: 50 ลูก)</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F269">
-        <v>8000</v>
+        <v>700</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>07/06/2026</v>
+        <v>09/06/2026</v>
       </c>
       <c r="B270" t="str">
         <v>Jun26</v>
@@ -6526,18 +6526,18 @@
         <v>COGS</v>
       </c>
       <c r="D270" t="str">
-        <v>Orange</v>
+        <v>Packaging</v>
       </c>
       <c r="E270" t="str">
-        <v>ส้ม 20x22กก 440กกx30 13,200บาท</v>
+        <v>แก้ว 1937*3 รวม 5,811</v>
       </c>
       <c r="F270">
-        <v>14300</v>
+        <v>6659</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>08/06/2026</v>
+        <v>09/06/2026</v>
       </c>
       <c r="B271" t="str">
         <v>Jun26</v>
@@ -6546,18 +6546,18 @@
         <v>COGS</v>
       </c>
       <c r="D271" t="str">
-        <v>Transportation</v>
+        <v>Packaging</v>
       </c>
       <c r="E271" t="str">
-        <v>Lalamove</v>
+        <v>หลอด 20 แพ็ก 671</v>
       </c>
       <c r="F271">
-        <v>2000</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>08/06/2026</v>
+        <v>09/06/2026</v>
       </c>
       <c r="B272" t="str">
         <v>Jun26</v>
@@ -6566,38 +6566,38 @@
         <v>COGS</v>
       </c>
       <c r="D272" t="str">
-        <v>Stock</v>
+        <v>Packaging</v>
       </c>
       <c r="E272" t="str">
-        <v>Stock June 2026 (split from rent slip)</v>
+        <v>ฝา1 714</v>
       </c>
       <c r="F272">
-        <v>12000</v>
+        <v>714</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>08/06/2026</v>
+        <v>09/06/2026</v>
       </c>
       <c r="B273" t="str">
         <v>Jun26</v>
       </c>
       <c r="C273" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D273" t="str">
-        <v>Rental</v>
+        <v>Packaging</v>
       </c>
       <c r="E273" t="str">
-        <v>ค่าเช่าร้านเดือน June (06) b1 35000</v>
+        <v>ถุงขยะ 4แพคใหญ่ 1019</v>
       </c>
       <c r="F273">
-        <v>35000</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>08/06/2026</v>
+        <v>11/06/2026</v>
       </c>
       <c r="B274" t="str">
         <v>Jun26</v>
@@ -6606,18 +6606,18 @@
         <v>COGS</v>
       </c>
       <c r="D274" t="str">
-        <v>Pineapple</v>
+        <v>Guava</v>
       </c>
       <c r="E274" t="str">
-        <v>สับปะรด 15 ลูก</v>
+        <v>ฝรั่ง 1 ลัง</v>
       </c>
       <c r="F274">
-        <v>504</v>
+        <v>700</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>08/06/2026</v>
+        <v>12/06/2026</v>
       </c>
       <c r="B275" t="str">
         <v>Jun26</v>
@@ -6626,18 +6626,18 @@
         <v>COGS</v>
       </c>
       <c r="D275" t="str">
-        <v>Mango</v>
+        <v>Coconut Water</v>
       </c>
       <c r="E275" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>น้ำมะพร้าว50*20 1,000</v>
       </c>
       <c r="F275">
-        <v>1170</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>08/06/2026</v>
+        <v>12/06/2026</v>
       </c>
       <c r="B276" t="str">
         <v>Jun26</v>
@@ -6646,18 +6646,18 @@
         <v>COGS</v>
       </c>
       <c r="D276" t="str">
-        <v>Apple</v>
+        <v>Mango</v>
       </c>
       <c r="E276" t="str">
-        <v>แอปเปิ้ล 5 ลัง</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F276">
-        <v>1750</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>08/06/2026</v>
+        <v>12/06/2026</v>
       </c>
       <c r="B277" t="str">
         <v>Jun26</v>
@@ -6666,18 +6666,18 @@
         <v>COGS</v>
       </c>
       <c r="D277" t="str">
-        <v>Guava</v>
+        <v>Apple</v>
       </c>
       <c r="E277" t="str">
-        <v>ฝรั่ง 1 ตะกร้า</v>
+        <v>แอปเปิ้ล 5 ลัง</v>
       </c>
       <c r="F277">
-        <v>700</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>09/06/2026</v>
+        <v>12/06/2026</v>
       </c>
       <c r="B278" t="str">
         <v>Jun26</v>
@@ -6686,18 +6686,18 @@
         <v>COGS</v>
       </c>
       <c r="D278" t="str">
-        <v>Packaging</v>
+        <v>Pineapple</v>
       </c>
       <c r="E278" t="str">
-        <v>แก้ว 1937*3 รวม 5,811</v>
+        <v>สับปะรด 19 ลูก</v>
       </c>
       <c r="F278">
-        <v>6659</v>
+        <v>950</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>09/06/2026</v>
+        <v>15/06/2026</v>
       </c>
       <c r="B279" t="str">
         <v>Jun26</v>
@@ -6706,18 +6706,18 @@
         <v>COGS</v>
       </c>
       <c r="D279" t="str">
-        <v>Packaging</v>
+        <v>Pineapple</v>
       </c>
       <c r="E279" t="str">
-        <v>หลอด 20 แพ็ก 671</v>
+        <v>สับปะรด 1 ลูก</v>
       </c>
       <c r="F279">
-        <v>1149</v>
+        <v>50</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>09/06/2026</v>
+        <v>15/06/2026</v>
       </c>
       <c r="B280" t="str">
         <v>Jun26</v>
@@ -6726,18 +6726,18 @@
         <v>COGS</v>
       </c>
       <c r="D280" t="str">
-        <v>Packaging</v>
+        <v>Ice</v>
       </c>
       <c r="E280" t="str">
-        <v>ฝา1 714</v>
+        <v>Unknown</v>
       </c>
       <c r="F280">
-        <v>714</v>
+        <v>18</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>09/06/2026</v>
+        <v>15/06/2026</v>
       </c>
       <c r="B281" t="str">
         <v>Jun26</v>
@@ -6746,18 +6746,18 @@
         <v>COGS</v>
       </c>
       <c r="D281" t="str">
-        <v>Packaging</v>
+        <v>Pineapple</v>
       </c>
       <c r="E281" t="str">
-        <v>ถุงขยะ 4แพคใหญ่ 1019</v>
+        <v>สับปะรด 12 ลูก</v>
       </c>
       <c r="F281">
-        <v>1830</v>
+        <v>525</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>11/06/2026</v>
+        <v>15/06/2026</v>
       </c>
       <c r="B282" t="str">
         <v>Jun26</v>
@@ -6769,15 +6769,15 @@
         <v>Guava</v>
       </c>
       <c r="E282" t="str">
-        <v>ฝรั่ง 1 ลัง</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F282">
-        <v>700</v>
+        <v>800</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>12/06/2026</v>
+        <v>09/06/2026</v>
       </c>
       <c r="B283" t="str">
         <v>Jun26</v>
@@ -6786,18 +6786,18 @@
         <v>COGS</v>
       </c>
       <c r="D283" t="str">
-        <v>Coconut Water</v>
+        <v>Orange</v>
       </c>
       <c r="E283" t="str">
-        <v>น้ำมะพร้าว50*20 1,000</v>
+        <v>รอบ 09/06/69</v>
       </c>
       <c r="F283">
-        <v>2200</v>
+        <v>16445</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>12/06/2026</v>
+        <v>18/06/2026</v>
       </c>
       <c r="B284" t="str">
         <v>Jun26</v>
@@ -6812,12 +6812,12 @@
         <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F284">
-        <v>1170</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>12/06/2026</v>
+        <v>18/06/2026</v>
       </c>
       <c r="B285" t="str">
         <v>Jun26</v>
@@ -6826,18 +6826,18 @@
         <v>COGS</v>
       </c>
       <c r="D285" t="str">
-        <v>Apple</v>
+        <v>Coconut Water</v>
       </c>
       <c r="E285" t="str">
-        <v>แอปเปิ้ล 5 ลัง</v>
+        <v>เนื้อมะพร้าว 20 * 120 2400 น้ำมะพร้าว 20 *</v>
       </c>
       <c r="F285">
-        <v>1750</v>
+        <v>3400</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>12/06/2026</v>
+        <v>18/06/2026</v>
       </c>
       <c r="B286" t="str">
         <v>Jun26</v>
@@ -6846,18 +6846,18 @@
         <v>COGS</v>
       </c>
       <c r="D286" t="str">
-        <v>Pineapple</v>
+        <v>Guava</v>
       </c>
       <c r="E286" t="str">
-        <v>สับปะรด 19 ลูก</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F286">
-        <v>950</v>
+        <v>800</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>14/06/2026</v>
+        <v>19/06/2026</v>
       </c>
       <c r="B287" t="str">
         <v>Jun26</v>
@@ -6866,18 +6866,18 @@
         <v>COGS</v>
       </c>
       <c r="D287" t="str">
-        <v>Watermelon</v>
+        <v>Coconut Water</v>
       </c>
       <c r="E287" t="str">
-        <v>แตงโม 90 ลูก (7-6-2569: 45 ลูก, 12-6-2569: 45 ลูก)</v>
+        <v>น้ำมะพร้าว40ลิตร ลิตรละ45บาท</v>
       </c>
       <c r="F287">
-        <v>7200</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>15/06/2026</v>
+        <v>19/06/2026</v>
       </c>
       <c r="B288" t="str">
         <v>Jun26</v>
@@ -6886,13 +6886,13 @@
         <v>COGS</v>
       </c>
       <c r="D288" t="str">
-        <v>Pineapple</v>
+        <v>Packaging</v>
       </c>
       <c r="E288" t="str">
-        <v>สับปะรด 1 ลูก</v>
+        <v>น้ำยาล้างจาน 7 ถุง ผงซักฟอก 1</v>
       </c>
       <c r="F288">
-        <v>50</v>
+        <v>149</v>
       </c>
     </row>
     <row r="289">
@@ -6906,18 +6906,18 @@
         <v>COGS</v>
       </c>
       <c r="D289" t="str">
-        <v>Ice</v>
+        <v>Watermelon</v>
       </c>
       <c r="E289" t="str">
-        <v>Unknown</v>
+        <v>15-6-2569 แตงโม 50บาท 50 ลูก ยอด 2,500</v>
       </c>
       <c r="F289">
-        <v>18</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>15/06/2026</v>
+        <v>22/06/2026</v>
       </c>
       <c r="B290" t="str">
         <v>Jun26</v>
@@ -6929,15 +6929,15 @@
         <v>Pineapple</v>
       </c>
       <c r="E290" t="str">
-        <v>สับปะรด 12 ลูก</v>
+        <v>สับปะรด 15 ลูก</v>
       </c>
       <c r="F290">
-        <v>525</v>
+        <v>700</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>15/06/2026</v>
+        <v>22/06/2026</v>
       </c>
       <c r="B291" t="str">
         <v>Jun26</v>
@@ -6946,18 +6946,18 @@
         <v>COGS</v>
       </c>
       <c r="D291" t="str">
-        <v>Guava</v>
+        <v>Mango</v>
       </c>
       <c r="E291" t="str">
-        <v>ฝรั่ง 1 ตะกร้า</v>
+        <v>มะม่วง 2 ลัง</v>
       </c>
       <c r="F291">
-        <v>800</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>17/06/2026</v>
+        <v>22/06/2026</v>
       </c>
       <c r="B292" t="str">
         <v>Jun26</v>
@@ -6966,18 +6966,18 @@
         <v>COGS</v>
       </c>
       <c r="D292" t="str">
-        <v>Orange</v>
+        <v>Transportation</v>
       </c>
       <c r="E292" t="str">
-        <v>รอบ 09/06/69</v>
+        <v>Lalamove</v>
       </c>
       <c r="F292">
-        <v>16445</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>18/06/2026</v>
+        <v>22/06/2026</v>
       </c>
       <c r="B293" t="str">
         <v>Jun26</v>
@@ -6986,18 +6986,18 @@
         <v>COGS</v>
       </c>
       <c r="D293" t="str">
-        <v>Mango</v>
+        <v>Apple</v>
       </c>
       <c r="E293" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>แอพเปิ้ล 5 ลัง</v>
       </c>
       <c r="F293">
-        <v>1300</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>18/06/2026</v>
+        <v>22/06/2026</v>
       </c>
       <c r="B294" t="str">
         <v>Jun26</v>
@@ -7006,18 +7006,18 @@
         <v>COGS</v>
       </c>
       <c r="D294" t="str">
-        <v>Coconut Water</v>
+        <v>Guava</v>
       </c>
       <c r="E294" t="str">
-        <v>เนื้อมะพร้าว 20 * 120 2400 น้ำมะพร้าว 20 *</v>
+        <v>ฝรั่ง 1 ลัง</v>
       </c>
       <c r="F294">
-        <v>3400</v>
+        <v>700</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>18/06/2026</v>
+        <v>24/06/2026</v>
       </c>
       <c r="B295" t="str">
         <v>Jun26</v>
@@ -7026,18 +7026,18 @@
         <v>COGS</v>
       </c>
       <c r="D295" t="str">
-        <v>Guava</v>
+        <v>Milk/Conden</v>
       </c>
       <c r="E295" t="str">
-        <v>ฝรั่ง 1 ตะกร้า</v>
+        <v>นมข้นจืด 2,221</v>
       </c>
       <c r="F295">
-        <v>800</v>
+        <v>5020</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>19/06/2026</v>
+        <v>24/06/2026</v>
       </c>
       <c r="B296" t="str">
         <v>Jun26</v>
@@ -7046,18 +7046,18 @@
         <v>COGS</v>
       </c>
       <c r="D296" t="str">
-        <v>Coconut Water</v>
+        <v>Milk/Conden</v>
       </c>
       <c r="E296" t="str">
-        <v>น้ำมะพร้าว40ลิตร ลิตรละ45บาท</v>
+        <v>นมข้นจืด1ลัง</v>
       </c>
       <c r="F296">
-        <v>5700</v>
+        <v>600</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>19/06/2026</v>
+        <v>24/06/2026</v>
       </c>
       <c r="B297" t="str">
         <v>Jun26</v>
@@ -7066,18 +7066,18 @@
         <v>COGS</v>
       </c>
       <c r="D297" t="str">
-        <v>Packaging</v>
+        <v>Milk/Conden</v>
       </c>
       <c r="E297" t="str">
-        <v>น้ำยาล้างจาน 7 ถุง ผงซักฟอก 1</v>
+        <v>นมข้นหวาน1ลัง</v>
       </c>
       <c r="F297">
-        <v>149</v>
+        <v>840</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>21/06/2026</v>
+        <v>27/06/2026</v>
       </c>
       <c r="B298" t="str">
         <v>Jun26</v>
@@ -7086,18 +7086,18 @@
         <v>COGS</v>
       </c>
       <c r="D298" t="str">
-        <v>Watermelon</v>
+        <v>Packaging</v>
       </c>
       <c r="E298" t="str">
-        <v>15-6-2569 แตงโม 50บาท 50 ลูก ยอด 2,500</v>
+        <v>ถุงมือ20กล่อง 2589</v>
       </c>
       <c r="F298">
-        <v>6500</v>
+        <v>4598</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>22/06/2026</v>
+        <v>27/06/2026</v>
       </c>
       <c r="B299" t="str">
         <v>Jun26</v>
@@ -7106,38 +7106,38 @@
         <v>COGS</v>
       </c>
       <c r="D299" t="str">
-        <v>Pineapple</v>
+        <v>Packaging</v>
       </c>
       <c r="E299" t="str">
-        <v>สับปะรด 15 ลูก</v>
+        <v>หลอด 20 แพค</v>
       </c>
       <c r="F299">
-        <v>700</v>
+        <v>630</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>22/06/2026</v>
+        <v>27/06/2026</v>
       </c>
       <c r="B300" t="str">
         <v>Jun26</v>
       </c>
       <c r="C300" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D300" t="str">
-        <v>Mango</v>
+        <v>Other</v>
       </c>
       <c r="E300" t="str">
-        <v>มะม่วง 2 ลัง</v>
+        <v>Unknown</v>
       </c>
       <c r="F300">
-        <v>1632</v>
+        <v>317</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>22/06/2026</v>
+        <v>29/06/2026</v>
       </c>
       <c r="B301" t="str">
         <v>Jun26</v>
@@ -7146,18 +7146,18 @@
         <v>COGS</v>
       </c>
       <c r="D301" t="str">
-        <v>Transportation</v>
+        <v>Packaging</v>
       </c>
       <c r="E301" t="str">
-        <v>Lalamove</v>
+        <v>ฝาแก้วภูเขาไฟ 1ลัง(954) 10แถว(987) 5แถว(561)</v>
       </c>
       <c r="F301">
-        <v>2000</v>
+        <v>2502</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>22/06/2026</v>
+        <v>29/06/2026</v>
       </c>
       <c r="B302" t="str">
         <v>Jun26</v>
@@ -7166,18 +7166,18 @@
         <v>COGS</v>
       </c>
       <c r="D302" t="str">
-        <v>Apple</v>
+        <v>Packaging</v>
       </c>
       <c r="E302" t="str">
-        <v>แอพเปิ้ล 5 ลัง</v>
+        <v>แก้ว2ลัง 1468*2 2,936</v>
       </c>
       <c r="F302">
-        <v>1750</v>
+        <v>3498</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>22/06/2026</v>
+        <v>29/06/2026</v>
       </c>
       <c r="B303" t="str">
         <v>Jun26</v>
@@ -7186,38 +7186,338 @@
         <v>COGS</v>
       </c>
       <c r="D303" t="str">
-        <v>Pineapple</v>
+        <v>Packaging</v>
       </c>
       <c r="E303" t="str">
-        <v>สับปะรด 15 ลูก</v>
+        <v>ฝา8แถว</v>
       </c>
       <c r="F303">
-        <v>700</v>
+        <v>896</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>22/06/2026</v>
+        <v>29/06/2026</v>
       </c>
       <c r="B304" t="str">
         <v>Jun26</v>
       </c>
       <c r="C304" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D304" t="str">
+        <v>Other</v>
+      </c>
+      <c r="E304" t="str">
+        <v>สกัดเย็น1เครื่อง</v>
+      </c>
+      <c r="F304">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="str">
+        <v>29/06/2026</v>
+      </c>
+      <c r="B305" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C305" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D305" t="str">
         <v>Guava</v>
       </c>
-      <c r="E304" t="str">
-        <v>ฝรั่ง 1 ลัง</v>
-      </c>
-      <c r="F304">
+      <c r="E305" t="str">
+        <v>ฝรั่ง 1 ตะกร้า</v>
+      </c>
+      <c r="F305">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="str">
+        <v>29/06/2026</v>
+      </c>
+      <c r="B306" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C306" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D306" t="str">
+        <v>Other</v>
+      </c>
+      <c r="E306" t="str">
+        <v>มังคุด 3 ตะกร้า</v>
+      </c>
+      <c r="F306">
+        <v>1932</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="str">
+        <v>29/06/2026</v>
+      </c>
+      <c r="B307" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C307" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D307" t="str">
+        <v>Apple</v>
+      </c>
+      <c r="E307" t="str">
+        <v>Apple 2 box</v>
+      </c>
+      <c r="F307">
         <v>700</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="str">
+        <v>29/06/2026</v>
+      </c>
+      <c r="B308" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C308" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D308" t="str">
+        <v>Pineapple</v>
+      </c>
+      <c r="E308" t="str">
+        <v>สับปะรด 15 ลูก</v>
+      </c>
+      <c r="F308">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="str">
+        <v>18/06/2026</v>
+      </c>
+      <c r="B309" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C309" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D309" t="str">
+        <v>Orange</v>
+      </c>
+      <c r="E309" t="str">
+        <v>รอบ 18/06/69</v>
+      </c>
+      <c r="F309">
+        <v>17815</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="str">
+        <v>30/06/2026</v>
+      </c>
+      <c r="B310" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C310" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D310" t="str">
+        <v>Salary</v>
+      </c>
+      <c r="E310" t="str">
+        <v>ค่าแรง 2 คน คนละ 12000 (B1 portion, split from joint payroll transfer ฿48,400 - see B2 for other portion + ฿400 day-rate)</v>
+      </c>
+      <c r="F310">
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="str">
+        <v>25/05/2026</v>
+      </c>
+      <c r="B311" t="str">
+        <v>May26</v>
+      </c>
+      <c r="C311" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D311" t="str">
+        <v>Watermelon</v>
+      </c>
+      <c r="E311" t="str">
+        <v>แตงโม 80 ลูก (split from 02/06 batch slip)</v>
+      </c>
+      <c r="F311">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="str">
+        <v>30/05/2026</v>
+      </c>
+      <c r="B312" t="str">
+        <v>May26</v>
+      </c>
+      <c r="C312" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D312" t="str">
+        <v>Watermelon</v>
+      </c>
+      <c r="E312" t="str">
+        <v>แตงโม 80 ลูก (split from 02/06 batch slip)</v>
+      </c>
+      <c r="F312">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="str">
+        <v>02/06/2026</v>
+      </c>
+      <c r="B313" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C313" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D313" t="str">
+        <v>Watermelon</v>
+      </c>
+      <c r="E313" t="str">
+        <v>แตงโม 50 ลูก (split from 05/06 batch slip)</v>
+      </c>
+      <c r="F313">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="str">
+        <v>04/06/2026</v>
+      </c>
+      <c r="B314" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C314" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D314" t="str">
+        <v>Watermelon</v>
+      </c>
+      <c r="E314" t="str">
+        <v>แตงโม 50 ลูก (split from 05/06 batch slip)</v>
+      </c>
+      <c r="F314">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="str">
+        <v>07/06/2026</v>
+      </c>
+      <c r="B315" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C315" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D315" t="str">
+        <v>Watermelon</v>
+      </c>
+      <c r="E315" t="str">
+        <v>แตงโม 45 ลูก (split from 14/06 batch slip)</v>
+      </c>
+      <c r="F315">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="str">
+        <v>12/06/2026</v>
+      </c>
+      <c r="B316" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C316" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D316" t="str">
+        <v>Watermelon</v>
+      </c>
+      <c r="E316" t="str">
+        <v>แตงโม 45 ลูก (split from 14/06 batch slip)</v>
+      </c>
+      <c r="F316">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="str">
+        <v>22/06/2026</v>
+      </c>
+      <c r="B317" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C317" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D317" t="str">
+        <v>Watermelon</v>
+      </c>
+      <c r="E317" t="str">
+        <v>แตงโม 30 ลูก (split from 25/06 batch slip)</v>
+      </c>
+      <c r="F317">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="str">
+        <v>25/06/2026</v>
+      </c>
+      <c r="B318" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C318" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D318" t="str">
+        <v>Watermelon</v>
+      </c>
+      <c r="E318" t="str">
+        <v>แตงโม 40 ลูก (split from 25/06 batch slip)</v>
+      </c>
+      <c r="F318">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="str">
+        <v>06/07/2026</v>
+      </c>
+      <c r="B319" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C319" t="str">
+        <v>PENDING_REFUND</v>
+      </c>
+      <c r="D319" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="E319" t="str">
+        <v>ค่าเช่าสต็อค เดือน June (b1) - DUPLICATE payment, pending refund (ref 016187141602BOR05219)</v>
+      </c>
+      <c r="F319">
+        <v>12000</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F304"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F319"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -19158,7 +19458,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AD25"/>
+  <dimension ref="A1:AD35"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -21097,45 +21397,137 @@
         <v>0</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>21/06/2026</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Sun</v>
+      </c>
+      <c r="C23">
+        <v>8680</v>
+      </c>
+      <c r="D23">
+        <v>5600</v>
+      </c>
+      <c r="E23">
+        <v>120</v>
+      </c>
+      <c r="F23">
+        <v>5480</v>
+      </c>
+      <c r="G23">
+        <v>3080</v>
+      </c>
+      <c r="H23">
+        <v>47</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>58</v>
+      </c>
+      <c r="K23">
+        <v>7</v>
+      </c>
+      <c r="L23">
+        <v>14</v>
+      </c>
+      <c r="M23">
+        <v>10</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>136</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>1.5</v>
+      </c>
+      <c r="U23">
+        <v>8</v>
+      </c>
+      <c r="V23">
+        <v>14</v>
+      </c>
+      <c r="W23">
+        <v>1.5</v>
+      </c>
+      <c r="X23">
+        <v>1.5</v>
+      </c>
+      <c r="Y23">
+        <v>1</v>
+      </c>
+      <c r="Z23">
+        <v>1</v>
+      </c>
+      <c r="AA23">
+        <v>20</v>
+      </c>
+      <c r="AB23">
+        <v>0</v>
+      </c>
+      <c r="AC23">
+        <v>0</v>
+      </c>
+      <c r="AD23">
+        <v>0</v>
+      </c>
+    </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>TOTAL</v>
+        <v>22/06/2026</v>
       </c>
       <c r="B24" t="str">
-        <v>20 days</v>
+        <v>Mon</v>
       </c>
       <c r="C24">
-        <v>124150</v>
+        <v>8030</v>
       </c>
       <c r="D24">
-        <v>67420</v>
+        <v>4910</v>
       </c>
       <c r="E24">
-        <v>2290</v>
+        <v>120</v>
       </c>
       <c r="F24">
-        <v>65130</v>
+        <v>4790</v>
       </c>
       <c r="G24">
-        <v>56730</v>
+        <v>3120</v>
       </c>
       <c r="H24">
-        <v>731</v>
+        <v>43</v>
       </c>
       <c r="I24">
         <v>0</v>
       </c>
       <c r="J24">
-        <v>779</v>
+        <v>59</v>
       </c>
       <c r="K24">
-        <v>96</v>
+        <v>9</v>
       </c>
       <c r="L24">
-        <v>339</v>
+        <v>14</v>
       </c>
       <c r="M24">
-        <v>205</v>
+        <v>7</v>
       </c>
       <c r="N24">
         <v>0</v>
@@ -21147,37 +21539,37 @@
         <v>0</v>
       </c>
       <c r="Q24">
-        <v>2150</v>
+        <v>132</v>
       </c>
       <c r="R24">
         <v>0</v>
       </c>
       <c r="S24">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="T24">
-        <v>32.5</v>
+        <v>2</v>
       </c>
       <c r="U24">
-        <v>150</v>
+        <v>11</v>
       </c>
       <c r="V24">
-        <v>148</v>
+        <v>16</v>
       </c>
       <c r="W24">
-        <v>32.5</v>
+        <v>1</v>
       </c>
       <c r="X24">
-        <v>32.5</v>
+        <v>1</v>
       </c>
       <c r="Y24">
-        <v>14.5</v>
+        <v>1</v>
       </c>
       <c r="Z24">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="AA24">
-        <v>347</v>
+        <v>14</v>
       </c>
       <c r="AB24">
         <v>0</v>
@@ -21191,96 +21583,924 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
+        <v>23/06/2026</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Tue</v>
+      </c>
+      <c r="C25">
+        <v>7800</v>
+      </c>
+      <c r="D25">
+        <v>3760</v>
+      </c>
+      <c r="E25">
+        <v>120</v>
+      </c>
+      <c r="F25">
+        <v>3640</v>
+      </c>
+      <c r="G25">
+        <v>4040</v>
+      </c>
+      <c r="H25">
+        <v>43</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>55</v>
+      </c>
+      <c r="K25">
+        <v>2</v>
+      </c>
+      <c r="L25">
+        <v>19</v>
+      </c>
+      <c r="M25">
+        <v>10</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>129</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>2</v>
+      </c>
+      <c r="U25">
+        <v>7</v>
+      </c>
+      <c r="V25">
+        <v>4</v>
+      </c>
+      <c r="W25">
+        <v>1</v>
+      </c>
+      <c r="X25">
+        <v>1</v>
+      </c>
+      <c r="Y25">
+        <v>1</v>
+      </c>
+      <c r="Z25">
+        <v>1</v>
+      </c>
+      <c r="AA25">
+        <v>20</v>
+      </c>
+      <c r="AB25">
+        <v>0</v>
+      </c>
+      <c r="AC25">
+        <v>0</v>
+      </c>
+      <c r="AD25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>24/06/2026</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Wed</v>
+      </c>
+      <c r="C26">
+        <v>5670</v>
+      </c>
+      <c r="D26">
+        <v>3820</v>
+      </c>
+      <c r="E26">
+        <v>120</v>
+      </c>
+      <c r="F26">
+        <v>3700</v>
+      </c>
+      <c r="G26">
+        <v>1850</v>
+      </c>
+      <c r="H26">
+        <v>25</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>46</v>
+      </c>
+      <c r="K26">
+        <v>2</v>
+      </c>
+      <c r="L26">
+        <v>16</v>
+      </c>
+      <c r="M26">
+        <v>8</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <v>97</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>1</v>
+      </c>
+      <c r="U26">
+        <v>8</v>
+      </c>
+      <c r="V26">
+        <v>1</v>
+      </c>
+      <c r="W26">
+        <v>1</v>
+      </c>
+      <c r="X26">
+        <v>1</v>
+      </c>
+      <c r="Y26">
+        <v>1</v>
+      </c>
+      <c r="Z26">
+        <v>1</v>
+      </c>
+      <c r="AA26">
+        <v>16</v>
+      </c>
+      <c r="AB26">
+        <v>0</v>
+      </c>
+      <c r="AC26">
+        <v>0</v>
+      </c>
+      <c r="AD26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>25/06/2026</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Thu</v>
+      </c>
+      <c r="C27">
+        <v>3850</v>
+      </c>
+      <c r="D27">
+        <v>1310</v>
+      </c>
+      <c r="E27">
+        <v>60</v>
+      </c>
+      <c r="F27">
+        <v>1250</v>
+      </c>
+      <c r="G27">
+        <v>2540</v>
+      </c>
+      <c r="H27">
+        <v>23</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>28</v>
+      </c>
+      <c r="K27">
+        <v>2</v>
+      </c>
+      <c r="L27">
+        <v>6</v>
+      </c>
+      <c r="M27">
+        <v>5</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>64</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>1</v>
+      </c>
+      <c r="U27">
+        <v>4</v>
+      </c>
+      <c r="V27">
+        <v>2</v>
+      </c>
+      <c r="W27">
+        <v>0.5</v>
+      </c>
+      <c r="X27">
+        <v>0.5</v>
+      </c>
+      <c r="Y27">
+        <v>0.5</v>
+      </c>
+      <c r="Z27">
+        <v>0.5</v>
+      </c>
+      <c r="AA27">
+        <v>8</v>
+      </c>
+      <c r="AB27">
+        <v>0</v>
+      </c>
+      <c r="AC27">
+        <v>0</v>
+      </c>
+      <c r="AD27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>26/06/2026</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Fri</v>
+      </c>
+      <c r="C28">
+        <v>5860</v>
+      </c>
+      <c r="D28">
+        <v>2720</v>
+      </c>
+      <c r="E28">
+        <v>120</v>
+      </c>
+      <c r="F28">
+        <v>2600</v>
+      </c>
+      <c r="G28">
+        <v>3140</v>
+      </c>
+      <c r="H28">
+        <v>21</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>50</v>
+      </c>
+      <c r="K28">
+        <v>7</v>
+      </c>
+      <c r="L28">
+        <v>9</v>
+      </c>
+      <c r="M28">
+        <v>10</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>97</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>1</v>
+      </c>
+      <c r="U28">
+        <v>6</v>
+      </c>
+      <c r="V28">
+        <v>14</v>
+      </c>
+      <c r="W28">
+        <v>1.5</v>
+      </c>
+      <c r="X28">
+        <v>1.5</v>
+      </c>
+      <c r="Y28">
+        <v>0.5</v>
+      </c>
+      <c r="Z28">
+        <v>0.5</v>
+      </c>
+      <c r="AA28">
+        <v>20</v>
+      </c>
+      <c r="AB28">
+        <v>0</v>
+      </c>
+      <c r="AC28">
+        <v>0</v>
+      </c>
+      <c r="AD28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>27/06/2026</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Sat</v>
+      </c>
+      <c r="C29">
+        <v>10680</v>
+      </c>
+      <c r="D29">
+        <v>6430</v>
+      </c>
+      <c r="E29">
+        <v>120</v>
+      </c>
+      <c r="F29">
+        <v>6310</v>
+      </c>
+      <c r="G29">
+        <v>4250</v>
+      </c>
+      <c r="H29">
+        <v>51</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>75</v>
+      </c>
+      <c r="K29">
+        <v>8</v>
+      </c>
+      <c r="L29">
+        <v>28</v>
+      </c>
+      <c r="M29">
+        <v>14</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <v>176</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>2</v>
+      </c>
+      <c r="U29">
+        <v>9</v>
+      </c>
+      <c r="V29">
+        <v>16</v>
+      </c>
+      <c r="W29">
+        <v>2.5</v>
+      </c>
+      <c r="X29">
+        <v>2</v>
+      </c>
+      <c r="Y29">
+        <v>1.5</v>
+      </c>
+      <c r="Z29">
+        <v>1.5</v>
+      </c>
+      <c r="AA29">
+        <v>28</v>
+      </c>
+      <c r="AB29">
+        <v>0</v>
+      </c>
+      <c r="AC29">
+        <v>0</v>
+      </c>
+      <c r="AD29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>28/06/2026</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Sun</v>
+      </c>
+      <c r="C30">
+        <v>6420</v>
+      </c>
+      <c r="D30">
+        <v>2310</v>
+      </c>
+      <c r="E30">
+        <v>120</v>
+      </c>
+      <c r="F30">
+        <v>2190</v>
+      </c>
+      <c r="G30">
+        <v>4110</v>
+      </c>
+      <c r="H30">
+        <v>30</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>51</v>
+      </c>
+      <c r="K30">
+        <v>7</v>
+      </c>
+      <c r="L30">
+        <v>11</v>
+      </c>
+      <c r="M30">
+        <v>6</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>0</v>
+      </c>
+      <c r="Q30">
+        <v>105</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <v>0.5</v>
+      </c>
+      <c r="U30">
+        <v>6</v>
+      </c>
+      <c r="V30">
+        <v>14</v>
+      </c>
+      <c r="W30">
+        <v>1.5</v>
+      </c>
+      <c r="X30">
+        <v>1.5</v>
+      </c>
+      <c r="Y30">
+        <v>1</v>
+      </c>
+      <c r="Z30">
+        <v>0.5</v>
+      </c>
+      <c r="AA30">
+        <v>12</v>
+      </c>
+      <c r="AB30">
+        <v>0</v>
+      </c>
+      <c r="AC30">
+        <v>0</v>
+      </c>
+      <c r="AD30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>29/06/2026</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Mon</v>
+      </c>
+      <c r="C31">
+        <v>3850</v>
+      </c>
+      <c r="D31">
+        <v>2080</v>
+      </c>
+      <c r="E31">
+        <v>60</v>
+      </c>
+      <c r="F31">
+        <v>2020</v>
+      </c>
+      <c r="G31">
+        <v>1770</v>
+      </c>
+      <c r="H31">
+        <v>14</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>27</v>
+      </c>
+      <c r="K31">
+        <v>6</v>
+      </c>
+      <c r="L31">
+        <v>13</v>
+      </c>
+      <c r="M31">
+        <v>4</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>0</v>
+      </c>
+      <c r="Q31">
+        <v>64</v>
+      </c>
+      <c r="R31">
+        <v>0</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="T31">
+        <v>1</v>
+      </c>
+      <c r="U31">
+        <v>2</v>
+      </c>
+      <c r="V31">
+        <v>6</v>
+      </c>
+      <c r="W31">
+        <v>1</v>
+      </c>
+      <c r="X31">
+        <v>0.5</v>
+      </c>
+      <c r="Y31">
+        <v>0.5</v>
+      </c>
+      <c r="Z31">
+        <v>0.5</v>
+      </c>
+      <c r="AA31">
+        <v>8</v>
+      </c>
+      <c r="AB31">
+        <v>0</v>
+      </c>
+      <c r="AC31">
+        <v>0</v>
+      </c>
+      <c r="AD31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>30/06/2026</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Tue</v>
+      </c>
+      <c r="C32">
+        <v>6730</v>
+      </c>
+      <c r="D32">
+        <v>4090</v>
+      </c>
+      <c r="E32">
+        <v>120</v>
+      </c>
+      <c r="F32">
+        <v>3970</v>
+      </c>
+      <c r="G32">
+        <v>2640</v>
+      </c>
+      <c r="H32">
+        <v>27</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>50</v>
+      </c>
+      <c r="K32">
+        <v>6</v>
+      </c>
+      <c r="L32">
+        <v>20</v>
+      </c>
+      <c r="M32">
+        <v>13</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>0</v>
+      </c>
+      <c r="Q32">
+        <v>116</v>
+      </c>
+      <c r="R32">
+        <v>0</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <v>1.5</v>
+      </c>
+      <c r="U32">
+        <v>7</v>
+      </c>
+      <c r="V32">
+        <v>6</v>
+      </c>
+      <c r="W32">
+        <v>1</v>
+      </c>
+      <c r="X32">
+        <v>1</v>
+      </c>
+      <c r="Y32">
+        <v>1</v>
+      </c>
+      <c r="Z32">
+        <v>1</v>
+      </c>
+      <c r="AA32">
+        <v>20</v>
+      </c>
+      <c r="AB32">
+        <v>0</v>
+      </c>
+      <c r="AC32">
+        <v>0</v>
+      </c>
+      <c r="AD32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>TOTAL</v>
+      </c>
+      <c r="B34" t="str">
+        <v>30 days</v>
+      </c>
+      <c r="C34">
+        <v>191720</v>
+      </c>
+      <c r="D34">
+        <v>104450</v>
+      </c>
+      <c r="E34">
+        <v>3370</v>
+      </c>
+      <c r="F34">
+        <v>101080</v>
+      </c>
+      <c r="G34">
+        <v>87270</v>
+      </c>
+      <c r="H34">
+        <v>1055</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>1278</v>
+      </c>
+      <c r="K34">
+        <v>152</v>
+      </c>
+      <c r="L34">
+        <v>489</v>
+      </c>
+      <c r="M34">
+        <v>292</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>0</v>
+      </c>
+      <c r="Q34">
+        <v>3266</v>
+      </c>
+      <c r="R34">
+        <v>0</v>
+      </c>
+      <c r="S34">
+        <v>8</v>
+      </c>
+      <c r="T34">
+        <v>46</v>
+      </c>
+      <c r="U34">
+        <v>218</v>
+      </c>
+      <c r="V34">
+        <v>241</v>
+      </c>
+      <c r="W34">
+        <v>45</v>
+      </c>
+      <c r="X34">
+        <v>44</v>
+      </c>
+      <c r="Y34">
+        <v>23.5</v>
+      </c>
+      <c r="Z34">
+        <v>31.5</v>
+      </c>
+      <c r="AA34">
+        <v>513</v>
+      </c>
+      <c r="AB34">
+        <v>0</v>
+      </c>
+      <c r="AC34">
+        <v>0</v>
+      </c>
+      <c r="AD34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
         <v>AVG/DAY</v>
       </c>
-      <c r="C25">
-        <v>6207.5</v>
-      </c>
-      <c r="D25">
-        <v>3371</v>
-      </c>
-      <c r="E25">
-        <v>114.5</v>
-      </c>
-      <c r="F25">
-        <v>3256.5</v>
-      </c>
-      <c r="G25">
-        <v>2836.5</v>
-      </c>
-      <c r="H25">
-        <v>36.55</v>
-      </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="J25">
-        <v>38.95</v>
-      </c>
-      <c r="K25">
-        <v>4.8</v>
-      </c>
-      <c r="L25">
-        <v>16.95</v>
-      </c>
-      <c r="M25">
-        <v>10.25</v>
-      </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
-      <c r="O25">
-        <v>0</v>
-      </c>
-      <c r="P25">
-        <v>0</v>
-      </c>
-      <c r="Q25">
-        <v>107.5</v>
-      </c>
-      <c r="R25">
-        <v>0</v>
-      </c>
-      <c r="S25">
-        <v>0.4</v>
-      </c>
-      <c r="T25">
-        <v>1.625</v>
-      </c>
-      <c r="U25">
-        <v>7.5</v>
-      </c>
-      <c r="V25">
-        <v>7.4</v>
-      </c>
-      <c r="W25">
-        <v>1.625</v>
-      </c>
-      <c r="X25">
-        <v>1.625</v>
-      </c>
-      <c r="Y25">
-        <v>0.725</v>
-      </c>
-      <c r="Z25">
-        <v>1.15</v>
-      </c>
-      <c r="AA25">
-        <v>17.35</v>
-      </c>
-      <c r="AB25">
-        <v>0</v>
-      </c>
-      <c r="AC25">
-        <v>0</v>
-      </c>
-      <c r="AD25">
+      <c r="C35">
+        <v>6390.666666666667</v>
+      </c>
+      <c r="D35">
+        <v>3481.6666666666665</v>
+      </c>
+      <c r="E35">
+        <v>112.33333333333333</v>
+      </c>
+      <c r="F35">
+        <v>3369.3333333333335</v>
+      </c>
+      <c r="G35">
+        <v>2909</v>
+      </c>
+      <c r="H35">
+        <v>35.166666666666664</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>42.6</v>
+      </c>
+      <c r="K35">
+        <v>5.066666666666666</v>
+      </c>
+      <c r="L35">
+        <v>16.3</v>
+      </c>
+      <c r="M35">
+        <v>9.733333333333333</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>0</v>
+      </c>
+      <c r="Q35">
+        <v>108.86666666666666</v>
+      </c>
+      <c r="R35">
+        <v>0</v>
+      </c>
+      <c r="S35">
+        <v>0.26666666666666666</v>
+      </c>
+      <c r="T35">
+        <v>1.5333333333333334</v>
+      </c>
+      <c r="U35">
+        <v>7.266666666666667</v>
+      </c>
+      <c r="V35">
+        <v>8.033333333333333</v>
+      </c>
+      <c r="W35">
+        <v>1.5</v>
+      </c>
+      <c r="X35">
+        <v>1.4666666666666666</v>
+      </c>
+      <c r="Y35">
+        <v>0.7833333333333333</v>
+      </c>
+      <c r="Z35">
+        <v>1.05</v>
+      </c>
+      <c r="AA35">
+        <v>17.1</v>
+      </c>
+      <c r="AB35">
+        <v>0</v>
+      </c>
+      <c r="AC35">
+        <v>0</v>
+      </c>
+      <c r="AD35">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AD25"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AD35"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/3_Automation_Dashboard/SomSaiJai_Dashboard_B1_2026.xlsx
+++ b/3_Automation_Dashboard/SomSaiJai_Dashboard_B1_2026.xlsx
@@ -1263,16 +1263,16 @@
         <v>Jan26</v>
       </c>
       <c r="C7" t="str">
-        <v>COGS</v>
+        <v>EXCLUDED</v>
       </c>
       <c r="D7" t="str">
-        <v>Ice</v>
+        <v>Profit Distribution</v>
       </c>
       <c r="E7" t="str">
-        <v>ส่วนแบ่ง60เปอ</v>
+        <v>ส่วนแบ่ง60เปอ — removed from P&amp;L, this is a partner profit-share payout, not a business expense (owner-confirmed)</v>
       </c>
       <c r="F7">
-        <v>47961</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1283,16 +1283,16 @@
         <v>Jan26</v>
       </c>
       <c r="C8" t="str">
-        <v>COGS</v>
+        <v>EXCLUDED</v>
       </c>
       <c r="D8" t="str">
-        <v>Ice</v>
+        <v>Profit Distribution</v>
       </c>
       <c r="E8" t="str">
-        <v>ค่าส่วนแบ่งกำไรเมน 40เปอ</v>
+        <v>ค่าส่วนแบ่งกำไรเมน 40เปอ — removed from P&amp;L, this is a partner profit-share payout, not a business expense (owner-confirmed)</v>
       </c>
       <c r="F8">
-        <v>32000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1486,7 +1486,7 @@
         <v>COGS</v>
       </c>
       <c r="D18" t="str">
-        <v>Ice</v>
+        <v>Transportation</v>
       </c>
       <c r="E18" t="str">
         <v>ค่าขนตะกร้ากลับ</v>
@@ -2343,10 +2343,10 @@
         <v>Feb26</v>
       </c>
       <c r="C61" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D61" t="str">
-        <v>Ice</v>
+        <v>Fixed Costs</v>
       </c>
       <c r="E61" t="str">
         <v>ค่าไฟเดือนมค</v>
@@ -2383,10 +2383,10 @@
         <v>Feb26</v>
       </c>
       <c r="C63" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D63" t="str">
-        <v>Other</v>
+        <v>Watermelon</v>
       </c>
       <c r="E63" t="str">
         <v>Unknown</v>
@@ -2406,7 +2406,7 @@
         <v>COGS</v>
       </c>
       <c r="D64" t="str">
-        <v>Ice</v>
+        <v>Apple</v>
       </c>
       <c r="E64" t="str">
         <v>Unknown</v>
@@ -2543,10 +2543,10 @@
         <v>Feb26</v>
       </c>
       <c r="C71" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D71" t="str">
-        <v>Ice</v>
+        <v>Other</v>
       </c>
       <c r="E71" t="str">
         <v>ผ้าปิดร้าน 218 ค่ารถ 198</v>
@@ -2923,10 +2923,10 @@
         <v>Mar26</v>
       </c>
       <c r="C90" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D90" t="str">
-        <v>Ice</v>
+        <v>Other</v>
       </c>
       <c r="E90" t="str">
         <v>ค่าทางด่วน</v>
@@ -3163,10 +3163,10 @@
         <v>Mar26</v>
       </c>
       <c r="C102" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D102" t="str">
-        <v>Ice</v>
+        <v>Other</v>
       </c>
       <c r="E102" t="str">
         <v>ค่าทางด่วน</v>
@@ -3203,10 +3203,10 @@
         <v>Mar26</v>
       </c>
       <c r="C104" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D104" t="str">
-        <v>Ice</v>
+        <v>Fixed Costs</v>
       </c>
       <c r="E104" t="str">
         <v>ค่าไฟเดือนกพ มีนา</v>
@@ -3243,10 +3243,10 @@
         <v>Mar26</v>
       </c>
       <c r="C106" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D106" t="str">
-        <v>Ice</v>
+        <v>Other</v>
       </c>
       <c r="E106" t="str">
         <v>สกรู กาวตะปู</v>
@@ -3303,10 +3303,10 @@
         <v>Mar26</v>
       </c>
       <c r="C109" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D109" t="str">
-        <v>Ice</v>
+        <v>Other</v>
       </c>
       <c r="E109" t="str">
         <v>รถเข็นของคันใหม่</v>
@@ -3626,7 +3626,7 @@
         <v>COGS</v>
       </c>
       <c r="D125" t="str">
-        <v>Ice</v>
+        <v>Water</v>
       </c>
       <c r="E125" t="str">
         <v>เนื้อ 1200 น้ำ 500</v>
@@ -3786,7 +3786,7 @@
         <v>COGS</v>
       </c>
       <c r="D133" t="str">
-        <v>Ice</v>
+        <v>Milk/Conden</v>
       </c>
       <c r="E133" t="str">
         <v>ค่านม</v>
@@ -3846,7 +3846,7 @@
         <v>COGS</v>
       </c>
       <c r="D136" t="str">
-        <v>Ice</v>
+        <v>Water</v>
       </c>
       <c r="E136" t="str">
         <v>น้ำ 500 เนื้อ 1200</v>
@@ -4246,7 +4246,7 @@
         <v>COGS</v>
       </c>
       <c r="D156" t="str">
-        <v>Ice</v>
+        <v>Water</v>
       </c>
       <c r="E156" t="str">
         <v>16/4/26 เนื้อ 10 น้ำ 10 21/4/26 เนื้อ 10</v>
@@ -4626,7 +4626,7 @@
         <v>COGS</v>
       </c>
       <c r="D175" t="str">
-        <v>Ice</v>
+        <v>Pineapple</v>
       </c>
       <c r="E175" t="str">
         <v>สับปะรส 3 ตะกร้า</v>
@@ -4686,7 +4686,7 @@
         <v>OPEX</v>
       </c>
       <c r="D178" t="str">
-        <v>Fixed Costs</v>
+        <v>Rental</v>
       </c>
       <c r="E178" t="str">
         <v>Rent</v>
@@ -4703,10 +4703,10 @@
         <v>Apr26</v>
       </c>
       <c r="C179" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D179" t="str">
-        <v>Investment</v>
+        <v>Stock</v>
       </c>
       <c r="E179" t="str">
         <v>Stock (Allocated 82.9%)</v>
@@ -4729,10 +4729,10 @@
         <v>Other</v>
       </c>
       <c r="E180" t="str">
-        <v>Pineapple</v>
+        <v>Pineapple (duplicate of 30/04/2026 slip entry, zeroed to avoid double-count)</v>
       </c>
       <c r="F180">
-        <v>1500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181">
@@ -4823,10 +4823,10 @@
         <v>May26</v>
       </c>
       <c r="C185" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D185" t="str">
-        <v>Ice</v>
+        <v>Other</v>
       </c>
       <c r="E185" t="str">
         <v>ค่าหาหมอเอ</v>
@@ -4843,10 +4843,10 @@
         <v>May26</v>
       </c>
       <c r="C186" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D186" t="str">
-        <v>Ice</v>
+        <v>Other</v>
       </c>
       <c r="E186" t="str">
         <v>ค่าหมอเอ</v>
@@ -4923,10 +4923,10 @@
         <v>May26</v>
       </c>
       <c r="C190" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D190" t="str">
-        <v>Other</v>
+        <v>Watermelon</v>
       </c>
       <c r="E190" t="str">
         <v>30-4-2569 เบอร์ 70฿ 60 ลูก</v>
@@ -5103,10 +5103,10 @@
         <v>May26</v>
       </c>
       <c r="C199" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D199" t="str">
-        <v>Other</v>
+        <v>Watermelon</v>
       </c>
       <c r="E199" t="str">
         <v>4-5-2569 เบอร์ 70฿ 60 ลูก ยอด 4,200</v>
@@ -5383,10 +5383,10 @@
         <v>May26</v>
       </c>
       <c r="C213" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D213" t="str">
-        <v>Other</v>
+        <v>Watermelon</v>
       </c>
       <c r="E213" t="str">
         <v>11-5-2569 50 ลูก ยอด 4,000</v>
@@ -5563,10 +5563,10 @@
         <v>May26</v>
       </c>
       <c r="C222" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D222" t="str">
-        <v>Other</v>
+        <v>Pineapple</v>
       </c>
       <c r="E222" t="str">
         <v>14/05/26 18 ลูก 504 บาท 16/05/26 18 ลูก</v>
@@ -5743,10 +5743,10 @@
         <v>May26</v>
       </c>
       <c r="C231" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D231" t="str">
-        <v>Other</v>
+        <v>Watermelon</v>
       </c>
       <c r="E231" t="str">
         <v>16-5-2569ยอด 4,000฿</v>
@@ -6103,10 +6103,10 @@
         <v>May26</v>
       </c>
       <c r="C249" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D249" t="str">
-        <v>Other</v>
+        <v>Apple</v>
       </c>
       <c r="E249" t="str">
         <v>Unknown</v>
@@ -6143,10 +6143,10 @@
         <v>May26</v>
       </c>
       <c r="C251" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D251" t="str">
-        <v>Investment</v>
+        <v>Stock</v>
       </c>
       <c r="E251" t="str">
         <v>Stock Adjustment (Allocated to B2)</v>
@@ -7203,10 +7203,10 @@
         <v>Jun26</v>
       </c>
       <c r="C304" t="str">
-        <v>OPEX</v>
+        <v>CAPEX</v>
       </c>
       <c r="D304" t="str">
-        <v>Other</v>
+        <v>Investment</v>
       </c>
       <c r="E304" t="str">
         <v>สกัดเย็น1เครื่อง</v>
@@ -7243,7 +7243,7 @@
         <v>Jun26</v>
       </c>
       <c r="C306" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D306" t="str">
         <v>Other</v>

--- a/3_Automation_Dashboard/SomSaiJai_Dashboard_B1_2026.xlsx
+++ b/3_Automation_Dashboard/SomSaiJai_Dashboard_B1_2026.xlsx
@@ -1168,7 +1168,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F319"/>
+  <dimension ref="A1:F320"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6169,10 +6169,10 @@
         <v>Salary</v>
       </c>
       <c r="E252" t="str">
-        <v>Unknown</v>
+        <v>Aye 12,000 + Wai 12,000 (May salary, B1 portion split from joint ฿41,200 SCB transfer 01/06 - see cost_may26.md)</v>
       </c>
       <c r="F252">
-        <v>0</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="253">
@@ -7515,9 +7515,29 @@
         <v>12000</v>
       </c>
     </row>
+    <row r="320">
+      <c r="A320" t="str">
+        <v>20/03/2026</v>
+      </c>
+      <c r="B320" t="str">
+        <v>Mar26</v>
+      </c>
+      <c r="C320" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D320" t="str">
+        <v>Fixed Costs</v>
+      </c>
+      <c r="E320" t="str">
+        <v>ค่าน้ำประปา เดือน 03/69 (MWA water bill, was never ingested by OCR pipeline)</v>
+      </c>
+      <c r="F320">
+        <v>449.25</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F319"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F320"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/3_Automation_Dashboard/SomSaiJai_Dashboard_B1_2026.xlsx
+++ b/3_Automation_Dashboard/SomSaiJai_Dashboard_B1_2026.xlsx
@@ -1168,7 +1168,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F320"/>
+  <dimension ref="A1:F321"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3546,7 +3546,7 @@
         <v>COGS</v>
       </c>
       <c r="D121" t="str">
-        <v>Ice</v>
+        <v>Orange</v>
       </c>
       <c r="E121" t="str">
         <v>Unknown</v>
@@ -4286,7 +4286,7 @@
         <v>COGS</v>
       </c>
       <c r="D158" t="str">
-        <v>Packaging</v>
+        <v>Other</v>
       </c>
       <c r="E158" t="str">
         <v>บาร์เลย 4 ถั่วแดง 3 ถุงละ 60</v>
@@ -5066,7 +5066,7 @@
         <v>COGS</v>
       </c>
       <c r="D197" t="str">
-        <v>Packaging</v>
+        <v>Water</v>
       </c>
       <c r="E197" t="str">
         <v>6 พ.ค. น้ำ 30 ขวด 1500 บาท เนื้อ 11 โล 1320 บาท</v>
@@ -5149,10 +5149,10 @@
         <v>Milk/Conden</v>
       </c>
       <c r="E201" t="str">
-        <v>นมข้นจืด 1ลัง 636</v>
+        <v>นมข้นจืด 1ลัง (drawer portion split out below)</v>
       </c>
       <c r="F201">
-        <v>1122</v>
+        <v>636</v>
       </c>
     </row>
     <row r="202">
@@ -5166,7 +5166,7 @@
         <v>COGS</v>
       </c>
       <c r="D202" t="str">
-        <v>Packaging</v>
+        <v>Milk/Conden</v>
       </c>
       <c r="E202" t="str">
         <v>นมข้น 3 ลัง 2568</v>
@@ -5826,7 +5826,7 @@
         <v>COGS</v>
       </c>
       <c r="D235" t="str">
-        <v>Packaging</v>
+        <v>Milk/Conden</v>
       </c>
       <c r="E235" t="str">
         <v>ฝา1 788</v>
@@ -7535,9 +7535,29 @@
         <v>449.25</v>
       </c>
     </row>
+    <row r="321">
+      <c r="A321" t="str">
+        <v>09/05/2026</v>
+      </c>
+      <c r="B321" t="str">
+        <v>May26</v>
+      </c>
+      <c r="C321" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D321" t="str">
+        <v>Other</v>
+      </c>
+      <c r="E321" t="str">
+        <v>ลิ้นชักเก็บเงิน (cash register drawer, split from combined 09/05 milk+equipment slip)</v>
+      </c>
+      <c r="F321">
+        <v>486</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F320"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F321"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/3_Automation_Dashboard/SomSaiJai_Dashboard_B1_2026.xlsx
+++ b/3_Automation_Dashboard/SomSaiJai_Dashboard_B1_2026.xlsx
@@ -1168,7 +1168,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F321"/>
+  <dimension ref="A1:F323"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2243,10 +2243,10 @@
         <v>Feb26</v>
       </c>
       <c r="C56" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D56" t="str">
-        <v>Ice</v>
+        <v>Other</v>
       </c>
       <c r="E56" t="str">
         <v>Unknown</v>
@@ -3686,7 +3686,7 @@
         <v>COGS</v>
       </c>
       <c r="D128" t="str">
-        <v>Ice</v>
+        <v>Watermelon</v>
       </c>
       <c r="E128" t="str">
         <v>4/4/68 40 ลูก</v>
@@ -4003,10 +4003,10 @@
         <v>Apr26</v>
       </c>
       <c r="C144" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D144" t="str">
-        <v>Other</v>
+        <v>Watermelon</v>
       </c>
       <c r="E144" t="str">
         <v>16/4/2569</v>
@@ -4283,16 +4283,16 @@
         <v>Apr26</v>
       </c>
       <c r="C158" t="str">
-        <v>COGS</v>
+        <v>EXCLUDED</v>
       </c>
       <c r="D158" t="str">
-        <v>Other</v>
+        <v>Removed</v>
       </c>
       <c r="E158" t="str">
-        <v>บาร์เลย 4 ถั่วแดง 3 ถุงละ 60</v>
+        <v>บาร์เลย 4 ถั่วแดง 3 ถุงละ 60 (removed at owner request)</v>
       </c>
       <c r="F158">
-        <v>420</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
@@ -4426,7 +4426,7 @@
         <v>COGS</v>
       </c>
       <c r="D165" t="str">
-        <v>Ice</v>
+        <v>Watermelon</v>
       </c>
       <c r="E165" t="str">
         <v>26/4/26 50 ลูก</v>
@@ -4749,10 +4749,10 @@
         <v>Guava</v>
       </c>
       <c r="E181" t="str">
-        <v>ร่ม 1176 ร่ม 843 ฝรั่ง 300 นมข้นจืด 785 ที่ปั้ม 176</v>
+        <v>ร่ม 1176 ร่ม 843 ฝรั่ง 300 นมข้นจืด 785 ที่ปั้ม 176 (Guava portion only)</v>
       </c>
       <c r="F181">
-        <v>7823</v>
+        <v>700</v>
       </c>
     </row>
     <row r="182">
@@ -5026,7 +5026,7 @@
         <v>COGS</v>
       </c>
       <c r="D195" t="str">
-        <v>Transportation</v>
+        <v>Coconut Water</v>
       </c>
       <c r="E195" t="str">
         <v>น้ำ 20 ขวด 900 ถอดเสื้อ 30 ลูก750 กล่องโฟม 3</v>
@@ -5066,7 +5066,7 @@
         <v>COGS</v>
       </c>
       <c r="D197" t="str">
-        <v>Water</v>
+        <v>Coconut Water</v>
       </c>
       <c r="E197" t="str">
         <v>6 พ.ค. น้ำ 30 ขวด 1500 บาท เนื้อ 11 โล 1320 บาท</v>
@@ -5523,16 +5523,16 @@
         <v>May26</v>
       </c>
       <c r="C220" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D220" t="str">
-        <v>Ice</v>
+        <v>Other</v>
       </c>
       <c r="E220" t="str">
-        <v>Police fees -2000 2 head</v>
+        <v>Police fees (portion of mixed 16/05 slip)</v>
       </c>
       <c r="F220">
-        <v>4290</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="221">
@@ -7555,9 +7555,49 @@
         <v>486</v>
       </c>
     </row>
+    <row r="322">
+      <c r="A322" t="str">
+        <v>01/05/2026</v>
+      </c>
+      <c r="B322" t="str">
+        <v>May26</v>
+      </c>
+      <c r="C322" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D322" t="str">
+        <v>Other</v>
+      </c>
+      <c r="E322" t="str">
+        <v>ร่ม+นมข้นจืด+ที่ปั้ม+ปืนฉีดน้ำ (remainder of mixed 01/05 slip, non-guava portion)</v>
+      </c>
+      <c r="F322">
+        <v>7123</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="str">
+        <v>16/05/2026</v>
+      </c>
+      <c r="B323" t="str">
+        <v>May26</v>
+      </c>
+      <c r="C323" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D323" t="str">
+        <v>Coconut</v>
+      </c>
+      <c r="E323" t="str">
+        <v>Coconut meat + water + apple (remainder of mixed 16/05 slip, non-police-fee portion)</v>
+      </c>
+      <c r="F323">
+        <v>2290</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F321"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F323"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/3_Automation_Dashboard/SomSaiJai_Dashboard_B1_2026.xlsx
+++ b/3_Automation_Dashboard/SomSaiJai_Dashboard_B1_2026.xlsx
@@ -1168,7 +1168,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F455"/>
+  <dimension ref="A1:F463"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6466,13 +6466,13 @@
         <v>COGS</v>
       </c>
       <c r="D267" t="str">
-        <v>Pineapple</v>
+        <v>Watermelon</v>
       </c>
       <c r="E267" t="str">
-        <v>Watermelon 750+pineapple - 750</v>
+        <v>สลิปรวม: แตงโม 750 (audit fix, was bundled into Pineapple line)</v>
       </c>
       <c r="F267">
-        <v>5750</v>
+        <v>750</v>
       </c>
     </row>
     <row r="268">
@@ -7809,15 +7809,15 @@
         <v>Mango</v>
       </c>
       <c r="E334" t="str">
-        <v>Cogs มะม่วง 3 ลัง 3900 และ งบลงทุน 810 (LINE_ALBUM_Cost July_260802_8.jpg)</v>
+        <v>มะม่วง 3 ลัง 3900 (LINE_ALBUM_Cost July_260802_8.jpg)</v>
       </c>
       <c r="F334">
-        <v>4710</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>26/07/2026</v>
+        <v>27/07/2026</v>
       </c>
       <c r="B335" t="str">
         <v>Jul26</v>
@@ -7829,10 +7829,10 @@
         <v>Coconut</v>
       </c>
       <c r="E335" t="str">
-        <v>น้ำมะพร้าว 30ลิตร 1350 เนื้อ 50kg 5000 ค่าส่ง 350 (LINE_ALBUM_Cost July_260802_9.jpg)</v>
+        <v>น้ำมะพร้าว 30ลิตร 1350 เนื้อ 50kg 5000 น้ำมะพร้าวขวด 920 ค่าส่ง 350 (LINE_ALBUM_Cost July_260802_14.jpg, audit fix - was dated 26/07 citing wrong image, missing ฿920 bottles line)</v>
       </c>
       <c r="F335">
-        <v>6700</v>
+        <v>7620</v>
       </c>
     </row>
     <row r="336">
@@ -7969,10 +7969,10 @@
         <v>Apple</v>
       </c>
       <c r="E342" t="str">
-        <v>แอปเปิ้ล 4 ลัง (LINE_ALBUM_Cost July_260802_16.jpg)</v>
+        <v>แอปเปิ้ล 5 ลัง (LINE_ALBUM_Cost July_260802_16.jpg, audit fix - was recorded as 4 ลัง/฿1600)</v>
       </c>
       <c r="F342">
-        <v>1600</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="343">
@@ -9943,13 +9943,13 @@
         <v>Jul26</v>
       </c>
       <c r="C441" t="str">
-        <v>COGS</v>
+        <v>CAPEX</v>
       </c>
       <c r="D441" t="str">
-        <v>Packaging</v>
+        <v>Investment</v>
       </c>
       <c r="E441" t="str">
-        <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
+        <v>เครื่องสกัดเย็น 1 เครื่อง (Shopee, audit fix - was COGS/Packaging)</v>
       </c>
       <c r="F441">
         <v>1015</v>
@@ -9963,13 +9963,13 @@
         <v>Jul26</v>
       </c>
       <c r="C442" t="str">
-        <v>COGS</v>
+        <v>CAPEX</v>
       </c>
       <c r="D442" t="str">
-        <v>Packaging</v>
+        <v>Investment</v>
       </c>
       <c r="E442" t="str">
-        <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
+        <v>เครื่องสกัดเย็น 1 เครื่อง (Shopee, audit fix - was COGS/Packaging)</v>
       </c>
       <c r="F442">
         <v>1087</v>
@@ -10235,9 +10235,169 @@
         <v>198</v>
       </c>
     </row>
+    <row r="456">
+      <c r="A456" t="str">
+        <v>04/06/2026</v>
+      </c>
+      <c r="B456" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C456" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D456" t="str">
+        <v>Pineapple</v>
+      </c>
+      <c r="E456" t="str">
+        <v>สลิปรวม: สับปะรด 750 (audit fix, was bundled)</v>
+      </c>
+      <c r="F456">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="str">
+        <v>04/06/2026</v>
+      </c>
+      <c r="B457" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C457" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D457" t="str">
+        <v>Orange</v>
+      </c>
+      <c r="E457" t="str">
+        <v>สลิปรวม: ส้ม 2250 (audit fix, was bundled into Pineapple line)</v>
+      </c>
+      <c r="F457">
+        <v>2250</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="str">
+        <v>04/06/2026</v>
+      </c>
+      <c r="B458" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C458" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D458" t="str">
+        <v>Other</v>
+      </c>
+      <c r="E458" t="str">
+        <v>ค่าปรับตำรวจ 2 คน (police fee, audit fix - was miscategorized as COGS/Pineapple)</v>
+      </c>
+      <c r="F458">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="str">
+        <v>26/07/2026</v>
+      </c>
+      <c r="B459" t="str">
+        <v>Jul26</v>
+      </c>
+      <c r="C459" t="str">
+        <v>CAPEX</v>
+      </c>
+      <c r="D459" t="str">
+        <v>Investment</v>
+      </c>
+      <c r="E459" t="str">
+        <v>งบลงทุน - ทดลองอื่นๆ (LINE_ALBUM_Cost July_260802_8.jpg, audit fix - was bundled into COGS/Mango)</v>
+      </c>
+      <c r="F459">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="str">
+        <v>26/07/2026</v>
+      </c>
+      <c r="B460" t="str">
+        <v>Jul26</v>
+      </c>
+      <c r="C460" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D460" t="str">
+        <v>Other</v>
+      </c>
+      <c r="E460" t="str">
+        <v>ค่าส่งของ (LINE_ALBUM_Cost July_260802_11.jpg, audit fix - missing entry)</v>
+      </c>
+      <c r="F460">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="str">
+        <v>28/07/2026</v>
+      </c>
+      <c r="B461" t="str">
+        <v>Jul26</v>
+      </c>
+      <c r="C461" t="str">
+        <v>COGS</v>
+      </c>
+      <c r="D461" t="str">
+        <v>Pineapple</v>
+      </c>
+      <c r="E461" t="str">
+        <v>สับปะรด 30 ลูก (LINE_ALBUM_Cost July_260802_17.jpg, audit fix - missing entry)</v>
+      </c>
+      <c r="F461">
+        <v>1188</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="str">
+        <v>28/07/2026</v>
+      </c>
+      <c r="B462" t="str">
+        <v>Jul26</v>
+      </c>
+      <c r="C462" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D462" t="str">
+        <v>Other</v>
+      </c>
+      <c r="E462" t="str">
+        <v>ค่าขนส่ง (LINE_ALBUM_Cost July_260802_19.jpg, audit fix - missing entry)</v>
+      </c>
+      <c r="F462">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="str">
+        <v>31/07/2026</v>
+      </c>
+      <c r="B463" t="str">
+        <v>Jul26</v>
+      </c>
+      <c r="C463" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D463" t="str">
+        <v>Other</v>
+      </c>
+      <c r="E463" t="str">
+        <v>Lalamove (LINE_ALBUM_Cost July_260802_25.jpg, audit fix - missing entry)</v>
+      </c>
+      <c r="F463">
+        <v>2000</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F455"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F463"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/3_Automation_Dashboard/SomSaiJai_Dashboard_B1_2026.xlsx
+++ b/3_Automation_Dashboard/SomSaiJai_Dashboard_B1_2026.xlsx
@@ -1168,7 +1168,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F463"/>
+  <dimension ref="A1:F464"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -10395,9 +10395,29 @@
         <v>2000</v>
       </c>
     </row>
+    <row r="464">
+      <c r="A464" t="str">
+        <v>30/04/2026</v>
+      </c>
+      <c r="B464" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C464" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D464" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="E464" t="str">
+        <v>ค่าเช่า stock เม.ย. (B1 ครึ่งหนึ่ง)</v>
+      </c>
+      <c r="F464">
+        <v>6000</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F463"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F464"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/3_Automation_Dashboard/SomSaiJai_Dashboard_B1_2026.xlsx
+++ b/3_Automation_Dashboard/SomSaiJai_Dashboard_B1_2026.xlsx
@@ -1168,7 +1168,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F464"/>
+  <dimension ref="A1:F465"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -10415,9 +10415,29 @@
         <v>6000</v>
       </c>
     </row>
+    <row r="465">
+      <c r="A465" t="str">
+        <v>05/03/2026</v>
+      </c>
+      <c r="B465" t="str">
+        <v>Mar26</v>
+      </c>
+      <c r="C465" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D465" t="str">
+        <v>Salary</v>
+      </c>
+      <c r="E465" t="str">
+        <v>เงินเดือนเมน 3/26</v>
+      </c>
+      <c r="F465">
+        <v>19000</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F464"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F465"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/3_Automation_Dashboard/SomSaiJai_Dashboard_B1_2026.xlsx
+++ b/3_Automation_Dashboard/SomSaiJai_Dashboard_B1_2026.xlsx
@@ -1168,7 +1168,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F465"/>
+  <dimension ref="A1:F468"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -10435,9 +10435,69 @@
         <v>19000</v>
       </c>
     </row>
+    <row r="466">
+      <c r="A466" t="str">
+        <v>27/02/2026</v>
+      </c>
+      <c r="B466" t="str">
+        <v>Feb26</v>
+      </c>
+      <c r="C466" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D466" t="str">
+        <v>Investment</v>
+      </c>
+      <c r="E466" t="str">
+        <v>อุปกรณ์ (จากสลิปโอนผู้จัดการ)</v>
+      </c>
+      <c r="F466">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="str">
+        <v>18/03/2026</v>
+      </c>
+      <c r="B467" t="str">
+        <v>Mar26</v>
+      </c>
+      <c r="C467" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D467" t="str">
+        <v>Milk/Conden</v>
+      </c>
+      <c r="E467" t="str">
+        <v>นม + นมข้นหวาน (จากสลิปโอนผู้จัดการ)</v>
+      </c>
+      <c r="F467">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="str">
+        <v>01/04/2026</v>
+      </c>
+      <c r="B468" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C468" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D468" t="str">
+        <v>Salary</v>
+      </c>
+      <c r="E468" t="str">
+        <v>เงินเดือนพนักงาน 3 คน มี.ค. 26</v>
+      </c>
+      <c r="F468">
+        <v>24600</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F465"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F468"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/3_Automation_Dashboard/SomSaiJai_Dashboard_B1_2026.xlsx
+++ b/3_Automation_Dashboard/SomSaiJai_Dashboard_B1_2026.xlsx
@@ -4846,13 +4846,13 @@
         <v>COGS</v>
       </c>
       <c r="D186" t="str">
-        <v>Other</v>
+        <v>Guava</v>
       </c>
       <c r="E186" t="str">
-        <v>Pineapple (duplicate of 30/04/2026 slip entry, zeroed to avoid double-count)</v>
+        <v>ฝรั่ง ตะกร้าแรก (นาง ประนอม, BBL X8148) [bank 30/04 22:50]</v>
       </c>
       <c r="F186">
-        <v>0</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="187">
@@ -7563,16 +7563,16 @@
         <v>Jun26</v>
       </c>
       <c r="C322" t="str">
-        <v>COGS</v>
+        <v>EXCLUDED</v>
       </c>
       <c r="D322" t="str">
-        <v>Mangosteen</v>
+        <v>Pass-Through</v>
       </c>
       <c r="E322" t="str">
-        <v>มังคุด 3 ตะกร้า</v>
+        <v>มังคุด 3 ตะกร้า (จ่ายแทน 1,932 แล้ว ฐนกร โอนคืน 29/06 13:56) - ไม่ใช่ต้นทุน SSJ [bank]</v>
       </c>
       <c r="F322">
-        <v>1932</v>
+        <v>0</v>
       </c>
     </row>
     <row r="323">
@@ -9323,16 +9323,16 @@
         <v>May26</v>
       </c>
       <c r="C410" t="str">
-        <v>COGS</v>
+        <v>EXCLUDED</v>
       </c>
       <c r="D410" t="str">
-        <v>Mangosteen</v>
+        <v>Pass-Through</v>
       </c>
       <c r="E410" t="str">
-        <v>มังคุด (โอน ฐนกร 23/05) [bank]</v>
+        <v>มังคุด (รับเงินสด 28,000 แล้วโอนต่อ ฐนกร 23/05 17:23) - ไม่ใช่ต้นทุน SSJ [bank]</v>
       </c>
       <c r="F410">
-        <v>28000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="411">

--- a/3_Automation_Dashboard/SomSaiJai_Dashboard_B1_2026.xlsx
+++ b/3_Automation_Dashboard/SomSaiJai_Dashboard_B1_2026.xlsx
@@ -1168,7 +1168,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F468"/>
+  <dimension ref="A1:F461"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2097,7 +2097,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>28/01/2026</v>
+        <v>30/01/2026</v>
       </c>
       <c r="B49" t="str">
         <v>Jan26</v>
@@ -2106,18 +2106,18 @@
         <v>COGS</v>
       </c>
       <c r="D49" t="str">
-        <v>Transportation</v>
+        <v>Watermelon</v>
       </c>
       <c r="E49" t="str">
-        <v>Unknown</v>
+        <v>แตงโม 25 ลูก</v>
       </c>
       <c r="F49">
-        <v>400</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>28/01/2026</v>
+        <v>30/01/2026</v>
       </c>
       <c r="B50" t="str">
         <v>Jan26</v>
@@ -2126,98 +2126,98 @@
         <v>COGS</v>
       </c>
       <c r="D50" t="str">
-        <v>Transportation</v>
+        <v>Apple</v>
       </c>
       <c r="E50" t="str">
-        <v>ค่าส่ง</v>
+        <v>แอปเปิ้ล เมล่อน</v>
       </c>
       <c r="F50">
-        <v>486</v>
+        <v>851</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>28/01/2026</v>
+        <v>31/01/2026</v>
       </c>
       <c r="B51" t="str">
         <v>Jan26</v>
       </c>
       <c r="C51" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D51" t="str">
-        <v>Watermelon</v>
+        <v>Salary</v>
       </c>
       <c r="E51" t="str">
-        <v>แตงโม 50 ลูก</v>
+        <v>เงินเดือนเมนมกราคม</v>
       </c>
       <c r="F51">
-        <v>4000</v>
+        <v>19000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>30/01/2026</v>
+        <v>02/02/2026</v>
       </c>
       <c r="B52" t="str">
-        <v>Jan26</v>
+        <v>Feb26</v>
       </c>
       <c r="C52" t="str">
         <v>COGS</v>
       </c>
       <c r="D52" t="str">
-        <v>Watermelon</v>
+        <v>Orange</v>
       </c>
       <c r="E52" t="str">
-        <v>แตงโม 25 ลูก</v>
+        <v>ส้ม 30 ตะกร้า</v>
       </c>
       <c r="F52">
-        <v>2000</v>
+        <v>10680</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>30/01/2026</v>
+        <v>02/02/2026</v>
       </c>
       <c r="B53" t="str">
-        <v>Jan26</v>
+        <v>Feb26</v>
       </c>
       <c r="C53" t="str">
         <v>COGS</v>
       </c>
       <c r="D53" t="str">
-        <v>Apple</v>
+        <v>Watermelon</v>
       </c>
       <c r="E53" t="str">
-        <v>แอปเปิ้ล เมล่อน</v>
+        <v>แตงโม 50 ลูก</v>
       </c>
       <c r="F53">
-        <v>851</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>31/01/2026</v>
+        <v>02/02/2026</v>
       </c>
       <c r="B54" t="str">
-        <v>Jan26</v>
+        <v>Feb26</v>
       </c>
       <c r="C54" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D54" t="str">
-        <v>Salary</v>
+        <v>Transportation</v>
       </c>
       <c r="E54" t="str">
-        <v>เงินเดือนเมนมกราคม</v>
+        <v>Unknown</v>
       </c>
       <c r="F54">
-        <v>19000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>02/02/2026</v>
+        <v>04/02/2026</v>
       </c>
       <c r="B55" t="str">
         <v>Feb26</v>
@@ -2226,18 +2226,18 @@
         <v>COGS</v>
       </c>
       <c r="D55" t="str">
-        <v>Orange</v>
+        <v>Packaging</v>
       </c>
       <c r="E55" t="str">
-        <v>ส้ม 30 ตะกร้า</v>
+        <v>ฝา 690 1000 ชิ้น แก้ว 1196 1000 ชิ้น หลอด 421</v>
       </c>
       <c r="F55">
-        <v>10680</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>02/02/2026</v>
+        <v>05/02/2026</v>
       </c>
       <c r="B56" t="str">
         <v>Feb26</v>
@@ -2257,7 +2257,7 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>02/02/2026</v>
+        <v>05/02/2026</v>
       </c>
       <c r="B57" t="str">
         <v>Feb26</v>
@@ -2266,18 +2266,18 @@
         <v>COGS</v>
       </c>
       <c r="D57" t="str">
-        <v>Transportation</v>
+        <v>Packaging</v>
       </c>
       <c r="E57" t="str">
-        <v>Unknown</v>
+        <v>แก้วสกรีน อย่างเดียวไม่รวมฝา 2280บาท</v>
       </c>
       <c r="F57">
-        <v>2000</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>04/02/2026</v>
+        <v>08/02/2026</v>
       </c>
       <c r="B58" t="str">
         <v>Feb26</v>
@@ -2286,18 +2286,18 @@
         <v>COGS</v>
       </c>
       <c r="D58" t="str">
-        <v>Packaging</v>
+        <v>Other</v>
       </c>
       <c r="E58" t="str">
-        <v>ฝา 690 1000 ชิ้น แก้ว 1196 1000 ชิ้น หลอด 421</v>
+        <v>Unknown</v>
       </c>
       <c r="F58">
-        <v>2023</v>
+        <v>798</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>05/02/2026</v>
+        <v>08/02/2026</v>
       </c>
       <c r="B59" t="str">
         <v>Feb26</v>
@@ -2309,7 +2309,7 @@
         <v>Watermelon</v>
       </c>
       <c r="E59" t="str">
-        <v>แตงโม 50 ลูก</v>
+        <v>แตงโม 50</v>
       </c>
       <c r="F59">
         <v>4000</v>
@@ -2317,7 +2317,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>05/02/2026</v>
+        <v>08/02/2026</v>
       </c>
       <c r="B60" t="str">
         <v>Feb26</v>
@@ -2326,18 +2326,18 @@
         <v>COGS</v>
       </c>
       <c r="D60" t="str">
-        <v>Packaging</v>
+        <v>Transportation</v>
       </c>
       <c r="E60" t="str">
-        <v>แก้วสกรีน อย่างเดียวไม่รวมฝา 2280บาท</v>
+        <v>Unknown</v>
       </c>
       <c r="F60">
-        <v>2280</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>08/02/2026</v>
+        <v>09/02/2026</v>
       </c>
       <c r="B61" t="str">
         <v>Feb26</v>
@@ -2346,18 +2346,18 @@
         <v>COGS</v>
       </c>
       <c r="D61" t="str">
-        <v>Other</v>
+        <v>Orange</v>
       </c>
       <c r="E61" t="str">
-        <v>Unknown</v>
+        <v>ส้ม 30 ตะกร้า</v>
       </c>
       <c r="F61">
-        <v>798</v>
+        <v>10680</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>08/02/2026</v>
+        <v>09/02/2026</v>
       </c>
       <c r="B62" t="str">
         <v>Feb26</v>
@@ -2366,38 +2366,38 @@
         <v>COGS</v>
       </c>
       <c r="D62" t="str">
-        <v>Watermelon</v>
+        <v>Orange</v>
       </c>
       <c r="E62" t="str">
-        <v>แตงโม 50</v>
+        <v>ค่าส่งส้ม</v>
       </c>
       <c r="F62">
-        <v>4000</v>
+        <v>685</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>08/02/2026</v>
+        <v>10/02/2026</v>
       </c>
       <c r="B63" t="str">
         <v>Feb26</v>
       </c>
       <c r="C63" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D63" t="str">
-        <v>Transportation</v>
+        <v>Utilities</v>
       </c>
       <c r="E63" t="str">
-        <v>Unknown</v>
+        <v>ค่าไฟเดือนมค</v>
       </c>
       <c r="F63">
-        <v>2000</v>
+        <v>389</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>09/02/2026</v>
+        <v>11/02/2026</v>
       </c>
       <c r="B64" t="str">
         <v>Feb26</v>
@@ -2406,58 +2406,58 @@
         <v>COGS</v>
       </c>
       <c r="D64" t="str">
-        <v>Orange</v>
+        <v>Watermelon</v>
       </c>
       <c r="E64" t="str">
-        <v>ส้ม 30 ตะกร้า</v>
+        <v>แตงโม 50 ลูก</v>
       </c>
       <c r="F64">
-        <v>10680</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>09/02/2026</v>
+        <v>14/02/2026</v>
       </c>
       <c r="B65" t="str">
         <v>Feb26</v>
       </c>
       <c r="C65" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D65" t="str">
-        <v>Orange</v>
+        <v>Other</v>
       </c>
       <c r="E65" t="str">
-        <v>ค่าส่งส้ม</v>
+        <v>Unknown</v>
       </c>
       <c r="F65">
-        <v>685</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>10/02/2026</v>
+        <v>14/02/2026</v>
       </c>
       <c r="B66" t="str">
         <v>Feb26</v>
       </c>
       <c r="C66" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D66" t="str">
-        <v>Utilities</v>
+        <v>Other</v>
       </c>
       <c r="E66" t="str">
-        <v>ค่าไฟเดือนมค</v>
+        <v>Unknown</v>
       </c>
       <c r="F66">
-        <v>389</v>
+        <v>350</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>11/02/2026</v>
+        <v>16/02/2026</v>
       </c>
       <c r="B67" t="str">
         <v>Feb26</v>
@@ -2466,38 +2466,38 @@
         <v>COGS</v>
       </c>
       <c r="D67" t="str">
-        <v>Watermelon</v>
+        <v>Orange</v>
       </c>
       <c r="E67" t="str">
-        <v>แตงโม 50 ลูก</v>
+        <v>ค่าส่งส้ม</v>
       </c>
       <c r="F67">
-        <v>4000</v>
+        <v>485</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>14/02/2026</v>
+        <v>16/02/2026</v>
       </c>
       <c r="B68" t="str">
         <v>Feb26</v>
       </c>
       <c r="C68" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D68" t="str">
-        <v>Other</v>
+        <v>Orange</v>
       </c>
       <c r="E68" t="str">
-        <v>Unknown</v>
+        <v>ค่าส้ม 30 ตะกร้า 13/2/69</v>
       </c>
       <c r="F68">
-        <v>4000</v>
+        <v>10680</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>14/02/2026</v>
+        <v>19/02/2026</v>
       </c>
       <c r="B69" t="str">
         <v>Feb26</v>
@@ -2506,18 +2506,18 @@
         <v>COGS</v>
       </c>
       <c r="D69" t="str">
-        <v>Other</v>
+        <v>Watermelon</v>
       </c>
       <c r="E69" t="str">
-        <v>Unknown</v>
+        <v>แตงโม 50 ลูก วันที่ 1719</v>
       </c>
       <c r="F69">
-        <v>350</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>16/02/2026</v>
+        <v>19/02/2026</v>
       </c>
       <c r="B70" t="str">
         <v>Feb26</v>
@@ -2526,18 +2526,18 @@
         <v>COGS</v>
       </c>
       <c r="D70" t="str">
-        <v>Orange</v>
+        <v>Packaging</v>
       </c>
       <c r="E70" t="str">
-        <v>ค่าส่งส้ม</v>
+        <v>แก้ว</v>
       </c>
       <c r="F70">
-        <v>485</v>
+        <v>3315</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>16/02/2026</v>
+        <v>19/02/2026</v>
       </c>
       <c r="B71" t="str">
         <v>Feb26</v>
@@ -2546,13 +2546,13 @@
         <v>COGS</v>
       </c>
       <c r="D71" t="str">
-        <v>Orange</v>
+        <v>Transportation</v>
       </c>
       <c r="E71" t="str">
-        <v>ค่าส้ม 30 ตะกร้า 13/2/69</v>
+        <v>แก้วสกรีน2ลัง(รอบที่1นะ แบ่งสั่งจะได้ไม่มีค่า</v>
       </c>
       <c r="F71">
-        <v>10680</v>
+        <v>6655</v>
       </c>
     </row>
     <row r="72">
@@ -2566,38 +2566,38 @@
         <v>COGS</v>
       </c>
       <c r="D72" t="str">
-        <v>Watermelon</v>
+        <v>Transportation</v>
       </c>
       <c r="E72" t="str">
-        <v>แตงโม 50 ลูก วันที่ 1719</v>
+        <v>Unknown</v>
       </c>
       <c r="F72">
-        <v>8000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>19/02/2026</v>
+        <v>20/02/2026</v>
       </c>
       <c r="B73" t="str">
         <v>Feb26</v>
       </c>
       <c r="C73" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D73" t="str">
-        <v>Packaging</v>
+        <v>Other</v>
       </c>
       <c r="E73" t="str">
-        <v>แก้ว</v>
+        <v>ผ้าปิดร้าน</v>
       </c>
       <c r="F73">
-        <v>3315</v>
+        <v>218</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>19/02/2026</v>
+        <v>23/02/2026</v>
       </c>
       <c r="B74" t="str">
         <v>Feb26</v>
@@ -2606,18 +2606,18 @@
         <v>COGS</v>
       </c>
       <c r="D74" t="str">
-        <v>Transportation</v>
+        <v>Watermelon</v>
       </c>
       <c r="E74" t="str">
-        <v>แก้วสกรีน2ลัง(รอบที่1นะ แบ่งสั่งจะได้ไม่มีค่า</v>
+        <v>แตงโม 21 50 ลูก 23 50 ลูก</v>
       </c>
       <c r="F74">
-        <v>6655</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>19/02/2026</v>
+        <v>24/02/2026</v>
       </c>
       <c r="B75" t="str">
         <v>Feb26</v>
@@ -2632,32 +2632,32 @@
         <v>Unknown</v>
       </c>
       <c r="F75">
-        <v>2000</v>
+        <v>209</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>20/02/2026</v>
+        <v>24/02/2026</v>
       </c>
       <c r="B76" t="str">
         <v>Feb26</v>
       </c>
       <c r="C76" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D76" t="str">
-        <v>Other</v>
+        <v>Orange</v>
       </c>
       <c r="E76" t="str">
-        <v>ผ้าปิดร้าน</v>
+        <v>ส้ม 30 18/2/69</v>
       </c>
       <c r="F76">
-        <v>218</v>
+        <v>10680</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>23/02/2026</v>
+        <v>24/02/2026</v>
       </c>
       <c r="B77" t="str">
         <v>Feb26</v>
@@ -2666,18 +2666,18 @@
         <v>COGS</v>
       </c>
       <c r="D77" t="str">
-        <v>Watermelon</v>
+        <v>Packaging</v>
       </c>
       <c r="E77" t="str">
-        <v>แตงโม 21 50 ลูก 23 50 ลูก</v>
+        <v>แก้ว 2400 ฝา 1670</v>
       </c>
       <c r="F77">
-        <v>8000</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>24/02/2026</v>
+        <v>25/02/2026</v>
       </c>
       <c r="B78" t="str">
         <v>Feb26</v>
@@ -2686,18 +2686,18 @@
         <v>COGS</v>
       </c>
       <c r="D78" t="str">
-        <v>Transportation</v>
+        <v>Watermelon</v>
       </c>
       <c r="E78" t="str">
-        <v>Unknown</v>
+        <v>แตงโม 50</v>
       </c>
       <c r="F78">
-        <v>209</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>24/02/2026</v>
+        <v>25/02/2026</v>
       </c>
       <c r="B79" t="str">
         <v>Feb26</v>
@@ -2706,18 +2706,18 @@
         <v>COGS</v>
       </c>
       <c r="D79" t="str">
-        <v>Orange</v>
+        <v>Transportation</v>
       </c>
       <c r="E79" t="str">
-        <v>ส้ม 30 18/2/69</v>
+        <v>Unknown</v>
       </c>
       <c r="F79">
-        <v>10680</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>24/02/2026</v>
+        <v>25/02/2026</v>
       </c>
       <c r="B80" t="str">
         <v>Feb26</v>
@@ -2726,13 +2726,13 @@
         <v>COGS</v>
       </c>
       <c r="D80" t="str">
-        <v>Packaging</v>
+        <v>Orange</v>
       </c>
       <c r="E80" t="str">
-        <v>แก้ว 2400 ฝา 1670</v>
+        <v>ส้ม20 ตะกร้า</v>
       </c>
       <c r="F80">
-        <v>4070</v>
+        <v>7312</v>
       </c>
     </row>
     <row r="81">
@@ -2746,18 +2746,18 @@
         <v>COGS</v>
       </c>
       <c r="D81" t="str">
-        <v>Watermelon</v>
+        <v>Orange</v>
       </c>
       <c r="E81" t="str">
-        <v>แตงโม 50</v>
+        <v>ค่าส่งส้ม</v>
       </c>
       <c r="F81">
-        <v>4000</v>
+        <v>806</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>25/02/2026</v>
+        <v>26/02/2026</v>
       </c>
       <c r="B82" t="str">
         <v>Feb26</v>
@@ -2766,18 +2766,18 @@
         <v>COGS</v>
       </c>
       <c r="D82" t="str">
-        <v>Transportation</v>
+        <v>Packaging</v>
       </c>
       <c r="E82" t="str">
-        <v>Unknown</v>
+        <v>ค่าขวดใหญ่</v>
       </c>
       <c r="F82">
-        <v>2000</v>
+        <v>319</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>25/02/2026</v>
+        <v>28/02/2026</v>
       </c>
       <c r="B83" t="str">
         <v>Feb26</v>
@@ -2789,35 +2789,35 @@
         <v>Orange</v>
       </c>
       <c r="E83" t="str">
-        <v>ส้ม20 ตะกร้า</v>
+        <v>ค่าส่งส้ม</v>
       </c>
       <c r="F83">
-        <v>7312</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>25/02/2026</v>
+        <v>28/02/2026</v>
       </c>
       <c r="B84" t="str">
         <v>Feb26</v>
       </c>
       <c r="C84" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D84" t="str">
-        <v>Orange</v>
+        <v>Rental</v>
       </c>
       <c r="E84" t="str">
-        <v>ค่าส่งส้ม</v>
+        <v>ค่าเช่าสต็อคกพ</v>
       </c>
       <c r="F84">
-        <v>806</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>26/02/2026</v>
+        <v>28/02/2026</v>
       </c>
       <c r="B85" t="str">
         <v>Feb26</v>
@@ -2826,78 +2826,78 @@
         <v>COGS</v>
       </c>
       <c r="D85" t="str">
-        <v>Packaging</v>
+        <v>Watermelon</v>
       </c>
       <c r="E85" t="str">
-        <v>ค่าขวดใหญ่</v>
+        <v>แตงโม 50 ลูก</v>
       </c>
       <c r="F85">
-        <v>319</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>28/02/2026</v>
+        <v>04/03/2026</v>
       </c>
       <c r="B86" t="str">
-        <v>Feb26</v>
+        <v>Mar26</v>
       </c>
       <c r="C86" t="str">
         <v>COGS</v>
       </c>
       <c r="D86" t="str">
-        <v>Orange</v>
+        <v>Watermelon</v>
       </c>
       <c r="E86" t="str">
-        <v>ค่าส่งส้ม</v>
+        <v>ค่าทางด่วนส่งแตงโม</v>
       </c>
       <c r="F86">
-        <v>2237</v>
+        <v>140</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>28/02/2026</v>
+        <v>04/03/2026</v>
       </c>
       <c r="B87" t="str">
-        <v>Feb26</v>
+        <v>Mar26</v>
       </c>
       <c r="C87" t="str">
         <v>COGS</v>
       </c>
       <c r="D87" t="str">
-        <v>Orange</v>
+        <v>Mango</v>
       </c>
       <c r="E87" t="str">
-        <v>ค่าส่งส้ม</v>
+        <v>มะม่วง 16 โล</v>
       </c>
       <c r="F87">
-        <v>2237</v>
+        <v>560</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>28/02/2026</v>
+        <v>05/03/2026</v>
       </c>
       <c r="B88" t="str">
         <v>Feb26</v>
       </c>
       <c r="C88" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D88" t="str">
-        <v>Rental</v>
+        <v>Mango</v>
       </c>
       <c r="E88" t="str">
-        <v>ค่าเช่าสต็อคกพ</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F88">
-        <v>12000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>28/02/2026</v>
+        <v>05/03/2026</v>
       </c>
       <c r="B89" t="str">
         <v>Feb26</v>
@@ -2906,18 +2906,18 @@
         <v>COGS</v>
       </c>
       <c r="D89" t="str">
-        <v>Watermelon</v>
+        <v>Orange</v>
       </c>
       <c r="E89" t="str">
-        <v>แตงโม 50 ลูก</v>
+        <v>ค่าส้มวันที่ 27269</v>
       </c>
       <c r="F89">
-        <v>4000</v>
+        <v>7312</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>04/03/2026</v>
+        <v>05/03/2026</v>
       </c>
       <c r="B90" t="str">
         <v>Mar26</v>
@@ -2926,18 +2926,18 @@
         <v>COGS</v>
       </c>
       <c r="D90" t="str">
-        <v>Watermelon</v>
+        <v>Orange</v>
       </c>
       <c r="E90" t="str">
-        <v>ค่าทางด่วนส่งแตงโม</v>
+        <v>แตงโม 51 ยอด3,500</v>
       </c>
       <c r="F90">
-        <v>140</v>
+        <v>7700</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>04/03/2026</v>
+        <v>05/03/2026</v>
       </c>
       <c r="B91" t="str">
         <v>Mar26</v>
@@ -2946,13 +2946,13 @@
         <v>COGS</v>
       </c>
       <c r="D91" t="str">
-        <v>Mango</v>
+        <v>Orange</v>
       </c>
       <c r="E91" t="str">
-        <v>มะม่วง 16 โล</v>
+        <v>ค่าส้ม 20 ตะกร้า</v>
       </c>
       <c r="F91">
-        <v>560</v>
+        <v>7312</v>
       </c>
     </row>
     <row r="92">
@@ -2960,19 +2960,19 @@
         <v>05/03/2026</v>
       </c>
       <c r="B92" t="str">
-        <v>Feb26</v>
+        <v>Mar26</v>
       </c>
       <c r="C92" t="str">
         <v>COGS</v>
       </c>
       <c r="D92" t="str">
-        <v>Mango</v>
+        <v>Transportation</v>
       </c>
       <c r="E92" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>ค่าทางด่วน</v>
       </c>
       <c r="F92">
-        <v>500</v>
+        <v>105</v>
       </c>
     </row>
     <row r="93">
@@ -2980,19 +2980,19 @@
         <v>05/03/2026</v>
       </c>
       <c r="B93" t="str">
-        <v>Feb26</v>
+        <v>Mar26</v>
       </c>
       <c r="C93" t="str">
         <v>COGS</v>
       </c>
       <c r="D93" t="str">
-        <v>Orange</v>
+        <v>Packaging</v>
       </c>
       <c r="E93" t="str">
-        <v>ค่าส้มวันที่ 27269</v>
+        <v>ถุงขยะ</v>
       </c>
       <c r="F93">
-        <v>7312</v>
+        <v>909</v>
       </c>
     </row>
     <row r="94">
@@ -3006,18 +3006,18 @@
         <v>COGS</v>
       </c>
       <c r="D94" t="str">
-        <v>Orange</v>
+        <v>Mango</v>
       </c>
       <c r="E94" t="str">
-        <v>แตงโม 51 ยอด3,500</v>
+        <v>มะม่วง 24 โล</v>
       </c>
       <c r="F94">
-        <v>7700</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>05/03/2026</v>
+        <v>07/03/2026</v>
       </c>
       <c r="B95" t="str">
         <v>Mar26</v>
@@ -3026,18 +3026,18 @@
         <v>COGS</v>
       </c>
       <c r="D95" t="str">
-        <v>Orange</v>
+        <v>Transportation</v>
       </c>
       <c r="E95" t="str">
-        <v>ค่าส้ม 20 ตะกร้า</v>
+        <v>Unknown</v>
       </c>
       <c r="F95">
-        <v>7312</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>05/03/2026</v>
+        <v>10/03/2026</v>
       </c>
       <c r="B96" t="str">
         <v>Mar26</v>
@@ -3046,18 +3046,18 @@
         <v>COGS</v>
       </c>
       <c r="D96" t="str">
-        <v>Transportation</v>
+        <v>Orange</v>
       </c>
       <c r="E96" t="str">
-        <v>ค่าทางด่วน</v>
+        <v>09/03/69</v>
       </c>
       <c r="F96">
-        <v>105</v>
+        <v>9804</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>05/03/2026</v>
+        <v>10/03/2026</v>
       </c>
       <c r="B97" t="str">
         <v>Mar26</v>
@@ -3066,38 +3066,38 @@
         <v>COGS</v>
       </c>
       <c r="D97" t="str">
-        <v>Packaging</v>
+        <v>Watermelon</v>
       </c>
       <c r="E97" t="str">
-        <v>ถุงขยะ</v>
+        <v>แตงโม 50 วันที่ 7 แตงโม 50 วันที่ 10</v>
       </c>
       <c r="F97">
-        <v>909</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>05/03/2026</v>
+        <v>10/03/2026</v>
       </c>
       <c r="B98" t="str">
         <v>Mar26</v>
       </c>
       <c r="C98" t="str">
-        <v>COGS</v>
+        <v>CAPEX</v>
       </c>
       <c r="D98" t="str">
-        <v>Mango</v>
+        <v>Investment</v>
       </c>
       <c r="E98" t="str">
-        <v>มะม่วง 24 โล</v>
+        <v>Unknown</v>
       </c>
       <c r="F98">
-        <v>1560</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>07/03/2026</v>
+        <v>10/03/2026</v>
       </c>
       <c r="B99" t="str">
         <v>Mar26</v>
@@ -3106,13 +3106,13 @@
         <v>COGS</v>
       </c>
       <c r="D99" t="str">
-        <v>Transportation</v>
+        <v>Packaging</v>
       </c>
       <c r="E99" t="str">
-        <v>Unknown</v>
+        <v>แก้ว2ลัง ลังละ 1560</v>
       </c>
       <c r="F99">
-        <v>2000</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="100">
@@ -3129,15 +3129,15 @@
         <v>Orange</v>
       </c>
       <c r="E100" t="str">
-        <v>09/03/69</v>
+        <v>แก้วร้านน้ำส้ม 2ลัง ลังละ1560</v>
       </c>
       <c r="F100">
-        <v>9804</v>
+        <v>5667</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>10/03/2026</v>
+        <v>13/03/2026</v>
       </c>
       <c r="B101" t="str">
         <v>Mar26</v>
@@ -3146,38 +3146,38 @@
         <v>COGS</v>
       </c>
       <c r="D101" t="str">
-        <v>Watermelon</v>
+        <v>Packaging</v>
       </c>
       <c r="E101" t="str">
-        <v>แตงโม 50 วันที่ 7 แตงโม 50 วันที่ 10</v>
+        <v>หลอด 20 แพค</v>
       </c>
       <c r="F101">
-        <v>8000</v>
+        <v>765</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>10/03/2026</v>
+        <v>14/03/2026</v>
       </c>
       <c r="B102" t="str">
         <v>Mar26</v>
       </c>
       <c r="C102" t="str">
-        <v>CAPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D102" t="str">
-        <v>Investment</v>
+        <v>Apple</v>
       </c>
       <c r="E102" t="str">
-        <v>Unknown</v>
+        <v>แอปเปิ้ลฟูจิ 32</v>
       </c>
       <c r="F102">
-        <v>6500</v>
+        <v>350</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>10/03/2026</v>
+        <v>14/03/2026</v>
       </c>
       <c r="B103" t="str">
         <v>Mar26</v>
@@ -3186,18 +3186,18 @@
         <v>COGS</v>
       </c>
       <c r="D103" t="str">
-        <v>Packaging</v>
+        <v>Mango</v>
       </c>
       <c r="E103" t="str">
-        <v>แก้ว2ลัง ลังละ 1560</v>
+        <v>มะม่วง 2 ลัง 44</v>
       </c>
       <c r="F103">
-        <v>3120</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>10/03/2026</v>
+        <v>15/03/2026</v>
       </c>
       <c r="B104" t="str">
         <v>Mar26</v>
@@ -3206,18 +3206,18 @@
         <v>COGS</v>
       </c>
       <c r="D104" t="str">
-        <v>Orange</v>
+        <v>Transportation</v>
       </c>
       <c r="E104" t="str">
-        <v>แก้วร้านน้ำส้ม 2ลัง ลังละ1560</v>
+        <v>ค่าทางด่วน</v>
       </c>
       <c r="F104">
-        <v>5667</v>
+        <v>115</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>13/03/2026</v>
+        <v>15/03/2026</v>
       </c>
       <c r="B105" t="str">
         <v>Mar26</v>
@@ -3226,38 +3226,38 @@
         <v>COGS</v>
       </c>
       <c r="D105" t="str">
-        <v>Packaging</v>
+        <v>Watermelon</v>
       </c>
       <c r="E105" t="str">
-        <v>หลอด 20 แพค</v>
+        <v>น้ำมะพร้าว 5ขวดเละ 50฿</v>
       </c>
       <c r="F105">
-        <v>765</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>14/03/2026</v>
+        <v>17/03/2026</v>
       </c>
       <c r="B106" t="str">
         <v>Mar26</v>
       </c>
       <c r="C106" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D106" t="str">
-        <v>Apple</v>
+        <v>Utilities</v>
       </c>
       <c r="E106" t="str">
-        <v>แอปเปิ้ลฟูจิ 32</v>
+        <v>ค่าไฟเดือนกพ มีนา</v>
       </c>
       <c r="F106">
-        <v>350</v>
+        <v>2779.47</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>14/03/2026</v>
+        <v>19/03/2026</v>
       </c>
       <c r="B107" t="str">
         <v>Mar26</v>
@@ -3266,38 +3266,38 @@
         <v>COGS</v>
       </c>
       <c r="D107" t="str">
-        <v>Mango</v>
+        <v>Watermelon</v>
       </c>
       <c r="E107" t="str">
-        <v>มะม่วง 2 ลัง 44</v>
+        <v>ค่าแตงโม 18/3/67 51 ลูก 4000 บาท</v>
       </c>
       <c r="F107">
-        <v>2420</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>15/03/2026</v>
+        <v>21/03/2026</v>
       </c>
       <c r="B108" t="str">
         <v>Mar26</v>
       </c>
       <c r="C108" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D108" t="str">
-        <v>Transportation</v>
+        <v>Other</v>
       </c>
       <c r="E108" t="str">
-        <v>ค่าทางด่วน</v>
+        <v>สกรู กาวตะปู</v>
       </c>
       <c r="F108">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>15/03/2026</v>
+        <v>23/03/2026</v>
       </c>
       <c r="B109" t="str">
         <v>Mar26</v>
@@ -3306,78 +3306,78 @@
         <v>COGS</v>
       </c>
       <c r="D109" t="str">
-        <v>Watermelon</v>
+        <v>Mango</v>
       </c>
       <c r="E109" t="str">
-        <v>น้ำมะพร้าว 5ขวดเละ 50฿</v>
+        <v>มะม่วง 44 โล</v>
       </c>
       <c r="F109">
-        <v>4800</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>17/03/2026</v>
+        <v>23/03/2026</v>
       </c>
       <c r="B110" t="str">
         <v>Mar26</v>
       </c>
       <c r="C110" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D110" t="str">
-        <v>Utilities</v>
+        <v>Orange</v>
       </c>
       <c r="E110" t="str">
-        <v>ค่าไฟเดือนกพ มีนา</v>
+        <v>22-3-2569</v>
       </c>
       <c r="F110">
-        <v>2779.47</v>
+        <v>5890</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>19/03/2026</v>
+        <v>24/03/2026</v>
       </c>
       <c r="B111" t="str">
         <v>Mar26</v>
       </c>
       <c r="C111" t="str">
-        <v>COGS</v>
+        <v>CAPEX</v>
       </c>
       <c r="D111" t="str">
-        <v>Watermelon</v>
+        <v>Investment</v>
       </c>
       <c r="E111" t="str">
-        <v>ค่าแตงโม 18/3/67 51 ลูก 4000 บาท</v>
+        <v>รถเข็นของคันใหม่</v>
       </c>
       <c r="F111">
-        <v>4000</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>21/03/2026</v>
+        <v>28/03/2026</v>
       </c>
       <c r="B112" t="str">
         <v>Mar26</v>
       </c>
       <c r="C112" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D112" t="str">
-        <v>Other</v>
+        <v>Coconut Water</v>
       </c>
       <c r="E112" t="str">
-        <v>สกรู กาวตะปู</v>
+        <v>น้ำมะพร้าว 10 ขวด</v>
       </c>
       <c r="F112">
-        <v>117</v>
+        <v>500</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>23/03/2026</v>
+        <v>28/03/2026</v>
       </c>
       <c r="B113" t="str">
         <v>Mar26</v>
@@ -3389,15 +3389,15 @@
         <v>Mango</v>
       </c>
       <c r="E113" t="str">
-        <v>มะม่วง 44 โล</v>
+        <v>มะม่วง 23 โล</v>
       </c>
       <c r="F113">
-        <v>2200</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>23/03/2026</v>
+        <v>28/03/2026</v>
       </c>
       <c r="B114" t="str">
         <v>Mar26</v>
@@ -3406,38 +3406,38 @@
         <v>COGS</v>
       </c>
       <c r="D114" t="str">
-        <v>Orange</v>
+        <v>Watermelon</v>
       </c>
       <c r="E114" t="str">
-        <v>22-3-2569</v>
+        <v>แตงโม 50 26/3/69</v>
       </c>
       <c r="F114">
-        <v>5890</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>24/03/2026</v>
+        <v>30/03/2026</v>
       </c>
       <c r="B115" t="str">
         <v>Mar26</v>
       </c>
       <c r="C115" t="str">
-        <v>CAPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D115" t="str">
-        <v>Investment</v>
+        <v>Packaging</v>
       </c>
       <c r="E115" t="str">
-        <v>รถเข็นของคันใหม่</v>
+        <v>นมข้นจืดสามลังหนึ่งลังมี 12 กล่อง 36 กล่อง</v>
       </c>
       <c r="F115">
-        <v>1752</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>28/03/2026</v>
+        <v>30/03/2026</v>
       </c>
       <c r="B116" t="str">
         <v>Mar26</v>
@@ -3446,18 +3446,18 @@
         <v>COGS</v>
       </c>
       <c r="D116" t="str">
-        <v>Coconut Water</v>
+        <v>Packaging</v>
       </c>
       <c r="E116" t="str">
-        <v>น้ำมะพร้าว 10 ขวด</v>
+        <v>นมข้นหวาน 3 ลัง 24 ถุง</v>
       </c>
       <c r="F116">
-        <v>500</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>28/03/2026</v>
+        <v>30/03/2026</v>
       </c>
       <c r="B117" t="str">
         <v>Mar26</v>
@@ -3466,18 +3466,18 @@
         <v>COGS</v>
       </c>
       <c r="D117" t="str">
-        <v>Mango</v>
+        <v>Watermelon</v>
       </c>
       <c r="E117" t="str">
-        <v>มะม่วง 23 โล</v>
+        <v>แตงโม 30 ลูก 2400 เนื้อมะพร้าว 10 โล 1100</v>
       </c>
       <c r="F117">
-        <v>1035</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>28/03/2026</v>
+        <v>30/03/2026</v>
       </c>
       <c r="B118" t="str">
         <v>Mar26</v>
@@ -3486,18 +3486,18 @@
         <v>COGS</v>
       </c>
       <c r="D118" t="str">
-        <v>Watermelon</v>
+        <v>Transportation</v>
       </c>
       <c r="E118" t="str">
-        <v>แตงโม 50 26/3/69</v>
+        <v>ค่าส่ง lalamove</v>
       </c>
       <c r="F118">
-        <v>4000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>30/03/2026</v>
+        <v>31/03/2026</v>
       </c>
       <c r="B119" t="str">
         <v>Mar26</v>
@@ -3506,78 +3506,78 @@
         <v>COGS</v>
       </c>
       <c r="D119" t="str">
-        <v>Packaging</v>
+        <v>Transportation</v>
       </c>
       <c r="E119" t="str">
-        <v>นมข้นจืดสามลังหนึ่งลังมี 12 กล่อง 36 กล่อง</v>
+        <v>Unknown</v>
       </c>
       <c r="F119">
-        <v>1720</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>30/03/2026</v>
+        <v>01/04/2026</v>
       </c>
       <c r="B120" t="str">
-        <v>Mar26</v>
+        <v>Apr26</v>
       </c>
       <c r="C120" t="str">
         <v>COGS</v>
       </c>
       <c r="D120" t="str">
-        <v>Packaging</v>
+        <v>Apple</v>
       </c>
       <c r="E120" t="str">
-        <v>นมข้นหวาน 3 ลัง 24 ถุง</v>
+        <v>แอปเปิ้ล 3 ลัง</v>
       </c>
       <c r="F120">
-        <v>2016</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>30/03/2026</v>
+        <v>01/04/2026</v>
       </c>
       <c r="B121" t="str">
-        <v>Mar26</v>
+        <v>Apr26</v>
       </c>
       <c r="C121" t="str">
         <v>COGS</v>
       </c>
       <c r="D121" t="str">
-        <v>Watermelon</v>
+        <v>Mango</v>
       </c>
       <c r="E121" t="str">
-        <v>แตงโม 30 ลูก 2400 เนื้อมะพร้าว 10 โล 1100</v>
+        <v>มะม่วง 2 ลัง</v>
       </c>
       <c r="F121">
-        <v>3500</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>30/03/2026</v>
+        <v>01/04/2026</v>
       </c>
       <c r="B122" t="str">
-        <v>Mar26</v>
+        <v>Apr26</v>
       </c>
       <c r="C122" t="str">
         <v>COGS</v>
       </c>
       <c r="D122" t="str">
-        <v>Transportation</v>
+        <v>Water</v>
       </c>
       <c r="E122" t="str">
-        <v>ค่าส่ง lalamove</v>
+        <v>น้ำ500</v>
       </c>
       <c r="F122">
-        <v>2000</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>31/03/2026</v>
+        <v>02/04/2026</v>
       </c>
       <c r="B123" t="str">
         <v>Mar26</v>
@@ -3586,18 +3586,18 @@
         <v>COGS</v>
       </c>
       <c r="D123" t="str">
-        <v>Transportation</v>
+        <v>Orange</v>
       </c>
       <c r="E123" t="str">
-        <v>Unknown</v>
+        <v>ส้มเพิ่มเติม มี.ค. (ตามรายงานต้นทุน Mar26: 23,202 + 49,560 = 72,762)</v>
       </c>
       <c r="F123">
-        <v>2000</v>
+        <v>49560</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>01/04/2026</v>
+        <v>04/04/2026</v>
       </c>
       <c r="B124" t="str">
         <v>Apr26</v>
@@ -3606,18 +3606,18 @@
         <v>COGS</v>
       </c>
       <c r="D124" t="str">
-        <v>Apple</v>
+        <v>Packaging</v>
       </c>
       <c r="E124" t="str">
-        <v>แอปเปิ้ล 3 ลัง</v>
+        <v>แก้ว3ลัง 1539 3 4617</v>
       </c>
       <c r="F124">
-        <v>1050</v>
+        <v>7066</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>01/04/2026</v>
+        <v>04/04/2026</v>
       </c>
       <c r="B125" t="str">
         <v>Apr26</v>
@@ -3626,18 +3626,18 @@
         <v>COGS</v>
       </c>
       <c r="D125" t="str">
-        <v>Mango</v>
+        <v>Packaging</v>
       </c>
       <c r="E125" t="str">
-        <v>มะม่วง 2 ลัง</v>
+        <v>แก้ว1ลัง 1539</v>
       </c>
       <c r="F125">
-        <v>1920</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>01/04/2026</v>
+        <v>04/04/2026</v>
       </c>
       <c r="B126" t="str">
         <v>Apr26</v>
@@ -3646,33 +3646,33 @@
         <v>COGS</v>
       </c>
       <c r="D126" t="str">
-        <v>Water</v>
+        <v>Coconut</v>
       </c>
       <c r="E126" t="str">
-        <v>น้ำ500</v>
+        <v>ค่ามะพร้าว 26 60ลูก 1560</v>
       </c>
       <c r="F126">
-        <v>1700</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>02/04/2026</v>
+        <v>04/04/2026</v>
       </c>
       <c r="B127" t="str">
-        <v>Mar26</v>
+        <v>Apr26</v>
       </c>
       <c r="C127" t="str">
         <v>COGS</v>
       </c>
       <c r="D127" t="str">
-        <v>Orange</v>
+        <v>Coconut</v>
       </c>
       <c r="E127" t="str">
-        <v>ส้มเพิ่มเติม มี.ค. (ตามรายงานต้นทุน Mar26: 23,202 + 49,560 = 72,762)</v>
+        <v>เนื้อ 1200 น้ำ 500</v>
       </c>
       <c r="F127">
-        <v>49560</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="128">
@@ -3686,13 +3686,13 @@
         <v>COGS</v>
       </c>
       <c r="D128" t="str">
-        <v>Packaging</v>
+        <v>Mango</v>
       </c>
       <c r="E128" t="str">
-        <v>แก้ว3ลัง 1539 3 4617</v>
+        <v>มะม่วง1ลัง</v>
       </c>
       <c r="F128">
-        <v>7066</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="129">
@@ -3706,13 +3706,13 @@
         <v>COGS</v>
       </c>
       <c r="D129" t="str">
-        <v>Packaging</v>
+        <v>Orange</v>
       </c>
       <c r="E129" t="str">
-        <v>แก้ว1ลัง 1539</v>
+        <v>ส้ม 4/4/69 20 ตะกร้า 30 บาท 13200 ค่าขนส่ง</v>
       </c>
       <c r="F129">
-        <v>1560</v>
+        <v>14160</v>
       </c>
     </row>
     <row r="130">
@@ -3726,13 +3726,13 @@
         <v>COGS</v>
       </c>
       <c r="D130" t="str">
-        <v>Coconut</v>
+        <v>Watermelon</v>
       </c>
       <c r="E130" t="str">
-        <v>ค่ามะพร้าว 26 60ลูก 1560</v>
+        <v>4/4/68 40 ลูก</v>
       </c>
       <c r="F130">
-        <v>1980</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="131">
@@ -3746,18 +3746,18 @@
         <v>COGS</v>
       </c>
       <c r="D131" t="str">
-        <v>Coconut</v>
+        <v>Watermelon</v>
       </c>
       <c r="E131" t="str">
-        <v>เนื้อ 1200 น้ำ 500</v>
+        <v>แตงโม 1/4/69 30 ลูก</v>
       </c>
       <c r="F131">
-        <v>1700</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>04/04/2026</v>
+        <v>07/04/2026</v>
       </c>
       <c r="B132" t="str">
         <v>Apr26</v>
@@ -3766,18 +3766,18 @@
         <v>COGS</v>
       </c>
       <c r="D132" t="str">
-        <v>Mango</v>
+        <v>Apple</v>
       </c>
       <c r="E132" t="str">
-        <v>มะม่วง1ลัง</v>
+        <v>แอปเปิ้ล 3 ลัง</v>
       </c>
       <c r="F132">
-        <v>1000</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>04/04/2026</v>
+        <v>07/04/2026</v>
       </c>
       <c r="B133" t="str">
         <v>Apr26</v>
@@ -3786,18 +3786,18 @@
         <v>COGS</v>
       </c>
       <c r="D133" t="str">
-        <v>Orange</v>
+        <v>Coconut Water</v>
       </c>
       <c r="E133" t="str">
-        <v>ส้ม 4/4/69 20 ตะกร้า 30 บาท 13200 ค่าขนส่ง</v>
+        <v>เนื้อมะพร้าว 10 - 1200 บาท น้ำมะพร้าว 10</v>
       </c>
       <c r="F133">
-        <v>14160</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>04/04/2026</v>
+        <v>07/04/2026</v>
       </c>
       <c r="B134" t="str">
         <v>Apr26</v>
@@ -3809,15 +3809,15 @@
         <v>Watermelon</v>
       </c>
       <c r="E134" t="str">
-        <v>4/4/68 40 ลูก</v>
+        <v>ค่าแตงโมวันที่ 4- 40 ลูก 3200 บาท วันที่ 7-40 ลูก</v>
       </c>
       <c r="F134">
-        <v>3200</v>
+        <v>6400</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>04/04/2026</v>
+        <v>10/04/2026</v>
       </c>
       <c r="B135" t="str">
         <v>Apr26</v>
@@ -3826,18 +3826,18 @@
         <v>COGS</v>
       </c>
       <c r="D135" t="str">
-        <v>Watermelon</v>
+        <v>Milk/Conden</v>
       </c>
       <c r="E135" t="str">
-        <v>แตงโม 1/4/69 30 ลูก</v>
+        <v>ค่านม</v>
       </c>
       <c r="F135">
-        <v>2400</v>
+        <v>180</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>07/04/2026</v>
+        <v>11/04/2026</v>
       </c>
       <c r="B136" t="str">
         <v>Apr26</v>
@@ -3846,18 +3846,18 @@
         <v>COGS</v>
       </c>
       <c r="D136" t="str">
-        <v>Apple</v>
+        <v>Transportation</v>
       </c>
       <c r="E136" t="str">
-        <v>แอปเปิ้ล 3 ลัง</v>
+        <v>ค่ารถ lalamove</v>
       </c>
       <c r="F136">
-        <v>1050</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>07/04/2026</v>
+        <v>11/04/2026</v>
       </c>
       <c r="B137" t="str">
         <v>Apr26</v>
@@ -3866,18 +3866,18 @@
         <v>COGS</v>
       </c>
       <c r="D137" t="str">
-        <v>Coconut Water</v>
+        <v>Apple</v>
       </c>
       <c r="E137" t="str">
-        <v>เนื้อมะพร้าว 10 - 1200 บาท น้ำมะพร้าว 10</v>
+        <v>แอปเปิ้ล 3 ลัง</v>
       </c>
       <c r="F137">
-        <v>1700</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>07/04/2026</v>
+        <v>11/04/2026</v>
       </c>
       <c r="B138" t="str">
         <v>Apr26</v>
@@ -3886,18 +3886,18 @@
         <v>COGS</v>
       </c>
       <c r="D138" t="str">
-        <v>Watermelon</v>
+        <v>Coconut</v>
       </c>
       <c r="E138" t="str">
-        <v>ค่าแตงโมวันที่ 4- 40 ลูก 3200 บาท วันที่ 7-40 ลูก</v>
+        <v>น้ำ 500 เนื้อ 1200</v>
       </c>
       <c r="F138">
-        <v>6400</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>10/04/2026</v>
+        <v>11/04/2026</v>
       </c>
       <c r="B139" t="str">
         <v>Apr26</v>
@@ -3906,18 +3906,18 @@
         <v>COGS</v>
       </c>
       <c r="D139" t="str">
-        <v>Milk/Conden</v>
+        <v>Mango</v>
       </c>
       <c r="E139" t="str">
-        <v>ค่านม</v>
+        <v>มะม่วง 1 ลัง 23 โล</v>
       </c>
       <c r="F139">
-        <v>180</v>
+        <v>690</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>11/04/2026</v>
+        <v>13/04/2026</v>
       </c>
       <c r="B140" t="str">
         <v>Apr26</v>
@@ -3926,18 +3926,18 @@
         <v>COGS</v>
       </c>
       <c r="D140" t="str">
-        <v>Transportation</v>
+        <v>Coconut Water</v>
       </c>
       <c r="E140" t="str">
-        <v>ค่ารถ lalamove</v>
+        <v>Unknown</v>
       </c>
       <c r="F140">
-        <v>2000</v>
+        <v>300</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>11/04/2026</v>
+        <v>13/04/2026</v>
       </c>
       <c r="B141" t="str">
         <v>Apr26</v>
@@ -3946,18 +3946,18 @@
         <v>COGS</v>
       </c>
       <c r="D141" t="str">
-        <v>Apple</v>
+        <v>Coconut Water</v>
       </c>
       <c r="E141" t="str">
-        <v>แอปเปิ้ล 3 ลัง</v>
+        <v>เนื้อมะพร้าว 1200 น้ำมะพร้าว 500</v>
       </c>
       <c r="F141">
-        <v>1050</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>11/04/2026</v>
+        <v>13/04/2026</v>
       </c>
       <c r="B142" t="str">
         <v>Apr26</v>
@@ -3966,18 +3966,18 @@
         <v>COGS</v>
       </c>
       <c r="D142" t="str">
-        <v>Coconut</v>
+        <v>Mango</v>
       </c>
       <c r="E142" t="str">
-        <v>น้ำ 500 เนื้อ 1200</v>
+        <v>Unknown</v>
       </c>
       <c r="F142">
-        <v>1700</v>
+        <v>750</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>11/04/2026</v>
+        <v>13/04/2026</v>
       </c>
       <c r="B143" t="str">
         <v>Apr26</v>
@@ -3986,18 +3986,18 @@
         <v>COGS</v>
       </c>
       <c r="D143" t="str">
-        <v>Mango</v>
+        <v>Watermelon</v>
       </c>
       <c r="E143" t="str">
-        <v>มะม่วง 1 ลัง 23 โล</v>
+        <v>Unknown</v>
       </c>
       <c r="F143">
-        <v>690</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>13/04/2026</v>
+        <v>18/04/2026</v>
       </c>
       <c r="B144" t="str">
         <v>Apr26</v>
@@ -4006,18 +4006,18 @@
         <v>COGS</v>
       </c>
       <c r="D144" t="str">
-        <v>Coconut Water</v>
+        <v>Apple</v>
       </c>
       <c r="E144" t="str">
-        <v>Unknown</v>
+        <v>แอปเปิ้ล 3 ลัง</v>
       </c>
       <c r="F144">
-        <v>300</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>13/04/2026</v>
+        <v>18/04/2026</v>
       </c>
       <c r="B145" t="str">
         <v>Apr26</v>
@@ -4026,38 +4026,38 @@
         <v>COGS</v>
       </c>
       <c r="D145" t="str">
-        <v>Coconut Water</v>
+        <v>Mango</v>
       </c>
       <c r="E145" t="str">
-        <v>เนื้อมะพร้าว 1200 น้ำมะพร้าว 500</v>
+        <v>16/04/26 มะม่วง 1 ลัง</v>
       </c>
       <c r="F145">
-        <v>1400</v>
+        <v>750</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>13/04/2026</v>
+        <v>18/04/2026</v>
       </c>
       <c r="B146" t="str">
         <v>Apr26</v>
       </c>
       <c r="C146" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D146" t="str">
-        <v>Mango</v>
+        <v>Other</v>
       </c>
       <c r="E146" t="str">
-        <v>Unknown</v>
+        <v>16/4/2569</v>
       </c>
       <c r="F146">
-        <v>750</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>13/04/2026</v>
+        <v>20/04/2026</v>
       </c>
       <c r="B147" t="str">
         <v>Apr26</v>
@@ -4066,18 +4066,18 @@
         <v>COGS</v>
       </c>
       <c r="D147" t="str">
-        <v>Watermelon</v>
+        <v>Orange</v>
       </c>
       <c r="E147" t="str">
-        <v>Unknown</v>
+        <v>ส้ม 40 ตะกร้า ตะกร้าละ 22 โล โลละ 30 บาท</v>
       </c>
       <c r="F147">
-        <v>3200</v>
+        <v>28600</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>18/04/2026</v>
+        <v>20/04/2026</v>
       </c>
       <c r="B148" t="str">
         <v>Apr26</v>
@@ -4086,18 +4086,18 @@
         <v>COGS</v>
       </c>
       <c r="D148" t="str">
-        <v>Apple</v>
+        <v>Transportation</v>
       </c>
       <c r="E148" t="str">
-        <v>แอปเปิ้ล 3 ลัง</v>
+        <v>ค่าส่งป้ายเมนูร้านใหม่</v>
       </c>
       <c r="F148">
-        <v>1050</v>
+        <v>335</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>18/04/2026</v>
+        <v>20/04/2026</v>
       </c>
       <c r="B149" t="str">
         <v>Apr26</v>
@@ -4106,33 +4106,33 @@
         <v>COGS</v>
       </c>
       <c r="D149" t="str">
-        <v>Mango</v>
+        <v>Packaging</v>
       </c>
       <c r="E149" t="str">
-        <v>16/04/26 มะม่วง 1 ลัง</v>
+        <v>ขวดใหญ่ 98 อัน</v>
       </c>
       <c r="F149">
-        <v>750</v>
+        <v>338</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>18/04/2026</v>
+        <v>20/04/2026</v>
       </c>
       <c r="B150" t="str">
         <v>Apr26</v>
       </c>
       <c r="C150" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D150" t="str">
-        <v>Other</v>
+        <v>Packaging</v>
       </c>
       <c r="E150" t="str">
-        <v>16/4/2569</v>
+        <v>ถุงขยะ 10 แพค</v>
       </c>
       <c r="F150">
-        <v>4000</v>
+        <v>520</v>
       </c>
     </row>
     <row r="151">
@@ -4146,13 +4146,13 @@
         <v>COGS</v>
       </c>
       <c r="D151" t="str">
-        <v>Orange</v>
+        <v>Watermelon</v>
       </c>
       <c r="E151" t="str">
-        <v>ส้ม 40 ตะกร้า ตะกร้าละ 22 โล โลละ 30 บาท</v>
+        <v>18/4/26 แตงโม 30 ลูก</v>
       </c>
       <c r="F151">
-        <v>28600</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="152">
@@ -4166,18 +4166,18 @@
         <v>COGS</v>
       </c>
       <c r="D152" t="str">
-        <v>Transportation</v>
+        <v>Mango</v>
       </c>
       <c r="E152" t="str">
-        <v>ค่าส่งป้ายเมนูร้านใหม่</v>
+        <v>18/4/26 มะม่วง 25 โล 750</v>
       </c>
       <c r="F152">
-        <v>335</v>
+        <v>750</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>20/04/2026</v>
+        <v>21/04/2026</v>
       </c>
       <c r="B153" t="str">
         <v>Apr26</v>
@@ -4186,18 +4186,18 @@
         <v>COGS</v>
       </c>
       <c r="D153" t="str">
-        <v>Packaging</v>
+        <v>Watermelon</v>
       </c>
       <c r="E153" t="str">
-        <v>ขวดใหญ่ 98 อัน</v>
+        <v>21/4/26 แตงโม60 ลูก</v>
       </c>
       <c r="F153">
-        <v>338</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>20/04/2026</v>
+        <v>21/04/2026</v>
       </c>
       <c r="B154" t="str">
         <v>Apr26</v>
@@ -4206,18 +4206,18 @@
         <v>COGS</v>
       </c>
       <c r="D154" t="str">
-        <v>Packaging</v>
+        <v>Transportation</v>
       </c>
       <c r="E154" t="str">
-        <v>ถุงขยะ 10 แพค</v>
+        <v>Lalamove</v>
       </c>
       <c r="F154">
-        <v>520</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>20/04/2026</v>
+        <v>21/04/2026</v>
       </c>
       <c r="B155" t="str">
         <v>Apr26</v>
@@ -4226,18 +4226,18 @@
         <v>COGS</v>
       </c>
       <c r="D155" t="str">
-        <v>Watermelon</v>
+        <v>Apple</v>
       </c>
       <c r="E155" t="str">
-        <v>18/4/26 แตงโม 30 ลูก</v>
+        <v>แอปเปิ้ล 4 ลัง</v>
       </c>
       <c r="F155">
-        <v>2400</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>20/04/2026</v>
+        <v>23/04/2026</v>
       </c>
       <c r="B156" t="str">
         <v>Apr26</v>
@@ -4249,15 +4249,15 @@
         <v>Mango</v>
       </c>
       <c r="E156" t="str">
-        <v>18/4/26 มะม่วง 25 โล 750</v>
+        <v>มะม่วง 2 ลัง</v>
       </c>
       <c r="F156">
-        <v>750</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>21/04/2026</v>
+        <v>23/04/2026</v>
       </c>
       <c r="B157" t="str">
         <v>Apr26</v>
@@ -4266,18 +4266,18 @@
         <v>COGS</v>
       </c>
       <c r="D157" t="str">
-        <v>Watermelon</v>
+        <v>Apple</v>
       </c>
       <c r="E157" t="str">
-        <v>21/4/26 แตงโม60 ลูก</v>
+        <v>แอปเปิ้ล 4 ลัง</v>
       </c>
       <c r="F157">
-        <v>4800</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>21/04/2026</v>
+        <v>23/04/2026</v>
       </c>
       <c r="B158" t="str">
         <v>Apr26</v>
@@ -4286,18 +4286,18 @@
         <v>COGS</v>
       </c>
       <c r="D158" t="str">
-        <v>Transportation</v>
+        <v>Coconut</v>
       </c>
       <c r="E158" t="str">
-        <v>Lalamove</v>
+        <v>16/4/26 เนื้อ 10 น้ำ 10 21/4/26 เนื้อ 10</v>
       </c>
       <c r="F158">
-        <v>2000</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>21/04/2026</v>
+        <v>23/04/2026</v>
       </c>
       <c r="B159" t="str">
         <v>Apr26</v>
@@ -4306,18 +4306,18 @@
         <v>COGS</v>
       </c>
       <c r="D159" t="str">
-        <v>Apple</v>
+        <v>Mango</v>
       </c>
       <c r="E159" t="str">
-        <v>แอปเปิ้ล 4 ลัง</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F159">
-        <v>1400</v>
+        <v>780</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>23/04/2026</v>
+        <v>24/04/2026</v>
       </c>
       <c r="B160" t="str">
         <v>Apr26</v>
@@ -4326,18 +4326,18 @@
         <v>COGS</v>
       </c>
       <c r="D160" t="str">
-        <v>Mango</v>
+        <v>Packaging</v>
       </c>
       <c r="E160" t="str">
-        <v>มะม่วง 2 ลัง</v>
+        <v>บาร์เลย 4 ถั่วแดง 3 ถุงละ 60</v>
       </c>
       <c r="F160">
-        <v>1560</v>
+        <v>420</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>23/04/2026</v>
+        <v>24/04/2026</v>
       </c>
       <c r="B161" t="str">
         <v>Apr26</v>
@@ -4346,18 +4346,18 @@
         <v>COGS</v>
       </c>
       <c r="D161" t="str">
-        <v>Apple</v>
+        <v>Watermelon</v>
       </c>
       <c r="E161" t="str">
-        <v>แอปเปิ้ล 4 ลัง</v>
+        <v>แตงโม 50 ลูก</v>
       </c>
       <c r="F161">
-        <v>1400</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>23/04/2026</v>
+        <v>25/04/2026</v>
       </c>
       <c r="B162" t="str">
         <v>Apr26</v>
@@ -4366,18 +4366,18 @@
         <v>COGS</v>
       </c>
       <c r="D162" t="str">
-        <v>Coconut</v>
+        <v>Orange</v>
       </c>
       <c r="E162" t="str">
-        <v>16/4/26 เนื้อ 10 น้ำ 10 21/4/26 เนื้อ 10</v>
+        <v>22/04/69</v>
       </c>
       <c r="F162">
-        <v>2900</v>
+        <v>14400</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>23/04/2026</v>
+        <v>26/04/2026</v>
       </c>
       <c r="B163" t="str">
         <v>Apr26</v>
@@ -4386,18 +4386,18 @@
         <v>COGS</v>
       </c>
       <c r="D163" t="str">
-        <v>Mango</v>
+        <v>Packaging</v>
       </c>
       <c r="E163" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>แก้ว 1 ลัง</v>
       </c>
       <c r="F163">
-        <v>780</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>24/04/2026</v>
+        <v>26/04/2026</v>
       </c>
       <c r="B164" t="str">
         <v>Apr26</v>
@@ -4409,15 +4409,15 @@
         <v>Packaging</v>
       </c>
       <c r="E164" t="str">
-        <v>บาร์เลย 4 ถั่วแดง 3 ถุงละ 60</v>
+        <v>แก้ว3ลัง</v>
       </c>
       <c r="F164">
-        <v>420</v>
+        <v>7090</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>24/04/2026</v>
+        <v>26/04/2026</v>
       </c>
       <c r="B165" t="str">
         <v>Apr26</v>
@@ -4426,18 +4426,18 @@
         <v>COGS</v>
       </c>
       <c r="D165" t="str">
-        <v>Watermelon</v>
+        <v>Mango</v>
       </c>
       <c r="E165" t="str">
-        <v>แตงโม 50 ลูก</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F165">
-        <v>4000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>25/04/2026</v>
+        <v>26/04/2026</v>
       </c>
       <c r="B166" t="str">
         <v>Apr26</v>
@@ -4446,18 +4446,18 @@
         <v>COGS</v>
       </c>
       <c r="D166" t="str">
-        <v>Orange</v>
+        <v>Apple</v>
       </c>
       <c r="E166" t="str">
-        <v>22/04/69</v>
+        <v>แอปเปิ้ล 4</v>
       </c>
       <c r="F166">
-        <v>14400</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>26/04/2026</v>
+        <v>27/04/2026</v>
       </c>
       <c r="B167" t="str">
         <v>Apr26</v>
@@ -4466,18 +4466,18 @@
         <v>COGS</v>
       </c>
       <c r="D167" t="str">
-        <v>Packaging</v>
+        <v>Watermelon</v>
       </c>
       <c r="E167" t="str">
-        <v>แก้ว 1 ลัง</v>
+        <v>26/4/26 50 ลูก</v>
       </c>
       <c r="F167">
-        <v>1539</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>26/04/2026</v>
+        <v>28/04/2026</v>
       </c>
       <c r="B168" t="str">
         <v>Apr26</v>
@@ -4489,15 +4489,15 @@
         <v>Packaging</v>
       </c>
       <c r="E168" t="str">
-        <v>แก้ว3ลัง</v>
+        <v>หลอด 704(20ห่อ)</v>
       </c>
       <c r="F168">
-        <v>7090</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>26/04/2026</v>
+        <v>28/04/2026</v>
       </c>
       <c r="B169" t="str">
         <v>Apr26</v>
@@ -4506,18 +4506,18 @@
         <v>COGS</v>
       </c>
       <c r="D169" t="str">
-        <v>Mango</v>
+        <v>Orange</v>
       </c>
       <c r="E169" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>รอบ 27/04/69</v>
       </c>
       <c r="F169">
-        <v>780</v>
+        <v>21600</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>26/04/2026</v>
+        <v>28/04/2026</v>
       </c>
       <c r="B170" t="str">
         <v>Apr26</v>
@@ -4526,18 +4526,18 @@
         <v>COGS</v>
       </c>
       <c r="D170" t="str">
-        <v>Apple</v>
+        <v>Coconut</v>
       </c>
       <c r="E170" t="str">
-        <v>แอปเปิ้ล 4</v>
+        <v>ค่าส่งมะพร้าว</v>
       </c>
       <c r="F170">
-        <v>1400</v>
+        <v>100</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>27/04/2026</v>
+        <v>28/04/2026</v>
       </c>
       <c r="B171" t="str">
         <v>Apr26</v>
@@ -4546,13 +4546,13 @@
         <v>COGS</v>
       </c>
       <c r="D171" t="str">
-        <v>Watermelon</v>
+        <v>Apple</v>
       </c>
       <c r="E171" t="str">
-        <v>26/4/26 50 ลูก</v>
+        <v>แอปเปิ้ล 4 ลัง</v>
       </c>
       <c r="F171">
-        <v>4000</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="172">
@@ -4566,18 +4566,18 @@
         <v>COGS</v>
       </c>
       <c r="D172" t="str">
-        <v>Packaging</v>
+        <v>Mango</v>
       </c>
       <c r="E172" t="str">
-        <v>หลอด 704(20ห่อ)</v>
+        <v>มะม่วง 2 ลัง</v>
       </c>
       <c r="F172">
-        <v>2110</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>28/04/2026</v>
+        <v>29/04/2026</v>
       </c>
       <c r="B173" t="str">
         <v>Apr26</v>
@@ -4586,18 +4586,18 @@
         <v>COGS</v>
       </c>
       <c r="D173" t="str">
-        <v>Orange</v>
+        <v>Milk/Conden</v>
       </c>
       <c r="E173" t="str">
-        <v>รอบ 27/04/69</v>
+        <v>นมข้นหวาน1ลัง 836</v>
       </c>
       <c r="F173">
-        <v>21600</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>28/04/2026</v>
+        <v>29/04/2026</v>
       </c>
       <c r="B174" t="str">
         <v>Apr26</v>
@@ -4606,18 +4606,18 @@
         <v>COGS</v>
       </c>
       <c r="D174" t="str">
-        <v>Coconut</v>
+        <v>Packaging</v>
       </c>
       <c r="E174" t="str">
-        <v>ค่าส่งมะพร้าว</v>
+        <v>นมข้นหวาน2ลัง 1602</v>
       </c>
       <c r="F174">
-        <v>100</v>
+        <v>3210</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>28/04/2026</v>
+        <v>29/04/2026</v>
       </c>
       <c r="B175" t="str">
         <v>Apr26</v>
@@ -4626,18 +4626,18 @@
         <v>COGS</v>
       </c>
       <c r="D175" t="str">
-        <v>Apple</v>
+        <v>Watermelon</v>
       </c>
       <c r="E175" t="str">
-        <v>แอปเปิ้ล 4 ลัง</v>
+        <v>แตงโม 60 ลูก</v>
       </c>
       <c r="F175">
-        <v>1400</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>28/04/2026</v>
+        <v>29/04/2026</v>
       </c>
       <c r="B176" t="str">
         <v>Apr26</v>
@@ -4646,18 +4646,18 @@
         <v>COGS</v>
       </c>
       <c r="D176" t="str">
-        <v>Mango</v>
+        <v>Transportation</v>
       </c>
       <c r="E176" t="str">
-        <v>มะม่วง 2 ลัง</v>
+        <v>เนื้อ 10 x 50 500</v>
       </c>
       <c r="F176">
-        <v>1560</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>29/04/2026</v>
+        <v>30/04/2026</v>
       </c>
       <c r="B177" t="str">
         <v>Apr26</v>
@@ -4666,38 +4666,38 @@
         <v>COGS</v>
       </c>
       <c r="D177" t="str">
-        <v>Milk/Conden</v>
+        <v>Pineapple</v>
       </c>
       <c r="E177" t="str">
-        <v>นมข้นหวาน1ลัง 836</v>
+        <v>สับปะรส 3 ตะกร้า</v>
       </c>
       <c r="F177">
-        <v>2160</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>29/04/2026</v>
+        <v>30/04/2026</v>
       </c>
       <c r="B178" t="str">
         <v>Apr26</v>
       </c>
       <c r="C178" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D178" t="str">
-        <v>Packaging</v>
+        <v>Rental</v>
       </c>
       <c r="E178" t="str">
-        <v>นมข้นหวาน2ลัง 1602</v>
+        <v>Rent</v>
       </c>
       <c r="F178">
-        <v>3210</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>29/04/2026</v>
+        <v>30/04/2026</v>
       </c>
       <c r="B179" t="str">
         <v>Apr26</v>
@@ -4706,18 +4706,18 @@
         <v>COGS</v>
       </c>
       <c r="D179" t="str">
-        <v>Watermelon</v>
+        <v>Stock</v>
       </c>
       <c r="E179" t="str">
-        <v>แตงโม 60 ลูก</v>
+        <v>Stock (Allocated 82.9%)</v>
       </c>
       <c r="F179">
-        <v>4200</v>
+        <v>9948</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>29/04/2026</v>
+        <v>30/04/2026</v>
       </c>
       <c r="B180" t="str">
         <v>Apr26</v>
@@ -4726,138 +4726,138 @@
         <v>COGS</v>
       </c>
       <c r="D180" t="str">
-        <v>Transportation</v>
+        <v>Guava</v>
       </c>
       <c r="E180" t="str">
-        <v>เนื้อ 10 x 50 500</v>
+        <v>ฝรั่ง ตะกร้าแรก (นาง ประนอม, BBL X8148) [bank 30/04 22:50]</v>
       </c>
       <c r="F180">
-        <v>2395</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>30/04/2026</v>
+        <v>01/05/2026</v>
       </c>
       <c r="B181" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C181" t="str">
         <v>COGS</v>
       </c>
       <c r="D181" t="str">
-        <v>Pineapple</v>
+        <v>Guava</v>
       </c>
       <c r="E181" t="str">
-        <v>สับปะรส 3 ตะกร้า</v>
+        <v>ฝรั่ง (แยกจากใบเสร็จรวม 01/05)</v>
       </c>
       <c r="F181">
-        <v>1500</v>
+        <v>300</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>30/04/2026</v>
+        <v>01/05/2026</v>
       </c>
       <c r="B182" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C182" t="str">
-        <v>OPEX</v>
+        <v>CAPEX</v>
       </c>
       <c r="D182" t="str">
-        <v>Salary</v>
+        <v>Investment</v>
       </c>
       <c r="E182" t="str">
-        <v>Employee 1</v>
+        <v>ร่ม 2 คัน (1,176 + 843)</v>
       </c>
       <c r="F182">
-        <v>19000</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>30/04/2026</v>
+        <v>01/05/2026</v>
       </c>
       <c r="B183" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C183" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D183" t="str">
-        <v>Salary</v>
+        <v>Milk/Conden</v>
       </c>
       <c r="E183" t="str">
-        <v>Employee 2</v>
+        <v>นมข้นจืด (แยกจากใบเสร็จรวม 01/05)</v>
       </c>
       <c r="F183">
-        <v>12000</v>
+        <v>785</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>30/04/2026</v>
+        <v>01/05/2026</v>
       </c>
       <c r="B184" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C184" t="str">
         <v>OPEX</v>
       </c>
       <c r="D184" t="str">
-        <v>Rental</v>
+        <v>Other</v>
       </c>
       <c r="E184" t="str">
-        <v>Rent</v>
+        <v>ที่ปั๊ม (แยกจากใบเสร็จรวม 01/05)</v>
       </c>
       <c r="F184">
-        <v>35000</v>
+        <v>176</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>30/04/2026</v>
+        <v>01/05/2026</v>
       </c>
       <c r="B185" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C185" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D185" t="str">
-        <v>Stock</v>
+        <v>Other</v>
       </c>
       <c r="E185" t="str">
-        <v>Stock (Allocated 82.9%)</v>
+        <v>ยอดคงเหลือใบเสร็จ 01/05 — ไม่ระบุรายการ ต้องตรวจสอบสลิป</v>
       </c>
       <c r="F185">
-        <v>9948</v>
+        <v>4543</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>30/04/2026</v>
+        <v>02/05/2026</v>
       </c>
       <c r="B186" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C186" t="str">
         <v>COGS</v>
       </c>
       <c r="D186" t="str">
-        <v>Guava</v>
+        <v>Mango</v>
       </c>
       <c r="E186" t="str">
-        <v>ฝรั่ง ตะกร้าแรก (นาง ประนอม, BBL X8148) [bank 30/04 22:50]</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F186">
-        <v>1500</v>
+        <v>910</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>01/05/2026</v>
+        <v>02/05/2026</v>
       </c>
       <c r="B187" t="str">
         <v>May26</v>
@@ -4866,58 +4866,58 @@
         <v>COGS</v>
       </c>
       <c r="D187" t="str">
-        <v>Guava</v>
+        <v>Apple</v>
       </c>
       <c r="E187" t="str">
-        <v>ฝรั่ง (แยกจากใบเสร็จรวม 01/05)</v>
+        <v>แอปเปิ้ล 4 ลัง</v>
       </c>
       <c r="F187">
-        <v>300</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>01/05/2026</v>
+        <v>02/05/2026</v>
       </c>
       <c r="B188" t="str">
         <v>May26</v>
       </c>
       <c r="C188" t="str">
-        <v>CAPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D188" t="str">
-        <v>Investment</v>
+        <v>Pineapple</v>
       </c>
       <c r="E188" t="str">
-        <v>ร่ม 2 คัน (1,176 + 843)</v>
+        <v>สับปะรด 30 ลูก</v>
       </c>
       <c r="F188">
-        <v>2019</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>01/05/2026</v>
+        <v>02/05/2026</v>
       </c>
       <c r="B189" t="str">
         <v>May26</v>
       </c>
       <c r="C189" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D189" t="str">
-        <v>Milk/Conden</v>
+        <v>Other</v>
       </c>
       <c r="E189" t="str">
-        <v>นมข้นจืด (แยกจากใบเสร็จรวม 01/05)</v>
+        <v>ค่าหาหมอเอ</v>
       </c>
       <c r="F189">
-        <v>785</v>
+        <v>706</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>01/05/2026</v>
+        <v>02/05/2026</v>
       </c>
       <c r="B190" t="str">
         <v>May26</v>
@@ -4929,35 +4929,35 @@
         <v>Other</v>
       </c>
       <c r="E190" t="str">
-        <v>ที่ปั๊ม (แยกจากใบเสร็จรวม 01/05)</v>
+        <v>ค่าหมอเอ</v>
       </c>
       <c r="F190">
-        <v>176</v>
+        <v>13</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>01/05/2026</v>
+        <v>04/05/2026</v>
       </c>
       <c r="B191" t="str">
         <v>May26</v>
       </c>
       <c r="C191" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D191" t="str">
-        <v>Other</v>
+        <v>Packaging</v>
       </c>
       <c r="E191" t="str">
-        <v>ยอดคงเหลือใบเสร็จ 01/05 — ไม่ระบุรายการ ต้องตรวจสอบสลิป</v>
+        <v>ถุงมือ4อัน</v>
       </c>
       <c r="F191">
-        <v>4543</v>
+        <v>499</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>02/05/2026</v>
+        <v>04/05/2026</v>
       </c>
       <c r="B192" t="str">
         <v>May26</v>
@@ -4966,18 +4966,18 @@
         <v>COGS</v>
       </c>
       <c r="D192" t="str">
-        <v>Mango</v>
+        <v>Apple</v>
       </c>
       <c r="E192" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>แอปเปิ้ล 4 ลัง</v>
       </c>
       <c r="F192">
-        <v>910</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>02/05/2026</v>
+        <v>04/05/2026</v>
       </c>
       <c r="B193" t="str">
         <v>May26</v>
@@ -4986,18 +4986,18 @@
         <v>COGS</v>
       </c>
       <c r="D193" t="str">
-        <v>Apple</v>
+        <v>Mango</v>
       </c>
       <c r="E193" t="str">
-        <v>แอปเปิ้ล 4 ลัง</v>
+        <v>มะม่วง 2 ลัง</v>
       </c>
       <c r="F193">
-        <v>1500</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>02/05/2026</v>
+        <v>04/05/2026</v>
       </c>
       <c r="B194" t="str">
         <v>May26</v>
@@ -5006,18 +5006,18 @@
         <v>COGS</v>
       </c>
       <c r="D194" t="str">
-        <v>Pineapple</v>
+        <v>Watermelon</v>
       </c>
       <c r="E194" t="str">
-        <v>สับปะรด 30 ลูก</v>
+        <v>30-4-2569 เบอร์ 70฿ 60 ลูก</v>
       </c>
       <c r="F194">
-        <v>1116</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>02/05/2026</v>
+        <v>06/05/2026</v>
       </c>
       <c r="B195" t="str">
         <v>May26</v>
@@ -5029,35 +5029,35 @@
         <v>Other</v>
       </c>
       <c r="E195" t="str">
-        <v>ค่าหาหมอเอ</v>
+        <v>ทิชชู่3แพค 36ห่อ</v>
       </c>
       <c r="F195">
-        <v>706</v>
+        <v>451</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>02/05/2026</v>
+        <v>06/05/2026</v>
       </c>
       <c r="B196" t="str">
         <v>May26</v>
       </c>
       <c r="C196" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D196" t="str">
-        <v>Other</v>
+        <v>Mango</v>
       </c>
       <c r="E196" t="str">
-        <v>ค่าหมอเอ</v>
+        <v>มะม่วง 2 ลัง</v>
       </c>
       <c r="F196">
-        <v>13</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>04/05/2026</v>
+        <v>06/05/2026</v>
       </c>
       <c r="B197" t="str">
         <v>May26</v>
@@ -5066,18 +5066,18 @@
         <v>COGS</v>
       </c>
       <c r="D197" t="str">
-        <v>Packaging</v>
+        <v>Pineapple</v>
       </c>
       <c r="E197" t="str">
-        <v>ถุงมือ4อัน</v>
+        <v>สับปะรด 18 ลูก</v>
       </c>
       <c r="F197">
-        <v>499</v>
+        <v>486</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>04/05/2026</v>
+        <v>06/05/2026</v>
       </c>
       <c r="B198" t="str">
         <v>May26</v>
@@ -5097,7 +5097,7 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>04/05/2026</v>
+        <v>08/05/2026</v>
       </c>
       <c r="B199" t="str">
         <v>May26</v>
@@ -5106,18 +5106,18 @@
         <v>COGS</v>
       </c>
       <c r="D199" t="str">
-        <v>Mango</v>
+        <v>Transportation</v>
       </c>
       <c r="E199" t="str">
-        <v>มะม่วง 2 ลัง</v>
+        <v>น้ำ 20 ขวด 900 ถอดเสื้อ 30 ลูก750 กล่องโฟม 3</v>
       </c>
       <c r="F199">
-        <v>1680</v>
+        <v>4555</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>04/05/2026</v>
+        <v>08/05/2026</v>
       </c>
       <c r="B200" t="str">
         <v>May26</v>
@@ -5126,58 +5126,58 @@
         <v>COGS</v>
       </c>
       <c r="D200" t="str">
-        <v>Watermelon</v>
+        <v>Water</v>
       </c>
       <c r="E200" t="str">
-        <v>30-4-2569 เบอร์ 70฿ 60 ลูก</v>
+        <v>น้ำมะร้าว 1 ลัง</v>
       </c>
       <c r="F200">
-        <v>7000</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>06/05/2026</v>
+        <v>08/05/2026</v>
       </c>
       <c r="B201" t="str">
         <v>May26</v>
       </c>
       <c r="C201" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D201" t="str">
-        <v>Other</v>
+        <v>Packaging</v>
       </c>
       <c r="E201" t="str">
-        <v>ทิชชู่3แพค 36ห่อ</v>
+        <v>6 พ.ค. น้ำ 30 ขวด 1500 บาท เนื้อ 11 โล 1320 บาท</v>
       </c>
       <c r="F201">
-        <v>451</v>
+        <v>2820</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>06/05/2026</v>
+        <v>08/05/2026</v>
       </c>
       <c r="B202" t="str">
         <v>May26</v>
       </c>
       <c r="C202" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D202" t="str">
-        <v>Mango</v>
+        <v>Other</v>
       </c>
       <c r="E202" t="str">
-        <v>มะม่วง 2 ลัง</v>
+        <v>ค่าทำความสะอาดตึกชั้น 1</v>
       </c>
       <c r="F202">
-        <v>1750</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>06/05/2026</v>
+        <v>08/05/2026</v>
       </c>
       <c r="B203" t="str">
         <v>May26</v>
@@ -5186,38 +5186,38 @@
         <v>COGS</v>
       </c>
       <c r="D203" t="str">
-        <v>Pineapple</v>
+        <v>Watermelon</v>
       </c>
       <c r="E203" t="str">
-        <v>สับปะรด 18 ลูก</v>
+        <v>4-5-2569 เบอร์ 70฿ 60 ลูก ยอด 4,200</v>
       </c>
       <c r="F203">
-        <v>486</v>
+        <v>8200</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>06/05/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="B204" t="str">
         <v>May26</v>
       </c>
       <c r="C204" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D204" t="str">
-        <v>Apple</v>
+        <v>Other</v>
       </c>
       <c r="E204" t="str">
-        <v>แอปเปิ้ล 4 ลัง</v>
+        <v>พรหมเช็ดเท้า 1 ผืน</v>
       </c>
       <c r="F204">
-        <v>1400</v>
+        <v>372</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>08/05/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="B205" t="str">
         <v>May26</v>
@@ -5226,18 +5226,18 @@
         <v>COGS</v>
       </c>
       <c r="D205" t="str">
-        <v>Transportation</v>
+        <v>Milk/Conden</v>
       </c>
       <c r="E205" t="str">
-        <v>น้ำ 20 ขวด 900 ถอดเสื้อ 30 ลูก750 กล่องโฟม 3</v>
+        <v>นมข้นจืด 1ลัง 636</v>
       </c>
       <c r="F205">
-        <v>4555</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>08/05/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="B206" t="str">
         <v>May26</v>
@@ -5246,18 +5246,18 @@
         <v>COGS</v>
       </c>
       <c r="D206" t="str">
-        <v>Water</v>
+        <v>Packaging</v>
       </c>
       <c r="E206" t="str">
-        <v>น้ำมะร้าว 1 ลัง</v>
+        <v>นมข้น 3 ลัง 2568</v>
       </c>
       <c r="F206">
-        <v>1100</v>
+        <v>4875</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>08/05/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="B207" t="str">
         <v>May26</v>
@@ -5269,35 +5269,35 @@
         <v>Packaging</v>
       </c>
       <c r="E207" t="str">
-        <v>6 พ.ค. น้ำ 30 ขวด 1500 บาท เนื้อ 11 โล 1320 บาท</v>
+        <v>แก้ว3ลัง 5,301</v>
       </c>
       <c r="F207">
-        <v>2820</v>
+        <v>6132</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>08/05/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="B208" t="str">
         <v>May26</v>
       </c>
       <c r="C208" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D208" t="str">
-        <v>Other</v>
+        <v>Packaging</v>
       </c>
       <c r="E208" t="str">
-        <v>ค่าทำความสะอาดตึกชั้น 1</v>
+        <v>ถุงมือ 20 กล่อง 2246 ฝา1ลัง 969</v>
       </c>
       <c r="F208">
-        <v>2700</v>
+        <v>4496</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>08/05/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="B209" t="str">
         <v>May26</v>
@@ -5306,18 +5306,18 @@
         <v>COGS</v>
       </c>
       <c r="D209" t="str">
-        <v>Watermelon</v>
+        <v>Transportation</v>
       </c>
       <c r="E209" t="str">
-        <v>4-5-2569 เบอร์ 70฿ 60 ลูก ยอด 4,200</v>
+        <v>Lalamove</v>
       </c>
       <c r="F209">
-        <v>8200</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>09/05/2026</v>
+        <v>10/05/2026</v>
       </c>
       <c r="B210" t="str">
         <v>May26</v>
@@ -5329,15 +5329,15 @@
         <v>Other</v>
       </c>
       <c r="E210" t="str">
-        <v>พรหมเช็ดเท้า 1 ผืน</v>
+        <v>ไฟ 2อัน 422</v>
       </c>
       <c r="F210">
-        <v>372</v>
+        <v>838</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>09/05/2026</v>
+        <v>11/05/2026</v>
       </c>
       <c r="B211" t="str">
         <v>May26</v>
@@ -5346,18 +5346,18 @@
         <v>COGS</v>
       </c>
       <c r="D211" t="str">
-        <v>Milk/Conden</v>
+        <v>Guava</v>
       </c>
       <c r="E211" t="str">
-        <v>นมข้นจืด 1ลัง 636</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F211">
-        <v>1122</v>
+        <v>600</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>09/05/2026</v>
+        <v>11/05/2026</v>
       </c>
       <c r="B212" t="str">
         <v>May26</v>
@@ -5366,18 +5366,18 @@
         <v>COGS</v>
       </c>
       <c r="D212" t="str">
-        <v>Packaging</v>
+        <v>Mango</v>
       </c>
       <c r="E212" t="str">
-        <v>นมข้น 3 ลัง 2568</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F212">
-        <v>4875</v>
+        <v>910</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>09/05/2026</v>
+        <v>11/05/2026</v>
       </c>
       <c r="B213" t="str">
         <v>May26</v>
@@ -5386,18 +5386,18 @@
         <v>COGS</v>
       </c>
       <c r="D213" t="str">
-        <v>Packaging</v>
+        <v>Watermelon</v>
       </c>
       <c r="E213" t="str">
-        <v>แก้ว3ลัง 5,301</v>
+        <v>แตงโม 4000 วันที่ 9-5-26</v>
       </c>
       <c r="F213">
-        <v>6132</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>09/05/2026</v>
+        <v>12/05/2026</v>
       </c>
       <c r="B214" t="str">
         <v>May26</v>
@@ -5406,58 +5406,58 @@
         <v>COGS</v>
       </c>
       <c r="D214" t="str">
-        <v>Packaging</v>
+        <v>Coconut Meat</v>
       </c>
       <c r="E214" t="str">
-        <v>ถุงมือ 20 กล่อง 2246 ฝา1ลัง 969</v>
+        <v>เนื้อมะพร้าว 1 ลัง</v>
       </c>
       <c r="F214">
-        <v>4496</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>09/05/2026</v>
+        <v>13/05/2026</v>
       </c>
       <c r="B215" t="str">
         <v>May26</v>
       </c>
       <c r="C215" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D215" t="str">
-        <v>Transportation</v>
+        <v>Other</v>
       </c>
       <c r="E215" t="str">
-        <v>Lalamove</v>
+        <v>ที่หนีบ 6ตัว 374 บาท</v>
       </c>
       <c r="F215">
-        <v>2000</v>
+        <v>374</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>10/05/2026</v>
+        <v>13/05/2026</v>
       </c>
       <c r="B216" t="str">
         <v>May26</v>
       </c>
       <c r="C216" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D216" t="str">
-        <v>Other</v>
+        <v>Pineapple</v>
       </c>
       <c r="E216" t="str">
-        <v>ไฟ 2อัน 422</v>
+        <v>09/05/26 สับปะรด 2 ตะกร้า</v>
       </c>
       <c r="F216">
-        <v>838</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>11/05/2026</v>
+        <v>14/05/2026</v>
       </c>
       <c r="B217" t="str">
         <v>May26</v>
@@ -5466,58 +5466,58 @@
         <v>COGS</v>
       </c>
       <c r="D217" t="str">
-        <v>Guava</v>
+        <v>Watermelon</v>
       </c>
       <c r="E217" t="str">
-        <v>ฝรั่ง 1 ตะกร้า</v>
+        <v>11-5-2569 50 ลูก ยอด 4,000</v>
       </c>
       <c r="F217">
-        <v>600</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>11/05/2026</v>
+        <v>14/05/2026</v>
       </c>
       <c r="B218" t="str">
         <v>May26</v>
       </c>
       <c r="C218" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D218" t="str">
-        <v>Mango</v>
+        <v>Rental</v>
       </c>
       <c r="E218" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>ค่าเช่าร้าน 1 พ.ค.</v>
       </c>
       <c r="F218">
-        <v>910</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>11/05/2026</v>
+        <v>14/05/2026</v>
       </c>
       <c r="B219" t="str">
         <v>May26</v>
       </c>
       <c r="C219" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D219" t="str">
-        <v>Watermelon</v>
+        <v>Rental</v>
       </c>
       <c r="E219" t="str">
-        <v>แตงโม 4000 วันที่ 9-5-26</v>
+        <v>ค่าเช่าคลัง พ.ค. (B1 ครึ่งหนึ่ง)</v>
       </c>
       <c r="F219">
-        <v>4000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>12/05/2026</v>
+        <v>14/05/2026</v>
       </c>
       <c r="B220" t="str">
         <v>May26</v>
@@ -5526,38 +5526,38 @@
         <v>COGS</v>
       </c>
       <c r="D220" t="str">
-        <v>Coconut Meat</v>
+        <v>Guava</v>
       </c>
       <c r="E220" t="str">
-        <v>เนื้อมะพร้าว 1 ลัง</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F220">
-        <v>3500</v>
+        <v>600</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>13/05/2026</v>
+        <v>14/05/2026</v>
       </c>
       <c r="B221" t="str">
         <v>May26</v>
       </c>
       <c r="C221" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D221" t="str">
-        <v>Other</v>
+        <v>Apple</v>
       </c>
       <c r="E221" t="str">
-        <v>ที่หนีบ 6ตัว 374 บาท</v>
+        <v>แอปเปิ้ล 3 ลัง</v>
       </c>
       <c r="F221">
-        <v>374</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>13/05/2026</v>
+        <v>14/05/2026</v>
       </c>
       <c r="B222" t="str">
         <v>May26</v>
@@ -5566,18 +5566,18 @@
         <v>COGS</v>
       </c>
       <c r="D222" t="str">
-        <v>Pineapple</v>
+        <v>Mango</v>
       </c>
       <c r="E222" t="str">
-        <v>09/05/26 สับปะรด 2 ตะกร้า</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F222">
-        <v>1008</v>
+        <v>875</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>14/05/2026</v>
+        <v>15/05/2026</v>
       </c>
       <c r="B223" t="str">
         <v>May26</v>
@@ -5586,38 +5586,38 @@
         <v>COGS</v>
       </c>
       <c r="D223" t="str">
-        <v>Watermelon</v>
+        <v>Orange</v>
       </c>
       <c r="E223" t="str">
-        <v>11-5-2569 50 ลูก ยอด 4,000</v>
+        <v>15/05/69</v>
       </c>
       <c r="F223">
-        <v>8000</v>
+        <v>15730</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>14/05/2026</v>
+        <v>15/05/2026</v>
       </c>
       <c r="B224" t="str">
         <v>May26</v>
       </c>
       <c r="C224" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D224" t="str">
-        <v>Rental</v>
+        <v>Orange</v>
       </c>
       <c r="E224" t="str">
-        <v>ค่าเช่าร้าน 1 พ.ค.</v>
+        <v>05/05/69 ส้ม 30x22กก 660กกx30</v>
       </c>
       <c r="F224">
-        <v>35000</v>
+        <v>21450</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>14/05/2026</v>
+        <v>16/05/2026</v>
       </c>
       <c r="B225" t="str">
         <v>May26</v>
@@ -5626,18 +5626,18 @@
         <v>OPEX</v>
       </c>
       <c r="D225" t="str">
-        <v>Rental</v>
+        <v>Other</v>
       </c>
       <c r="E225" t="str">
-        <v>ค่าเช่าคลัง พ.ค. (B1 ครึ่งหนึ่ง)</v>
+        <v>Police fees -2000 2 head</v>
       </c>
       <c r="F225">
-        <v>6000</v>
+        <v>4290</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>14/05/2026</v>
+        <v>16/05/2026</v>
       </c>
       <c r="B226" t="str">
         <v>May26</v>
@@ -5646,18 +5646,18 @@
         <v>COGS</v>
       </c>
       <c r="D226" t="str">
-        <v>Guava</v>
+        <v>Coconut</v>
       </c>
       <c r="E226" t="str">
-        <v>ฝรั่ง 1 ตะกร้า</v>
+        <v>มะพร้าว 20 โล</v>
       </c>
       <c r="F226">
-        <v>600</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>14/05/2026</v>
+        <v>16/05/2026</v>
       </c>
       <c r="B227" t="str">
         <v>May26</v>
@@ -5666,18 +5666,18 @@
         <v>COGS</v>
       </c>
       <c r="D227" t="str">
-        <v>Apple</v>
+        <v>Watermelon</v>
       </c>
       <c r="E227" t="str">
-        <v>แอปเปิ้ล 3 ลัง</v>
+        <v>14/05/26 18 ลูก 504 บาท 16/05/26 18 ลูก</v>
       </c>
       <c r="F227">
-        <v>1050</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>14/05/2026</v>
+        <v>16/05/2026</v>
       </c>
       <c r="B228" t="str">
         <v>May26</v>
@@ -5689,7 +5689,7 @@
         <v>Mango</v>
       </c>
       <c r="E228" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>มะม่วง 1</v>
       </c>
       <c r="F228">
         <v>875</v>
@@ -5697,7 +5697,7 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>15/05/2026</v>
+        <v>19/05/2026</v>
       </c>
       <c r="B229" t="str">
         <v>May26</v>
@@ -5706,18 +5706,18 @@
         <v>COGS</v>
       </c>
       <c r="D229" t="str">
-        <v>Orange</v>
+        <v>Mango</v>
       </c>
       <c r="E229" t="str">
-        <v>15/05/69</v>
+        <v>มะม่วง 1 ลัง (25 โล)</v>
       </c>
       <c r="F229">
-        <v>15730</v>
+        <v>875</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>15/05/2026</v>
+        <v>19/05/2026</v>
       </c>
       <c r="B230" t="str">
         <v>May26</v>
@@ -5726,38 +5726,38 @@
         <v>COGS</v>
       </c>
       <c r="D230" t="str">
-        <v>Orange</v>
+        <v>Guava</v>
       </c>
       <c r="E230" t="str">
-        <v>05/05/69 ส้ม 30x22กก 660กกx30</v>
+        <v>ฝรั่ง 1 ลัง</v>
       </c>
       <c r="F230">
-        <v>21450</v>
+        <v>600</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>16/05/2026</v>
+        <v>19/05/2026</v>
       </c>
       <c r="B231" t="str">
         <v>May26</v>
       </c>
       <c r="C231" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D231" t="str">
-        <v>Other</v>
+        <v>Apple</v>
       </c>
       <c r="E231" t="str">
-        <v>Police fees -2000 2 head</v>
+        <v>แอปเปิ้ล 4 ลังครับ</v>
       </c>
       <c r="F231">
-        <v>4290</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>16/05/2026</v>
+        <v>19/05/2026</v>
       </c>
       <c r="B232" t="str">
         <v>May26</v>
@@ -5766,18 +5766,18 @@
         <v>COGS</v>
       </c>
       <c r="D232" t="str">
-        <v>Coconut</v>
+        <v>Pineapple</v>
       </c>
       <c r="E232" t="str">
-        <v>มะพร้าว 20 โล</v>
+        <v>36*18 648</v>
       </c>
       <c r="F232">
-        <v>2400</v>
+        <v>648</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>16/05/2026</v>
+        <v>22/05/2026</v>
       </c>
       <c r="B233" t="str">
         <v>May26</v>
@@ -5786,18 +5786,18 @@
         <v>COGS</v>
       </c>
       <c r="D233" t="str">
-        <v>Watermelon</v>
+        <v>Apple</v>
       </c>
       <c r="E233" t="str">
-        <v>14/05/26 18 ลูก 504 บาท 16/05/26 18 ลูก</v>
+        <v>แอปเปิ้ล 2 ลัง</v>
       </c>
       <c r="F233">
-        <v>1008</v>
+        <v>700</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>16/05/2026</v>
+        <v>22/05/2026</v>
       </c>
       <c r="B234" t="str">
         <v>May26</v>
@@ -5806,18 +5806,18 @@
         <v>COGS</v>
       </c>
       <c r="D234" t="str">
-        <v>Mango</v>
+        <v>Pineapple</v>
       </c>
       <c r="E234" t="str">
-        <v>มะม่วง 1</v>
+        <v>สับปะรด 18 ลูก</v>
       </c>
       <c r="F234">
-        <v>875</v>
+        <v>522</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>19/05/2026</v>
+        <v>22/05/2026</v>
       </c>
       <c r="B235" t="str">
         <v>May26</v>
@@ -5829,15 +5829,15 @@
         <v>Mango</v>
       </c>
       <c r="E235" t="str">
-        <v>มะม่วง 1 ลัง (25 โล)</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F235">
-        <v>875</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>19/05/2026</v>
+        <v>22/05/2026</v>
       </c>
       <c r="B236" t="str">
         <v>May26</v>
@@ -5846,18 +5846,18 @@
         <v>COGS</v>
       </c>
       <c r="D236" t="str">
-        <v>Guava</v>
+        <v>Watermelon</v>
       </c>
       <c r="E236" t="str">
-        <v>ฝรั่ง 1 ลัง</v>
+        <v>16-5-2569ยอด 4,000฿</v>
       </c>
       <c r="F236">
-        <v>600</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>19/05/2026</v>
+        <v>22/05/2026</v>
       </c>
       <c r="B237" t="str">
         <v>May26</v>
@@ -5866,18 +5866,18 @@
         <v>COGS</v>
       </c>
       <c r="D237" t="str">
-        <v>Apple</v>
+        <v>Guava</v>
       </c>
       <c r="E237" t="str">
-        <v>แอปเปิ้ล 4 ลังครับ</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F237">
-        <v>1400</v>
+        <v>600</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>19/05/2026</v>
+        <v>22/05/2026</v>
       </c>
       <c r="B238" t="str">
         <v>May26</v>
@@ -5886,18 +5886,18 @@
         <v>COGS</v>
       </c>
       <c r="D238" t="str">
-        <v>Pineapple</v>
+        <v>Transportation</v>
       </c>
       <c r="E238" t="str">
-        <v>36*18 648</v>
+        <v>ค่าขนส่ง</v>
       </c>
       <c r="F238">
-        <v>648</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>22/05/2026</v>
+        <v>23/05/2026</v>
       </c>
       <c r="B239" t="str">
         <v>May26</v>
@@ -5906,18 +5906,18 @@
         <v>COGS</v>
       </c>
       <c r="D239" t="str">
-        <v>Apple</v>
+        <v>Packaging</v>
       </c>
       <c r="E239" t="str">
-        <v>แอปเปิ้ล 2 ลัง</v>
+        <v>แก้ว 3 ลัง</v>
       </c>
       <c r="F239">
-        <v>700</v>
+        <v>4680</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>22/05/2026</v>
+        <v>23/05/2026</v>
       </c>
       <c r="B240" t="str">
         <v>May26</v>
@@ -5926,18 +5926,18 @@
         <v>COGS</v>
       </c>
       <c r="D240" t="str">
-        <v>Pineapple</v>
+        <v>Packaging</v>
       </c>
       <c r="E240" t="str">
-        <v>สับปะรด 18 ลูก</v>
+        <v>ฝา1 788</v>
       </c>
       <c r="F240">
-        <v>522</v>
+        <v>2902</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>22/05/2026</v>
+        <v>23/05/2026</v>
       </c>
       <c r="B241" t="str">
         <v>May26</v>
@@ -5946,18 +5946,18 @@
         <v>COGS</v>
       </c>
       <c r="D241" t="str">
-        <v>Mango</v>
+        <v>Packaging</v>
       </c>
       <c r="E241" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>หลอด20 แพค (767)</v>
       </c>
       <c r="F241">
-        <v>1000</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>22/05/2026</v>
+        <v>25/05/2026</v>
       </c>
       <c r="B242" t="str">
         <v>May26</v>
@@ -5966,18 +5966,18 @@
         <v>COGS</v>
       </c>
       <c r="D242" t="str">
-        <v>Watermelon</v>
+        <v>Pineapple</v>
       </c>
       <c r="E242" t="str">
-        <v>16-5-2569ยอด 4,000฿</v>
+        <v>สับปะรด 18 ลูก</v>
       </c>
       <c r="F242">
-        <v>12000</v>
+        <v>594</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>22/05/2026</v>
+        <v>25/05/2026</v>
       </c>
       <c r="B243" t="str">
         <v>May26</v>
@@ -5986,18 +5986,18 @@
         <v>COGS</v>
       </c>
       <c r="D243" t="str">
-        <v>Guava</v>
+        <v>Apple</v>
       </c>
       <c r="E243" t="str">
-        <v>ฝรั่ง 1 ตะกร้า</v>
+        <v>แอปเปิ้ล 3 ลังครับ</v>
       </c>
       <c r="F243">
-        <v>600</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>22/05/2026</v>
+        <v>25/05/2026</v>
       </c>
       <c r="B244" t="str">
         <v>May26</v>
@@ -6006,18 +6006,18 @@
         <v>COGS</v>
       </c>
       <c r="D244" t="str">
-        <v>Transportation</v>
+        <v>Orange</v>
       </c>
       <c r="E244" t="str">
-        <v>ค่าขนส่ง</v>
+        <v>ค่าส่งส้ม Lalamove หักผ่านบัตร</v>
       </c>
       <c r="F244">
-        <v>2000</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>23/05/2026</v>
+        <v>25/05/2026</v>
       </c>
       <c r="B245" t="str">
         <v>May26</v>
@@ -6026,38 +6026,38 @@
         <v>COGS</v>
       </c>
       <c r="D245" t="str">
-        <v>Packaging</v>
+        <v>Orange</v>
       </c>
       <c r="E245" t="str">
-        <v>แก้ว 3 ลัง</v>
+        <v>24/05/69</v>
       </c>
       <c r="F245">
-        <v>4680</v>
+        <v>15015</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>23/05/2026</v>
+        <v>25/05/2026</v>
       </c>
       <c r="B246" t="str">
         <v>May26</v>
       </c>
       <c r="C246" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D246" t="str">
-        <v>Packaging</v>
+        <v>Salary</v>
       </c>
       <c r="E246" t="str">
-        <v>ฝา1 788</v>
+        <v>เงินเดือนซี เดือนพ.ค. (แก้ไข: ยืนยัน 24,000)</v>
       </c>
       <c r="F246">
-        <v>2902</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>23/05/2026</v>
+        <v>25/05/2026</v>
       </c>
       <c r="B247" t="str">
         <v>May26</v>
@@ -6066,13 +6066,13 @@
         <v>COGS</v>
       </c>
       <c r="D247" t="str">
-        <v>Packaging</v>
+        <v>Guava</v>
       </c>
       <c r="E247" t="str">
-        <v>หลอด20 แพค (767)</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F247">
-        <v>1502</v>
+        <v>600</v>
       </c>
     </row>
     <row r="248">
@@ -6086,58 +6086,58 @@
         <v>COGS</v>
       </c>
       <c r="D248" t="str">
-        <v>Pineapple</v>
+        <v>Mango</v>
       </c>
       <c r="E248" t="str">
-        <v>สับปะรด 18 ลูก</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F248">
-        <v>594</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>25/05/2026</v>
+        <v>27/05/2026</v>
       </c>
       <c r="B249" t="str">
         <v>May26</v>
       </c>
       <c r="C249" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D249" t="str">
-        <v>Apple</v>
+        <v>Salary</v>
       </c>
       <c r="E249" t="str">
-        <v>แอปเปิ้ล 3 ลังครับ</v>
+        <v>เงินเดือนเมน 5/26</v>
       </c>
       <c r="F249">
-        <v>1050</v>
+        <v>19000</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>25/05/2026</v>
+        <v>28/05/2026</v>
       </c>
       <c r="B250" t="str">
         <v>May26</v>
       </c>
       <c r="C250" t="str">
-        <v>COGS</v>
+        <v>CAPEX</v>
       </c>
       <c r="D250" t="str">
-        <v>Orange</v>
+        <v>Investment</v>
       </c>
       <c r="E250" t="str">
-        <v>ค่าส่งส้ม Lalamove หักผ่านบัตร</v>
+        <v>เครื่องสกัดเย็น 1</v>
       </c>
       <c r="F250">
-        <v>1245</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>25/05/2026</v>
+        <v>28/05/2026</v>
       </c>
       <c r="B251" t="str">
         <v>May26</v>
@@ -6146,38 +6146,38 @@
         <v>COGS</v>
       </c>
       <c r="D251" t="str">
-        <v>Orange</v>
+        <v>Coconut</v>
       </c>
       <c r="E251" t="str">
-        <v>24/05/69</v>
+        <v>มะพร้าวถอดเสื้อ 23 ลูก *35 ราคา 805 ค่าส่ง 150</v>
       </c>
       <c r="F251">
-        <v>15015</v>
+        <v>955</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>25/05/2026</v>
+        <v>30/05/2026</v>
       </c>
       <c r="B252" t="str">
         <v>May26</v>
       </c>
       <c r="C252" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D252" t="str">
-        <v>Salary</v>
+        <v>Pineapple</v>
       </c>
       <c r="E252" t="str">
-        <v>เงินเดือนซี เดือนพ.ค. (แก้ไข: ยืนยัน 24,000)</v>
+        <v>สับปะรด 18 ลูก</v>
       </c>
       <c r="F252">
-        <v>24000</v>
+        <v>576</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>25/05/2026</v>
+        <v>30/05/2026</v>
       </c>
       <c r="B253" t="str">
         <v>May26</v>
@@ -6186,101 +6186,101 @@
         <v>COGS</v>
       </c>
       <c r="D253" t="str">
-        <v>Guava</v>
+        <v>Mango</v>
       </c>
       <c r="E253" t="str">
-        <v>ฝรั่ง 1 ตะกร้า</v>
+        <v>มะม่วง 1 ตะกร้า</v>
       </c>
       <c r="F253">
-        <v>600</v>
+        <v>960</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>25/05/2026</v>
+        <v>30/05/2026</v>
       </c>
       <c r="B254" t="str">
         <v>May26</v>
       </c>
       <c r="C254" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D254" t="str">
-        <v>Mango</v>
+        <v>Other</v>
       </c>
       <c r="E254" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>Unknown</v>
       </c>
       <c r="F254">
-        <v>1000</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>27/05/2026</v>
+        <v>30/05/2026</v>
       </c>
       <c r="B255" t="str">
         <v>May26</v>
       </c>
       <c r="C255" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D255" t="str">
-        <v>Salary</v>
+        <v>Guava</v>
       </c>
       <c r="E255" t="str">
-        <v>เงินเดือนเมน 5/26</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F255">
-        <v>19000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>28/05/2026</v>
+        <v>31/05/2026</v>
       </c>
       <c r="B256" t="str">
         <v>May26</v>
       </c>
       <c r="C256" t="str">
-        <v>CAPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D256" t="str">
-        <v>Investment</v>
+        <v>Stock</v>
       </c>
       <c r="E256" t="str">
-        <v>เครื่องสกัดเย็น 1</v>
+        <v>Stock Adjustment (Allocated to B2)</v>
       </c>
       <c r="F256">
-        <v>1065</v>
+        <v>-4830</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>28/05/2026</v>
+        <v>01/06/2026</v>
       </c>
       <c r="B257" t="str">
         <v>May26</v>
       </c>
       <c r="C257" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D257" t="str">
-        <v>Coconut</v>
+        <v>Salary</v>
       </c>
       <c r="E257" t="str">
-        <v>มะพร้าวถอดเสื้อ 23 ลูก *35 ราคา 805 ค่าส่ง 150</v>
+        <v>Unknown</v>
       </c>
       <c r="F257">
-        <v>955</v>
+        <v>0</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>30/05/2026</v>
+        <v>02/06/2026</v>
       </c>
       <c r="B258" t="str">
-        <v>May26</v>
+        <v>Jun26</v>
       </c>
       <c r="C258" t="str">
         <v>COGS</v>
@@ -6289,115 +6289,115 @@
         <v>Pineapple</v>
       </c>
       <c r="E258" t="str">
-        <v>สับปะรด 18 ลูก</v>
+        <v>สับปะรด ราคา 31*18 ลูก 558</v>
       </c>
       <c r="F258">
-        <v>576</v>
+        <v>558</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>30/05/2026</v>
+        <v>02/06/2026</v>
       </c>
       <c r="B259" t="str">
-        <v>May26</v>
+        <v>Jun26</v>
       </c>
       <c r="C259" t="str">
         <v>COGS</v>
       </c>
       <c r="D259" t="str">
-        <v>Mango</v>
+        <v>Guava</v>
       </c>
       <c r="E259" t="str">
-        <v>มะม่วง 1 ตะกร้า</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F259">
-        <v>960</v>
+        <v>600</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>30/05/2026</v>
+        <v>02/06/2026</v>
       </c>
       <c r="B260" t="str">
-        <v>May26</v>
+        <v>Jun26</v>
       </c>
       <c r="C260" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D260" t="str">
-        <v>Other</v>
+        <v>Watermelon</v>
       </c>
       <c r="E260" t="str">
-        <v>Unknown</v>
+        <v>แตงโม 160 ลูก (25-5-2569: 80 ลูก, 30-5-2569: 80 ลูก)</v>
       </c>
       <c r="F260">
-        <v>1050</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>30/05/2026</v>
+        <v>04/06/2026</v>
       </c>
       <c r="B261" t="str">
-        <v>May26</v>
+        <v>Jun26</v>
       </c>
       <c r="C261" t="str">
         <v>COGS</v>
       </c>
       <c r="D261" t="str">
-        <v>Guava</v>
+        <v>Watermelon</v>
       </c>
       <c r="E261" t="str">
-        <v>ฝรั่ง 1 ตะกร้า</v>
+        <v>สลิปรวม: แตงโม 750 (audit fix, was bundled into Pineapple line)</v>
       </c>
       <c r="F261">
-        <v>600</v>
+        <v>750</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>31/05/2026</v>
+        <v>04/06/2026</v>
       </c>
       <c r="B262" t="str">
-        <v>May26</v>
+        <v>Jun26</v>
       </c>
       <c r="C262" t="str">
         <v>COGS</v>
       </c>
       <c r="D262" t="str">
-        <v>Stock</v>
+        <v>Guava</v>
       </c>
       <c r="E262" t="str">
-        <v>Stock Adjustment (Allocated to B2)</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F262">
-        <v>-4830</v>
+        <v>700</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>01/06/2026</v>
+        <v>04/06/2026</v>
       </c>
       <c r="B263" t="str">
-        <v>May26</v>
+        <v>Jun26</v>
       </c>
       <c r="C263" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D263" t="str">
-        <v>Salary</v>
+        <v>Mango</v>
       </c>
       <c r="E263" t="str">
-        <v>Unknown</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F263">
-        <v>0</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>02/06/2026</v>
+        <v>04/06/2026</v>
       </c>
       <c r="B264" t="str">
         <v>Jun26</v>
@@ -6406,18 +6406,18 @@
         <v>COGS</v>
       </c>
       <c r="D264" t="str">
-        <v>Pineapple</v>
+        <v>Apple</v>
       </c>
       <c r="E264" t="str">
-        <v>สับปะรด ราคา 31*18 ลูก 558</v>
+        <v>แอพเปิ้ล 4 ลัง</v>
       </c>
       <c r="F264">
-        <v>558</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>02/06/2026</v>
+        <v>04/06/2026</v>
       </c>
       <c r="B265" t="str">
         <v>Jun26</v>
@@ -6426,18 +6426,18 @@
         <v>COGS</v>
       </c>
       <c r="D265" t="str">
-        <v>Guava</v>
+        <v>Pineapple</v>
       </c>
       <c r="E265" t="str">
-        <v>ฝรั่ง 1 ตะกร้า</v>
+        <v>สับปะรด 2 ลูก</v>
       </c>
       <c r="F265">
-        <v>600</v>
+        <v>36</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>02/06/2026</v>
+        <v>04/06/2026</v>
       </c>
       <c r="B266" t="str">
         <v>Jun26</v>
@@ -6446,18 +6446,18 @@
         <v>COGS</v>
       </c>
       <c r="D266" t="str">
-        <v>Watermelon</v>
+        <v>Packaging</v>
       </c>
       <c r="E266" t="str">
-        <v>แตงโม 160 ลูก (25-5-2569: 80 ลูก, 30-5-2569: 80 ลูก)</v>
+        <v>ขวดใหญ่ 1000ml 98 ใบ 364 ถุงเล็ก 20</v>
       </c>
       <c r="F266">
-        <v>8000</v>
+        <v>764</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>04/06/2026</v>
+        <v>05/06/2026</v>
       </c>
       <c r="B267" t="str">
         <v>Jun26</v>
@@ -6466,18 +6466,18 @@
         <v>COGS</v>
       </c>
       <c r="D267" t="str">
-        <v>Watermelon</v>
+        <v>Pineapple</v>
       </c>
       <c r="E267" t="str">
-        <v>สลิปรวม: แตงโม 750 (audit fix, was bundled into Pineapple line)</v>
+        <v>สับปะรด 33*18 รวม 594</v>
       </c>
       <c r="F267">
-        <v>750</v>
+        <v>594</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>04/06/2026</v>
+        <v>05/06/2026</v>
       </c>
       <c r="B268" t="str">
         <v>Jun26</v>
@@ -6486,18 +6486,18 @@
         <v>COGS</v>
       </c>
       <c r="D268" t="str">
-        <v>Guava</v>
+        <v>Watermelon</v>
       </c>
       <c r="E268" t="str">
-        <v>ฝรั่ง 1 ตะกร้า</v>
+        <v>แตงโม 100 ลูก (2-6-2569: 50 ลูก, 4-6-2569: 50 ลูก)</v>
       </c>
       <c r="F268">
-        <v>700</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>04/06/2026</v>
+        <v>07/06/2026</v>
       </c>
       <c r="B269" t="str">
         <v>Jun26</v>
@@ -6506,18 +6506,18 @@
         <v>COGS</v>
       </c>
       <c r="D269" t="str">
-        <v>Mango</v>
+        <v>Orange</v>
       </c>
       <c r="E269" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>ส้ม 20x22กก 440กกx30 13,200บาท</v>
       </c>
       <c r="F269">
-        <v>1040</v>
+        <v>14300</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>04/06/2026</v>
+        <v>08/06/2026</v>
       </c>
       <c r="B270" t="str">
         <v>Jun26</v>
@@ -6526,18 +6526,18 @@
         <v>COGS</v>
       </c>
       <c r="D270" t="str">
-        <v>Apple</v>
+        <v>Transportation</v>
       </c>
       <c r="E270" t="str">
-        <v>แอพเปิ้ล 4 ลัง</v>
+        <v>Lalamove</v>
       </c>
       <c r="F270">
-        <v>1400</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>04/06/2026</v>
+        <v>08/06/2026</v>
       </c>
       <c r="B271" t="str">
         <v>Jun26</v>
@@ -6546,38 +6546,38 @@
         <v>COGS</v>
       </c>
       <c r="D271" t="str">
-        <v>Pineapple</v>
+        <v>Stock</v>
       </c>
       <c r="E271" t="str">
-        <v>สับปะรด 2 ลูก</v>
+        <v>Stock June 2026 (B1 ครึ่งหนึ่ง 6,000; B2 ถืออีก 6,000)</v>
       </c>
       <c r="F271">
-        <v>36</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>04/06/2026</v>
+        <v>08/06/2026</v>
       </c>
       <c r="B272" t="str">
         <v>Jun26</v>
       </c>
       <c r="C272" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D272" t="str">
-        <v>Packaging</v>
+        <v>Rental</v>
       </c>
       <c r="E272" t="str">
-        <v>ขวดใหญ่ 1000ml 98 ใบ 364 ถุงเล็ก 20</v>
+        <v>ค่าเช่าร้านเดือน June (06) b1 35000</v>
       </c>
       <c r="F272">
-        <v>764</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>05/06/2026</v>
+        <v>08/06/2026</v>
       </c>
       <c r="B273" t="str">
         <v>Jun26</v>
@@ -6589,15 +6589,15 @@
         <v>Pineapple</v>
       </c>
       <c r="E273" t="str">
-        <v>สับปะรด 33*18 รวม 594</v>
+        <v>สับปะรด 15 ลูก</v>
       </c>
       <c r="F273">
-        <v>594</v>
+        <v>504</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>05/06/2026</v>
+        <v>08/06/2026</v>
       </c>
       <c r="B274" t="str">
         <v>Jun26</v>
@@ -6606,18 +6606,18 @@
         <v>COGS</v>
       </c>
       <c r="D274" t="str">
-        <v>Watermelon</v>
+        <v>Mango</v>
       </c>
       <c r="E274" t="str">
-        <v>แตงโม 100 ลูก (2-6-2569: 50 ลูก, 4-6-2569: 50 ลูก)</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F274">
-        <v>8000</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>07/06/2026</v>
+        <v>08/06/2026</v>
       </c>
       <c r="B275" t="str">
         <v>Jun26</v>
@@ -6626,13 +6626,13 @@
         <v>COGS</v>
       </c>
       <c r="D275" t="str">
-        <v>Orange</v>
+        <v>Apple</v>
       </c>
       <c r="E275" t="str">
-        <v>ส้ม 20x22กก 440กกx30 13,200บาท</v>
+        <v>แอปเปิ้ล 5 ลัง</v>
       </c>
       <c r="F275">
-        <v>14300</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="276">
@@ -6646,18 +6646,18 @@
         <v>COGS</v>
       </c>
       <c r="D276" t="str">
-        <v>Transportation</v>
+        <v>Guava</v>
       </c>
       <c r="E276" t="str">
-        <v>Lalamove</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F276">
-        <v>2000</v>
+        <v>700</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>08/06/2026</v>
+        <v>09/06/2026</v>
       </c>
       <c r="B277" t="str">
         <v>Jun26</v>
@@ -6666,38 +6666,38 @@
         <v>COGS</v>
       </c>
       <c r="D277" t="str">
-        <v>Stock</v>
+        <v>Packaging</v>
       </c>
       <c r="E277" t="str">
-        <v>Stock June 2026 (B1 ครึ่งหนึ่ง 6,000; B2 ถืออีก 6,000)</v>
+        <v>แก้ว 1937*3 รวม 5,811</v>
       </c>
       <c r="F277">
-        <v>6000</v>
+        <v>6659</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>08/06/2026</v>
+        <v>09/06/2026</v>
       </c>
       <c r="B278" t="str">
         <v>Jun26</v>
       </c>
       <c r="C278" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D278" t="str">
-        <v>Rental</v>
+        <v>Packaging</v>
       </c>
       <c r="E278" t="str">
-        <v>ค่าเช่าร้านเดือน June (06) b1 35000</v>
+        <v>หลอด 20 แพ็ก 671</v>
       </c>
       <c r="F278">
-        <v>35000</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>08/06/2026</v>
+        <v>09/06/2026</v>
       </c>
       <c r="B279" t="str">
         <v>Jun26</v>
@@ -6706,18 +6706,18 @@
         <v>COGS</v>
       </c>
       <c r="D279" t="str">
-        <v>Pineapple</v>
+        <v>Packaging</v>
       </c>
       <c r="E279" t="str">
-        <v>สับปะรด 15 ลูก</v>
+        <v>ฝา1 714</v>
       </c>
       <c r="F279">
-        <v>504</v>
+        <v>714</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>08/06/2026</v>
+        <v>09/06/2026</v>
       </c>
       <c r="B280" t="str">
         <v>Jun26</v>
@@ -6726,18 +6726,18 @@
         <v>COGS</v>
       </c>
       <c r="D280" t="str">
-        <v>Mango</v>
+        <v>Packaging</v>
       </c>
       <c r="E280" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>ถุงขยะ 4แพคใหญ่ 1019</v>
       </c>
       <c r="F280">
-        <v>1170</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>08/06/2026</v>
+        <v>11/06/2026</v>
       </c>
       <c r="B281" t="str">
         <v>Jun26</v>
@@ -6746,18 +6746,18 @@
         <v>COGS</v>
       </c>
       <c r="D281" t="str">
-        <v>Apple</v>
+        <v>Guava</v>
       </c>
       <c r="E281" t="str">
-        <v>แอปเปิ้ล 5 ลัง</v>
+        <v>ฝรั่ง 1 ลัง</v>
       </c>
       <c r="F281">
-        <v>1750</v>
+        <v>700</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>08/06/2026</v>
+        <v>12/06/2026</v>
       </c>
       <c r="B282" t="str">
         <v>Jun26</v>
@@ -6766,18 +6766,18 @@
         <v>COGS</v>
       </c>
       <c r="D282" t="str">
-        <v>Guava</v>
+        <v>Coconut Water</v>
       </c>
       <c r="E282" t="str">
-        <v>ฝรั่ง 1 ตะกร้า</v>
+        <v>น้ำมะพร้าว50*20 1,000</v>
       </c>
       <c r="F282">
-        <v>700</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>09/06/2026</v>
+        <v>12/06/2026</v>
       </c>
       <c r="B283" t="str">
         <v>Jun26</v>
@@ -6786,18 +6786,18 @@
         <v>COGS</v>
       </c>
       <c r="D283" t="str">
-        <v>Packaging</v>
+        <v>Mango</v>
       </c>
       <c r="E283" t="str">
-        <v>แก้ว 1937*3 รวม 5,811</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F283">
-        <v>6659</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>09/06/2026</v>
+        <v>12/06/2026</v>
       </c>
       <c r="B284" t="str">
         <v>Jun26</v>
@@ -6806,18 +6806,18 @@
         <v>COGS</v>
       </c>
       <c r="D284" t="str">
-        <v>Packaging</v>
+        <v>Apple</v>
       </c>
       <c r="E284" t="str">
-        <v>หลอด 20 แพ็ก 671</v>
+        <v>แอปเปิ้ล 5 ลัง</v>
       </c>
       <c r="F284">
-        <v>1149</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>09/06/2026</v>
+        <v>12/06/2026</v>
       </c>
       <c r="B285" t="str">
         <v>Jun26</v>
@@ -6826,18 +6826,18 @@
         <v>COGS</v>
       </c>
       <c r="D285" t="str">
-        <v>Packaging</v>
+        <v>Pineapple</v>
       </c>
       <c r="E285" t="str">
-        <v>ฝา1 714</v>
+        <v>สับปะรด 19 ลูก</v>
       </c>
       <c r="F285">
-        <v>714</v>
+        <v>950</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>09/06/2026</v>
+        <v>14/06/2026</v>
       </c>
       <c r="B286" t="str">
         <v>Jun26</v>
@@ -6846,18 +6846,18 @@
         <v>COGS</v>
       </c>
       <c r="D286" t="str">
-        <v>Packaging</v>
+        <v>Watermelon</v>
       </c>
       <c r="E286" t="str">
-        <v>ถุงขยะ 4แพคใหญ่ 1019</v>
+        <v>แตงโม 90 ลูก (7-6-2569: 45 ลูก, 12-6-2569: 45 ลูก)</v>
       </c>
       <c r="F286">
-        <v>1830</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>11/06/2026</v>
+        <v>15/06/2026</v>
       </c>
       <c r="B287" t="str">
         <v>Jun26</v>
@@ -6866,18 +6866,18 @@
         <v>COGS</v>
       </c>
       <c r="D287" t="str">
-        <v>Guava</v>
+        <v>Pineapple</v>
       </c>
       <c r="E287" t="str">
-        <v>ฝรั่ง 1 ลัง</v>
+        <v>สับปะรด 1 ลูก</v>
       </c>
       <c r="F287">
-        <v>700</v>
+        <v>50</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>12/06/2026</v>
+        <v>15/06/2026</v>
       </c>
       <c r="B288" t="str">
         <v>Jun26</v>
@@ -6886,18 +6886,18 @@
         <v>COGS</v>
       </c>
       <c r="D288" t="str">
-        <v>Coconut Water</v>
+        <v>Other</v>
       </c>
       <c r="E288" t="str">
-        <v>น้ำมะพร้าว50*20 1,000</v>
+        <v>Unknown</v>
       </c>
       <c r="F288">
-        <v>2200</v>
+        <v>18</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>12/06/2026</v>
+        <v>15/06/2026</v>
       </c>
       <c r="B289" t="str">
         <v>Jun26</v>
@@ -6906,18 +6906,18 @@
         <v>COGS</v>
       </c>
       <c r="D289" t="str">
-        <v>Mango</v>
+        <v>Pineapple</v>
       </c>
       <c r="E289" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>สับปะรด 12 ลูก</v>
       </c>
       <c r="F289">
-        <v>1170</v>
+        <v>525</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>12/06/2026</v>
+        <v>15/06/2026</v>
       </c>
       <c r="B290" t="str">
         <v>Jun26</v>
@@ -6926,18 +6926,18 @@
         <v>COGS</v>
       </c>
       <c r="D290" t="str">
-        <v>Apple</v>
+        <v>Guava</v>
       </c>
       <c r="E290" t="str">
-        <v>แอปเปิ้ล 5 ลัง</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F290">
-        <v>1750</v>
+        <v>800</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>12/06/2026</v>
+        <v>17/06/2026</v>
       </c>
       <c r="B291" t="str">
         <v>Jun26</v>
@@ -6946,18 +6946,18 @@
         <v>COGS</v>
       </c>
       <c r="D291" t="str">
-        <v>Pineapple</v>
+        <v>Orange</v>
       </c>
       <c r="E291" t="str">
-        <v>สับปะรด 19 ลูก</v>
+        <v>รอบ 09/06/69</v>
       </c>
       <c r="F291">
-        <v>950</v>
+        <v>16445</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>14/06/2026</v>
+        <v>18/06/2026</v>
       </c>
       <c r="B292" t="str">
         <v>Jun26</v>
@@ -6966,18 +6966,18 @@
         <v>COGS</v>
       </c>
       <c r="D292" t="str">
-        <v>Watermelon</v>
+        <v>Mango</v>
       </c>
       <c r="E292" t="str">
-        <v>แตงโม 90 ลูก (7-6-2569: 45 ลูก, 12-6-2569: 45 ลูก)</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F292">
-        <v>7200</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>15/06/2026</v>
+        <v>18/06/2026</v>
       </c>
       <c r="B293" t="str">
         <v>Jun26</v>
@@ -6986,18 +6986,18 @@
         <v>COGS</v>
       </c>
       <c r="D293" t="str">
-        <v>Pineapple</v>
+        <v>Coconut Water</v>
       </c>
       <c r="E293" t="str">
-        <v>สับปะรด 1 ลูก</v>
+        <v>เนื้อมะพร้าว 20 * 120 2400 น้ำมะพร้าว 20 *</v>
       </c>
       <c r="F293">
-        <v>50</v>
+        <v>3400</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>15/06/2026</v>
+        <v>18/06/2026</v>
       </c>
       <c r="B294" t="str">
         <v>Jun26</v>
@@ -7006,18 +7006,18 @@
         <v>COGS</v>
       </c>
       <c r="D294" t="str">
-        <v>Other</v>
+        <v>Guava</v>
       </c>
       <c r="E294" t="str">
-        <v>Unknown</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F294">
-        <v>18</v>
+        <v>800</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>15/06/2026</v>
+        <v>19/06/2026</v>
       </c>
       <c r="B295" t="str">
         <v>Jun26</v>
@@ -7026,18 +7026,18 @@
         <v>COGS</v>
       </c>
       <c r="D295" t="str">
-        <v>Pineapple</v>
+        <v>Coconut Water</v>
       </c>
       <c r="E295" t="str">
-        <v>สับปะรด 12 ลูก</v>
+        <v>น้ำมะพร้าว40ลิตร ลิตรละ45บาท</v>
       </c>
       <c r="F295">
-        <v>525</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>15/06/2026</v>
+        <v>19/06/2026</v>
       </c>
       <c r="B296" t="str">
         <v>Jun26</v>
@@ -7046,18 +7046,18 @@
         <v>COGS</v>
       </c>
       <c r="D296" t="str">
-        <v>Guava</v>
+        <v>Packaging</v>
       </c>
       <c r="E296" t="str">
-        <v>ฝรั่ง 1 ตะกร้า</v>
+        <v>น้ำยาล้างจาน 7 ถุง ผงซักฟอก 1</v>
       </c>
       <c r="F296">
-        <v>800</v>
+        <v>149</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>17/06/2026</v>
+        <v>21/06/2026</v>
       </c>
       <c r="B297" t="str">
         <v>Jun26</v>
@@ -7066,18 +7066,18 @@
         <v>COGS</v>
       </c>
       <c r="D297" t="str">
-        <v>Orange</v>
+        <v>Watermelon</v>
       </c>
       <c r="E297" t="str">
-        <v>รอบ 09/06/69</v>
+        <v>15-6-2569 แตงโม 50บาท 50 ลูก ยอด 2,500</v>
       </c>
       <c r="F297">
-        <v>16445</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>18/06/2026</v>
+        <v>22/06/2026</v>
       </c>
       <c r="B298" t="str">
         <v>Jun26</v>
@@ -7086,18 +7086,18 @@
         <v>COGS</v>
       </c>
       <c r="D298" t="str">
-        <v>Mango</v>
+        <v>Pineapple</v>
       </c>
       <c r="E298" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>สับปะรด 15 ลูก</v>
       </c>
       <c r="F298">
-        <v>1300</v>
+        <v>700</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>18/06/2026</v>
+        <v>22/06/2026</v>
       </c>
       <c r="B299" t="str">
         <v>Jun26</v>
@@ -7106,18 +7106,18 @@
         <v>COGS</v>
       </c>
       <c r="D299" t="str">
-        <v>Coconut Water</v>
+        <v>Mango</v>
       </c>
       <c r="E299" t="str">
-        <v>เนื้อมะพร้าว 20 * 120 2400 น้ำมะพร้าว 20 *</v>
+        <v>มะม่วง 2 ลัง</v>
       </c>
       <c r="F299">
-        <v>3400</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>18/06/2026</v>
+        <v>22/06/2026</v>
       </c>
       <c r="B300" t="str">
         <v>Jun26</v>
@@ -7126,18 +7126,18 @@
         <v>COGS</v>
       </c>
       <c r="D300" t="str">
-        <v>Guava</v>
+        <v>Transportation</v>
       </c>
       <c r="E300" t="str">
-        <v>ฝรั่ง 1 ตะกร้า</v>
+        <v>Lalamove</v>
       </c>
       <c r="F300">
-        <v>800</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>19/06/2026</v>
+        <v>22/06/2026</v>
       </c>
       <c r="B301" t="str">
         <v>Jun26</v>
@@ -7146,18 +7146,18 @@
         <v>COGS</v>
       </c>
       <c r="D301" t="str">
-        <v>Coconut Water</v>
+        <v>Apple</v>
       </c>
       <c r="E301" t="str">
-        <v>น้ำมะพร้าว40ลิตร ลิตรละ45บาท</v>
+        <v>แอพเปิ้ล 5 ลัง</v>
       </c>
       <c r="F301">
-        <v>5700</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>19/06/2026</v>
+        <v>22/06/2026</v>
       </c>
       <c r="B302" t="str">
         <v>Jun26</v>
@@ -7166,18 +7166,18 @@
         <v>COGS</v>
       </c>
       <c r="D302" t="str">
-        <v>Packaging</v>
+        <v>Pineapple</v>
       </c>
       <c r="E302" t="str">
-        <v>น้ำยาล้างจาน 7 ถุง ผงซักฟอก 1</v>
+        <v>สับปะรด 15 ลูก</v>
       </c>
       <c r="F302">
-        <v>149</v>
+        <v>700</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>21/06/2026</v>
+        <v>22/06/2026</v>
       </c>
       <c r="B303" t="str">
         <v>Jun26</v>
@@ -7186,18 +7186,18 @@
         <v>COGS</v>
       </c>
       <c r="D303" t="str">
-        <v>Watermelon</v>
+        <v>Guava</v>
       </c>
       <c r="E303" t="str">
-        <v>15-6-2569 แตงโม 50บาท 50 ลูก ยอด 2,500</v>
+        <v>ฝรั่ง 1 ลัง</v>
       </c>
       <c r="F303">
-        <v>6500</v>
+        <v>700</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>22/06/2026</v>
+        <v>24/06/2026</v>
       </c>
       <c r="B304" t="str">
         <v>Jun26</v>
@@ -7206,18 +7206,18 @@
         <v>COGS</v>
       </c>
       <c r="D304" t="str">
-        <v>Pineapple</v>
+        <v>Milk/Conden</v>
       </c>
       <c r="E304" t="str">
-        <v>สับปะรด 15 ลูก</v>
+        <v>นมข้นจืด 2,221</v>
       </c>
       <c r="F304">
-        <v>700</v>
+        <v>5020</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>22/06/2026</v>
+        <v>24/06/2026</v>
       </c>
       <c r="B305" t="str">
         <v>Jun26</v>
@@ -7226,18 +7226,18 @@
         <v>COGS</v>
       </c>
       <c r="D305" t="str">
-        <v>Mango</v>
+        <v>Milk/Conden</v>
       </c>
       <c r="E305" t="str">
-        <v>มะม่วง 2 ลัง</v>
+        <v>นมข้นจืด1ลัง</v>
       </c>
       <c r="F305">
-        <v>1632</v>
+        <v>600</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>22/06/2026</v>
+        <v>24/06/2026</v>
       </c>
       <c r="B306" t="str">
         <v>Jun26</v>
@@ -7246,18 +7246,18 @@
         <v>COGS</v>
       </c>
       <c r="D306" t="str">
-        <v>Transportation</v>
+        <v>Milk/Conden</v>
       </c>
       <c r="E306" t="str">
-        <v>Lalamove</v>
+        <v>นมข้นหวาน1ลัง</v>
       </c>
       <c r="F306">
-        <v>2000</v>
+        <v>840</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>22/06/2026</v>
+        <v>25/06/2026</v>
       </c>
       <c r="B307" t="str">
         <v>Jun26</v>
@@ -7266,18 +7266,18 @@
         <v>COGS</v>
       </c>
       <c r="D307" t="str">
-        <v>Apple</v>
+        <v>Watermelon</v>
       </c>
       <c r="E307" t="str">
-        <v>แอพเปิ้ล 5 ลัง</v>
+        <v>แตงโม 22-6-2569 30 ลูก 2400 25-6-2569 40</v>
       </c>
       <c r="F307">
-        <v>1750</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>22/06/2026</v>
+        <v>27/06/2026</v>
       </c>
       <c r="B308" t="str">
         <v>Jun26</v>
@@ -7286,18 +7286,18 @@
         <v>COGS</v>
       </c>
       <c r="D308" t="str">
-        <v>Pineapple</v>
+        <v>Packaging</v>
       </c>
       <c r="E308" t="str">
-        <v>สับปะรด 15 ลูก</v>
+        <v>ถุงมือ20กล่อง 2589</v>
       </c>
       <c r="F308">
-        <v>700</v>
+        <v>4598</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>22/06/2026</v>
+        <v>27/06/2026</v>
       </c>
       <c r="B309" t="str">
         <v>Jun26</v>
@@ -7306,38 +7306,38 @@
         <v>COGS</v>
       </c>
       <c r="D309" t="str">
-        <v>Guava</v>
+        <v>Packaging</v>
       </c>
       <c r="E309" t="str">
-        <v>ฝรั่ง 1 ลัง</v>
+        <v>หลอด 20 แพค</v>
       </c>
       <c r="F309">
-        <v>700</v>
+        <v>630</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>24/06/2026</v>
+        <v>27/06/2026</v>
       </c>
       <c r="B310" t="str">
         <v>Jun26</v>
       </c>
       <c r="C310" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D310" t="str">
-        <v>Milk/Conden</v>
+        <v>Other</v>
       </c>
       <c r="E310" t="str">
-        <v>นมข้นจืด 2,221</v>
+        <v>Unknown</v>
       </c>
       <c r="F310">
-        <v>5020</v>
+        <v>317</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>24/06/2026</v>
+        <v>29/06/2026</v>
       </c>
       <c r="B311" t="str">
         <v>Jun26</v>
@@ -7346,18 +7346,18 @@
         <v>COGS</v>
       </c>
       <c r="D311" t="str">
-        <v>Milk/Conden</v>
+        <v>Packaging</v>
       </c>
       <c r="E311" t="str">
-        <v>นมข้นจืด1ลัง</v>
+        <v>ฝาแก้วภูเขาไฟ 1ลัง(954) 10แถว(987) 5แถว(561)</v>
       </c>
       <c r="F311">
-        <v>600</v>
+        <v>2502</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>24/06/2026</v>
+        <v>29/06/2026</v>
       </c>
       <c r="B312" t="str">
         <v>Jun26</v>
@@ -7366,18 +7366,18 @@
         <v>COGS</v>
       </c>
       <c r="D312" t="str">
-        <v>Milk/Conden</v>
+        <v>Packaging</v>
       </c>
       <c r="E312" t="str">
-        <v>นมข้นหวาน1ลัง</v>
+        <v>แก้ว2ลัง 1468*2 2,936</v>
       </c>
       <c r="F312">
-        <v>840</v>
+        <v>3498</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>25/06/2026</v>
+        <v>29/06/2026</v>
       </c>
       <c r="B313" t="str">
         <v>Jun26</v>
@@ -7386,38 +7386,38 @@
         <v>COGS</v>
       </c>
       <c r="D313" t="str">
-        <v>Watermelon</v>
+        <v>Packaging</v>
       </c>
       <c r="E313" t="str">
-        <v>แตงโม 22-6-2569 30 ลูก 2400 25-6-2569 40</v>
+        <v>ฝา8แถว</v>
       </c>
       <c r="F313">
-        <v>6000</v>
+        <v>896</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>27/06/2026</v>
+        <v>29/06/2026</v>
       </c>
       <c r="B314" t="str">
         <v>Jun26</v>
       </c>
       <c r="C314" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D314" t="str">
-        <v>Packaging</v>
+        <v>Other</v>
       </c>
       <c r="E314" t="str">
-        <v>ถุงมือ20กล่อง 2589</v>
+        <v>สกัดเย็น1เครื่อง</v>
       </c>
       <c r="F314">
-        <v>4598</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>27/06/2026</v>
+        <v>29/06/2026</v>
       </c>
       <c r="B315" t="str">
         <v>Jun26</v>
@@ -7426,33 +7426,33 @@
         <v>COGS</v>
       </c>
       <c r="D315" t="str">
-        <v>Packaging</v>
+        <v>Guava</v>
       </c>
       <c r="E315" t="str">
-        <v>หลอด 20 แพค</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F315">
-        <v>630</v>
+        <v>800</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>27/06/2026</v>
+        <v>29/06/2026</v>
       </c>
       <c r="B316" t="str">
         <v>Jun26</v>
       </c>
       <c r="C316" t="str">
-        <v>OPEX</v>
+        <v>EXCLUDED</v>
       </c>
       <c r="D316" t="str">
-        <v>Other</v>
+        <v>Pass-Through</v>
       </c>
       <c r="E316" t="str">
-        <v>Unknown</v>
+        <v>มังคุด 3 ตะกร้า (จ่ายแทน 1,932 แล้ว ฐนกร โอนคืน 29/06 13:56) - ไม่ใช่ต้นทุน SSJ [bank]</v>
       </c>
       <c r="F316">
-        <v>317</v>
+        <v>0</v>
       </c>
     </row>
     <row r="317">
@@ -7463,16 +7463,16 @@
         <v>Jun26</v>
       </c>
       <c r="C317" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D317" t="str">
-        <v>Packaging</v>
+        <v>Other</v>
       </c>
       <c r="E317" t="str">
-        <v>ฝาแก้วภูเขาไฟ 1ลัง(954) 10แถว(987) 5แถว(561)</v>
+        <v>Apple 2 box</v>
       </c>
       <c r="F317">
-        <v>2502</v>
+        <v>700</v>
       </c>
     </row>
     <row r="318">
@@ -7486,13 +7486,13 @@
         <v>COGS</v>
       </c>
       <c r="D318" t="str">
-        <v>Packaging</v>
+        <v>Pineapple</v>
       </c>
       <c r="E318" t="str">
-        <v>แก้ว2ลัง 1468*2 2,936</v>
+        <v>สับปะรด 15 ลูก</v>
       </c>
       <c r="F318">
-        <v>3498</v>
+        <v>675</v>
       </c>
     </row>
     <row r="319">
@@ -7506,18 +7506,18 @@
         <v>COGS</v>
       </c>
       <c r="D319" t="str">
-        <v>Packaging</v>
+        <v>Orange</v>
       </c>
       <c r="E319" t="str">
-        <v>ฝา8แถว</v>
+        <v>รอบ 18/06/69</v>
       </c>
       <c r="F319">
-        <v>896</v>
+        <v>17815</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>29/06/2026</v>
+        <v>30/06/2026</v>
       </c>
       <c r="B320" t="str">
         <v>Jun26</v>
@@ -7526,138 +7526,138 @@
         <v>OPEX</v>
       </c>
       <c r="D320" t="str">
-        <v>Other</v>
+        <v>Salary</v>
       </c>
       <c r="E320" t="str">
-        <v>สกัดเย็น1เครื่อง</v>
+        <v>ค่าแรง 4 คน คนคนละ 12000 และ รายวัน 1</v>
       </c>
       <c r="F320">
-        <v>1402</v>
+        <v>48400</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>29/06/2026</v>
+        <v>24/07/2026</v>
       </c>
       <c r="B321" t="str">
-        <v>Jun26</v>
+        <v>Jul26</v>
       </c>
       <c r="C321" t="str">
         <v>COGS</v>
       </c>
       <c r="D321" t="str">
-        <v>Guava</v>
+        <v>Stock</v>
       </c>
       <c r="E321" t="str">
-        <v>ฝรั่ง 1 ตะกร้า</v>
+        <v>ฝา 1 ลัง 509 นมข้นหวาน 1 ลัง 785 นมข้นจืด 2 ลัง 1342 บาท (LINE_ALBUM_Cost July_260802_1.jpg)</v>
       </c>
       <c r="F321">
-        <v>800</v>
+        <v>2636</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>29/06/2026</v>
+        <v>24/07/2026</v>
       </c>
       <c r="B322" t="str">
-        <v>Jun26</v>
+        <v>Jul26</v>
       </c>
       <c r="C322" t="str">
-        <v>EXCLUDED</v>
+        <v>COGS</v>
       </c>
       <c r="D322" t="str">
-        <v>Pass-Through</v>
+        <v>Stock</v>
       </c>
       <c r="E322" t="str">
-        <v>มังคุด 3 ตะกร้า (จ่ายแทน 1,932 แล้ว ฐนกร โอนคืน 29/06 13:56) - ไม่ใช่ต้นทุน SSJ [bank]</v>
+        <v>ฝา 1 ลัง 502 บาท นมข้นหวาน 3 ลัง 2582 บาท (LINE_ALBUM_Cost July_260802_2.jpg)</v>
       </c>
       <c r="F322">
-        <v>0</v>
+        <v>3084</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>29/06/2026</v>
+        <v>24/07/2026</v>
       </c>
       <c r="B323" t="str">
-        <v>Jun26</v>
+        <v>Jul26</v>
       </c>
       <c r="C323" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D323" t="str">
-        <v>Other</v>
+        <v>Stock</v>
       </c>
       <c r="E323" t="str">
-        <v>Apple 2 box</v>
+        <v>ฝา 1 ลัง 474 นมข้นจืด 1 ลัง 751 (LINE_ALBUM_Cost July_260802_3.jpg)</v>
       </c>
       <c r="F323">
-        <v>700</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>29/06/2026</v>
+        <v>24/07/2026</v>
       </c>
       <c r="B324" t="str">
-        <v>Jun26</v>
+        <v>Jul26</v>
       </c>
       <c r="C324" t="str">
         <v>COGS</v>
       </c>
       <c r="D324" t="str">
-        <v>Pineapple</v>
+        <v>Stock</v>
       </c>
       <c r="E324" t="str">
-        <v>สับปะรด 15 ลูก</v>
+        <v>ฝา 1 ลัง (LINE_ALBUM_Cost July_260802_4.jpg)</v>
       </c>
       <c r="F324">
-        <v>675</v>
+        <v>472</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>29/06/2026</v>
+        <v>24/07/2026</v>
       </c>
       <c r="B325" t="str">
-        <v>Jun26</v>
+        <v>Jul26</v>
       </c>
       <c r="C325" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D325" t="str">
-        <v>Orange</v>
+        <v>Other</v>
       </c>
       <c r="E325" t="str">
-        <v>รอบ 18/06/69</v>
+        <v>Lalamove (LINE_ALBUM_Cost July_260802_5.jpg)</v>
       </c>
       <c r="F325">
-        <v>17815</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>30/06/2026</v>
+        <v>26/07/2026</v>
       </c>
       <c r="B326" t="str">
-        <v>Jun26</v>
+        <v>Jul26</v>
       </c>
       <c r="C326" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D326" t="str">
-        <v>Salary</v>
+        <v>Apple</v>
       </c>
       <c r="E326" t="str">
-        <v>ค่าแรง 4 คน คนคนละ 12000 และ รายวัน 1</v>
+        <v>Apple 5 box (LINE_ALBUM_Cost July_260802_6.jpg)</v>
       </c>
       <c r="F326">
-        <v>48400</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>24/07/2026</v>
+        <v>26/07/2026</v>
       </c>
       <c r="B327" t="str">
         <v>Jul26</v>
@@ -7666,18 +7666,18 @@
         <v>COGS</v>
       </c>
       <c r="D327" t="str">
-        <v>Stock</v>
+        <v>Guava</v>
       </c>
       <c r="E327" t="str">
-        <v>ฝา 1 ลัง 509 นมข้นหวาน 1 ลัง 785 นมข้นจืด 2 ลัง 1342 บาท (LINE_ALBUM_Cost July_260802_1.jpg)</v>
+        <v>ฝรั่ง 2 ตะกร้า (LINE_ALBUM_Cost July_260802_7.jpg)</v>
       </c>
       <c r="F327">
-        <v>2636</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>24/07/2026</v>
+        <v>26/07/2026</v>
       </c>
       <c r="B328" t="str">
         <v>Jul26</v>
@@ -7686,18 +7686,18 @@
         <v>COGS</v>
       </c>
       <c r="D328" t="str">
-        <v>Stock</v>
+        <v>Mango</v>
       </c>
       <c r="E328" t="str">
-        <v>ฝา 1 ลัง 502 บาท นมข้นหวาน 3 ลัง 2582 บาท (LINE_ALBUM_Cost July_260802_2.jpg)</v>
+        <v>มะม่วง 3 ลัง 3900 (LINE_ALBUM_Cost July_260802_8.jpg)</v>
       </c>
       <c r="F328">
-        <v>3084</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>24/07/2026</v>
+        <v>27/07/2026</v>
       </c>
       <c r="B329" t="str">
         <v>Jul26</v>
@@ -7706,18 +7706,18 @@
         <v>COGS</v>
       </c>
       <c r="D329" t="str">
-        <v>Stock</v>
+        <v>Coconut</v>
       </c>
       <c r="E329" t="str">
-        <v>ฝา 1 ลัง 474 นมข้นจืด 1 ลัง 751 (LINE_ALBUM_Cost July_260802_3.jpg)</v>
+        <v>น้ำมะพร้าว 30ลิตร 1350 เนื้อ 50kg 5000 น้ำมะพร้าวขวด 920 ค่าส่ง 350 (LINE_ALBUM_Cost July_260802_14.jpg, audit fix - was dated 26/07 citing wrong image, missing ฿920 bottles line)</v>
       </c>
       <c r="F329">
-        <v>1225</v>
+        <v>7620</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>24/07/2026</v>
+        <v>27/07/2026</v>
       </c>
       <c r="B330" t="str">
         <v>Jul26</v>
@@ -7726,30 +7726,30 @@
         <v>COGS</v>
       </c>
       <c r="D330" t="str">
-        <v>Stock</v>
+        <v>Apple</v>
       </c>
       <c r="E330" t="str">
-        <v>ฝา 1 ลัง (LINE_ALBUM_Cost July_260802_4.jpg)</v>
+        <v>Apple 4 box (LINE_ALBUM_Cost July_260802_10.jpg)</v>
       </c>
       <c r="F330">
-        <v>472</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>24/07/2026</v>
+        <v>27/07/2026</v>
       </c>
       <c r="B331" t="str">
         <v>Jul26</v>
       </c>
       <c r="C331" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D331" t="str">
-        <v>Other</v>
+        <v>Guava</v>
       </c>
       <c r="E331" t="str">
-        <v>Lalamove (LINE_ALBUM_Cost July_260802_5.jpg)</v>
+        <v>ฝรั่ง 2 ตะกร้า (LINE_ALBUM_Cost July_260802_11.jpg)</v>
       </c>
       <c r="F331">
         <v>2000</v>
@@ -7757,7 +7757,7 @@
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>26/07/2026</v>
+        <v>27/07/2026</v>
       </c>
       <c r="B332" t="str">
         <v>Jul26</v>
@@ -7766,18 +7766,18 @@
         <v>COGS</v>
       </c>
       <c r="D332" t="str">
-        <v>Apple</v>
+        <v>Mango</v>
       </c>
       <c r="E332" t="str">
-        <v>Apple 5 box (LINE_ALBUM_Cost July_260802_6.jpg)</v>
+        <v>มะม่วง 2 ลัง (LINE_ALBUM_Cost July_260802_12.jpg)</v>
       </c>
       <c r="F332">
-        <v>2000</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>26/07/2026</v>
+        <v>27/07/2026</v>
       </c>
       <c r="B333" t="str">
         <v>Jul26</v>
@@ -7786,38 +7786,38 @@
         <v>COGS</v>
       </c>
       <c r="D333" t="str">
-        <v>Guava</v>
+        <v>Watermelon</v>
       </c>
       <c r="E333" t="str">
-        <v>ฝรั่ง 2 ตะกร้า (LINE_ALBUM_Cost July_260802_7.jpg)</v>
+        <v>แตงโม 40 ลูก (LINE_ALBUM_Cost July_260802_13.jpg)</v>
       </c>
       <c r="F333">
-        <v>2000</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>26/07/2026</v>
+        <v>28/07/2026</v>
       </c>
       <c r="B334" t="str">
         <v>Jul26</v>
       </c>
       <c r="C334" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D334" t="str">
-        <v>Mango</v>
+        <v>Other</v>
       </c>
       <c r="E334" t="str">
-        <v>มะม่วง 3 ลัง 3900 (LINE_ALBUM_Cost July_260802_8.jpg)</v>
+        <v>Lalamove (LINE_ALBUM_Cost July_260802_14.jpg)</v>
       </c>
       <c r="F334">
-        <v>3900</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>27/07/2026</v>
+        <v>28/07/2026</v>
       </c>
       <c r="B335" t="str">
         <v>Jul26</v>
@@ -7826,18 +7826,18 @@
         <v>COGS</v>
       </c>
       <c r="D335" t="str">
-        <v>Coconut</v>
+        <v>Guava</v>
       </c>
       <c r="E335" t="str">
-        <v>น้ำมะพร้าว 30ลิตร 1350 เนื้อ 50kg 5000 น้ำมะพร้าวขวด 920 ค่าส่ง 350 (LINE_ALBUM_Cost July_260802_14.jpg, audit fix - was dated 26/07 citing wrong image, missing ฿920 bottles line)</v>
+        <v>ฝรั่ง 2 ลัง (LINE_ALBUM_Cost July_260802_15.jpg)</v>
       </c>
       <c r="F335">
-        <v>7620</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>27/07/2026</v>
+        <v>28/07/2026</v>
       </c>
       <c r="B336" t="str">
         <v>Jul26</v>
@@ -7849,15 +7849,15 @@
         <v>Apple</v>
       </c>
       <c r="E336" t="str">
-        <v>Apple 4 box (LINE_ALBUM_Cost July_260802_10.jpg)</v>
+        <v>แอปเปิ้ล 5 ลัง (LINE_ALBUM_Cost July_260802_16.jpg, audit fix - was recorded as 4 ลัง/฿1600)</v>
       </c>
       <c r="F336">
-        <v>1600</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>27/07/2026</v>
+        <v>28/07/2026</v>
       </c>
       <c r="B337" t="str">
         <v>Jul26</v>
@@ -7866,18 +7866,18 @@
         <v>COGS</v>
       </c>
       <c r="D337" t="str">
-        <v>Guava</v>
+        <v>Mango</v>
       </c>
       <c r="E337" t="str">
-        <v>ฝรั่ง 2 ตะกร้า (LINE_ALBUM_Cost July_260802_11.jpg)</v>
+        <v>มะม่วง 2 ลัง (LINE_ALBUM_Cost July_260802_17.jpg)</v>
       </c>
       <c r="F337">
-        <v>2000</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>27/07/2026</v>
+        <v>28/07/2026</v>
       </c>
       <c r="B338" t="str">
         <v>Jul26</v>
@@ -7886,98 +7886,98 @@
         <v>COGS</v>
       </c>
       <c r="D338" t="str">
-        <v>Mango</v>
+        <v>Watermelon</v>
       </c>
       <c r="E338" t="str">
-        <v>มะม่วง 2 ลัง (LINE_ALBUM_Cost July_260802_12.jpg)</v>
+        <v>แตงโม 40 ลูก (LINE_ALBUM_Cost July_260802_18.jpg)</v>
       </c>
       <c r="F338">
-        <v>2600</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>27/07/2026</v>
+        <v>29/07/2026</v>
       </c>
       <c r="B339" t="str">
         <v>Jul26</v>
       </c>
       <c r="C339" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D339" t="str">
-        <v>Watermelon</v>
+        <v>Other</v>
       </c>
       <c r="E339" t="str">
-        <v>แตงโม 40 ลูก (LINE_ALBUM_Cost July_260802_13.jpg)</v>
+        <v>ค่าขนส่ง (LINE_ALBUM_Cost July_260802_19.jpg)</v>
       </c>
       <c r="F339">
-        <v>3200</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>28/07/2026</v>
+        <v>29/07/2026</v>
       </c>
       <c r="B340" t="str">
         <v>Jul26</v>
       </c>
       <c r="C340" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D340" t="str">
-        <v>Other</v>
+        <v>Orange</v>
       </c>
       <c r="E340" t="str">
-        <v>Lalamove (LINE_ALBUM_Cost July_260802_14.jpg)</v>
+        <v>ส้ม 31x22กก 682กกx30 20,460บาท ค่าขนส่ง 31ตกx 50 1550 (LINE_ALBUM_Cost July_260802_20.jpg)</v>
       </c>
       <c r="F340">
-        <v>1000</v>
+        <v>22010</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>28/07/2026</v>
+        <v>30/07/2026</v>
       </c>
       <c r="B341" t="str">
         <v>Jul26</v>
       </c>
       <c r="C341" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D341" t="str">
-        <v>Guava</v>
+        <v>Other</v>
       </c>
       <c r="E341" t="str">
-        <v>ฝรั่ง 2 ลัง (LINE_ALBUM_Cost July_260802_15.jpg)</v>
+        <v>ตะแกรงคว่ำจาน 6อัน ป้ายไฟ3อัน (LINE_ALBUM_Cost July_260802_21.jpg)</v>
       </c>
       <c r="F341">
-        <v>2000</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>28/07/2026</v>
+        <v>30/07/2026</v>
       </c>
       <c r="B342" t="str">
         <v>Jul26</v>
       </c>
       <c r="C342" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D342" t="str">
-        <v>Apple</v>
+        <v>Other</v>
       </c>
       <c r="E342" t="str">
-        <v>แอปเปิ้ล 5 ลัง (LINE_ALBUM_Cost July_260802_16.jpg, audit fix - was recorded as 4 ลัง/฿1600)</v>
+        <v>ถุงขยะ 5*5แพค (LINE_ALBUM_Cost July_260802_22.jpg)</v>
       </c>
       <c r="F342">
-        <v>2150</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>28/07/2026</v>
+        <v>31/07/2026</v>
       </c>
       <c r="B343" t="str">
         <v>Jul26</v>
@@ -7986,18 +7986,18 @@
         <v>COGS</v>
       </c>
       <c r="D343" t="str">
-        <v>Mango</v>
+        <v>Apple</v>
       </c>
       <c r="E343" t="str">
-        <v>มะม่วง 2 ลัง (LINE_ALBUM_Cost July_260802_17.jpg)</v>
+        <v>แอปเปิ้ล 4 ลัง (LINE_ALBUM_Cost July_260802_23.jpg)</v>
       </c>
       <c r="F343">
-        <v>2600</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>28/07/2026</v>
+        <v>31/07/2026</v>
       </c>
       <c r="B344" t="str">
         <v>Jul26</v>
@@ -8006,18 +8006,18 @@
         <v>COGS</v>
       </c>
       <c r="D344" t="str">
-        <v>Watermelon</v>
+        <v>Mango</v>
       </c>
       <c r="E344" t="str">
-        <v>แตงโม 40 ลูก (LINE_ALBUM_Cost July_260802_18.jpg)</v>
+        <v>มะม่วง 4 ลัง (LINE_ALBUM_Cost July_260802_24.jpg)</v>
       </c>
       <c r="F344">
-        <v>3200</v>
+        <v>4680</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>29/07/2026</v>
+        <v>31/07/2026</v>
       </c>
       <c r="B345" t="str">
         <v>Jul26</v>
@@ -8029,7 +8029,7 @@
         <v>Other</v>
       </c>
       <c r="E345" t="str">
-        <v>ค่าขนส่ง (LINE_ALBUM_Cost July_260802_19.jpg)</v>
+        <v>ค่าขนส่ง (LINE_ALBUM_Cost July_260802_25.jpg)</v>
       </c>
       <c r="F345">
         <v>2000</v>
@@ -8037,7 +8037,7 @@
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>29/07/2026</v>
+        <v>31/07/2026</v>
       </c>
       <c r="B346" t="str">
         <v>Jul26</v>
@@ -8046,38 +8046,38 @@
         <v>COGS</v>
       </c>
       <c r="D346" t="str">
-        <v>Orange</v>
+        <v>Guava</v>
       </c>
       <c r="E346" t="str">
-        <v>ส้ม 31x22กก 682กกx30 20,460บาท ค่าขนส่ง 31ตกx 50 1550 (LINE_ALBUM_Cost July_260802_20.jpg)</v>
+        <v>ฝรั่ง 3 ลัง (LINE_ALBUM_Cost July_260802_26.jpg)</v>
       </c>
       <c r="F346">
-        <v>22010</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>30/07/2026</v>
+        <v>31/07/2026</v>
       </c>
       <c r="B347" t="str">
         <v>Jul26</v>
       </c>
       <c r="C347" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D347" t="str">
         <v>Other</v>
       </c>
       <c r="E347" t="str">
-        <v>ตะแกรงคว่ำจาน 6อัน ป้ายไฟ3อัน (LINE_ALBUM_Cost July_260802_21.jpg)</v>
+        <v>ทุเรียน 20.6 กิโลกรัม (LINE_ALBUM_Cost July_260802_27.jpg)</v>
       </c>
       <c r="F347">
-        <v>1790</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>30/07/2026</v>
+        <v>31/07/2026</v>
       </c>
       <c r="B348" t="str">
         <v>Jul26</v>
@@ -8089,15 +8089,15 @@
         <v>Other</v>
       </c>
       <c r="E348" t="str">
-        <v>ถุงขยะ 5*5แพค (LINE_ALBUM_Cost July_260802_22.jpg)</v>
+        <v>ตะกร้าแต่งร้าน 3 (LINE_ALBUM_Cost July_260802_28.jpg)</v>
       </c>
       <c r="F348">
-        <v>1101</v>
+        <v>558</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>31/07/2026</v>
+        <v>02/07/2026</v>
       </c>
       <c r="B349" t="str">
         <v>Jul26</v>
@@ -8106,18 +8106,18 @@
         <v>COGS</v>
       </c>
       <c r="D349" t="str">
-        <v>Apple</v>
+        <v>Orange</v>
       </c>
       <c r="E349" t="str">
-        <v>แอปเปิ้ล 4 ลัง (LINE_ALBUM_Cost July_260802_23.jpg)</v>
+        <v>ค่าส่งส้มเดือน 6 (LINE_ALBUM_Cost July_260802_29.jpg)</v>
       </c>
       <c r="F349">
-        <v>1200</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>31/07/2026</v>
+        <v>03/07/2026</v>
       </c>
       <c r="B350" t="str">
         <v>Jul26</v>
@@ -8126,38 +8126,38 @@
         <v>COGS</v>
       </c>
       <c r="D350" t="str">
-        <v>Mango</v>
+        <v>Pineapple</v>
       </c>
       <c r="E350" t="str">
-        <v>มะม่วง 4 ลัง (LINE_ALBUM_Cost July_260802_24.jpg)</v>
+        <v>1 สับปะรด 15 ลูก 750 2 สับปะรด 15 ลูก 729 (LINE_ALBUM_Cost July_260802_30.jpg)</v>
       </c>
       <c r="F350">
-        <v>4680</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>31/07/2026</v>
+        <v>03/07/2026</v>
       </c>
       <c r="B351" t="str">
         <v>Jul26</v>
       </c>
       <c r="C351" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D351" t="str">
-        <v>Other</v>
+        <v>Apple</v>
       </c>
       <c r="E351" t="str">
-        <v>ค่าขนส่ง (LINE_ALBUM_Cost July_260802_25.jpg)</v>
+        <v>แอปเปิ้ล 3 ลัง (LINE_ALBUM_Cost July_260802_31.jpg)</v>
       </c>
       <c r="F351">
-        <v>2000</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>31/07/2026</v>
+        <v>03/07/2026</v>
       </c>
       <c r="B352" t="str">
         <v>Jul26</v>
@@ -8166,18 +8166,18 @@
         <v>COGS</v>
       </c>
       <c r="D352" t="str">
-        <v>Guava</v>
+        <v>Mango</v>
       </c>
       <c r="E352" t="str">
-        <v>ฝรั่ง 3 ลัง (LINE_ALBUM_Cost July_260802_26.jpg)</v>
+        <v>มะม่วง 1 ลัง (LINE_ALBUM_Cost July_260802_32.jpg)</v>
       </c>
       <c r="F352">
-        <v>3600</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>31/07/2026</v>
+        <v>03/07/2026</v>
       </c>
       <c r="B353" t="str">
         <v>Jul26</v>
@@ -8186,18 +8186,18 @@
         <v>COGS</v>
       </c>
       <c r="D353" t="str">
-        <v>Other</v>
+        <v>Guava</v>
       </c>
       <c r="E353" t="str">
-        <v>ทุเรียน 20.6 กิโลกรัม (LINE_ALBUM_Cost July_260802_27.jpg)</v>
+        <v>ฝรั่ง 1 ลัง (LINE_ALBUM_Cost July_260802_33.jpg)</v>
       </c>
       <c r="F353">
-        <v>2255</v>
+        <v>900</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>31/07/2026</v>
+        <v>03/07/2026</v>
       </c>
       <c r="B354" t="str">
         <v>Jul26</v>
@@ -8209,35 +8209,35 @@
         <v>Other</v>
       </c>
       <c r="E354" t="str">
-        <v>ตะกร้าแต่งร้าน 3 (LINE_ALBUM_Cost July_260802_28.jpg)</v>
+        <v>ค่าส่ง (LINE_ALBUM_Cost July_260802_34.jpg)</v>
       </c>
       <c r="F354">
-        <v>558</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>02/07/2026</v>
+        <v>06/07/2026</v>
       </c>
       <c r="B355" t="str">
         <v>Jul26</v>
       </c>
       <c r="C355" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D355" t="str">
-        <v>Orange</v>
+        <v>Rental</v>
       </c>
       <c r="E355" t="str">
-        <v>ค่าส่งส้มเดือน 6 (LINE_ALBUM_Cost July_260802_29.jpg)</v>
+        <v>ค่าเช่า stock เดือน june (1/3 split B1) (LINE_ALBUM_Cost July_260802_35.jpg)</v>
       </c>
       <c r="F355">
-        <v>1598</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>03/07/2026</v>
+        <v>06/07/2026</v>
       </c>
       <c r="B356" t="str">
         <v>Jul26</v>
@@ -8249,15 +8249,15 @@
         <v>Pineapple</v>
       </c>
       <c r="E356" t="str">
-        <v>1 สับปะรด 15 ลูก 750 2 สับปะรด 15 ลูก 729 (LINE_ALBUM_Cost July_260802_30.jpg)</v>
+        <v>สับปะรด 20 ลูก (LINE_ALBUM_Cost July_260802_36.jpg)</v>
       </c>
       <c r="F356">
-        <v>1479</v>
+        <v>783</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>03/07/2026</v>
+        <v>06/07/2026</v>
       </c>
       <c r="B357" t="str">
         <v>Jul26</v>
@@ -8266,18 +8266,18 @@
         <v>COGS</v>
       </c>
       <c r="D357" t="str">
-        <v>Apple</v>
+        <v>Mango</v>
       </c>
       <c r="E357" t="str">
-        <v>แอปเปิ้ล 3 ลัง (LINE_ALBUM_Cost July_260802_31.jpg)</v>
+        <v>มะม่วง 2 ลัง (LINE_ALBUM_Cost July_260802_37.jpg)</v>
       </c>
       <c r="F357">
-        <v>1140</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>03/07/2026</v>
+        <v>06/07/2026</v>
       </c>
       <c r="B358" t="str">
         <v>Jul26</v>
@@ -8286,18 +8286,18 @@
         <v>COGS</v>
       </c>
       <c r="D358" t="str">
-        <v>Mango</v>
+        <v>Guava</v>
       </c>
       <c r="E358" t="str">
-        <v>มะม่วง 1 ลัง (LINE_ALBUM_Cost July_260802_32.jpg)</v>
+        <v>ฝรั่ง 1 ตะกร้า (LINE_ALBUM_Cost July_260802_38.jpg)</v>
       </c>
       <c r="F358">
-        <v>1040</v>
+        <v>900</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>03/07/2026</v>
+        <v>06/07/2026</v>
       </c>
       <c r="B359" t="str">
         <v>Jul26</v>
@@ -8306,10 +8306,10 @@
         <v>COGS</v>
       </c>
       <c r="D359" t="str">
-        <v>Guava</v>
+        <v>Apple</v>
       </c>
       <c r="E359" t="str">
-        <v>ฝรั่ง 1 ลัง (LINE_ALBUM_Cost July_260802_33.jpg)</v>
+        <v>แอปเปิ้ล 3 ลัง (LINE_ALBUM_Cost July_260802_39.jpg)</v>
       </c>
       <c r="F359">
         <v>900</v>
@@ -8317,27 +8317,27 @@
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>03/07/2026</v>
+        <v>08/07/2026</v>
       </c>
       <c r="B360" t="str">
         <v>Jul26</v>
       </c>
       <c r="C360" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D360" t="str">
-        <v>Other</v>
+        <v>Watermelon</v>
       </c>
       <c r="E360" t="str">
-        <v>ค่าส่ง (LINE_ALBUM_Cost July_260802_34.jpg)</v>
+        <v>แตงโม 3-7-69 36 ลูก ลูกละ 80 บาท 6-7-69 50 ลูก ลูกละ 80 บาท (LINE_ALBUM_Cost July_260802_40.jpg)</v>
       </c>
       <c r="F360">
-        <v>2000</v>
+        <v>6880</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>06/07/2026</v>
+        <v>08/07/2026</v>
       </c>
       <c r="B361" t="str">
         <v>Jul26</v>
@@ -8346,18 +8346,18 @@
         <v>OPEX</v>
       </c>
       <c r="D361" t="str">
-        <v>Rental</v>
+        <v>Other</v>
       </c>
       <c r="E361" t="str">
-        <v>ค่าเช่า stock เดือน june (1/3 split B1) (LINE_ALBUM_Cost July_260802_35.jpg)</v>
+        <v>เต้น (tent) (LINE_ALBUM_Cost July_260802_41.jpg)</v>
       </c>
       <c r="F361">
-        <v>4000</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>06/07/2026</v>
+        <v>09/07/2026</v>
       </c>
       <c r="B362" t="str">
         <v>Jul26</v>
@@ -8366,18 +8366,18 @@
         <v>COGS</v>
       </c>
       <c r="D362" t="str">
-        <v>Pineapple</v>
+        <v>Coconut</v>
       </c>
       <c r="E362" t="str">
-        <v>สับปะรด 20 ลูก (LINE_ALBUM_Cost July_260802_36.jpg)</v>
+        <v>น้ำ 25ลิตร ลิตรละ45บาท เนื้อคว้าน 50kg.กิโลละ 100บาท ค่าส่ง350บาท (LINE_ALBUM_Cost July_260802_42.jpg)</v>
       </c>
       <c r="F362">
-        <v>783</v>
+        <v>6470</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>06/07/2026</v>
+        <v>10/07/2026</v>
       </c>
       <c r="B363" t="str">
         <v>Jul26</v>
@@ -8386,18 +8386,18 @@
         <v>COGS</v>
       </c>
       <c r="D363" t="str">
-        <v>Mango</v>
+        <v>Guava</v>
       </c>
       <c r="E363" t="str">
-        <v>มะม่วง 2 ลัง (LINE_ALBUM_Cost July_260802_37.jpg)</v>
+        <v>ฝรั่ง 1 ลัง (LINE_ALBUM_Cost July_260802_43.jpg)</v>
       </c>
       <c r="F363">
-        <v>2340</v>
+        <v>900</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>06/07/2026</v>
+        <v>10/07/2026</v>
       </c>
       <c r="B364" t="str">
         <v>Jul26</v>
@@ -8406,18 +8406,18 @@
         <v>COGS</v>
       </c>
       <c r="D364" t="str">
-        <v>Guava</v>
+        <v>Apple</v>
       </c>
       <c r="E364" t="str">
-        <v>ฝรั่ง 1 ตะกร้า (LINE_ALBUM_Cost July_260802_38.jpg)</v>
+        <v>Apple 5 box (LINE_ALBUM_Cost July_260802_44.jpg)</v>
       </c>
       <c r="F364">
-        <v>900</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>06/07/2026</v>
+        <v>11/07/2026</v>
       </c>
       <c r="B365" t="str">
         <v>Jul26</v>
@@ -8426,10 +8426,10 @@
         <v>COGS</v>
       </c>
       <c r="D365" t="str">
-        <v>Apple</v>
+        <v>Guava</v>
       </c>
       <c r="E365" t="str">
-        <v>แอปเปิ้ล 3 ลัง (LINE_ALBUM_Cost July_260802_39.jpg)</v>
+        <v>ฝรั่ง 1 ตะกร้า (LINE_ALBUM_Cost July_260802_45.jpg)</v>
       </c>
       <c r="F365">
         <v>900</v>
@@ -8437,7 +8437,7 @@
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>08/07/2026</v>
+        <v>11/07/2026</v>
       </c>
       <c r="B366" t="str">
         <v>Jul26</v>
@@ -8446,58 +8446,58 @@
         <v>COGS</v>
       </c>
       <c r="D366" t="str">
-        <v>Watermelon</v>
+        <v>Mango</v>
       </c>
       <c r="E366" t="str">
-        <v>แตงโม 3-7-69 36 ลูก ลูกละ 80 บาท 6-7-69 50 ลูก ลูกละ 80 บาท (LINE_ALBUM_Cost July_260802_40.jpg)</v>
+        <v>มะม่วง 3 ลัง (LINE_ALBUM_Cost July_260802_46.jpg)</v>
       </c>
       <c r="F366">
-        <v>6880</v>
+        <v>4300</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>08/07/2026</v>
+        <v>11/07/2026</v>
       </c>
       <c r="B367" t="str">
         <v>Jul26</v>
       </c>
       <c r="C367" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D367" t="str">
-        <v>Other</v>
+        <v>Apple</v>
       </c>
       <c r="E367" t="str">
-        <v>เต้น (tent) (LINE_ALBUM_Cost July_260802_41.jpg)</v>
+        <v>แอปเปิ้ล 3 ลัง (LINE_ALBUM_Cost July_260802_47.jpg)</v>
       </c>
       <c r="F367">
-        <v>1342</v>
+        <v>900</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>09/07/2026</v>
+        <v>13/07/2026</v>
       </c>
       <c r="B368" t="str">
         <v>Jul26</v>
       </c>
       <c r="C368" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D368" t="str">
-        <v>Coconut</v>
+        <v>Other</v>
       </c>
       <c r="E368" t="str">
-        <v>น้ำ 25ลิตร ลิตรละ45บาท เนื้อคว้าน 50kg.กิโลละ 100บาท ค่าส่ง350บาท (LINE_ALBUM_Cost July_260802_42.jpg)</v>
+        <v>ค่าขนส่ง (LINE_ALBUM_Cost July_260802_48.jpg)</v>
       </c>
       <c r="F368">
-        <v>6470</v>
+        <v>344</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>10/07/2026</v>
+        <v>13/07/2026</v>
       </c>
       <c r="B369" t="str">
         <v>Jul26</v>
@@ -8506,18 +8506,18 @@
         <v>COGS</v>
       </c>
       <c r="D369" t="str">
-        <v>Guava</v>
+        <v>Packaging</v>
       </c>
       <c r="E369" t="str">
-        <v>ฝรั่ง 1 ลัง (LINE_ALBUM_Cost July_260802_43.jpg)</v>
+        <v>ทิชชู4(636) หลอด20 (671) ถุงเล็ก3(605) ถุงใหญ่2(943) (LINE_ALBUM_Cost July_260802_49.jpg)</v>
       </c>
       <c r="F369">
-        <v>900</v>
+        <v>2855</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>10/07/2026</v>
+        <v>13/07/2026</v>
       </c>
       <c r="B370" t="str">
         <v>Jul26</v>
@@ -8526,18 +8526,18 @@
         <v>COGS</v>
       </c>
       <c r="D370" t="str">
-        <v>Apple</v>
+        <v>Packaging</v>
       </c>
       <c r="E370" t="str">
-        <v>Apple 5 box (LINE_ALBUM_Cost July_260802_44.jpg)</v>
+        <v>แก้ว98 4ลัง 7656-635 7,021 ฝา635 (LINE_ALBUM_Cost July_260802_50.jpg)</v>
       </c>
       <c r="F370">
-        <v>1500</v>
+        <v>7656</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>11/07/2026</v>
+        <v>14/07/2026</v>
       </c>
       <c r="B371" t="str">
         <v>Jul26</v>
@@ -8546,18 +8546,18 @@
         <v>COGS</v>
       </c>
       <c r="D371" t="str">
-        <v>Guava</v>
+        <v>Pineapple</v>
       </c>
       <c r="E371" t="str">
-        <v>ฝรั่ง 1 ตะกร้า (LINE_ALBUM_Cost July_260802_45.jpg)</v>
+        <v>11/7/69 10 ลูก 620 14/7/69 25 ลูก 1269 (LINE_ALBUM_Cost July_260802_51.jpg)</v>
       </c>
       <c r="F371">
-        <v>900</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>11/07/2026</v>
+        <v>14/07/2026</v>
       </c>
       <c r="B372" t="str">
         <v>Jul26</v>
@@ -8566,18 +8566,18 @@
         <v>COGS</v>
       </c>
       <c r="D372" t="str">
-        <v>Mango</v>
+        <v>Apple</v>
       </c>
       <c r="E372" t="str">
-        <v>มะม่วง 3 ลัง (LINE_ALBUM_Cost July_260802_46.jpg)</v>
+        <v>Apple 3 ลัง (LINE_ALBUM_Cost July_260802_52.jpg)</v>
       </c>
       <c r="F372">
-        <v>4300</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>11/07/2026</v>
+        <v>15/07/2026</v>
       </c>
       <c r="B373" t="str">
         <v>Jul26</v>
@@ -8586,38 +8586,38 @@
         <v>COGS</v>
       </c>
       <c r="D373" t="str">
-        <v>Apple</v>
+        <v>Guava</v>
       </c>
       <c r="E373" t="str">
-        <v>แอปเปิ้ล 3 ลัง (LINE_ALBUM_Cost July_260802_47.jpg)</v>
+        <v>ฝรั่ง 2 ตะกร้า ตะกร้าละ 20 โล (LINE_ALBUM_Cost July_260802_53.jpg)</v>
       </c>
       <c r="F373">
-        <v>900</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>13/07/2026</v>
+        <v>16/07/2026</v>
       </c>
       <c r="B374" t="str">
         <v>Jul26</v>
       </c>
       <c r="C374" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D374" t="str">
-        <v>Other</v>
+        <v>Orange</v>
       </c>
       <c r="E374" t="str">
-        <v>ค่าขนส่ง (LINE_ALBUM_Cost July_260802_48.jpg)</v>
+        <v>รอบ 01/07/69 ส้ม 28x22กก 616กกx30 18,480บาท ค่าขนส่ง 28ตกx 55 1540 (LINE_ALBUM_Cost July_260802_54.jpg)</v>
       </c>
       <c r="F374">
-        <v>344</v>
+        <v>20020</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>13/07/2026</v>
+        <v>17/07/2026</v>
       </c>
       <c r="B375" t="str">
         <v>Jul26</v>
@@ -8626,18 +8626,18 @@
         <v>COGS</v>
       </c>
       <c r="D375" t="str">
-        <v>Packaging</v>
+        <v>Orange</v>
       </c>
       <c r="E375" t="str">
-        <v>ทิชชู4(636) หลอด20 (671) ถุงเล็ก3(605) ถุงใหญ่2(943) (LINE_ALBUM_Cost July_260802_49.jpg)</v>
+        <v>ส้ม 125 โล 3450 ค่าส่ง 300 (LINE_ALBUM_Cost July_260802_55.jpg)</v>
       </c>
       <c r="F375">
-        <v>2855</v>
+        <v>3750</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>13/07/2026</v>
+        <v>17/07/2026</v>
       </c>
       <c r="B376" t="str">
         <v>Jul26</v>
@@ -8646,18 +8646,18 @@
         <v>COGS</v>
       </c>
       <c r="D376" t="str">
-        <v>Packaging</v>
+        <v>Pineapple</v>
       </c>
       <c r="E376" t="str">
-        <v>แก้ว98 4ลัง 7656-635 7,021 ฝา635 (LINE_ALBUM_Cost July_260802_50.jpg)</v>
+        <v>สับปะรด 25 ลูก (LINE_ALBUM_Cost July_260802_56.jpg)</v>
       </c>
       <c r="F376">
-        <v>7656</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>14/07/2026</v>
+        <v>17/07/2026</v>
       </c>
       <c r="B377" t="str">
         <v>Jul26</v>
@@ -8666,18 +8666,18 @@
         <v>COGS</v>
       </c>
       <c r="D377" t="str">
-        <v>Pineapple</v>
+        <v>Watermelon</v>
       </c>
       <c r="E377" t="str">
-        <v>11/7/69 10 ลูก 620 14/7/69 25 ลูก 1269 (LINE_ALBUM_Cost July_260802_51.jpg)</v>
+        <v>แตงโม 10-7-69 50 ลูก 4000 11-7-69 40 ลูก 3200 (LINE_ALBUM_Cost July_260802_57.jpg)</v>
       </c>
       <c r="F377">
-        <v>1889</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>14/07/2026</v>
+        <v>17/07/2026</v>
       </c>
       <c r="B378" t="str">
         <v>Jul26</v>
@@ -8686,18 +8686,18 @@
         <v>COGS</v>
       </c>
       <c r="D378" t="str">
-        <v>Apple</v>
+        <v>Other</v>
       </c>
       <c r="E378" t="str">
-        <v>Apple 3 ลัง (LINE_ALBUM_Cost July_260802_52.jpg)</v>
+        <v>ทุเรียน 50 โล โลละ 85 รวม 4250 มัดจำตะกร้า 200 (LINE_ALBUM_Cost July_260802_58.jpg)</v>
       </c>
       <c r="F378">
-        <v>1200</v>
+        <v>4450</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>15/07/2026</v>
+        <v>17/07/2026</v>
       </c>
       <c r="B379" t="str">
         <v>Jul26</v>
@@ -8706,18 +8706,18 @@
         <v>COGS</v>
       </c>
       <c r="D379" t="str">
-        <v>Guava</v>
+        <v>Watermelon</v>
       </c>
       <c r="E379" t="str">
-        <v>ฝรั่ง 2 ตะกร้า ตะกร้าละ 20 โล (LINE_ALBUM_Cost July_260802_53.jpg)</v>
+        <v>แตงโม 14-7-69 50 ลูก 4000 (LINE_ALBUM_Cost July_260802_59.jpg)</v>
       </c>
       <c r="F379">
-        <v>2000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>16/07/2026</v>
+        <v>17/07/2026</v>
       </c>
       <c r="B380" t="str">
         <v>Jul26</v>
@@ -8726,13 +8726,13 @@
         <v>COGS</v>
       </c>
       <c r="D380" t="str">
-        <v>Orange</v>
+        <v>Mango</v>
       </c>
       <c r="E380" t="str">
-        <v>รอบ 01/07/69 ส้ม 28x22กก 616กกx30 18,480บาท ค่าขนส่ง 28ตกx 55 1540 (LINE_ALBUM_Cost July_260802_54.jpg)</v>
+        <v>มะม่วง 52 โล(2 ตะกร้า) โลละ 50 (LINE_ALBUM_Cost July_260802_60.jpg)</v>
       </c>
       <c r="F380">
-        <v>20020</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="381">
@@ -8746,13 +8746,13 @@
         <v>COGS</v>
       </c>
       <c r="D381" t="str">
-        <v>Orange</v>
+        <v>Guava</v>
       </c>
       <c r="E381" t="str">
-        <v>ส้ม 125 โล 3450 ค่าส่ง 300 (LINE_ALBUM_Cost July_260802_55.jpg)</v>
+        <v>ฝรั่ง 2 ตะกร้า (ตะกร้าละ 20 โล) (LINE_ALBUM_Cost July_260802_61.jpg)</v>
       </c>
       <c r="F381">
-        <v>3750</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="382">
@@ -8766,13 +8766,13 @@
         <v>COGS</v>
       </c>
       <c r="D382" t="str">
-        <v>Pineapple</v>
+        <v>Apple</v>
       </c>
       <c r="E382" t="str">
-        <v>สับปะรด 25 ลูก (LINE_ALBUM_Cost July_260802_56.jpg)</v>
+        <v>แอปเปิ้ล 5 ลัง (LINE_ALBUM_Cost July_260802_62.jpg)</v>
       </c>
       <c r="F382">
-        <v>1539</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="383">
@@ -8786,18 +8786,18 @@
         <v>COGS</v>
       </c>
       <c r="D383" t="str">
-        <v>Watermelon</v>
+        <v>Coconut</v>
       </c>
       <c r="E383" t="str">
-        <v>แตงโม 10-7-69 50 ลูก 4000 11-7-69 40 ลูก 3200 (LINE_ALBUM_Cost July_260802_57.jpg)</v>
+        <v>น้ำ 30ลิตร ลิตรละ45บาท เนื้อมะพร้าว 50kg.กิโลละ 100บาท ค่าส่ง350 (LINE_ALBUM_Cost July_260802_63.jpg)</v>
       </c>
       <c r="F383">
-        <v>7200</v>
+        <v>6700</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>17/07/2026</v>
+        <v>20/07/2026</v>
       </c>
       <c r="B384" t="str">
         <v>Jul26</v>
@@ -8806,18 +8806,18 @@
         <v>COGS</v>
       </c>
       <c r="D384" t="str">
-        <v>Other</v>
+        <v>Guava</v>
       </c>
       <c r="E384" t="str">
-        <v>ทุเรียน 50 โล โลละ 85 รวม 4250 มัดจำตะกร้า 200 (LINE_ALBUM_Cost July_260802_58.jpg)</v>
+        <v>ฝรั่ง 2 ตะกร้า (LINE_ALBUM_Cost July_260802_64.jpg)</v>
       </c>
       <c r="F384">
-        <v>4450</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>17/07/2026</v>
+        <v>20/07/2026</v>
       </c>
       <c r="B385" t="str">
         <v>Jul26</v>
@@ -8826,18 +8826,18 @@
         <v>COGS</v>
       </c>
       <c r="D385" t="str">
-        <v>Watermelon</v>
+        <v>Pineapple</v>
       </c>
       <c r="E385" t="str">
-        <v>แตงโม 14-7-69 50 ลูก 4000 (LINE_ALBUM_Cost July_260802_59.jpg)</v>
+        <v>สับปะรด 20 ลูก (LINE_ALBUM_Cost July_260802_65.jpg)</v>
       </c>
       <c r="F385">
-        <v>4000</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>17/07/2026</v>
+        <v>20/07/2026</v>
       </c>
       <c r="B386" t="str">
         <v>Jul26</v>
@@ -8849,7 +8849,7 @@
         <v>Mango</v>
       </c>
       <c r="E386" t="str">
-        <v>มะม่วง 52 โล(2 ตะกร้า) โลละ 50 (LINE_ALBUM_Cost July_260802_60.jpg)</v>
+        <v>มะม่วง 2 ลัง (LINE_ALBUM_Cost July_260802_66.jpg)</v>
       </c>
       <c r="F386">
         <v>2600</v>
@@ -8857,7 +8857,7 @@
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>17/07/2026</v>
+        <v>20/07/2026</v>
       </c>
       <c r="B387" t="str">
         <v>Jul26</v>
@@ -8866,30 +8866,30 @@
         <v>COGS</v>
       </c>
       <c r="D387" t="str">
-        <v>Guava</v>
+        <v>Watermelon</v>
       </c>
       <c r="E387" t="str">
-        <v>ฝรั่ง 2 ตะกร้า (ตะกร้าละ 20 โล) (LINE_ALBUM_Cost July_260802_61.jpg)</v>
+        <v>แตงโม 17-7-2569 เบอร์ 80บาท 50 ลูก (LINE_ALBUM_Cost July_260802_67.jpg)</v>
       </c>
       <c r="F387">
-        <v>2000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>17/07/2026</v>
+        <v>21/07/2026</v>
       </c>
       <c r="B388" t="str">
         <v>Jul26</v>
       </c>
       <c r="C388" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D388" t="str">
-        <v>Apple</v>
+        <v>Other</v>
       </c>
       <c r="E388" t="str">
-        <v>แอปเปิ้ล 5 ลัง (LINE_ALBUM_Cost July_260802_62.jpg)</v>
+        <v xml:space="preserve"> (LINE_ALBUM_Cost July_260802_68.jpg)</v>
       </c>
       <c r="F388">
         <v>2000</v>
@@ -8897,7 +8897,7 @@
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>17/07/2026</v>
+        <v>22/07/2026</v>
       </c>
       <c r="B389" t="str">
         <v>Jul26</v>
@@ -8906,18 +8906,18 @@
         <v>COGS</v>
       </c>
       <c r="D389" t="str">
-        <v>Coconut</v>
+        <v>Orange</v>
       </c>
       <c r="E389" t="str">
-        <v>น้ำ 30ลิตร ลิตรละ45บาท เนื้อมะพร้าว 50kg.กิโลละ 100บาท ค่าส่ง350 (LINE_ALBUM_Cost July_260802_63.jpg)</v>
+        <v>ส้ม 25x22กก รวม 550กกx30 บ รวม 16500บาท ค่าขนส่ง 25ตกx 50 บ 1250 (LINE_ALBUM_Cost July_260802_69.jpg)</v>
       </c>
       <c r="F389">
-        <v>6700</v>
+        <v>17750</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>20/07/2026</v>
+        <v>22/07/2026</v>
       </c>
       <c r="B390" t="str">
         <v>Jul26</v>
@@ -8926,18 +8926,18 @@
         <v>COGS</v>
       </c>
       <c r="D390" t="str">
-        <v>Guava</v>
+        <v>Apple</v>
       </c>
       <c r="E390" t="str">
-        <v>ฝรั่ง 2 ตะกร้า (LINE_ALBUM_Cost July_260802_64.jpg)</v>
+        <v>แอปเปิ้ล 4 ลัง (LINE_ALBUM_Cost July_260802_70.jpg)</v>
       </c>
       <c r="F390">
-        <v>2000</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>20/07/2026</v>
+        <v>22/07/2026</v>
       </c>
       <c r="B391" t="str">
         <v>Jul26</v>
@@ -8946,58 +8946,58 @@
         <v>COGS</v>
       </c>
       <c r="D391" t="str">
-        <v>Pineapple</v>
+        <v>Mango</v>
       </c>
       <c r="E391" t="str">
-        <v>สับปะรด 20 ลูก (LINE_ALBUM_Cost July_260802_65.jpg)</v>
+        <v>มะม่วง 78 กิโล 3 ลัง (LINE_ALBUM_Cost July_260802_71.jpg)</v>
       </c>
       <c r="F391">
-        <v>1296</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>20/07/2026</v>
+        <v>22/07/2026</v>
       </c>
       <c r="B392" t="str">
         <v>Jul26</v>
       </c>
       <c r="C392" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D392" t="str">
-        <v>Mango</v>
+        <v>Other</v>
       </c>
       <c r="E392" t="str">
-        <v>มะม่วง 2 ลัง (LINE_ALBUM_Cost July_260802_66.jpg)</v>
+        <v>OPEX Avocado milk (LINE_ALBUM_Cost July_260802_74.jpg)</v>
       </c>
       <c r="F392">
-        <v>2600</v>
+        <v>440.75</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>20/07/2026</v>
+        <v>22/07/2026</v>
       </c>
       <c r="B393" t="str">
         <v>Jul26</v>
       </c>
       <c r="C393" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D393" t="str">
-        <v>Watermelon</v>
+        <v>Other</v>
       </c>
       <c r="E393" t="str">
-        <v>แตงโม 17-7-2569 เบอร์ 80บาท 50 ลูก (LINE_ALBUM_Cost July_260802_67.jpg)</v>
+        <v>Opex knife (LINE_ALBUM_Cost July_260802_75.jpg)</v>
       </c>
       <c r="F393">
-        <v>4000</v>
+        <v>199</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>21/07/2026</v>
+        <v>22/07/2026</v>
       </c>
       <c r="B394" t="str">
         <v>Jul26</v>
@@ -9009,10 +9009,10 @@
         <v>Other</v>
       </c>
       <c r="E394" t="str">
-        <v xml:space="preserve"> (LINE_ALBUM_Cost July_260802_68.jpg)</v>
+        <v>Opex equipment (LINE_ALBUM_Cost July_260802_76.jpg)</v>
       </c>
       <c r="F394">
-        <v>2000</v>
+        <v>221</v>
       </c>
     </row>
     <row r="395">
@@ -9026,13 +9026,13 @@
         <v>COGS</v>
       </c>
       <c r="D395" t="str">
-        <v>Orange</v>
+        <v>Stock</v>
       </c>
       <c r="E395" t="str">
-        <v>ส้ม 25x22กก รวม 550กกx30 บ รวม 16500บาท ค่าขนส่ง 25ตกx 50 บ 1250 (LINE_ALBUM_Cost July_260802_69.jpg)</v>
+        <v>Cogs Falcon milk (LINE_ALBUM_Cost July_260802_77.jpg)</v>
       </c>
       <c r="F395">
-        <v>17750</v>
+        <v>716</v>
       </c>
     </row>
     <row r="396">
@@ -9043,16 +9043,16 @@
         <v>Jul26</v>
       </c>
       <c r="C396" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D396" t="str">
-        <v>Apple</v>
+        <v>Other</v>
       </c>
       <c r="E396" t="str">
-        <v>แอปเปิ้ล 4 ลัง (LINE_ALBUM_Cost July_260802_70.jpg)</v>
+        <v>Opex B1 police fee 1000 / person (LINE_ALBUM_Cost July_260802_78.jpg)</v>
       </c>
       <c r="F396">
-        <v>1600</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="397">
@@ -9063,16 +9063,16 @@
         <v>Jul26</v>
       </c>
       <c r="C397" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D397" t="str">
-        <v>Mango</v>
+        <v>Other</v>
       </c>
       <c r="E397" t="str">
-        <v>มะม่วง 78 กิโล 3 ลัง (LINE_ALBUM_Cost July_260802_71.jpg)</v>
+        <v>Opex equipments (LINE_ALBUM_Cost July_260802_79.jpg)</v>
       </c>
       <c r="F397">
-        <v>3900</v>
+        <v>506</v>
       </c>
     </row>
     <row r="398">
@@ -9089,55 +9089,55 @@
         <v>Other</v>
       </c>
       <c r="E398" t="str">
-        <v>OPEX Avocado milk (LINE_ALBUM_Cost July_260802_74.jpg)</v>
+        <v>Opex other (LINE_ALBUM_Cost July_260802_80.jpg)</v>
       </c>
       <c r="F398">
-        <v>440.75</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>22/07/2026</v>
+        <v>23/07/2026</v>
       </c>
       <c r="B399" t="str">
         <v>Jul26</v>
       </c>
       <c r="C399" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D399" t="str">
-        <v>Other</v>
+        <v>Watermelon</v>
       </c>
       <c r="E399" t="str">
-        <v>Opex knife (LINE_ALBUM_Cost July_260802_75.jpg)</v>
+        <v>20-7-2569 ราคา 80 - 45ลูก 22-7-2569 ราคา 80 - 30 ลูก 23-7-2569 ราคา 80 - 30 ลูก (LINE_ALBUM_Cost July_260802_81.jpg)</v>
       </c>
       <c r="F399">
-        <v>199</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>22/07/2026</v>
+        <v>23/07/2026</v>
       </c>
       <c r="B400" t="str">
         <v>Jul26</v>
       </c>
       <c r="C400" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D400" t="str">
-        <v>Other</v>
+        <v>Guava</v>
       </c>
       <c r="E400" t="str">
-        <v>Opex equipment (LINE_ALBUM_Cost July_260802_76.jpg)</v>
+        <v>ฝรั่ง 2 ลัง ลังละ 20 กิโล กิโลละ 50 บาท รวม 2000 บาท (LINE_ALBUM_Cost July_260802_82.jpg)</v>
       </c>
       <c r="F400">
-        <v>221</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>22/07/2026</v>
+        <v>23/07/2026</v>
       </c>
       <c r="B401" t="str">
         <v>Jul26</v>
@@ -9146,18 +9146,18 @@
         <v>COGS</v>
       </c>
       <c r="D401" t="str">
-        <v>Stock</v>
+        <v>Pineapple</v>
       </c>
       <c r="E401" t="str">
-        <v>Cogs Falcon milk (LINE_ALBUM_Cost July_260802_77.jpg)</v>
+        <v>สับปะรด 41 กิโล *27 บาท รวม 1107 บาท (LINE_ALBUM_Cost July_260802_83.jpg)</v>
       </c>
       <c r="F401">
-        <v>716</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>22/07/2026</v>
+        <v>31/07/2026</v>
       </c>
       <c r="B402" t="str">
         <v>Jul26</v>
@@ -9166,18 +9166,18 @@
         <v>OPEX</v>
       </c>
       <c r="D402" t="str">
-        <v>Other</v>
+        <v>Rental</v>
       </c>
       <c r="E402" t="str">
-        <v>Opex B1 police fee 1000 / person (LINE_ALBUM_Cost July_260802_78.jpg)</v>
+        <v>Rent B1</v>
       </c>
       <c r="F402">
-        <v>2000</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>22/07/2026</v>
+        <v>31/07/2026</v>
       </c>
       <c r="B403" t="str">
         <v>Jul26</v>
@@ -9186,301 +9186,301 @@
         <v>OPEX</v>
       </c>
       <c r="D403" t="str">
-        <v>Other</v>
+        <v>Salary</v>
       </c>
       <c r="E403" t="str">
-        <v>Opex equipments (LINE_ALBUM_Cost July_260802_79.jpg)</v>
+        <v>Salary B1</v>
       </c>
       <c r="F403">
-        <v>506</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>22/07/2026</v>
+        <v>23/05/2026</v>
       </c>
       <c r="B404" t="str">
-        <v>Jul26</v>
+        <v>May26</v>
       </c>
       <c r="C404" t="str">
-        <v>OPEX</v>
+        <v>EXCLUDED</v>
       </c>
       <c r="D404" t="str">
-        <v>Other</v>
+        <v>Pass-Through</v>
       </c>
       <c r="E404" t="str">
-        <v>Opex other (LINE_ALBUM_Cost July_260802_80.jpg)</v>
+        <v>มังคุด (รับเงินสด 28,000 แล้วโอนต่อ ฐนกร 23/05 17:23) - ไม่ใช่ต้นทุน SSJ [bank]</v>
       </c>
       <c r="F404">
-        <v>1918</v>
+        <v>0</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>23/07/2026</v>
+        <v>01/05/2026</v>
       </c>
       <c r="B405" t="str">
-        <v>Jul26</v>
+        <v>May26</v>
       </c>
       <c r="C405" t="str">
         <v>COGS</v>
       </c>
       <c r="D405" t="str">
-        <v>Watermelon</v>
+        <v>Transportation</v>
       </c>
       <c r="E405" t="str">
-        <v>20-7-2569 ราคา 80 - 45ลูก 22-7-2569 ราคา 80 - 30 ลูก 23-7-2569 ราคา 80 - 30 ลูก (LINE_ALBUM_Cost July_260802_81.jpg)</v>
+        <v>ลาลามูฟ Lalamove [bank]</v>
       </c>
       <c r="F405">
-        <v>8400</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>23/07/2026</v>
+        <v>07/05/2026</v>
       </c>
       <c r="B406" t="str">
-        <v>Jul26</v>
+        <v>May26</v>
       </c>
       <c r="C406" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D406" t="str">
-        <v>Guava</v>
+        <v>Other</v>
       </c>
       <c r="E406" t="str">
-        <v>ฝรั่ง 2 ลัง ลังละ 20 กิโล กิโลละ 50 บาท รวม 2000 บาท (LINE_ALBUM_Cost July_260802_82.jpg)</v>
+        <v>บจก. อาร์.เอ็น.คลีน ทำความสะอาด [bank]</v>
       </c>
       <c r="F406">
-        <v>2000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>23/07/2026</v>
+        <v>01/05/2026</v>
       </c>
       <c r="B407" t="str">
-        <v>Jul26</v>
+        <v>May26</v>
       </c>
       <c r="C407" t="str">
         <v>COGS</v>
       </c>
       <c r="D407" t="str">
-        <v>Pineapple</v>
+        <v>Mango</v>
       </c>
       <c r="E407" t="str">
-        <v>สับปะรด 41 กิโล *27 บาท รวม 1107 บาท (LINE_ALBUM_Cost July_260802_83.jpg)</v>
+        <v>LINE Pay Merchant [bank]</v>
       </c>
       <c r="F407">
-        <v>1107</v>
+        <v>780</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>31/07/2026</v>
+        <v>01/05/2026</v>
       </c>
       <c r="B408" t="str">
-        <v>Jul26</v>
+        <v>May26</v>
       </c>
       <c r="C408" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D408" t="str">
-        <v>Rental</v>
+        <v>Pineapple</v>
       </c>
       <c r="E408" t="str">
-        <v>Rent B1</v>
+        <v>น.ส. สุพิชญา [bank]</v>
       </c>
       <c r="F408">
-        <v>35000</v>
+        <v>684</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>31/07/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="B409" t="str">
-        <v>Jul26</v>
+        <v>May26</v>
       </c>
       <c r="C409" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D409" t="str">
-        <v>Salary</v>
+        <v>Guava</v>
       </c>
       <c r="E409" t="str">
-        <v>Salary B1</v>
+        <v>ฝรั่ง 1 ตะกร้า (นาง ประนอม) [bank]</v>
       </c>
       <c r="F409">
-        <v>35000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>23/05/2026</v>
+        <v>30/04/2026</v>
       </c>
       <c r="B410" t="str">
-        <v>May26</v>
+        <v>Apr26</v>
       </c>
       <c r="C410" t="str">
-        <v>EXCLUDED</v>
+        <v>OPEX</v>
       </c>
       <c r="D410" t="str">
-        <v>Pass-Through</v>
+        <v>Marketing</v>
       </c>
       <c r="E410" t="str">
-        <v>มังคุด (รับเงินสด 28,000 แล้วโอนต่อ ฐนกร 23/05 17:23) - ไม่ใช่ต้นทุน SSJ [bank]</v>
+        <v>ปืนฉีดน้ำ สงกรานต์ (จ่าย 06/05) [bank]</v>
       </c>
       <c r="F410">
-        <v>0</v>
+        <v>24016</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>01/05/2026</v>
+        <v>30/04/2026</v>
       </c>
       <c r="B411" t="str">
-        <v>May26</v>
+        <v>Apr26</v>
       </c>
       <c r="C411" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D411" t="str">
-        <v>Transportation</v>
+        <v>Salary</v>
       </c>
       <c r="E411" t="str">
-        <v>ลาลามูฟ Lalamove [bank]</v>
+        <v>เงินเดือน เม.ย. (จ่าย 01/05) [bank]</v>
       </c>
       <c r="F411">
-        <v>2000</v>
+        <v>31000</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>07/05/2026</v>
+        <v>04/04/2026</v>
       </c>
       <c r="B412" t="str">
-        <v>May26</v>
+        <v>Apr26</v>
       </c>
       <c r="C412" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D412" t="str">
-        <v>Other</v>
+        <v>Packaging</v>
       </c>
       <c r="E412" t="str">
-        <v>บจก. อาร์.เอ็น.คลีน ทำความสะอาด [bank]</v>
+        <v>Shopee (ทีมจัดซื้อ) [bank SA8285]</v>
       </c>
       <c r="F412">
-        <v>1000</v>
+        <v>11732</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>01/05/2026</v>
+        <v>05/04/2026</v>
       </c>
       <c r="B413" t="str">
-        <v>May26</v>
+        <v>Apr26</v>
       </c>
       <c r="C413" t="str">
         <v>COGS</v>
       </c>
       <c r="D413" t="str">
-        <v>Mango</v>
+        <v>Packaging</v>
       </c>
       <c r="E413" t="str">
-        <v>LINE Pay Merchant [bank]</v>
+        <v>Shopee (ทีมจัดซื้อ) [bank SA8285]</v>
       </c>
       <c r="F413">
-        <v>780</v>
+        <v>672</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>01/05/2026</v>
+        <v>16/04/2026</v>
       </c>
       <c r="B414" t="str">
-        <v>May26</v>
+        <v>Apr26</v>
       </c>
       <c r="C414" t="str">
         <v>COGS</v>
       </c>
       <c r="D414" t="str">
-        <v>Pineapple</v>
+        <v>Packaging</v>
       </c>
       <c r="E414" t="str">
-        <v>น.ส. สุพิชญา [bank]</v>
+        <v>Shopee (ทีมจัดซื้อ) [bank SA8285]</v>
       </c>
       <c r="F414">
-        <v>684</v>
+        <v>11560</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>09/05/2026</v>
+        <v>20/04/2026</v>
       </c>
       <c r="B415" t="str">
-        <v>May26</v>
+        <v>Apr26</v>
       </c>
       <c r="C415" t="str">
         <v>COGS</v>
       </c>
       <c r="D415" t="str">
-        <v>Guava</v>
+        <v>Packaging</v>
       </c>
       <c r="E415" t="str">
-        <v>ฝรั่ง 1 ตะกร้า (นาง ประนอม) [bank]</v>
+        <v>Shopee (ทีมจัดซื้อ) [bank SA8285]</v>
       </c>
       <c r="F415">
-        <v>600</v>
+        <v>692</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>30/04/2026</v>
+        <v>25/04/2026</v>
       </c>
       <c r="B416" t="str">
         <v>Apr26</v>
       </c>
       <c r="C416" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D416" t="str">
-        <v>Marketing</v>
+        <v>Packaging</v>
       </c>
       <c r="E416" t="str">
-        <v>ปืนฉีดน้ำ สงกรานต์ (จ่าย 06/05) [bank]</v>
+        <v>Shopee (ทีมจัดซื้อ) [bank SA8285]</v>
       </c>
       <c r="F416">
-        <v>24016</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>30/04/2026</v>
+        <v>21/06/2026</v>
       </c>
       <c r="B417" t="str">
-        <v>Apr26</v>
+        <v>Jun26</v>
       </c>
       <c r="C417" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D417" t="str">
-        <v>Salary</v>
+        <v>Packaging</v>
       </c>
       <c r="E417" t="str">
-        <v>เงินเดือน เม.ย. (จ่าย 01/05) [bank]</v>
+        <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F417">
-        <v>31000</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>04/04/2026</v>
+        <v>21/06/2026</v>
       </c>
       <c r="B418" t="str">
-        <v>Apr26</v>
+        <v>Jun26</v>
       </c>
       <c r="C418" t="str">
         <v>COGS</v>
@@ -9489,18 +9489,18 @@
         <v>Packaging</v>
       </c>
       <c r="E418" t="str">
-        <v>Shopee (ทีมจัดซื้อ) [bank SA8285]</v>
+        <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F418">
-        <v>11732</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>05/04/2026</v>
+        <v>21/06/2026</v>
       </c>
       <c r="B419" t="str">
-        <v>Apr26</v>
+        <v>Jun26</v>
       </c>
       <c r="C419" t="str">
         <v>COGS</v>
@@ -9509,18 +9509,18 @@
         <v>Packaging</v>
       </c>
       <c r="E419" t="str">
-        <v>Shopee (ทีมจัดซื้อ) [bank SA8285]</v>
+        <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F419">
-        <v>672</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>16/04/2026</v>
+        <v>21/06/2026</v>
       </c>
       <c r="B420" t="str">
-        <v>Apr26</v>
+        <v>Jun26</v>
       </c>
       <c r="C420" t="str">
         <v>COGS</v>
@@ -9529,18 +9529,18 @@
         <v>Packaging</v>
       </c>
       <c r="E420" t="str">
-        <v>Shopee (ทีมจัดซื้อ) [bank SA8285]</v>
+        <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F420">
-        <v>11560</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>20/04/2026</v>
+        <v>21/06/2026</v>
       </c>
       <c r="B421" t="str">
-        <v>Apr26</v>
+        <v>Jun26</v>
       </c>
       <c r="C421" t="str">
         <v>COGS</v>
@@ -9549,18 +9549,18 @@
         <v>Packaging</v>
       </c>
       <c r="E421" t="str">
-        <v>Shopee (ทีมจัดซื้อ) [bank SA8285]</v>
+        <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F421">
-        <v>692</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>25/04/2026</v>
+        <v>21/06/2026</v>
       </c>
       <c r="B422" t="str">
-        <v>Apr26</v>
+        <v>Jun26</v>
       </c>
       <c r="C422" t="str">
         <v>COGS</v>
@@ -9569,10 +9569,10 @@
         <v>Packaging</v>
       </c>
       <c r="E422" t="str">
-        <v>Shopee (ทีมจัดซื้อ) [bank SA8285]</v>
+        <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F422">
-        <v>1838</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="423">
@@ -9592,7 +9592,7 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F423">
-        <v>1377</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="424">
@@ -9612,7 +9612,7 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F424">
-        <v>1210</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="425">
@@ -9632,7 +9632,7 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F425">
-        <v>1210</v>
+        <v>3051</v>
       </c>
     </row>
     <row r="426">
@@ -9652,12 +9652,12 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F426">
-        <v>1242</v>
+        <v>755</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>21/06/2026</v>
+        <v>29/06/2026</v>
       </c>
       <c r="B427" t="str">
         <v>Jun26</v>
@@ -9672,12 +9672,12 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F427">
-        <v>1232</v>
+        <v>7766</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>21/06/2026</v>
+        <v>29/06/2026</v>
       </c>
       <c r="B428" t="str">
         <v>Jun26</v>
@@ -9692,12 +9692,12 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F428">
-        <v>1286</v>
+        <v>539</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>21/06/2026</v>
+        <v>29/06/2026</v>
       </c>
       <c r="B429" t="str">
         <v>Jun26</v>
@@ -9712,15 +9712,15 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F429">
-        <v>1295</v>
+        <v>596</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>21/06/2026</v>
+        <v>07/07/2026</v>
       </c>
       <c r="B430" t="str">
-        <v>Jun26</v>
+        <v>Jul26</v>
       </c>
       <c r="C430" t="str">
         <v>COGS</v>
@@ -9732,15 +9732,15 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F430">
-        <v>1445</v>
+        <v>141</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>21/06/2026</v>
+        <v>07/07/2026</v>
       </c>
       <c r="B431" t="str">
-        <v>Jun26</v>
+        <v>Jul26</v>
       </c>
       <c r="C431" t="str">
         <v>COGS</v>
@@ -9752,15 +9752,15 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F431">
-        <v>3051</v>
+        <v>7999</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>21/06/2026</v>
+        <v>07/07/2026</v>
       </c>
       <c r="B432" t="str">
-        <v>Jun26</v>
+        <v>Jul26</v>
       </c>
       <c r="C432" t="str">
         <v>COGS</v>
@@ -9772,15 +9772,15 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F432">
-        <v>755</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>29/06/2026</v>
+        <v>08/07/2026</v>
       </c>
       <c r="B433" t="str">
-        <v>Jun26</v>
+        <v>Jul26</v>
       </c>
       <c r="C433" t="str">
         <v>COGS</v>
@@ -9792,15 +9792,15 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F433">
-        <v>7766</v>
+        <v>9870</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>29/06/2026</v>
+        <v>24/07/2026</v>
       </c>
       <c r="B434" t="str">
-        <v>Jun26</v>
+        <v>Jul26</v>
       </c>
       <c r="C434" t="str">
         <v>COGS</v>
@@ -9812,52 +9812,52 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F434">
-        <v>539</v>
+        <v>7410</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>29/06/2026</v>
+        <v>26/07/2026</v>
       </c>
       <c r="B435" t="str">
-        <v>Jun26</v>
+        <v>Jul26</v>
       </c>
       <c r="C435" t="str">
-        <v>COGS</v>
+        <v>CAPEX</v>
       </c>
       <c r="D435" t="str">
-        <v>Packaging</v>
+        <v>Investment</v>
       </c>
       <c r="E435" t="str">
-        <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
+        <v>เครื่องสกัดเย็น 1 เครื่อง (Shopee, audit fix - was COGS/Packaging)</v>
       </c>
       <c r="F435">
-        <v>596</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>07/07/2026</v>
+        <v>26/07/2026</v>
       </c>
       <c r="B436" t="str">
         <v>Jul26</v>
       </c>
       <c r="C436" t="str">
-        <v>COGS</v>
+        <v>CAPEX</v>
       </c>
       <c r="D436" t="str">
-        <v>Packaging</v>
+        <v>Investment</v>
       </c>
       <c r="E436" t="str">
-        <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
+        <v>เครื่องสกัดเย็น 1 เครื่อง (Shopee, audit fix - was COGS/Packaging)</v>
       </c>
       <c r="F436">
-        <v>141</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>07/07/2026</v>
+        <v>27/07/2026</v>
       </c>
       <c r="B437" t="str">
         <v>Jul26</v>
@@ -9872,12 +9872,12 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F437">
-        <v>7999</v>
+        <v>4309</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>07/07/2026</v>
+        <v>27/07/2026</v>
       </c>
       <c r="B438" t="str">
         <v>Jul26</v>
@@ -9892,612 +9892,472 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F438">
-        <v>1399</v>
+        <v>2589</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>08/07/2026</v>
+        <v>31/01/2026</v>
       </c>
       <c r="B439" t="str">
-        <v>Jul26</v>
+        <v>Jan26</v>
       </c>
       <c r="C439" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D439" t="str">
-        <v>Packaging</v>
+        <v>Rental</v>
       </c>
       <c r="E439" t="str">
-        <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
+        <v>ค่าเช่าร้าน Jan26 (ปรับตามงบการเงินเจ้าของ)</v>
       </c>
       <c r="F439">
-        <v>9870</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>24/07/2026</v>
+        <v>28/02/2026</v>
       </c>
       <c r="B440" t="str">
-        <v>Jul26</v>
+        <v>Feb26</v>
       </c>
       <c r="C440" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D440" t="str">
-        <v>Packaging</v>
+        <v>Rental</v>
       </c>
       <c r="E440" t="str">
-        <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
+        <v>ค่าเช่าร้าน Feb26 (ปรับตามงบการเงินเจ้าของ)</v>
       </c>
       <c r="F440">
-        <v>7410</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>26/07/2026</v>
+        <v>28/02/2026</v>
       </c>
       <c r="B441" t="str">
-        <v>Jul26</v>
+        <v>Feb26</v>
       </c>
       <c r="C441" t="str">
-        <v>CAPEX</v>
+        <v>OPEX</v>
       </c>
       <c r="D441" t="str">
-        <v>Investment</v>
+        <v>Salary</v>
       </c>
       <c r="E441" t="str">
-        <v>เครื่องสกัดเย็น 1 เครื่อง (Shopee, audit fix - was COGS/Packaging)</v>
+        <v>ค่าแรงคนงาน Feb26 (ปรับตามงบการเงินเจ้าของ)</v>
       </c>
       <c r="F441">
-        <v>1015</v>
+        <v>19000</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>26/07/2026</v>
+        <v>31/03/2026</v>
       </c>
       <c r="B442" t="str">
-        <v>Jul26</v>
+        <v>Mar26</v>
       </c>
       <c r="C442" t="str">
-        <v>CAPEX</v>
+        <v>OPEX</v>
       </c>
       <c r="D442" t="str">
-        <v>Investment</v>
+        <v>Rental</v>
       </c>
       <c r="E442" t="str">
-        <v>เครื่องสกัดเย็น 1 เครื่อง (Shopee, audit fix - was COGS/Packaging)</v>
+        <v>ค่าเช่าร้าน Mar26 (ปรับตามงบการเงินเจ้าของ)</v>
       </c>
       <c r="F442">
-        <v>1087</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>27/07/2026</v>
+        <v>31/03/2026</v>
       </c>
       <c r="B443" t="str">
-        <v>Jul26</v>
+        <v>Mar26</v>
       </c>
       <c r="C443" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D443" t="str">
-        <v>Packaging</v>
+        <v>Rental</v>
       </c>
       <c r="E443" t="str">
-        <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
+        <v>ค่าเช่าคลัง Mar26 (ปรับตามงบการเงินเจ้าของ)</v>
       </c>
       <c r="F443">
-        <v>4309</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>27/07/2026</v>
+        <v>31/03/2026</v>
       </c>
       <c r="B444" t="str">
-        <v>Jul26</v>
+        <v>Mar26</v>
       </c>
       <c r="C444" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D444" t="str">
-        <v>Packaging</v>
+        <v>Salary</v>
       </c>
       <c r="E444" t="str">
-        <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
+        <v>ค่าแรงคนงาน Mar26 (ปรับตามงบการเงินเจ้าของ)</v>
       </c>
       <c r="F444">
-        <v>2589</v>
+        <v>27600</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>31/01/2026</v>
+        <v>31/03/2026</v>
       </c>
       <c r="B445" t="str">
-        <v>Jan26</v>
+        <v>Mar26</v>
       </c>
       <c r="C445" t="str">
         <v>OPEX</v>
       </c>
       <c r="D445" t="str">
-        <v>Rental</v>
+        <v>Other</v>
       </c>
       <c r="E445" t="str">
-        <v>ค่าเช่าร้าน Jan26 (ปรับตามงบการเงินเจ้าของ)</v>
+        <v>ค่าน้ำ + ค่าไฟ Mar26 (ปรับตามงบการเงินเจ้าของ)</v>
       </c>
       <c r="F445">
-        <v>30000</v>
+        <v>3229</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>28/02/2026</v>
+        <v>22/06/2026</v>
       </c>
       <c r="B446" t="str">
-        <v>Feb26</v>
+        <v>Jun26</v>
       </c>
       <c r="C446" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D446" t="str">
-        <v>Rental</v>
+        <v>Guava</v>
       </c>
       <c r="E446" t="str">
-        <v>ค่าเช่าร้าน Feb26 (ปรับตามงบการเงินเจ้าของ)</v>
+        <v>ฝรั่ง (นาง ประนอม) [bank]</v>
       </c>
       <c r="F446">
-        <v>35000</v>
+        <v>100</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>28/02/2026</v>
+        <v>25/06/2026</v>
       </c>
       <c r="B447" t="str">
-        <v>Feb26</v>
+        <v>Jun26</v>
       </c>
       <c r="C447" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D447" t="str">
-        <v>Salary</v>
+        <v>Guava</v>
       </c>
       <c r="E447" t="str">
-        <v>ค่าแรงคนงาน Feb26 (ปรับตามงบการเงินเจ้าของ)</v>
+        <v>ฝรั่ง 1 ตะกร้า (นาง ประนอม) [bank]</v>
       </c>
       <c r="F447">
-        <v>19000</v>
+        <v>800</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>31/03/2026</v>
+        <v>28/07/2026</v>
       </c>
       <c r="B448" t="str">
-        <v>Mar26</v>
+        <v>Jul26</v>
       </c>
       <c r="C448" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D448" t="str">
-        <v>Rental</v>
+        <v>Guava</v>
       </c>
       <c r="E448" t="str">
-        <v>ค่าเช่าร้าน Mar26 (ปรับตามงบการเงินเจ้าของ)</v>
+        <v>ฝรั่ง (นาง ประนอม) [bank]</v>
       </c>
       <c r="F448">
-        <v>35000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>31/03/2026</v>
+        <v>20/02/2026</v>
       </c>
       <c r="B449" t="str">
-        <v>Mar26</v>
+        <v>Feb26</v>
       </c>
       <c r="C449" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D449" t="str">
-        <v>Rental</v>
+        <v>Transportation</v>
       </c>
       <c r="E449" t="str">
-        <v>ค่าเช่าคลัง Mar26 (ปรับตามงบการเงินเจ้าของ)</v>
+        <v>ค่ารถ (แยกจากใบเสร็จผ้าปิดร้าน 416)</v>
       </c>
       <c r="F449">
-        <v>12000</v>
+        <v>198</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>31/03/2026</v>
+        <v>04/06/2026</v>
       </c>
       <c r="B450" t="str">
-        <v>Mar26</v>
+        <v>Jun26</v>
       </c>
       <c r="C450" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D450" t="str">
-        <v>Salary</v>
+        <v>Pineapple</v>
       </c>
       <c r="E450" t="str">
-        <v>ค่าแรงคนงาน Mar26 (ปรับตามงบการเงินเจ้าของ)</v>
+        <v>สลิปรวม: สับปะรด 750 (audit fix, was bundled)</v>
       </c>
       <c r="F450">
-        <v>27600</v>
+        <v>750</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>31/03/2026</v>
+        <v>04/06/2026</v>
       </c>
       <c r="B451" t="str">
-        <v>Mar26</v>
+        <v>Jun26</v>
       </c>
       <c r="C451" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D451" t="str">
-        <v>Other</v>
+        <v>Orange</v>
       </c>
       <c r="E451" t="str">
-        <v>ค่าน้ำ + ค่าไฟ Mar26 (ปรับตามงบการเงินเจ้าของ)</v>
+        <v>สลิปรวม: ส้ม 2250 (audit fix, was bundled into Pineapple line)</v>
       </c>
       <c r="F451">
-        <v>3229</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>22/06/2026</v>
+        <v>04/06/2026</v>
       </c>
       <c r="B452" t="str">
         <v>Jun26</v>
       </c>
       <c r="C452" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D452" t="str">
-        <v>Guava</v>
+        <v>Other</v>
       </c>
       <c r="E452" t="str">
-        <v>ฝรั่ง (นาง ประนอม) [bank]</v>
+        <v>ค่าปรับตำรวจ 2 คน (police fee, audit fix - was miscategorized as COGS/Pineapple)</v>
       </c>
       <c r="F452">
-        <v>100</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>25/06/2026</v>
+        <v>26/07/2026</v>
       </c>
       <c r="B453" t="str">
-        <v>Jun26</v>
+        <v>Jul26</v>
       </c>
       <c r="C453" t="str">
-        <v>COGS</v>
+        <v>CAPEX</v>
       </c>
       <c r="D453" t="str">
-        <v>Guava</v>
+        <v>Investment</v>
       </c>
       <c r="E453" t="str">
-        <v>ฝรั่ง 1 ตะกร้า (นาง ประนอม) [bank]</v>
+        <v>งบลงทุน - ทดลองอื่นๆ (LINE_ALBUM_Cost July_260802_8.jpg, audit fix - was bundled into COGS/Mango)</v>
       </c>
       <c r="F453">
-        <v>800</v>
+        <v>810</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>28/07/2026</v>
+        <v>26/07/2026</v>
       </c>
       <c r="B454" t="str">
         <v>Jul26</v>
       </c>
       <c r="C454" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D454" t="str">
-        <v>Guava</v>
+        <v>Other</v>
       </c>
       <c r="E454" t="str">
-        <v>ฝรั่ง (นาง ประนอม) [bank]</v>
+        <v>ค่าส่งของ (LINE_ALBUM_Cost July_260802_11.jpg, audit fix - missing entry)</v>
       </c>
       <c r="F454">
-        <v>3000</v>
+        <v>212</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>20/02/2026</v>
+        <v>28/07/2026</v>
       </c>
       <c r="B455" t="str">
-        <v>Feb26</v>
+        <v>Jul26</v>
       </c>
       <c r="C455" t="str">
         <v>COGS</v>
       </c>
       <c r="D455" t="str">
-        <v>Transportation</v>
+        <v>Pineapple</v>
       </c>
       <c r="E455" t="str">
-        <v>ค่ารถ (แยกจากใบเสร็จผ้าปิดร้าน 416)</v>
+        <v>สับปะรด 30 ลูก (LINE_ALBUM_Cost July_260802_17.jpg, audit fix - missing entry)</v>
       </c>
       <c r="F455">
-        <v>198</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>04/06/2026</v>
+        <v>28/07/2026</v>
       </c>
       <c r="B456" t="str">
-        <v>Jun26</v>
+        <v>Jul26</v>
       </c>
       <c r="C456" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D456" t="str">
-        <v>Pineapple</v>
+        <v>Other</v>
       </c>
       <c r="E456" t="str">
-        <v>สลิปรวม: สับปะรด 750 (audit fix, was bundled)</v>
+        <v>ค่าขนส่ง (LINE_ALBUM_Cost July_260802_19.jpg, audit fix - missing entry)</v>
       </c>
       <c r="F456">
-        <v>750</v>
+        <v>100</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>04/06/2026</v>
+        <v>30/04/2026</v>
       </c>
       <c r="B457" t="str">
-        <v>Jun26</v>
+        <v>Apr26</v>
       </c>
       <c r="C457" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D457" t="str">
-        <v>Orange</v>
+        <v>Rental</v>
       </c>
       <c r="E457" t="str">
-        <v>สลิปรวม: ส้ม 2250 (audit fix, was bundled into Pineapple line)</v>
+        <v>ค่าเช่า stock เม.ย. (B1 ครึ่งหนึ่ง)</v>
       </c>
       <c r="F457">
-        <v>2250</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>04/06/2026</v>
+        <v>05/03/2026</v>
       </c>
       <c r="B458" t="str">
-        <v>Jun26</v>
+        <v>Mar26</v>
       </c>
       <c r="C458" t="str">
         <v>OPEX</v>
       </c>
       <c r="D458" t="str">
-        <v>Other</v>
+        <v>Salary</v>
       </c>
       <c r="E458" t="str">
-        <v>ค่าปรับตำรวจ 2 คน (police fee, audit fix - was miscategorized as COGS/Pineapple)</v>
+        <v>เงินเดือนเมน 3/26</v>
       </c>
       <c r="F458">
-        <v>2000</v>
+        <v>19000</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>26/07/2026</v>
+        <v>27/02/2026</v>
       </c>
       <c r="B459" t="str">
-        <v>Jul26</v>
+        <v>Feb26</v>
       </c>
       <c r="C459" t="str">
-        <v>CAPEX</v>
+        <v>OPEX</v>
       </c>
       <c r="D459" t="str">
         <v>Investment</v>
       </c>
       <c r="E459" t="str">
-        <v>งบลงทุน - ทดลองอื่นๆ (LINE_ALBUM_Cost July_260802_8.jpg, audit fix - was bundled into COGS/Mango)</v>
+        <v>อุปกรณ์ (จากสลิปโอนผู้จัดการ)</v>
       </c>
       <c r="F459">
-        <v>810</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>26/07/2026</v>
+        <v>18/03/2026</v>
       </c>
       <c r="B460" t="str">
-        <v>Jul26</v>
+        <v>Mar26</v>
       </c>
       <c r="C460" t="str">
         <v>OPEX</v>
       </c>
       <c r="D460" t="str">
-        <v>Other</v>
+        <v>Milk/Conden</v>
       </c>
       <c r="E460" t="str">
-        <v>ค่าส่งของ (LINE_ALBUM_Cost July_260802_11.jpg, audit fix - missing entry)</v>
+        <v>นม + นมข้นหวาน (จากสลิปโอนผู้จัดการ)</v>
       </c>
       <c r="F460">
-        <v>212</v>
+        <v>230</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>28/07/2026</v>
+        <v>01/04/2026</v>
       </c>
       <c r="B461" t="str">
-        <v>Jul26</v>
+        <v>Mar26</v>
       </c>
       <c r="C461" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D461" t="str">
-        <v>Pineapple</v>
+        <v>Salary</v>
       </c>
       <c r="E461" t="str">
-        <v>สับปะรด 30 ลูก (LINE_ALBUM_Cost July_260802_17.jpg, audit fix - missing entry)</v>
+        <v>เงินเดือนพนักงาน 3 คน มี.ค. 26</v>
       </c>
       <c r="F461">
-        <v>1188</v>
-      </c>
-    </row>
-    <row r="462">
-      <c r="A462" t="str">
-        <v>28/07/2026</v>
-      </c>
-      <c r="B462" t="str">
-        <v>Jul26</v>
-      </c>
-      <c r="C462" t="str">
-        <v>OPEX</v>
-      </c>
-      <c r="D462" t="str">
-        <v>Other</v>
-      </c>
-      <c r="E462" t="str">
-        <v>ค่าขนส่ง (LINE_ALBUM_Cost July_260802_19.jpg, audit fix - missing entry)</v>
-      </c>
-      <c r="F462">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="463">
-      <c r="A463" t="str">
-        <v>31/07/2026</v>
-      </c>
-      <c r="B463" t="str">
-        <v>Jul26</v>
-      </c>
-      <c r="C463" t="str">
-        <v>OPEX</v>
-      </c>
-      <c r="D463" t="str">
-        <v>Other</v>
-      </c>
-      <c r="E463" t="str">
-        <v>Lalamove (LINE_ALBUM_Cost July_260802_25.jpg, audit fix - missing entry)</v>
-      </c>
-      <c r="F463">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="464">
-      <c r="A464" t="str">
-        <v>30/04/2026</v>
-      </c>
-      <c r="B464" t="str">
-        <v>Apr26</v>
-      </c>
-      <c r="C464" t="str">
-        <v>OPEX</v>
-      </c>
-      <c r="D464" t="str">
-        <v>Rental</v>
-      </c>
-      <c r="E464" t="str">
-        <v>ค่าเช่า stock เม.ย. (B1 ครึ่งหนึ่ง)</v>
-      </c>
-      <c r="F464">
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="465">
-      <c r="A465" t="str">
-        <v>05/03/2026</v>
-      </c>
-      <c r="B465" t="str">
-        <v>Mar26</v>
-      </c>
-      <c r="C465" t="str">
-        <v>OPEX</v>
-      </c>
-      <c r="D465" t="str">
-        <v>Salary</v>
-      </c>
-      <c r="E465" t="str">
-        <v>เงินเดือนเมน 3/26</v>
-      </c>
-      <c r="F465">
-        <v>19000</v>
-      </c>
-    </row>
-    <row r="466">
-      <c r="A466" t="str">
-        <v>27/02/2026</v>
-      </c>
-      <c r="B466" t="str">
-        <v>Feb26</v>
-      </c>
-      <c r="C466" t="str">
-        <v>OPEX</v>
-      </c>
-      <c r="D466" t="str">
-        <v>Investment</v>
-      </c>
-      <c r="E466" t="str">
-        <v>อุปกรณ์ (จากสลิปโอนผู้จัดการ)</v>
-      </c>
-      <c r="F466">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="467">
-      <c r="A467" t="str">
-        <v>18/03/2026</v>
-      </c>
-      <c r="B467" t="str">
-        <v>Mar26</v>
-      </c>
-      <c r="C467" t="str">
-        <v>OPEX</v>
-      </c>
-      <c r="D467" t="str">
-        <v>Milk/Conden</v>
-      </c>
-      <c r="E467" t="str">
-        <v>นม + นมข้นหวาน (จากสลิปโอนผู้จัดการ)</v>
-      </c>
-      <c r="F467">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="468">
-      <c r="A468" t="str">
-        <v>01/04/2026</v>
-      </c>
-      <c r="B468" t="str">
-        <v>Apr26</v>
-      </c>
-      <c r="C468" t="str">
-        <v>OPEX</v>
-      </c>
-      <c r="D468" t="str">
-        <v>Salary</v>
-      </c>
-      <c r="E468" t="str">
-        <v>เงินเดือนพนักงาน 3 คน มี.ค. 26</v>
-      </c>
-      <c r="F468">
         <v>24600</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F468"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F461"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/3_Automation_Dashboard/SomSaiJai_Dashboard_B1_2026.xlsx
+++ b/3_Automation_Dashboard/SomSaiJai_Dashboard_B1_2026.xlsx
@@ -10340,7 +10340,7 @@
         <v>01/04/2026</v>
       </c>
       <c r="B461" t="str">
-        <v>Mar26</v>
+        <v>Apr26</v>
       </c>
       <c r="C461" t="str">
         <v>OPEX</v>

--- a/3_Automation_Dashboard/SomSaiJai_Dashboard_B1_2026.xlsx
+++ b/3_Automation_Dashboard/SomSaiJai_Dashboard_B1_2026.xlsx
@@ -1168,7 +1168,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F461"/>
+  <dimension ref="A1:F460"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -10006,38 +10006,38 @@
         <v>OPEX</v>
       </c>
       <c r="D444" t="str">
-        <v>Salary</v>
+        <v>Other</v>
       </c>
       <c r="E444" t="str">
-        <v>ค่าแรงคนงาน Mar26 (ปรับตามงบการเงินเจ้าของ)</v>
+        <v>ค่าน้ำ + ค่าไฟ Mar26 (ปรับตามงบการเงินเจ้าของ)</v>
       </c>
       <c r="F444">
-        <v>27600</v>
+        <v>3229</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>31/03/2026</v>
+        <v>22/06/2026</v>
       </c>
       <c r="B445" t="str">
-        <v>Mar26</v>
+        <v>Jun26</v>
       </c>
       <c r="C445" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D445" t="str">
-        <v>Other</v>
+        <v>Guava</v>
       </c>
       <c r="E445" t="str">
-        <v>ค่าน้ำ + ค่าไฟ Mar26 (ปรับตามงบการเงินเจ้าของ)</v>
+        <v>ฝรั่ง (นาง ประนอม) [bank]</v>
       </c>
       <c r="F445">
-        <v>3229</v>
+        <v>100</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>22/06/2026</v>
+        <v>25/06/2026</v>
       </c>
       <c r="B446" t="str">
         <v>Jun26</v>
@@ -10049,18 +10049,18 @@
         <v>Guava</v>
       </c>
       <c r="E446" t="str">
-        <v>ฝรั่ง (นาง ประนอม) [bank]</v>
+        <v>ฝรั่ง 1 ตะกร้า (นาง ประนอม) [bank]</v>
       </c>
       <c r="F446">
-        <v>100</v>
+        <v>800</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>25/06/2026</v>
+        <v>28/07/2026</v>
       </c>
       <c r="B447" t="str">
-        <v>Jun26</v>
+        <v>Jul26</v>
       </c>
       <c r="C447" t="str">
         <v>COGS</v>
@@ -10069,50 +10069,50 @@
         <v>Guava</v>
       </c>
       <c r="E447" t="str">
-        <v>ฝรั่ง 1 ตะกร้า (นาง ประนอม) [bank]</v>
+        <v>ฝรั่ง (นาง ประนอม) [bank]</v>
       </c>
       <c r="F447">
-        <v>800</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>28/07/2026</v>
+        <v>20/02/2026</v>
       </c>
       <c r="B448" t="str">
-        <v>Jul26</v>
+        <v>Feb26</v>
       </c>
       <c r="C448" t="str">
         <v>COGS</v>
       </c>
       <c r="D448" t="str">
-        <v>Guava</v>
+        <v>Transportation</v>
       </c>
       <c r="E448" t="str">
-        <v>ฝรั่ง (นาง ประนอม) [bank]</v>
+        <v>ค่ารถ (แยกจากใบเสร็จผ้าปิดร้าน 416)</v>
       </c>
       <c r="F448">
-        <v>3000</v>
+        <v>198</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>20/02/2026</v>
+        <v>04/06/2026</v>
       </c>
       <c r="B449" t="str">
-        <v>Feb26</v>
+        <v>Jun26</v>
       </c>
       <c r="C449" t="str">
         <v>COGS</v>
       </c>
       <c r="D449" t="str">
-        <v>Transportation</v>
+        <v>Pineapple</v>
       </c>
       <c r="E449" t="str">
-        <v>ค่ารถ (แยกจากใบเสร็จผ้าปิดร้าน 416)</v>
+        <v>สลิปรวม: สับปะรด 750 (audit fix, was bundled)</v>
       </c>
       <c r="F449">
-        <v>198</v>
+        <v>750</v>
       </c>
     </row>
     <row r="450">
@@ -10126,13 +10126,13 @@
         <v>COGS</v>
       </c>
       <c r="D450" t="str">
-        <v>Pineapple</v>
+        <v>Orange</v>
       </c>
       <c r="E450" t="str">
-        <v>สลิปรวม: สับปะรด 750 (audit fix, was bundled)</v>
+        <v>สลิปรวม: ส้ม 2250 (audit fix, was bundled into Pineapple line)</v>
       </c>
       <c r="F450">
-        <v>750</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="451">
@@ -10143,36 +10143,36 @@
         <v>Jun26</v>
       </c>
       <c r="C451" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D451" t="str">
-        <v>Orange</v>
+        <v>Other</v>
       </c>
       <c r="E451" t="str">
-        <v>สลิปรวม: ส้ม 2250 (audit fix, was bundled into Pineapple line)</v>
+        <v>ค่าปรับตำรวจ 2 คน (police fee, audit fix - was miscategorized as COGS/Pineapple)</v>
       </c>
       <c r="F451">
-        <v>2250</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>04/06/2026</v>
+        <v>26/07/2026</v>
       </c>
       <c r="B452" t="str">
-        <v>Jun26</v>
+        <v>Jul26</v>
       </c>
       <c r="C452" t="str">
-        <v>OPEX</v>
+        <v>CAPEX</v>
       </c>
       <c r="D452" t="str">
-        <v>Other</v>
+        <v>Investment</v>
       </c>
       <c r="E452" t="str">
-        <v>ค่าปรับตำรวจ 2 คน (police fee, audit fix - was miscategorized as COGS/Pineapple)</v>
+        <v>งบลงทุน - ทดลองอื่นๆ (LINE_ALBUM_Cost July_260802_8.jpg, audit fix - was bundled into COGS/Mango)</v>
       </c>
       <c r="F452">
-        <v>2000</v>
+        <v>810</v>
       </c>
     </row>
     <row r="453">
@@ -10183,36 +10183,36 @@
         <v>Jul26</v>
       </c>
       <c r="C453" t="str">
-        <v>CAPEX</v>
+        <v>OPEX</v>
       </c>
       <c r="D453" t="str">
-        <v>Investment</v>
+        <v>Other</v>
       </c>
       <c r="E453" t="str">
-        <v>งบลงทุน - ทดลองอื่นๆ (LINE_ALBUM_Cost July_260802_8.jpg, audit fix - was bundled into COGS/Mango)</v>
+        <v>ค่าส่งของ (LINE_ALBUM_Cost July_260802_11.jpg, audit fix - missing entry)</v>
       </c>
       <c r="F453">
-        <v>810</v>
+        <v>212</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>26/07/2026</v>
+        <v>28/07/2026</v>
       </c>
       <c r="B454" t="str">
         <v>Jul26</v>
       </c>
       <c r="C454" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D454" t="str">
-        <v>Other</v>
+        <v>Pineapple</v>
       </c>
       <c r="E454" t="str">
-        <v>ค่าส่งของ (LINE_ALBUM_Cost July_260802_11.jpg, audit fix - missing entry)</v>
+        <v>สับปะรด 30 ลูก (LINE_ALBUM_Cost July_260802_17.jpg, audit fix - missing entry)</v>
       </c>
       <c r="F454">
-        <v>212</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="455">
@@ -10223,101 +10223,101 @@
         <v>Jul26</v>
       </c>
       <c r="C455" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D455" t="str">
-        <v>Pineapple</v>
+        <v>Other</v>
       </c>
       <c r="E455" t="str">
-        <v>สับปะรด 30 ลูก (LINE_ALBUM_Cost July_260802_17.jpg, audit fix - missing entry)</v>
+        <v>ค่าขนส่ง (LINE_ALBUM_Cost July_260802_19.jpg, audit fix - missing entry)</v>
       </c>
       <c r="F455">
-        <v>1188</v>
+        <v>100</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>28/07/2026</v>
+        <v>30/04/2026</v>
       </c>
       <c r="B456" t="str">
-        <v>Jul26</v>
+        <v>Apr26</v>
       </c>
       <c r="C456" t="str">
         <v>OPEX</v>
       </c>
       <c r="D456" t="str">
-        <v>Other</v>
+        <v>Rental</v>
       </c>
       <c r="E456" t="str">
-        <v>ค่าขนส่ง (LINE_ALBUM_Cost July_260802_19.jpg, audit fix - missing entry)</v>
+        <v>ค่าเช่า stock เม.ย. (B1 ครึ่งหนึ่ง)</v>
       </c>
       <c r="F456">
-        <v>100</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>30/04/2026</v>
+        <v>05/03/2026</v>
       </c>
       <c r="B457" t="str">
-        <v>Apr26</v>
+        <v>Mar26</v>
       </c>
       <c r="C457" t="str">
         <v>OPEX</v>
       </c>
       <c r="D457" t="str">
-        <v>Rental</v>
+        <v>Salary</v>
       </c>
       <c r="E457" t="str">
-        <v>ค่าเช่า stock เม.ย. (B1 ครึ่งหนึ่ง)</v>
+        <v>เงินเดือนเมน 3/26</v>
       </c>
       <c r="F457">
-        <v>6000</v>
+        <v>19000</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>05/03/2026</v>
+        <v>27/02/2026</v>
       </c>
       <c r="B458" t="str">
-        <v>Mar26</v>
+        <v>Feb26</v>
       </c>
       <c r="C458" t="str">
         <v>OPEX</v>
       </c>
       <c r="D458" t="str">
-        <v>Salary</v>
+        <v>Investment</v>
       </c>
       <c r="E458" t="str">
-        <v>เงินเดือนเมน 3/26</v>
+        <v>อุปกรณ์ (จากสลิปโอนผู้จัดการ)</v>
       </c>
       <c r="F458">
-        <v>19000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>27/02/2026</v>
+        <v>18/03/2026</v>
       </c>
       <c r="B459" t="str">
-        <v>Feb26</v>
+        <v>Mar26</v>
       </c>
       <c r="C459" t="str">
         <v>OPEX</v>
       </c>
       <c r="D459" t="str">
-        <v>Investment</v>
+        <v>Milk/Conden</v>
       </c>
       <c r="E459" t="str">
-        <v>อุปกรณ์ (จากสลิปโอนผู้จัดการ)</v>
+        <v>นม + นมข้นหวาน (จากสลิปโอนผู้จัดการ)</v>
       </c>
       <c r="F459">
-        <v>5000</v>
+        <v>230</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>18/03/2026</v>
+        <v>01/04/2026</v>
       </c>
       <c r="B460" t="str">
         <v>Mar26</v>
@@ -10326,38 +10326,18 @@
         <v>OPEX</v>
       </c>
       <c r="D460" t="str">
-        <v>Milk/Conden</v>
+        <v>Salary</v>
       </c>
       <c r="E460" t="str">
-        <v>นม + นมข้นหวาน (จากสลิปโอนผู้จัดการ)</v>
+        <v>เงินเดือนพนักงาน 3 คน มี.ค. 26 (จ่าย 01/04) [bank]</v>
       </c>
       <c r="F460">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="461">
-      <c r="A461" t="str">
-        <v>01/04/2026</v>
-      </c>
-      <c r="B461" t="str">
-        <v>Apr26</v>
-      </c>
-      <c r="C461" t="str">
-        <v>OPEX</v>
-      </c>
-      <c r="D461" t="str">
-        <v>Salary</v>
-      </c>
-      <c r="E461" t="str">
-        <v>เงินเดือนพนักงาน 3 คน มี.ค. 26</v>
-      </c>
-      <c r="F461">
         <v>24600</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F461"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F460"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/3_Automation_Dashboard/SomSaiJai_Dashboard_B1_2026.xlsx
+++ b/3_Automation_Dashboard/SomSaiJai_Dashboard_B1_2026.xlsx
@@ -1168,7 +1168,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F460"/>
+  <dimension ref="A1:F461"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -10335,9 +10335,29 @@
         <v>24600</v>
       </c>
     </row>
+    <row r="461">
+      <c r="A461" t="str">
+        <v>08/06/2026</v>
+      </c>
+      <c r="B461" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C461" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D461" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="E461" t="str">
+        <v>ค่าเช่าคลัง มิ.ย. (B1 ครึ่งหนึ่ง ของ 12,000 จากสลิป 47,000 วันที่ 08/06)</v>
+      </c>
+      <c r="F461">
+        <v>6000</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F460"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F461"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/3_Automation_Dashboard/SomSaiJai_Dashboard_B1_2026.xlsx
+++ b/3_Automation_Dashboard/SomSaiJai_Dashboard_B1_2026.xlsx
@@ -2926,10 +2926,10 @@
         <v>COGS</v>
       </c>
       <c r="D90" t="str">
-        <v>Orange</v>
+        <v>Watermelon</v>
       </c>
       <c r="E90" t="str">
-        <v>แตงโม 51 ยอด3,500</v>
+        <v>แตงโม 51 ยอด3,500 (แก้หมวด: เดิมลง Orange ผิด)</v>
       </c>
       <c r="F90">
         <v>7700</v>

--- a/3_Automation_Dashboard/SomSaiJai_Dashboard_B1_2026.xlsx
+++ b/3_Automation_Dashboard/SomSaiJai_Dashboard_B1_2026.xlsx
@@ -11941,7 +11941,7 @@
         <v>Sun</v>
       </c>
       <c r="C28">
-        <v>12210</v>
+        <v>11210</v>
       </c>
       <c r="D28">
         <v>6160</v>

--- a/3_Automation_Dashboard/SomSaiJai_Dashboard_B1_2026.xlsx
+++ b/3_Automation_Dashboard/SomSaiJai_Dashboard_B1_2026.xlsx
@@ -9169,7 +9169,7 @@
         <v>Rental</v>
       </c>
       <c r="E402" t="str">
-        <v>Rent B1</v>
+        <v>ค่าเช่าร้าน B1 ก.ค. (จ่ายเงินสดจากหน้าร้านก่อนนำเข้าบัญชี - ไม่มีสลิป ยืนยันโดยเจ้าของ 28/08)</v>
       </c>
       <c r="F402">
         <v>35000</v>

--- a/3_Automation_Dashboard/SomSaiJai_Dashboard_B1_2026.xlsx
+++ b/3_Automation_Dashboard/SomSaiJai_Dashboard_B1_2026.xlsx
@@ -1168,7 +1168,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F461"/>
+  <dimension ref="A1:F463"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2649,7 +2649,7 @@
         <v>Orange</v>
       </c>
       <c r="E76" t="str">
-        <v>ส้ม 30 18/2/69</v>
+        <v>ส้ม 30 ตะกร้า (660 กก.) 18/2/69</v>
       </c>
       <c r="F76">
         <v>10680</v>
@@ -2909,7 +2909,7 @@
         <v>Orange</v>
       </c>
       <c r="E89" t="str">
-        <v>ค่าส้มวันที่ 27269</v>
+        <v>ค่าส้ม 20 ตะกร้า (440 กก.) วันที่ 27/2/69</v>
       </c>
       <c r="F89">
         <v>7312</v>
@@ -2929,10 +2929,10 @@
         <v>Watermelon</v>
       </c>
       <c r="E90" t="str">
-        <v>แตงโม 51 ยอด3,500 (แก้หมวด: เดิมลง Orange ผิด)</v>
+        <v>แตงโม 51 ลูก ยอด 3,500 (แยกจากสลิปรวม 7,700 - นาง ศิริพร)</v>
       </c>
       <c r="F90">
-        <v>7700</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="91">
@@ -2949,10 +2949,10 @@
         <v>Orange</v>
       </c>
       <c r="E91" t="str">
-        <v>ค่าส้ม 20 ตะกร้า</v>
+        <v>ส้ม 150 กก. ยอด 4,200 (แยกจากสลิปรวม 7,700 - นาง ศิริพร)</v>
       </c>
       <c r="F91">
-        <v>7312</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="92">
@@ -2966,13 +2966,13 @@
         <v>COGS</v>
       </c>
       <c r="D92" t="str">
-        <v>Transportation</v>
+        <v>Orange</v>
       </c>
       <c r="E92" t="str">
-        <v>ค่าทางด่วน</v>
+        <v>ค่าส้ม 20 ตะกร้า</v>
       </c>
       <c r="F92">
-        <v>105</v>
+        <v>7312</v>
       </c>
     </row>
     <row r="93">
@@ -2986,13 +2986,13 @@
         <v>COGS</v>
       </c>
       <c r="D93" t="str">
-        <v>Packaging</v>
+        <v>Transportation</v>
       </c>
       <c r="E93" t="str">
-        <v>ถุงขยะ</v>
+        <v>ค่าทางด่วน</v>
       </c>
       <c r="F93">
-        <v>909</v>
+        <v>105</v>
       </c>
     </row>
     <row r="94">
@@ -3006,18 +3006,18 @@
         <v>COGS</v>
       </c>
       <c r="D94" t="str">
-        <v>Mango</v>
+        <v>Packaging</v>
       </c>
       <c r="E94" t="str">
-        <v>มะม่วง 24 โล</v>
+        <v>ถุงขยะ</v>
       </c>
       <c r="F94">
-        <v>1560</v>
+        <v>909</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>07/03/2026</v>
+        <v>05/03/2026</v>
       </c>
       <c r="B95" t="str">
         <v>Mar26</v>
@@ -3026,18 +3026,18 @@
         <v>COGS</v>
       </c>
       <c r="D95" t="str">
-        <v>Transportation</v>
+        <v>Mango</v>
       </c>
       <c r="E95" t="str">
-        <v>Unknown</v>
+        <v>มะม่วง 24 โล</v>
       </c>
       <c r="F95">
-        <v>2000</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>10/03/2026</v>
+        <v>07/03/2026</v>
       </c>
       <c r="B96" t="str">
         <v>Mar26</v>
@@ -3046,13 +3046,13 @@
         <v>COGS</v>
       </c>
       <c r="D96" t="str">
-        <v>Orange</v>
+        <v>Transportation</v>
       </c>
       <c r="E96" t="str">
-        <v>09/03/69</v>
+        <v>Unknown</v>
       </c>
       <c r="F96">
-        <v>9804</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="97">
@@ -3066,13 +3066,13 @@
         <v>COGS</v>
       </c>
       <c r="D97" t="str">
-        <v>Watermelon</v>
+        <v>Orange</v>
       </c>
       <c r="E97" t="str">
-        <v>แตงโม 50 วันที่ 7 แตงโม 50 วันที่ 10</v>
+        <v>ส้ม 660 กก. x14 = 9,240 + ค่าส่ง 1,140 - ลบยอดเกิน 576 (09/03/69)</v>
       </c>
       <c r="F97">
-        <v>8000</v>
+        <v>9804</v>
       </c>
     </row>
     <row r="98">
@@ -3083,16 +3083,16 @@
         <v>Mar26</v>
       </c>
       <c r="C98" t="str">
-        <v>CAPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D98" t="str">
-        <v>Investment</v>
+        <v>Watermelon</v>
       </c>
       <c r="E98" t="str">
-        <v>Unknown</v>
+        <v>แตงโม 50 วันที่ 7 แตงโม 50 วันที่ 10</v>
       </c>
       <c r="F98">
-        <v>6500</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="99">
@@ -3103,16 +3103,16 @@
         <v>Mar26</v>
       </c>
       <c r="C99" t="str">
-        <v>COGS</v>
+        <v>CAPEX</v>
       </c>
       <c r="D99" t="str">
-        <v>Packaging</v>
+        <v>Investment</v>
       </c>
       <c r="E99" t="str">
-        <v>แก้ว2ลัง ลังละ 1560</v>
+        <v>Unknown</v>
       </c>
       <c r="F99">
-        <v>3120</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="100">
@@ -3126,18 +3126,18 @@
         <v>COGS</v>
       </c>
       <c r="D100" t="str">
-        <v>Orange</v>
+        <v>Packaging</v>
       </c>
       <c r="E100" t="str">
-        <v>แก้วร้านน้ำส้ม 2ลัง ลังละ1560</v>
+        <v>แก้ว2ลัง ลังละ 1560</v>
       </c>
       <c r="F100">
-        <v>5667</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>13/03/2026</v>
+        <v>10/03/2026</v>
       </c>
       <c r="B101" t="str">
         <v>Mar26</v>
@@ -3146,18 +3146,18 @@
         <v>COGS</v>
       </c>
       <c r="D101" t="str">
-        <v>Packaging</v>
+        <v>Orange</v>
       </c>
       <c r="E101" t="str">
-        <v>หลอด 20 แพค</v>
+        <v>แก้วร้านน้ำส้ม 2ลัง ลังละ1560</v>
       </c>
       <c r="F101">
-        <v>765</v>
+        <v>5667</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>14/03/2026</v>
+        <v>13/03/2026</v>
       </c>
       <c r="B102" t="str">
         <v>Mar26</v>
@@ -3166,13 +3166,13 @@
         <v>COGS</v>
       </c>
       <c r="D102" t="str">
-        <v>Apple</v>
+        <v>Packaging</v>
       </c>
       <c r="E102" t="str">
-        <v>แอปเปิ้ลฟูจิ 32</v>
+        <v>หลอด 20 แพค</v>
       </c>
       <c r="F102">
-        <v>350</v>
+        <v>765</v>
       </c>
     </row>
     <row r="103">
@@ -3186,18 +3186,18 @@
         <v>COGS</v>
       </c>
       <c r="D103" t="str">
-        <v>Mango</v>
+        <v>Apple</v>
       </c>
       <c r="E103" t="str">
-        <v>มะม่วง 2 ลัง 44</v>
+        <v>แอปเปิ้ลฟูจิ 32</v>
       </c>
       <c r="F103">
-        <v>2420</v>
+        <v>350</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>15/03/2026</v>
+        <v>14/03/2026</v>
       </c>
       <c r="B104" t="str">
         <v>Mar26</v>
@@ -3206,13 +3206,13 @@
         <v>COGS</v>
       </c>
       <c r="D104" t="str">
-        <v>Transportation</v>
+        <v>Mango</v>
       </c>
       <c r="E104" t="str">
-        <v>ค่าทางด่วน</v>
+        <v>มะม่วง 2 ลัง 44</v>
       </c>
       <c r="F104">
-        <v>115</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="105">
@@ -3226,93 +3226,93 @@
         <v>COGS</v>
       </c>
       <c r="D105" t="str">
-        <v>Watermelon</v>
+        <v>Transportation</v>
       </c>
       <c r="E105" t="str">
-        <v>น้ำมะพร้าว 5ขวดเละ 50฿</v>
+        <v>ค่าทางด่วน</v>
       </c>
       <c r="F105">
-        <v>4800</v>
+        <v>115</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>17/03/2026</v>
+        <v>15/03/2026</v>
       </c>
       <c r="B106" t="str">
         <v>Mar26</v>
       </c>
       <c r="C106" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D106" t="str">
-        <v>Utilities</v>
+        <v>Watermelon</v>
       </c>
       <c r="E106" t="str">
-        <v>ค่าไฟเดือนกพ มีนา</v>
+        <v>น้ำมะพร้าว 5ขวดเละ 50฿</v>
       </c>
       <c r="F106">
-        <v>2779.47</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>19/03/2026</v>
+        <v>17/03/2026</v>
       </c>
       <c r="B107" t="str">
         <v>Mar26</v>
       </c>
       <c r="C107" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D107" t="str">
-        <v>Watermelon</v>
+        <v>Utilities</v>
       </c>
       <c r="E107" t="str">
-        <v>ค่าแตงโม 18/3/67 51 ลูก 4000 บาท</v>
+        <v>ค่าไฟเดือนกพ มีนา</v>
       </c>
       <c r="F107">
-        <v>4000</v>
+        <v>2779.47</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>21/03/2026</v>
+        <v>19/03/2026</v>
       </c>
       <c r="B108" t="str">
         <v>Mar26</v>
       </c>
       <c r="C108" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D108" t="str">
-        <v>Other</v>
+        <v>Watermelon</v>
       </c>
       <c r="E108" t="str">
-        <v>สกรู กาวตะปู</v>
+        <v>ค่าแตงโม 18/3/67 51 ลูก 4000 บาท</v>
       </c>
       <c r="F108">
-        <v>117</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>23/03/2026</v>
+        <v>21/03/2026</v>
       </c>
       <c r="B109" t="str">
         <v>Mar26</v>
       </c>
       <c r="C109" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D109" t="str">
-        <v>Mango</v>
+        <v>Other</v>
       </c>
       <c r="E109" t="str">
-        <v>มะม่วง 44 โล</v>
+        <v>สกรู กาวตะปู</v>
       </c>
       <c r="F109">
-        <v>2200</v>
+        <v>117</v>
       </c>
     </row>
     <row r="110">
@@ -3326,38 +3326,38 @@
         <v>COGS</v>
       </c>
       <c r="D110" t="str">
-        <v>Orange</v>
+        <v>Mango</v>
       </c>
       <c r="E110" t="str">
-        <v>22-3-2569</v>
+        <v>มะม่วง 44 โล</v>
       </c>
       <c r="F110">
-        <v>5890</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>24/03/2026</v>
+        <v>23/03/2026</v>
       </c>
       <c r="B111" t="str">
         <v>Mar26</v>
       </c>
       <c r="C111" t="str">
-        <v>CAPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D111" t="str">
-        <v>Investment</v>
+        <v>Watermelon</v>
       </c>
       <c r="E111" t="str">
-        <v>รถเข็นของคันใหม่</v>
+        <v>แตงโม 43 ลูก x80 = 3,440 (แยกจากสลิปรวม 5,890 - นาง ศิริพร 22/3)</v>
       </c>
       <c r="F111">
-        <v>1752</v>
+        <v>3440</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>28/03/2026</v>
+        <v>23/03/2026</v>
       </c>
       <c r="B112" t="str">
         <v>Mar26</v>
@@ -3366,33 +3366,33 @@
         <v>COGS</v>
       </c>
       <c r="D112" t="str">
-        <v>Coconut Water</v>
+        <v>Orange</v>
       </c>
       <c r="E112" t="str">
-        <v>น้ำมะพร้าว 10 ขวด</v>
+        <v>ส้ม 70 กก. x35 = 2,450 (แยกจากสลิปรวม 5,890 - นาง ศิริพร 22/3)</v>
       </c>
       <c r="F112">
-        <v>500</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>28/03/2026</v>
+        <v>24/03/2026</v>
       </c>
       <c r="B113" t="str">
         <v>Mar26</v>
       </c>
       <c r="C113" t="str">
-        <v>COGS</v>
+        <v>CAPEX</v>
       </c>
       <c r="D113" t="str">
-        <v>Mango</v>
+        <v>Investment</v>
       </c>
       <c r="E113" t="str">
-        <v>มะม่วง 23 โล</v>
+        <v>รถเข็นของคันใหม่</v>
       </c>
       <c r="F113">
-        <v>1035</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="114">
@@ -3406,18 +3406,18 @@
         <v>COGS</v>
       </c>
       <c r="D114" t="str">
-        <v>Watermelon</v>
+        <v>Coconut Water</v>
       </c>
       <c r="E114" t="str">
-        <v>แตงโม 50 26/3/69</v>
+        <v>น้ำมะพร้าว 10 ขวด</v>
       </c>
       <c r="F114">
-        <v>4000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>30/03/2026</v>
+        <v>28/03/2026</v>
       </c>
       <c r="B115" t="str">
         <v>Mar26</v>
@@ -3426,18 +3426,18 @@
         <v>COGS</v>
       </c>
       <c r="D115" t="str">
-        <v>Packaging</v>
+        <v>Mango</v>
       </c>
       <c r="E115" t="str">
-        <v>นมข้นจืดสามลังหนึ่งลังมี 12 กล่อง 36 กล่อง</v>
+        <v>มะม่วง 23 โล</v>
       </c>
       <c r="F115">
-        <v>1720</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>30/03/2026</v>
+        <v>28/03/2026</v>
       </c>
       <c r="B116" t="str">
         <v>Mar26</v>
@@ -3446,13 +3446,13 @@
         <v>COGS</v>
       </c>
       <c r="D116" t="str">
-        <v>Packaging</v>
+        <v>Watermelon</v>
       </c>
       <c r="E116" t="str">
-        <v>นมข้นหวาน 3 ลัง 24 ถุง</v>
+        <v>แตงโม 50 26/3/69</v>
       </c>
       <c r="F116">
-        <v>2016</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="117">
@@ -3466,13 +3466,13 @@
         <v>COGS</v>
       </c>
       <c r="D117" t="str">
-        <v>Watermelon</v>
+        <v>Packaging</v>
       </c>
       <c r="E117" t="str">
-        <v>แตงโม 30 ลูก 2400 เนื้อมะพร้าว 10 โล 1100</v>
+        <v>นมข้นจืดสามลังหนึ่งลังมี 12 กล่อง 36 กล่อง</v>
       </c>
       <c r="F117">
-        <v>3500</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="118">
@@ -3486,18 +3486,18 @@
         <v>COGS</v>
       </c>
       <c r="D118" t="str">
-        <v>Transportation</v>
+        <v>Packaging</v>
       </c>
       <c r="E118" t="str">
-        <v>ค่าส่ง lalamove</v>
+        <v>นมข้นหวาน 3 ลัง 24 ถุง</v>
       </c>
       <c r="F118">
-        <v>2000</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>31/03/2026</v>
+        <v>30/03/2026</v>
       </c>
       <c r="B119" t="str">
         <v>Mar26</v>
@@ -3506,53 +3506,53 @@
         <v>COGS</v>
       </c>
       <c r="D119" t="str">
-        <v>Transportation</v>
+        <v>Watermelon</v>
       </c>
       <c r="E119" t="str">
-        <v>Unknown</v>
+        <v>แตงโม 30 ลูก 2400 เนื้อมะพร้าว 10 โล 1100</v>
       </c>
       <c r="F119">
-        <v>2000</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>01/04/2026</v>
+        <v>30/03/2026</v>
       </c>
       <c r="B120" t="str">
-        <v>Apr26</v>
+        <v>Mar26</v>
       </c>
       <c r="C120" t="str">
         <v>COGS</v>
       </c>
       <c r="D120" t="str">
-        <v>Apple</v>
+        <v>Transportation</v>
       </c>
       <c r="E120" t="str">
-        <v>แอปเปิ้ล 3 ลัง</v>
+        <v>ค่าส่ง lalamove</v>
       </c>
       <c r="F120">
-        <v>1050</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>01/04/2026</v>
+        <v>31/03/2026</v>
       </c>
       <c r="B121" t="str">
-        <v>Apr26</v>
+        <v>Mar26</v>
       </c>
       <c r="C121" t="str">
         <v>COGS</v>
       </c>
       <c r="D121" t="str">
-        <v>Mango</v>
+        <v>Transportation</v>
       </c>
       <c r="E121" t="str">
-        <v>มะม่วง 2 ลัง</v>
+        <v>Unknown</v>
       </c>
       <c r="F121">
-        <v>1920</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="122">
@@ -3566,38 +3566,38 @@
         <v>COGS</v>
       </c>
       <c r="D122" t="str">
-        <v>Water</v>
+        <v>Apple</v>
       </c>
       <c r="E122" t="str">
-        <v>น้ำ500</v>
+        <v>แอปเปิ้ล 3 ลัง</v>
       </c>
       <c r="F122">
-        <v>1700</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>02/04/2026</v>
+        <v>01/04/2026</v>
       </c>
       <c r="B123" t="str">
-        <v>Mar26</v>
+        <v>Apr26</v>
       </c>
       <c r="C123" t="str">
         <v>COGS</v>
       </c>
       <c r="D123" t="str">
-        <v>Orange</v>
+        <v>Mango</v>
       </c>
       <c r="E123" t="str">
-        <v>ส้มเพิ่มเติม มี.ค. (ตามรายงานต้นทุน Mar26: 23,202 + 49,560 = 72,762)</v>
+        <v>มะม่วง 2 ลัง</v>
       </c>
       <c r="F123">
-        <v>49560</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>04/04/2026</v>
+        <v>01/04/2026</v>
       </c>
       <c r="B124" t="str">
         <v>Apr26</v>
@@ -3606,33 +3606,33 @@
         <v>COGS</v>
       </c>
       <c r="D124" t="str">
-        <v>Packaging</v>
+        <v>Water</v>
       </c>
       <c r="E124" t="str">
-        <v>แก้ว3ลัง 1539 3 4617</v>
+        <v>น้ำ500</v>
       </c>
       <c r="F124">
-        <v>7066</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>04/04/2026</v>
+        <v>02/04/2026</v>
       </c>
       <c r="B125" t="str">
-        <v>Apr26</v>
+        <v>Mar26</v>
       </c>
       <c r="C125" t="str">
         <v>COGS</v>
       </c>
       <c r="D125" t="str">
-        <v>Packaging</v>
+        <v>Orange</v>
       </c>
       <c r="E125" t="str">
-        <v>แก้ว1ลัง 1539</v>
+        <v>ส้มเพิ่มเติม มี.ค. (สลิปไม่มีบันทึกช่วยจำ - ไม่ทราบจำนวน) [bank 02/04]</v>
       </c>
       <c r="F125">
-        <v>1560</v>
+        <v>49560</v>
       </c>
     </row>
     <row r="126">
@@ -3646,13 +3646,13 @@
         <v>COGS</v>
       </c>
       <c r="D126" t="str">
-        <v>Coconut</v>
+        <v>Packaging</v>
       </c>
       <c r="E126" t="str">
-        <v>ค่ามะพร้าว 26 60ลูก 1560</v>
+        <v>แก้ว3ลัง 1539 3 4617</v>
       </c>
       <c r="F126">
-        <v>1980</v>
+        <v>7066</v>
       </c>
     </row>
     <row r="127">
@@ -3666,13 +3666,13 @@
         <v>COGS</v>
       </c>
       <c r="D127" t="str">
-        <v>Coconut</v>
+        <v>Packaging</v>
       </c>
       <c r="E127" t="str">
-        <v>เนื้อ 1200 น้ำ 500</v>
+        <v>แก้ว1ลัง 1539</v>
       </c>
       <c r="F127">
-        <v>1700</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="128">
@@ -3686,13 +3686,13 @@
         <v>COGS</v>
       </c>
       <c r="D128" t="str">
-        <v>Mango</v>
+        <v>Coconut</v>
       </c>
       <c r="E128" t="str">
-        <v>มะม่วง1ลัง</v>
+        <v>ค่ามะพร้าว 26 60ลูก 1560</v>
       </c>
       <c r="F128">
-        <v>1000</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="129">
@@ -3706,13 +3706,13 @@
         <v>COGS</v>
       </c>
       <c r="D129" t="str">
-        <v>Orange</v>
+        <v>Coconut</v>
       </c>
       <c r="E129" t="str">
-        <v>ส้ม 4/4/69 20 ตะกร้า 30 บาท 13200 ค่าขนส่ง</v>
+        <v>เนื้อ 1200 น้ำ 500</v>
       </c>
       <c r="F129">
-        <v>14160</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="130">
@@ -3726,13 +3726,13 @@
         <v>COGS</v>
       </c>
       <c r="D130" t="str">
-        <v>Watermelon</v>
+        <v>Mango</v>
       </c>
       <c r="E130" t="str">
-        <v>4/4/68 40 ลูก</v>
+        <v>มะม่วง1ลัง</v>
       </c>
       <c r="F130">
-        <v>3200</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="131">
@@ -3746,18 +3746,18 @@
         <v>COGS</v>
       </c>
       <c r="D131" t="str">
-        <v>Watermelon</v>
+        <v>Orange</v>
       </c>
       <c r="E131" t="str">
-        <v>แตงโม 1/4/69 30 ลูก</v>
+        <v>ส้ม 4/4/69 20 ตะกร้า 30 บาท 13200 ค่าขนส่ง</v>
       </c>
       <c r="F131">
-        <v>2400</v>
+        <v>14160</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>07/04/2026</v>
+        <v>04/04/2026</v>
       </c>
       <c r="B132" t="str">
         <v>Apr26</v>
@@ -3766,18 +3766,18 @@
         <v>COGS</v>
       </c>
       <c r="D132" t="str">
-        <v>Apple</v>
+        <v>Watermelon</v>
       </c>
       <c r="E132" t="str">
-        <v>แอปเปิ้ล 3 ลัง</v>
+        <v>4/4/68 40 ลูก</v>
       </c>
       <c r="F132">
-        <v>1050</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>07/04/2026</v>
+        <v>04/04/2026</v>
       </c>
       <c r="B133" t="str">
         <v>Apr26</v>
@@ -3786,13 +3786,13 @@
         <v>COGS</v>
       </c>
       <c r="D133" t="str">
-        <v>Coconut Water</v>
+        <v>Watermelon</v>
       </c>
       <c r="E133" t="str">
-        <v>เนื้อมะพร้าว 10 - 1200 บาท น้ำมะพร้าว 10</v>
+        <v>แตงโม 1/4/69 30 ลูก</v>
       </c>
       <c r="F133">
-        <v>1700</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="134">
@@ -3806,18 +3806,18 @@
         <v>COGS</v>
       </c>
       <c r="D134" t="str">
-        <v>Watermelon</v>
+        <v>Apple</v>
       </c>
       <c r="E134" t="str">
-        <v>ค่าแตงโมวันที่ 4- 40 ลูก 3200 บาท วันที่ 7-40 ลูก</v>
+        <v>แอปเปิ้ล 3 ลัง</v>
       </c>
       <c r="F134">
-        <v>6400</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>10/04/2026</v>
+        <v>07/04/2026</v>
       </c>
       <c r="B135" t="str">
         <v>Apr26</v>
@@ -3826,18 +3826,18 @@
         <v>COGS</v>
       </c>
       <c r="D135" t="str">
-        <v>Milk/Conden</v>
+        <v>Coconut Water</v>
       </c>
       <c r="E135" t="str">
-        <v>ค่านม</v>
+        <v>เนื้อมะพร้าว 10 - 1200 บาท น้ำมะพร้าว 10</v>
       </c>
       <c r="F135">
-        <v>180</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>11/04/2026</v>
+        <v>07/04/2026</v>
       </c>
       <c r="B136" t="str">
         <v>Apr26</v>
@@ -3846,18 +3846,18 @@
         <v>COGS</v>
       </c>
       <c r="D136" t="str">
-        <v>Transportation</v>
+        <v>Watermelon</v>
       </c>
       <c r="E136" t="str">
-        <v>ค่ารถ lalamove</v>
+        <v>ค่าแตงโมวันที่ 4- 40 ลูก 3200 บาท วันที่ 7-40 ลูก</v>
       </c>
       <c r="F136">
-        <v>2000</v>
+        <v>6400</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>11/04/2026</v>
+        <v>10/04/2026</v>
       </c>
       <c r="B137" t="str">
         <v>Apr26</v>
@@ -3866,13 +3866,13 @@
         <v>COGS</v>
       </c>
       <c r="D137" t="str">
-        <v>Apple</v>
+        <v>Milk/Conden</v>
       </c>
       <c r="E137" t="str">
-        <v>แอปเปิ้ล 3 ลัง</v>
+        <v>ค่านม</v>
       </c>
       <c r="F137">
-        <v>1050</v>
+        <v>180</v>
       </c>
     </row>
     <row r="138">
@@ -3886,13 +3886,13 @@
         <v>COGS</v>
       </c>
       <c r="D138" t="str">
-        <v>Coconut</v>
+        <v>Transportation</v>
       </c>
       <c r="E138" t="str">
-        <v>น้ำ 500 เนื้อ 1200</v>
+        <v>ค่ารถ lalamove</v>
       </c>
       <c r="F138">
-        <v>1700</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="139">
@@ -3906,18 +3906,18 @@
         <v>COGS</v>
       </c>
       <c r="D139" t="str">
-        <v>Mango</v>
+        <v>Apple</v>
       </c>
       <c r="E139" t="str">
-        <v>มะม่วง 1 ลัง 23 โล</v>
+        <v>แอปเปิ้ล 3 ลัง</v>
       </c>
       <c r="F139">
-        <v>690</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>13/04/2026</v>
+        <v>11/04/2026</v>
       </c>
       <c r="B140" t="str">
         <v>Apr26</v>
@@ -3926,18 +3926,18 @@
         <v>COGS</v>
       </c>
       <c r="D140" t="str">
-        <v>Coconut Water</v>
+        <v>Coconut</v>
       </c>
       <c r="E140" t="str">
-        <v>Unknown</v>
+        <v>น้ำ 500 เนื้อ 1200</v>
       </c>
       <c r="F140">
-        <v>300</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>13/04/2026</v>
+        <v>11/04/2026</v>
       </c>
       <c r="B141" t="str">
         <v>Apr26</v>
@@ -3946,13 +3946,13 @@
         <v>COGS</v>
       </c>
       <c r="D141" t="str">
-        <v>Coconut Water</v>
+        <v>Mango</v>
       </c>
       <c r="E141" t="str">
-        <v>เนื้อมะพร้าว 1200 น้ำมะพร้าว 500</v>
+        <v>มะม่วง 1 ลัง 23 โล</v>
       </c>
       <c r="F141">
-        <v>1400</v>
+        <v>690</v>
       </c>
     </row>
     <row r="142">
@@ -3966,13 +3966,13 @@
         <v>COGS</v>
       </c>
       <c r="D142" t="str">
-        <v>Mango</v>
+        <v>Coconut Water</v>
       </c>
       <c r="E142" t="str">
         <v>Unknown</v>
       </c>
       <c r="F142">
-        <v>750</v>
+        <v>300</v>
       </c>
     </row>
     <row r="143">
@@ -3986,18 +3986,18 @@
         <v>COGS</v>
       </c>
       <c r="D143" t="str">
-        <v>Watermelon</v>
+        <v>Coconut Water</v>
       </c>
       <c r="E143" t="str">
-        <v>Unknown</v>
+        <v>เนื้อมะพร้าว 1200 น้ำมะพร้าว 500</v>
       </c>
       <c r="F143">
-        <v>3200</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>18/04/2026</v>
+        <v>13/04/2026</v>
       </c>
       <c r="B144" t="str">
         <v>Apr26</v>
@@ -4006,18 +4006,18 @@
         <v>COGS</v>
       </c>
       <c r="D144" t="str">
-        <v>Apple</v>
+        <v>Mango</v>
       </c>
       <c r="E144" t="str">
-        <v>แอปเปิ้ล 3 ลัง</v>
+        <v>Unknown</v>
       </c>
       <c r="F144">
-        <v>1050</v>
+        <v>750</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>18/04/2026</v>
+        <v>13/04/2026</v>
       </c>
       <c r="B145" t="str">
         <v>Apr26</v>
@@ -4026,13 +4026,13 @@
         <v>COGS</v>
       </c>
       <c r="D145" t="str">
-        <v>Mango</v>
+        <v>Watermelon</v>
       </c>
       <c r="E145" t="str">
-        <v>16/04/26 มะม่วง 1 ลัง</v>
+        <v>Unknown</v>
       </c>
       <c r="F145">
-        <v>750</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="146">
@@ -4043,21 +4043,21 @@
         <v>Apr26</v>
       </c>
       <c r="C146" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D146" t="str">
-        <v>Other</v>
+        <v>Apple</v>
       </c>
       <c r="E146" t="str">
-        <v>16/4/2569</v>
+        <v>แอปเปิ้ล 3 ลัง</v>
       </c>
       <c r="F146">
-        <v>4000</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>20/04/2026</v>
+        <v>18/04/2026</v>
       </c>
       <c r="B147" t="str">
         <v>Apr26</v>
@@ -4066,33 +4066,33 @@
         <v>COGS</v>
       </c>
       <c r="D147" t="str">
-        <v>Orange</v>
+        <v>Mango</v>
       </c>
       <c r="E147" t="str">
-        <v>ส้ม 40 ตะกร้า ตะกร้าละ 22 โล โลละ 30 บาท</v>
+        <v>16/04/26 มะม่วง 1 ลัง</v>
       </c>
       <c r="F147">
-        <v>28600</v>
+        <v>750</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>20/04/2026</v>
+        <v>18/04/2026</v>
       </c>
       <c r="B148" t="str">
         <v>Apr26</v>
       </c>
       <c r="C148" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D148" t="str">
-        <v>Transportation</v>
+        <v>Other</v>
       </c>
       <c r="E148" t="str">
-        <v>ค่าส่งป้ายเมนูร้านใหม่</v>
+        <v>16/4/2569</v>
       </c>
       <c r="F148">
-        <v>335</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="149">
@@ -4106,13 +4106,13 @@
         <v>COGS</v>
       </c>
       <c r="D149" t="str">
-        <v>Packaging</v>
+        <v>Orange</v>
       </c>
       <c r="E149" t="str">
-        <v>ขวดใหญ่ 98 อัน</v>
+        <v>ส้ม 40 ตะกร้า ตะกร้าละ 22 โล โลละ 30 บาท</v>
       </c>
       <c r="F149">
-        <v>338</v>
+        <v>28600</v>
       </c>
     </row>
     <row r="150">
@@ -4126,13 +4126,13 @@
         <v>COGS</v>
       </c>
       <c r="D150" t="str">
-        <v>Packaging</v>
+        <v>Transportation</v>
       </c>
       <c r="E150" t="str">
-        <v>ถุงขยะ 10 แพค</v>
+        <v>ค่าส่งป้ายเมนูร้านใหม่</v>
       </c>
       <c r="F150">
-        <v>520</v>
+        <v>335</v>
       </c>
     </row>
     <row r="151">
@@ -4146,13 +4146,13 @@
         <v>COGS</v>
       </c>
       <c r="D151" t="str">
-        <v>Watermelon</v>
+        <v>Packaging</v>
       </c>
       <c r="E151" t="str">
-        <v>18/4/26 แตงโม 30 ลูก</v>
+        <v>ขวดใหญ่ 98 อัน</v>
       </c>
       <c r="F151">
-        <v>2400</v>
+        <v>338</v>
       </c>
     </row>
     <row r="152">
@@ -4166,18 +4166,18 @@
         <v>COGS</v>
       </c>
       <c r="D152" t="str">
-        <v>Mango</v>
+        <v>Packaging</v>
       </c>
       <c r="E152" t="str">
-        <v>18/4/26 มะม่วง 25 โล 750</v>
+        <v>ถุงขยะ 10 แพค</v>
       </c>
       <c r="F152">
-        <v>750</v>
+        <v>520</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>21/04/2026</v>
+        <v>20/04/2026</v>
       </c>
       <c r="B153" t="str">
         <v>Apr26</v>
@@ -4189,15 +4189,15 @@
         <v>Watermelon</v>
       </c>
       <c r="E153" t="str">
-        <v>21/4/26 แตงโม60 ลูก</v>
+        <v>18/4/26 แตงโม 30 ลูก</v>
       </c>
       <c r="F153">
-        <v>4800</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>21/04/2026</v>
+        <v>20/04/2026</v>
       </c>
       <c r="B154" t="str">
         <v>Apr26</v>
@@ -4206,13 +4206,13 @@
         <v>COGS</v>
       </c>
       <c r="D154" t="str">
-        <v>Transportation</v>
+        <v>Mango</v>
       </c>
       <c r="E154" t="str">
-        <v>Lalamove</v>
+        <v>18/4/26 มะม่วง 25 โล 750</v>
       </c>
       <c r="F154">
-        <v>2000</v>
+        <v>750</v>
       </c>
     </row>
     <row r="155">
@@ -4226,18 +4226,18 @@
         <v>COGS</v>
       </c>
       <c r="D155" t="str">
-        <v>Apple</v>
+        <v>Watermelon</v>
       </c>
       <c r="E155" t="str">
-        <v>แอปเปิ้ล 4 ลัง</v>
+        <v>21/4/26 แตงโม60 ลูก</v>
       </c>
       <c r="F155">
-        <v>1400</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>23/04/2026</v>
+        <v>21/04/2026</v>
       </c>
       <c r="B156" t="str">
         <v>Apr26</v>
@@ -4246,18 +4246,18 @@
         <v>COGS</v>
       </c>
       <c r="D156" t="str">
-        <v>Mango</v>
+        <v>Transportation</v>
       </c>
       <c r="E156" t="str">
-        <v>มะม่วง 2 ลัง</v>
+        <v>Lalamove</v>
       </c>
       <c r="F156">
-        <v>1560</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>23/04/2026</v>
+        <v>21/04/2026</v>
       </c>
       <c r="B157" t="str">
         <v>Apr26</v>
@@ -4286,13 +4286,13 @@
         <v>COGS</v>
       </c>
       <c r="D158" t="str">
-        <v>Coconut</v>
+        <v>Mango</v>
       </c>
       <c r="E158" t="str">
-        <v>16/4/26 เนื้อ 10 น้ำ 10 21/4/26 เนื้อ 10</v>
+        <v>มะม่วง 2 ลัง</v>
       </c>
       <c r="F158">
-        <v>2900</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="159">
@@ -4306,18 +4306,18 @@
         <v>COGS</v>
       </c>
       <c r="D159" t="str">
-        <v>Mango</v>
+        <v>Apple</v>
       </c>
       <c r="E159" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>แอปเปิ้ล 4 ลัง</v>
       </c>
       <c r="F159">
-        <v>780</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>24/04/2026</v>
+        <v>23/04/2026</v>
       </c>
       <c r="B160" t="str">
         <v>Apr26</v>
@@ -4326,18 +4326,18 @@
         <v>COGS</v>
       </c>
       <c r="D160" t="str">
-        <v>Packaging</v>
+        <v>Coconut</v>
       </c>
       <c r="E160" t="str">
-        <v>บาร์เลย 4 ถั่วแดง 3 ถุงละ 60</v>
+        <v>16/4/26 เนื้อ 10 น้ำ 10 21/4/26 เนื้อ 10</v>
       </c>
       <c r="F160">
-        <v>420</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>24/04/2026</v>
+        <v>23/04/2026</v>
       </c>
       <c r="B161" t="str">
         <v>Apr26</v>
@@ -4346,18 +4346,18 @@
         <v>COGS</v>
       </c>
       <c r="D161" t="str">
-        <v>Watermelon</v>
+        <v>Mango</v>
       </c>
       <c r="E161" t="str">
-        <v>แตงโม 50 ลูก</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F161">
-        <v>4000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>25/04/2026</v>
+        <v>24/04/2026</v>
       </c>
       <c r="B162" t="str">
         <v>Apr26</v>
@@ -4366,18 +4366,18 @@
         <v>COGS</v>
       </c>
       <c r="D162" t="str">
-        <v>Orange</v>
+        <v>Packaging</v>
       </c>
       <c r="E162" t="str">
-        <v>22/04/69</v>
+        <v>บาร์เลย 4 ถั่วแดง 3 ถุงละ 60</v>
       </c>
       <c r="F162">
-        <v>14400</v>
+        <v>420</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>26/04/2026</v>
+        <v>24/04/2026</v>
       </c>
       <c r="B163" t="str">
         <v>Apr26</v>
@@ -4386,18 +4386,18 @@
         <v>COGS</v>
       </c>
       <c r="D163" t="str">
-        <v>Packaging</v>
+        <v>Watermelon</v>
       </c>
       <c r="E163" t="str">
-        <v>แก้ว 1 ลัง</v>
+        <v>แตงโม 50 ลูก</v>
       </c>
       <c r="F163">
-        <v>1539</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>26/04/2026</v>
+        <v>25/04/2026</v>
       </c>
       <c r="B164" t="str">
         <v>Apr26</v>
@@ -4406,13 +4406,13 @@
         <v>COGS</v>
       </c>
       <c r="D164" t="str">
-        <v>Packaging</v>
+        <v>Orange</v>
       </c>
       <c r="E164" t="str">
-        <v>แก้ว3ลัง</v>
+        <v>ส้ม 20x22กก 440 กก. x30 = 13,200 + ค่าขนส่ง 1,200 (22/04/69)</v>
       </c>
       <c r="F164">
-        <v>7090</v>
+        <v>14400</v>
       </c>
     </row>
     <row r="165">
@@ -4426,13 +4426,13 @@
         <v>COGS</v>
       </c>
       <c r="D165" t="str">
-        <v>Mango</v>
+        <v>Packaging</v>
       </c>
       <c r="E165" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>แก้ว 1 ลัง</v>
       </c>
       <c r="F165">
-        <v>780</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="166">
@@ -4446,18 +4446,18 @@
         <v>COGS</v>
       </c>
       <c r="D166" t="str">
-        <v>Apple</v>
+        <v>Packaging</v>
       </c>
       <c r="E166" t="str">
-        <v>แอปเปิ้ล 4</v>
+        <v>แก้ว3ลัง</v>
       </c>
       <c r="F166">
-        <v>1400</v>
+        <v>7090</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>27/04/2026</v>
+        <v>26/04/2026</v>
       </c>
       <c r="B167" t="str">
         <v>Apr26</v>
@@ -4466,18 +4466,18 @@
         <v>COGS</v>
       </c>
       <c r="D167" t="str">
-        <v>Watermelon</v>
+        <v>Mango</v>
       </c>
       <c r="E167" t="str">
-        <v>26/4/26 50 ลูก</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F167">
-        <v>4000</v>
+        <v>780</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>28/04/2026</v>
+        <v>26/04/2026</v>
       </c>
       <c r="B168" t="str">
         <v>Apr26</v>
@@ -4486,18 +4486,18 @@
         <v>COGS</v>
       </c>
       <c r="D168" t="str">
-        <v>Packaging</v>
+        <v>Apple</v>
       </c>
       <c r="E168" t="str">
-        <v>หลอด 704(20ห่อ)</v>
+        <v>แอปเปิ้ล 4</v>
       </c>
       <c r="F168">
-        <v>2110</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>28/04/2026</v>
+        <v>27/04/2026</v>
       </c>
       <c r="B169" t="str">
         <v>Apr26</v>
@@ -4506,13 +4506,13 @@
         <v>COGS</v>
       </c>
       <c r="D169" t="str">
-        <v>Orange</v>
+        <v>Watermelon</v>
       </c>
       <c r="E169" t="str">
-        <v>รอบ 27/04/69</v>
+        <v>26/4/26 50 ลูก</v>
       </c>
       <c r="F169">
-        <v>21600</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="170">
@@ -4526,13 +4526,13 @@
         <v>COGS</v>
       </c>
       <c r="D170" t="str">
-        <v>Coconut</v>
+        <v>Packaging</v>
       </c>
       <c r="E170" t="str">
-        <v>ค่าส่งมะพร้าว</v>
+        <v>หลอด 704(20ห่อ)</v>
       </c>
       <c r="F170">
-        <v>100</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="171">
@@ -4546,13 +4546,13 @@
         <v>COGS</v>
       </c>
       <c r="D171" t="str">
-        <v>Apple</v>
+        <v>Orange</v>
       </c>
       <c r="E171" t="str">
-        <v>แอปเปิ้ล 4 ลัง</v>
+        <v>ส้ม 660 กก. x30 = 19,800 + ค่าส่ง 1,800 (รอบ 27/04/69)</v>
       </c>
       <c r="F171">
-        <v>1400</v>
+        <v>21600</v>
       </c>
     </row>
     <row r="172">
@@ -4566,18 +4566,18 @@
         <v>COGS</v>
       </c>
       <c r="D172" t="str">
-        <v>Mango</v>
+        <v>Coconut</v>
       </c>
       <c r="E172" t="str">
-        <v>มะม่วง 2 ลัง</v>
+        <v>ค่าส่งมะพร้าว</v>
       </c>
       <c r="F172">
-        <v>1560</v>
+        <v>100</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>29/04/2026</v>
+        <v>28/04/2026</v>
       </c>
       <c r="B173" t="str">
         <v>Apr26</v>
@@ -4586,18 +4586,18 @@
         <v>COGS</v>
       </c>
       <c r="D173" t="str">
-        <v>Milk/Conden</v>
+        <v>Apple</v>
       </c>
       <c r="E173" t="str">
-        <v>นมข้นหวาน1ลัง 836</v>
+        <v>แอปเปิ้ล 4 ลัง</v>
       </c>
       <c r="F173">
-        <v>2160</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>29/04/2026</v>
+        <v>28/04/2026</v>
       </c>
       <c r="B174" t="str">
         <v>Apr26</v>
@@ -4606,13 +4606,13 @@
         <v>COGS</v>
       </c>
       <c r="D174" t="str">
-        <v>Packaging</v>
+        <v>Mango</v>
       </c>
       <c r="E174" t="str">
-        <v>นมข้นหวาน2ลัง 1602</v>
+        <v>มะม่วง 2 ลัง</v>
       </c>
       <c r="F174">
-        <v>3210</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="175">
@@ -4626,13 +4626,13 @@
         <v>COGS</v>
       </c>
       <c r="D175" t="str">
-        <v>Watermelon</v>
+        <v>Milk/Conden</v>
       </c>
       <c r="E175" t="str">
-        <v>แตงโม 60 ลูก</v>
+        <v>นมข้นหวาน1ลัง 836</v>
       </c>
       <c r="F175">
-        <v>4200</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="176">
@@ -4646,18 +4646,18 @@
         <v>COGS</v>
       </c>
       <c r="D176" t="str">
-        <v>Transportation</v>
+        <v>Packaging</v>
       </c>
       <c r="E176" t="str">
-        <v>เนื้อ 10 x 50 500</v>
+        <v>นมข้นหวาน2ลัง 1602</v>
       </c>
       <c r="F176">
-        <v>2395</v>
+        <v>3210</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>30/04/2026</v>
+        <v>29/04/2026</v>
       </c>
       <c r="B177" t="str">
         <v>Apr26</v>
@@ -4666,33 +4666,33 @@
         <v>COGS</v>
       </c>
       <c r="D177" t="str">
-        <v>Pineapple</v>
+        <v>Watermelon</v>
       </c>
       <c r="E177" t="str">
-        <v>สับปะรส 3 ตะกร้า</v>
+        <v>แตงโม 60 ลูก</v>
       </c>
       <c r="F177">
-        <v>1500</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>30/04/2026</v>
+        <v>29/04/2026</v>
       </c>
       <c r="B178" t="str">
         <v>Apr26</v>
       </c>
       <c r="C178" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D178" t="str">
-        <v>Rental</v>
+        <v>Transportation</v>
       </c>
       <c r="E178" t="str">
-        <v>Rent</v>
+        <v>เนื้อ 10 x 50 500</v>
       </c>
       <c r="F178">
-        <v>35000</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="179">
@@ -4706,13 +4706,13 @@
         <v>COGS</v>
       </c>
       <c r="D179" t="str">
-        <v>Stock</v>
+        <v>Pineapple</v>
       </c>
       <c r="E179" t="str">
-        <v>Stock (Allocated 82.9%)</v>
+        <v>สับปะรส 3 ตะกร้า</v>
       </c>
       <c r="F179">
-        <v>9948</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="180">
@@ -4723,56 +4723,56 @@
         <v>Apr26</v>
       </c>
       <c r="C180" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D180" t="str">
-        <v>Guava</v>
+        <v>Rental</v>
       </c>
       <c r="E180" t="str">
-        <v>ฝรั่ง ตะกร้าแรก (นาง ประนอม, BBL X8148) [bank 30/04 22:50]</v>
+        <v>Rent</v>
       </c>
       <c r="F180">
-        <v>1500</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>01/05/2026</v>
+        <v>30/04/2026</v>
       </c>
       <c r="B181" t="str">
-        <v>May26</v>
+        <v>Apr26</v>
       </c>
       <c r="C181" t="str">
         <v>COGS</v>
       </c>
       <c r="D181" t="str">
-        <v>Guava</v>
+        <v>Stock</v>
       </c>
       <c r="E181" t="str">
-        <v>ฝรั่ง (แยกจากใบเสร็จรวม 01/05)</v>
+        <v>Stock (Allocated 82.9%)</v>
       </c>
       <c r="F181">
-        <v>300</v>
+        <v>9948</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>01/05/2026</v>
+        <v>30/04/2026</v>
       </c>
       <c r="B182" t="str">
-        <v>May26</v>
+        <v>Apr26</v>
       </c>
       <c r="C182" t="str">
-        <v>CAPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D182" t="str">
-        <v>Investment</v>
+        <v>Guava</v>
       </c>
       <c r="E182" t="str">
-        <v>ร่ม 2 คัน (1,176 + 843)</v>
+        <v>ฝรั่ง ตะกร้าแรก (นาง ประนอม, BBL X8148) [bank 30/04 22:50]</v>
       </c>
       <c r="F182">
-        <v>2019</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="183">
@@ -4786,13 +4786,13 @@
         <v>COGS</v>
       </c>
       <c r="D183" t="str">
-        <v>Milk/Conden</v>
+        <v>Guava</v>
       </c>
       <c r="E183" t="str">
-        <v>นมข้นจืด (แยกจากใบเสร็จรวม 01/05)</v>
+        <v>ฝรั่ง (แยกจากใบเสร็จรวม 01/05)</v>
       </c>
       <c r="F183">
-        <v>785</v>
+        <v>300</v>
       </c>
     </row>
     <row r="184">
@@ -4803,16 +4803,16 @@
         <v>May26</v>
       </c>
       <c r="C184" t="str">
-        <v>OPEX</v>
+        <v>CAPEX</v>
       </c>
       <c r="D184" t="str">
-        <v>Other</v>
+        <v>Investment</v>
       </c>
       <c r="E184" t="str">
-        <v>ที่ปั๊ม (แยกจากใบเสร็จรวม 01/05)</v>
+        <v>ร่ม 2 คัน (1,176 + 843)</v>
       </c>
       <c r="F184">
-        <v>176</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="185">
@@ -4823,56 +4823,56 @@
         <v>May26</v>
       </c>
       <c r="C185" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D185" t="str">
-        <v>Other</v>
+        <v>Milk/Conden</v>
       </c>
       <c r="E185" t="str">
-        <v>ยอดคงเหลือใบเสร็จ 01/05 — ไม่ระบุรายการ ต้องตรวจสอบสลิป</v>
+        <v>นมข้นจืด (แยกจากใบเสร็จรวม 01/05)</v>
       </c>
       <c r="F185">
-        <v>4543</v>
+        <v>785</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>02/05/2026</v>
+        <v>01/05/2026</v>
       </c>
       <c r="B186" t="str">
         <v>May26</v>
       </c>
       <c r="C186" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D186" t="str">
-        <v>Mango</v>
+        <v>Other</v>
       </c>
       <c r="E186" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>ที่ปั๊ม (แยกจากใบเสร็จรวม 01/05)</v>
       </c>
       <c r="F186">
-        <v>910</v>
+        <v>176</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>02/05/2026</v>
+        <v>01/05/2026</v>
       </c>
       <c r="B187" t="str">
         <v>May26</v>
       </c>
       <c r="C187" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D187" t="str">
-        <v>Apple</v>
+        <v>Other</v>
       </c>
       <c r="E187" t="str">
-        <v>แอปเปิ้ล 4 ลัง</v>
+        <v>ยอดคงเหลือใบเสร็จ 01/05 — ไม่ระบุรายการ ต้องตรวจสอบสลิป</v>
       </c>
       <c r="F187">
-        <v>1500</v>
+        <v>4543</v>
       </c>
     </row>
     <row r="188">
@@ -4886,13 +4886,13 @@
         <v>COGS</v>
       </c>
       <c r="D188" t="str">
-        <v>Pineapple</v>
+        <v>Mango</v>
       </c>
       <c r="E188" t="str">
-        <v>สับปะรด 30 ลูก</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F188">
-        <v>1116</v>
+        <v>910</v>
       </c>
     </row>
     <row r="189">
@@ -4903,16 +4903,16 @@
         <v>May26</v>
       </c>
       <c r="C189" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D189" t="str">
-        <v>Other</v>
+        <v>Apple</v>
       </c>
       <c r="E189" t="str">
-        <v>ค่าหาหมอเอ</v>
+        <v>แอปเปิ้ล 4 ลัง</v>
       </c>
       <c r="F189">
-        <v>706</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="190">
@@ -4923,56 +4923,56 @@
         <v>May26</v>
       </c>
       <c r="C190" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D190" t="str">
-        <v>Other</v>
+        <v>Pineapple</v>
       </c>
       <c r="E190" t="str">
-        <v>ค่าหมอเอ</v>
+        <v>สับปะรด 30 ลูก</v>
       </c>
       <c r="F190">
-        <v>13</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>04/05/2026</v>
+        <v>02/05/2026</v>
       </c>
       <c r="B191" t="str">
         <v>May26</v>
       </c>
       <c r="C191" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D191" t="str">
-        <v>Packaging</v>
+        <v>Other</v>
       </c>
       <c r="E191" t="str">
-        <v>ถุงมือ4อัน</v>
+        <v>ค่าหาหมอเอ</v>
       </c>
       <c r="F191">
-        <v>499</v>
+        <v>706</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>04/05/2026</v>
+        <v>02/05/2026</v>
       </c>
       <c r="B192" t="str">
         <v>May26</v>
       </c>
       <c r="C192" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D192" t="str">
-        <v>Apple</v>
+        <v>Other</v>
       </c>
       <c r="E192" t="str">
-        <v>แอปเปิ้ล 4 ลัง</v>
+        <v>ค่าหมอเอ</v>
       </c>
       <c r="F192">
-        <v>1400</v>
+        <v>13</v>
       </c>
     </row>
     <row r="193">
@@ -4986,13 +4986,13 @@
         <v>COGS</v>
       </c>
       <c r="D193" t="str">
-        <v>Mango</v>
+        <v>Packaging</v>
       </c>
       <c r="E193" t="str">
-        <v>มะม่วง 2 ลัง</v>
+        <v>ถุงมือ4อัน</v>
       </c>
       <c r="F193">
-        <v>1680</v>
+        <v>499</v>
       </c>
     </row>
     <row r="194">
@@ -5006,38 +5006,38 @@
         <v>COGS</v>
       </c>
       <c r="D194" t="str">
-        <v>Watermelon</v>
+        <v>Apple</v>
       </c>
       <c r="E194" t="str">
-        <v>30-4-2569 เบอร์ 70฿ 60 ลูก</v>
+        <v>แอปเปิ้ล 4 ลัง</v>
       </c>
       <c r="F194">
-        <v>7000</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>06/05/2026</v>
+        <v>04/05/2026</v>
       </c>
       <c r="B195" t="str">
         <v>May26</v>
       </c>
       <c r="C195" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D195" t="str">
-        <v>Other</v>
+        <v>Mango</v>
       </c>
       <c r="E195" t="str">
-        <v>ทิชชู่3แพค 36ห่อ</v>
+        <v>มะม่วง 2 ลัง</v>
       </c>
       <c r="F195">
-        <v>451</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>06/05/2026</v>
+        <v>04/05/2026</v>
       </c>
       <c r="B196" t="str">
         <v>May26</v>
@@ -5046,13 +5046,13 @@
         <v>COGS</v>
       </c>
       <c r="D196" t="str">
-        <v>Mango</v>
+        <v>Watermelon</v>
       </c>
       <c r="E196" t="str">
-        <v>มะม่วง 2 ลัง</v>
+        <v>30-4-2569 เบอร์ 70฿ 60 ลูก</v>
       </c>
       <c r="F196">
-        <v>1750</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="197">
@@ -5063,16 +5063,16 @@
         <v>May26</v>
       </c>
       <c r="C197" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D197" t="str">
-        <v>Pineapple</v>
+        <v>Other</v>
       </c>
       <c r="E197" t="str">
-        <v>สับปะรด 18 ลูก</v>
+        <v>ทิชชู่3แพค 36ห่อ</v>
       </c>
       <c r="F197">
-        <v>486</v>
+        <v>451</v>
       </c>
     </row>
     <row r="198">
@@ -5086,18 +5086,18 @@
         <v>COGS</v>
       </c>
       <c r="D198" t="str">
-        <v>Apple</v>
+        <v>Mango</v>
       </c>
       <c r="E198" t="str">
-        <v>แอปเปิ้ล 4 ลัง</v>
+        <v>มะม่วง 2 ลัง</v>
       </c>
       <c r="F198">
-        <v>1400</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>08/05/2026</v>
+        <v>06/05/2026</v>
       </c>
       <c r="B199" t="str">
         <v>May26</v>
@@ -5106,18 +5106,18 @@
         <v>COGS</v>
       </c>
       <c r="D199" t="str">
-        <v>Transportation</v>
+        <v>Pineapple</v>
       </c>
       <c r="E199" t="str">
-        <v>น้ำ 20 ขวด 900 ถอดเสื้อ 30 ลูก750 กล่องโฟม 3</v>
+        <v>สับปะรด 18 ลูก</v>
       </c>
       <c r="F199">
-        <v>4555</v>
+        <v>486</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>08/05/2026</v>
+        <v>06/05/2026</v>
       </c>
       <c r="B200" t="str">
         <v>May26</v>
@@ -5126,13 +5126,13 @@
         <v>COGS</v>
       </c>
       <c r="D200" t="str">
-        <v>Water</v>
+        <v>Apple</v>
       </c>
       <c r="E200" t="str">
-        <v>น้ำมะร้าว 1 ลัง</v>
+        <v>แอปเปิ้ล 4 ลัง</v>
       </c>
       <c r="F200">
-        <v>1100</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="201">
@@ -5146,13 +5146,13 @@
         <v>COGS</v>
       </c>
       <c r="D201" t="str">
-        <v>Packaging</v>
+        <v>Transportation</v>
       </c>
       <c r="E201" t="str">
-        <v>6 พ.ค. น้ำ 30 ขวด 1500 บาท เนื้อ 11 โล 1320 บาท</v>
+        <v>น้ำ 20 ขวด 900 ถอดเสื้อ 30 ลูก750 กล่องโฟม 3</v>
       </c>
       <c r="F201">
-        <v>2820</v>
+        <v>4555</v>
       </c>
     </row>
     <row r="202">
@@ -5163,16 +5163,16 @@
         <v>May26</v>
       </c>
       <c r="C202" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D202" t="str">
-        <v>Other</v>
+        <v>Water</v>
       </c>
       <c r="E202" t="str">
-        <v>ค่าทำความสะอาดตึกชั้น 1</v>
+        <v>น้ำมะร้าว 1 ลัง</v>
       </c>
       <c r="F202">
-        <v>2700</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="203">
@@ -5186,18 +5186,18 @@
         <v>COGS</v>
       </c>
       <c r="D203" t="str">
-        <v>Watermelon</v>
+        <v>Packaging</v>
       </c>
       <c r="E203" t="str">
-        <v>4-5-2569 เบอร์ 70฿ 60 ลูก ยอด 4,200</v>
+        <v>6 พ.ค. น้ำ 30 ขวด 1500 บาท เนื้อ 11 โล 1320 บาท</v>
       </c>
       <c r="F203">
-        <v>8200</v>
+        <v>2820</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>09/05/2026</v>
+        <v>08/05/2026</v>
       </c>
       <c r="B204" t="str">
         <v>May26</v>
@@ -5209,15 +5209,15 @@
         <v>Other</v>
       </c>
       <c r="E204" t="str">
-        <v>พรหมเช็ดเท้า 1 ผืน</v>
+        <v>ค่าทำความสะอาดตึกชั้น 1</v>
       </c>
       <c r="F204">
-        <v>372</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>09/05/2026</v>
+        <v>08/05/2026</v>
       </c>
       <c r="B205" t="str">
         <v>May26</v>
@@ -5226,13 +5226,13 @@
         <v>COGS</v>
       </c>
       <c r="D205" t="str">
-        <v>Milk/Conden</v>
+        <v>Watermelon</v>
       </c>
       <c r="E205" t="str">
-        <v>นมข้นจืด 1ลัง 636</v>
+        <v>4-5-2569 เบอร์ 70฿ 60 ลูก ยอด 4,200</v>
       </c>
       <c r="F205">
-        <v>1122</v>
+        <v>8200</v>
       </c>
     </row>
     <row r="206">
@@ -5243,16 +5243,16 @@
         <v>May26</v>
       </c>
       <c r="C206" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D206" t="str">
-        <v>Packaging</v>
+        <v>Other</v>
       </c>
       <c r="E206" t="str">
-        <v>นมข้น 3 ลัง 2568</v>
+        <v>พรหมเช็ดเท้า 1 ผืน</v>
       </c>
       <c r="F206">
-        <v>4875</v>
+        <v>372</v>
       </c>
     </row>
     <row r="207">
@@ -5266,13 +5266,13 @@
         <v>COGS</v>
       </c>
       <c r="D207" t="str">
-        <v>Packaging</v>
+        <v>Milk/Conden</v>
       </c>
       <c r="E207" t="str">
-        <v>แก้ว3ลัง 5,301</v>
+        <v>นมข้นจืด 1ลัง 636</v>
       </c>
       <c r="F207">
-        <v>6132</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="208">
@@ -5289,10 +5289,10 @@
         <v>Packaging</v>
       </c>
       <c r="E208" t="str">
-        <v>ถุงมือ 20 กล่อง 2246 ฝา1ลัง 969</v>
+        <v>นมข้น 3 ลัง 2568</v>
       </c>
       <c r="F208">
-        <v>4496</v>
+        <v>4875</v>
       </c>
     </row>
     <row r="209">
@@ -5306,38 +5306,38 @@
         <v>COGS</v>
       </c>
       <c r="D209" t="str">
-        <v>Transportation</v>
+        <v>Packaging</v>
       </c>
       <c r="E209" t="str">
-        <v>Lalamove</v>
+        <v>แก้ว3ลัง 5,301</v>
       </c>
       <c r="F209">
-        <v>2000</v>
+        <v>6132</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>10/05/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="B210" t="str">
         <v>May26</v>
       </c>
       <c r="C210" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D210" t="str">
-        <v>Other</v>
+        <v>Packaging</v>
       </c>
       <c r="E210" t="str">
-        <v>ไฟ 2อัน 422</v>
+        <v>ถุงมือ 20 กล่อง 2246 ฝา1ลัง 969</v>
       </c>
       <c r="F210">
-        <v>838</v>
+        <v>4496</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>11/05/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="B211" t="str">
         <v>May26</v>
@@ -5346,33 +5346,33 @@
         <v>COGS</v>
       </c>
       <c r="D211" t="str">
-        <v>Guava</v>
+        <v>Transportation</v>
       </c>
       <c r="E211" t="str">
-        <v>ฝรั่ง 1 ตะกร้า</v>
+        <v>Lalamove</v>
       </c>
       <c r="F211">
-        <v>600</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>11/05/2026</v>
+        <v>10/05/2026</v>
       </c>
       <c r="B212" t="str">
         <v>May26</v>
       </c>
       <c r="C212" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D212" t="str">
-        <v>Mango</v>
+        <v>Other</v>
       </c>
       <c r="E212" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>ไฟ 2อัน 422</v>
       </c>
       <c r="F212">
-        <v>910</v>
+        <v>838</v>
       </c>
     </row>
     <row r="213">
@@ -5386,18 +5386,18 @@
         <v>COGS</v>
       </c>
       <c r="D213" t="str">
-        <v>Watermelon</v>
+        <v>Guava</v>
       </c>
       <c r="E213" t="str">
-        <v>แตงโม 4000 วันที่ 9-5-26</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F213">
-        <v>4000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>12/05/2026</v>
+        <v>11/05/2026</v>
       </c>
       <c r="B214" t="str">
         <v>May26</v>
@@ -5406,38 +5406,38 @@
         <v>COGS</v>
       </c>
       <c r="D214" t="str">
-        <v>Coconut Meat</v>
+        <v>Mango</v>
       </c>
       <c r="E214" t="str">
-        <v>เนื้อมะพร้าว 1 ลัง</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F214">
-        <v>3500</v>
+        <v>910</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>13/05/2026</v>
+        <v>11/05/2026</v>
       </c>
       <c r="B215" t="str">
         <v>May26</v>
       </c>
       <c r="C215" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D215" t="str">
-        <v>Other</v>
+        <v>Watermelon</v>
       </c>
       <c r="E215" t="str">
-        <v>ที่หนีบ 6ตัว 374 บาท</v>
+        <v>แตงโม 4000 วันที่ 9-5-26</v>
       </c>
       <c r="F215">
-        <v>374</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>13/05/2026</v>
+        <v>12/05/2026</v>
       </c>
       <c r="B216" t="str">
         <v>May26</v>
@@ -5446,53 +5446,53 @@
         <v>COGS</v>
       </c>
       <c r="D216" t="str">
-        <v>Pineapple</v>
+        <v>Coconut Meat</v>
       </c>
       <c r="E216" t="str">
-        <v>09/05/26 สับปะรด 2 ตะกร้า</v>
+        <v>เนื้อมะพร้าว 1 ลัง</v>
       </c>
       <c r="F216">
-        <v>1008</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>14/05/2026</v>
+        <v>13/05/2026</v>
       </c>
       <c r="B217" t="str">
         <v>May26</v>
       </c>
       <c r="C217" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D217" t="str">
-        <v>Watermelon</v>
+        <v>Other</v>
       </c>
       <c r="E217" t="str">
-        <v>11-5-2569 50 ลูก ยอด 4,000</v>
+        <v>ที่หนีบ 6ตัว 374 บาท</v>
       </c>
       <c r="F217">
-        <v>8000</v>
+        <v>374</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>14/05/2026</v>
+        <v>13/05/2026</v>
       </c>
       <c r="B218" t="str">
         <v>May26</v>
       </c>
       <c r="C218" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D218" t="str">
-        <v>Rental</v>
+        <v>Pineapple</v>
       </c>
       <c r="E218" t="str">
-        <v>ค่าเช่าร้าน 1 พ.ค.</v>
+        <v>09/05/26 สับปะรด 2 ตะกร้า</v>
       </c>
       <c r="F218">
-        <v>35000</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="219">
@@ -5503,16 +5503,16 @@
         <v>May26</v>
       </c>
       <c r="C219" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D219" t="str">
-        <v>Rental</v>
+        <v>Watermelon</v>
       </c>
       <c r="E219" t="str">
-        <v>ค่าเช่าคลัง พ.ค. (B1 ครึ่งหนึ่ง)</v>
+        <v>11-5-2569 50 ลูก ยอด 4,000</v>
       </c>
       <c r="F219">
-        <v>6000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="220">
@@ -5523,16 +5523,16 @@
         <v>May26</v>
       </c>
       <c r="C220" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D220" t="str">
-        <v>Guava</v>
+        <v>Rental</v>
       </c>
       <c r="E220" t="str">
-        <v>ฝรั่ง 1 ตะกร้า</v>
+        <v>ค่าเช่าร้าน 1 พ.ค.</v>
       </c>
       <c r="F220">
-        <v>600</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="221">
@@ -5543,16 +5543,16 @@
         <v>May26</v>
       </c>
       <c r="C221" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D221" t="str">
-        <v>Apple</v>
+        <v>Rental</v>
       </c>
       <c r="E221" t="str">
-        <v>แอปเปิ้ล 3 ลัง</v>
+        <v>ค่าเช่าคลัง พ.ค. (B1 ครึ่งหนึ่ง)</v>
       </c>
       <c r="F221">
-        <v>1050</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="222">
@@ -5566,18 +5566,18 @@
         <v>COGS</v>
       </c>
       <c r="D222" t="str">
-        <v>Mango</v>
+        <v>Guava</v>
       </c>
       <c r="E222" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F222">
-        <v>875</v>
+        <v>600</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>15/05/2026</v>
+        <v>14/05/2026</v>
       </c>
       <c r="B223" t="str">
         <v>May26</v>
@@ -5586,18 +5586,18 @@
         <v>COGS</v>
       </c>
       <c r="D223" t="str">
-        <v>Orange</v>
+        <v>Apple</v>
       </c>
       <c r="E223" t="str">
-        <v>15/05/69</v>
+        <v>แอปเปิ้ล 3 ลัง</v>
       </c>
       <c r="F223">
-        <v>15730</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>15/05/2026</v>
+        <v>14/05/2026</v>
       </c>
       <c r="B224" t="str">
         <v>May26</v>
@@ -5606,38 +5606,38 @@
         <v>COGS</v>
       </c>
       <c r="D224" t="str">
-        <v>Orange</v>
+        <v>Mango</v>
       </c>
       <c r="E224" t="str">
-        <v>05/05/69 ส้ม 30x22กก 660กกx30</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F224">
-        <v>21450</v>
+        <v>875</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>16/05/2026</v>
+        <v>15/05/2026</v>
       </c>
       <c r="B225" t="str">
         <v>May26</v>
       </c>
       <c r="C225" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D225" t="str">
-        <v>Other</v>
+        <v>Orange</v>
       </c>
       <c r="E225" t="str">
-        <v>Police fees -2000 2 head</v>
+        <v>ส้ม 22x22กก 484 กก. x30 = 14,520 + ค่าส่ง 22x55 = 1,210 (15/05/69)</v>
       </c>
       <c r="F225">
-        <v>4290</v>
+        <v>15730</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>16/05/2026</v>
+        <v>15/05/2026</v>
       </c>
       <c r="B226" t="str">
         <v>May26</v>
@@ -5646,13 +5646,13 @@
         <v>COGS</v>
       </c>
       <c r="D226" t="str">
-        <v>Coconut</v>
+        <v>Orange</v>
       </c>
       <c r="E226" t="str">
-        <v>มะพร้าว 20 โล</v>
+        <v>05/05/69 ส้ม 30x22กก 660กกx30</v>
       </c>
       <c r="F226">
-        <v>2400</v>
+        <v>21450</v>
       </c>
     </row>
     <row r="227">
@@ -5663,16 +5663,16 @@
         <v>May26</v>
       </c>
       <c r="C227" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D227" t="str">
-        <v>Watermelon</v>
+        <v>Other</v>
       </c>
       <c r="E227" t="str">
-        <v>14/05/26 18 ลูก 504 บาท 16/05/26 18 ลูก</v>
+        <v>Police fees -2000 2 head</v>
       </c>
       <c r="F227">
-        <v>1008</v>
+        <v>4290</v>
       </c>
     </row>
     <row r="228">
@@ -5686,18 +5686,18 @@
         <v>COGS</v>
       </c>
       <c r="D228" t="str">
-        <v>Mango</v>
+        <v>Coconut</v>
       </c>
       <c r="E228" t="str">
-        <v>มะม่วง 1</v>
+        <v>มะพร้าว 20 โล</v>
       </c>
       <c r="F228">
-        <v>875</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>19/05/2026</v>
+        <v>16/05/2026</v>
       </c>
       <c r="B229" t="str">
         <v>May26</v>
@@ -5706,18 +5706,18 @@
         <v>COGS</v>
       </c>
       <c r="D229" t="str">
-        <v>Mango</v>
+        <v>Watermelon</v>
       </c>
       <c r="E229" t="str">
-        <v>มะม่วง 1 ลัง (25 โล)</v>
+        <v>14/05/26 18 ลูก 504 บาท 16/05/26 18 ลูก</v>
       </c>
       <c r="F229">
-        <v>875</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>19/05/2026</v>
+        <v>16/05/2026</v>
       </c>
       <c r="B230" t="str">
         <v>May26</v>
@@ -5726,13 +5726,13 @@
         <v>COGS</v>
       </c>
       <c r="D230" t="str">
-        <v>Guava</v>
+        <v>Mango</v>
       </c>
       <c r="E230" t="str">
-        <v>ฝรั่ง 1 ลัง</v>
+        <v>มะม่วง 1</v>
       </c>
       <c r="F230">
-        <v>600</v>
+        <v>875</v>
       </c>
     </row>
     <row r="231">
@@ -5746,13 +5746,13 @@
         <v>COGS</v>
       </c>
       <c r="D231" t="str">
-        <v>Apple</v>
+        <v>Mango</v>
       </c>
       <c r="E231" t="str">
-        <v>แอปเปิ้ล 4 ลังครับ</v>
+        <v>มะม่วง 1 ลัง (25 โล)</v>
       </c>
       <c r="F231">
-        <v>1400</v>
+        <v>875</v>
       </c>
     </row>
     <row r="232">
@@ -5766,18 +5766,18 @@
         <v>COGS</v>
       </c>
       <c r="D232" t="str">
-        <v>Pineapple</v>
+        <v>Guava</v>
       </c>
       <c r="E232" t="str">
-        <v>36*18 648</v>
+        <v>ฝรั่ง 1 ลัง</v>
       </c>
       <c r="F232">
-        <v>648</v>
+        <v>600</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>22/05/2026</v>
+        <v>19/05/2026</v>
       </c>
       <c r="B233" t="str">
         <v>May26</v>
@@ -5789,15 +5789,15 @@
         <v>Apple</v>
       </c>
       <c r="E233" t="str">
-        <v>แอปเปิ้ล 2 ลัง</v>
+        <v>แอปเปิ้ล 4 ลังครับ</v>
       </c>
       <c r="F233">
-        <v>700</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>22/05/2026</v>
+        <v>19/05/2026</v>
       </c>
       <c r="B234" t="str">
         <v>May26</v>
@@ -5809,10 +5809,10 @@
         <v>Pineapple</v>
       </c>
       <c r="E234" t="str">
-        <v>สับปะรด 18 ลูก</v>
+        <v>36*18 648</v>
       </c>
       <c r="F234">
-        <v>522</v>
+        <v>648</v>
       </c>
     </row>
     <row r="235">
@@ -5826,13 +5826,13 @@
         <v>COGS</v>
       </c>
       <c r="D235" t="str">
-        <v>Mango</v>
+        <v>Apple</v>
       </c>
       <c r="E235" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>แอปเปิ้ล 2 ลัง</v>
       </c>
       <c r="F235">
-        <v>1000</v>
+        <v>700</v>
       </c>
     </row>
     <row r="236">
@@ -5846,13 +5846,13 @@
         <v>COGS</v>
       </c>
       <c r="D236" t="str">
-        <v>Watermelon</v>
+        <v>Pineapple</v>
       </c>
       <c r="E236" t="str">
-        <v>16-5-2569ยอด 4,000฿</v>
+        <v>สับปะรด 18 ลูก</v>
       </c>
       <c r="F236">
-        <v>12000</v>
+        <v>522</v>
       </c>
     </row>
     <row r="237">
@@ -5866,13 +5866,13 @@
         <v>COGS</v>
       </c>
       <c r="D237" t="str">
-        <v>Guava</v>
+        <v>Mango</v>
       </c>
       <c r="E237" t="str">
-        <v>ฝรั่ง 1 ตะกร้า</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F237">
-        <v>600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="238">
@@ -5886,18 +5886,18 @@
         <v>COGS</v>
       </c>
       <c r="D238" t="str">
-        <v>Transportation</v>
+        <v>Watermelon</v>
       </c>
       <c r="E238" t="str">
-        <v>ค่าขนส่ง</v>
+        <v>16-5-2569ยอด 4,000฿</v>
       </c>
       <c r="F238">
-        <v>2000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>23/05/2026</v>
+        <v>22/05/2026</v>
       </c>
       <c r="B239" t="str">
         <v>May26</v>
@@ -5906,18 +5906,18 @@
         <v>COGS</v>
       </c>
       <c r="D239" t="str">
-        <v>Packaging</v>
+        <v>Guava</v>
       </c>
       <c r="E239" t="str">
-        <v>แก้ว 3 ลัง</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F239">
-        <v>4680</v>
+        <v>600</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>23/05/2026</v>
+        <v>22/05/2026</v>
       </c>
       <c r="B240" t="str">
         <v>May26</v>
@@ -5926,13 +5926,13 @@
         <v>COGS</v>
       </c>
       <c r="D240" t="str">
-        <v>Packaging</v>
+        <v>Transportation</v>
       </c>
       <c r="E240" t="str">
-        <v>ฝา1 788</v>
+        <v>ค่าขนส่ง</v>
       </c>
       <c r="F240">
-        <v>2902</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="241">
@@ -5949,15 +5949,15 @@
         <v>Packaging</v>
       </c>
       <c r="E241" t="str">
-        <v>หลอด20 แพค (767)</v>
+        <v>แก้ว 3 ลัง</v>
       </c>
       <c r="F241">
-        <v>1502</v>
+        <v>4680</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>25/05/2026</v>
+        <v>23/05/2026</v>
       </c>
       <c r="B242" t="str">
         <v>May26</v>
@@ -5966,18 +5966,18 @@
         <v>COGS</v>
       </c>
       <c r="D242" t="str">
-        <v>Pineapple</v>
+        <v>Packaging</v>
       </c>
       <c r="E242" t="str">
-        <v>สับปะรด 18 ลูก</v>
+        <v>ฝา1 788</v>
       </c>
       <c r="F242">
-        <v>594</v>
+        <v>2902</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>25/05/2026</v>
+        <v>23/05/2026</v>
       </c>
       <c r="B243" t="str">
         <v>May26</v>
@@ -5986,13 +5986,13 @@
         <v>COGS</v>
       </c>
       <c r="D243" t="str">
-        <v>Apple</v>
+        <v>Packaging</v>
       </c>
       <c r="E243" t="str">
-        <v>แอปเปิ้ล 3 ลังครับ</v>
+        <v>หลอด20 แพค (767)</v>
       </c>
       <c r="F243">
-        <v>1050</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="244">
@@ -6006,13 +6006,13 @@
         <v>COGS</v>
       </c>
       <c r="D244" t="str">
-        <v>Orange</v>
+        <v>Pineapple</v>
       </c>
       <c r="E244" t="str">
-        <v>ค่าส่งส้ม Lalamove หักผ่านบัตร</v>
+        <v>สับปะรด 18 ลูก</v>
       </c>
       <c r="F244">
-        <v>1245</v>
+        <v>594</v>
       </c>
     </row>
     <row r="245">
@@ -6026,13 +6026,13 @@
         <v>COGS</v>
       </c>
       <c r="D245" t="str">
-        <v>Orange</v>
+        <v>Apple</v>
       </c>
       <c r="E245" t="str">
-        <v>24/05/69</v>
+        <v>แอปเปิ้ล 3 ลังครับ</v>
       </c>
       <c r="F245">
-        <v>15015</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="246">
@@ -6043,16 +6043,16 @@
         <v>May26</v>
       </c>
       <c r="C246" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D246" t="str">
-        <v>Salary</v>
+        <v>Orange</v>
       </c>
       <c r="E246" t="str">
-        <v>เงินเดือนซี เดือนพ.ค. (แก้ไข: ยืนยัน 24,000)</v>
+        <v>ค่าส่งส้ม Lalamove หักผ่านบัตร</v>
       </c>
       <c r="F246">
-        <v>24000</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="247">
@@ -6066,13 +6066,13 @@
         <v>COGS</v>
       </c>
       <c r="D247" t="str">
-        <v>Guava</v>
+        <v>Orange</v>
       </c>
       <c r="E247" t="str">
-        <v>ฝรั่ง 1 ตะกร้า</v>
+        <v>ส้ม 21x22กก 462 กก. x30 = 13,860 + ค่าส่ง 21x55 = 1,155 (24/05/69)</v>
       </c>
       <c r="F247">
-        <v>600</v>
+        <v>15015</v>
       </c>
     </row>
     <row r="248">
@@ -6083,101 +6083,101 @@
         <v>May26</v>
       </c>
       <c r="C248" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D248" t="str">
-        <v>Mango</v>
+        <v>Salary</v>
       </c>
       <c r="E248" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>เงินเดือนซี เดือนพ.ค. (แก้ไข: ยืนยัน 24,000)</v>
       </c>
       <c r="F248">
-        <v>1000</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>27/05/2026</v>
+        <v>25/05/2026</v>
       </c>
       <c r="B249" t="str">
         <v>May26</v>
       </c>
       <c r="C249" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D249" t="str">
-        <v>Salary</v>
+        <v>Guava</v>
       </c>
       <c r="E249" t="str">
-        <v>เงินเดือนเมน 5/26</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F249">
-        <v>19000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>28/05/2026</v>
+        <v>25/05/2026</v>
       </c>
       <c r="B250" t="str">
         <v>May26</v>
       </c>
       <c r="C250" t="str">
-        <v>CAPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D250" t="str">
-        <v>Investment</v>
+        <v>Mango</v>
       </c>
       <c r="E250" t="str">
-        <v>เครื่องสกัดเย็น 1</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F250">
-        <v>1065</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>28/05/2026</v>
+        <v>27/05/2026</v>
       </c>
       <c r="B251" t="str">
         <v>May26</v>
       </c>
       <c r="C251" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D251" t="str">
-        <v>Coconut</v>
+        <v>Salary</v>
       </c>
       <c r="E251" t="str">
-        <v>มะพร้าวถอดเสื้อ 23 ลูก *35 ราคา 805 ค่าส่ง 150</v>
+        <v>เงินเดือนเมน 5/26</v>
       </c>
       <c r="F251">
-        <v>955</v>
+        <v>19000</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>30/05/2026</v>
+        <v>28/05/2026</v>
       </c>
       <c r="B252" t="str">
         <v>May26</v>
       </c>
       <c r="C252" t="str">
-        <v>COGS</v>
+        <v>CAPEX</v>
       </c>
       <c r="D252" t="str">
-        <v>Pineapple</v>
+        <v>Investment</v>
       </c>
       <c r="E252" t="str">
-        <v>สับปะรด 18 ลูก</v>
+        <v>เครื่องสกัดเย็น 1</v>
       </c>
       <c r="F252">
-        <v>576</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>30/05/2026</v>
+        <v>28/05/2026</v>
       </c>
       <c r="B253" t="str">
         <v>May26</v>
@@ -6186,13 +6186,13 @@
         <v>COGS</v>
       </c>
       <c r="D253" t="str">
-        <v>Mango</v>
+        <v>Coconut</v>
       </c>
       <c r="E253" t="str">
-        <v>มะม่วง 1 ตะกร้า</v>
+        <v>มะพร้าวถอดเสื้อ 23 ลูก *35 ราคา 805 ค่าส่ง 150</v>
       </c>
       <c r="F253">
-        <v>960</v>
+        <v>955</v>
       </c>
     </row>
     <row r="254">
@@ -6203,16 +6203,16 @@
         <v>May26</v>
       </c>
       <c r="C254" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D254" t="str">
-        <v>Other</v>
+        <v>Pineapple</v>
       </c>
       <c r="E254" t="str">
-        <v>Unknown</v>
+        <v>สับปะรด 18 ลูก</v>
       </c>
       <c r="F254">
-        <v>1050</v>
+        <v>576</v>
       </c>
     </row>
     <row r="255">
@@ -6226,93 +6226,93 @@
         <v>COGS</v>
       </c>
       <c r="D255" t="str">
-        <v>Guava</v>
+        <v>Mango</v>
       </c>
       <c r="E255" t="str">
-        <v>ฝรั่ง 1 ตะกร้า</v>
+        <v>มะม่วง 1 ตะกร้า</v>
       </c>
       <c r="F255">
-        <v>600</v>
+        <v>960</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>31/05/2026</v>
+        <v>30/05/2026</v>
       </c>
       <c r="B256" t="str">
         <v>May26</v>
       </c>
       <c r="C256" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D256" t="str">
-        <v>Stock</v>
+        <v>Other</v>
       </c>
       <c r="E256" t="str">
-        <v>Stock Adjustment (Allocated to B2)</v>
+        <v>Unknown</v>
       </c>
       <c r="F256">
-        <v>-4830</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>01/06/2026</v>
+        <v>30/05/2026</v>
       </c>
       <c r="B257" t="str">
         <v>May26</v>
       </c>
       <c r="C257" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D257" t="str">
-        <v>Salary</v>
+        <v>Guava</v>
       </c>
       <c r="E257" t="str">
-        <v>Unknown</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F257">
-        <v>0</v>
+        <v>600</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>02/06/2026</v>
+        <v>31/05/2026</v>
       </c>
       <c r="B258" t="str">
-        <v>Jun26</v>
+        <v>May26</v>
       </c>
       <c r="C258" t="str">
         <v>COGS</v>
       </c>
       <c r="D258" t="str">
-        <v>Pineapple</v>
+        <v>Stock</v>
       </c>
       <c r="E258" t="str">
-        <v>สับปะรด ราคา 31*18 ลูก 558</v>
+        <v>Stock Adjustment (Allocated to B2)</v>
       </c>
       <c r="F258">
-        <v>558</v>
+        <v>-4830</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>02/06/2026</v>
+        <v>01/06/2026</v>
       </c>
       <c r="B259" t="str">
-        <v>Jun26</v>
+        <v>May26</v>
       </c>
       <c r="C259" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D259" t="str">
-        <v>Guava</v>
+        <v>Salary</v>
       </c>
       <c r="E259" t="str">
-        <v>ฝรั่ง 1 ตะกร้า</v>
+        <v>Unknown</v>
       </c>
       <c r="F259">
-        <v>600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="260">
@@ -6326,18 +6326,18 @@
         <v>COGS</v>
       </c>
       <c r="D260" t="str">
-        <v>Watermelon</v>
+        <v>Pineapple</v>
       </c>
       <c r="E260" t="str">
-        <v>แตงโม 160 ลูก (25-5-2569: 80 ลูก, 30-5-2569: 80 ลูก)</v>
+        <v>สับปะรด ราคา 31*18 ลูก 558</v>
       </c>
       <c r="F260">
-        <v>8000</v>
+        <v>558</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>04/06/2026</v>
+        <v>02/06/2026</v>
       </c>
       <c r="B261" t="str">
         <v>Jun26</v>
@@ -6346,18 +6346,18 @@
         <v>COGS</v>
       </c>
       <c r="D261" t="str">
-        <v>Watermelon</v>
+        <v>Guava</v>
       </c>
       <c r="E261" t="str">
-        <v>สลิปรวม: แตงโม 750 (audit fix, was bundled into Pineapple line)</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F261">
-        <v>750</v>
+        <v>600</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>04/06/2026</v>
+        <v>02/06/2026</v>
       </c>
       <c r="B262" t="str">
         <v>Jun26</v>
@@ -6366,13 +6366,13 @@
         <v>COGS</v>
       </c>
       <c r="D262" t="str">
-        <v>Guava</v>
+        <v>Watermelon</v>
       </c>
       <c r="E262" t="str">
-        <v>ฝรั่ง 1 ตะกร้า</v>
+        <v>แตงโม 160 ลูก (25-5-2569: 80 ลูก, 30-5-2569: 80 ลูก)</v>
       </c>
       <c r="F262">
-        <v>700</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="263">
@@ -6386,13 +6386,13 @@
         <v>COGS</v>
       </c>
       <c r="D263" t="str">
-        <v>Mango</v>
+        <v>Watermelon</v>
       </c>
       <c r="E263" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>สลิปรวม: แตงโม 750 (audit fix, was bundled into Pineapple line)</v>
       </c>
       <c r="F263">
-        <v>1040</v>
+        <v>750</v>
       </c>
     </row>
     <row r="264">
@@ -6406,13 +6406,13 @@
         <v>COGS</v>
       </c>
       <c r="D264" t="str">
-        <v>Apple</v>
+        <v>Guava</v>
       </c>
       <c r="E264" t="str">
-        <v>แอพเปิ้ล 4 ลัง</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F264">
-        <v>1400</v>
+        <v>700</v>
       </c>
     </row>
     <row r="265">
@@ -6426,13 +6426,13 @@
         <v>COGS</v>
       </c>
       <c r="D265" t="str">
-        <v>Pineapple</v>
+        <v>Mango</v>
       </c>
       <c r="E265" t="str">
-        <v>สับปะรด 2 ลูก</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F265">
-        <v>36</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="266">
@@ -6446,18 +6446,18 @@
         <v>COGS</v>
       </c>
       <c r="D266" t="str">
-        <v>Packaging</v>
+        <v>Apple</v>
       </c>
       <c r="E266" t="str">
-        <v>ขวดใหญ่ 1000ml 98 ใบ 364 ถุงเล็ก 20</v>
+        <v>แอพเปิ้ล 4 ลัง</v>
       </c>
       <c r="F266">
-        <v>764</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>05/06/2026</v>
+        <v>04/06/2026</v>
       </c>
       <c r="B267" t="str">
         <v>Jun26</v>
@@ -6469,15 +6469,15 @@
         <v>Pineapple</v>
       </c>
       <c r="E267" t="str">
-        <v>สับปะรด 33*18 รวม 594</v>
+        <v>สับปะรด 2 ลูก</v>
       </c>
       <c r="F267">
-        <v>594</v>
+        <v>36</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>05/06/2026</v>
+        <v>04/06/2026</v>
       </c>
       <c r="B268" t="str">
         <v>Jun26</v>
@@ -6486,18 +6486,18 @@
         <v>COGS</v>
       </c>
       <c r="D268" t="str">
-        <v>Watermelon</v>
+        <v>Packaging</v>
       </c>
       <c r="E268" t="str">
-        <v>แตงโม 100 ลูก (2-6-2569: 50 ลูก, 4-6-2569: 50 ลูก)</v>
+        <v>ขวดใหญ่ 1000ml 98 ใบ 364 ถุงเล็ก 20</v>
       </c>
       <c r="F268">
-        <v>8000</v>
+        <v>764</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>07/06/2026</v>
+        <v>05/06/2026</v>
       </c>
       <c r="B269" t="str">
         <v>Jun26</v>
@@ -6506,18 +6506,18 @@
         <v>COGS</v>
       </c>
       <c r="D269" t="str">
-        <v>Orange</v>
+        <v>Pineapple</v>
       </c>
       <c r="E269" t="str">
-        <v>ส้ม 20x22กก 440กกx30 13,200บาท</v>
+        <v>สับปะรด 33*18 รวม 594</v>
       </c>
       <c r="F269">
-        <v>14300</v>
+        <v>594</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>08/06/2026</v>
+        <v>05/06/2026</v>
       </c>
       <c r="B270" t="str">
         <v>Jun26</v>
@@ -6526,18 +6526,18 @@
         <v>COGS</v>
       </c>
       <c r="D270" t="str">
-        <v>Transportation</v>
+        <v>Watermelon</v>
       </c>
       <c r="E270" t="str">
-        <v>Lalamove</v>
+        <v>แตงโม 100 ลูก (2-6-2569: 50 ลูก, 4-6-2569: 50 ลูก)</v>
       </c>
       <c r="F270">
-        <v>2000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>08/06/2026</v>
+        <v>07/06/2026</v>
       </c>
       <c r="B271" t="str">
         <v>Jun26</v>
@@ -6546,13 +6546,13 @@
         <v>COGS</v>
       </c>
       <c r="D271" t="str">
-        <v>Stock</v>
+        <v>Orange</v>
       </c>
       <c r="E271" t="str">
-        <v>Stock June 2026 (B1 ครึ่งหนึ่ง 6,000; B2 ถืออีก 6,000)</v>
+        <v>ส้ม 20x22กก 440กกx30 13,200บาท</v>
       </c>
       <c r="F271">
-        <v>6000</v>
+        <v>14300</v>
       </c>
     </row>
     <row r="272">
@@ -6563,16 +6563,16 @@
         <v>Jun26</v>
       </c>
       <c r="C272" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D272" t="str">
-        <v>Rental</v>
+        <v>Transportation</v>
       </c>
       <c r="E272" t="str">
-        <v>ค่าเช่าร้านเดือน June (06) b1 35000</v>
+        <v>Lalamove</v>
       </c>
       <c r="F272">
-        <v>35000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="273">
@@ -6586,13 +6586,13 @@
         <v>COGS</v>
       </c>
       <c r="D273" t="str">
-        <v>Pineapple</v>
+        <v>Stock</v>
       </c>
       <c r="E273" t="str">
-        <v>สับปะรด 15 ลูก</v>
+        <v>Stock June 2026 (B1 ครึ่งหนึ่ง 6,000; B2 ถืออีก 6,000)</v>
       </c>
       <c r="F273">
-        <v>504</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="274">
@@ -6603,16 +6603,16 @@
         <v>Jun26</v>
       </c>
       <c r="C274" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D274" t="str">
-        <v>Mango</v>
+        <v>Rental</v>
       </c>
       <c r="E274" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>ค่าเช่าร้านเดือน June (06) b1 35000</v>
       </c>
       <c r="F274">
-        <v>1170</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="275">
@@ -6626,13 +6626,13 @@
         <v>COGS</v>
       </c>
       <c r="D275" t="str">
-        <v>Apple</v>
+        <v>Pineapple</v>
       </c>
       <c r="E275" t="str">
-        <v>แอปเปิ้ล 5 ลัง</v>
+        <v>สับปะรด 15 ลูก</v>
       </c>
       <c r="F275">
-        <v>1750</v>
+        <v>504</v>
       </c>
     </row>
     <row r="276">
@@ -6646,18 +6646,18 @@
         <v>COGS</v>
       </c>
       <c r="D276" t="str">
-        <v>Guava</v>
+        <v>Mango</v>
       </c>
       <c r="E276" t="str">
-        <v>ฝรั่ง 1 ตะกร้า</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F276">
-        <v>700</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>09/06/2026</v>
+        <v>08/06/2026</v>
       </c>
       <c r="B277" t="str">
         <v>Jun26</v>
@@ -6666,18 +6666,18 @@
         <v>COGS</v>
       </c>
       <c r="D277" t="str">
-        <v>Packaging</v>
+        <v>Apple</v>
       </c>
       <c r="E277" t="str">
-        <v>แก้ว 1937*3 รวม 5,811</v>
+        <v>แอปเปิ้ล 5 ลัง</v>
       </c>
       <c r="F277">
-        <v>6659</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>09/06/2026</v>
+        <v>08/06/2026</v>
       </c>
       <c r="B278" t="str">
         <v>Jun26</v>
@@ -6686,13 +6686,13 @@
         <v>COGS</v>
       </c>
       <c r="D278" t="str">
-        <v>Packaging</v>
+        <v>Guava</v>
       </c>
       <c r="E278" t="str">
-        <v>หลอด 20 แพ็ก 671</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F278">
-        <v>1149</v>
+        <v>700</v>
       </c>
     </row>
     <row r="279">
@@ -6709,10 +6709,10 @@
         <v>Packaging</v>
       </c>
       <c r="E279" t="str">
-        <v>ฝา1 714</v>
+        <v>แก้ว 1937*3 รวม 5,811</v>
       </c>
       <c r="F279">
-        <v>714</v>
+        <v>6659</v>
       </c>
     </row>
     <row r="280">
@@ -6729,15 +6729,15 @@
         <v>Packaging</v>
       </c>
       <c r="E280" t="str">
-        <v>ถุงขยะ 4แพคใหญ่ 1019</v>
+        <v>หลอด 20 แพ็ก 671</v>
       </c>
       <c r="F280">
-        <v>1830</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>11/06/2026</v>
+        <v>09/06/2026</v>
       </c>
       <c r="B281" t="str">
         <v>Jun26</v>
@@ -6746,18 +6746,18 @@
         <v>COGS</v>
       </c>
       <c r="D281" t="str">
-        <v>Guava</v>
+        <v>Packaging</v>
       </c>
       <c r="E281" t="str">
-        <v>ฝรั่ง 1 ลัง</v>
+        <v>ฝา1 714</v>
       </c>
       <c r="F281">
-        <v>700</v>
+        <v>714</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>12/06/2026</v>
+        <v>09/06/2026</v>
       </c>
       <c r="B282" t="str">
         <v>Jun26</v>
@@ -6766,18 +6766,18 @@
         <v>COGS</v>
       </c>
       <c r="D282" t="str">
-        <v>Coconut Water</v>
+        <v>Packaging</v>
       </c>
       <c r="E282" t="str">
-        <v>น้ำมะพร้าว50*20 1,000</v>
+        <v>ถุงขยะ 4แพคใหญ่ 1019</v>
       </c>
       <c r="F282">
-        <v>2200</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>12/06/2026</v>
+        <v>11/06/2026</v>
       </c>
       <c r="B283" t="str">
         <v>Jun26</v>
@@ -6786,13 +6786,13 @@
         <v>COGS</v>
       </c>
       <c r="D283" t="str">
-        <v>Mango</v>
+        <v>Guava</v>
       </c>
       <c r="E283" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>ฝรั่ง 1 ลัง</v>
       </c>
       <c r="F283">
-        <v>1170</v>
+        <v>700</v>
       </c>
     </row>
     <row r="284">
@@ -6806,13 +6806,13 @@
         <v>COGS</v>
       </c>
       <c r="D284" t="str">
-        <v>Apple</v>
+        <v>Coconut Water</v>
       </c>
       <c r="E284" t="str">
-        <v>แอปเปิ้ล 5 ลัง</v>
+        <v>น้ำมะพร้าว50*20 1,000</v>
       </c>
       <c r="F284">
-        <v>1750</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="285">
@@ -6826,18 +6826,18 @@
         <v>COGS</v>
       </c>
       <c r="D285" t="str">
-        <v>Pineapple</v>
+        <v>Mango</v>
       </c>
       <c r="E285" t="str">
-        <v>สับปะรด 19 ลูก</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F285">
-        <v>950</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>14/06/2026</v>
+        <v>12/06/2026</v>
       </c>
       <c r="B286" t="str">
         <v>Jun26</v>
@@ -6846,18 +6846,18 @@
         <v>COGS</v>
       </c>
       <c r="D286" t="str">
-        <v>Watermelon</v>
+        <v>Apple</v>
       </c>
       <c r="E286" t="str">
-        <v>แตงโม 90 ลูก (7-6-2569: 45 ลูก, 12-6-2569: 45 ลูก)</v>
+        <v>แอปเปิ้ล 5 ลัง</v>
       </c>
       <c r="F286">
-        <v>7200</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>15/06/2026</v>
+        <v>12/06/2026</v>
       </c>
       <c r="B287" t="str">
         <v>Jun26</v>
@@ -6869,15 +6869,15 @@
         <v>Pineapple</v>
       </c>
       <c r="E287" t="str">
-        <v>สับปะรด 1 ลูก</v>
+        <v>สับปะรด 19 ลูก</v>
       </c>
       <c r="F287">
-        <v>50</v>
+        <v>950</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>15/06/2026</v>
+        <v>14/06/2026</v>
       </c>
       <c r="B288" t="str">
         <v>Jun26</v>
@@ -6886,13 +6886,13 @@
         <v>COGS</v>
       </c>
       <c r="D288" t="str">
-        <v>Other</v>
+        <v>Watermelon</v>
       </c>
       <c r="E288" t="str">
-        <v>Unknown</v>
+        <v>แตงโม 90 ลูก (7-6-2569: 45 ลูก, 12-6-2569: 45 ลูก)</v>
       </c>
       <c r="F288">
-        <v>18</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="289">
@@ -6909,10 +6909,10 @@
         <v>Pineapple</v>
       </c>
       <c r="E289" t="str">
-        <v>สับปะรด 12 ลูก</v>
+        <v>สับปะรด 1 ลูก</v>
       </c>
       <c r="F289">
-        <v>525</v>
+        <v>50</v>
       </c>
     </row>
     <row r="290">
@@ -6926,18 +6926,18 @@
         <v>COGS</v>
       </c>
       <c r="D290" t="str">
-        <v>Guava</v>
+        <v>Other</v>
       </c>
       <c r="E290" t="str">
-        <v>ฝรั่ง 1 ตะกร้า</v>
+        <v>Unknown</v>
       </c>
       <c r="F290">
-        <v>800</v>
+        <v>18</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>17/06/2026</v>
+        <v>15/06/2026</v>
       </c>
       <c r="B291" t="str">
         <v>Jun26</v>
@@ -6946,18 +6946,18 @@
         <v>COGS</v>
       </c>
       <c r="D291" t="str">
-        <v>Orange</v>
+        <v>Pineapple</v>
       </c>
       <c r="E291" t="str">
-        <v>รอบ 09/06/69</v>
+        <v>สับปะรด 12 ลูก</v>
       </c>
       <c r="F291">
-        <v>16445</v>
+        <v>525</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>18/06/2026</v>
+        <v>15/06/2026</v>
       </c>
       <c r="B292" t="str">
         <v>Jun26</v>
@@ -6966,18 +6966,18 @@
         <v>COGS</v>
       </c>
       <c r="D292" t="str">
-        <v>Mango</v>
+        <v>Guava</v>
       </c>
       <c r="E292" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F292">
-        <v>1300</v>
+        <v>800</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>18/06/2026</v>
+        <v>17/06/2026</v>
       </c>
       <c r="B293" t="str">
         <v>Jun26</v>
@@ -6986,13 +6986,13 @@
         <v>COGS</v>
       </c>
       <c r="D293" t="str">
-        <v>Coconut Water</v>
+        <v>Orange</v>
       </c>
       <c r="E293" t="str">
-        <v>เนื้อมะพร้าว 20 * 120 2400 น้ำมะพร้าว 20 *</v>
+        <v>ส้ม 23x22กก 506 กก. x30 = 15,180 + ค่าขนส่ง 23x55 = 1,265 (รอบ 09/06/69)</v>
       </c>
       <c r="F293">
-        <v>3400</v>
+        <v>16445</v>
       </c>
     </row>
     <row r="294">
@@ -7006,18 +7006,18 @@
         <v>COGS</v>
       </c>
       <c r="D294" t="str">
-        <v>Guava</v>
+        <v>Mango</v>
       </c>
       <c r="E294" t="str">
-        <v>ฝรั่ง 1 ตะกร้า</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F294">
-        <v>800</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>19/06/2026</v>
+        <v>18/06/2026</v>
       </c>
       <c r="B295" t="str">
         <v>Jun26</v>
@@ -7029,15 +7029,15 @@
         <v>Coconut Water</v>
       </c>
       <c r="E295" t="str">
-        <v>น้ำมะพร้าว40ลิตร ลิตรละ45บาท</v>
+        <v>เนื้อมะพร้าว 20 * 120 2400 น้ำมะพร้าว 20 *</v>
       </c>
       <c r="F295">
-        <v>5700</v>
+        <v>3400</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>19/06/2026</v>
+        <v>18/06/2026</v>
       </c>
       <c r="B296" t="str">
         <v>Jun26</v>
@@ -7046,18 +7046,18 @@
         <v>COGS</v>
       </c>
       <c r="D296" t="str">
-        <v>Packaging</v>
+        <v>Guava</v>
       </c>
       <c r="E296" t="str">
-        <v>น้ำยาล้างจาน 7 ถุง ผงซักฟอก 1</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F296">
-        <v>149</v>
+        <v>800</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>21/06/2026</v>
+        <v>19/06/2026</v>
       </c>
       <c r="B297" t="str">
         <v>Jun26</v>
@@ -7066,18 +7066,18 @@
         <v>COGS</v>
       </c>
       <c r="D297" t="str">
-        <v>Watermelon</v>
+        <v>Coconut Water</v>
       </c>
       <c r="E297" t="str">
-        <v>15-6-2569 แตงโม 50บาท 50 ลูก ยอด 2,500</v>
+        <v>น้ำมะพร้าว40ลิตร ลิตรละ45บาท</v>
       </c>
       <c r="F297">
-        <v>6500</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>22/06/2026</v>
+        <v>19/06/2026</v>
       </c>
       <c r="B298" t="str">
         <v>Jun26</v>
@@ -7086,18 +7086,18 @@
         <v>COGS</v>
       </c>
       <c r="D298" t="str">
-        <v>Pineapple</v>
+        <v>Packaging</v>
       </c>
       <c r="E298" t="str">
-        <v>สับปะรด 15 ลูก</v>
+        <v>น้ำยาล้างจาน 7 ถุง ผงซักฟอก 1</v>
       </c>
       <c r="F298">
-        <v>700</v>
+        <v>149</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>22/06/2026</v>
+        <v>21/06/2026</v>
       </c>
       <c r="B299" t="str">
         <v>Jun26</v>
@@ -7106,13 +7106,13 @@
         <v>COGS</v>
       </c>
       <c r="D299" t="str">
-        <v>Mango</v>
+        <v>Watermelon</v>
       </c>
       <c r="E299" t="str">
-        <v>มะม่วง 2 ลัง</v>
+        <v>15-6-2569 แตงโม 50บาท 50 ลูก ยอด 2,500</v>
       </c>
       <c r="F299">
-        <v>1632</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="300">
@@ -7126,13 +7126,13 @@
         <v>COGS</v>
       </c>
       <c r="D300" t="str">
-        <v>Transportation</v>
+        <v>Pineapple</v>
       </c>
       <c r="E300" t="str">
-        <v>Lalamove</v>
+        <v>สับปะรด 15 ลูก</v>
       </c>
       <c r="F300">
-        <v>2000</v>
+        <v>700</v>
       </c>
     </row>
     <row r="301">
@@ -7146,13 +7146,13 @@
         <v>COGS</v>
       </c>
       <c r="D301" t="str">
-        <v>Apple</v>
+        <v>Mango</v>
       </c>
       <c r="E301" t="str">
-        <v>แอพเปิ้ล 5 ลัง</v>
+        <v>มะม่วง 2 ลัง</v>
       </c>
       <c r="F301">
-        <v>1750</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="302">
@@ -7166,13 +7166,13 @@
         <v>COGS</v>
       </c>
       <c r="D302" t="str">
-        <v>Pineapple</v>
+        <v>Transportation</v>
       </c>
       <c r="E302" t="str">
-        <v>สับปะรด 15 ลูก</v>
+        <v>Lalamove</v>
       </c>
       <c r="F302">
-        <v>700</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="303">
@@ -7186,18 +7186,18 @@
         <v>COGS</v>
       </c>
       <c r="D303" t="str">
-        <v>Guava</v>
+        <v>Apple</v>
       </c>
       <c r="E303" t="str">
-        <v>ฝรั่ง 1 ลัง</v>
+        <v>แอพเปิ้ล 5 ลัง</v>
       </c>
       <c r="F303">
-        <v>700</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>24/06/2026</v>
+        <v>22/06/2026</v>
       </c>
       <c r="B304" t="str">
         <v>Jun26</v>
@@ -7206,18 +7206,18 @@
         <v>COGS</v>
       </c>
       <c r="D304" t="str">
-        <v>Milk/Conden</v>
+        <v>Pineapple</v>
       </c>
       <c r="E304" t="str">
-        <v>นมข้นจืด 2,221</v>
+        <v>สับปะรด 15 ลูก</v>
       </c>
       <c r="F304">
-        <v>5020</v>
+        <v>700</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>24/06/2026</v>
+        <v>22/06/2026</v>
       </c>
       <c r="B305" t="str">
         <v>Jun26</v>
@@ -7226,13 +7226,13 @@
         <v>COGS</v>
       </c>
       <c r="D305" t="str">
-        <v>Milk/Conden</v>
+        <v>Guava</v>
       </c>
       <c r="E305" t="str">
-        <v>นมข้นจืด1ลัง</v>
+        <v>ฝรั่ง 1 ลัง</v>
       </c>
       <c r="F305">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="306">
@@ -7249,15 +7249,15 @@
         <v>Milk/Conden</v>
       </c>
       <c r="E306" t="str">
-        <v>นมข้นหวาน1ลัง</v>
+        <v>นมข้นจืด 2,221</v>
       </c>
       <c r="F306">
-        <v>840</v>
+        <v>5020</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>25/06/2026</v>
+        <v>24/06/2026</v>
       </c>
       <c r="B307" t="str">
         <v>Jun26</v>
@@ -7266,18 +7266,18 @@
         <v>COGS</v>
       </c>
       <c r="D307" t="str">
-        <v>Watermelon</v>
+        <v>Milk/Conden</v>
       </c>
       <c r="E307" t="str">
-        <v>แตงโม 22-6-2569 30 ลูก 2400 25-6-2569 40</v>
+        <v>นมข้นจืด1ลัง</v>
       </c>
       <c r="F307">
-        <v>6000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>27/06/2026</v>
+        <v>24/06/2026</v>
       </c>
       <c r="B308" t="str">
         <v>Jun26</v>
@@ -7286,18 +7286,18 @@
         <v>COGS</v>
       </c>
       <c r="D308" t="str">
-        <v>Packaging</v>
+        <v>Milk/Conden</v>
       </c>
       <c r="E308" t="str">
-        <v>ถุงมือ20กล่อง 2589</v>
+        <v>นมข้นหวาน1ลัง</v>
       </c>
       <c r="F308">
-        <v>4598</v>
+        <v>840</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>27/06/2026</v>
+        <v>25/06/2026</v>
       </c>
       <c r="B309" t="str">
         <v>Jun26</v>
@@ -7306,13 +7306,13 @@
         <v>COGS</v>
       </c>
       <c r="D309" t="str">
-        <v>Packaging</v>
+        <v>Watermelon</v>
       </c>
       <c r="E309" t="str">
-        <v>หลอด 20 แพค</v>
+        <v>แตงโม 22-6-2569 30 ลูก 2400 25-6-2569 40</v>
       </c>
       <c r="F309">
-        <v>630</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="310">
@@ -7323,21 +7323,21 @@
         <v>Jun26</v>
       </c>
       <c r="C310" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D310" t="str">
-        <v>Other</v>
+        <v>Packaging</v>
       </c>
       <c r="E310" t="str">
-        <v>Unknown</v>
+        <v>ถุงมือ20กล่อง 2589</v>
       </c>
       <c r="F310">
-        <v>317</v>
+        <v>4598</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>29/06/2026</v>
+        <v>27/06/2026</v>
       </c>
       <c r="B311" t="str">
         <v>Jun26</v>
@@ -7349,30 +7349,30 @@
         <v>Packaging</v>
       </c>
       <c r="E311" t="str">
-        <v>ฝาแก้วภูเขาไฟ 1ลัง(954) 10แถว(987) 5แถว(561)</v>
+        <v>หลอด 20 แพค</v>
       </c>
       <c r="F311">
-        <v>2502</v>
+        <v>630</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>29/06/2026</v>
+        <v>27/06/2026</v>
       </c>
       <c r="B312" t="str">
         <v>Jun26</v>
       </c>
       <c r="C312" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D312" t="str">
-        <v>Packaging</v>
+        <v>Other</v>
       </c>
       <c r="E312" t="str">
-        <v>แก้ว2ลัง 1468*2 2,936</v>
+        <v>Unknown</v>
       </c>
       <c r="F312">
-        <v>3498</v>
+        <v>317</v>
       </c>
     </row>
     <row r="313">
@@ -7389,10 +7389,10 @@
         <v>Packaging</v>
       </c>
       <c r="E313" t="str">
-        <v>ฝา8แถว</v>
+        <v>ฝาแก้วภูเขาไฟ 1ลัง(954) 10แถว(987) 5แถว(561)</v>
       </c>
       <c r="F313">
-        <v>896</v>
+        <v>2502</v>
       </c>
     </row>
     <row r="314">
@@ -7403,16 +7403,16 @@
         <v>Jun26</v>
       </c>
       <c r="C314" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D314" t="str">
-        <v>Other</v>
+        <v>Packaging</v>
       </c>
       <c r="E314" t="str">
-        <v>สกัดเย็น1เครื่อง</v>
+        <v>แก้ว2ลัง 1468*2 2,936</v>
       </c>
       <c r="F314">
-        <v>1402</v>
+        <v>3498</v>
       </c>
     </row>
     <row r="315">
@@ -7426,13 +7426,13 @@
         <v>COGS</v>
       </c>
       <c r="D315" t="str">
-        <v>Guava</v>
+        <v>Packaging</v>
       </c>
       <c r="E315" t="str">
-        <v>ฝรั่ง 1 ตะกร้า</v>
+        <v>ฝา8แถว</v>
       </c>
       <c r="F315">
-        <v>800</v>
+        <v>896</v>
       </c>
     </row>
     <row r="316">
@@ -7443,16 +7443,16 @@
         <v>Jun26</v>
       </c>
       <c r="C316" t="str">
-        <v>EXCLUDED</v>
+        <v>OPEX</v>
       </c>
       <c r="D316" t="str">
-        <v>Pass-Through</v>
+        <v>Other</v>
       </c>
       <c r="E316" t="str">
-        <v>มังคุด 3 ตะกร้า (จ่ายแทน 1,932 แล้ว ฐนกร โอนคืน 29/06 13:56) - ไม่ใช่ต้นทุน SSJ [bank]</v>
+        <v>สกัดเย็น1เครื่อง</v>
       </c>
       <c r="F316">
-        <v>0</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="317">
@@ -7463,16 +7463,16 @@
         <v>Jun26</v>
       </c>
       <c r="C317" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D317" t="str">
-        <v>Other</v>
+        <v>Guava</v>
       </c>
       <c r="E317" t="str">
-        <v>Apple 2 box</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F317">
-        <v>700</v>
+        <v>800</v>
       </c>
     </row>
     <row r="318">
@@ -7483,16 +7483,16 @@
         <v>Jun26</v>
       </c>
       <c r="C318" t="str">
-        <v>COGS</v>
+        <v>EXCLUDED</v>
       </c>
       <c r="D318" t="str">
-        <v>Pineapple</v>
+        <v>Pass-Through</v>
       </c>
       <c r="E318" t="str">
-        <v>สับปะรด 15 ลูก</v>
+        <v>มังคุด 3 ตะกร้า (จ่ายแทน 1,932 แล้ว ฐนกร โอนคืน 29/06 13:56) - ไม่ใช่ต้นทุน SSJ [bank]</v>
       </c>
       <c r="F318">
-        <v>675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="319">
@@ -7503,76 +7503,76 @@
         <v>Jun26</v>
       </c>
       <c r="C319" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D319" t="str">
-        <v>Orange</v>
+        <v>Other</v>
       </c>
       <c r="E319" t="str">
-        <v>รอบ 18/06/69</v>
+        <v>Apple 2 box</v>
       </c>
       <c r="F319">
-        <v>17815</v>
+        <v>700</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>30/06/2026</v>
+        <v>29/06/2026</v>
       </c>
       <c r="B320" t="str">
         <v>Jun26</v>
       </c>
       <c r="C320" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D320" t="str">
-        <v>Salary</v>
+        <v>Pineapple</v>
       </c>
       <c r="E320" t="str">
-        <v>ค่าแรง 4 คน คนคนละ 12000 และ รายวัน 1</v>
+        <v>สับปะรด 15 ลูก</v>
       </c>
       <c r="F320">
-        <v>48400</v>
+        <v>675</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>24/07/2026</v>
+        <v>29/06/2026</v>
       </c>
       <c r="B321" t="str">
-        <v>Jul26</v>
+        <v>Jun26</v>
       </c>
       <c r="C321" t="str">
         <v>COGS</v>
       </c>
       <c r="D321" t="str">
-        <v>Stock</v>
+        <v>Orange</v>
       </c>
       <c r="E321" t="str">
-        <v>ฝา 1 ลัง 509 นมข้นหวาน 1 ลัง 785 นมข้นจืด 2 ลัง 1342 บาท (LINE_ALBUM_Cost July_260802_1.jpg)</v>
+        <v>ส้ม 25x22กก 550 กก. x30 = 16,500 + ค่าขนส่ง 25x55 = 1,375 (รอบ 18/06/69)</v>
       </c>
       <c r="F321">
-        <v>2636</v>
+        <v>17815</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>24/07/2026</v>
+        <v>30/06/2026</v>
       </c>
       <c r="B322" t="str">
-        <v>Jul26</v>
+        <v>Jun26</v>
       </c>
       <c r="C322" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D322" t="str">
-        <v>Stock</v>
+        <v>Salary</v>
       </c>
       <c r="E322" t="str">
-        <v>ฝา 1 ลัง 502 บาท นมข้นหวาน 3 ลัง 2582 บาท (LINE_ALBUM_Cost July_260802_2.jpg)</v>
+        <v>ค่าแรง 4 คน คนคนละ 12000 และ รายวัน 1</v>
       </c>
       <c r="F322">
-        <v>3084</v>
+        <v>48400</v>
       </c>
     </row>
     <row r="323">
@@ -7589,10 +7589,10 @@
         <v>Stock</v>
       </c>
       <c r="E323" t="str">
-        <v>ฝา 1 ลัง 474 นมข้นจืด 1 ลัง 751 (LINE_ALBUM_Cost July_260802_3.jpg)</v>
+        <v>ฝา 1 ลัง 509 นมข้นหวาน 1 ลัง 785 นมข้นจืด 2 ลัง 1342 บาท (LINE_ALBUM_Cost July_260802_1.jpg)</v>
       </c>
       <c r="F323">
-        <v>1225</v>
+        <v>2636</v>
       </c>
     </row>
     <row r="324">
@@ -7609,10 +7609,10 @@
         <v>Stock</v>
       </c>
       <c r="E324" t="str">
-        <v>ฝา 1 ลัง (LINE_ALBUM_Cost July_260802_4.jpg)</v>
+        <v>ฝา 1 ลัง 502 บาท นมข้นหวาน 3 ลัง 2582 บาท (LINE_ALBUM_Cost July_260802_2.jpg)</v>
       </c>
       <c r="F324">
-        <v>472</v>
+        <v>3084</v>
       </c>
     </row>
     <row r="325">
@@ -7623,21 +7623,21 @@
         <v>Jul26</v>
       </c>
       <c r="C325" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D325" t="str">
-        <v>Other</v>
+        <v>Stock</v>
       </c>
       <c r="E325" t="str">
-        <v>Lalamove (LINE_ALBUM_Cost July_260802_5.jpg)</v>
+        <v>ฝา 1 ลัง 474 นมข้นจืด 1 ลัง 751 (LINE_ALBUM_Cost July_260802_3.jpg)</v>
       </c>
       <c r="F325">
-        <v>2000</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>26/07/2026</v>
+        <v>24/07/2026</v>
       </c>
       <c r="B326" t="str">
         <v>Jul26</v>
@@ -7646,30 +7646,30 @@
         <v>COGS</v>
       </c>
       <c r="D326" t="str">
-        <v>Apple</v>
+        <v>Stock</v>
       </c>
       <c r="E326" t="str">
-        <v>Apple 5 box (LINE_ALBUM_Cost July_260802_6.jpg)</v>
+        <v>ฝา 1 ลัง (LINE_ALBUM_Cost July_260802_4.jpg)</v>
       </c>
       <c r="F326">
-        <v>2000</v>
+        <v>472</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>26/07/2026</v>
+        <v>24/07/2026</v>
       </c>
       <c r="B327" t="str">
         <v>Jul26</v>
       </c>
       <c r="C327" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D327" t="str">
-        <v>Guava</v>
+        <v>Other</v>
       </c>
       <c r="E327" t="str">
-        <v>ฝรั่ง 2 ตะกร้า (LINE_ALBUM_Cost July_260802_7.jpg)</v>
+        <v>Lalamove (LINE_ALBUM_Cost July_260802_5.jpg)</v>
       </c>
       <c r="F327">
         <v>2000</v>
@@ -7686,18 +7686,18 @@
         <v>COGS</v>
       </c>
       <c r="D328" t="str">
-        <v>Mango</v>
+        <v>Apple</v>
       </c>
       <c r="E328" t="str">
-        <v>มะม่วง 3 ลัง 3900 (LINE_ALBUM_Cost July_260802_8.jpg)</v>
+        <v>Apple 5 box (LINE_ALBUM_Cost July_260802_6.jpg)</v>
       </c>
       <c r="F328">
-        <v>3900</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>27/07/2026</v>
+        <v>26/07/2026</v>
       </c>
       <c r="B329" t="str">
         <v>Jul26</v>
@@ -7706,18 +7706,18 @@
         <v>COGS</v>
       </c>
       <c r="D329" t="str">
-        <v>Coconut</v>
+        <v>Guava</v>
       </c>
       <c r="E329" t="str">
-        <v>น้ำมะพร้าว 30ลิตร 1350 เนื้อ 50kg 5000 น้ำมะพร้าวขวด 920 ค่าส่ง 350 (LINE_ALBUM_Cost July_260802_14.jpg, audit fix - was dated 26/07 citing wrong image, missing ฿920 bottles line)</v>
+        <v>ฝรั่ง 2 ตะกร้า (LINE_ALBUM_Cost July_260802_7.jpg)</v>
       </c>
       <c r="F329">
-        <v>7620</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>27/07/2026</v>
+        <v>26/07/2026</v>
       </c>
       <c r="B330" t="str">
         <v>Jul26</v>
@@ -7726,13 +7726,13 @@
         <v>COGS</v>
       </c>
       <c r="D330" t="str">
-        <v>Apple</v>
+        <v>Mango</v>
       </c>
       <c r="E330" t="str">
-        <v>Apple 4 box (LINE_ALBUM_Cost July_260802_10.jpg)</v>
+        <v>มะม่วง 3 ลัง 3900 (LINE_ALBUM_Cost July_260802_8.jpg)</v>
       </c>
       <c r="F330">
-        <v>1600</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="331">
@@ -7746,13 +7746,13 @@
         <v>COGS</v>
       </c>
       <c r="D331" t="str">
-        <v>Guava</v>
+        <v>Coconut</v>
       </c>
       <c r="E331" t="str">
-        <v>ฝรั่ง 2 ตะกร้า (LINE_ALBUM_Cost July_260802_11.jpg)</v>
+        <v>น้ำมะพร้าว 30ลิตร 1350 เนื้อ 50kg 5000 น้ำมะพร้าวขวด 920 ค่าส่ง 350 (LINE_ALBUM_Cost July_260802_14.jpg, audit fix - was dated 26/07 citing wrong image, missing ฿920 bottles line)</v>
       </c>
       <c r="F331">
-        <v>2000</v>
+        <v>7620</v>
       </c>
     </row>
     <row r="332">
@@ -7766,13 +7766,13 @@
         <v>COGS</v>
       </c>
       <c r="D332" t="str">
-        <v>Mango</v>
+        <v>Apple</v>
       </c>
       <c r="E332" t="str">
-        <v>มะม่วง 2 ลัง (LINE_ALBUM_Cost July_260802_12.jpg)</v>
+        <v>Apple 4 box (LINE_ALBUM_Cost July_260802_10.jpg)</v>
       </c>
       <c r="F332">
-        <v>2600</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="333">
@@ -7786,38 +7786,38 @@
         <v>COGS</v>
       </c>
       <c r="D333" t="str">
-        <v>Watermelon</v>
+        <v>Guava</v>
       </c>
       <c r="E333" t="str">
-        <v>แตงโม 40 ลูก (LINE_ALBUM_Cost July_260802_13.jpg)</v>
+        <v>ฝรั่ง 2 ตะกร้า (LINE_ALBUM_Cost July_260802_11.jpg)</v>
       </c>
       <c r="F333">
-        <v>3200</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>28/07/2026</v>
+        <v>27/07/2026</v>
       </c>
       <c r="B334" t="str">
         <v>Jul26</v>
       </c>
       <c r="C334" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D334" t="str">
-        <v>Other</v>
+        <v>Mango</v>
       </c>
       <c r="E334" t="str">
-        <v>Lalamove (LINE_ALBUM_Cost July_260802_14.jpg)</v>
+        <v>มะม่วง 2 ลัง (LINE_ALBUM_Cost July_260802_12.jpg)</v>
       </c>
       <c r="F334">
-        <v>1000</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>28/07/2026</v>
+        <v>27/07/2026</v>
       </c>
       <c r="B335" t="str">
         <v>Jul26</v>
@@ -7826,13 +7826,13 @@
         <v>COGS</v>
       </c>
       <c r="D335" t="str">
-        <v>Guava</v>
+        <v>Watermelon</v>
       </c>
       <c r="E335" t="str">
-        <v>ฝรั่ง 2 ลัง (LINE_ALBUM_Cost July_260802_15.jpg)</v>
+        <v>แตงโม 40 ลูก (LINE_ALBUM_Cost July_260802_13.jpg)</v>
       </c>
       <c r="F335">
-        <v>2000</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="336">
@@ -7843,16 +7843,16 @@
         <v>Jul26</v>
       </c>
       <c r="C336" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D336" t="str">
-        <v>Apple</v>
+        <v>Other</v>
       </c>
       <c r="E336" t="str">
-        <v>แอปเปิ้ล 5 ลัง (LINE_ALBUM_Cost July_260802_16.jpg, audit fix - was recorded as 4 ลัง/฿1600)</v>
+        <v>Lalamove (LINE_ALBUM_Cost July_260802_14.jpg)</v>
       </c>
       <c r="F336">
-        <v>2150</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="337">
@@ -7866,13 +7866,13 @@
         <v>COGS</v>
       </c>
       <c r="D337" t="str">
-        <v>Mango</v>
+        <v>Guava</v>
       </c>
       <c r="E337" t="str">
-        <v>มะม่วง 2 ลัง (LINE_ALBUM_Cost July_260802_17.jpg)</v>
+        <v>ฝรั่ง 2 ลัง (LINE_ALBUM_Cost July_260802_15.jpg)</v>
       </c>
       <c r="F337">
-        <v>2600</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="338">
@@ -7886,38 +7886,38 @@
         <v>COGS</v>
       </c>
       <c r="D338" t="str">
-        <v>Watermelon</v>
+        <v>Apple</v>
       </c>
       <c r="E338" t="str">
-        <v>แตงโม 40 ลูก (LINE_ALBUM_Cost July_260802_18.jpg)</v>
+        <v>แอปเปิ้ล 5 ลัง (LINE_ALBUM_Cost July_260802_16.jpg, audit fix - was recorded as 4 ลัง/฿1600)</v>
       </c>
       <c r="F338">
-        <v>3200</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>29/07/2026</v>
+        <v>28/07/2026</v>
       </c>
       <c r="B339" t="str">
         <v>Jul26</v>
       </c>
       <c r="C339" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D339" t="str">
-        <v>Other</v>
+        <v>Mango</v>
       </c>
       <c r="E339" t="str">
-        <v>ค่าขนส่ง (LINE_ALBUM_Cost July_260802_19.jpg)</v>
+        <v>มะม่วง 2 ลัง (LINE_ALBUM_Cost July_260802_17.jpg)</v>
       </c>
       <c r="F339">
-        <v>2000</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>29/07/2026</v>
+        <v>28/07/2026</v>
       </c>
       <c r="B340" t="str">
         <v>Jul26</v>
@@ -7926,18 +7926,18 @@
         <v>COGS</v>
       </c>
       <c r="D340" t="str">
-        <v>Orange</v>
+        <v>Watermelon</v>
       </c>
       <c r="E340" t="str">
-        <v>ส้ม 31x22กก 682กกx30 20,460บาท ค่าขนส่ง 31ตกx 50 1550 (LINE_ALBUM_Cost July_260802_20.jpg)</v>
+        <v>แตงโม 40 ลูก (LINE_ALBUM_Cost July_260802_18.jpg)</v>
       </c>
       <c r="F340">
-        <v>22010</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>30/07/2026</v>
+        <v>29/07/2026</v>
       </c>
       <c r="B341" t="str">
         <v>Jul26</v>
@@ -7949,70 +7949,70 @@
         <v>Other</v>
       </c>
       <c r="E341" t="str">
-        <v>ตะแกรงคว่ำจาน 6อัน ป้ายไฟ3อัน (LINE_ALBUM_Cost July_260802_21.jpg)</v>
+        <v>ค่าขนส่ง (LINE_ALBUM_Cost July_260802_19.jpg)</v>
       </c>
       <c r="F341">
-        <v>1790</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>30/07/2026</v>
+        <v>29/07/2026</v>
       </c>
       <c r="B342" t="str">
         <v>Jul26</v>
       </c>
       <c r="C342" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D342" t="str">
-        <v>Other</v>
+        <v>Orange</v>
       </c>
       <c r="E342" t="str">
-        <v>ถุงขยะ 5*5แพค (LINE_ALBUM_Cost July_260802_22.jpg)</v>
+        <v>ส้ม 31x22กก 682กกx30 20,460บาท ค่าขนส่ง 31ตกx 50 1550 (LINE_ALBUM_Cost July_260802_20.jpg)</v>
       </c>
       <c r="F342">
-        <v>1101</v>
+        <v>22010</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>31/07/2026</v>
+        <v>30/07/2026</v>
       </c>
       <c r="B343" t="str">
         <v>Jul26</v>
       </c>
       <c r="C343" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D343" t="str">
-        <v>Apple</v>
+        <v>Other</v>
       </c>
       <c r="E343" t="str">
-        <v>แอปเปิ้ล 4 ลัง (LINE_ALBUM_Cost July_260802_23.jpg)</v>
+        <v>ตะแกรงคว่ำจาน 6อัน ป้ายไฟ3อัน (LINE_ALBUM_Cost July_260802_21.jpg)</v>
       </c>
       <c r="F343">
-        <v>1200</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>31/07/2026</v>
+        <v>30/07/2026</v>
       </c>
       <c r="B344" t="str">
         <v>Jul26</v>
       </c>
       <c r="C344" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D344" t="str">
-        <v>Mango</v>
+        <v>Other</v>
       </c>
       <c r="E344" t="str">
-        <v>มะม่วง 4 ลัง (LINE_ALBUM_Cost July_260802_24.jpg)</v>
+        <v>ถุงขยะ 5*5แพค (LINE_ALBUM_Cost July_260802_22.jpg)</v>
       </c>
       <c r="F344">
-        <v>4680</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="345">
@@ -8023,16 +8023,16 @@
         <v>Jul26</v>
       </c>
       <c r="C345" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D345" t="str">
-        <v>Other</v>
+        <v>Apple</v>
       </c>
       <c r="E345" t="str">
-        <v>ค่าขนส่ง (LINE_ALBUM_Cost July_260802_25.jpg)</v>
+        <v>แอปเปิ้ล 4 ลัง (LINE_ALBUM_Cost July_260802_23.jpg)</v>
       </c>
       <c r="F345">
-        <v>2000</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="346">
@@ -8046,13 +8046,13 @@
         <v>COGS</v>
       </c>
       <c r="D346" t="str">
-        <v>Guava</v>
+        <v>Mango</v>
       </c>
       <c r="E346" t="str">
-        <v>ฝรั่ง 3 ลัง (LINE_ALBUM_Cost July_260802_26.jpg)</v>
+        <v>มะม่วง 4 ลัง (LINE_ALBUM_Cost July_260802_24.jpg)</v>
       </c>
       <c r="F346">
-        <v>3600</v>
+        <v>4680</v>
       </c>
     </row>
     <row r="347">
@@ -8063,16 +8063,16 @@
         <v>Jul26</v>
       </c>
       <c r="C347" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D347" t="str">
         <v>Other</v>
       </c>
       <c r="E347" t="str">
-        <v>ทุเรียน 20.6 กิโลกรัม (LINE_ALBUM_Cost July_260802_27.jpg)</v>
+        <v>ค่าขนส่ง (LINE_ALBUM_Cost July_260802_25.jpg)</v>
       </c>
       <c r="F347">
-        <v>2255</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="348">
@@ -8083,21 +8083,21 @@
         <v>Jul26</v>
       </c>
       <c r="C348" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D348" t="str">
-        <v>Other</v>
+        <v>Guava</v>
       </c>
       <c r="E348" t="str">
-        <v>ตะกร้าแต่งร้าน 3 (LINE_ALBUM_Cost July_260802_28.jpg)</v>
+        <v>ฝรั่ง 3 ลัง (LINE_ALBUM_Cost July_260802_26.jpg)</v>
       </c>
       <c r="F348">
-        <v>558</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>02/07/2026</v>
+        <v>31/07/2026</v>
       </c>
       <c r="B349" t="str">
         <v>Jul26</v>
@@ -8106,38 +8106,38 @@
         <v>COGS</v>
       </c>
       <c r="D349" t="str">
-        <v>Orange</v>
+        <v>Other</v>
       </c>
       <c r="E349" t="str">
-        <v>ค่าส่งส้มเดือน 6 (LINE_ALBUM_Cost July_260802_29.jpg)</v>
+        <v>ทุเรียน 20.6 กิโลกรัม (LINE_ALBUM_Cost July_260802_27.jpg)</v>
       </c>
       <c r="F349">
-        <v>1598</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>03/07/2026</v>
+        <v>31/07/2026</v>
       </c>
       <c r="B350" t="str">
         <v>Jul26</v>
       </c>
       <c r="C350" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D350" t="str">
-        <v>Pineapple</v>
+        <v>Other</v>
       </c>
       <c r="E350" t="str">
-        <v>1 สับปะรด 15 ลูก 750 2 สับปะรด 15 ลูก 729 (LINE_ALBUM_Cost July_260802_30.jpg)</v>
+        <v>ตะกร้าแต่งร้าน 3 (LINE_ALBUM_Cost July_260802_28.jpg)</v>
       </c>
       <c r="F350">
-        <v>1479</v>
+        <v>558</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>03/07/2026</v>
+        <v>02/07/2026</v>
       </c>
       <c r="B351" t="str">
         <v>Jul26</v>
@@ -8146,13 +8146,13 @@
         <v>COGS</v>
       </c>
       <c r="D351" t="str">
-        <v>Apple</v>
+        <v>Orange</v>
       </c>
       <c r="E351" t="str">
-        <v>แอปเปิ้ล 3 ลัง (LINE_ALBUM_Cost July_260802_31.jpg)</v>
+        <v>ค่าส่งส้มเดือน 6 (LINE_ALBUM_Cost July_260802_29.jpg)</v>
       </c>
       <c r="F351">
-        <v>1140</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="352">
@@ -8166,13 +8166,13 @@
         <v>COGS</v>
       </c>
       <c r="D352" t="str">
-        <v>Mango</v>
+        <v>Pineapple</v>
       </c>
       <c r="E352" t="str">
-        <v>มะม่วง 1 ลัง (LINE_ALBUM_Cost July_260802_32.jpg)</v>
+        <v>1 สับปะรด 15 ลูก 750 2 สับปะรด 15 ลูก 729 (LINE_ALBUM_Cost July_260802_30.jpg)</v>
       </c>
       <c r="F352">
-        <v>1040</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="353">
@@ -8186,13 +8186,13 @@
         <v>COGS</v>
       </c>
       <c r="D353" t="str">
-        <v>Guava</v>
+        <v>Apple</v>
       </c>
       <c r="E353" t="str">
-        <v>ฝรั่ง 1 ลัง (LINE_ALBUM_Cost July_260802_33.jpg)</v>
+        <v>แอปเปิ้ล 3 ลัง (LINE_ALBUM_Cost July_260802_31.jpg)</v>
       </c>
       <c r="F353">
-        <v>900</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="354">
@@ -8203,56 +8203,56 @@
         <v>Jul26</v>
       </c>
       <c r="C354" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D354" t="str">
-        <v>Other</v>
+        <v>Mango</v>
       </c>
       <c r="E354" t="str">
-        <v>ค่าส่ง (LINE_ALBUM_Cost July_260802_34.jpg)</v>
+        <v>มะม่วง 1 ลัง (LINE_ALBUM_Cost July_260802_32.jpg)</v>
       </c>
       <c r="F354">
-        <v>2000</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>06/07/2026</v>
+        <v>03/07/2026</v>
       </c>
       <c r="B355" t="str">
         <v>Jul26</v>
       </c>
       <c r="C355" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D355" t="str">
-        <v>Rental</v>
+        <v>Guava</v>
       </c>
       <c r="E355" t="str">
-        <v>ค่าเช่า stock เดือน june (1/3 split B1) (LINE_ALBUM_Cost July_260802_35.jpg)</v>
+        <v>ฝรั่ง 1 ลัง (LINE_ALBUM_Cost July_260802_33.jpg)</v>
       </c>
       <c r="F355">
-        <v>4000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>06/07/2026</v>
+        <v>03/07/2026</v>
       </c>
       <c r="B356" t="str">
         <v>Jul26</v>
       </c>
       <c r="C356" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D356" t="str">
-        <v>Pineapple</v>
+        <v>Other</v>
       </c>
       <c r="E356" t="str">
-        <v>สับปะรด 20 ลูก (LINE_ALBUM_Cost July_260802_36.jpg)</v>
+        <v>ค่าส่ง (LINE_ALBUM_Cost July_260802_34.jpg)</v>
       </c>
       <c r="F356">
-        <v>783</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="357">
@@ -8263,16 +8263,16 @@
         <v>Jul26</v>
       </c>
       <c r="C357" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D357" t="str">
-        <v>Mango</v>
+        <v>Rental</v>
       </c>
       <c r="E357" t="str">
-        <v>มะม่วง 2 ลัง (LINE_ALBUM_Cost July_260802_37.jpg)</v>
+        <v>ค่าเช่า stock เดือน june (1/3 split B1) (LINE_ALBUM_Cost July_260802_35.jpg)</v>
       </c>
       <c r="F357">
-        <v>2340</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="358">
@@ -8286,13 +8286,13 @@
         <v>COGS</v>
       </c>
       <c r="D358" t="str">
-        <v>Guava</v>
+        <v>Pineapple</v>
       </c>
       <c r="E358" t="str">
-        <v>ฝรั่ง 1 ตะกร้า (LINE_ALBUM_Cost July_260802_38.jpg)</v>
+        <v>สับปะรด 20 ลูก (LINE_ALBUM_Cost July_260802_36.jpg)</v>
       </c>
       <c r="F358">
-        <v>900</v>
+        <v>783</v>
       </c>
     </row>
     <row r="359">
@@ -8306,18 +8306,18 @@
         <v>COGS</v>
       </c>
       <c r="D359" t="str">
-        <v>Apple</v>
+        <v>Mango</v>
       </c>
       <c r="E359" t="str">
-        <v>แอปเปิ้ล 3 ลัง (LINE_ALBUM_Cost July_260802_39.jpg)</v>
+        <v>มะม่วง 2 ลัง (LINE_ALBUM_Cost July_260802_37.jpg)</v>
       </c>
       <c r="F359">
-        <v>900</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>08/07/2026</v>
+        <v>06/07/2026</v>
       </c>
       <c r="B360" t="str">
         <v>Jul26</v>
@@ -8326,38 +8326,38 @@
         <v>COGS</v>
       </c>
       <c r="D360" t="str">
-        <v>Watermelon</v>
+        <v>Guava</v>
       </c>
       <c r="E360" t="str">
-        <v>แตงโม 3-7-69 36 ลูก ลูกละ 80 บาท 6-7-69 50 ลูก ลูกละ 80 บาท (LINE_ALBUM_Cost July_260802_40.jpg)</v>
+        <v>ฝรั่ง 1 ตะกร้า (LINE_ALBUM_Cost July_260802_38.jpg)</v>
       </c>
       <c r="F360">
-        <v>6880</v>
+        <v>900</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>08/07/2026</v>
+        <v>06/07/2026</v>
       </c>
       <c r="B361" t="str">
         <v>Jul26</v>
       </c>
       <c r="C361" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D361" t="str">
-        <v>Other</v>
+        <v>Apple</v>
       </c>
       <c r="E361" t="str">
-        <v>เต้น (tent) (LINE_ALBUM_Cost July_260802_41.jpg)</v>
+        <v>แอปเปิ้ล 3 ลัง (LINE_ALBUM_Cost July_260802_39.jpg)</v>
       </c>
       <c r="F361">
-        <v>1342</v>
+        <v>900</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>09/07/2026</v>
+        <v>08/07/2026</v>
       </c>
       <c r="B362" t="str">
         <v>Jul26</v>
@@ -8366,38 +8366,38 @@
         <v>COGS</v>
       </c>
       <c r="D362" t="str">
-        <v>Coconut</v>
+        <v>Watermelon</v>
       </c>
       <c r="E362" t="str">
-        <v>น้ำ 25ลิตร ลิตรละ45บาท เนื้อคว้าน 50kg.กิโลละ 100บาท ค่าส่ง350บาท (LINE_ALBUM_Cost July_260802_42.jpg)</v>
+        <v>แตงโม 3-7-69 36 ลูก ลูกละ 80 บาท 6-7-69 50 ลูก ลูกละ 80 บาท (LINE_ALBUM_Cost July_260802_40.jpg)</v>
       </c>
       <c r="F362">
-        <v>6470</v>
+        <v>6880</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>10/07/2026</v>
+        <v>08/07/2026</v>
       </c>
       <c r="B363" t="str">
         <v>Jul26</v>
       </c>
       <c r="C363" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D363" t="str">
-        <v>Guava</v>
+        <v>Other</v>
       </c>
       <c r="E363" t="str">
-        <v>ฝรั่ง 1 ลัง (LINE_ALBUM_Cost July_260802_43.jpg)</v>
+        <v>เต้น (tent) (LINE_ALBUM_Cost July_260802_41.jpg)</v>
       </c>
       <c r="F363">
-        <v>900</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>10/07/2026</v>
+        <v>09/07/2026</v>
       </c>
       <c r="B364" t="str">
         <v>Jul26</v>
@@ -8406,18 +8406,18 @@
         <v>COGS</v>
       </c>
       <c r="D364" t="str">
-        <v>Apple</v>
+        <v>Coconut</v>
       </c>
       <c r="E364" t="str">
-        <v>Apple 5 box (LINE_ALBUM_Cost July_260802_44.jpg)</v>
+        <v>น้ำ 25ลิตร ลิตรละ45บาท เนื้อคว้าน 50kg.กิโลละ 100บาท ค่าส่ง350บาท (LINE_ALBUM_Cost July_260802_42.jpg)</v>
       </c>
       <c r="F364">
-        <v>1500</v>
+        <v>6470</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>11/07/2026</v>
+        <v>10/07/2026</v>
       </c>
       <c r="B365" t="str">
         <v>Jul26</v>
@@ -8429,7 +8429,7 @@
         <v>Guava</v>
       </c>
       <c r="E365" t="str">
-        <v>ฝรั่ง 1 ตะกร้า (LINE_ALBUM_Cost July_260802_45.jpg)</v>
+        <v>ฝรั่ง 1 ลัง (LINE_ALBUM_Cost July_260802_43.jpg)</v>
       </c>
       <c r="F365">
         <v>900</v>
@@ -8437,7 +8437,7 @@
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>11/07/2026</v>
+        <v>10/07/2026</v>
       </c>
       <c r="B366" t="str">
         <v>Jul26</v>
@@ -8446,13 +8446,13 @@
         <v>COGS</v>
       </c>
       <c r="D366" t="str">
-        <v>Mango</v>
+        <v>Apple</v>
       </c>
       <c r="E366" t="str">
-        <v>มะม่วง 3 ลัง (LINE_ALBUM_Cost July_260802_46.jpg)</v>
+        <v>Apple 5 box (LINE_ALBUM_Cost July_260802_44.jpg)</v>
       </c>
       <c r="F366">
-        <v>4300</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="367">
@@ -8466,10 +8466,10 @@
         <v>COGS</v>
       </c>
       <c r="D367" t="str">
-        <v>Apple</v>
+        <v>Guava</v>
       </c>
       <c r="E367" t="str">
-        <v>แอปเปิ้ล 3 ลัง (LINE_ALBUM_Cost July_260802_47.jpg)</v>
+        <v>ฝรั่ง 1 ตะกร้า (LINE_ALBUM_Cost July_260802_45.jpg)</v>
       </c>
       <c r="F367">
         <v>900</v>
@@ -8477,27 +8477,27 @@
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>13/07/2026</v>
+        <v>11/07/2026</v>
       </c>
       <c r="B368" t="str">
         <v>Jul26</v>
       </c>
       <c r="C368" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D368" t="str">
-        <v>Other</v>
+        <v>Mango</v>
       </c>
       <c r="E368" t="str">
-        <v>ค่าขนส่ง (LINE_ALBUM_Cost July_260802_48.jpg)</v>
+        <v>มะม่วง 3 ลัง (LINE_ALBUM_Cost July_260802_46.jpg)</v>
       </c>
       <c r="F368">
-        <v>344</v>
+        <v>4300</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>13/07/2026</v>
+        <v>11/07/2026</v>
       </c>
       <c r="B369" t="str">
         <v>Jul26</v>
@@ -8506,13 +8506,13 @@
         <v>COGS</v>
       </c>
       <c r="D369" t="str">
-        <v>Packaging</v>
+        <v>Apple</v>
       </c>
       <c r="E369" t="str">
-        <v>ทิชชู4(636) หลอด20 (671) ถุงเล็ก3(605) ถุงใหญ่2(943) (LINE_ALBUM_Cost July_260802_49.jpg)</v>
+        <v>แอปเปิ้ล 3 ลัง (LINE_ALBUM_Cost July_260802_47.jpg)</v>
       </c>
       <c r="F369">
-        <v>2855</v>
+        <v>900</v>
       </c>
     </row>
     <row r="370">
@@ -8523,21 +8523,21 @@
         <v>Jul26</v>
       </c>
       <c r="C370" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D370" t="str">
-        <v>Packaging</v>
+        <v>Other</v>
       </c>
       <c r="E370" t="str">
-        <v>แก้ว98 4ลัง 7656-635 7,021 ฝา635 (LINE_ALBUM_Cost July_260802_50.jpg)</v>
+        <v>ค่าขนส่ง (LINE_ALBUM_Cost July_260802_48.jpg)</v>
       </c>
       <c r="F370">
-        <v>7656</v>
+        <v>344</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>14/07/2026</v>
+        <v>13/07/2026</v>
       </c>
       <c r="B371" t="str">
         <v>Jul26</v>
@@ -8546,18 +8546,18 @@
         <v>COGS</v>
       </c>
       <c r="D371" t="str">
-        <v>Pineapple</v>
+        <v>Packaging</v>
       </c>
       <c r="E371" t="str">
-        <v>11/7/69 10 ลูก 620 14/7/69 25 ลูก 1269 (LINE_ALBUM_Cost July_260802_51.jpg)</v>
+        <v>ทิชชู4(636) หลอด20 (671) ถุงเล็ก3(605) ถุงใหญ่2(943) (LINE_ALBUM_Cost July_260802_49.jpg)</v>
       </c>
       <c r="F371">
-        <v>1889</v>
+        <v>2855</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>14/07/2026</v>
+        <v>13/07/2026</v>
       </c>
       <c r="B372" t="str">
         <v>Jul26</v>
@@ -8566,18 +8566,18 @@
         <v>COGS</v>
       </c>
       <c r="D372" t="str">
-        <v>Apple</v>
+        <v>Packaging</v>
       </c>
       <c r="E372" t="str">
-        <v>Apple 3 ลัง (LINE_ALBUM_Cost July_260802_52.jpg)</v>
+        <v>แก้ว98 4ลัง 7656-635 7,021 ฝา635 (LINE_ALBUM_Cost July_260802_50.jpg)</v>
       </c>
       <c r="F372">
-        <v>1200</v>
+        <v>7656</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>15/07/2026</v>
+        <v>14/07/2026</v>
       </c>
       <c r="B373" t="str">
         <v>Jul26</v>
@@ -8586,18 +8586,18 @@
         <v>COGS</v>
       </c>
       <c r="D373" t="str">
-        <v>Guava</v>
+        <v>Pineapple</v>
       </c>
       <c r="E373" t="str">
-        <v>ฝรั่ง 2 ตะกร้า ตะกร้าละ 20 โล (LINE_ALBUM_Cost July_260802_53.jpg)</v>
+        <v>11/7/69 10 ลูก 620 14/7/69 25 ลูก 1269 (LINE_ALBUM_Cost July_260802_51.jpg)</v>
       </c>
       <c r="F373">
-        <v>2000</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>16/07/2026</v>
+        <v>14/07/2026</v>
       </c>
       <c r="B374" t="str">
         <v>Jul26</v>
@@ -8606,18 +8606,18 @@
         <v>COGS</v>
       </c>
       <c r="D374" t="str">
-        <v>Orange</v>
+        <v>Apple</v>
       </c>
       <c r="E374" t="str">
-        <v>รอบ 01/07/69 ส้ม 28x22กก 616กกx30 18,480บาท ค่าขนส่ง 28ตกx 55 1540 (LINE_ALBUM_Cost July_260802_54.jpg)</v>
+        <v>Apple 3 ลัง (LINE_ALBUM_Cost July_260802_52.jpg)</v>
       </c>
       <c r="F374">
-        <v>20020</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>17/07/2026</v>
+        <v>15/07/2026</v>
       </c>
       <c r="B375" t="str">
         <v>Jul26</v>
@@ -8626,18 +8626,18 @@
         <v>COGS</v>
       </c>
       <c r="D375" t="str">
-        <v>Orange</v>
+        <v>Guava</v>
       </c>
       <c r="E375" t="str">
-        <v>ส้ม 125 โล 3450 ค่าส่ง 300 (LINE_ALBUM_Cost July_260802_55.jpg)</v>
+        <v>ฝรั่ง 2 ตะกร้า ตะกร้าละ 20 โล (LINE_ALBUM_Cost July_260802_53.jpg)</v>
       </c>
       <c r="F375">
-        <v>3750</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>17/07/2026</v>
+        <v>16/07/2026</v>
       </c>
       <c r="B376" t="str">
         <v>Jul26</v>
@@ -8646,13 +8646,13 @@
         <v>COGS</v>
       </c>
       <c r="D376" t="str">
-        <v>Pineapple</v>
+        <v>Orange</v>
       </c>
       <c r="E376" t="str">
-        <v>สับปะรด 25 ลูก (LINE_ALBUM_Cost July_260802_56.jpg)</v>
+        <v>รอบ 01/07/69 ส้ม 28x22กก 616กกx30 18,480บาท ค่าขนส่ง 28ตกx 55 1540 (LINE_ALBUM_Cost July_260802_54.jpg)</v>
       </c>
       <c r="F376">
-        <v>1539</v>
+        <v>20020</v>
       </c>
     </row>
     <row r="377">
@@ -8666,13 +8666,13 @@
         <v>COGS</v>
       </c>
       <c r="D377" t="str">
-        <v>Watermelon</v>
+        <v>Orange</v>
       </c>
       <c r="E377" t="str">
-        <v>แตงโม 10-7-69 50 ลูก 4000 11-7-69 40 ลูก 3200 (LINE_ALBUM_Cost July_260802_57.jpg)</v>
+        <v>ส้ม 125 โล 3450 ค่าส่ง 300 (LINE_ALBUM_Cost July_260802_55.jpg)</v>
       </c>
       <c r="F377">
-        <v>7200</v>
+        <v>3750</v>
       </c>
     </row>
     <row r="378">
@@ -8686,13 +8686,13 @@
         <v>COGS</v>
       </c>
       <c r="D378" t="str">
-        <v>Other</v>
+        <v>Pineapple</v>
       </c>
       <c r="E378" t="str">
-        <v>ทุเรียน 50 โล โลละ 85 รวม 4250 มัดจำตะกร้า 200 (LINE_ALBUM_Cost July_260802_58.jpg)</v>
+        <v>สับปะรด 25 ลูก (LINE_ALBUM_Cost July_260802_56.jpg)</v>
       </c>
       <c r="F378">
-        <v>4450</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="379">
@@ -8709,10 +8709,10 @@
         <v>Watermelon</v>
       </c>
       <c r="E379" t="str">
-        <v>แตงโม 14-7-69 50 ลูก 4000 (LINE_ALBUM_Cost July_260802_59.jpg)</v>
+        <v>แตงโม 10-7-69 50 ลูก 4000 11-7-69 40 ลูก 3200 (LINE_ALBUM_Cost July_260802_57.jpg)</v>
       </c>
       <c r="F379">
-        <v>4000</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="380">
@@ -8726,13 +8726,13 @@
         <v>COGS</v>
       </c>
       <c r="D380" t="str">
-        <v>Mango</v>
+        <v>Other</v>
       </c>
       <c r="E380" t="str">
-        <v>มะม่วง 52 โล(2 ตะกร้า) โลละ 50 (LINE_ALBUM_Cost July_260802_60.jpg)</v>
+        <v>ทุเรียน 50 โล โลละ 85 รวม 4250 มัดจำตะกร้า 200 (LINE_ALBUM_Cost July_260802_58.jpg)</v>
       </c>
       <c r="F380">
-        <v>2600</v>
+        <v>4450</v>
       </c>
     </row>
     <row r="381">
@@ -8746,13 +8746,13 @@
         <v>COGS</v>
       </c>
       <c r="D381" t="str">
-        <v>Guava</v>
+        <v>Watermelon</v>
       </c>
       <c r="E381" t="str">
-        <v>ฝรั่ง 2 ตะกร้า (ตะกร้าละ 20 โล) (LINE_ALBUM_Cost July_260802_61.jpg)</v>
+        <v>แตงโม 14-7-69 50 ลูก 4000 (LINE_ALBUM_Cost July_260802_59.jpg)</v>
       </c>
       <c r="F381">
-        <v>2000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="382">
@@ -8766,13 +8766,13 @@
         <v>COGS</v>
       </c>
       <c r="D382" t="str">
-        <v>Apple</v>
+        <v>Mango</v>
       </c>
       <c r="E382" t="str">
-        <v>แอปเปิ้ล 5 ลัง (LINE_ALBUM_Cost July_260802_62.jpg)</v>
+        <v>มะม่วง 52 โล(2 ตะกร้า) โลละ 50 (LINE_ALBUM_Cost July_260802_60.jpg)</v>
       </c>
       <c r="F382">
-        <v>2000</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="383">
@@ -8786,18 +8786,18 @@
         <v>COGS</v>
       </c>
       <c r="D383" t="str">
-        <v>Coconut</v>
+        <v>Guava</v>
       </c>
       <c r="E383" t="str">
-        <v>น้ำ 30ลิตร ลิตรละ45บาท เนื้อมะพร้าว 50kg.กิโลละ 100บาท ค่าส่ง350 (LINE_ALBUM_Cost July_260802_63.jpg)</v>
+        <v>ฝรั่ง 2 ตะกร้า (ตะกร้าละ 20 โล) (LINE_ALBUM_Cost July_260802_61.jpg)</v>
       </c>
       <c r="F383">
-        <v>6700</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>20/07/2026</v>
+        <v>17/07/2026</v>
       </c>
       <c r="B384" t="str">
         <v>Jul26</v>
@@ -8806,10 +8806,10 @@
         <v>COGS</v>
       </c>
       <c r="D384" t="str">
-        <v>Guava</v>
+        <v>Apple</v>
       </c>
       <c r="E384" t="str">
-        <v>ฝรั่ง 2 ตะกร้า (LINE_ALBUM_Cost July_260802_64.jpg)</v>
+        <v>แอปเปิ้ล 5 ลัง (LINE_ALBUM_Cost July_260802_62.jpg)</v>
       </c>
       <c r="F384">
         <v>2000</v>
@@ -8817,7 +8817,7 @@
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>20/07/2026</v>
+        <v>17/07/2026</v>
       </c>
       <c r="B385" t="str">
         <v>Jul26</v>
@@ -8826,13 +8826,13 @@
         <v>COGS</v>
       </c>
       <c r="D385" t="str">
-        <v>Pineapple</v>
+        <v>Coconut</v>
       </c>
       <c r="E385" t="str">
-        <v>สับปะรด 20 ลูก (LINE_ALBUM_Cost July_260802_65.jpg)</v>
+        <v>น้ำ 30ลิตร ลิตรละ45บาท เนื้อมะพร้าว 50kg.กิโลละ 100บาท ค่าส่ง350 (LINE_ALBUM_Cost July_260802_63.jpg)</v>
       </c>
       <c r="F385">
-        <v>1296</v>
+        <v>6700</v>
       </c>
     </row>
     <row r="386">
@@ -8846,13 +8846,13 @@
         <v>COGS</v>
       </c>
       <c r="D386" t="str">
-        <v>Mango</v>
+        <v>Guava</v>
       </c>
       <c r="E386" t="str">
-        <v>มะม่วง 2 ลัง (LINE_ALBUM_Cost July_260802_66.jpg)</v>
+        <v>ฝรั่ง 2 ตะกร้า (LINE_ALBUM_Cost July_260802_64.jpg)</v>
       </c>
       <c r="F386">
-        <v>2600</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="387">
@@ -8866,38 +8866,38 @@
         <v>COGS</v>
       </c>
       <c r="D387" t="str">
-        <v>Watermelon</v>
+        <v>Pineapple</v>
       </c>
       <c r="E387" t="str">
-        <v>แตงโม 17-7-2569 เบอร์ 80บาท 50 ลูก (LINE_ALBUM_Cost July_260802_67.jpg)</v>
+        <v>สับปะรด 20 ลูก (LINE_ALBUM_Cost July_260802_65.jpg)</v>
       </c>
       <c r="F387">
-        <v>4000</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>21/07/2026</v>
+        <v>20/07/2026</v>
       </c>
       <c r="B388" t="str">
         <v>Jul26</v>
       </c>
       <c r="C388" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D388" t="str">
-        <v>Other</v>
+        <v>Mango</v>
       </c>
       <c r="E388" t="str">
-        <v xml:space="preserve"> (LINE_ALBUM_Cost July_260802_68.jpg)</v>
+        <v>มะม่วง 2 ลัง (LINE_ALBUM_Cost July_260802_66.jpg)</v>
       </c>
       <c r="F388">
-        <v>2000</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>22/07/2026</v>
+        <v>20/07/2026</v>
       </c>
       <c r="B389" t="str">
         <v>Jul26</v>
@@ -8906,33 +8906,33 @@
         <v>COGS</v>
       </c>
       <c r="D389" t="str">
-        <v>Orange</v>
+        <v>Watermelon</v>
       </c>
       <c r="E389" t="str">
-        <v>ส้ม 25x22กก รวม 550กกx30 บ รวม 16500บาท ค่าขนส่ง 25ตกx 50 บ 1250 (LINE_ALBUM_Cost July_260802_69.jpg)</v>
+        <v>แตงโม 17-7-2569 เบอร์ 80บาท 50 ลูก (LINE_ALBUM_Cost July_260802_67.jpg)</v>
       </c>
       <c r="F389">
-        <v>17750</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>22/07/2026</v>
+        <v>21/07/2026</v>
       </c>
       <c r="B390" t="str">
         <v>Jul26</v>
       </c>
       <c r="C390" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D390" t="str">
-        <v>Apple</v>
+        <v>Other</v>
       </c>
       <c r="E390" t="str">
-        <v>แอปเปิ้ล 4 ลัง (LINE_ALBUM_Cost July_260802_70.jpg)</v>
+        <v xml:space="preserve"> (LINE_ALBUM_Cost July_260802_68.jpg)</v>
       </c>
       <c r="F390">
-        <v>1600</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="391">
@@ -8946,13 +8946,13 @@
         <v>COGS</v>
       </c>
       <c r="D391" t="str">
-        <v>Mango</v>
+        <v>Orange</v>
       </c>
       <c r="E391" t="str">
-        <v>มะม่วง 78 กิโล 3 ลัง (LINE_ALBUM_Cost July_260802_71.jpg)</v>
+        <v>ส้ม 25x22กก รวม 550กกx30 บ รวม 16500บาท ค่าขนส่ง 25ตกx 50 บ 1250 (LINE_ALBUM_Cost July_260802_69.jpg)</v>
       </c>
       <c r="F391">
-        <v>3900</v>
+        <v>17750</v>
       </c>
     </row>
     <row r="392">
@@ -8963,16 +8963,16 @@
         <v>Jul26</v>
       </c>
       <c r="C392" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D392" t="str">
-        <v>Other</v>
+        <v>Apple</v>
       </c>
       <c r="E392" t="str">
-        <v>OPEX Avocado milk (LINE_ALBUM_Cost July_260802_74.jpg)</v>
+        <v>แอปเปิ้ล 4 ลัง (LINE_ALBUM_Cost July_260802_70.jpg)</v>
       </c>
       <c r="F392">
-        <v>440.75</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="393">
@@ -8983,16 +8983,16 @@
         <v>Jul26</v>
       </c>
       <c r="C393" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D393" t="str">
-        <v>Other</v>
+        <v>Mango</v>
       </c>
       <c r="E393" t="str">
-        <v>Opex knife (LINE_ALBUM_Cost July_260802_75.jpg)</v>
+        <v>มะม่วง 78 กิโล 3 ลัง (LINE_ALBUM_Cost July_260802_71.jpg)</v>
       </c>
       <c r="F393">
-        <v>199</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="394">
@@ -9009,10 +9009,10 @@
         <v>Other</v>
       </c>
       <c r="E394" t="str">
-        <v>Opex equipment (LINE_ALBUM_Cost July_260802_76.jpg)</v>
+        <v>OPEX Avocado milk (LINE_ALBUM_Cost July_260802_74.jpg)</v>
       </c>
       <c r="F394">
-        <v>221</v>
+        <v>440.75</v>
       </c>
     </row>
     <row r="395">
@@ -9023,16 +9023,16 @@
         <v>Jul26</v>
       </c>
       <c r="C395" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D395" t="str">
-        <v>Stock</v>
+        <v>Other</v>
       </c>
       <c r="E395" t="str">
-        <v>Cogs Falcon milk (LINE_ALBUM_Cost July_260802_77.jpg)</v>
+        <v>Opex knife (LINE_ALBUM_Cost July_260802_75.jpg)</v>
       </c>
       <c r="F395">
-        <v>716</v>
+        <v>199</v>
       </c>
     </row>
     <row r="396">
@@ -9049,10 +9049,10 @@
         <v>Other</v>
       </c>
       <c r="E396" t="str">
-        <v>Opex B1 police fee 1000 / person (LINE_ALBUM_Cost July_260802_78.jpg)</v>
+        <v>Opex equipment (LINE_ALBUM_Cost July_260802_76.jpg)</v>
       </c>
       <c r="F396">
-        <v>2000</v>
+        <v>221</v>
       </c>
     </row>
     <row r="397">
@@ -9063,16 +9063,16 @@
         <v>Jul26</v>
       </c>
       <c r="C397" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D397" t="str">
-        <v>Other</v>
+        <v>Stock</v>
       </c>
       <c r="E397" t="str">
-        <v>Opex equipments (LINE_ALBUM_Cost July_260802_79.jpg)</v>
+        <v>Cogs Falcon milk (LINE_ALBUM_Cost July_260802_77.jpg)</v>
       </c>
       <c r="F397">
-        <v>506</v>
+        <v>716</v>
       </c>
     </row>
     <row r="398">
@@ -9089,50 +9089,50 @@
         <v>Other</v>
       </c>
       <c r="E398" t="str">
-        <v>Opex other (LINE_ALBUM_Cost July_260802_80.jpg)</v>
+        <v>Opex B1 police fee 1000 / person (LINE_ALBUM_Cost July_260802_78.jpg)</v>
       </c>
       <c r="F398">
-        <v>1918</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>23/07/2026</v>
+        <v>22/07/2026</v>
       </c>
       <c r="B399" t="str">
         <v>Jul26</v>
       </c>
       <c r="C399" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D399" t="str">
-        <v>Watermelon</v>
+        <v>Other</v>
       </c>
       <c r="E399" t="str">
-        <v>20-7-2569 ราคา 80 - 45ลูก 22-7-2569 ราคา 80 - 30 ลูก 23-7-2569 ราคา 80 - 30 ลูก (LINE_ALBUM_Cost July_260802_81.jpg)</v>
+        <v>Opex equipments (LINE_ALBUM_Cost July_260802_79.jpg)</v>
       </c>
       <c r="F399">
-        <v>8400</v>
+        <v>506</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>23/07/2026</v>
+        <v>22/07/2026</v>
       </c>
       <c r="B400" t="str">
         <v>Jul26</v>
       </c>
       <c r="C400" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D400" t="str">
-        <v>Guava</v>
+        <v>Other</v>
       </c>
       <c r="E400" t="str">
-        <v>ฝรั่ง 2 ลัง ลังละ 20 กิโล กิโลละ 50 บาท รวม 2000 บาท (LINE_ALBUM_Cost July_260802_82.jpg)</v>
+        <v>Opex other (LINE_ALBUM_Cost July_260802_80.jpg)</v>
       </c>
       <c r="F400">
-        <v>2000</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="401">
@@ -9146,113 +9146,113 @@
         <v>COGS</v>
       </c>
       <c r="D401" t="str">
-        <v>Pineapple</v>
+        <v>Watermelon</v>
       </c>
       <c r="E401" t="str">
-        <v>สับปะรด 41 กิโล *27 บาท รวม 1107 บาท (LINE_ALBUM_Cost July_260802_83.jpg)</v>
+        <v>20-7-2569 ราคา 80 - 45ลูก 22-7-2569 ราคา 80 - 30 ลูก 23-7-2569 ราคา 80 - 30 ลูก (LINE_ALBUM_Cost July_260802_81.jpg)</v>
       </c>
       <c r="F401">
-        <v>1107</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>31/07/2026</v>
+        <v>23/07/2026</v>
       </c>
       <c r="B402" t="str">
         <v>Jul26</v>
       </c>
       <c r="C402" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D402" t="str">
-        <v>Rental</v>
+        <v>Guava</v>
       </c>
       <c r="E402" t="str">
-        <v>ค่าเช่าร้าน B1 ก.ค. (จ่ายเงินสดจากหน้าร้านก่อนนำเข้าบัญชี - ไม่มีสลิป ยืนยันโดยเจ้าของ 28/08)</v>
+        <v>ฝรั่ง 2 ลัง ลังละ 20 กิโล กิโลละ 50 บาท รวม 2000 บาท (LINE_ALBUM_Cost July_260802_82.jpg)</v>
       </c>
       <c r="F402">
-        <v>35000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>31/07/2026</v>
+        <v>23/07/2026</v>
       </c>
       <c r="B403" t="str">
         <v>Jul26</v>
       </c>
       <c r="C403" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D403" t="str">
-        <v>Salary</v>
+        <v>Pineapple</v>
       </c>
       <c r="E403" t="str">
-        <v>Salary B1</v>
+        <v>สับปะรด 41 กิโล *27 บาท รวม 1107 บาท (LINE_ALBUM_Cost July_260802_83.jpg)</v>
       </c>
       <c r="F403">
-        <v>35000</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>23/05/2026</v>
+        <v>31/07/2026</v>
       </c>
       <c r="B404" t="str">
-        <v>May26</v>
+        <v>Jul26</v>
       </c>
       <c r="C404" t="str">
-        <v>EXCLUDED</v>
+        <v>OPEX</v>
       </c>
       <c r="D404" t="str">
-        <v>Pass-Through</v>
+        <v>Rental</v>
       </c>
       <c r="E404" t="str">
-        <v>มังคุด (รับเงินสด 28,000 แล้วโอนต่อ ฐนกร 23/05 17:23) - ไม่ใช่ต้นทุน SSJ [bank]</v>
+        <v>ค่าเช่าร้าน B1 ก.ค. (จ่ายเงินสดจากหน้าร้านก่อนนำเข้าบัญชี - ไม่มีสลิป ยืนยันโดยเจ้าของ 28/08)</v>
       </c>
       <c r="F404">
-        <v>0</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>01/05/2026</v>
+        <v>31/07/2026</v>
       </c>
       <c r="B405" t="str">
-        <v>May26</v>
+        <v>Jul26</v>
       </c>
       <c r="C405" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D405" t="str">
-        <v>Transportation</v>
+        <v>Salary</v>
       </c>
       <c r="E405" t="str">
-        <v>ลาลามูฟ Lalamove [bank]</v>
+        <v>Salary B1</v>
       </c>
       <c r="F405">
-        <v>2000</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>07/05/2026</v>
+        <v>23/05/2026</v>
       </c>
       <c r="B406" t="str">
         <v>May26</v>
       </c>
       <c r="C406" t="str">
-        <v>OPEX</v>
+        <v>EXCLUDED</v>
       </c>
       <c r="D406" t="str">
-        <v>Other</v>
+        <v>Pass-Through</v>
       </c>
       <c r="E406" t="str">
-        <v>บจก. อาร์.เอ็น.คลีน ทำความสะอาด [bank]</v>
+        <v>มังคุด (รับเงินสด 28,000 แล้วโอนต่อ ฐนกร 23/05 17:23) - ไม่ใช่ต้นทุน SSJ [bank]</v>
       </c>
       <c r="F406">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="407">
@@ -9266,38 +9266,38 @@
         <v>COGS</v>
       </c>
       <c r="D407" t="str">
-        <v>Mango</v>
+        <v>Transportation</v>
       </c>
       <c r="E407" t="str">
-        <v>LINE Pay Merchant [bank]</v>
+        <v>ลาลามูฟ Lalamove [bank]</v>
       </c>
       <c r="F407">
-        <v>780</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>01/05/2026</v>
+        <v>07/05/2026</v>
       </c>
       <c r="B408" t="str">
         <v>May26</v>
       </c>
       <c r="C408" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D408" t="str">
-        <v>Pineapple</v>
+        <v>Other</v>
       </c>
       <c r="E408" t="str">
-        <v>น.ส. สุพิชญา [bank]</v>
+        <v>บจก. อาร์.เอ็น.คลีน ทำความสะอาด [bank]</v>
       </c>
       <c r="F408">
-        <v>684</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>09/05/2026</v>
+        <v>01/05/2026</v>
       </c>
       <c r="B409" t="str">
         <v>May26</v>
@@ -9306,98 +9306,98 @@
         <v>COGS</v>
       </c>
       <c r="D409" t="str">
-        <v>Guava</v>
+        <v>Mango</v>
       </c>
       <c r="E409" t="str">
-        <v>ฝรั่ง 1 ตะกร้า (นาง ประนอม) [bank]</v>
+        <v>LINE Pay Merchant [bank]</v>
       </c>
       <c r="F409">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>30/04/2026</v>
+        <v>01/05/2026</v>
       </c>
       <c r="B410" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C410" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D410" t="str">
-        <v>Marketing</v>
+        <v>Pineapple</v>
       </c>
       <c r="E410" t="str">
-        <v>ปืนฉีดน้ำ สงกรานต์ (จ่าย 06/05) [bank]</v>
+        <v>น.ส. สุพิชญา [bank]</v>
       </c>
       <c r="F410">
-        <v>24016</v>
+        <v>684</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>30/04/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="B411" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C411" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D411" t="str">
-        <v>Salary</v>
+        <v>Guava</v>
       </c>
       <c r="E411" t="str">
-        <v>เงินเดือน เม.ย. (จ่าย 01/05) [bank]</v>
+        <v>ฝรั่ง 1 ตะกร้า (นาง ประนอม) [bank]</v>
       </c>
       <c r="F411">
-        <v>31000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>04/04/2026</v>
+        <v>30/04/2026</v>
       </c>
       <c r="B412" t="str">
         <v>Apr26</v>
       </c>
       <c r="C412" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D412" t="str">
-        <v>Packaging</v>
+        <v>Marketing</v>
       </c>
       <c r="E412" t="str">
-        <v>Shopee (ทีมจัดซื้อ) [bank SA8285]</v>
+        <v>ปืนฉีดน้ำ สงกรานต์ (จ่าย 06/05) [bank]</v>
       </c>
       <c r="F412">
-        <v>11732</v>
+        <v>24016</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>05/04/2026</v>
+        <v>30/04/2026</v>
       </c>
       <c r="B413" t="str">
         <v>Apr26</v>
       </c>
       <c r="C413" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D413" t="str">
-        <v>Packaging</v>
+        <v>Salary</v>
       </c>
       <c r="E413" t="str">
-        <v>Shopee (ทีมจัดซื้อ) [bank SA8285]</v>
+        <v>เงินเดือน เม.ย. (จ่าย 01/05) [bank]</v>
       </c>
       <c r="F413">
-        <v>672</v>
+        <v>31000</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>16/04/2026</v>
+        <v>04/04/2026</v>
       </c>
       <c r="B414" t="str">
         <v>Apr26</v>
@@ -9412,12 +9412,12 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA8285]</v>
       </c>
       <c r="F414">
-        <v>11560</v>
+        <v>11732</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>20/04/2026</v>
+        <v>05/04/2026</v>
       </c>
       <c r="B415" t="str">
         <v>Apr26</v>
@@ -9432,12 +9432,12 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA8285]</v>
       </c>
       <c r="F415">
-        <v>692</v>
+        <v>672</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>25/04/2026</v>
+        <v>16/04/2026</v>
       </c>
       <c r="B416" t="str">
         <v>Apr26</v>
@@ -9452,15 +9452,15 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA8285]</v>
       </c>
       <c r="F416">
-        <v>1838</v>
+        <v>11560</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>21/06/2026</v>
+        <v>20/04/2026</v>
       </c>
       <c r="B417" t="str">
-        <v>Jun26</v>
+        <v>Apr26</v>
       </c>
       <c r="C417" t="str">
         <v>COGS</v>
@@ -9469,18 +9469,18 @@
         <v>Packaging</v>
       </c>
       <c r="E417" t="str">
-        <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
+        <v>Shopee (ทีมจัดซื้อ) [bank SA8285]</v>
       </c>
       <c r="F417">
-        <v>1377</v>
+        <v>692</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>21/06/2026</v>
+        <v>25/04/2026</v>
       </c>
       <c r="B418" t="str">
-        <v>Jun26</v>
+        <v>Apr26</v>
       </c>
       <c r="C418" t="str">
         <v>COGS</v>
@@ -9489,10 +9489,10 @@
         <v>Packaging</v>
       </c>
       <c r="E418" t="str">
-        <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
+        <v>Shopee (ทีมจัดซื้อ) [bank SA8285]</v>
       </c>
       <c r="F418">
-        <v>1210</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="419">
@@ -9512,7 +9512,7 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F419">
-        <v>1210</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="420">
@@ -9532,7 +9532,7 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F420">
-        <v>1242</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="421">
@@ -9552,7 +9552,7 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F421">
-        <v>1232</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="422">
@@ -9572,7 +9572,7 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F422">
-        <v>1286</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="423">
@@ -9592,7 +9592,7 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F423">
-        <v>1295</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="424">
@@ -9612,7 +9612,7 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F424">
-        <v>1445</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="425">
@@ -9632,7 +9632,7 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F425">
-        <v>3051</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="426">
@@ -9652,12 +9652,12 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F426">
-        <v>755</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>29/06/2026</v>
+        <v>21/06/2026</v>
       </c>
       <c r="B427" t="str">
         <v>Jun26</v>
@@ -9672,12 +9672,12 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F427">
-        <v>7766</v>
+        <v>3051</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>29/06/2026</v>
+        <v>21/06/2026</v>
       </c>
       <c r="B428" t="str">
         <v>Jun26</v>
@@ -9692,7 +9692,7 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F428">
-        <v>539</v>
+        <v>755</v>
       </c>
     </row>
     <row r="429">
@@ -9712,15 +9712,15 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F429">
-        <v>596</v>
+        <v>7766</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>07/07/2026</v>
+        <v>29/06/2026</v>
       </c>
       <c r="B430" t="str">
-        <v>Jul26</v>
+        <v>Jun26</v>
       </c>
       <c r="C430" t="str">
         <v>COGS</v>
@@ -9732,15 +9732,15 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F430">
-        <v>141</v>
+        <v>539</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>07/07/2026</v>
+        <v>29/06/2026</v>
       </c>
       <c r="B431" t="str">
-        <v>Jul26</v>
+        <v>Jun26</v>
       </c>
       <c r="C431" t="str">
         <v>COGS</v>
@@ -9752,7 +9752,7 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F431">
-        <v>7999</v>
+        <v>596</v>
       </c>
     </row>
     <row r="432">
@@ -9772,12 +9772,12 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F432">
-        <v>1399</v>
+        <v>141</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>08/07/2026</v>
+        <v>07/07/2026</v>
       </c>
       <c r="B433" t="str">
         <v>Jul26</v>
@@ -9792,12 +9792,12 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F433">
-        <v>9870</v>
+        <v>7999</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>24/07/2026</v>
+        <v>07/07/2026</v>
       </c>
       <c r="B434" t="str">
         <v>Jul26</v>
@@ -9812,155 +9812,155 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F434">
-        <v>7410</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>26/07/2026</v>
+        <v>08/07/2026</v>
       </c>
       <c r="B435" t="str">
         <v>Jul26</v>
       </c>
       <c r="C435" t="str">
-        <v>CAPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D435" t="str">
-        <v>Investment</v>
+        <v>Packaging</v>
       </c>
       <c r="E435" t="str">
-        <v>เครื่องสกัดเย็น 1 เครื่อง (Shopee, audit fix - was COGS/Packaging)</v>
+        <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F435">
-        <v>1015</v>
+        <v>9870</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>26/07/2026</v>
+        <v>24/07/2026</v>
       </c>
       <c r="B436" t="str">
         <v>Jul26</v>
       </c>
       <c r="C436" t="str">
-        <v>CAPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D436" t="str">
-        <v>Investment</v>
+        <v>Packaging</v>
       </c>
       <c r="E436" t="str">
-        <v>เครื่องสกัดเย็น 1 เครื่อง (Shopee, audit fix - was COGS/Packaging)</v>
+        <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F436">
-        <v>1087</v>
+        <v>7410</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>27/07/2026</v>
+        <v>26/07/2026</v>
       </c>
       <c r="B437" t="str">
         <v>Jul26</v>
       </c>
       <c r="C437" t="str">
-        <v>COGS</v>
+        <v>CAPEX</v>
       </c>
       <c r="D437" t="str">
-        <v>Packaging</v>
+        <v>Investment</v>
       </c>
       <c r="E437" t="str">
-        <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
+        <v>เครื่องสกัดเย็น 1 เครื่อง (Shopee, audit fix - was COGS/Packaging)</v>
       </c>
       <c r="F437">
-        <v>4309</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>27/07/2026</v>
+        <v>26/07/2026</v>
       </c>
       <c r="B438" t="str">
         <v>Jul26</v>
       </c>
       <c r="C438" t="str">
-        <v>COGS</v>
+        <v>CAPEX</v>
       </c>
       <c r="D438" t="str">
-        <v>Packaging</v>
+        <v>Investment</v>
       </c>
       <c r="E438" t="str">
-        <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
+        <v>เครื่องสกัดเย็น 1 เครื่อง (Shopee, audit fix - was COGS/Packaging)</v>
       </c>
       <c r="F438">
-        <v>2589</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>31/01/2026</v>
+        <v>27/07/2026</v>
       </c>
       <c r="B439" t="str">
-        <v>Jan26</v>
+        <v>Jul26</v>
       </c>
       <c r="C439" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D439" t="str">
-        <v>Rental</v>
+        <v>Packaging</v>
       </c>
       <c r="E439" t="str">
-        <v>ค่าเช่าร้าน Jan26 (ปรับตามงบการเงินเจ้าของ)</v>
+        <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F439">
-        <v>30000</v>
+        <v>4309</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>28/02/2026</v>
+        <v>27/07/2026</v>
       </c>
       <c r="B440" t="str">
-        <v>Feb26</v>
+        <v>Jul26</v>
       </c>
       <c r="C440" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D440" t="str">
-        <v>Rental</v>
+        <v>Packaging</v>
       </c>
       <c r="E440" t="str">
-        <v>ค่าเช่าร้าน Feb26 (ปรับตามงบการเงินเจ้าของ)</v>
+        <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F440">
-        <v>35000</v>
+        <v>2589</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>28/02/2026</v>
+        <v>31/01/2026</v>
       </c>
       <c r="B441" t="str">
-        <v>Feb26</v>
+        <v>Jan26</v>
       </c>
       <c r="C441" t="str">
         <v>OPEX</v>
       </c>
       <c r="D441" t="str">
-        <v>Salary</v>
+        <v>Rental</v>
       </c>
       <c r="E441" t="str">
-        <v>ค่าแรงคนงาน Feb26 (ปรับตามงบการเงินเจ้าของ)</v>
+        <v>ค่าเช่าร้าน Jan26 (ปรับตามงบการเงินเจ้าของ)</v>
       </c>
       <c r="F441">
-        <v>19000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>31/03/2026</v>
+        <v>28/02/2026</v>
       </c>
       <c r="B442" t="str">
-        <v>Mar26</v>
+        <v>Feb26</v>
       </c>
       <c r="C442" t="str">
         <v>OPEX</v>
@@ -9969,7 +9969,7 @@
         <v>Rental</v>
       </c>
       <c r="E442" t="str">
-        <v>ค่าเช่าร้าน Mar26 (ปรับตามงบการเงินเจ้าของ)</v>
+        <v>ค่าเช่าร้าน Feb26 (ปรับตามงบการเงินเจ้าของ)</v>
       </c>
       <c r="F442">
         <v>35000</v>
@@ -9977,22 +9977,22 @@
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>31/03/2026</v>
+        <v>28/02/2026</v>
       </c>
       <c r="B443" t="str">
-        <v>Mar26</v>
+        <v>Feb26</v>
       </c>
       <c r="C443" t="str">
         <v>OPEX</v>
       </c>
       <c r="D443" t="str">
-        <v>Rental</v>
+        <v>Salary</v>
       </c>
       <c r="E443" t="str">
-        <v>ค่าเช่าคลัง Mar26 (ปรับตามงบการเงินเจ้าของ)</v>
+        <v>ค่าแรงคนงาน Feb26 (ปรับตามงบการเงินเจ้าของ)</v>
       </c>
       <c r="F443">
-        <v>12000</v>
+        <v>19000</v>
       </c>
     </row>
     <row r="444">
@@ -10006,61 +10006,61 @@
         <v>OPEX</v>
       </c>
       <c r="D444" t="str">
-        <v>Other</v>
+        <v>Rental</v>
       </c>
       <c r="E444" t="str">
-        <v>ค่าน้ำ + ค่าไฟ Mar26 (ปรับตามงบการเงินเจ้าของ)</v>
+        <v>ค่าเช่าร้าน Mar26 (ปรับตามงบการเงินเจ้าของ)</v>
       </c>
       <c r="F444">
-        <v>3229</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>22/06/2026</v>
+        <v>31/03/2026</v>
       </c>
       <c r="B445" t="str">
-        <v>Jun26</v>
+        <v>Mar26</v>
       </c>
       <c r="C445" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D445" t="str">
-        <v>Guava</v>
+        <v>Rental</v>
       </c>
       <c r="E445" t="str">
-        <v>ฝรั่ง (นาง ประนอม) [bank]</v>
+        <v>ค่าเช่าคลัง Mar26 (ปรับตามงบการเงินเจ้าของ)</v>
       </c>
       <c r="F445">
-        <v>100</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>25/06/2026</v>
+        <v>31/03/2026</v>
       </c>
       <c r="B446" t="str">
-        <v>Jun26</v>
+        <v>Mar26</v>
       </c>
       <c r="C446" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D446" t="str">
-        <v>Guava</v>
+        <v>Other</v>
       </c>
       <c r="E446" t="str">
-        <v>ฝรั่ง 1 ตะกร้า (นาง ประนอม) [bank]</v>
+        <v>ค่าน้ำ + ค่าไฟ Mar26 (ปรับตามงบการเงินเจ้าของ)</v>
       </c>
       <c r="F446">
-        <v>800</v>
+        <v>3229</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>28/07/2026</v>
+        <v>22/06/2026</v>
       </c>
       <c r="B447" t="str">
-        <v>Jul26</v>
+        <v>Jun26</v>
       </c>
       <c r="C447" t="str">
         <v>COGS</v>
@@ -10072,67 +10072,67 @@
         <v>ฝรั่ง (นาง ประนอม) [bank]</v>
       </c>
       <c r="F447">
-        <v>3000</v>
+        <v>100</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>20/02/2026</v>
+        <v>25/06/2026</v>
       </c>
       <c r="B448" t="str">
-        <v>Feb26</v>
+        <v>Jun26</v>
       </c>
       <c r="C448" t="str">
         <v>COGS</v>
       </c>
       <c r="D448" t="str">
-        <v>Transportation</v>
+        <v>Guava</v>
       </c>
       <c r="E448" t="str">
-        <v>ค่ารถ (แยกจากใบเสร็จผ้าปิดร้าน 416)</v>
+        <v>ฝรั่ง 1 ตะกร้า (นาง ประนอม) [bank]</v>
       </c>
       <c r="F448">
-        <v>198</v>
+        <v>800</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>04/06/2026</v>
+        <v>28/07/2026</v>
       </c>
       <c r="B449" t="str">
-        <v>Jun26</v>
+        <v>Jul26</v>
       </c>
       <c r="C449" t="str">
         <v>COGS</v>
       </c>
       <c r="D449" t="str">
-        <v>Pineapple</v>
+        <v>Guava</v>
       </c>
       <c r="E449" t="str">
-        <v>สลิปรวม: สับปะรด 750 (audit fix, was bundled)</v>
+        <v>ฝรั่ง (นาง ประนอม) [bank]</v>
       </c>
       <c r="F449">
-        <v>750</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>04/06/2026</v>
+        <v>20/02/2026</v>
       </c>
       <c r="B450" t="str">
-        <v>Jun26</v>
+        <v>Feb26</v>
       </c>
       <c r="C450" t="str">
         <v>COGS</v>
       </c>
       <c r="D450" t="str">
-        <v>Orange</v>
+        <v>Transportation</v>
       </c>
       <c r="E450" t="str">
-        <v>สลิปรวม: ส้ม 2250 (audit fix, was bundled into Pineapple line)</v>
+        <v>ค่ารถ (แยกจากใบเสร็จผ้าปิดร้าน 416)</v>
       </c>
       <c r="F450">
-        <v>2250</v>
+        <v>198</v>
       </c>
     </row>
     <row r="451">
@@ -10143,44 +10143,44 @@
         <v>Jun26</v>
       </c>
       <c r="C451" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D451" t="str">
-        <v>Other</v>
+        <v>Pineapple</v>
       </c>
       <c r="E451" t="str">
-        <v>ค่าปรับตำรวจ 2 คน (police fee, audit fix - was miscategorized as COGS/Pineapple)</v>
+        <v>สลิปรวม: สับปะรด 750 (audit fix, was bundled)</v>
       </c>
       <c r="F451">
-        <v>2000</v>
+        <v>750</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>26/07/2026</v>
+        <v>04/06/2026</v>
       </c>
       <c r="B452" t="str">
-        <v>Jul26</v>
+        <v>Jun26</v>
       </c>
       <c r="C452" t="str">
-        <v>CAPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D452" t="str">
-        <v>Investment</v>
+        <v>Orange</v>
       </c>
       <c r="E452" t="str">
-        <v>งบลงทุน - ทดลองอื่นๆ (LINE_ALBUM_Cost July_260802_8.jpg, audit fix - was bundled into COGS/Mango)</v>
+        <v>สลิปรวม: ส้ม 2250 (audit fix, was bundled into Pineapple line)</v>
       </c>
       <c r="F452">
-        <v>810</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>26/07/2026</v>
+        <v>04/06/2026</v>
       </c>
       <c r="B453" t="str">
-        <v>Jul26</v>
+        <v>Jun26</v>
       </c>
       <c r="C453" t="str">
         <v>OPEX</v>
@@ -10189,35 +10189,35 @@
         <v>Other</v>
       </c>
       <c r="E453" t="str">
-        <v>ค่าส่งของ (LINE_ALBUM_Cost July_260802_11.jpg, audit fix - missing entry)</v>
+        <v>ค่าปรับตำรวจ 2 คน (police fee, audit fix - was miscategorized as COGS/Pineapple)</v>
       </c>
       <c r="F453">
-        <v>212</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>28/07/2026</v>
+        <v>26/07/2026</v>
       </c>
       <c r="B454" t="str">
         <v>Jul26</v>
       </c>
       <c r="C454" t="str">
-        <v>COGS</v>
+        <v>CAPEX</v>
       </c>
       <c r="D454" t="str">
-        <v>Pineapple</v>
+        <v>Investment</v>
       </c>
       <c r="E454" t="str">
-        <v>สับปะรด 30 ลูก (LINE_ALBUM_Cost July_260802_17.jpg, audit fix - missing entry)</v>
+        <v>งบลงทุน - ทดลองอื่นๆ (LINE_ALBUM_Cost July_260802_8.jpg, audit fix - was bundled into COGS/Mango)</v>
       </c>
       <c r="F454">
-        <v>1188</v>
+        <v>810</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>28/07/2026</v>
+        <v>26/07/2026</v>
       </c>
       <c r="B455" t="str">
         <v>Jul26</v>
@@ -10229,75 +10229,75 @@
         <v>Other</v>
       </c>
       <c r="E455" t="str">
-        <v>ค่าขนส่ง (LINE_ALBUM_Cost July_260802_19.jpg, audit fix - missing entry)</v>
+        <v>ค่าส่งของ (LINE_ALBUM_Cost July_260802_11.jpg, audit fix - missing entry)</v>
       </c>
       <c r="F455">
-        <v>100</v>
+        <v>212</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>30/04/2026</v>
+        <v>28/07/2026</v>
       </c>
       <c r="B456" t="str">
-        <v>Apr26</v>
+        <v>Jul26</v>
       </c>
       <c r="C456" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D456" t="str">
-        <v>Rental</v>
+        <v>Pineapple</v>
       </c>
       <c r="E456" t="str">
-        <v>ค่าเช่า stock เม.ย. (B1 ครึ่งหนึ่ง)</v>
+        <v>สับปะรด 30 ลูก (LINE_ALBUM_Cost July_260802_17.jpg, audit fix - missing entry)</v>
       </c>
       <c r="F456">
-        <v>6000</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>05/03/2026</v>
+        <v>28/07/2026</v>
       </c>
       <c r="B457" t="str">
-        <v>Mar26</v>
+        <v>Jul26</v>
       </c>
       <c r="C457" t="str">
         <v>OPEX</v>
       </c>
       <c r="D457" t="str">
-        <v>Salary</v>
+        <v>Other</v>
       </c>
       <c r="E457" t="str">
-        <v>เงินเดือนเมน 3/26</v>
+        <v>ค่าขนส่ง (LINE_ALBUM_Cost July_260802_19.jpg, audit fix - missing entry)</v>
       </c>
       <c r="F457">
-        <v>19000</v>
+        <v>100</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>27/02/2026</v>
+        <v>30/04/2026</v>
       </c>
       <c r="B458" t="str">
-        <v>Feb26</v>
+        <v>Apr26</v>
       </c>
       <c r="C458" t="str">
         <v>OPEX</v>
       </c>
       <c r="D458" t="str">
-        <v>Investment</v>
+        <v>Rental</v>
       </c>
       <c r="E458" t="str">
-        <v>อุปกรณ์ (จากสลิปโอนผู้จัดการ)</v>
+        <v>ค่าเช่า stock เม.ย. (B1 ครึ่งหนึ่ง)</v>
       </c>
       <c r="F458">
-        <v>5000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>18/03/2026</v>
+        <v>05/03/2026</v>
       </c>
       <c r="B459" t="str">
         <v>Mar26</v>
@@ -10306,58 +10306,98 @@
         <v>OPEX</v>
       </c>
       <c r="D459" t="str">
-        <v>Milk/Conden</v>
+        <v>Salary</v>
       </c>
       <c r="E459" t="str">
-        <v>นม + นมข้นหวาน (จากสลิปโอนผู้จัดการ)</v>
+        <v>เงินเดือนเมน 3/26</v>
       </c>
       <c r="F459">
-        <v>230</v>
+        <v>19000</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>01/04/2026</v>
+        <v>27/02/2026</v>
       </c>
       <c r="B460" t="str">
-        <v>Mar26</v>
+        <v>Feb26</v>
       </c>
       <c r="C460" t="str">
         <v>OPEX</v>
       </c>
       <c r="D460" t="str">
-        <v>Salary</v>
+        <v>Investment</v>
       </c>
       <c r="E460" t="str">
-        <v>เงินเดือนพนักงาน 3 คน มี.ค. 26 (จ่าย 01/04) [bank]</v>
+        <v>อุปกรณ์ (จากสลิปโอนผู้จัดการ)</v>
       </c>
       <c r="F460">
-        <v>24600</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>08/06/2026</v>
+        <v>18/03/2026</v>
       </c>
       <c r="B461" t="str">
-        <v>Jun26</v>
+        <v>Mar26</v>
       </c>
       <c r="C461" t="str">
         <v>OPEX</v>
       </c>
       <c r="D461" t="str">
+        <v>Milk/Conden</v>
+      </c>
+      <c r="E461" t="str">
+        <v>นม + นมข้นหวาน (จากสลิปโอนผู้จัดการ)</v>
+      </c>
+      <c r="F461">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="str">
+        <v>01/04/2026</v>
+      </c>
+      <c r="B462" t="str">
+        <v>Mar26</v>
+      </c>
+      <c r="C462" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D462" t="str">
+        <v>Salary</v>
+      </c>
+      <c r="E462" t="str">
+        <v>เงินเดือนพนักงาน 3 คน มี.ค. 26 (จ่าย 01/04) [bank]</v>
+      </c>
+      <c r="F462">
+        <v>24600</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="str">
+        <v>08/06/2026</v>
+      </c>
+      <c r="B463" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C463" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D463" t="str">
         <v>Rental</v>
       </c>
-      <c r="E461" t="str">
+      <c r="E463" t="str">
         <v>ค่าเช่าคลัง มิ.ย. (B1 ครึ่งหนึ่ง ของ 12,000 จากสลิป 47,000 วันที่ 08/06)</v>
       </c>
-      <c r="F461">
+      <c r="F463">
         <v>6000</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F461"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F463"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/3_Automation_Dashboard/SomSaiJai_Dashboard_B1_2026.xlsx
+++ b/3_Automation_Dashboard/SomSaiJai_Dashboard_B1_2026.xlsx
@@ -1168,7 +1168,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F463"/>
+  <dimension ref="A1:F469"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3466,10 +3466,10 @@
         <v>COGS</v>
       </c>
       <c r="D117" t="str">
-        <v>Packaging</v>
+        <v>Milk/Conden</v>
       </c>
       <c r="E117" t="str">
-        <v>นมข้นจืดสามลังหนึ่งลังมี 12 กล่อง 36 กล่อง</v>
+        <v>นมข้นจืด 3 ลัง (36 กล่อง)</v>
       </c>
       <c r="F117">
         <v>1720</v>
@@ -3486,7 +3486,7 @@
         <v>COGS</v>
       </c>
       <c r="D118" t="str">
-        <v>Packaging</v>
+        <v>Milk/Conden</v>
       </c>
       <c r="E118" t="str">
         <v>นมข้นหวาน 3 ลัง 24 ถุง</v>
@@ -4646,13 +4646,13 @@
         <v>COGS</v>
       </c>
       <c r="D176" t="str">
-        <v>Packaging</v>
+        <v>Milk/Conden</v>
       </c>
       <c r="E176" t="str">
-        <v>นมข้นหวาน2ลัง 1602</v>
+        <v>นมข้นหวาน 2 ลัง 1,602 + นมข้นจืด 1 ลัง 638</v>
       </c>
       <c r="F176">
-        <v>3210</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="177">
@@ -4666,13 +4666,13 @@
         <v>COGS</v>
       </c>
       <c r="D177" t="str">
-        <v>Watermelon</v>
+        <v>Packaging</v>
       </c>
       <c r="E177" t="str">
-        <v>แตงโม 60 ลูก</v>
+        <v>ถุงขยะ 15 แพค 970</v>
       </c>
       <c r="F177">
-        <v>4200</v>
+        <v>970</v>
       </c>
     </row>
     <row r="178">
@@ -4686,18 +4686,18 @@
         <v>COGS</v>
       </c>
       <c r="D178" t="str">
-        <v>Transportation</v>
+        <v>Watermelon</v>
       </c>
       <c r="E178" t="str">
-        <v>เนื้อ 10 x 50 500</v>
+        <v>แตงโม 60 ลูก</v>
       </c>
       <c r="F178">
-        <v>2395</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>30/04/2026</v>
+        <v>29/04/2026</v>
       </c>
       <c r="B179" t="str">
         <v>Apr26</v>
@@ -4706,13 +4706,13 @@
         <v>COGS</v>
       </c>
       <c r="D179" t="str">
-        <v>Pineapple</v>
+        <v>Transportation</v>
       </c>
       <c r="E179" t="str">
-        <v>สับปะรส 3 ตะกร้า</v>
+        <v>เนื้อ 10 x 50 500</v>
       </c>
       <c r="F179">
-        <v>1500</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="180">
@@ -4723,16 +4723,16 @@
         <v>Apr26</v>
       </c>
       <c r="C180" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D180" t="str">
-        <v>Rental</v>
+        <v>Pineapple</v>
       </c>
       <c r="E180" t="str">
-        <v>Rent</v>
+        <v>สับปะรส 3 ตะกร้า</v>
       </c>
       <c r="F180">
-        <v>35000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="181">
@@ -4743,16 +4743,16 @@
         <v>Apr26</v>
       </c>
       <c r="C181" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D181" t="str">
-        <v>Stock</v>
+        <v>Rental</v>
       </c>
       <c r="E181" t="str">
-        <v>Stock (Allocated 82.9%)</v>
+        <v>Rent</v>
       </c>
       <c r="F181">
-        <v>9948</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="182">
@@ -4766,21 +4766,21 @@
         <v>COGS</v>
       </c>
       <c r="D182" t="str">
-        <v>Guava</v>
+        <v>Stock</v>
       </c>
       <c r="E182" t="str">
-        <v>ฝรั่ง ตะกร้าแรก (นาง ประนอม, BBL X8148) [bank 30/04 22:50]</v>
+        <v>Stock (Allocated 82.9%)</v>
       </c>
       <c r="F182">
-        <v>1500</v>
+        <v>9948</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>01/05/2026</v>
+        <v>30/04/2026</v>
       </c>
       <c r="B183" t="str">
-        <v>May26</v>
+        <v>Apr26</v>
       </c>
       <c r="C183" t="str">
         <v>COGS</v>
@@ -4789,10 +4789,10 @@
         <v>Guava</v>
       </c>
       <c r="E183" t="str">
-        <v>ฝรั่ง (แยกจากใบเสร็จรวม 01/05)</v>
+        <v>ฝรั่ง ตะกร้าแรก (นาง ประนอม, BBL X8148) [bank 30/04 22:50]</v>
       </c>
       <c r="F183">
-        <v>300</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="184">
@@ -4803,16 +4803,16 @@
         <v>May26</v>
       </c>
       <c r="C184" t="str">
-        <v>CAPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D184" t="str">
-        <v>Investment</v>
+        <v>Guava</v>
       </c>
       <c r="E184" t="str">
-        <v>ร่ม 2 คัน (1,176 + 843)</v>
+        <v>ฝรั่ง (แยกจากใบเสร็จรวม 01/05)</v>
       </c>
       <c r="F184">
-        <v>2019</v>
+        <v>300</v>
       </c>
     </row>
     <row r="185">
@@ -4823,16 +4823,16 @@
         <v>May26</v>
       </c>
       <c r="C185" t="str">
-        <v>COGS</v>
+        <v>CAPEX</v>
       </c>
       <c r="D185" t="str">
-        <v>Milk/Conden</v>
+        <v>Investment</v>
       </c>
       <c r="E185" t="str">
-        <v>นมข้นจืด (แยกจากใบเสร็จรวม 01/05)</v>
+        <v>ร่ม 2 คัน (1,176 + 843)</v>
       </c>
       <c r="F185">
-        <v>785</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="186">
@@ -4843,16 +4843,16 @@
         <v>May26</v>
       </c>
       <c r="C186" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D186" t="str">
-        <v>Other</v>
+        <v>Milk/Conden</v>
       </c>
       <c r="E186" t="str">
-        <v>ที่ปั๊ม (แยกจากใบเสร็จรวม 01/05)</v>
+        <v>นมข้นจืด (แยกจากใบเสร็จรวม 01/05)</v>
       </c>
       <c r="F186">
-        <v>176</v>
+        <v>785</v>
       </c>
     </row>
     <row r="187">
@@ -4869,30 +4869,30 @@
         <v>Other</v>
       </c>
       <c r="E187" t="str">
-        <v>ยอดคงเหลือใบเสร็จ 01/05 — ไม่ระบุรายการ ต้องตรวจสอบสลิป</v>
+        <v>ที่ปั๊ม (แยกจากใบเสร็จรวม 01/05)</v>
       </c>
       <c r="F187">
-        <v>4543</v>
+        <v>176</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>02/05/2026</v>
+        <v>01/05/2026</v>
       </c>
       <c r="B188" t="str">
         <v>May26</v>
       </c>
       <c r="C188" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D188" t="str">
-        <v>Mango</v>
+        <v>Other</v>
       </c>
       <c r="E188" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>ยอดคงเหลือใบเสร็จ 01/05 — ไม่ระบุรายการ ต้องตรวจสอบสลิป</v>
       </c>
       <c r="F188">
-        <v>910</v>
+        <v>4543</v>
       </c>
     </row>
     <row r="189">
@@ -4906,13 +4906,13 @@
         <v>COGS</v>
       </c>
       <c r="D189" t="str">
-        <v>Apple</v>
+        <v>Mango</v>
       </c>
       <c r="E189" t="str">
-        <v>แอปเปิ้ล 4 ลัง</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F189">
-        <v>1500</v>
+        <v>910</v>
       </c>
     </row>
     <row r="190">
@@ -4926,13 +4926,13 @@
         <v>COGS</v>
       </c>
       <c r="D190" t="str">
-        <v>Pineapple</v>
+        <v>Apple</v>
       </c>
       <c r="E190" t="str">
-        <v>สับปะรด 30 ลูก</v>
+        <v>แอปเปิ้ล 4 ลัง</v>
       </c>
       <c r="F190">
-        <v>1116</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="191">
@@ -4943,16 +4943,16 @@
         <v>May26</v>
       </c>
       <c r="C191" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D191" t="str">
-        <v>Other</v>
+        <v>Pineapple</v>
       </c>
       <c r="E191" t="str">
-        <v>ค่าหาหมอเอ</v>
+        <v>สับปะรด 30 ลูก</v>
       </c>
       <c r="F191">
-        <v>706</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="192">
@@ -4969,30 +4969,30 @@
         <v>Other</v>
       </c>
       <c r="E192" t="str">
-        <v>ค่าหมอเอ</v>
+        <v>ค่าหาหมอเอ</v>
       </c>
       <c r="F192">
-        <v>13</v>
+        <v>706</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>04/05/2026</v>
+        <v>02/05/2026</v>
       </c>
       <c r="B193" t="str">
         <v>May26</v>
       </c>
       <c r="C193" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D193" t="str">
-        <v>Packaging</v>
+        <v>Other</v>
       </c>
       <c r="E193" t="str">
-        <v>ถุงมือ4อัน</v>
+        <v>ค่าหมอเอ</v>
       </c>
       <c r="F193">
-        <v>499</v>
+        <v>13</v>
       </c>
     </row>
     <row r="194">
@@ -5006,13 +5006,13 @@
         <v>COGS</v>
       </c>
       <c r="D194" t="str">
-        <v>Apple</v>
+        <v>Packaging</v>
       </c>
       <c r="E194" t="str">
-        <v>แอปเปิ้ล 4 ลัง</v>
+        <v>ถุงมือ4อัน</v>
       </c>
       <c r="F194">
-        <v>1400</v>
+        <v>499</v>
       </c>
     </row>
     <row r="195">
@@ -5026,13 +5026,13 @@
         <v>COGS</v>
       </c>
       <c r="D195" t="str">
-        <v>Mango</v>
+        <v>Apple</v>
       </c>
       <c r="E195" t="str">
-        <v>มะม่วง 2 ลัง</v>
+        <v>แอปเปิ้ล 4 ลัง</v>
       </c>
       <c r="F195">
-        <v>1680</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="196">
@@ -5046,33 +5046,33 @@
         <v>COGS</v>
       </c>
       <c r="D196" t="str">
-        <v>Watermelon</v>
+        <v>Mango</v>
       </c>
       <c r="E196" t="str">
-        <v>30-4-2569 เบอร์ 70฿ 60 ลูก</v>
+        <v>มะม่วง 2 ลัง</v>
       </c>
       <c r="F196">
-        <v>7000</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>06/05/2026</v>
+        <v>04/05/2026</v>
       </c>
       <c r="B197" t="str">
         <v>May26</v>
       </c>
       <c r="C197" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D197" t="str">
-        <v>Other</v>
+        <v>Watermelon</v>
       </c>
       <c r="E197" t="str">
-        <v>ทิชชู่3แพค 36ห่อ</v>
+        <v>30-4-2569 เบอร์ 70฿ 60 ลูก</v>
       </c>
       <c r="F197">
-        <v>451</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="198">
@@ -5083,16 +5083,16 @@
         <v>May26</v>
       </c>
       <c r="C198" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D198" t="str">
-        <v>Mango</v>
+        <v>Other</v>
       </c>
       <c r="E198" t="str">
-        <v>มะม่วง 2 ลัง</v>
+        <v>ทิชชู่3แพค 36ห่อ</v>
       </c>
       <c r="F198">
-        <v>1750</v>
+        <v>451</v>
       </c>
     </row>
     <row r="199">
@@ -5106,13 +5106,13 @@
         <v>COGS</v>
       </c>
       <c r="D199" t="str">
-        <v>Pineapple</v>
+        <v>Mango</v>
       </c>
       <c r="E199" t="str">
-        <v>สับปะรด 18 ลูก</v>
+        <v>มะม่วง 2 ลัง</v>
       </c>
       <c r="F199">
-        <v>486</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="200">
@@ -5126,18 +5126,18 @@
         <v>COGS</v>
       </c>
       <c r="D200" t="str">
-        <v>Apple</v>
+        <v>Pineapple</v>
       </c>
       <c r="E200" t="str">
-        <v>แอปเปิ้ล 4 ลัง</v>
+        <v>สับปะรด 18 ลูก</v>
       </c>
       <c r="F200">
-        <v>1400</v>
+        <v>486</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>08/05/2026</v>
+        <v>06/05/2026</v>
       </c>
       <c r="B201" t="str">
         <v>May26</v>
@@ -5146,13 +5146,13 @@
         <v>COGS</v>
       </c>
       <c r="D201" t="str">
-        <v>Transportation</v>
+        <v>Apple</v>
       </c>
       <c r="E201" t="str">
-        <v>น้ำ 20 ขวด 900 ถอดเสื้อ 30 ลูก750 กล่องโฟม 3</v>
+        <v>แอปเปิ้ล 4 ลัง</v>
       </c>
       <c r="F201">
-        <v>4555</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="202">
@@ -5166,13 +5166,13 @@
         <v>COGS</v>
       </c>
       <c r="D202" t="str">
-        <v>Water</v>
+        <v>Transportation</v>
       </c>
       <c r="E202" t="str">
-        <v>น้ำมะร้าว 1 ลัง</v>
+        <v>น้ำ 20 ขวด 900 ถอดเสื้อ 30 ลูก750 กล่องโฟม 3</v>
       </c>
       <c r="F202">
-        <v>1100</v>
+        <v>4555</v>
       </c>
     </row>
     <row r="203">
@@ -5186,13 +5186,13 @@
         <v>COGS</v>
       </c>
       <c r="D203" t="str">
-        <v>Packaging</v>
+        <v>Water</v>
       </c>
       <c r="E203" t="str">
-        <v>6 พ.ค. น้ำ 30 ขวด 1500 บาท เนื้อ 11 โล 1320 บาท</v>
+        <v>น้ำมะร้าว 1 ลัง</v>
       </c>
       <c r="F203">
-        <v>2820</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="204">
@@ -5203,16 +5203,16 @@
         <v>May26</v>
       </c>
       <c r="C204" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D204" t="str">
-        <v>Other</v>
+        <v>Packaging</v>
       </c>
       <c r="E204" t="str">
-        <v>ค่าทำความสะอาดตึกชั้น 1</v>
+        <v>6 พ.ค. น้ำ 30 ขวด 1500 บาท เนื้อ 11 โล 1320 บาท</v>
       </c>
       <c r="F204">
-        <v>2700</v>
+        <v>2820</v>
       </c>
     </row>
     <row r="205">
@@ -5223,36 +5223,36 @@
         <v>May26</v>
       </c>
       <c r="C205" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D205" t="str">
-        <v>Watermelon</v>
+        <v>Other</v>
       </c>
       <c r="E205" t="str">
-        <v>4-5-2569 เบอร์ 70฿ 60 ลูก ยอด 4,200</v>
+        <v>ค่าทำความสะอาดตึกชั้น 1</v>
       </c>
       <c r="F205">
-        <v>8200</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>09/05/2026</v>
+        <v>08/05/2026</v>
       </c>
       <c r="B206" t="str">
         <v>May26</v>
       </c>
       <c r="C206" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D206" t="str">
-        <v>Other</v>
+        <v>Watermelon</v>
       </c>
       <c r="E206" t="str">
-        <v>พรหมเช็ดเท้า 1 ผืน</v>
+        <v>4-5-2569 เบอร์ 70฿ 60 ลูก ยอด 4,200</v>
       </c>
       <c r="F206">
-        <v>372</v>
+        <v>8200</v>
       </c>
     </row>
     <row r="207">
@@ -5263,16 +5263,16 @@
         <v>May26</v>
       </c>
       <c r="C207" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D207" t="str">
-        <v>Milk/Conden</v>
+        <v>Other</v>
       </c>
       <c r="E207" t="str">
-        <v>นมข้นจืด 1ลัง 636</v>
+        <v>พรหมเช็ดเท้า 1 ผืน</v>
       </c>
       <c r="F207">
-        <v>1122</v>
+        <v>372</v>
       </c>
     </row>
     <row r="208">
@@ -5286,13 +5286,13 @@
         <v>COGS</v>
       </c>
       <c r="D208" t="str">
-        <v>Packaging</v>
+        <v>Milk/Conden</v>
       </c>
       <c r="E208" t="str">
-        <v>นมข้น 3 ลัง 2568</v>
+        <v>นมข้นจืด 1 ลัง 636</v>
       </c>
       <c r="F208">
-        <v>4875</v>
+        <v>636</v>
       </c>
     </row>
     <row r="209">
@@ -5303,16 +5303,16 @@
         <v>May26</v>
       </c>
       <c r="C209" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D209" t="str">
-        <v>Packaging</v>
+        <v>Other</v>
       </c>
       <c r="E209" t="str">
-        <v>แก้ว3ลัง 5,301</v>
+        <v>ลิ้นชักเก็บเงิน 486</v>
       </c>
       <c r="F209">
-        <v>6132</v>
+        <v>486</v>
       </c>
     </row>
     <row r="210">
@@ -5326,13 +5326,13 @@
         <v>COGS</v>
       </c>
       <c r="D210" t="str">
-        <v>Packaging</v>
+        <v>Milk/Conden</v>
       </c>
       <c r="E210" t="str">
-        <v>ถุงมือ 20 กล่อง 2246 ฝา1ลัง 969</v>
+        <v>นมข้น 3 ลัง 2,568 + นมข้นจืด 2 ลัง 1,479</v>
       </c>
       <c r="F210">
-        <v>4496</v>
+        <v>4047</v>
       </c>
     </row>
     <row r="211">
@@ -5346,38 +5346,38 @@
         <v>COGS</v>
       </c>
       <c r="D211" t="str">
-        <v>Transportation</v>
+        <v>Packaging</v>
       </c>
       <c r="E211" t="str">
-        <v>Lalamove</v>
+        <v>ฝา 1 ลัง 828</v>
       </c>
       <c r="F211">
-        <v>2000</v>
+        <v>828</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>10/05/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="B212" t="str">
         <v>May26</v>
       </c>
       <c r="C212" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D212" t="str">
-        <v>Other</v>
+        <v>Packaging</v>
       </c>
       <c r="E212" t="str">
-        <v>ไฟ 2อัน 422</v>
+        <v>แก้ว3ลัง 5,301</v>
       </c>
       <c r="F212">
-        <v>838</v>
+        <v>6132</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>11/05/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="B213" t="str">
         <v>May26</v>
@@ -5386,18 +5386,18 @@
         <v>COGS</v>
       </c>
       <c r="D213" t="str">
-        <v>Guava</v>
+        <v>Packaging</v>
       </c>
       <c r="E213" t="str">
-        <v>ฝรั่ง 1 ตะกร้า</v>
+        <v>ถุงมือ 20 กล่อง 2246 ฝา1ลัง 969</v>
       </c>
       <c r="F213">
-        <v>600</v>
+        <v>4496</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>11/05/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="B214" t="str">
         <v>May26</v>
@@ -5406,38 +5406,38 @@
         <v>COGS</v>
       </c>
       <c r="D214" t="str">
-        <v>Mango</v>
+        <v>Transportation</v>
       </c>
       <c r="E214" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>Lalamove</v>
       </c>
       <c r="F214">
-        <v>910</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>11/05/2026</v>
+        <v>10/05/2026</v>
       </c>
       <c r="B215" t="str">
         <v>May26</v>
       </c>
       <c r="C215" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D215" t="str">
-        <v>Watermelon</v>
+        <v>Other</v>
       </c>
       <c r="E215" t="str">
-        <v>แตงโม 4000 วันที่ 9-5-26</v>
+        <v>ไฟ 2อัน 422</v>
       </c>
       <c r="F215">
-        <v>4000</v>
+        <v>838</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>12/05/2026</v>
+        <v>11/05/2026</v>
       </c>
       <c r="B216" t="str">
         <v>May26</v>
@@ -5446,38 +5446,38 @@
         <v>COGS</v>
       </c>
       <c r="D216" t="str">
-        <v>Coconut Meat</v>
+        <v>Guava</v>
       </c>
       <c r="E216" t="str">
-        <v>เนื้อมะพร้าว 1 ลัง</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F216">
-        <v>3500</v>
+        <v>600</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>13/05/2026</v>
+        <v>11/05/2026</v>
       </c>
       <c r="B217" t="str">
         <v>May26</v>
       </c>
       <c r="C217" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D217" t="str">
-        <v>Other</v>
+        <v>Mango</v>
       </c>
       <c r="E217" t="str">
-        <v>ที่หนีบ 6ตัว 374 บาท</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F217">
-        <v>374</v>
+        <v>910</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>13/05/2026</v>
+        <v>11/05/2026</v>
       </c>
       <c r="B218" t="str">
         <v>May26</v>
@@ -5486,18 +5486,18 @@
         <v>COGS</v>
       </c>
       <c r="D218" t="str">
-        <v>Pineapple</v>
+        <v>Watermelon</v>
       </c>
       <c r="E218" t="str">
-        <v>09/05/26 สับปะรด 2 ตะกร้า</v>
+        <v>แตงโม 4000 วันที่ 9-5-26</v>
       </c>
       <c r="F218">
-        <v>1008</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>14/05/2026</v>
+        <v>12/05/2026</v>
       </c>
       <c r="B219" t="str">
         <v>May26</v>
@@ -5506,18 +5506,18 @@
         <v>COGS</v>
       </c>
       <c r="D219" t="str">
-        <v>Watermelon</v>
+        <v>Coconut Meat</v>
       </c>
       <c r="E219" t="str">
-        <v>11-5-2569 50 ลูก ยอด 4,000</v>
+        <v>เนื้อมะพร้าว 1 ลัง</v>
       </c>
       <c r="F219">
-        <v>8000</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>14/05/2026</v>
+        <v>13/05/2026</v>
       </c>
       <c r="B220" t="str">
         <v>May26</v>
@@ -5526,33 +5526,33 @@
         <v>OPEX</v>
       </c>
       <c r="D220" t="str">
-        <v>Rental</v>
+        <v>Other</v>
       </c>
       <c r="E220" t="str">
-        <v>ค่าเช่าร้าน 1 พ.ค.</v>
+        <v>ที่หนีบ 6ตัว 374 บาท</v>
       </c>
       <c r="F220">
-        <v>35000</v>
+        <v>374</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>14/05/2026</v>
+        <v>13/05/2026</v>
       </c>
       <c r="B221" t="str">
         <v>May26</v>
       </c>
       <c r="C221" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D221" t="str">
-        <v>Rental</v>
+        <v>Pineapple</v>
       </c>
       <c r="E221" t="str">
-        <v>ค่าเช่าคลัง พ.ค. (B1 ครึ่งหนึ่ง)</v>
+        <v>09/05/26 สับปะรด 2 ตะกร้า</v>
       </c>
       <c r="F221">
-        <v>6000</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="222">
@@ -5566,13 +5566,13 @@
         <v>COGS</v>
       </c>
       <c r="D222" t="str">
-        <v>Guava</v>
+        <v>Watermelon</v>
       </c>
       <c r="E222" t="str">
-        <v>ฝรั่ง 1 ตะกร้า</v>
+        <v>11-5-2569 50 ลูก ยอด 4,000</v>
       </c>
       <c r="F222">
-        <v>600</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="223">
@@ -5583,16 +5583,16 @@
         <v>May26</v>
       </c>
       <c r="C223" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D223" t="str">
-        <v>Apple</v>
+        <v>Rental</v>
       </c>
       <c r="E223" t="str">
-        <v>แอปเปิ้ล 3 ลัง</v>
+        <v>ค่าเช่าร้าน 1 พ.ค.</v>
       </c>
       <c r="F223">
-        <v>1050</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="224">
@@ -5603,21 +5603,21 @@
         <v>May26</v>
       </c>
       <c r="C224" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D224" t="str">
-        <v>Mango</v>
+        <v>Rental</v>
       </c>
       <c r="E224" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>ค่าเช่าคลัง พ.ค. (B1 ครึ่งหนึ่ง)</v>
       </c>
       <c r="F224">
-        <v>875</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>15/05/2026</v>
+        <v>14/05/2026</v>
       </c>
       <c r="B225" t="str">
         <v>May26</v>
@@ -5626,18 +5626,18 @@
         <v>COGS</v>
       </c>
       <c r="D225" t="str">
-        <v>Orange</v>
+        <v>Guava</v>
       </c>
       <c r="E225" t="str">
-        <v>ส้ม 22x22กก 484 กก. x30 = 14,520 + ค่าส่ง 22x55 = 1,210 (15/05/69)</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F225">
-        <v>15730</v>
+        <v>600</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>15/05/2026</v>
+        <v>14/05/2026</v>
       </c>
       <c r="B226" t="str">
         <v>May26</v>
@@ -5646,38 +5646,38 @@
         <v>COGS</v>
       </c>
       <c r="D226" t="str">
-        <v>Orange</v>
+        <v>Apple</v>
       </c>
       <c r="E226" t="str">
-        <v>05/05/69 ส้ม 30x22กก 660กกx30</v>
+        <v>แอปเปิ้ล 3 ลัง</v>
       </c>
       <c r="F226">
-        <v>21450</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>16/05/2026</v>
+        <v>14/05/2026</v>
       </c>
       <c r="B227" t="str">
         <v>May26</v>
       </c>
       <c r="C227" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D227" t="str">
-        <v>Other</v>
+        <v>Mango</v>
       </c>
       <c r="E227" t="str">
-        <v>Police fees -2000 2 head</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F227">
-        <v>4290</v>
+        <v>875</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>16/05/2026</v>
+        <v>15/05/2026</v>
       </c>
       <c r="B228" t="str">
         <v>May26</v>
@@ -5686,18 +5686,18 @@
         <v>COGS</v>
       </c>
       <c r="D228" t="str">
-        <v>Coconut</v>
+        <v>Orange</v>
       </c>
       <c r="E228" t="str">
-        <v>มะพร้าว 20 โล</v>
+        <v>ส้ม 22x22กก 484 กก. x30 = 14,520 + ค่าส่ง 22x55 = 1,210 (15/05/69)</v>
       </c>
       <c r="F228">
-        <v>2400</v>
+        <v>15730</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>16/05/2026</v>
+        <v>15/05/2026</v>
       </c>
       <c r="B229" t="str">
         <v>May26</v>
@@ -5706,13 +5706,13 @@
         <v>COGS</v>
       </c>
       <c r="D229" t="str">
-        <v>Watermelon</v>
+        <v>Orange</v>
       </c>
       <c r="E229" t="str">
-        <v>14/05/26 18 ลูก 504 บาท 16/05/26 18 ลูก</v>
+        <v>05/05/69 ส้ม 30x22กก 660กกx30</v>
       </c>
       <c r="F229">
-        <v>1008</v>
+        <v>21450</v>
       </c>
     </row>
     <row r="230">
@@ -5723,21 +5723,21 @@
         <v>May26</v>
       </c>
       <c r="C230" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D230" t="str">
-        <v>Mango</v>
+        <v>Other</v>
       </c>
       <c r="E230" t="str">
-        <v>มะม่วง 1</v>
+        <v>Police fees -2000 2 head</v>
       </c>
       <c r="F230">
-        <v>875</v>
+        <v>4290</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>19/05/2026</v>
+        <v>16/05/2026</v>
       </c>
       <c r="B231" t="str">
         <v>May26</v>
@@ -5746,18 +5746,18 @@
         <v>COGS</v>
       </c>
       <c r="D231" t="str">
-        <v>Mango</v>
+        <v>Coconut</v>
       </c>
       <c r="E231" t="str">
-        <v>มะม่วง 1 ลัง (25 โล)</v>
+        <v>มะพร้าว 20 โล</v>
       </c>
       <c r="F231">
-        <v>875</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>19/05/2026</v>
+        <v>16/05/2026</v>
       </c>
       <c r="B232" t="str">
         <v>May26</v>
@@ -5766,18 +5766,18 @@
         <v>COGS</v>
       </c>
       <c r="D232" t="str">
-        <v>Guava</v>
+        <v>Watermelon</v>
       </c>
       <c r="E232" t="str">
-        <v>ฝรั่ง 1 ลัง</v>
+        <v>14/05/26 18 ลูก 504 บาท 16/05/26 18 ลูก</v>
       </c>
       <c r="F232">
-        <v>600</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>19/05/2026</v>
+        <v>16/05/2026</v>
       </c>
       <c r="B233" t="str">
         <v>May26</v>
@@ -5786,13 +5786,13 @@
         <v>COGS</v>
       </c>
       <c r="D233" t="str">
-        <v>Apple</v>
+        <v>Mango</v>
       </c>
       <c r="E233" t="str">
-        <v>แอปเปิ้ล 4 ลังครับ</v>
+        <v>มะม่วง 1</v>
       </c>
       <c r="F233">
-        <v>1400</v>
+        <v>875</v>
       </c>
     </row>
     <row r="234">
@@ -5806,18 +5806,18 @@
         <v>COGS</v>
       </c>
       <c r="D234" t="str">
-        <v>Pineapple</v>
+        <v>Mango</v>
       </c>
       <c r="E234" t="str">
-        <v>36*18 648</v>
+        <v>มะม่วง 1 ลัง (25 โล)</v>
       </c>
       <c r="F234">
-        <v>648</v>
+        <v>875</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>22/05/2026</v>
+        <v>19/05/2026</v>
       </c>
       <c r="B235" t="str">
         <v>May26</v>
@@ -5826,18 +5826,18 @@
         <v>COGS</v>
       </c>
       <c r="D235" t="str">
-        <v>Apple</v>
+        <v>Guava</v>
       </c>
       <c r="E235" t="str">
-        <v>แอปเปิ้ล 2 ลัง</v>
+        <v>ฝรั่ง 1 ลัง</v>
       </c>
       <c r="F235">
-        <v>700</v>
+        <v>600</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>22/05/2026</v>
+        <v>19/05/2026</v>
       </c>
       <c r="B236" t="str">
         <v>May26</v>
@@ -5846,18 +5846,18 @@
         <v>COGS</v>
       </c>
       <c r="D236" t="str">
-        <v>Pineapple</v>
+        <v>Apple</v>
       </c>
       <c r="E236" t="str">
-        <v>สับปะรด 18 ลูก</v>
+        <v>แอปเปิ้ล 4 ลังครับ</v>
       </c>
       <c r="F236">
-        <v>522</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>22/05/2026</v>
+        <v>19/05/2026</v>
       </c>
       <c r="B237" t="str">
         <v>May26</v>
@@ -5866,13 +5866,13 @@
         <v>COGS</v>
       </c>
       <c r="D237" t="str">
-        <v>Mango</v>
+        <v>Pineapple</v>
       </c>
       <c r="E237" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>36*18 648</v>
       </c>
       <c r="F237">
-        <v>1000</v>
+        <v>648</v>
       </c>
     </row>
     <row r="238">
@@ -5886,13 +5886,13 @@
         <v>COGS</v>
       </c>
       <c r="D238" t="str">
-        <v>Watermelon</v>
+        <v>Apple</v>
       </c>
       <c r="E238" t="str">
-        <v>16-5-2569ยอด 4,000฿</v>
+        <v>แอปเปิ้ล 2 ลัง</v>
       </c>
       <c r="F238">
-        <v>12000</v>
+        <v>700</v>
       </c>
     </row>
     <row r="239">
@@ -5906,13 +5906,13 @@
         <v>COGS</v>
       </c>
       <c r="D239" t="str">
-        <v>Guava</v>
+        <v>Pineapple</v>
       </c>
       <c r="E239" t="str">
-        <v>ฝรั่ง 1 ตะกร้า</v>
+        <v>สับปะรด 18 ลูก</v>
       </c>
       <c r="F239">
-        <v>600</v>
+        <v>522</v>
       </c>
     </row>
     <row r="240">
@@ -5926,18 +5926,18 @@
         <v>COGS</v>
       </c>
       <c r="D240" t="str">
-        <v>Transportation</v>
+        <v>Mango</v>
       </c>
       <c r="E240" t="str">
-        <v>ค่าขนส่ง</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F240">
-        <v>2000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>23/05/2026</v>
+        <v>22/05/2026</v>
       </c>
       <c r="B241" t="str">
         <v>May26</v>
@@ -5946,18 +5946,18 @@
         <v>COGS</v>
       </c>
       <c r="D241" t="str">
-        <v>Packaging</v>
+        <v>Watermelon</v>
       </c>
       <c r="E241" t="str">
-        <v>แก้ว 3 ลัง</v>
+        <v>16-5-2569ยอด 4,000฿</v>
       </c>
       <c r="F241">
-        <v>4680</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>23/05/2026</v>
+        <v>22/05/2026</v>
       </c>
       <c r="B242" t="str">
         <v>May26</v>
@@ -5966,18 +5966,18 @@
         <v>COGS</v>
       </c>
       <c r="D242" t="str">
-        <v>Packaging</v>
+        <v>Guava</v>
       </c>
       <c r="E242" t="str">
-        <v>ฝา1 788</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F242">
-        <v>2902</v>
+        <v>600</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>23/05/2026</v>
+        <v>22/05/2026</v>
       </c>
       <c r="B243" t="str">
         <v>May26</v>
@@ -5986,18 +5986,18 @@
         <v>COGS</v>
       </c>
       <c r="D243" t="str">
-        <v>Packaging</v>
+        <v>Transportation</v>
       </c>
       <c r="E243" t="str">
-        <v>หลอด20 แพค (767)</v>
+        <v>ค่าขนส่ง</v>
       </c>
       <c r="F243">
-        <v>1502</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>25/05/2026</v>
+        <v>23/05/2026</v>
       </c>
       <c r="B244" t="str">
         <v>May26</v>
@@ -6006,18 +6006,18 @@
         <v>COGS</v>
       </c>
       <c r="D244" t="str">
-        <v>Pineapple</v>
+        <v>Packaging</v>
       </c>
       <c r="E244" t="str">
-        <v>สับปะรด 18 ลูก</v>
+        <v>แก้ว 3 ลัง</v>
       </c>
       <c r="F244">
-        <v>594</v>
+        <v>4680</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>25/05/2026</v>
+        <v>23/05/2026</v>
       </c>
       <c r="B245" t="str">
         <v>May26</v>
@@ -6026,18 +6026,18 @@
         <v>COGS</v>
       </c>
       <c r="D245" t="str">
-        <v>Apple</v>
+        <v>Packaging</v>
       </c>
       <c r="E245" t="str">
-        <v>แอปเปิ้ล 3 ลังครับ</v>
+        <v>ฝา1 788</v>
       </c>
       <c r="F245">
-        <v>1050</v>
+        <v>2902</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>25/05/2026</v>
+        <v>23/05/2026</v>
       </c>
       <c r="B246" t="str">
         <v>May26</v>
@@ -6046,13 +6046,13 @@
         <v>COGS</v>
       </c>
       <c r="D246" t="str">
-        <v>Orange</v>
+        <v>Packaging</v>
       </c>
       <c r="E246" t="str">
-        <v>ค่าส่งส้ม Lalamove หักผ่านบัตร</v>
+        <v>หลอด20 แพค (767)</v>
       </c>
       <c r="F246">
-        <v>1245</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="247">
@@ -6066,13 +6066,13 @@
         <v>COGS</v>
       </c>
       <c r="D247" t="str">
-        <v>Orange</v>
+        <v>Pineapple</v>
       </c>
       <c r="E247" t="str">
-        <v>ส้ม 21x22กก 462 กก. x30 = 13,860 + ค่าส่ง 21x55 = 1,155 (24/05/69)</v>
+        <v>สับปะรด 18 ลูก</v>
       </c>
       <c r="F247">
-        <v>15015</v>
+        <v>594</v>
       </c>
     </row>
     <row r="248">
@@ -6083,16 +6083,16 @@
         <v>May26</v>
       </c>
       <c r="C248" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D248" t="str">
-        <v>Salary</v>
+        <v>Apple</v>
       </c>
       <c r="E248" t="str">
-        <v>เงินเดือนซี เดือนพ.ค. (แก้ไข: ยืนยัน 24,000)</v>
+        <v>แอปเปิ้ล 3 ลังครับ</v>
       </c>
       <c r="F248">
-        <v>24000</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="249">
@@ -6106,13 +6106,13 @@
         <v>COGS</v>
       </c>
       <c r="D249" t="str">
-        <v>Guava</v>
+        <v>Orange</v>
       </c>
       <c r="E249" t="str">
-        <v>ฝรั่ง 1 ตะกร้า</v>
+        <v>ค่าส่งส้ม Lalamove หักผ่านบัตร</v>
       </c>
       <c r="F249">
-        <v>600</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="250">
@@ -6126,18 +6126,18 @@
         <v>COGS</v>
       </c>
       <c r="D250" t="str">
-        <v>Mango</v>
+        <v>Orange</v>
       </c>
       <c r="E250" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>ส้ม 21x22กก 462 กก. x30 = 13,860 + ค่าส่ง 21x55 = 1,155 (24/05/69)</v>
       </c>
       <c r="F250">
-        <v>1000</v>
+        <v>15015</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>27/05/2026</v>
+        <v>25/05/2026</v>
       </c>
       <c r="B251" t="str">
         <v>May26</v>
@@ -6149,35 +6149,35 @@
         <v>Salary</v>
       </c>
       <c r="E251" t="str">
-        <v>เงินเดือนเมน 5/26</v>
+        <v>เงินเดือนซี เดือนพ.ค. (แก้ไข: ยืนยัน 24,000)</v>
       </c>
       <c r="F251">
-        <v>19000</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>28/05/2026</v>
+        <v>25/05/2026</v>
       </c>
       <c r="B252" t="str">
         <v>May26</v>
       </c>
       <c r="C252" t="str">
-        <v>CAPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D252" t="str">
-        <v>Investment</v>
+        <v>Guava</v>
       </c>
       <c r="E252" t="str">
-        <v>เครื่องสกัดเย็น 1</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F252">
-        <v>1065</v>
+        <v>600</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>28/05/2026</v>
+        <v>25/05/2026</v>
       </c>
       <c r="B253" t="str">
         <v>May26</v>
@@ -6186,73 +6186,73 @@
         <v>COGS</v>
       </c>
       <c r="D253" t="str">
-        <v>Coconut</v>
+        <v>Mango</v>
       </c>
       <c r="E253" t="str">
-        <v>มะพร้าวถอดเสื้อ 23 ลูก *35 ราคา 805 ค่าส่ง 150</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F253">
-        <v>955</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>30/05/2026</v>
+        <v>27/05/2026</v>
       </c>
       <c r="B254" t="str">
         <v>May26</v>
       </c>
       <c r="C254" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D254" t="str">
-        <v>Pineapple</v>
+        <v>Salary</v>
       </c>
       <c r="E254" t="str">
-        <v>สับปะรด 18 ลูก</v>
+        <v>เงินเดือนเมน 5/26</v>
       </c>
       <c r="F254">
-        <v>576</v>
+        <v>19000</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>30/05/2026</v>
+        <v>28/05/2026</v>
       </c>
       <c r="B255" t="str">
         <v>May26</v>
       </c>
       <c r="C255" t="str">
-        <v>COGS</v>
+        <v>CAPEX</v>
       </c>
       <c r="D255" t="str">
-        <v>Mango</v>
+        <v>Investment</v>
       </c>
       <c r="E255" t="str">
-        <v>มะม่วง 1 ตะกร้า</v>
+        <v>เครื่องสกัดเย็น 1</v>
       </c>
       <c r="F255">
-        <v>960</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>30/05/2026</v>
+        <v>28/05/2026</v>
       </c>
       <c r="B256" t="str">
         <v>May26</v>
       </c>
       <c r="C256" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D256" t="str">
-        <v>Other</v>
+        <v>Coconut</v>
       </c>
       <c r="E256" t="str">
-        <v>Unknown</v>
+        <v>มะพร้าวถอดเสื้อ 23 ลูก *35 ราคา 805 ค่าส่ง 150</v>
       </c>
       <c r="F256">
-        <v>1050</v>
+        <v>955</v>
       </c>
     </row>
     <row r="257">
@@ -6266,18 +6266,18 @@
         <v>COGS</v>
       </c>
       <c r="D257" t="str">
-        <v>Guava</v>
+        <v>Pineapple</v>
       </c>
       <c r="E257" t="str">
-        <v>ฝรั่ง 1 ตะกร้า</v>
+        <v>สับปะรด 18 ลูก</v>
       </c>
       <c r="F257">
-        <v>600</v>
+        <v>576</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>31/05/2026</v>
+        <v>30/05/2026</v>
       </c>
       <c r="B258" t="str">
         <v>May26</v>
@@ -6286,18 +6286,18 @@
         <v>COGS</v>
       </c>
       <c r="D258" t="str">
-        <v>Stock</v>
+        <v>Mango</v>
       </c>
       <c r="E258" t="str">
-        <v>Stock Adjustment (Allocated to B2)</v>
+        <v>มะม่วง 1 ตะกร้า</v>
       </c>
       <c r="F258">
-        <v>-4830</v>
+        <v>960</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>01/06/2026</v>
+        <v>30/05/2026</v>
       </c>
       <c r="B259" t="str">
         <v>May26</v>
@@ -6306,78 +6306,78 @@
         <v>OPEX</v>
       </c>
       <c r="D259" t="str">
-        <v>Salary</v>
+        <v>Other</v>
       </c>
       <c r="E259" t="str">
         <v>Unknown</v>
       </c>
       <c r="F259">
-        <v>0</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>02/06/2026</v>
+        <v>30/05/2026</v>
       </c>
       <c r="B260" t="str">
-        <v>Jun26</v>
+        <v>May26</v>
       </c>
       <c r="C260" t="str">
         <v>COGS</v>
       </c>
       <c r="D260" t="str">
-        <v>Pineapple</v>
+        <v>Guava</v>
       </c>
       <c r="E260" t="str">
-        <v>สับปะรด ราคา 31*18 ลูก 558</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F260">
-        <v>558</v>
+        <v>600</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>02/06/2026</v>
+        <v>31/05/2026</v>
       </c>
       <c r="B261" t="str">
-        <v>Jun26</v>
+        <v>May26</v>
       </c>
       <c r="C261" t="str">
         <v>COGS</v>
       </c>
       <c r="D261" t="str">
-        <v>Guava</v>
+        <v>Stock</v>
       </c>
       <c r="E261" t="str">
-        <v>ฝรั่ง 1 ตะกร้า</v>
+        <v>Stock Adjustment (Allocated to B2)</v>
       </c>
       <c r="F261">
-        <v>600</v>
+        <v>-4830</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>02/06/2026</v>
+        <v>01/06/2026</v>
       </c>
       <c r="B262" t="str">
-        <v>Jun26</v>
+        <v>May26</v>
       </c>
       <c r="C262" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D262" t="str">
-        <v>Watermelon</v>
+        <v>Salary</v>
       </c>
       <c r="E262" t="str">
-        <v>แตงโม 160 ลูก (25-5-2569: 80 ลูก, 30-5-2569: 80 ลูก)</v>
+        <v>Unknown</v>
       </c>
       <c r="F262">
-        <v>8000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>04/06/2026</v>
+        <v>02/06/2026</v>
       </c>
       <c r="B263" t="str">
         <v>Jun26</v>
@@ -6386,18 +6386,18 @@
         <v>COGS</v>
       </c>
       <c r="D263" t="str">
-        <v>Watermelon</v>
+        <v>Pineapple</v>
       </c>
       <c r="E263" t="str">
-        <v>สลิปรวม: แตงโม 750 (audit fix, was bundled into Pineapple line)</v>
+        <v>สับปะรด ราคา 31*18 ลูก 558</v>
       </c>
       <c r="F263">
-        <v>750</v>
+        <v>558</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>04/06/2026</v>
+        <v>02/06/2026</v>
       </c>
       <c r="B264" t="str">
         <v>Jun26</v>
@@ -6412,12 +6412,12 @@
         <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F264">
-        <v>700</v>
+        <v>600</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>04/06/2026</v>
+        <v>02/06/2026</v>
       </c>
       <c r="B265" t="str">
         <v>Jun26</v>
@@ -6426,13 +6426,13 @@
         <v>COGS</v>
       </c>
       <c r="D265" t="str">
-        <v>Mango</v>
+        <v>Watermelon</v>
       </c>
       <c r="E265" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>แตงโม 160 ลูก (25-5-2569: 80 ลูก, 30-5-2569: 80 ลูก)</v>
       </c>
       <c r="F265">
-        <v>1040</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="266">
@@ -6446,13 +6446,13 @@
         <v>COGS</v>
       </c>
       <c r="D266" t="str">
-        <v>Apple</v>
+        <v>Watermelon</v>
       </c>
       <c r="E266" t="str">
-        <v>แอพเปิ้ล 4 ลัง</v>
+        <v>สลิปรวม: แตงโม 750 (audit fix, was bundled into Pineapple line)</v>
       </c>
       <c r="F266">
-        <v>1400</v>
+        <v>750</v>
       </c>
     </row>
     <row r="267">
@@ -6466,13 +6466,13 @@
         <v>COGS</v>
       </c>
       <c r="D267" t="str">
-        <v>Pineapple</v>
+        <v>Guava</v>
       </c>
       <c r="E267" t="str">
-        <v>สับปะรด 2 ลูก</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F267">
-        <v>36</v>
+        <v>700</v>
       </c>
     </row>
     <row r="268">
@@ -6486,18 +6486,18 @@
         <v>COGS</v>
       </c>
       <c r="D268" t="str">
-        <v>Packaging</v>
+        <v>Mango</v>
       </c>
       <c r="E268" t="str">
-        <v>ขวดใหญ่ 1000ml 98 ใบ 364 ถุงเล็ก 20</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F268">
-        <v>764</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>05/06/2026</v>
+        <v>04/06/2026</v>
       </c>
       <c r="B269" t="str">
         <v>Jun26</v>
@@ -6506,18 +6506,18 @@
         <v>COGS</v>
       </c>
       <c r="D269" t="str">
-        <v>Pineapple</v>
+        <v>Apple</v>
       </c>
       <c r="E269" t="str">
-        <v>สับปะรด 33*18 รวม 594</v>
+        <v>แอพเปิ้ล 4 ลัง</v>
       </c>
       <c r="F269">
-        <v>594</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>05/06/2026</v>
+        <v>04/06/2026</v>
       </c>
       <c r="B270" t="str">
         <v>Jun26</v>
@@ -6526,18 +6526,18 @@
         <v>COGS</v>
       </c>
       <c r="D270" t="str">
-        <v>Watermelon</v>
+        <v>Pineapple</v>
       </c>
       <c r="E270" t="str">
-        <v>แตงโม 100 ลูก (2-6-2569: 50 ลูก, 4-6-2569: 50 ลูก)</v>
+        <v>สับปะรด 2 ลูก</v>
       </c>
       <c r="F270">
-        <v>8000</v>
+        <v>36</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>07/06/2026</v>
+        <v>04/06/2026</v>
       </c>
       <c r="B271" t="str">
         <v>Jun26</v>
@@ -6546,18 +6546,18 @@
         <v>COGS</v>
       </c>
       <c r="D271" t="str">
-        <v>Orange</v>
+        <v>Packaging</v>
       </c>
       <c r="E271" t="str">
-        <v>ส้ม 20x22กก 440กกx30 13,200บาท</v>
+        <v>ขวดใหญ่ 1000ml 98 ใบ 364 ถุงเล็ก 20</v>
       </c>
       <c r="F271">
-        <v>14300</v>
+        <v>764</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>08/06/2026</v>
+        <v>05/06/2026</v>
       </c>
       <c r="B272" t="str">
         <v>Jun26</v>
@@ -6566,18 +6566,18 @@
         <v>COGS</v>
       </c>
       <c r="D272" t="str">
-        <v>Transportation</v>
+        <v>Pineapple</v>
       </c>
       <c r="E272" t="str">
-        <v>Lalamove</v>
+        <v>สับปะรด 33*18 รวม 594</v>
       </c>
       <c r="F272">
-        <v>2000</v>
+        <v>594</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>08/06/2026</v>
+        <v>05/06/2026</v>
       </c>
       <c r="B273" t="str">
         <v>Jun26</v>
@@ -6586,33 +6586,33 @@
         <v>COGS</v>
       </c>
       <c r="D273" t="str">
-        <v>Stock</v>
+        <v>Watermelon</v>
       </c>
       <c r="E273" t="str">
-        <v>Stock June 2026 (B1 ครึ่งหนึ่ง 6,000; B2 ถืออีก 6,000)</v>
+        <v>แตงโม 100 ลูก (2-6-2569: 50 ลูก, 4-6-2569: 50 ลูก)</v>
       </c>
       <c r="F273">
-        <v>6000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>08/06/2026</v>
+        <v>07/06/2026</v>
       </c>
       <c r="B274" t="str">
         <v>Jun26</v>
       </c>
       <c r="C274" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D274" t="str">
-        <v>Rental</v>
+        <v>Orange</v>
       </c>
       <c r="E274" t="str">
-        <v>ค่าเช่าร้านเดือน June (06) b1 35000</v>
+        <v>ส้ม 20x22กก 440กกx30 13,200บาท</v>
       </c>
       <c r="F274">
-        <v>35000</v>
+        <v>14300</v>
       </c>
     </row>
     <row r="275">
@@ -6626,13 +6626,13 @@
         <v>COGS</v>
       </c>
       <c r="D275" t="str">
-        <v>Pineapple</v>
+        <v>Transportation</v>
       </c>
       <c r="E275" t="str">
-        <v>สับปะรด 15 ลูก</v>
+        <v>Lalamove</v>
       </c>
       <c r="F275">
-        <v>504</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="276">
@@ -6646,13 +6646,13 @@
         <v>COGS</v>
       </c>
       <c r="D276" t="str">
-        <v>Mango</v>
+        <v>Stock</v>
       </c>
       <c r="E276" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>Stock June 2026 (B1 ครึ่งหนึ่ง 6,000; B2 ถืออีก 6,000)</v>
       </c>
       <c r="F276">
-        <v>1170</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="277">
@@ -6663,16 +6663,16 @@
         <v>Jun26</v>
       </c>
       <c r="C277" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D277" t="str">
-        <v>Apple</v>
+        <v>Rental</v>
       </c>
       <c r="E277" t="str">
-        <v>แอปเปิ้ล 5 ลัง</v>
+        <v>ค่าเช่าร้านเดือน June (06) b1 35000</v>
       </c>
       <c r="F277">
-        <v>1750</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="278">
@@ -6686,18 +6686,18 @@
         <v>COGS</v>
       </c>
       <c r="D278" t="str">
-        <v>Guava</v>
+        <v>Pineapple</v>
       </c>
       <c r="E278" t="str">
-        <v>ฝรั่ง 1 ตะกร้า</v>
+        <v>สับปะรด 15 ลูก</v>
       </c>
       <c r="F278">
-        <v>700</v>
+        <v>504</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>09/06/2026</v>
+        <v>08/06/2026</v>
       </c>
       <c r="B279" t="str">
         <v>Jun26</v>
@@ -6706,18 +6706,18 @@
         <v>COGS</v>
       </c>
       <c r="D279" t="str">
-        <v>Packaging</v>
+        <v>Mango</v>
       </c>
       <c r="E279" t="str">
-        <v>แก้ว 1937*3 รวม 5,811</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F279">
-        <v>6659</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>09/06/2026</v>
+        <v>08/06/2026</v>
       </c>
       <c r="B280" t="str">
         <v>Jun26</v>
@@ -6726,18 +6726,18 @@
         <v>COGS</v>
       </c>
       <c r="D280" t="str">
-        <v>Packaging</v>
+        <v>Apple</v>
       </c>
       <c r="E280" t="str">
-        <v>หลอด 20 แพ็ก 671</v>
+        <v>แอปเปิ้ล 5 ลัง</v>
       </c>
       <c r="F280">
-        <v>1149</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>09/06/2026</v>
+        <v>08/06/2026</v>
       </c>
       <c r="B281" t="str">
         <v>Jun26</v>
@@ -6746,13 +6746,13 @@
         <v>COGS</v>
       </c>
       <c r="D281" t="str">
-        <v>Packaging</v>
+        <v>Guava</v>
       </c>
       <c r="E281" t="str">
-        <v>ฝา1 714</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F281">
-        <v>714</v>
+        <v>700</v>
       </c>
     </row>
     <row r="282">
@@ -6769,15 +6769,15 @@
         <v>Packaging</v>
       </c>
       <c r="E282" t="str">
-        <v>ถุงขยะ 4แพคใหญ่ 1019</v>
+        <v>แก้ว 1937*3 รวม 5,811</v>
       </c>
       <c r="F282">
-        <v>1830</v>
+        <v>6659</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>11/06/2026</v>
+        <v>09/06/2026</v>
       </c>
       <c r="B283" t="str">
         <v>Jun26</v>
@@ -6786,18 +6786,18 @@
         <v>COGS</v>
       </c>
       <c r="D283" t="str">
-        <v>Guava</v>
+        <v>Packaging</v>
       </c>
       <c r="E283" t="str">
-        <v>ฝรั่ง 1 ลัง</v>
+        <v>หลอด 20 แพ็ก 671</v>
       </c>
       <c r="F283">
-        <v>700</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>12/06/2026</v>
+        <v>09/06/2026</v>
       </c>
       <c r="B284" t="str">
         <v>Jun26</v>
@@ -6806,18 +6806,18 @@
         <v>COGS</v>
       </c>
       <c r="D284" t="str">
-        <v>Coconut Water</v>
+        <v>Packaging</v>
       </c>
       <c r="E284" t="str">
-        <v>น้ำมะพร้าว50*20 1,000</v>
+        <v>ฝา1 714</v>
       </c>
       <c r="F284">
-        <v>2200</v>
+        <v>714</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>12/06/2026</v>
+        <v>09/06/2026</v>
       </c>
       <c r="B285" t="str">
         <v>Jun26</v>
@@ -6826,18 +6826,18 @@
         <v>COGS</v>
       </c>
       <c r="D285" t="str">
-        <v>Mango</v>
+        <v>Packaging</v>
       </c>
       <c r="E285" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>ถุงขยะ 4แพคใหญ่ 1019</v>
       </c>
       <c r="F285">
-        <v>1170</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>12/06/2026</v>
+        <v>11/06/2026</v>
       </c>
       <c r="B286" t="str">
         <v>Jun26</v>
@@ -6846,13 +6846,13 @@
         <v>COGS</v>
       </c>
       <c r="D286" t="str">
-        <v>Apple</v>
+        <v>Guava</v>
       </c>
       <c r="E286" t="str">
-        <v>แอปเปิ้ล 5 ลัง</v>
+        <v>ฝรั่ง 1 ลัง</v>
       </c>
       <c r="F286">
-        <v>1750</v>
+        <v>700</v>
       </c>
     </row>
     <row r="287">
@@ -6866,18 +6866,18 @@
         <v>COGS</v>
       </c>
       <c r="D287" t="str">
-        <v>Pineapple</v>
+        <v>Coconut Water</v>
       </c>
       <c r="E287" t="str">
-        <v>สับปะรด 19 ลูก</v>
+        <v>น้ำมะพร้าว50*20 1,000</v>
       </c>
       <c r="F287">
-        <v>950</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>14/06/2026</v>
+        <v>12/06/2026</v>
       </c>
       <c r="B288" t="str">
         <v>Jun26</v>
@@ -6886,18 +6886,18 @@
         <v>COGS</v>
       </c>
       <c r="D288" t="str">
-        <v>Watermelon</v>
+        <v>Mango</v>
       </c>
       <c r="E288" t="str">
-        <v>แตงโม 90 ลูก (7-6-2569: 45 ลูก, 12-6-2569: 45 ลูก)</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F288">
-        <v>7200</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>15/06/2026</v>
+        <v>12/06/2026</v>
       </c>
       <c r="B289" t="str">
         <v>Jun26</v>
@@ -6906,18 +6906,18 @@
         <v>COGS</v>
       </c>
       <c r="D289" t="str">
-        <v>Pineapple</v>
+        <v>Apple</v>
       </c>
       <c r="E289" t="str">
-        <v>สับปะรด 1 ลูก</v>
+        <v>แอปเปิ้ล 5 ลัง</v>
       </c>
       <c r="F289">
-        <v>50</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>15/06/2026</v>
+        <v>12/06/2026</v>
       </c>
       <c r="B290" t="str">
         <v>Jun26</v>
@@ -6926,18 +6926,18 @@
         <v>COGS</v>
       </c>
       <c r="D290" t="str">
-        <v>Other</v>
+        <v>Pineapple</v>
       </c>
       <c r="E290" t="str">
-        <v>Unknown</v>
+        <v>สับปะรด 19 ลูก</v>
       </c>
       <c r="F290">
-        <v>18</v>
+        <v>950</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>15/06/2026</v>
+        <v>14/06/2026</v>
       </c>
       <c r="B291" t="str">
         <v>Jun26</v>
@@ -6946,13 +6946,13 @@
         <v>COGS</v>
       </c>
       <c r="D291" t="str">
-        <v>Pineapple</v>
+        <v>Watermelon</v>
       </c>
       <c r="E291" t="str">
-        <v>สับปะรด 12 ลูก</v>
+        <v>แตงโม 90 ลูก (7-6-2569: 45 ลูก, 12-6-2569: 45 ลูก)</v>
       </c>
       <c r="F291">
-        <v>525</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="292">
@@ -6966,18 +6966,18 @@
         <v>COGS</v>
       </c>
       <c r="D292" t="str">
-        <v>Guava</v>
+        <v>Pineapple</v>
       </c>
       <c r="E292" t="str">
-        <v>ฝรั่ง 1 ตะกร้า</v>
+        <v>สับปะรด 1 ลูก</v>
       </c>
       <c r="F292">
-        <v>800</v>
+        <v>50</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>17/06/2026</v>
+        <v>15/06/2026</v>
       </c>
       <c r="B293" t="str">
         <v>Jun26</v>
@@ -6986,18 +6986,18 @@
         <v>COGS</v>
       </c>
       <c r="D293" t="str">
-        <v>Orange</v>
+        <v>Other</v>
       </c>
       <c r="E293" t="str">
-        <v>ส้ม 23x22กก 506 กก. x30 = 15,180 + ค่าขนส่ง 23x55 = 1,265 (รอบ 09/06/69)</v>
+        <v>Unknown</v>
       </c>
       <c r="F293">
-        <v>16445</v>
+        <v>18</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>18/06/2026</v>
+        <v>15/06/2026</v>
       </c>
       <c r="B294" t="str">
         <v>Jun26</v>
@@ -7006,18 +7006,18 @@
         <v>COGS</v>
       </c>
       <c r="D294" t="str">
-        <v>Mango</v>
+        <v>Pineapple</v>
       </c>
       <c r="E294" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>สับปะรด 12 ลูก</v>
       </c>
       <c r="F294">
-        <v>1300</v>
+        <v>525</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>18/06/2026</v>
+        <v>15/06/2026</v>
       </c>
       <c r="B295" t="str">
         <v>Jun26</v>
@@ -7026,18 +7026,18 @@
         <v>COGS</v>
       </c>
       <c r="D295" t="str">
-        <v>Coconut Water</v>
+        <v>Guava</v>
       </c>
       <c r="E295" t="str">
-        <v>เนื้อมะพร้าว 20 * 120 2400 น้ำมะพร้าว 20 *</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F295">
-        <v>3400</v>
+        <v>800</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>18/06/2026</v>
+        <v>17/06/2026</v>
       </c>
       <c r="B296" t="str">
         <v>Jun26</v>
@@ -7046,18 +7046,18 @@
         <v>COGS</v>
       </c>
       <c r="D296" t="str">
-        <v>Guava</v>
+        <v>Orange</v>
       </c>
       <c r="E296" t="str">
-        <v>ฝรั่ง 1 ตะกร้า</v>
+        <v>ส้ม 23x22กก 506 กก. x30 = 15,180 + ค่าขนส่ง 23x55 = 1,265 (รอบ 09/06/69)</v>
       </c>
       <c r="F296">
-        <v>800</v>
+        <v>16445</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>19/06/2026</v>
+        <v>18/06/2026</v>
       </c>
       <c r="B297" t="str">
         <v>Jun26</v>
@@ -7066,18 +7066,18 @@
         <v>COGS</v>
       </c>
       <c r="D297" t="str">
-        <v>Coconut Water</v>
+        <v>Mango</v>
       </c>
       <c r="E297" t="str">
-        <v>น้ำมะพร้าว40ลิตร ลิตรละ45บาท</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F297">
-        <v>5700</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>19/06/2026</v>
+        <v>18/06/2026</v>
       </c>
       <c r="B298" t="str">
         <v>Jun26</v>
@@ -7086,18 +7086,18 @@
         <v>COGS</v>
       </c>
       <c r="D298" t="str">
-        <v>Packaging</v>
+        <v>Coconut Water</v>
       </c>
       <c r="E298" t="str">
-        <v>น้ำยาล้างจาน 7 ถุง ผงซักฟอก 1</v>
+        <v>เนื้อมะพร้าว 20 * 120 2400 น้ำมะพร้าว 20 *</v>
       </c>
       <c r="F298">
-        <v>149</v>
+        <v>3400</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>21/06/2026</v>
+        <v>18/06/2026</v>
       </c>
       <c r="B299" t="str">
         <v>Jun26</v>
@@ -7106,18 +7106,18 @@
         <v>COGS</v>
       </c>
       <c r="D299" t="str">
-        <v>Watermelon</v>
+        <v>Guava</v>
       </c>
       <c r="E299" t="str">
-        <v>15-6-2569 แตงโม 50บาท 50 ลูก ยอด 2,500</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F299">
-        <v>6500</v>
+        <v>800</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>22/06/2026</v>
+        <v>19/06/2026</v>
       </c>
       <c r="B300" t="str">
         <v>Jun26</v>
@@ -7126,18 +7126,18 @@
         <v>COGS</v>
       </c>
       <c r="D300" t="str">
-        <v>Pineapple</v>
+        <v>Coconut Water</v>
       </c>
       <c r="E300" t="str">
-        <v>สับปะรด 15 ลูก</v>
+        <v>น้ำมะพร้าว40ลิตร ลิตรละ45บาท</v>
       </c>
       <c r="F300">
-        <v>700</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>22/06/2026</v>
+        <v>19/06/2026</v>
       </c>
       <c r="B301" t="str">
         <v>Jun26</v>
@@ -7146,18 +7146,18 @@
         <v>COGS</v>
       </c>
       <c r="D301" t="str">
-        <v>Mango</v>
+        <v>Packaging</v>
       </c>
       <c r="E301" t="str">
-        <v>มะม่วง 2 ลัง</v>
+        <v>น้ำยาล้างจาน 7 ถุง ผงซักฟอก 1</v>
       </c>
       <c r="F301">
-        <v>1632</v>
+        <v>149</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>22/06/2026</v>
+        <v>21/06/2026</v>
       </c>
       <c r="B302" t="str">
         <v>Jun26</v>
@@ -7166,13 +7166,13 @@
         <v>COGS</v>
       </c>
       <c r="D302" t="str">
-        <v>Transportation</v>
+        <v>Watermelon</v>
       </c>
       <c r="E302" t="str">
-        <v>Lalamove</v>
+        <v>15-6-2569 แตงโม 50บาท 50 ลูก ยอด 2,500</v>
       </c>
       <c r="F302">
-        <v>2000</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="303">
@@ -7186,13 +7186,13 @@
         <v>COGS</v>
       </c>
       <c r="D303" t="str">
-        <v>Apple</v>
+        <v>Pineapple</v>
       </c>
       <c r="E303" t="str">
-        <v>แอพเปิ้ล 5 ลัง</v>
+        <v>สับปะรด 15 ลูก</v>
       </c>
       <c r="F303">
-        <v>1750</v>
+        <v>700</v>
       </c>
     </row>
     <row r="304">
@@ -7206,13 +7206,13 @@
         <v>COGS</v>
       </c>
       <c r="D304" t="str">
-        <v>Pineapple</v>
+        <v>Mango</v>
       </c>
       <c r="E304" t="str">
-        <v>สับปะรด 15 ลูก</v>
+        <v>มะม่วง 2 ลัง</v>
       </c>
       <c r="F304">
-        <v>700</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="305">
@@ -7226,18 +7226,18 @@
         <v>COGS</v>
       </c>
       <c r="D305" t="str">
-        <v>Guava</v>
+        <v>Transportation</v>
       </c>
       <c r="E305" t="str">
-        <v>ฝรั่ง 1 ลัง</v>
+        <v>Lalamove</v>
       </c>
       <c r="F305">
-        <v>700</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>24/06/2026</v>
+        <v>22/06/2026</v>
       </c>
       <c r="B306" t="str">
         <v>Jun26</v>
@@ -7246,18 +7246,18 @@
         <v>COGS</v>
       </c>
       <c r="D306" t="str">
-        <v>Milk/Conden</v>
+        <v>Apple</v>
       </c>
       <c r="E306" t="str">
-        <v>นมข้นจืด 2,221</v>
+        <v>แอพเปิ้ล 5 ลัง</v>
       </c>
       <c r="F306">
-        <v>5020</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>24/06/2026</v>
+        <v>22/06/2026</v>
       </c>
       <c r="B307" t="str">
         <v>Jun26</v>
@@ -7266,18 +7266,18 @@
         <v>COGS</v>
       </c>
       <c r="D307" t="str">
-        <v>Milk/Conden</v>
+        <v>Pineapple</v>
       </c>
       <c r="E307" t="str">
-        <v>นมข้นจืด1ลัง</v>
+        <v>สับปะรด 15 ลูก</v>
       </c>
       <c r="F307">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>24/06/2026</v>
+        <v>22/06/2026</v>
       </c>
       <c r="B308" t="str">
         <v>Jun26</v>
@@ -7286,18 +7286,18 @@
         <v>COGS</v>
       </c>
       <c r="D308" t="str">
-        <v>Milk/Conden</v>
+        <v>Guava</v>
       </c>
       <c r="E308" t="str">
-        <v>นมข้นหวาน1ลัง</v>
+        <v>ฝรั่ง 1 ลัง</v>
       </c>
       <c r="F308">
-        <v>840</v>
+        <v>700</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>25/06/2026</v>
+        <v>24/06/2026</v>
       </c>
       <c r="B309" t="str">
         <v>Jun26</v>
@@ -7306,18 +7306,18 @@
         <v>COGS</v>
       </c>
       <c r="D309" t="str">
-        <v>Watermelon</v>
+        <v>Milk/Conden</v>
       </c>
       <c r="E309" t="str">
-        <v>แตงโม 22-6-2569 30 ลูก 2400 25-6-2569 40</v>
+        <v>นมข้นจืด 2,221</v>
       </c>
       <c r="F309">
-        <v>6000</v>
+        <v>5020</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>27/06/2026</v>
+        <v>24/06/2026</v>
       </c>
       <c r="B310" t="str">
         <v>Jun26</v>
@@ -7326,18 +7326,18 @@
         <v>COGS</v>
       </c>
       <c r="D310" t="str">
-        <v>Packaging</v>
+        <v>Milk/Conden</v>
       </c>
       <c r="E310" t="str">
-        <v>ถุงมือ20กล่อง 2589</v>
+        <v>นมข้นจืด1ลัง</v>
       </c>
       <c r="F310">
-        <v>4598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>27/06/2026</v>
+        <v>24/06/2026</v>
       </c>
       <c r="B311" t="str">
         <v>Jun26</v>
@@ -7346,38 +7346,38 @@
         <v>COGS</v>
       </c>
       <c r="D311" t="str">
-        <v>Packaging</v>
+        <v>Milk/Conden</v>
       </c>
       <c r="E311" t="str">
-        <v>หลอด 20 แพค</v>
+        <v>นมข้นหวาน1ลัง</v>
       </c>
       <c r="F311">
-        <v>630</v>
+        <v>840</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>27/06/2026</v>
+        <v>25/06/2026</v>
       </c>
       <c r="B312" t="str">
         <v>Jun26</v>
       </c>
       <c r="C312" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D312" t="str">
-        <v>Other</v>
+        <v>Watermelon</v>
       </c>
       <c r="E312" t="str">
-        <v>Unknown</v>
+        <v>แตงโม 22-6-2569 30 ลูก 2400 25-6-2569 40</v>
       </c>
       <c r="F312">
-        <v>317</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>29/06/2026</v>
+        <v>27/06/2026</v>
       </c>
       <c r="B313" t="str">
         <v>Jun26</v>
@@ -7389,15 +7389,15 @@
         <v>Packaging</v>
       </c>
       <c r="E313" t="str">
-        <v>ฝาแก้วภูเขาไฟ 1ลัง(954) 10แถว(987) 5แถว(561)</v>
+        <v>ถุงมือ20กล่อง 2589</v>
       </c>
       <c r="F313">
-        <v>2502</v>
+        <v>4598</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>29/06/2026</v>
+        <v>27/06/2026</v>
       </c>
       <c r="B314" t="str">
         <v>Jun26</v>
@@ -7409,30 +7409,30 @@
         <v>Packaging</v>
       </c>
       <c r="E314" t="str">
-        <v>แก้ว2ลัง 1468*2 2,936</v>
+        <v>หลอด 20 แพค</v>
       </c>
       <c r="F314">
-        <v>3498</v>
+        <v>630</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>29/06/2026</v>
+        <v>27/06/2026</v>
       </c>
       <c r="B315" t="str">
         <v>Jun26</v>
       </c>
       <c r="C315" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D315" t="str">
-        <v>Packaging</v>
+        <v>Other</v>
       </c>
       <c r="E315" t="str">
-        <v>ฝา8แถว</v>
+        <v>Unknown</v>
       </c>
       <c r="F315">
-        <v>896</v>
+        <v>317</v>
       </c>
     </row>
     <row r="316">
@@ -7443,16 +7443,16 @@
         <v>Jun26</v>
       </c>
       <c r="C316" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D316" t="str">
-        <v>Other</v>
+        <v>Packaging</v>
       </c>
       <c r="E316" t="str">
-        <v>สกัดเย็น1เครื่อง</v>
+        <v>ฝาแก้วภูเขาไฟ 1ลัง(954) 10แถว(987) 5แถว(561)</v>
       </c>
       <c r="F316">
-        <v>1402</v>
+        <v>2502</v>
       </c>
     </row>
     <row r="317">
@@ -7466,13 +7466,13 @@
         <v>COGS</v>
       </c>
       <c r="D317" t="str">
-        <v>Guava</v>
+        <v>Packaging</v>
       </c>
       <c r="E317" t="str">
-        <v>ฝรั่ง 1 ตะกร้า</v>
+        <v>แก้ว2ลัง 1468*2 2,936</v>
       </c>
       <c r="F317">
-        <v>800</v>
+        <v>3498</v>
       </c>
     </row>
     <row r="318">
@@ -7483,16 +7483,16 @@
         <v>Jun26</v>
       </c>
       <c r="C318" t="str">
-        <v>EXCLUDED</v>
+        <v>COGS</v>
       </c>
       <c r="D318" t="str">
-        <v>Pass-Through</v>
+        <v>Packaging</v>
       </c>
       <c r="E318" t="str">
-        <v>มังคุด 3 ตะกร้า (จ่ายแทน 1,932 แล้ว ฐนกร โอนคืน 29/06 13:56) - ไม่ใช่ต้นทุน SSJ [bank]</v>
+        <v>ฝา8แถว</v>
       </c>
       <c r="F318">
-        <v>0</v>
+        <v>896</v>
       </c>
     </row>
     <row r="319">
@@ -7509,10 +7509,10 @@
         <v>Other</v>
       </c>
       <c r="E319" t="str">
-        <v>Apple 2 box</v>
+        <v>สกัดเย็น1เครื่อง</v>
       </c>
       <c r="F319">
-        <v>700</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="320">
@@ -7526,13 +7526,13 @@
         <v>COGS</v>
       </c>
       <c r="D320" t="str">
-        <v>Pineapple</v>
+        <v>Guava</v>
       </c>
       <c r="E320" t="str">
-        <v>สับปะรด 15 ลูก</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F320">
-        <v>675</v>
+        <v>800</v>
       </c>
     </row>
     <row r="321">
@@ -7543,21 +7543,21 @@
         <v>Jun26</v>
       </c>
       <c r="C321" t="str">
-        <v>COGS</v>
+        <v>EXCLUDED</v>
       </c>
       <c r="D321" t="str">
-        <v>Orange</v>
+        <v>Pass-Through</v>
       </c>
       <c r="E321" t="str">
-        <v>ส้ม 25x22กก 550 กก. x30 = 16,500 + ค่าขนส่ง 25x55 = 1,375 (รอบ 18/06/69)</v>
+        <v>มังคุด 3 ตะกร้า (จ่ายแทน 1,932 แล้ว ฐนกร โอนคืน 29/06 13:56) - ไม่ใช่ต้นทุน SSJ [bank]</v>
       </c>
       <c r="F321">
-        <v>17815</v>
+        <v>0</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>30/06/2026</v>
+        <v>29/06/2026</v>
       </c>
       <c r="B322" t="str">
         <v>Jun26</v>
@@ -7566,73 +7566,73 @@
         <v>OPEX</v>
       </c>
       <c r="D322" t="str">
-        <v>Salary</v>
+        <v>Other</v>
       </c>
       <c r="E322" t="str">
-        <v>ค่าแรง 4 คน คนคนละ 12000 และ รายวัน 1</v>
+        <v>Apple 2 box</v>
       </c>
       <c r="F322">
-        <v>48400</v>
+        <v>700</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>24/07/2026</v>
+        <v>29/06/2026</v>
       </c>
       <c r="B323" t="str">
-        <v>Jul26</v>
+        <v>Jun26</v>
       </c>
       <c r="C323" t="str">
         <v>COGS</v>
       </c>
       <c r="D323" t="str">
-        <v>Stock</v>
+        <v>Pineapple</v>
       </c>
       <c r="E323" t="str">
-        <v>ฝา 1 ลัง 509 นมข้นหวาน 1 ลัง 785 นมข้นจืด 2 ลัง 1342 บาท (LINE_ALBUM_Cost July_260802_1.jpg)</v>
+        <v>สับปะรด 15 ลูก</v>
       </c>
       <c r="F323">
-        <v>2636</v>
+        <v>675</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>24/07/2026</v>
+        <v>29/06/2026</v>
       </c>
       <c r="B324" t="str">
-        <v>Jul26</v>
+        <v>Jun26</v>
       </c>
       <c r="C324" t="str">
         <v>COGS</v>
       </c>
       <c r="D324" t="str">
-        <v>Stock</v>
+        <v>Orange</v>
       </c>
       <c r="E324" t="str">
-        <v>ฝา 1 ลัง 502 บาท นมข้นหวาน 3 ลัง 2582 บาท (LINE_ALBUM_Cost July_260802_2.jpg)</v>
+        <v>ส้ม 25x22กก 550 กก. x30 = 16,500 + ค่าขนส่ง 25x55 = 1,375 (รอบ 18/06/69)</v>
       </c>
       <c r="F324">
-        <v>3084</v>
+        <v>17815</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>24/07/2026</v>
+        <v>30/06/2026</v>
       </c>
       <c r="B325" t="str">
-        <v>Jul26</v>
+        <v>Jun26</v>
       </c>
       <c r="C325" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D325" t="str">
-        <v>Stock</v>
+        <v>Salary</v>
       </c>
       <c r="E325" t="str">
-        <v>ฝา 1 ลัง 474 นมข้นจืด 1 ลัง 751 (LINE_ALBUM_Cost July_260802_3.jpg)</v>
+        <v>ค่าแรง 4 คน คนคนละ 12000 และ รายวัน 1</v>
       </c>
       <c r="F325">
-        <v>1225</v>
+        <v>48400</v>
       </c>
     </row>
     <row r="326">
@@ -7646,13 +7646,13 @@
         <v>COGS</v>
       </c>
       <c r="D326" t="str">
-        <v>Stock</v>
+        <v>Milk/Conden</v>
       </c>
       <c r="E326" t="str">
-        <v>ฝา 1 ลัง (LINE_ALBUM_Cost July_260802_4.jpg)</v>
+        <v>นมข้นหวาน 1 ลัง 785 + นมข้นจืด 2 ลัง 1,342</v>
       </c>
       <c r="F326">
-        <v>472</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="327">
@@ -7663,21 +7663,21 @@
         <v>Jul26</v>
       </c>
       <c r="C327" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D327" t="str">
-        <v>Other</v>
+        <v>Packaging</v>
       </c>
       <c r="E327" t="str">
-        <v>Lalamove (LINE_ALBUM_Cost July_260802_5.jpg)</v>
+        <v>ฝา 1 ลัง 509</v>
       </c>
       <c r="F327">
-        <v>2000</v>
+        <v>509</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>26/07/2026</v>
+        <v>24/07/2026</v>
       </c>
       <c r="B328" t="str">
         <v>Jul26</v>
@@ -7686,18 +7686,18 @@
         <v>COGS</v>
       </c>
       <c r="D328" t="str">
-        <v>Apple</v>
+        <v>Milk/Conden</v>
       </c>
       <c r="E328" t="str">
-        <v>Apple 5 box (LINE_ALBUM_Cost July_260802_6.jpg)</v>
+        <v>นมข้นหวาน 3 ลัง 2,582</v>
       </c>
       <c r="F328">
-        <v>2000</v>
+        <v>2582</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>26/07/2026</v>
+        <v>24/07/2026</v>
       </c>
       <c r="B329" t="str">
         <v>Jul26</v>
@@ -7706,18 +7706,18 @@
         <v>COGS</v>
       </c>
       <c r="D329" t="str">
-        <v>Guava</v>
+        <v>Packaging</v>
       </c>
       <c r="E329" t="str">
-        <v>ฝรั่ง 2 ตะกร้า (LINE_ALBUM_Cost July_260802_7.jpg)</v>
+        <v>ฝา 1 ลัง 502</v>
       </c>
       <c r="F329">
-        <v>2000</v>
+        <v>502</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>26/07/2026</v>
+        <v>24/07/2026</v>
       </c>
       <c r="B330" t="str">
         <v>Jul26</v>
@@ -7726,18 +7726,18 @@
         <v>COGS</v>
       </c>
       <c r="D330" t="str">
-        <v>Mango</v>
+        <v>Milk/Conden</v>
       </c>
       <c r="E330" t="str">
-        <v>มะม่วง 3 ลัง 3900 (LINE_ALBUM_Cost July_260802_8.jpg)</v>
+        <v>นมข้นจืด 1 ลัง 751</v>
       </c>
       <c r="F330">
-        <v>3900</v>
+        <v>751</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>27/07/2026</v>
+        <v>24/07/2026</v>
       </c>
       <c r="B331" t="str">
         <v>Jul26</v>
@@ -7746,18 +7746,18 @@
         <v>COGS</v>
       </c>
       <c r="D331" t="str">
-        <v>Coconut</v>
+        <v>Packaging</v>
       </c>
       <c r="E331" t="str">
-        <v>น้ำมะพร้าว 30ลิตร 1350 เนื้อ 50kg 5000 น้ำมะพร้าวขวด 920 ค่าส่ง 350 (LINE_ALBUM_Cost July_260802_14.jpg, audit fix - was dated 26/07 citing wrong image, missing ฿920 bottles line)</v>
+        <v>ฝา 1 ลัง 474</v>
       </c>
       <c r="F331">
-        <v>7620</v>
+        <v>474</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>27/07/2026</v>
+        <v>24/07/2026</v>
       </c>
       <c r="B332" t="str">
         <v>Jul26</v>
@@ -7766,30 +7766,30 @@
         <v>COGS</v>
       </c>
       <c r="D332" t="str">
-        <v>Apple</v>
+        <v>Stock</v>
       </c>
       <c r="E332" t="str">
-        <v>Apple 4 box (LINE_ALBUM_Cost July_260802_10.jpg)</v>
+        <v>ฝา 1 ลัง (LINE_ALBUM_Cost July_260802_4.jpg)</v>
       </c>
       <c r="F332">
-        <v>1600</v>
+        <v>472</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>27/07/2026</v>
+        <v>24/07/2026</v>
       </c>
       <c r="B333" t="str">
         <v>Jul26</v>
       </c>
       <c r="C333" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D333" t="str">
-        <v>Guava</v>
+        <v>Other</v>
       </c>
       <c r="E333" t="str">
-        <v>ฝรั่ง 2 ตะกร้า (LINE_ALBUM_Cost July_260802_11.jpg)</v>
+        <v>Lalamove (LINE_ALBUM_Cost July_260802_5.jpg)</v>
       </c>
       <c r="F333">
         <v>2000</v>
@@ -7797,7 +7797,7 @@
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>27/07/2026</v>
+        <v>26/07/2026</v>
       </c>
       <c r="B334" t="str">
         <v>Jul26</v>
@@ -7806,18 +7806,18 @@
         <v>COGS</v>
       </c>
       <c r="D334" t="str">
-        <v>Mango</v>
+        <v>Apple</v>
       </c>
       <c r="E334" t="str">
-        <v>มะม่วง 2 ลัง (LINE_ALBUM_Cost July_260802_12.jpg)</v>
+        <v>Apple 5 box (LINE_ALBUM_Cost July_260802_6.jpg)</v>
       </c>
       <c r="F334">
-        <v>2600</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>27/07/2026</v>
+        <v>26/07/2026</v>
       </c>
       <c r="B335" t="str">
         <v>Jul26</v>
@@ -7826,38 +7826,38 @@
         <v>COGS</v>
       </c>
       <c r="D335" t="str">
-        <v>Watermelon</v>
+        <v>Guava</v>
       </c>
       <c r="E335" t="str">
-        <v>แตงโม 40 ลูก (LINE_ALBUM_Cost July_260802_13.jpg)</v>
+        <v>ฝรั่ง 2 ตะกร้า (LINE_ALBUM_Cost July_260802_7.jpg)</v>
       </c>
       <c r="F335">
-        <v>3200</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>28/07/2026</v>
+        <v>26/07/2026</v>
       </c>
       <c r="B336" t="str">
         <v>Jul26</v>
       </c>
       <c r="C336" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D336" t="str">
-        <v>Other</v>
+        <v>Mango</v>
       </c>
       <c r="E336" t="str">
-        <v>Lalamove (LINE_ALBUM_Cost July_260802_14.jpg)</v>
+        <v>มะม่วง 3 ลัง 3900 (LINE_ALBUM_Cost July_260802_8.jpg)</v>
       </c>
       <c r="F336">
-        <v>1000</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>28/07/2026</v>
+        <v>27/07/2026</v>
       </c>
       <c r="B337" t="str">
         <v>Jul26</v>
@@ -7866,18 +7866,18 @@
         <v>COGS</v>
       </c>
       <c r="D337" t="str">
-        <v>Guava</v>
+        <v>Coconut</v>
       </c>
       <c r="E337" t="str">
-        <v>ฝรั่ง 2 ลัง (LINE_ALBUM_Cost July_260802_15.jpg)</v>
+        <v>น้ำมะพร้าว 30ลิตร 1350 เนื้อ 50kg 5000 น้ำมะพร้าวขวด 920 ค่าส่ง 350 (LINE_ALBUM_Cost July_260802_14.jpg, audit fix - was dated 26/07 citing wrong image, missing ฿920 bottles line)</v>
       </c>
       <c r="F337">
-        <v>2000</v>
+        <v>7620</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>28/07/2026</v>
+        <v>27/07/2026</v>
       </c>
       <c r="B338" t="str">
         <v>Jul26</v>
@@ -7889,15 +7889,15 @@
         <v>Apple</v>
       </c>
       <c r="E338" t="str">
-        <v>แอปเปิ้ล 5 ลัง (LINE_ALBUM_Cost July_260802_16.jpg, audit fix - was recorded as 4 ลัง/฿1600)</v>
+        <v>Apple 4 box (LINE_ALBUM_Cost July_260802_10.jpg)</v>
       </c>
       <c r="F338">
-        <v>2150</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>28/07/2026</v>
+        <v>27/07/2026</v>
       </c>
       <c r="B339" t="str">
         <v>Jul26</v>
@@ -7906,18 +7906,18 @@
         <v>COGS</v>
       </c>
       <c r="D339" t="str">
-        <v>Mango</v>
+        <v>Guava</v>
       </c>
       <c r="E339" t="str">
-        <v>มะม่วง 2 ลัง (LINE_ALBUM_Cost July_260802_17.jpg)</v>
+        <v>ฝรั่ง 2 ตะกร้า (LINE_ALBUM_Cost July_260802_11.jpg)</v>
       </c>
       <c r="F339">
-        <v>2600</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>28/07/2026</v>
+        <v>27/07/2026</v>
       </c>
       <c r="B340" t="str">
         <v>Jul26</v>
@@ -7926,98 +7926,98 @@
         <v>COGS</v>
       </c>
       <c r="D340" t="str">
-        <v>Watermelon</v>
+        <v>Mango</v>
       </c>
       <c r="E340" t="str">
-        <v>แตงโม 40 ลูก (LINE_ALBUM_Cost July_260802_18.jpg)</v>
+        <v>มะม่วง 2 ลัง (LINE_ALBUM_Cost July_260802_12.jpg)</v>
       </c>
       <c r="F340">
-        <v>3200</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>29/07/2026</v>
+        <v>27/07/2026</v>
       </c>
       <c r="B341" t="str">
         <v>Jul26</v>
       </c>
       <c r="C341" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D341" t="str">
-        <v>Other</v>
+        <v>Watermelon</v>
       </c>
       <c r="E341" t="str">
-        <v>ค่าขนส่ง (LINE_ALBUM_Cost July_260802_19.jpg)</v>
+        <v>แตงโม 40 ลูก (LINE_ALBUM_Cost July_260802_13.jpg)</v>
       </c>
       <c r="F341">
-        <v>2000</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>29/07/2026</v>
+        <v>28/07/2026</v>
       </c>
       <c r="B342" t="str">
         <v>Jul26</v>
       </c>
       <c r="C342" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D342" t="str">
-        <v>Orange</v>
+        <v>Other</v>
       </c>
       <c r="E342" t="str">
-        <v>ส้ม 31x22กก 682กกx30 20,460บาท ค่าขนส่ง 31ตกx 50 1550 (LINE_ALBUM_Cost July_260802_20.jpg)</v>
+        <v>Lalamove (LINE_ALBUM_Cost July_260802_14.jpg)</v>
       </c>
       <c r="F342">
-        <v>22010</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>30/07/2026</v>
+        <v>28/07/2026</v>
       </c>
       <c r="B343" t="str">
         <v>Jul26</v>
       </c>
       <c r="C343" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D343" t="str">
-        <v>Other</v>
+        <v>Guava</v>
       </c>
       <c r="E343" t="str">
-        <v>ตะแกรงคว่ำจาน 6อัน ป้ายไฟ3อัน (LINE_ALBUM_Cost July_260802_21.jpg)</v>
+        <v>ฝรั่ง 2 ลัง (LINE_ALBUM_Cost July_260802_15.jpg)</v>
       </c>
       <c r="F343">
-        <v>1790</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>30/07/2026</v>
+        <v>28/07/2026</v>
       </c>
       <c r="B344" t="str">
         <v>Jul26</v>
       </c>
       <c r="C344" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D344" t="str">
-        <v>Other</v>
+        <v>Apple</v>
       </c>
       <c r="E344" t="str">
-        <v>ถุงขยะ 5*5แพค (LINE_ALBUM_Cost July_260802_22.jpg)</v>
+        <v>แอปเปิ้ล 5 ลัง (LINE_ALBUM_Cost July_260802_16.jpg, audit fix - was recorded as 4 ลัง/฿1600)</v>
       </c>
       <c r="F344">
-        <v>1101</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>31/07/2026</v>
+        <v>28/07/2026</v>
       </c>
       <c r="B345" t="str">
         <v>Jul26</v>
@@ -8026,18 +8026,18 @@
         <v>COGS</v>
       </c>
       <c r="D345" t="str">
-        <v>Apple</v>
+        <v>Mango</v>
       </c>
       <c r="E345" t="str">
-        <v>แอปเปิ้ล 4 ลัง (LINE_ALBUM_Cost July_260802_23.jpg)</v>
+        <v>มะม่วง 2 ลัง (LINE_ALBUM_Cost July_260802_17.jpg)</v>
       </c>
       <c r="F345">
-        <v>1200</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>31/07/2026</v>
+        <v>28/07/2026</v>
       </c>
       <c r="B346" t="str">
         <v>Jul26</v>
@@ -8046,18 +8046,18 @@
         <v>COGS</v>
       </c>
       <c r="D346" t="str">
-        <v>Mango</v>
+        <v>Watermelon</v>
       </c>
       <c r="E346" t="str">
-        <v>มะม่วง 4 ลัง (LINE_ALBUM_Cost July_260802_24.jpg)</v>
+        <v>แตงโม 40 ลูก (LINE_ALBUM_Cost July_260802_18.jpg)</v>
       </c>
       <c r="F346">
-        <v>4680</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>31/07/2026</v>
+        <v>29/07/2026</v>
       </c>
       <c r="B347" t="str">
         <v>Jul26</v>
@@ -8069,7 +8069,7 @@
         <v>Other</v>
       </c>
       <c r="E347" t="str">
-        <v>ค่าขนส่ง (LINE_ALBUM_Cost July_260802_25.jpg)</v>
+        <v>ค่าขนส่ง (LINE_ALBUM_Cost July_260802_19.jpg)</v>
       </c>
       <c r="F347">
         <v>2000</v>
@@ -8077,7 +8077,7 @@
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>31/07/2026</v>
+        <v>29/07/2026</v>
       </c>
       <c r="B348" t="str">
         <v>Jul26</v>
@@ -8086,38 +8086,38 @@
         <v>COGS</v>
       </c>
       <c r="D348" t="str">
-        <v>Guava</v>
+        <v>Orange</v>
       </c>
       <c r="E348" t="str">
-        <v>ฝรั่ง 3 ลัง (LINE_ALBUM_Cost July_260802_26.jpg)</v>
+        <v>ส้ม 31x22กก 682กกx30 20,460บาท ค่าขนส่ง 31ตกx 50 1550 (LINE_ALBUM_Cost July_260802_20.jpg)</v>
       </c>
       <c r="F348">
-        <v>3600</v>
+        <v>22010</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>31/07/2026</v>
+        <v>30/07/2026</v>
       </c>
       <c r="B349" t="str">
         <v>Jul26</v>
       </c>
       <c r="C349" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D349" t="str">
         <v>Other</v>
       </c>
       <c r="E349" t="str">
-        <v>ทุเรียน 20.6 กิโลกรัม (LINE_ALBUM_Cost July_260802_27.jpg)</v>
+        <v>ตะแกรงคว่ำจาน 6อัน ป้ายไฟ3อัน (LINE_ALBUM_Cost July_260802_21.jpg)</v>
       </c>
       <c r="F349">
-        <v>2255</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>31/07/2026</v>
+        <v>30/07/2026</v>
       </c>
       <c r="B350" t="str">
         <v>Jul26</v>
@@ -8129,15 +8129,15 @@
         <v>Other</v>
       </c>
       <c r="E350" t="str">
-        <v>ตะกร้าแต่งร้าน 3 (LINE_ALBUM_Cost July_260802_28.jpg)</v>
+        <v>ถุงขยะ 5*5แพค (LINE_ALBUM_Cost July_260802_22.jpg)</v>
       </c>
       <c r="F350">
-        <v>558</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>02/07/2026</v>
+        <v>31/07/2026</v>
       </c>
       <c r="B351" t="str">
         <v>Jul26</v>
@@ -8146,18 +8146,18 @@
         <v>COGS</v>
       </c>
       <c r="D351" t="str">
-        <v>Orange</v>
+        <v>Apple</v>
       </c>
       <c r="E351" t="str">
-        <v>ค่าส่งส้มเดือน 6 (LINE_ALBUM_Cost July_260802_29.jpg)</v>
+        <v>แอปเปิ้ล 4 ลัง (LINE_ALBUM_Cost July_260802_23.jpg)</v>
       </c>
       <c r="F351">
-        <v>1598</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>03/07/2026</v>
+        <v>31/07/2026</v>
       </c>
       <c r="B352" t="str">
         <v>Jul26</v>
@@ -8166,38 +8166,38 @@
         <v>COGS</v>
       </c>
       <c r="D352" t="str">
-        <v>Pineapple</v>
+        <v>Mango</v>
       </c>
       <c r="E352" t="str">
-        <v>1 สับปะรด 15 ลูก 750 2 สับปะรด 15 ลูก 729 (LINE_ALBUM_Cost July_260802_30.jpg)</v>
+        <v>มะม่วง 4 ลัง (LINE_ALBUM_Cost July_260802_24.jpg)</v>
       </c>
       <c r="F352">
-        <v>1479</v>
+        <v>4680</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>03/07/2026</v>
+        <v>31/07/2026</v>
       </c>
       <c r="B353" t="str">
         <v>Jul26</v>
       </c>
       <c r="C353" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D353" t="str">
-        <v>Apple</v>
+        <v>Other</v>
       </c>
       <c r="E353" t="str">
-        <v>แอปเปิ้ล 3 ลัง (LINE_ALBUM_Cost July_260802_31.jpg)</v>
+        <v>ค่าขนส่ง (LINE_ALBUM_Cost July_260802_25.jpg)</v>
       </c>
       <c r="F353">
-        <v>1140</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>03/07/2026</v>
+        <v>31/07/2026</v>
       </c>
       <c r="B354" t="str">
         <v>Jul26</v>
@@ -8206,18 +8206,18 @@
         <v>COGS</v>
       </c>
       <c r="D354" t="str">
-        <v>Mango</v>
+        <v>Guava</v>
       </c>
       <c r="E354" t="str">
-        <v>มะม่วง 1 ลัง (LINE_ALBUM_Cost July_260802_32.jpg)</v>
+        <v>ฝรั่ง 3 ลัง (LINE_ALBUM_Cost July_260802_26.jpg)</v>
       </c>
       <c r="F354">
-        <v>1040</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>03/07/2026</v>
+        <v>31/07/2026</v>
       </c>
       <c r="B355" t="str">
         <v>Jul26</v>
@@ -8226,18 +8226,18 @@
         <v>COGS</v>
       </c>
       <c r="D355" t="str">
-        <v>Guava</v>
+        <v>Other</v>
       </c>
       <c r="E355" t="str">
-        <v>ฝรั่ง 1 ลัง (LINE_ALBUM_Cost July_260802_33.jpg)</v>
+        <v>ทุเรียน 20.6 กิโลกรัม (LINE_ALBUM_Cost July_260802_27.jpg)</v>
       </c>
       <c r="F355">
-        <v>900</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>03/07/2026</v>
+        <v>31/07/2026</v>
       </c>
       <c r="B356" t="str">
         <v>Jul26</v>
@@ -8249,35 +8249,35 @@
         <v>Other</v>
       </c>
       <c r="E356" t="str">
-        <v>ค่าส่ง (LINE_ALBUM_Cost July_260802_34.jpg)</v>
+        <v>ตะกร้าแต่งร้าน 3 (LINE_ALBUM_Cost July_260802_28.jpg)</v>
       </c>
       <c r="F356">
-        <v>2000</v>
+        <v>558</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>06/07/2026</v>
+        <v>02/07/2026</v>
       </c>
       <c r="B357" t="str">
         <v>Jul26</v>
       </c>
       <c r="C357" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D357" t="str">
-        <v>Rental</v>
+        <v>Orange</v>
       </c>
       <c r="E357" t="str">
-        <v>ค่าเช่า stock เดือน june (1/3 split B1) (LINE_ALBUM_Cost July_260802_35.jpg)</v>
+        <v>ค่าส่งส้มเดือน 6 (LINE_ALBUM_Cost July_260802_29.jpg)</v>
       </c>
       <c r="F357">
-        <v>4000</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>06/07/2026</v>
+        <v>03/07/2026</v>
       </c>
       <c r="B358" t="str">
         <v>Jul26</v>
@@ -8289,15 +8289,15 @@
         <v>Pineapple</v>
       </c>
       <c r="E358" t="str">
-        <v>สับปะรด 20 ลูก (LINE_ALBUM_Cost July_260802_36.jpg)</v>
+        <v>1 สับปะรด 15 ลูก 750 2 สับปะรด 15 ลูก 729 (LINE_ALBUM_Cost July_260802_30.jpg)</v>
       </c>
       <c r="F358">
-        <v>783</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>06/07/2026</v>
+        <v>03/07/2026</v>
       </c>
       <c r="B359" t="str">
         <v>Jul26</v>
@@ -8306,18 +8306,18 @@
         <v>COGS</v>
       </c>
       <c r="D359" t="str">
-        <v>Mango</v>
+        <v>Apple</v>
       </c>
       <c r="E359" t="str">
-        <v>มะม่วง 2 ลัง (LINE_ALBUM_Cost July_260802_37.jpg)</v>
+        <v>แอปเปิ้ล 3 ลัง (LINE_ALBUM_Cost July_260802_31.jpg)</v>
       </c>
       <c r="F359">
-        <v>2340</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>06/07/2026</v>
+        <v>03/07/2026</v>
       </c>
       <c r="B360" t="str">
         <v>Jul26</v>
@@ -8326,18 +8326,18 @@
         <v>COGS</v>
       </c>
       <c r="D360" t="str">
-        <v>Guava</v>
+        <v>Mango</v>
       </c>
       <c r="E360" t="str">
-        <v>ฝรั่ง 1 ตะกร้า (LINE_ALBUM_Cost July_260802_38.jpg)</v>
+        <v>มะม่วง 1 ลัง (LINE_ALBUM_Cost July_260802_32.jpg)</v>
       </c>
       <c r="F360">
-        <v>900</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>06/07/2026</v>
+        <v>03/07/2026</v>
       </c>
       <c r="B361" t="str">
         <v>Jul26</v>
@@ -8346,10 +8346,10 @@
         <v>COGS</v>
       </c>
       <c r="D361" t="str">
-        <v>Apple</v>
+        <v>Guava</v>
       </c>
       <c r="E361" t="str">
-        <v>แอปเปิ้ล 3 ลัง (LINE_ALBUM_Cost July_260802_39.jpg)</v>
+        <v>ฝรั่ง 1 ลัง (LINE_ALBUM_Cost July_260802_33.jpg)</v>
       </c>
       <c r="F361">
         <v>900</v>
@@ -8357,27 +8357,27 @@
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>08/07/2026</v>
+        <v>03/07/2026</v>
       </c>
       <c r="B362" t="str">
         <v>Jul26</v>
       </c>
       <c r="C362" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D362" t="str">
-        <v>Watermelon</v>
+        <v>Other</v>
       </c>
       <c r="E362" t="str">
-        <v>แตงโม 3-7-69 36 ลูก ลูกละ 80 บาท 6-7-69 50 ลูก ลูกละ 80 บาท (LINE_ALBUM_Cost July_260802_40.jpg)</v>
+        <v>ค่าส่ง (LINE_ALBUM_Cost July_260802_34.jpg)</v>
       </c>
       <c r="F362">
-        <v>6880</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>08/07/2026</v>
+        <v>06/07/2026</v>
       </c>
       <c r="B363" t="str">
         <v>Jul26</v>
@@ -8386,18 +8386,18 @@
         <v>OPEX</v>
       </c>
       <c r="D363" t="str">
-        <v>Other</v>
+        <v>Rental</v>
       </c>
       <c r="E363" t="str">
-        <v>เต้น (tent) (LINE_ALBUM_Cost July_260802_41.jpg)</v>
+        <v>ค่าเช่า stock เดือน june (1/3 split B1) (LINE_ALBUM_Cost July_260802_35.jpg)</v>
       </c>
       <c r="F363">
-        <v>1342</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>09/07/2026</v>
+        <v>06/07/2026</v>
       </c>
       <c r="B364" t="str">
         <v>Jul26</v>
@@ -8406,18 +8406,18 @@
         <v>COGS</v>
       </c>
       <c r="D364" t="str">
-        <v>Coconut</v>
+        <v>Pineapple</v>
       </c>
       <c r="E364" t="str">
-        <v>น้ำ 25ลิตร ลิตรละ45บาท เนื้อคว้าน 50kg.กิโลละ 100บาท ค่าส่ง350บาท (LINE_ALBUM_Cost July_260802_42.jpg)</v>
+        <v>สับปะรด 20 ลูก (LINE_ALBUM_Cost July_260802_36.jpg)</v>
       </c>
       <c r="F364">
-        <v>6470</v>
+        <v>783</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>10/07/2026</v>
+        <v>06/07/2026</v>
       </c>
       <c r="B365" t="str">
         <v>Jul26</v>
@@ -8426,18 +8426,18 @@
         <v>COGS</v>
       </c>
       <c r="D365" t="str">
-        <v>Guava</v>
+        <v>Mango</v>
       </c>
       <c r="E365" t="str">
-        <v>ฝรั่ง 1 ลัง (LINE_ALBUM_Cost July_260802_43.jpg)</v>
+        <v>มะม่วง 2 ลัง (LINE_ALBUM_Cost July_260802_37.jpg)</v>
       </c>
       <c r="F365">
-        <v>900</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>10/07/2026</v>
+        <v>06/07/2026</v>
       </c>
       <c r="B366" t="str">
         <v>Jul26</v>
@@ -8446,18 +8446,18 @@
         <v>COGS</v>
       </c>
       <c r="D366" t="str">
-        <v>Apple</v>
+        <v>Guava</v>
       </c>
       <c r="E366" t="str">
-        <v>Apple 5 box (LINE_ALBUM_Cost July_260802_44.jpg)</v>
+        <v>ฝรั่ง 1 ตะกร้า (LINE_ALBUM_Cost July_260802_38.jpg)</v>
       </c>
       <c r="F366">
-        <v>1500</v>
+        <v>900</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>11/07/2026</v>
+        <v>06/07/2026</v>
       </c>
       <c r="B367" t="str">
         <v>Jul26</v>
@@ -8466,10 +8466,10 @@
         <v>COGS</v>
       </c>
       <c r="D367" t="str">
-        <v>Guava</v>
+        <v>Apple</v>
       </c>
       <c r="E367" t="str">
-        <v>ฝรั่ง 1 ตะกร้า (LINE_ALBUM_Cost July_260802_45.jpg)</v>
+        <v>แอปเปิ้ล 3 ลัง (LINE_ALBUM_Cost July_260802_39.jpg)</v>
       </c>
       <c r="F367">
         <v>900</v>
@@ -8477,7 +8477,7 @@
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>11/07/2026</v>
+        <v>08/07/2026</v>
       </c>
       <c r="B368" t="str">
         <v>Jul26</v>
@@ -8486,58 +8486,58 @@
         <v>COGS</v>
       </c>
       <c r="D368" t="str">
-        <v>Mango</v>
+        <v>Watermelon</v>
       </c>
       <c r="E368" t="str">
-        <v>มะม่วง 3 ลัง (LINE_ALBUM_Cost July_260802_46.jpg)</v>
+        <v>แตงโม 3-7-69 36 ลูก ลูกละ 80 บาท 6-7-69 50 ลูก ลูกละ 80 บาท (LINE_ALBUM_Cost July_260802_40.jpg)</v>
       </c>
       <c r="F368">
-        <v>4300</v>
+        <v>6880</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>11/07/2026</v>
+        <v>08/07/2026</v>
       </c>
       <c r="B369" t="str">
         <v>Jul26</v>
       </c>
       <c r="C369" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D369" t="str">
-        <v>Apple</v>
+        <v>Other</v>
       </c>
       <c r="E369" t="str">
-        <v>แอปเปิ้ล 3 ลัง (LINE_ALBUM_Cost July_260802_47.jpg)</v>
+        <v>เต้น (tent) (LINE_ALBUM_Cost July_260802_41.jpg)</v>
       </c>
       <c r="F369">
-        <v>900</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>13/07/2026</v>
+        <v>09/07/2026</v>
       </c>
       <c r="B370" t="str">
         <v>Jul26</v>
       </c>
       <c r="C370" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D370" t="str">
-        <v>Other</v>
+        <v>Coconut</v>
       </c>
       <c r="E370" t="str">
-        <v>ค่าขนส่ง (LINE_ALBUM_Cost July_260802_48.jpg)</v>
+        <v>น้ำ 25ลิตร ลิตรละ45บาท เนื้อคว้าน 50kg.กิโลละ 100บาท ค่าส่ง350บาท (LINE_ALBUM_Cost July_260802_42.jpg)</v>
       </c>
       <c r="F370">
-        <v>344</v>
+        <v>6470</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>13/07/2026</v>
+        <v>10/07/2026</v>
       </c>
       <c r="B371" t="str">
         <v>Jul26</v>
@@ -8546,18 +8546,18 @@
         <v>COGS</v>
       </c>
       <c r="D371" t="str">
-        <v>Packaging</v>
+        <v>Guava</v>
       </c>
       <c r="E371" t="str">
-        <v>ทิชชู4(636) หลอด20 (671) ถุงเล็ก3(605) ถุงใหญ่2(943) (LINE_ALBUM_Cost July_260802_49.jpg)</v>
+        <v>ฝรั่ง 1 ลัง (LINE_ALBUM_Cost July_260802_43.jpg)</v>
       </c>
       <c r="F371">
-        <v>2855</v>
+        <v>900</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>13/07/2026</v>
+        <v>10/07/2026</v>
       </c>
       <c r="B372" t="str">
         <v>Jul26</v>
@@ -8566,18 +8566,18 @@
         <v>COGS</v>
       </c>
       <c r="D372" t="str">
-        <v>Packaging</v>
+        <v>Apple</v>
       </c>
       <c r="E372" t="str">
-        <v>แก้ว98 4ลัง 7656-635 7,021 ฝา635 (LINE_ALBUM_Cost July_260802_50.jpg)</v>
+        <v>Apple 5 box (LINE_ALBUM_Cost July_260802_44.jpg)</v>
       </c>
       <c r="F372">
-        <v>7656</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>14/07/2026</v>
+        <v>11/07/2026</v>
       </c>
       <c r="B373" t="str">
         <v>Jul26</v>
@@ -8586,18 +8586,18 @@
         <v>COGS</v>
       </c>
       <c r="D373" t="str">
-        <v>Pineapple</v>
+        <v>Guava</v>
       </c>
       <c r="E373" t="str">
-        <v>11/7/69 10 ลูก 620 14/7/69 25 ลูก 1269 (LINE_ALBUM_Cost July_260802_51.jpg)</v>
+        <v>ฝรั่ง 1 ตะกร้า (LINE_ALBUM_Cost July_260802_45.jpg)</v>
       </c>
       <c r="F373">
-        <v>1889</v>
+        <v>900</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>14/07/2026</v>
+        <v>11/07/2026</v>
       </c>
       <c r="B374" t="str">
         <v>Jul26</v>
@@ -8606,18 +8606,18 @@
         <v>COGS</v>
       </c>
       <c r="D374" t="str">
-        <v>Apple</v>
+        <v>Mango</v>
       </c>
       <c r="E374" t="str">
-        <v>Apple 3 ลัง (LINE_ALBUM_Cost July_260802_52.jpg)</v>
+        <v>มะม่วง 3 ลัง (LINE_ALBUM_Cost July_260802_46.jpg)</v>
       </c>
       <c r="F374">
-        <v>1200</v>
+        <v>4300</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>15/07/2026</v>
+        <v>11/07/2026</v>
       </c>
       <c r="B375" t="str">
         <v>Jul26</v>
@@ -8626,38 +8626,38 @@
         <v>COGS</v>
       </c>
       <c r="D375" t="str">
-        <v>Guava</v>
+        <v>Apple</v>
       </c>
       <c r="E375" t="str">
-        <v>ฝรั่ง 2 ตะกร้า ตะกร้าละ 20 โล (LINE_ALBUM_Cost July_260802_53.jpg)</v>
+        <v>แอปเปิ้ล 3 ลัง (LINE_ALBUM_Cost July_260802_47.jpg)</v>
       </c>
       <c r="F375">
-        <v>2000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>16/07/2026</v>
+        <v>13/07/2026</v>
       </c>
       <c r="B376" t="str">
         <v>Jul26</v>
       </c>
       <c r="C376" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D376" t="str">
-        <v>Orange</v>
+        <v>Other</v>
       </c>
       <c r="E376" t="str">
-        <v>รอบ 01/07/69 ส้ม 28x22กก 616กกx30 18,480บาท ค่าขนส่ง 28ตกx 55 1540 (LINE_ALBUM_Cost July_260802_54.jpg)</v>
+        <v>ค่าขนส่ง (LINE_ALBUM_Cost July_260802_48.jpg)</v>
       </c>
       <c r="F376">
-        <v>20020</v>
+        <v>344</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>17/07/2026</v>
+        <v>13/07/2026</v>
       </c>
       <c r="B377" t="str">
         <v>Jul26</v>
@@ -8666,18 +8666,18 @@
         <v>COGS</v>
       </c>
       <c r="D377" t="str">
-        <v>Orange</v>
+        <v>Packaging</v>
       </c>
       <c r="E377" t="str">
-        <v>ส้ม 125 โล 3450 ค่าส่ง 300 (LINE_ALBUM_Cost July_260802_55.jpg)</v>
+        <v>ทิชชู4(636) หลอด20 (671) ถุงเล็ก3(605) ถุงใหญ่2(943) (LINE_ALBUM_Cost July_260802_49.jpg)</v>
       </c>
       <c r="F377">
-        <v>3750</v>
+        <v>2855</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>17/07/2026</v>
+        <v>13/07/2026</v>
       </c>
       <c r="B378" t="str">
         <v>Jul26</v>
@@ -8686,18 +8686,18 @@
         <v>COGS</v>
       </c>
       <c r="D378" t="str">
-        <v>Pineapple</v>
+        <v>Packaging</v>
       </c>
       <c r="E378" t="str">
-        <v>สับปะรด 25 ลูก (LINE_ALBUM_Cost July_260802_56.jpg)</v>
+        <v>แก้ว98 4ลัง 7656-635 7,021 ฝา635 (LINE_ALBUM_Cost July_260802_50.jpg)</v>
       </c>
       <c r="F378">
-        <v>1539</v>
+        <v>7656</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>17/07/2026</v>
+        <v>14/07/2026</v>
       </c>
       <c r="B379" t="str">
         <v>Jul26</v>
@@ -8706,18 +8706,18 @@
         <v>COGS</v>
       </c>
       <c r="D379" t="str">
-        <v>Watermelon</v>
+        <v>Pineapple</v>
       </c>
       <c r="E379" t="str">
-        <v>แตงโม 10-7-69 50 ลูก 4000 11-7-69 40 ลูก 3200 (LINE_ALBUM_Cost July_260802_57.jpg)</v>
+        <v>11/7/69 10 ลูก 620 14/7/69 25 ลูก 1269 (LINE_ALBUM_Cost July_260802_51.jpg)</v>
       </c>
       <c r="F379">
-        <v>7200</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>17/07/2026</v>
+        <v>14/07/2026</v>
       </c>
       <c r="B380" t="str">
         <v>Jul26</v>
@@ -8726,18 +8726,18 @@
         <v>COGS</v>
       </c>
       <c r="D380" t="str">
-        <v>Other</v>
+        <v>Apple</v>
       </c>
       <c r="E380" t="str">
-        <v>ทุเรียน 50 โล โลละ 85 รวม 4250 มัดจำตะกร้า 200 (LINE_ALBUM_Cost July_260802_58.jpg)</v>
+        <v>Apple 3 ลัง (LINE_ALBUM_Cost July_260802_52.jpg)</v>
       </c>
       <c r="F380">
-        <v>4450</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>17/07/2026</v>
+        <v>15/07/2026</v>
       </c>
       <c r="B381" t="str">
         <v>Jul26</v>
@@ -8746,18 +8746,18 @@
         <v>COGS</v>
       </c>
       <c r="D381" t="str">
-        <v>Watermelon</v>
+        <v>Guava</v>
       </c>
       <c r="E381" t="str">
-        <v>แตงโม 14-7-69 50 ลูก 4000 (LINE_ALBUM_Cost July_260802_59.jpg)</v>
+        <v>ฝรั่ง 2 ตะกร้า ตะกร้าละ 20 โล (LINE_ALBUM_Cost July_260802_53.jpg)</v>
       </c>
       <c r="F381">
-        <v>4000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>17/07/2026</v>
+        <v>16/07/2026</v>
       </c>
       <c r="B382" t="str">
         <v>Jul26</v>
@@ -8766,13 +8766,13 @@
         <v>COGS</v>
       </c>
       <c r="D382" t="str">
-        <v>Mango</v>
+        <v>Orange</v>
       </c>
       <c r="E382" t="str">
-        <v>มะม่วง 52 โล(2 ตะกร้า) โลละ 50 (LINE_ALBUM_Cost July_260802_60.jpg)</v>
+        <v>รอบ 01/07/69 ส้ม 28x22กก 616กกx30 18,480บาท ค่าขนส่ง 28ตกx 55 1540 (LINE_ALBUM_Cost July_260802_54.jpg)</v>
       </c>
       <c r="F382">
-        <v>2600</v>
+        <v>20020</v>
       </c>
     </row>
     <row r="383">
@@ -8786,13 +8786,13 @@
         <v>COGS</v>
       </c>
       <c r="D383" t="str">
-        <v>Guava</v>
+        <v>Orange</v>
       </c>
       <c r="E383" t="str">
-        <v>ฝรั่ง 2 ตะกร้า (ตะกร้าละ 20 โล) (LINE_ALBUM_Cost July_260802_61.jpg)</v>
+        <v>ส้ม 125 โล 3450 ค่าส่ง 300 (LINE_ALBUM_Cost July_260802_55.jpg)</v>
       </c>
       <c r="F383">
-        <v>2000</v>
+        <v>3750</v>
       </c>
     </row>
     <row r="384">
@@ -8806,13 +8806,13 @@
         <v>COGS</v>
       </c>
       <c r="D384" t="str">
-        <v>Apple</v>
+        <v>Pineapple</v>
       </c>
       <c r="E384" t="str">
-        <v>แอปเปิ้ล 5 ลัง (LINE_ALBUM_Cost July_260802_62.jpg)</v>
+        <v>สับปะรด 25 ลูก (LINE_ALBUM_Cost July_260802_56.jpg)</v>
       </c>
       <c r="F384">
-        <v>2000</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="385">
@@ -8826,18 +8826,18 @@
         <v>COGS</v>
       </c>
       <c r="D385" t="str">
-        <v>Coconut</v>
+        <v>Watermelon</v>
       </c>
       <c r="E385" t="str">
-        <v>น้ำ 30ลิตร ลิตรละ45บาท เนื้อมะพร้าว 50kg.กิโลละ 100บาท ค่าส่ง350 (LINE_ALBUM_Cost July_260802_63.jpg)</v>
+        <v>แตงโม 10-7-69 50 ลูก 4000 11-7-69 40 ลูก 3200 (LINE_ALBUM_Cost July_260802_57.jpg)</v>
       </c>
       <c r="F385">
-        <v>6700</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>20/07/2026</v>
+        <v>17/07/2026</v>
       </c>
       <c r="B386" t="str">
         <v>Jul26</v>
@@ -8846,18 +8846,18 @@
         <v>COGS</v>
       </c>
       <c r="D386" t="str">
-        <v>Guava</v>
+        <v>Other</v>
       </c>
       <c r="E386" t="str">
-        <v>ฝรั่ง 2 ตะกร้า (LINE_ALBUM_Cost July_260802_64.jpg)</v>
+        <v>ทุเรียน 50 โล โลละ 85 รวม 4250 มัดจำตะกร้า 200 (LINE_ALBUM_Cost July_260802_58.jpg)</v>
       </c>
       <c r="F386">
-        <v>2000</v>
+        <v>4450</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>20/07/2026</v>
+        <v>17/07/2026</v>
       </c>
       <c r="B387" t="str">
         <v>Jul26</v>
@@ -8866,18 +8866,18 @@
         <v>COGS</v>
       </c>
       <c r="D387" t="str">
-        <v>Pineapple</v>
+        <v>Watermelon</v>
       </c>
       <c r="E387" t="str">
-        <v>สับปะรด 20 ลูก (LINE_ALBUM_Cost July_260802_65.jpg)</v>
+        <v>แตงโม 14-7-69 50 ลูก 4000 (LINE_ALBUM_Cost July_260802_59.jpg)</v>
       </c>
       <c r="F387">
-        <v>1296</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>20/07/2026</v>
+        <v>17/07/2026</v>
       </c>
       <c r="B388" t="str">
         <v>Jul26</v>
@@ -8889,7 +8889,7 @@
         <v>Mango</v>
       </c>
       <c r="E388" t="str">
-        <v>มะม่วง 2 ลัง (LINE_ALBUM_Cost July_260802_66.jpg)</v>
+        <v>มะม่วง 52 โล(2 ตะกร้า) โลละ 50 (LINE_ALBUM_Cost July_260802_60.jpg)</v>
       </c>
       <c r="F388">
         <v>2600</v>
@@ -8897,7 +8897,7 @@
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>20/07/2026</v>
+        <v>17/07/2026</v>
       </c>
       <c r="B389" t="str">
         <v>Jul26</v>
@@ -8906,30 +8906,30 @@
         <v>COGS</v>
       </c>
       <c r="D389" t="str">
-        <v>Watermelon</v>
+        <v>Guava</v>
       </c>
       <c r="E389" t="str">
-        <v>แตงโม 17-7-2569 เบอร์ 80บาท 50 ลูก (LINE_ALBUM_Cost July_260802_67.jpg)</v>
+        <v>ฝรั่ง 2 ตะกร้า (ตะกร้าละ 20 โล) (LINE_ALBUM_Cost July_260802_61.jpg)</v>
       </c>
       <c r="F389">
-        <v>4000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>21/07/2026</v>
+        <v>17/07/2026</v>
       </c>
       <c r="B390" t="str">
         <v>Jul26</v>
       </c>
       <c r="C390" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D390" t="str">
-        <v>Other</v>
+        <v>Apple</v>
       </c>
       <c r="E390" t="str">
-        <v xml:space="preserve"> (LINE_ALBUM_Cost July_260802_68.jpg)</v>
+        <v>แอปเปิ้ล 5 ลัง (LINE_ALBUM_Cost July_260802_62.jpg)</v>
       </c>
       <c r="F390">
         <v>2000</v>
@@ -8937,7 +8937,7 @@
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>22/07/2026</v>
+        <v>17/07/2026</v>
       </c>
       <c r="B391" t="str">
         <v>Jul26</v>
@@ -8946,18 +8946,18 @@
         <v>COGS</v>
       </c>
       <c r="D391" t="str">
-        <v>Orange</v>
+        <v>Coconut</v>
       </c>
       <c r="E391" t="str">
-        <v>ส้ม 25x22กก รวม 550กกx30 บ รวม 16500บาท ค่าขนส่ง 25ตกx 50 บ 1250 (LINE_ALBUM_Cost July_260802_69.jpg)</v>
+        <v>น้ำ 30ลิตร ลิตรละ45บาท เนื้อมะพร้าว 50kg.กิโลละ 100บาท ค่าส่ง350 (LINE_ALBUM_Cost July_260802_63.jpg)</v>
       </c>
       <c r="F391">
-        <v>17750</v>
+        <v>6700</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>22/07/2026</v>
+        <v>20/07/2026</v>
       </c>
       <c r="B392" t="str">
         <v>Jul26</v>
@@ -8966,18 +8966,18 @@
         <v>COGS</v>
       </c>
       <c r="D392" t="str">
-        <v>Apple</v>
+        <v>Guava</v>
       </c>
       <c r="E392" t="str">
-        <v>แอปเปิ้ล 4 ลัง (LINE_ALBUM_Cost July_260802_70.jpg)</v>
+        <v>ฝรั่ง 2 ตะกร้า (LINE_ALBUM_Cost July_260802_64.jpg)</v>
       </c>
       <c r="F392">
-        <v>1600</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>22/07/2026</v>
+        <v>20/07/2026</v>
       </c>
       <c r="B393" t="str">
         <v>Jul26</v>
@@ -8986,58 +8986,58 @@
         <v>COGS</v>
       </c>
       <c r="D393" t="str">
-        <v>Mango</v>
+        <v>Pineapple</v>
       </c>
       <c r="E393" t="str">
-        <v>มะม่วง 78 กิโล 3 ลัง (LINE_ALBUM_Cost July_260802_71.jpg)</v>
+        <v>สับปะรด 20 ลูก (LINE_ALBUM_Cost July_260802_65.jpg)</v>
       </c>
       <c r="F393">
-        <v>3900</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>22/07/2026</v>
+        <v>20/07/2026</v>
       </c>
       <c r="B394" t="str">
         <v>Jul26</v>
       </c>
       <c r="C394" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D394" t="str">
-        <v>Other</v>
+        <v>Mango</v>
       </c>
       <c r="E394" t="str">
-        <v>OPEX Avocado milk (LINE_ALBUM_Cost July_260802_74.jpg)</v>
+        <v>มะม่วง 2 ลัง (LINE_ALBUM_Cost July_260802_66.jpg)</v>
       </c>
       <c r="F394">
-        <v>440.75</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>22/07/2026</v>
+        <v>20/07/2026</v>
       </c>
       <c r="B395" t="str">
         <v>Jul26</v>
       </c>
       <c r="C395" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D395" t="str">
-        <v>Other</v>
+        <v>Watermelon</v>
       </c>
       <c r="E395" t="str">
-        <v>Opex knife (LINE_ALBUM_Cost July_260802_75.jpg)</v>
+        <v>แตงโม 17-7-2569 เบอร์ 80บาท 50 ลูก (LINE_ALBUM_Cost July_260802_67.jpg)</v>
       </c>
       <c r="F395">
-        <v>199</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>22/07/2026</v>
+        <v>21/07/2026</v>
       </c>
       <c r="B396" t="str">
         <v>Jul26</v>
@@ -9049,10 +9049,10 @@
         <v>Other</v>
       </c>
       <c r="E396" t="str">
-        <v>Opex equipment (LINE_ALBUM_Cost July_260802_76.jpg)</v>
+        <v xml:space="preserve"> (LINE_ALBUM_Cost July_260802_68.jpg)</v>
       </c>
       <c r="F396">
-        <v>221</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="397">
@@ -9066,13 +9066,13 @@
         <v>COGS</v>
       </c>
       <c r="D397" t="str">
-        <v>Stock</v>
+        <v>Orange</v>
       </c>
       <c r="E397" t="str">
-        <v>Cogs Falcon milk (LINE_ALBUM_Cost July_260802_77.jpg)</v>
+        <v>ส้ม 25x22กก รวม 550กกx30 บ รวม 16500บาท ค่าขนส่ง 25ตกx 50 บ 1250 (LINE_ALBUM_Cost July_260802_69.jpg)</v>
       </c>
       <c r="F397">
-        <v>716</v>
+        <v>17750</v>
       </c>
     </row>
     <row r="398">
@@ -9083,16 +9083,16 @@
         <v>Jul26</v>
       </c>
       <c r="C398" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D398" t="str">
-        <v>Other</v>
+        <v>Apple</v>
       </c>
       <c r="E398" t="str">
-        <v>Opex B1 police fee 1000 / person (LINE_ALBUM_Cost July_260802_78.jpg)</v>
+        <v>แอปเปิ้ล 4 ลัง (LINE_ALBUM_Cost July_260802_70.jpg)</v>
       </c>
       <c r="F398">
-        <v>2000</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="399">
@@ -9103,16 +9103,16 @@
         <v>Jul26</v>
       </c>
       <c r="C399" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D399" t="str">
-        <v>Other</v>
+        <v>Mango</v>
       </c>
       <c r="E399" t="str">
-        <v>Opex equipments (LINE_ALBUM_Cost July_260802_79.jpg)</v>
+        <v>มะม่วง 78 กิโล 3 ลัง (LINE_ALBUM_Cost July_260802_71.jpg)</v>
       </c>
       <c r="F399">
-        <v>506</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="400">
@@ -9129,55 +9129,55 @@
         <v>Other</v>
       </c>
       <c r="E400" t="str">
-        <v>Opex other (LINE_ALBUM_Cost July_260802_80.jpg)</v>
+        <v>OPEX Avocado milk (LINE_ALBUM_Cost July_260802_74.jpg)</v>
       </c>
       <c r="F400">
-        <v>1918</v>
+        <v>440.75</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>23/07/2026</v>
+        <v>22/07/2026</v>
       </c>
       <c r="B401" t="str">
         <v>Jul26</v>
       </c>
       <c r="C401" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D401" t="str">
-        <v>Watermelon</v>
+        <v>Other</v>
       </c>
       <c r="E401" t="str">
-        <v>20-7-2569 ราคา 80 - 45ลูก 22-7-2569 ราคา 80 - 30 ลูก 23-7-2569 ราคา 80 - 30 ลูก (LINE_ALBUM_Cost July_260802_81.jpg)</v>
+        <v>Opex knife (LINE_ALBUM_Cost July_260802_75.jpg)</v>
       </c>
       <c r="F401">
-        <v>8400</v>
+        <v>199</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>23/07/2026</v>
+        <v>22/07/2026</v>
       </c>
       <c r="B402" t="str">
         <v>Jul26</v>
       </c>
       <c r="C402" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D402" t="str">
-        <v>Guava</v>
+        <v>Other</v>
       </c>
       <c r="E402" t="str">
-        <v>ฝรั่ง 2 ลัง ลังละ 20 กิโล กิโลละ 50 บาท รวม 2000 บาท (LINE_ALBUM_Cost July_260802_82.jpg)</v>
+        <v>Opex equipment (LINE_ALBUM_Cost July_260802_76.jpg)</v>
       </c>
       <c r="F402">
-        <v>2000</v>
+        <v>221</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>23/07/2026</v>
+        <v>22/07/2026</v>
       </c>
       <c r="B403" t="str">
         <v>Jul26</v>
@@ -9186,18 +9186,18 @@
         <v>COGS</v>
       </c>
       <c r="D403" t="str">
-        <v>Pineapple</v>
+        <v>Milk/Conden</v>
       </c>
       <c r="E403" t="str">
-        <v>สับปะรด 41 กิโล *27 บาท รวม 1107 บาท (LINE_ALBUM_Cost July_260802_83.jpg)</v>
+        <v>นมข้นจืด Falcon (LINE_ALBUM_Cost July_260802_77.jpg)</v>
       </c>
       <c r="F403">
-        <v>1107</v>
+        <v>716</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>31/07/2026</v>
+        <v>22/07/2026</v>
       </c>
       <c r="B404" t="str">
         <v>Jul26</v>
@@ -9206,18 +9206,18 @@
         <v>OPEX</v>
       </c>
       <c r="D404" t="str">
-        <v>Rental</v>
+        <v>Other</v>
       </c>
       <c r="E404" t="str">
-        <v>ค่าเช่าร้าน B1 ก.ค. (จ่ายเงินสดจากหน้าร้านก่อนนำเข้าบัญชี - ไม่มีสลิป ยืนยันโดยเจ้าของ 28/08)</v>
+        <v>Opex B1 police fee 1000 / person (LINE_ALBUM_Cost July_260802_78.jpg)</v>
       </c>
       <c r="F404">
-        <v>35000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>31/07/2026</v>
+        <v>22/07/2026</v>
       </c>
       <c r="B405" t="str">
         <v>Jul26</v>
@@ -9226,301 +9226,301 @@
         <v>OPEX</v>
       </c>
       <c r="D405" t="str">
-        <v>Salary</v>
+        <v>Other</v>
       </c>
       <c r="E405" t="str">
-        <v>Salary B1</v>
+        <v>Opex equipments (LINE_ALBUM_Cost July_260802_79.jpg)</v>
       </c>
       <c r="F405">
-        <v>35000</v>
+        <v>506</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>23/05/2026</v>
+        <v>22/07/2026</v>
       </c>
       <c r="B406" t="str">
-        <v>May26</v>
+        <v>Jul26</v>
       </c>
       <c r="C406" t="str">
-        <v>EXCLUDED</v>
+        <v>OPEX</v>
       </c>
       <c r="D406" t="str">
-        <v>Pass-Through</v>
+        <v>Other</v>
       </c>
       <c r="E406" t="str">
-        <v>มังคุด (รับเงินสด 28,000 แล้วโอนต่อ ฐนกร 23/05 17:23) - ไม่ใช่ต้นทุน SSJ [bank]</v>
+        <v>Opex other (LINE_ALBUM_Cost July_260802_80.jpg)</v>
       </c>
       <c r="F406">
-        <v>0</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>01/05/2026</v>
+        <v>23/07/2026</v>
       </c>
       <c r="B407" t="str">
-        <v>May26</v>
+        <v>Jul26</v>
       </c>
       <c r="C407" t="str">
         <v>COGS</v>
       </c>
       <c r="D407" t="str">
-        <v>Transportation</v>
+        <v>Watermelon</v>
       </c>
       <c r="E407" t="str">
-        <v>ลาลามูฟ Lalamove [bank]</v>
+        <v>20-7-2569 ราคา 80 - 45ลูก 22-7-2569 ราคา 80 - 30 ลูก 23-7-2569 ราคา 80 - 30 ลูก (LINE_ALBUM_Cost July_260802_81.jpg)</v>
       </c>
       <c r="F407">
-        <v>2000</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>07/05/2026</v>
+        <v>23/07/2026</v>
       </c>
       <c r="B408" t="str">
-        <v>May26</v>
+        <v>Jul26</v>
       </c>
       <c r="C408" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D408" t="str">
-        <v>Other</v>
+        <v>Guava</v>
       </c>
       <c r="E408" t="str">
-        <v>บจก. อาร์.เอ็น.คลีน ทำความสะอาด [bank]</v>
+        <v>ฝรั่ง 2 ลัง ลังละ 20 กิโล กิโลละ 50 บาท รวม 2000 บาท (LINE_ALBUM_Cost July_260802_82.jpg)</v>
       </c>
       <c r="F408">
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>01/05/2026</v>
+        <v>23/07/2026</v>
       </c>
       <c r="B409" t="str">
-        <v>May26</v>
+        <v>Jul26</v>
       </c>
       <c r="C409" t="str">
         <v>COGS</v>
       </c>
       <c r="D409" t="str">
-        <v>Mango</v>
+        <v>Pineapple</v>
       </c>
       <c r="E409" t="str">
-        <v>LINE Pay Merchant [bank]</v>
+        <v>สับปะรด 41 กิโล *27 บาท รวม 1107 บาท (LINE_ALBUM_Cost July_260802_83.jpg)</v>
       </c>
       <c r="F409">
-        <v>780</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>01/05/2026</v>
+        <v>31/07/2026</v>
       </c>
       <c r="B410" t="str">
-        <v>May26</v>
+        <v>Jul26</v>
       </c>
       <c r="C410" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D410" t="str">
-        <v>Pineapple</v>
+        <v>Rental</v>
       </c>
       <c r="E410" t="str">
-        <v>น.ส. สุพิชญา [bank]</v>
+        <v>ค่าเช่าร้าน B1 ก.ค. (จ่ายเงินสดจากหน้าร้านก่อนนำเข้าบัญชี - ไม่มีสลิป ยืนยันโดยเจ้าของ 28/08)</v>
       </c>
       <c r="F410">
-        <v>684</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>09/05/2026</v>
+        <v>31/07/2026</v>
       </c>
       <c r="B411" t="str">
-        <v>May26</v>
+        <v>Jul26</v>
       </c>
       <c r="C411" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D411" t="str">
-        <v>Guava</v>
+        <v>Salary</v>
       </c>
       <c r="E411" t="str">
-        <v>ฝรั่ง 1 ตะกร้า (นาง ประนอม) [bank]</v>
+        <v>Salary B1</v>
       </c>
       <c r="F411">
-        <v>600</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>30/04/2026</v>
+        <v>23/05/2026</v>
       </c>
       <c r="B412" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C412" t="str">
-        <v>OPEX</v>
+        <v>EXCLUDED</v>
       </c>
       <c r="D412" t="str">
-        <v>Marketing</v>
+        <v>Pass-Through</v>
       </c>
       <c r="E412" t="str">
-        <v>ปืนฉีดน้ำ สงกรานต์ (จ่าย 06/05) [bank]</v>
+        <v>มังคุด (รับเงินสด 28,000 แล้วโอนต่อ ฐนกร 23/05 17:23) - ไม่ใช่ต้นทุน SSJ [bank]</v>
       </c>
       <c r="F412">
-        <v>24016</v>
+        <v>0</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>30/04/2026</v>
+        <v>01/05/2026</v>
       </c>
       <c r="B413" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C413" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D413" t="str">
-        <v>Salary</v>
+        <v>Transportation</v>
       </c>
       <c r="E413" t="str">
-        <v>เงินเดือน เม.ย. (จ่าย 01/05) [bank]</v>
+        <v>ลาลามูฟ Lalamove [bank]</v>
       </c>
       <c r="F413">
-        <v>31000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>04/04/2026</v>
+        <v>07/05/2026</v>
       </c>
       <c r="B414" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C414" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D414" t="str">
-        <v>Packaging</v>
+        <v>Other</v>
       </c>
       <c r="E414" t="str">
-        <v>Shopee (ทีมจัดซื้อ) [bank SA8285]</v>
+        <v>บจก. อาร์.เอ็น.คลีน ทำความสะอาด [bank]</v>
       </c>
       <c r="F414">
-        <v>11732</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>05/04/2026</v>
+        <v>01/05/2026</v>
       </c>
       <c r="B415" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C415" t="str">
         <v>COGS</v>
       </c>
       <c r="D415" t="str">
-        <v>Packaging</v>
+        <v>Mango</v>
       </c>
       <c r="E415" t="str">
-        <v>Shopee (ทีมจัดซื้อ) [bank SA8285]</v>
+        <v>LINE Pay Merchant [bank]</v>
       </c>
       <c r="F415">
-        <v>672</v>
+        <v>780</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>16/04/2026</v>
+        <v>01/05/2026</v>
       </c>
       <c r="B416" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C416" t="str">
         <v>COGS</v>
       </c>
       <c r="D416" t="str">
-        <v>Packaging</v>
+        <v>Pineapple</v>
       </c>
       <c r="E416" t="str">
-        <v>Shopee (ทีมจัดซื้อ) [bank SA8285]</v>
+        <v>น.ส. สุพิชญา [bank]</v>
       </c>
       <c r="F416">
-        <v>11560</v>
+        <v>684</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>20/04/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="B417" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C417" t="str">
         <v>COGS</v>
       </c>
       <c r="D417" t="str">
-        <v>Packaging</v>
+        <v>Guava</v>
       </c>
       <c r="E417" t="str">
-        <v>Shopee (ทีมจัดซื้อ) [bank SA8285]</v>
+        <v>ฝรั่ง 1 ตะกร้า (นาง ประนอม) [bank]</v>
       </c>
       <c r="F417">
-        <v>692</v>
+        <v>600</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>25/04/2026</v>
+        <v>30/04/2026</v>
       </c>
       <c r="B418" t="str">
         <v>Apr26</v>
       </c>
       <c r="C418" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D418" t="str">
-        <v>Packaging</v>
+        <v>Marketing</v>
       </c>
       <c r="E418" t="str">
-        <v>Shopee (ทีมจัดซื้อ) [bank SA8285]</v>
+        <v>ปืนฉีดน้ำ สงกรานต์ (จ่าย 06/05) [bank]</v>
       </c>
       <c r="F418">
-        <v>1838</v>
+        <v>24016</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>21/06/2026</v>
+        <v>30/04/2026</v>
       </c>
       <c r="B419" t="str">
-        <v>Jun26</v>
+        <v>Apr26</v>
       </c>
       <c r="C419" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D419" t="str">
-        <v>Packaging</v>
+        <v>Salary</v>
       </c>
       <c r="E419" t="str">
-        <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
+        <v>เงินเดือน เม.ย. (จ่าย 01/05) [bank]</v>
       </c>
       <c r="F419">
-        <v>1377</v>
+        <v>31000</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>21/06/2026</v>
+        <v>04/04/2026</v>
       </c>
       <c r="B420" t="str">
-        <v>Jun26</v>
+        <v>Apr26</v>
       </c>
       <c r="C420" t="str">
         <v>COGS</v>
@@ -9529,18 +9529,18 @@
         <v>Packaging</v>
       </c>
       <c r="E420" t="str">
-        <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
+        <v>Shopee (ทีมจัดซื้อ) [bank SA8285]</v>
       </c>
       <c r="F420">
-        <v>1210</v>
+        <v>11732</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>21/06/2026</v>
+        <v>05/04/2026</v>
       </c>
       <c r="B421" t="str">
-        <v>Jun26</v>
+        <v>Apr26</v>
       </c>
       <c r="C421" t="str">
         <v>COGS</v>
@@ -9549,18 +9549,18 @@
         <v>Packaging</v>
       </c>
       <c r="E421" t="str">
-        <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
+        <v>Shopee (ทีมจัดซื้อ) [bank SA8285]</v>
       </c>
       <c r="F421">
-        <v>1210</v>
+        <v>672</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>21/06/2026</v>
+        <v>16/04/2026</v>
       </c>
       <c r="B422" t="str">
-        <v>Jun26</v>
+        <v>Apr26</v>
       </c>
       <c r="C422" t="str">
         <v>COGS</v>
@@ -9569,18 +9569,18 @@
         <v>Packaging</v>
       </c>
       <c r="E422" t="str">
-        <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
+        <v>Shopee (ทีมจัดซื้อ) [bank SA8285]</v>
       </c>
       <c r="F422">
-        <v>1242</v>
+        <v>11560</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>21/06/2026</v>
+        <v>20/04/2026</v>
       </c>
       <c r="B423" t="str">
-        <v>Jun26</v>
+        <v>Apr26</v>
       </c>
       <c r="C423" t="str">
         <v>COGS</v>
@@ -9589,18 +9589,18 @@
         <v>Packaging</v>
       </c>
       <c r="E423" t="str">
-        <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
+        <v>Shopee (ทีมจัดซื้อ) [bank SA8285]</v>
       </c>
       <c r="F423">
-        <v>1232</v>
+        <v>692</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>21/06/2026</v>
+        <v>25/04/2026</v>
       </c>
       <c r="B424" t="str">
-        <v>Jun26</v>
+        <v>Apr26</v>
       </c>
       <c r="C424" t="str">
         <v>COGS</v>
@@ -9609,10 +9609,10 @@
         <v>Packaging</v>
       </c>
       <c r="E424" t="str">
-        <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
+        <v>Shopee (ทีมจัดซื้อ) [bank SA8285]</v>
       </c>
       <c r="F424">
-        <v>1286</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="425">
@@ -9632,7 +9632,7 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F425">
-        <v>1295</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="426">
@@ -9652,7 +9652,7 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F426">
-        <v>1445</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="427">
@@ -9672,7 +9672,7 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F427">
-        <v>3051</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="428">
@@ -9692,12 +9692,12 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F428">
-        <v>755</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>29/06/2026</v>
+        <v>21/06/2026</v>
       </c>
       <c r="B429" t="str">
         <v>Jun26</v>
@@ -9712,12 +9712,12 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F429">
-        <v>7766</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>29/06/2026</v>
+        <v>21/06/2026</v>
       </c>
       <c r="B430" t="str">
         <v>Jun26</v>
@@ -9732,12 +9732,12 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F430">
-        <v>539</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>29/06/2026</v>
+        <v>21/06/2026</v>
       </c>
       <c r="B431" t="str">
         <v>Jun26</v>
@@ -9752,15 +9752,15 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F431">
-        <v>596</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>07/07/2026</v>
+        <v>21/06/2026</v>
       </c>
       <c r="B432" t="str">
-        <v>Jul26</v>
+        <v>Jun26</v>
       </c>
       <c r="C432" t="str">
         <v>COGS</v>
@@ -9772,15 +9772,15 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F432">
-        <v>141</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>07/07/2026</v>
+        <v>21/06/2026</v>
       </c>
       <c r="B433" t="str">
-        <v>Jul26</v>
+        <v>Jun26</v>
       </c>
       <c r="C433" t="str">
         <v>COGS</v>
@@ -9792,15 +9792,15 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F433">
-        <v>7999</v>
+        <v>3051</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>07/07/2026</v>
+        <v>21/06/2026</v>
       </c>
       <c r="B434" t="str">
-        <v>Jul26</v>
+        <v>Jun26</v>
       </c>
       <c r="C434" t="str">
         <v>COGS</v>
@@ -9812,15 +9812,15 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F434">
-        <v>1399</v>
+        <v>755</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>08/07/2026</v>
+        <v>29/06/2026</v>
       </c>
       <c r="B435" t="str">
-        <v>Jul26</v>
+        <v>Jun26</v>
       </c>
       <c r="C435" t="str">
         <v>COGS</v>
@@ -9832,15 +9832,15 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F435">
-        <v>9870</v>
+        <v>7766</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>24/07/2026</v>
+        <v>29/06/2026</v>
       </c>
       <c r="B436" t="str">
-        <v>Jul26</v>
+        <v>Jun26</v>
       </c>
       <c r="C436" t="str">
         <v>COGS</v>
@@ -9852,52 +9852,52 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F436">
-        <v>7410</v>
+        <v>539</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>26/07/2026</v>
+        <v>29/06/2026</v>
       </c>
       <c r="B437" t="str">
-        <v>Jul26</v>
+        <v>Jun26</v>
       </c>
       <c r="C437" t="str">
-        <v>CAPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D437" t="str">
-        <v>Investment</v>
+        <v>Packaging</v>
       </c>
       <c r="E437" t="str">
-        <v>เครื่องสกัดเย็น 1 เครื่อง (Shopee, audit fix - was COGS/Packaging)</v>
+        <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F437">
-        <v>1015</v>
+        <v>596</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>26/07/2026</v>
+        <v>07/07/2026</v>
       </c>
       <c r="B438" t="str">
         <v>Jul26</v>
       </c>
       <c r="C438" t="str">
-        <v>CAPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D438" t="str">
-        <v>Investment</v>
+        <v>Packaging</v>
       </c>
       <c r="E438" t="str">
-        <v>เครื่องสกัดเย็น 1 เครื่อง (Shopee, audit fix - was COGS/Packaging)</v>
+        <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F438">
-        <v>1087</v>
+        <v>141</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>27/07/2026</v>
+        <v>07/07/2026</v>
       </c>
       <c r="B439" t="str">
         <v>Jul26</v>
@@ -9912,12 +9912,12 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F439">
-        <v>4309</v>
+        <v>7999</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>27/07/2026</v>
+        <v>07/07/2026</v>
       </c>
       <c r="B440" t="str">
         <v>Jul26</v>
@@ -9932,472 +9932,592 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F440">
-        <v>2589</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>31/01/2026</v>
+        <v>08/07/2026</v>
       </c>
       <c r="B441" t="str">
-        <v>Jan26</v>
+        <v>Jul26</v>
       </c>
       <c r="C441" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D441" t="str">
-        <v>Rental</v>
+        <v>Packaging</v>
       </c>
       <c r="E441" t="str">
-        <v>ค่าเช่าร้าน Jan26 (ปรับตามงบการเงินเจ้าของ)</v>
+        <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F441">
-        <v>30000</v>
+        <v>9870</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>28/02/2026</v>
+        <v>24/07/2026</v>
       </c>
       <c r="B442" t="str">
-        <v>Feb26</v>
+        <v>Jul26</v>
       </c>
       <c r="C442" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D442" t="str">
-        <v>Rental</v>
+        <v>Packaging</v>
       </c>
       <c r="E442" t="str">
-        <v>ค่าเช่าร้าน Feb26 (ปรับตามงบการเงินเจ้าของ)</v>
+        <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F442">
-        <v>35000</v>
+        <v>7410</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>28/02/2026</v>
+        <v>26/07/2026</v>
       </c>
       <c r="B443" t="str">
-        <v>Feb26</v>
+        <v>Jul26</v>
       </c>
       <c r="C443" t="str">
-        <v>OPEX</v>
+        <v>CAPEX</v>
       </c>
       <c r="D443" t="str">
-        <v>Salary</v>
+        <v>Investment</v>
       </c>
       <c r="E443" t="str">
-        <v>ค่าแรงคนงาน Feb26 (ปรับตามงบการเงินเจ้าของ)</v>
+        <v>เครื่องสกัดเย็น 1 เครื่อง (Shopee, audit fix - was COGS/Packaging)</v>
       </c>
       <c r="F443">
-        <v>19000</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>31/03/2026</v>
+        <v>26/07/2026</v>
       </c>
       <c r="B444" t="str">
-        <v>Mar26</v>
+        <v>Jul26</v>
       </c>
       <c r="C444" t="str">
-        <v>OPEX</v>
+        <v>CAPEX</v>
       </c>
       <c r="D444" t="str">
-        <v>Rental</v>
+        <v>Investment</v>
       </c>
       <c r="E444" t="str">
-        <v>ค่าเช่าร้าน Mar26 (ปรับตามงบการเงินเจ้าของ)</v>
+        <v>เครื่องสกัดเย็น 1 เครื่อง (Shopee, audit fix - was COGS/Packaging)</v>
       </c>
       <c r="F444">
-        <v>35000</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>31/03/2026</v>
+        <v>27/07/2026</v>
       </c>
       <c r="B445" t="str">
-        <v>Mar26</v>
+        <v>Jul26</v>
       </c>
       <c r="C445" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D445" t="str">
-        <v>Rental</v>
+        <v>Packaging</v>
       </c>
       <c r="E445" t="str">
-        <v>ค่าเช่าคลัง Mar26 (ปรับตามงบการเงินเจ้าของ)</v>
+        <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F445">
-        <v>12000</v>
+        <v>4309</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>31/03/2026</v>
+        <v>27/07/2026</v>
       </c>
       <c r="B446" t="str">
-        <v>Mar26</v>
+        <v>Jul26</v>
       </c>
       <c r="C446" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D446" t="str">
-        <v>Other</v>
+        <v>Packaging</v>
       </c>
       <c r="E446" t="str">
-        <v>ค่าน้ำ + ค่าไฟ Mar26 (ปรับตามงบการเงินเจ้าของ)</v>
+        <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F446">
-        <v>3229</v>
+        <v>2589</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>22/06/2026</v>
+        <v>31/01/2026</v>
       </c>
       <c r="B447" t="str">
-        <v>Jun26</v>
+        <v>Jan26</v>
       </c>
       <c r="C447" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D447" t="str">
-        <v>Guava</v>
+        <v>Rental</v>
       </c>
       <c r="E447" t="str">
-        <v>ฝรั่ง (นาง ประนอม) [bank]</v>
+        <v>ค่าเช่าร้าน Jan26 (ปรับตามงบการเงินเจ้าของ)</v>
       </c>
       <c r="F447">
-        <v>100</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>25/06/2026</v>
+        <v>28/02/2026</v>
       </c>
       <c r="B448" t="str">
-        <v>Jun26</v>
+        <v>Feb26</v>
       </c>
       <c r="C448" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D448" t="str">
-        <v>Guava</v>
+        <v>Rental</v>
       </c>
       <c r="E448" t="str">
-        <v>ฝรั่ง 1 ตะกร้า (นาง ประนอม) [bank]</v>
+        <v>ค่าเช่าร้าน Feb26 (ปรับตามงบการเงินเจ้าของ)</v>
       </c>
       <c r="F448">
-        <v>800</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>28/07/2026</v>
+        <v>28/02/2026</v>
       </c>
       <c r="B449" t="str">
-        <v>Jul26</v>
+        <v>Feb26</v>
       </c>
       <c r="C449" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D449" t="str">
-        <v>Guava</v>
+        <v>Salary</v>
       </c>
       <c r="E449" t="str">
-        <v>ฝรั่ง (นาง ประนอม) [bank]</v>
+        <v>ค่าแรงคนงาน Feb26 (ปรับตามงบการเงินเจ้าของ)</v>
       </c>
       <c r="F449">
-        <v>3000</v>
+        <v>19000</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>20/02/2026</v>
+        <v>31/03/2026</v>
       </c>
       <c r="B450" t="str">
-        <v>Feb26</v>
+        <v>Mar26</v>
       </c>
       <c r="C450" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D450" t="str">
-        <v>Transportation</v>
+        <v>Rental</v>
       </c>
       <c r="E450" t="str">
-        <v>ค่ารถ (แยกจากใบเสร็จผ้าปิดร้าน 416)</v>
+        <v>ค่าเช่าร้าน Mar26 (ปรับตามงบการเงินเจ้าของ)</v>
       </c>
       <c r="F450">
-        <v>198</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>04/06/2026</v>
+        <v>31/03/2026</v>
       </c>
       <c r="B451" t="str">
-        <v>Jun26</v>
+        <v>Mar26</v>
       </c>
       <c r="C451" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D451" t="str">
-        <v>Pineapple</v>
+        <v>Rental</v>
       </c>
       <c r="E451" t="str">
-        <v>สลิปรวม: สับปะรด 750 (audit fix, was bundled)</v>
+        <v>ค่าเช่าคลัง Mar26 (ปรับตามงบการเงินเจ้าของ)</v>
       </c>
       <c r="F451">
-        <v>750</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>04/06/2026</v>
+        <v>31/03/2026</v>
       </c>
       <c r="B452" t="str">
-        <v>Jun26</v>
+        <v>Mar26</v>
       </c>
       <c r="C452" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D452" t="str">
-        <v>Orange</v>
+        <v>Other</v>
       </c>
       <c r="E452" t="str">
-        <v>สลิปรวม: ส้ม 2250 (audit fix, was bundled into Pineapple line)</v>
+        <v>ค่าน้ำ + ค่าไฟ Mar26 (ปรับตามงบการเงินเจ้าของ)</v>
       </c>
       <c r="F452">
-        <v>2250</v>
+        <v>3229</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>04/06/2026</v>
+        <v>22/06/2026</v>
       </c>
       <c r="B453" t="str">
         <v>Jun26</v>
       </c>
       <c r="C453" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D453" t="str">
-        <v>Other</v>
+        <v>Guava</v>
       </c>
       <c r="E453" t="str">
-        <v>ค่าปรับตำรวจ 2 คน (police fee, audit fix - was miscategorized as COGS/Pineapple)</v>
+        <v>ฝรั่ง (นาง ประนอม) [bank]</v>
       </c>
       <c r="F453">
-        <v>2000</v>
+        <v>100</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>26/07/2026</v>
+        <v>25/06/2026</v>
       </c>
       <c r="B454" t="str">
-        <v>Jul26</v>
+        <v>Jun26</v>
       </c>
       <c r="C454" t="str">
-        <v>CAPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D454" t="str">
-        <v>Investment</v>
+        <v>Guava</v>
       </c>
       <c r="E454" t="str">
-        <v>งบลงทุน - ทดลองอื่นๆ (LINE_ALBUM_Cost July_260802_8.jpg, audit fix - was bundled into COGS/Mango)</v>
+        <v>ฝรั่ง 1 ตะกร้า (นาง ประนอม) [bank]</v>
       </c>
       <c r="F454">
-        <v>810</v>
+        <v>800</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>26/07/2026</v>
+        <v>28/07/2026</v>
       </c>
       <c r="B455" t="str">
         <v>Jul26</v>
       </c>
       <c r="C455" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D455" t="str">
-        <v>Other</v>
+        <v>Guava</v>
       </c>
       <c r="E455" t="str">
-        <v>ค่าส่งของ (LINE_ALBUM_Cost July_260802_11.jpg, audit fix - missing entry)</v>
+        <v>ฝรั่ง (นาง ประนอม) [bank]</v>
       </c>
       <c r="F455">
-        <v>212</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>28/07/2026</v>
+        <v>20/02/2026</v>
       </c>
       <c r="B456" t="str">
-        <v>Jul26</v>
+        <v>Feb26</v>
       </c>
       <c r="C456" t="str">
         <v>COGS</v>
       </c>
       <c r="D456" t="str">
-        <v>Pineapple</v>
+        <v>Transportation</v>
       </c>
       <c r="E456" t="str">
-        <v>สับปะรด 30 ลูก (LINE_ALBUM_Cost July_260802_17.jpg, audit fix - missing entry)</v>
+        <v>ค่ารถ (แยกจากใบเสร็จผ้าปิดร้าน 416)</v>
       </c>
       <c r="F456">
-        <v>1188</v>
+        <v>198</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>28/07/2026</v>
+        <v>04/06/2026</v>
       </c>
       <c r="B457" t="str">
-        <v>Jul26</v>
+        <v>Jun26</v>
       </c>
       <c r="C457" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D457" t="str">
-        <v>Other</v>
+        <v>Pineapple</v>
       </c>
       <c r="E457" t="str">
-        <v>ค่าขนส่ง (LINE_ALBUM_Cost July_260802_19.jpg, audit fix - missing entry)</v>
+        <v>สลิปรวม: สับปะรด 750 (audit fix, was bundled)</v>
       </c>
       <c r="F457">
-        <v>100</v>
+        <v>750</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>30/04/2026</v>
+        <v>04/06/2026</v>
       </c>
       <c r="B458" t="str">
-        <v>Apr26</v>
+        <v>Jun26</v>
       </c>
       <c r="C458" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D458" t="str">
-        <v>Rental</v>
+        <v>Orange</v>
       </c>
       <c r="E458" t="str">
-        <v>ค่าเช่า stock เม.ย. (B1 ครึ่งหนึ่ง)</v>
+        <v>สลิปรวม: ส้ม 2250 (audit fix, was bundled into Pineapple line)</v>
       </c>
       <c r="F458">
-        <v>6000</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>05/03/2026</v>
+        <v>04/06/2026</v>
       </c>
       <c r="B459" t="str">
-        <v>Mar26</v>
+        <v>Jun26</v>
       </c>
       <c r="C459" t="str">
         <v>OPEX</v>
       </c>
       <c r="D459" t="str">
-        <v>Salary</v>
+        <v>Other</v>
       </c>
       <c r="E459" t="str">
-        <v>เงินเดือนเมน 3/26</v>
+        <v>ค่าปรับตำรวจ 2 คน (police fee, audit fix - was miscategorized as COGS/Pineapple)</v>
       </c>
       <c r="F459">
-        <v>19000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>27/02/2026</v>
+        <v>26/07/2026</v>
       </c>
       <c r="B460" t="str">
-        <v>Feb26</v>
+        <v>Jul26</v>
       </c>
       <c r="C460" t="str">
-        <v>OPEX</v>
+        <v>CAPEX</v>
       </c>
       <c r="D460" t="str">
         <v>Investment</v>
       </c>
       <c r="E460" t="str">
-        <v>อุปกรณ์ (จากสลิปโอนผู้จัดการ)</v>
+        <v>งบลงทุน - ทดลองอื่นๆ (LINE_ALBUM_Cost July_260802_8.jpg, audit fix - was bundled into COGS/Mango)</v>
       </c>
       <c r="F460">
-        <v>5000</v>
+        <v>810</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>18/03/2026</v>
+        <v>26/07/2026</v>
       </c>
       <c r="B461" t="str">
-        <v>Mar26</v>
+        <v>Jul26</v>
       </c>
       <c r="C461" t="str">
         <v>OPEX</v>
       </c>
       <c r="D461" t="str">
-        <v>Milk/Conden</v>
+        <v>Other</v>
       </c>
       <c r="E461" t="str">
-        <v>นม + นมข้นหวาน (จากสลิปโอนผู้จัดการ)</v>
+        <v>ค่าส่งของ (LINE_ALBUM_Cost July_260802_11.jpg, audit fix - missing entry)</v>
       </c>
       <c r="F461">
-        <v>230</v>
+        <v>212</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>01/04/2026</v>
+        <v>28/07/2026</v>
       </c>
       <c r="B462" t="str">
-        <v>Mar26</v>
+        <v>Jul26</v>
       </c>
       <c r="C462" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D462" t="str">
-        <v>Salary</v>
+        <v>Pineapple</v>
       </c>
       <c r="E462" t="str">
-        <v>เงินเดือนพนักงาน 3 คน มี.ค. 26 (จ่าย 01/04) [bank]</v>
+        <v>สับปะรด 30 ลูก (LINE_ALBUM_Cost July_260802_17.jpg, audit fix - missing entry)</v>
       </c>
       <c r="F462">
-        <v>24600</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>08/06/2026</v>
+        <v>28/07/2026</v>
       </c>
       <c r="B463" t="str">
-        <v>Jun26</v>
+        <v>Jul26</v>
       </c>
       <c r="C463" t="str">
         <v>OPEX</v>
       </c>
       <c r="D463" t="str">
+        <v>Other</v>
+      </c>
+      <c r="E463" t="str">
+        <v>ค่าขนส่ง (LINE_ALBUM_Cost July_260802_19.jpg, audit fix - missing entry)</v>
+      </c>
+      <c r="F463">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="str">
+        <v>30/04/2026</v>
+      </c>
+      <c r="B464" t="str">
+        <v>Apr26</v>
+      </c>
+      <c r="C464" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D464" t="str">
         <v>Rental</v>
       </c>
-      <c r="E463" t="str">
+      <c r="E464" t="str">
+        <v>ค่าเช่า stock เม.ย. (B1 ครึ่งหนึ่ง)</v>
+      </c>
+      <c r="F464">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="str">
+        <v>05/03/2026</v>
+      </c>
+      <c r="B465" t="str">
+        <v>Mar26</v>
+      </c>
+      <c r="C465" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D465" t="str">
+        <v>Salary</v>
+      </c>
+      <c r="E465" t="str">
+        <v>เงินเดือนเมน 3/26</v>
+      </c>
+      <c r="F465">
+        <v>19000</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="str">
+        <v>27/02/2026</v>
+      </c>
+      <c r="B466" t="str">
+        <v>Feb26</v>
+      </c>
+      <c r="C466" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D466" t="str">
+        <v>Investment</v>
+      </c>
+      <c r="E466" t="str">
+        <v>อุปกรณ์ (จากสลิปโอนผู้จัดการ)</v>
+      </c>
+      <c r="F466">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="str">
+        <v>18/03/2026</v>
+      </c>
+      <c r="B467" t="str">
+        <v>Mar26</v>
+      </c>
+      <c r="C467" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D467" t="str">
+        <v>Milk/Conden</v>
+      </c>
+      <c r="E467" t="str">
+        <v>นม + นมข้นหวาน (จากสลิปโอนผู้จัดการ)</v>
+      </c>
+      <c r="F467">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="str">
+        <v>01/04/2026</v>
+      </c>
+      <c r="B468" t="str">
+        <v>Mar26</v>
+      </c>
+      <c r="C468" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D468" t="str">
+        <v>Salary</v>
+      </c>
+      <c r="E468" t="str">
+        <v>เงินเดือนพนักงาน 3 คน มี.ค. 26 (จ่าย 01/04) [bank]</v>
+      </c>
+      <c r="F468">
+        <v>24600</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="str">
+        <v>08/06/2026</v>
+      </c>
+      <c r="B469" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C469" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D469" t="str">
+        <v>Rental</v>
+      </c>
+      <c r="E469" t="str">
         <v>ค่าเช่าคลัง มิ.ย. (B1 ครึ่งหนึ่ง ของ 12,000 จากสลิป 47,000 วันที่ 08/06)</v>
       </c>
-      <c r="F463">
+      <c r="F469">
         <v>6000</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F463"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F469"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/3_Automation_Dashboard/SomSaiJai_Dashboard_B1_2026.xlsx
+++ b/3_Automation_Dashboard/SomSaiJai_Dashboard_B1_2026.xlsx
@@ -1168,7 +1168,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F469"/>
+  <dimension ref="A1:F472"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3146,10 +3146,10 @@
         <v>COGS</v>
       </c>
       <c r="D101" t="str">
-        <v>Orange</v>
+        <v>Packaging</v>
       </c>
       <c r="E101" t="str">
-        <v>แก้วร้านน้ำส้ม 2ลัง ลังละ1560</v>
+        <v>แก้วร้านน้ำส้ม 2 ลัง x1,560 = 3,120 + ฝา 4 ลัง 2,547</v>
       </c>
       <c r="F101">
         <v>5667</v>
@@ -3249,35 +3249,35 @@
         <v>Watermelon</v>
       </c>
       <c r="E106" t="str">
-        <v>น้ำมะพร้าว 5ขวดเละ 50฿</v>
+        <v>แตงโม เบอร์ 80฿ 50 ลูก = 4,000 (แยกจากสลิปรวม 4,800)</v>
       </c>
       <c r="F106">
-        <v>4800</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>17/03/2026</v>
+        <v>15/03/2026</v>
       </c>
       <c r="B107" t="str">
         <v>Mar26</v>
       </c>
       <c r="C107" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D107" t="str">
-        <v>Utilities</v>
+        <v>Coconut Meat</v>
       </c>
       <c r="E107" t="str">
-        <v>ค่าไฟเดือนกพ มีนา</v>
+        <v>เนื้อมะพร้าว 5 โล x110 = 550 (แยกจากสลิปรวม 4,800)</v>
       </c>
       <c r="F107">
-        <v>2779.47</v>
+        <v>550</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>19/03/2026</v>
+        <v>15/03/2026</v>
       </c>
       <c r="B108" t="str">
         <v>Mar26</v>
@@ -3286,18 +3286,18 @@
         <v>COGS</v>
       </c>
       <c r="D108" t="str">
-        <v>Watermelon</v>
+        <v>Coconut Water</v>
       </c>
       <c r="E108" t="str">
-        <v>ค่าแตงโม 18/3/67 51 ลูก 4000 บาท</v>
+        <v>น้ำมะพร้าว 5 ขวด x50 = 250 (แยกจากสลิปรวม 4,800)</v>
       </c>
       <c r="F108">
-        <v>4000</v>
+        <v>250</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>21/03/2026</v>
+        <v>17/03/2026</v>
       </c>
       <c r="B109" t="str">
         <v>Mar26</v>
@@ -3306,18 +3306,18 @@
         <v>OPEX</v>
       </c>
       <c r="D109" t="str">
-        <v>Other</v>
+        <v>Utilities</v>
       </c>
       <c r="E109" t="str">
-        <v>สกรู กาวตะปู</v>
+        <v>ค่าไฟเดือนกพ มีนา</v>
       </c>
       <c r="F109">
-        <v>117</v>
+        <v>2779.47</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>23/03/2026</v>
+        <v>19/03/2026</v>
       </c>
       <c r="B110" t="str">
         <v>Mar26</v>
@@ -3326,33 +3326,33 @@
         <v>COGS</v>
       </c>
       <c r="D110" t="str">
-        <v>Mango</v>
+        <v>Watermelon</v>
       </c>
       <c r="E110" t="str">
-        <v>มะม่วง 44 โล</v>
+        <v>ค่าแตงโม 18/3/67 51 ลูก 4000 บาท</v>
       </c>
       <c r="F110">
-        <v>2200</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>23/03/2026</v>
+        <v>21/03/2026</v>
       </c>
       <c r="B111" t="str">
         <v>Mar26</v>
       </c>
       <c r="C111" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D111" t="str">
-        <v>Watermelon</v>
+        <v>Other</v>
       </c>
       <c r="E111" t="str">
-        <v>แตงโม 43 ลูก x80 = 3,440 (แยกจากสลิปรวม 5,890 - นาง ศิริพร 22/3)</v>
+        <v>สกรู กาวตะปู</v>
       </c>
       <c r="F111">
-        <v>3440</v>
+        <v>117</v>
       </c>
     </row>
     <row r="112">
@@ -3366,38 +3366,38 @@
         <v>COGS</v>
       </c>
       <c r="D112" t="str">
-        <v>Orange</v>
+        <v>Mango</v>
       </c>
       <c r="E112" t="str">
-        <v>ส้ม 70 กก. x35 = 2,450 (แยกจากสลิปรวม 5,890 - นาง ศิริพร 22/3)</v>
+        <v>มะม่วง 44 โล</v>
       </c>
       <c r="F112">
-        <v>2450</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>24/03/2026</v>
+        <v>23/03/2026</v>
       </c>
       <c r="B113" t="str">
         <v>Mar26</v>
       </c>
       <c r="C113" t="str">
-        <v>CAPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D113" t="str">
-        <v>Investment</v>
+        <v>Watermelon</v>
       </c>
       <c r="E113" t="str">
-        <v>รถเข็นของคันใหม่</v>
+        <v>แตงโม 43 ลูก x80 = 3,440 (แยกจากสลิปรวม 5,890 - นาง ศิริพร 22/3)</v>
       </c>
       <c r="F113">
-        <v>1752</v>
+        <v>3440</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>28/03/2026</v>
+        <v>23/03/2026</v>
       </c>
       <c r="B114" t="str">
         <v>Mar26</v>
@@ -3406,33 +3406,33 @@
         <v>COGS</v>
       </c>
       <c r="D114" t="str">
-        <v>Coconut Water</v>
+        <v>Orange</v>
       </c>
       <c r="E114" t="str">
-        <v>น้ำมะพร้าว 10 ขวด</v>
+        <v>ส้ม 70 กก. x35 = 2,450 (แยกจากสลิปรวม 5,890 - นาง ศิริพร 22/3)</v>
       </c>
       <c r="F114">
-        <v>500</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>28/03/2026</v>
+        <v>24/03/2026</v>
       </c>
       <c r="B115" t="str">
         <v>Mar26</v>
       </c>
       <c r="C115" t="str">
-        <v>COGS</v>
+        <v>CAPEX</v>
       </c>
       <c r="D115" t="str">
-        <v>Mango</v>
+        <v>Investment</v>
       </c>
       <c r="E115" t="str">
-        <v>มะม่วง 23 โล</v>
+        <v>รถเข็นของคันใหม่</v>
       </c>
       <c r="F115">
-        <v>1035</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="116">
@@ -3446,18 +3446,18 @@
         <v>COGS</v>
       </c>
       <c r="D116" t="str">
-        <v>Watermelon</v>
+        <v>Coconut Water</v>
       </c>
       <c r="E116" t="str">
-        <v>แตงโม 50 26/3/69</v>
+        <v>น้ำมะพร้าว 10 ขวด</v>
       </c>
       <c r="F116">
-        <v>4000</v>
+        <v>500</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>30/03/2026</v>
+        <v>28/03/2026</v>
       </c>
       <c r="B117" t="str">
         <v>Mar26</v>
@@ -3466,18 +3466,18 @@
         <v>COGS</v>
       </c>
       <c r="D117" t="str">
-        <v>Milk/Conden</v>
+        <v>Mango</v>
       </c>
       <c r="E117" t="str">
-        <v>นมข้นจืด 3 ลัง (36 กล่อง)</v>
+        <v>มะม่วง 23 โล</v>
       </c>
       <c r="F117">
-        <v>1720</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>30/03/2026</v>
+        <v>28/03/2026</v>
       </c>
       <c r="B118" t="str">
         <v>Mar26</v>
@@ -3486,13 +3486,13 @@
         <v>COGS</v>
       </c>
       <c r="D118" t="str">
-        <v>Milk/Conden</v>
+        <v>Watermelon</v>
       </c>
       <c r="E118" t="str">
-        <v>นมข้นหวาน 3 ลัง 24 ถุง</v>
+        <v>แตงโม 50 26/3/69</v>
       </c>
       <c r="F118">
-        <v>2016</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="119">
@@ -3506,13 +3506,13 @@
         <v>COGS</v>
       </c>
       <c r="D119" t="str">
-        <v>Watermelon</v>
+        <v>Milk/Conden</v>
       </c>
       <c r="E119" t="str">
-        <v>แตงโม 30 ลูก 2400 เนื้อมะพร้าว 10 โล 1100</v>
+        <v>นมข้นจืด 3 ลัง (36 กล่อง)</v>
       </c>
       <c r="F119">
-        <v>3500</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="120">
@@ -3526,18 +3526,18 @@
         <v>COGS</v>
       </c>
       <c r="D120" t="str">
-        <v>Transportation</v>
+        <v>Milk/Conden</v>
       </c>
       <c r="E120" t="str">
-        <v>ค่าส่ง lalamove</v>
+        <v>นมข้นหวาน 3 ลัง 24 ถุง</v>
       </c>
       <c r="F120">
-        <v>2000</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>31/03/2026</v>
+        <v>30/03/2026</v>
       </c>
       <c r="B121" t="str">
         <v>Mar26</v>
@@ -3546,98 +3546,98 @@
         <v>COGS</v>
       </c>
       <c r="D121" t="str">
-        <v>Transportation</v>
+        <v>Watermelon</v>
       </c>
       <c r="E121" t="str">
-        <v>Unknown</v>
+        <v>แตงโม 30 ลูก = 2,400 (แยกจากสลิปรวม 3,500)</v>
       </c>
       <c r="F121">
-        <v>2000</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>01/04/2026</v>
+        <v>30/03/2026</v>
       </c>
       <c r="B122" t="str">
-        <v>Apr26</v>
+        <v>Mar26</v>
       </c>
       <c r="C122" t="str">
         <v>COGS</v>
       </c>
       <c r="D122" t="str">
-        <v>Apple</v>
+        <v>Coconut Meat</v>
       </c>
       <c r="E122" t="str">
-        <v>แอปเปิ้ล 3 ลัง</v>
+        <v>เนื้อมะพร้าว 10 โล = 1,100 (แยกจากสลิปรวม 3,500)</v>
       </c>
       <c r="F122">
-        <v>1050</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>01/04/2026</v>
+        <v>30/03/2026</v>
       </c>
       <c r="B123" t="str">
-        <v>Apr26</v>
+        <v>Mar26</v>
       </c>
       <c r="C123" t="str">
         <v>COGS</v>
       </c>
       <c r="D123" t="str">
-        <v>Mango</v>
+        <v>Transportation</v>
       </c>
       <c r="E123" t="str">
-        <v>มะม่วง 2 ลัง</v>
+        <v>ค่าส่ง lalamove</v>
       </c>
       <c r="F123">
-        <v>1920</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>01/04/2026</v>
+        <v>31/03/2026</v>
       </c>
       <c r="B124" t="str">
-        <v>Apr26</v>
+        <v>Mar26</v>
       </c>
       <c r="C124" t="str">
         <v>COGS</v>
       </c>
       <c r="D124" t="str">
-        <v>Water</v>
+        <v>Transportation</v>
       </c>
       <c r="E124" t="str">
-        <v>น้ำ500</v>
+        <v>Unknown</v>
       </c>
       <c r="F124">
-        <v>1700</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>02/04/2026</v>
+        <v>01/04/2026</v>
       </c>
       <c r="B125" t="str">
-        <v>Mar26</v>
+        <v>Apr26</v>
       </c>
       <c r="C125" t="str">
         <v>COGS</v>
       </c>
       <c r="D125" t="str">
-        <v>Orange</v>
+        <v>Apple</v>
       </c>
       <c r="E125" t="str">
-        <v>ส้มเพิ่มเติม มี.ค. (สลิปไม่มีบันทึกช่วยจำ - ไม่ทราบจำนวน) [bank 02/04]</v>
+        <v>แอปเปิ้ล 3 ลัง</v>
       </c>
       <c r="F125">
-        <v>49560</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>04/04/2026</v>
+        <v>01/04/2026</v>
       </c>
       <c r="B126" t="str">
         <v>Apr26</v>
@@ -3646,18 +3646,18 @@
         <v>COGS</v>
       </c>
       <c r="D126" t="str">
-        <v>Packaging</v>
+        <v>Mango</v>
       </c>
       <c r="E126" t="str">
-        <v>แก้ว3ลัง 1539 3 4617</v>
+        <v>มะม่วง 2 ลัง</v>
       </c>
       <c r="F126">
-        <v>7066</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>04/04/2026</v>
+        <v>01/04/2026</v>
       </c>
       <c r="B127" t="str">
         <v>Apr26</v>
@@ -3666,33 +3666,33 @@
         <v>COGS</v>
       </c>
       <c r="D127" t="str">
-        <v>Packaging</v>
+        <v>Water</v>
       </c>
       <c r="E127" t="str">
-        <v>แก้ว1ลัง 1539</v>
+        <v>น้ำ500</v>
       </c>
       <c r="F127">
-        <v>1560</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>04/04/2026</v>
+        <v>02/04/2026</v>
       </c>
       <c r="B128" t="str">
-        <v>Apr26</v>
+        <v>Mar26</v>
       </c>
       <c r="C128" t="str">
         <v>COGS</v>
       </c>
       <c r="D128" t="str">
-        <v>Coconut</v>
+        <v>Orange</v>
       </c>
       <c r="E128" t="str">
-        <v>ค่ามะพร้าว 26 60ลูก 1560</v>
+        <v>ส้มเพิ่มเติม มี.ค. (สลิปไม่มีบันทึกช่วยจำ - ไม่ทราบจำนวน) [bank 02/04]</v>
       </c>
       <c r="F128">
-        <v>1980</v>
+        <v>49560</v>
       </c>
     </row>
     <row r="129">
@@ -3706,13 +3706,13 @@
         <v>COGS</v>
       </c>
       <c r="D129" t="str">
-        <v>Coconut</v>
+        <v>Packaging</v>
       </c>
       <c r="E129" t="str">
-        <v>เนื้อ 1200 น้ำ 500</v>
+        <v>แก้ว3ลัง 1539 3 4617</v>
       </c>
       <c r="F129">
-        <v>1700</v>
+        <v>7066</v>
       </c>
     </row>
     <row r="130">
@@ -3726,13 +3726,13 @@
         <v>COGS</v>
       </c>
       <c r="D130" t="str">
-        <v>Mango</v>
+        <v>Packaging</v>
       </c>
       <c r="E130" t="str">
-        <v>มะม่วง1ลัง</v>
+        <v>แก้ว1ลัง 1539</v>
       </c>
       <c r="F130">
-        <v>1000</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="131">
@@ -3746,13 +3746,13 @@
         <v>COGS</v>
       </c>
       <c r="D131" t="str">
-        <v>Orange</v>
+        <v>Coconut</v>
       </c>
       <c r="E131" t="str">
-        <v>ส้ม 4/4/69 20 ตะกร้า 30 บาท 13200 ค่าขนส่ง</v>
+        <v>ค่ามะพร้าว 26 60ลูก 1560</v>
       </c>
       <c r="F131">
-        <v>14160</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="132">
@@ -3766,13 +3766,13 @@
         <v>COGS</v>
       </c>
       <c r="D132" t="str">
-        <v>Watermelon</v>
+        <v>Coconut</v>
       </c>
       <c r="E132" t="str">
-        <v>4/4/68 40 ลูก</v>
+        <v>เนื้อ 1200 น้ำ 500</v>
       </c>
       <c r="F132">
-        <v>3200</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="133">
@@ -3786,18 +3786,18 @@
         <v>COGS</v>
       </c>
       <c r="D133" t="str">
-        <v>Watermelon</v>
+        <v>Mango</v>
       </c>
       <c r="E133" t="str">
-        <v>แตงโม 1/4/69 30 ลูก</v>
+        <v>มะม่วง1ลัง</v>
       </c>
       <c r="F133">
-        <v>2400</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>07/04/2026</v>
+        <v>04/04/2026</v>
       </c>
       <c r="B134" t="str">
         <v>Apr26</v>
@@ -3806,18 +3806,18 @@
         <v>COGS</v>
       </c>
       <c r="D134" t="str">
-        <v>Apple</v>
+        <v>Orange</v>
       </c>
       <c r="E134" t="str">
-        <v>แอปเปิ้ล 3 ลัง</v>
+        <v>ส้ม 4/4/69 20 ตะกร้า 30 บาท 13200 ค่าขนส่ง</v>
       </c>
       <c r="F134">
-        <v>1050</v>
+        <v>14160</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>07/04/2026</v>
+        <v>04/04/2026</v>
       </c>
       <c r="B135" t="str">
         <v>Apr26</v>
@@ -3826,18 +3826,18 @@
         <v>COGS</v>
       </c>
       <c r="D135" t="str">
-        <v>Coconut Water</v>
+        <v>Watermelon</v>
       </c>
       <c r="E135" t="str">
-        <v>เนื้อมะพร้าว 10 - 1200 บาท น้ำมะพร้าว 10</v>
+        <v>4/4/68 40 ลูก</v>
       </c>
       <c r="F135">
-        <v>1700</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>07/04/2026</v>
+        <v>04/04/2026</v>
       </c>
       <c r="B136" t="str">
         <v>Apr26</v>
@@ -3849,15 +3849,15 @@
         <v>Watermelon</v>
       </c>
       <c r="E136" t="str">
-        <v>ค่าแตงโมวันที่ 4- 40 ลูก 3200 บาท วันที่ 7-40 ลูก</v>
+        <v>แตงโม 1/4/69 30 ลูก</v>
       </c>
       <c r="F136">
-        <v>6400</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>10/04/2026</v>
+        <v>07/04/2026</v>
       </c>
       <c r="B137" t="str">
         <v>Apr26</v>
@@ -3866,18 +3866,18 @@
         <v>COGS</v>
       </c>
       <c r="D137" t="str">
-        <v>Milk/Conden</v>
+        <v>Apple</v>
       </c>
       <c r="E137" t="str">
-        <v>ค่านม</v>
+        <v>แอปเปิ้ล 3 ลัง</v>
       </c>
       <c r="F137">
-        <v>180</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>11/04/2026</v>
+        <v>07/04/2026</v>
       </c>
       <c r="B138" t="str">
         <v>Apr26</v>
@@ -3886,18 +3886,18 @@
         <v>COGS</v>
       </c>
       <c r="D138" t="str">
-        <v>Transportation</v>
+        <v>Coconut Water</v>
       </c>
       <c r="E138" t="str">
-        <v>ค่ารถ lalamove</v>
+        <v>เนื้อมะพร้าว 10 - 1200 บาท น้ำมะพร้าว 10</v>
       </c>
       <c r="F138">
-        <v>2000</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>11/04/2026</v>
+        <v>07/04/2026</v>
       </c>
       <c r="B139" t="str">
         <v>Apr26</v>
@@ -3906,18 +3906,18 @@
         <v>COGS</v>
       </c>
       <c r="D139" t="str">
-        <v>Apple</v>
+        <v>Watermelon</v>
       </c>
       <c r="E139" t="str">
-        <v>แอปเปิ้ล 3 ลัง</v>
+        <v>ค่าแตงโมวันที่ 4- 40 ลูก 3200 บาท วันที่ 7-40 ลูก</v>
       </c>
       <c r="F139">
-        <v>1050</v>
+        <v>6400</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>11/04/2026</v>
+        <v>10/04/2026</v>
       </c>
       <c r="B140" t="str">
         <v>Apr26</v>
@@ -3926,13 +3926,13 @@
         <v>COGS</v>
       </c>
       <c r="D140" t="str">
-        <v>Coconut</v>
+        <v>Milk/Conden</v>
       </c>
       <c r="E140" t="str">
-        <v>น้ำ 500 เนื้อ 1200</v>
+        <v>ค่านม</v>
       </c>
       <c r="F140">
-        <v>1700</v>
+        <v>180</v>
       </c>
     </row>
     <row r="141">
@@ -3946,18 +3946,18 @@
         <v>COGS</v>
       </c>
       <c r="D141" t="str">
-        <v>Mango</v>
+        <v>Transportation</v>
       </c>
       <c r="E141" t="str">
-        <v>มะม่วง 1 ลัง 23 โล</v>
+        <v>ค่ารถ lalamove</v>
       </c>
       <c r="F141">
-        <v>690</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>13/04/2026</v>
+        <v>11/04/2026</v>
       </c>
       <c r="B142" t="str">
         <v>Apr26</v>
@@ -3966,18 +3966,18 @@
         <v>COGS</v>
       </c>
       <c r="D142" t="str">
-        <v>Coconut Water</v>
+        <v>Apple</v>
       </c>
       <c r="E142" t="str">
-        <v>Unknown</v>
+        <v>แอปเปิ้ล 3 ลัง</v>
       </c>
       <c r="F142">
-        <v>300</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>13/04/2026</v>
+        <v>11/04/2026</v>
       </c>
       <c r="B143" t="str">
         <v>Apr26</v>
@@ -3986,18 +3986,18 @@
         <v>COGS</v>
       </c>
       <c r="D143" t="str">
-        <v>Coconut Water</v>
+        <v>Coconut</v>
       </c>
       <c r="E143" t="str">
-        <v>เนื้อมะพร้าว 1200 น้ำมะพร้าว 500</v>
+        <v>น้ำ 500 เนื้อ 1200</v>
       </c>
       <c r="F143">
-        <v>1400</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>13/04/2026</v>
+        <v>11/04/2026</v>
       </c>
       <c r="B144" t="str">
         <v>Apr26</v>
@@ -4009,10 +4009,10 @@
         <v>Mango</v>
       </c>
       <c r="E144" t="str">
-        <v>Unknown</v>
+        <v>มะม่วง 1 ลัง 23 โล</v>
       </c>
       <c r="F144">
-        <v>750</v>
+        <v>690</v>
       </c>
     </row>
     <row r="145">
@@ -4026,18 +4026,18 @@
         <v>COGS</v>
       </c>
       <c r="D145" t="str">
-        <v>Watermelon</v>
+        <v>Coconut Water</v>
       </c>
       <c r="E145" t="str">
         <v>Unknown</v>
       </c>
       <c r="F145">
-        <v>3200</v>
+        <v>300</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>18/04/2026</v>
+        <v>13/04/2026</v>
       </c>
       <c r="B146" t="str">
         <v>Apr26</v>
@@ -4046,18 +4046,18 @@
         <v>COGS</v>
       </c>
       <c r="D146" t="str">
-        <v>Apple</v>
+        <v>Coconut Water</v>
       </c>
       <c r="E146" t="str">
-        <v>แอปเปิ้ล 3 ลัง</v>
+        <v>เนื้อมะพร้าว 1200 น้ำมะพร้าว 500</v>
       </c>
       <c r="F146">
-        <v>1050</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>18/04/2026</v>
+        <v>13/04/2026</v>
       </c>
       <c r="B147" t="str">
         <v>Apr26</v>
@@ -4069,7 +4069,7 @@
         <v>Mango</v>
       </c>
       <c r="E147" t="str">
-        <v>16/04/26 มะม่วง 1 ลัง</v>
+        <v>Unknown</v>
       </c>
       <c r="F147">
         <v>750</v>
@@ -4077,27 +4077,27 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>18/04/2026</v>
+        <v>13/04/2026</v>
       </c>
       <c r="B148" t="str">
         <v>Apr26</v>
       </c>
       <c r="C148" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D148" t="str">
-        <v>Other</v>
+        <v>Watermelon</v>
       </c>
       <c r="E148" t="str">
-        <v>16/4/2569</v>
+        <v>Unknown</v>
       </c>
       <c r="F148">
-        <v>4000</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>20/04/2026</v>
+        <v>18/04/2026</v>
       </c>
       <c r="B149" t="str">
         <v>Apr26</v>
@@ -4106,18 +4106,18 @@
         <v>COGS</v>
       </c>
       <c r="D149" t="str">
-        <v>Orange</v>
+        <v>Apple</v>
       </c>
       <c r="E149" t="str">
-        <v>ส้ม 40 ตะกร้า ตะกร้าละ 22 โล โลละ 30 บาท</v>
+        <v>แอปเปิ้ล 3 ลัง</v>
       </c>
       <c r="F149">
-        <v>28600</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>20/04/2026</v>
+        <v>18/04/2026</v>
       </c>
       <c r="B150" t="str">
         <v>Apr26</v>
@@ -4126,33 +4126,33 @@
         <v>COGS</v>
       </c>
       <c r="D150" t="str">
-        <v>Transportation</v>
+        <v>Mango</v>
       </c>
       <c r="E150" t="str">
-        <v>ค่าส่งป้ายเมนูร้านใหม่</v>
+        <v>16/04/26 มะม่วง 1 ลัง</v>
       </c>
       <c r="F150">
-        <v>335</v>
+        <v>750</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>20/04/2026</v>
+        <v>18/04/2026</v>
       </c>
       <c r="B151" t="str">
         <v>Apr26</v>
       </c>
       <c r="C151" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D151" t="str">
-        <v>Packaging</v>
+        <v>Other</v>
       </c>
       <c r="E151" t="str">
-        <v>ขวดใหญ่ 98 อัน</v>
+        <v>16/4/2569</v>
       </c>
       <c r="F151">
-        <v>338</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="152">
@@ -4166,13 +4166,13 @@
         <v>COGS</v>
       </c>
       <c r="D152" t="str">
-        <v>Packaging</v>
+        <v>Orange</v>
       </c>
       <c r="E152" t="str">
-        <v>ถุงขยะ 10 แพค</v>
+        <v>ส้ม 40 ตะกร้า ตะกร้าละ 22 โล โลละ 30 บาท</v>
       </c>
       <c r="F152">
-        <v>520</v>
+        <v>28600</v>
       </c>
     </row>
     <row r="153">
@@ -4186,13 +4186,13 @@
         <v>COGS</v>
       </c>
       <c r="D153" t="str">
-        <v>Watermelon</v>
+        <v>Transportation</v>
       </c>
       <c r="E153" t="str">
-        <v>18/4/26 แตงโม 30 ลูก</v>
+        <v>ค่าส่งป้ายเมนูร้านใหม่</v>
       </c>
       <c r="F153">
-        <v>2400</v>
+        <v>335</v>
       </c>
     </row>
     <row r="154">
@@ -4206,18 +4206,18 @@
         <v>COGS</v>
       </c>
       <c r="D154" t="str">
-        <v>Mango</v>
+        <v>Packaging</v>
       </c>
       <c r="E154" t="str">
-        <v>18/4/26 มะม่วง 25 โล 750</v>
+        <v>ขวดใหญ่ 98 อัน</v>
       </c>
       <c r="F154">
-        <v>750</v>
+        <v>338</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>21/04/2026</v>
+        <v>20/04/2026</v>
       </c>
       <c r="B155" t="str">
         <v>Apr26</v>
@@ -4226,18 +4226,18 @@
         <v>COGS</v>
       </c>
       <c r="D155" t="str">
-        <v>Watermelon</v>
+        <v>Packaging</v>
       </c>
       <c r="E155" t="str">
-        <v>21/4/26 แตงโม60 ลูก</v>
+        <v>ถุงขยะ 10 แพค</v>
       </c>
       <c r="F155">
-        <v>4800</v>
+        <v>520</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>21/04/2026</v>
+        <v>20/04/2026</v>
       </c>
       <c r="B156" t="str">
         <v>Apr26</v>
@@ -4246,18 +4246,18 @@
         <v>COGS</v>
       </c>
       <c r="D156" t="str">
-        <v>Transportation</v>
+        <v>Watermelon</v>
       </c>
       <c r="E156" t="str">
-        <v>Lalamove</v>
+        <v>18/4/26 แตงโม 30 ลูก</v>
       </c>
       <c r="F156">
-        <v>2000</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>21/04/2026</v>
+        <v>20/04/2026</v>
       </c>
       <c r="B157" t="str">
         <v>Apr26</v>
@@ -4266,18 +4266,18 @@
         <v>COGS</v>
       </c>
       <c r="D157" t="str">
-        <v>Apple</v>
+        <v>Mango</v>
       </c>
       <c r="E157" t="str">
-        <v>แอปเปิ้ล 4 ลัง</v>
+        <v>18/4/26 มะม่วง 25 โล 750</v>
       </c>
       <c r="F157">
-        <v>1400</v>
+        <v>750</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>23/04/2026</v>
+        <v>21/04/2026</v>
       </c>
       <c r="B158" t="str">
         <v>Apr26</v>
@@ -4286,18 +4286,18 @@
         <v>COGS</v>
       </c>
       <c r="D158" t="str">
-        <v>Mango</v>
+        <v>Watermelon</v>
       </c>
       <c r="E158" t="str">
-        <v>มะม่วง 2 ลัง</v>
+        <v>21/4/26 แตงโม60 ลูก</v>
       </c>
       <c r="F158">
-        <v>1560</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>23/04/2026</v>
+        <v>21/04/2026</v>
       </c>
       <c r="B159" t="str">
         <v>Apr26</v>
@@ -4306,18 +4306,18 @@
         <v>COGS</v>
       </c>
       <c r="D159" t="str">
-        <v>Apple</v>
+        <v>Transportation</v>
       </c>
       <c r="E159" t="str">
-        <v>แอปเปิ้ล 4 ลัง</v>
+        <v>Lalamove</v>
       </c>
       <c r="F159">
-        <v>1400</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>23/04/2026</v>
+        <v>21/04/2026</v>
       </c>
       <c r="B160" t="str">
         <v>Apr26</v>
@@ -4326,13 +4326,13 @@
         <v>COGS</v>
       </c>
       <c r="D160" t="str">
-        <v>Coconut</v>
+        <v>Apple</v>
       </c>
       <c r="E160" t="str">
-        <v>16/4/26 เนื้อ 10 น้ำ 10 21/4/26 เนื้อ 10</v>
+        <v>แอปเปิ้ล 4 ลัง</v>
       </c>
       <c r="F160">
-        <v>2900</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="161">
@@ -4349,15 +4349,15 @@
         <v>Mango</v>
       </c>
       <c r="E161" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>มะม่วง 2 ลัง</v>
       </c>
       <c r="F161">
-        <v>780</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>24/04/2026</v>
+        <v>23/04/2026</v>
       </c>
       <c r="B162" t="str">
         <v>Apr26</v>
@@ -4366,18 +4366,18 @@
         <v>COGS</v>
       </c>
       <c r="D162" t="str">
-        <v>Packaging</v>
+        <v>Apple</v>
       </c>
       <c r="E162" t="str">
-        <v>บาร์เลย 4 ถั่วแดง 3 ถุงละ 60</v>
+        <v>แอปเปิ้ล 4 ลัง</v>
       </c>
       <c r="F162">
-        <v>420</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>24/04/2026</v>
+        <v>23/04/2026</v>
       </c>
       <c r="B163" t="str">
         <v>Apr26</v>
@@ -4386,18 +4386,18 @@
         <v>COGS</v>
       </c>
       <c r="D163" t="str">
-        <v>Watermelon</v>
+        <v>Coconut</v>
       </c>
       <c r="E163" t="str">
-        <v>แตงโม 50 ลูก</v>
+        <v>16/4/26 เนื้อ 10 น้ำ 10 21/4/26 เนื้อ 10</v>
       </c>
       <c r="F163">
-        <v>4000</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>25/04/2026</v>
+        <v>23/04/2026</v>
       </c>
       <c r="B164" t="str">
         <v>Apr26</v>
@@ -4406,18 +4406,18 @@
         <v>COGS</v>
       </c>
       <c r="D164" t="str">
-        <v>Orange</v>
+        <v>Mango</v>
       </c>
       <c r="E164" t="str">
-        <v>ส้ม 20x22กก 440 กก. x30 = 13,200 + ค่าขนส่ง 1,200 (22/04/69)</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F164">
-        <v>14400</v>
+        <v>780</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>26/04/2026</v>
+        <v>24/04/2026</v>
       </c>
       <c r="B165" t="str">
         <v>Apr26</v>
@@ -4429,15 +4429,15 @@
         <v>Packaging</v>
       </c>
       <c r="E165" t="str">
-        <v>แก้ว 1 ลัง</v>
+        <v>บาร์เลย 4 ถั่วแดง 3 ถุงละ 60</v>
       </c>
       <c r="F165">
-        <v>1539</v>
+        <v>420</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>26/04/2026</v>
+        <v>24/04/2026</v>
       </c>
       <c r="B166" t="str">
         <v>Apr26</v>
@@ -4446,18 +4446,18 @@
         <v>COGS</v>
       </c>
       <c r="D166" t="str">
-        <v>Packaging</v>
+        <v>Watermelon</v>
       </c>
       <c r="E166" t="str">
-        <v>แก้ว3ลัง</v>
+        <v>แตงโม 50 ลูก</v>
       </c>
       <c r="F166">
-        <v>7090</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>26/04/2026</v>
+        <v>25/04/2026</v>
       </c>
       <c r="B167" t="str">
         <v>Apr26</v>
@@ -4466,13 +4466,13 @@
         <v>COGS</v>
       </c>
       <c r="D167" t="str">
-        <v>Mango</v>
+        <v>Orange</v>
       </c>
       <c r="E167" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>ส้ม 20x22กก 440 กก. x30 = 13,200 + ค่าขนส่ง 1,200 (22/04/69)</v>
       </c>
       <c r="F167">
-        <v>780</v>
+        <v>14400</v>
       </c>
     </row>
     <row r="168">
@@ -4486,18 +4486,18 @@
         <v>COGS</v>
       </c>
       <c r="D168" t="str">
-        <v>Apple</v>
+        <v>Packaging</v>
       </c>
       <c r="E168" t="str">
-        <v>แอปเปิ้ล 4</v>
+        <v>แก้ว 1 ลัง</v>
       </c>
       <c r="F168">
-        <v>1400</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>27/04/2026</v>
+        <v>26/04/2026</v>
       </c>
       <c r="B169" t="str">
         <v>Apr26</v>
@@ -4506,18 +4506,18 @@
         <v>COGS</v>
       </c>
       <c r="D169" t="str">
-        <v>Watermelon</v>
+        <v>Packaging</v>
       </c>
       <c r="E169" t="str">
-        <v>26/4/26 50 ลูก</v>
+        <v>แก้ว3ลัง</v>
       </c>
       <c r="F169">
-        <v>4000</v>
+        <v>7090</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>28/04/2026</v>
+        <v>26/04/2026</v>
       </c>
       <c r="B170" t="str">
         <v>Apr26</v>
@@ -4526,18 +4526,18 @@
         <v>COGS</v>
       </c>
       <c r="D170" t="str">
-        <v>Packaging</v>
+        <v>Mango</v>
       </c>
       <c r="E170" t="str">
-        <v>หลอด 704(20ห่อ)</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F170">
-        <v>2110</v>
+        <v>780</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>28/04/2026</v>
+        <v>26/04/2026</v>
       </c>
       <c r="B171" t="str">
         <v>Apr26</v>
@@ -4546,18 +4546,18 @@
         <v>COGS</v>
       </c>
       <c r="D171" t="str">
-        <v>Orange</v>
+        <v>Apple</v>
       </c>
       <c r="E171" t="str">
-        <v>ส้ม 660 กก. x30 = 19,800 + ค่าส่ง 1,800 (รอบ 27/04/69)</v>
+        <v>แอปเปิ้ล 4</v>
       </c>
       <c r="F171">
-        <v>21600</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>28/04/2026</v>
+        <v>27/04/2026</v>
       </c>
       <c r="B172" t="str">
         <v>Apr26</v>
@@ -4566,13 +4566,13 @@
         <v>COGS</v>
       </c>
       <c r="D172" t="str">
-        <v>Coconut</v>
+        <v>Watermelon</v>
       </c>
       <c r="E172" t="str">
-        <v>ค่าส่งมะพร้าว</v>
+        <v>26/4/26 50 ลูก</v>
       </c>
       <c r="F172">
-        <v>100</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="173">
@@ -4586,13 +4586,13 @@
         <v>COGS</v>
       </c>
       <c r="D173" t="str">
-        <v>Apple</v>
+        <v>Packaging</v>
       </c>
       <c r="E173" t="str">
-        <v>แอปเปิ้ล 4 ลัง</v>
+        <v>หลอด 704(20ห่อ)</v>
       </c>
       <c r="F173">
-        <v>1400</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="174">
@@ -4606,18 +4606,18 @@
         <v>COGS</v>
       </c>
       <c r="D174" t="str">
-        <v>Mango</v>
+        <v>Orange</v>
       </c>
       <c r="E174" t="str">
-        <v>มะม่วง 2 ลัง</v>
+        <v>ส้ม 660 กก. x30 = 19,800 + ค่าส่ง 1,800 (รอบ 27/04/69)</v>
       </c>
       <c r="F174">
-        <v>1560</v>
+        <v>21600</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>29/04/2026</v>
+        <v>28/04/2026</v>
       </c>
       <c r="B175" t="str">
         <v>Apr26</v>
@@ -4626,18 +4626,18 @@
         <v>COGS</v>
       </c>
       <c r="D175" t="str">
-        <v>Milk/Conden</v>
+        <v>Coconut</v>
       </c>
       <c r="E175" t="str">
-        <v>นมข้นหวาน1ลัง 836</v>
+        <v>ค่าส่งมะพร้าว</v>
       </c>
       <c r="F175">
-        <v>2160</v>
+        <v>100</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>29/04/2026</v>
+        <v>28/04/2026</v>
       </c>
       <c r="B176" t="str">
         <v>Apr26</v>
@@ -4646,18 +4646,18 @@
         <v>COGS</v>
       </c>
       <c r="D176" t="str">
-        <v>Milk/Conden</v>
+        <v>Apple</v>
       </c>
       <c r="E176" t="str">
-        <v>นมข้นหวาน 2 ลัง 1,602 + นมข้นจืด 1 ลัง 638</v>
+        <v>แอปเปิ้ล 4 ลัง</v>
       </c>
       <c r="F176">
-        <v>2240</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>29/04/2026</v>
+        <v>28/04/2026</v>
       </c>
       <c r="B177" t="str">
         <v>Apr26</v>
@@ -4666,13 +4666,13 @@
         <v>COGS</v>
       </c>
       <c r="D177" t="str">
-        <v>Packaging</v>
+        <v>Mango</v>
       </c>
       <c r="E177" t="str">
-        <v>ถุงขยะ 15 แพค 970</v>
+        <v>มะม่วง 2 ลัง</v>
       </c>
       <c r="F177">
-        <v>970</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="178">
@@ -4686,13 +4686,13 @@
         <v>COGS</v>
       </c>
       <c r="D178" t="str">
-        <v>Watermelon</v>
+        <v>Milk/Conden</v>
       </c>
       <c r="E178" t="str">
-        <v>แตงโม 60 ลูก</v>
+        <v>นมข้นหวาน1ลัง 836</v>
       </c>
       <c r="F178">
-        <v>4200</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="179">
@@ -4706,18 +4706,18 @@
         <v>COGS</v>
       </c>
       <c r="D179" t="str">
-        <v>Transportation</v>
+        <v>Milk/Conden</v>
       </c>
       <c r="E179" t="str">
-        <v>เนื้อ 10 x 50 500</v>
+        <v>นมข้นหวาน 2 ลัง 1,602 + นมข้นจืด 1 ลัง 638</v>
       </c>
       <c r="F179">
-        <v>2395</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>30/04/2026</v>
+        <v>29/04/2026</v>
       </c>
       <c r="B180" t="str">
         <v>Apr26</v>
@@ -4726,38 +4726,38 @@
         <v>COGS</v>
       </c>
       <c r="D180" t="str">
-        <v>Pineapple</v>
+        <v>Packaging</v>
       </c>
       <c r="E180" t="str">
-        <v>สับปะรส 3 ตะกร้า</v>
+        <v>ถุงขยะ 15 แพค 970</v>
       </c>
       <c r="F180">
-        <v>1500</v>
+        <v>970</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>30/04/2026</v>
+        <v>29/04/2026</v>
       </c>
       <c r="B181" t="str">
         <v>Apr26</v>
       </c>
       <c r="C181" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D181" t="str">
-        <v>Rental</v>
+        <v>Watermelon</v>
       </c>
       <c r="E181" t="str">
-        <v>Rent</v>
+        <v>แตงโม 60 ลูก</v>
       </c>
       <c r="F181">
-        <v>35000</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>30/04/2026</v>
+        <v>29/04/2026</v>
       </c>
       <c r="B182" t="str">
         <v>Apr26</v>
@@ -4766,13 +4766,13 @@
         <v>COGS</v>
       </c>
       <c r="D182" t="str">
-        <v>Stock</v>
+        <v>Transportation</v>
       </c>
       <c r="E182" t="str">
-        <v>Stock (Allocated 82.9%)</v>
+        <v>เนื้อ 10 x 50 500</v>
       </c>
       <c r="F182">
-        <v>9948</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="183">
@@ -4786,10 +4786,10 @@
         <v>COGS</v>
       </c>
       <c r="D183" t="str">
-        <v>Guava</v>
+        <v>Pineapple</v>
       </c>
       <c r="E183" t="str">
-        <v>ฝรั่ง ตะกร้าแรก (นาง ประนอม, BBL X8148) [bank 30/04 22:50]</v>
+        <v>สับปะรส 3 ตะกร้า</v>
       </c>
       <c r="F183">
         <v>1500</v>
@@ -4797,62 +4797,62 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>01/05/2026</v>
+        <v>30/04/2026</v>
       </c>
       <c r="B184" t="str">
-        <v>May26</v>
+        <v>Apr26</v>
       </c>
       <c r="C184" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D184" t="str">
-        <v>Guava</v>
+        <v>Rental</v>
       </c>
       <c r="E184" t="str">
-        <v>ฝรั่ง (แยกจากใบเสร็จรวม 01/05)</v>
+        <v>Rent</v>
       </c>
       <c r="F184">
-        <v>300</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>01/05/2026</v>
+        <v>30/04/2026</v>
       </c>
       <c r="B185" t="str">
-        <v>May26</v>
+        <v>Apr26</v>
       </c>
       <c r="C185" t="str">
-        <v>CAPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D185" t="str">
-        <v>Investment</v>
+        <v>Stock</v>
       </c>
       <c r="E185" t="str">
-        <v>ร่ม 2 คัน (1,176 + 843)</v>
+        <v>Stock (Allocated 82.9%)</v>
       </c>
       <c r="F185">
-        <v>2019</v>
+        <v>9948</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>01/05/2026</v>
+        <v>30/04/2026</v>
       </c>
       <c r="B186" t="str">
-        <v>May26</v>
+        <v>Apr26</v>
       </c>
       <c r="C186" t="str">
         <v>COGS</v>
       </c>
       <c r="D186" t="str">
-        <v>Milk/Conden</v>
+        <v>Guava</v>
       </c>
       <c r="E186" t="str">
-        <v>นมข้นจืด (แยกจากใบเสร็จรวม 01/05)</v>
+        <v>ฝรั่ง ตะกร้าแรก (นาง ประนอม, BBL X8148) [bank 30/04 22:50]</v>
       </c>
       <c r="F186">
-        <v>785</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="187">
@@ -4863,16 +4863,16 @@
         <v>May26</v>
       </c>
       <c r="C187" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D187" t="str">
-        <v>Other</v>
+        <v>Guava</v>
       </c>
       <c r="E187" t="str">
-        <v>ที่ปั๊ม (แยกจากใบเสร็จรวม 01/05)</v>
+        <v>ฝรั่ง (แยกจากใบเสร็จรวม 01/05)</v>
       </c>
       <c r="F187">
-        <v>176</v>
+        <v>300</v>
       </c>
     </row>
     <row r="188">
@@ -4883,21 +4883,21 @@
         <v>May26</v>
       </c>
       <c r="C188" t="str">
-        <v>OPEX</v>
+        <v>CAPEX</v>
       </c>
       <c r="D188" t="str">
-        <v>Other</v>
+        <v>Investment</v>
       </c>
       <c r="E188" t="str">
-        <v>ยอดคงเหลือใบเสร็จ 01/05 — ไม่ระบุรายการ ต้องตรวจสอบสลิป</v>
+        <v>ร่ม 2 คัน (1,176 + 843)</v>
       </c>
       <c r="F188">
-        <v>4543</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>02/05/2026</v>
+        <v>01/05/2026</v>
       </c>
       <c r="B189" t="str">
         <v>May26</v>
@@ -4906,53 +4906,53 @@
         <v>COGS</v>
       </c>
       <c r="D189" t="str">
-        <v>Mango</v>
+        <v>Milk/Conden</v>
       </c>
       <c r="E189" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>นมข้นจืด (แยกจากใบเสร็จรวม 01/05)</v>
       </c>
       <c r="F189">
-        <v>910</v>
+        <v>785</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>02/05/2026</v>
+        <v>01/05/2026</v>
       </c>
       <c r="B190" t="str">
         <v>May26</v>
       </c>
       <c r="C190" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D190" t="str">
-        <v>Apple</v>
+        <v>Other</v>
       </c>
       <c r="E190" t="str">
-        <v>แอปเปิ้ล 4 ลัง</v>
+        <v>ที่ปั๊ม (แยกจากใบเสร็จรวม 01/05)</v>
       </c>
       <c r="F190">
-        <v>1500</v>
+        <v>176</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>02/05/2026</v>
+        <v>01/05/2026</v>
       </c>
       <c r="B191" t="str">
         <v>May26</v>
       </c>
       <c r="C191" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D191" t="str">
-        <v>Pineapple</v>
+        <v>Other</v>
       </c>
       <c r="E191" t="str">
-        <v>สับปะรด 30 ลูก</v>
+        <v>ยอดคงเหลือใบเสร็จ 01/05 — ไม่ระบุรายการ ต้องตรวจสอบสลิป</v>
       </c>
       <c r="F191">
-        <v>1116</v>
+        <v>4543</v>
       </c>
     </row>
     <row r="192">
@@ -4963,16 +4963,16 @@
         <v>May26</v>
       </c>
       <c r="C192" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D192" t="str">
-        <v>Other</v>
+        <v>Mango</v>
       </c>
       <c r="E192" t="str">
-        <v>ค่าหาหมอเอ</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F192">
-        <v>706</v>
+        <v>910</v>
       </c>
     </row>
     <row r="193">
@@ -4983,21 +4983,21 @@
         <v>May26</v>
       </c>
       <c r="C193" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D193" t="str">
-        <v>Other</v>
+        <v>Apple</v>
       </c>
       <c r="E193" t="str">
-        <v>ค่าหมอเอ</v>
+        <v>แอปเปิ้ล 4 ลัง</v>
       </c>
       <c r="F193">
-        <v>13</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>04/05/2026</v>
+        <v>02/05/2026</v>
       </c>
       <c r="B194" t="str">
         <v>May26</v>
@@ -5006,53 +5006,53 @@
         <v>COGS</v>
       </c>
       <c r="D194" t="str">
-        <v>Packaging</v>
+        <v>Pineapple</v>
       </c>
       <c r="E194" t="str">
-        <v>ถุงมือ4อัน</v>
+        <v>สับปะรด 30 ลูก</v>
       </c>
       <c r="F194">
-        <v>499</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>04/05/2026</v>
+        <v>02/05/2026</v>
       </c>
       <c r="B195" t="str">
         <v>May26</v>
       </c>
       <c r="C195" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D195" t="str">
-        <v>Apple</v>
+        <v>Other</v>
       </c>
       <c r="E195" t="str">
-        <v>แอปเปิ้ล 4 ลัง</v>
+        <v>ค่าหาหมอเอ</v>
       </c>
       <c r="F195">
-        <v>1400</v>
+        <v>706</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>04/05/2026</v>
+        <v>02/05/2026</v>
       </c>
       <c r="B196" t="str">
         <v>May26</v>
       </c>
       <c r="C196" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D196" t="str">
-        <v>Mango</v>
+        <v>Other</v>
       </c>
       <c r="E196" t="str">
-        <v>มะม่วง 2 ลัง</v>
+        <v>ค่าหมอเอ</v>
       </c>
       <c r="F196">
-        <v>1680</v>
+        <v>13</v>
       </c>
     </row>
     <row r="197">
@@ -5066,38 +5066,38 @@
         <v>COGS</v>
       </c>
       <c r="D197" t="str">
-        <v>Watermelon</v>
+        <v>Packaging</v>
       </c>
       <c r="E197" t="str">
-        <v>30-4-2569 เบอร์ 70฿ 60 ลูก</v>
+        <v>ถุงมือ4อัน</v>
       </c>
       <c r="F197">
-        <v>7000</v>
+        <v>499</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>06/05/2026</v>
+        <v>04/05/2026</v>
       </c>
       <c r="B198" t="str">
         <v>May26</v>
       </c>
       <c r="C198" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D198" t="str">
-        <v>Other</v>
+        <v>Apple</v>
       </c>
       <c r="E198" t="str">
-        <v>ทิชชู่3แพค 36ห่อ</v>
+        <v>แอปเปิ้ล 4 ลัง</v>
       </c>
       <c r="F198">
-        <v>451</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>06/05/2026</v>
+        <v>04/05/2026</v>
       </c>
       <c r="B199" t="str">
         <v>May26</v>
@@ -5112,12 +5112,12 @@
         <v>มะม่วง 2 ลัง</v>
       </c>
       <c r="F199">
-        <v>1750</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>06/05/2026</v>
+        <v>04/05/2026</v>
       </c>
       <c r="B200" t="str">
         <v>May26</v>
@@ -5126,13 +5126,13 @@
         <v>COGS</v>
       </c>
       <c r="D200" t="str">
-        <v>Pineapple</v>
+        <v>Watermelon</v>
       </c>
       <c r="E200" t="str">
-        <v>สับปะรด 18 ลูก</v>
+        <v>30-4-2569 เบอร์ 70฿ 60 ลูก</v>
       </c>
       <c r="F200">
-        <v>486</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="201">
@@ -5143,21 +5143,21 @@
         <v>May26</v>
       </c>
       <c r="C201" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D201" t="str">
-        <v>Apple</v>
+        <v>Other</v>
       </c>
       <c r="E201" t="str">
-        <v>แอปเปิ้ล 4 ลัง</v>
+        <v>ทิชชู่3แพค 36ห่อ</v>
       </c>
       <c r="F201">
-        <v>1400</v>
+        <v>451</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>08/05/2026</v>
+        <v>06/05/2026</v>
       </c>
       <c r="B202" t="str">
         <v>May26</v>
@@ -5166,18 +5166,18 @@
         <v>COGS</v>
       </c>
       <c r="D202" t="str">
-        <v>Transportation</v>
+        <v>Mango</v>
       </c>
       <c r="E202" t="str">
-        <v>น้ำ 20 ขวด 900 ถอดเสื้อ 30 ลูก750 กล่องโฟม 3</v>
+        <v>มะม่วง 2 ลัง</v>
       </c>
       <c r="F202">
-        <v>4555</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>08/05/2026</v>
+        <v>06/05/2026</v>
       </c>
       <c r="B203" t="str">
         <v>May26</v>
@@ -5186,18 +5186,18 @@
         <v>COGS</v>
       </c>
       <c r="D203" t="str">
-        <v>Water</v>
+        <v>Pineapple</v>
       </c>
       <c r="E203" t="str">
-        <v>น้ำมะร้าว 1 ลัง</v>
+        <v>สับปะรด 18 ลูก</v>
       </c>
       <c r="F203">
-        <v>1100</v>
+        <v>486</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>08/05/2026</v>
+        <v>06/05/2026</v>
       </c>
       <c r="B204" t="str">
         <v>May26</v>
@@ -5206,13 +5206,13 @@
         <v>COGS</v>
       </c>
       <c r="D204" t="str">
-        <v>Packaging</v>
+        <v>Apple</v>
       </c>
       <c r="E204" t="str">
-        <v>6 พ.ค. น้ำ 30 ขวด 1500 บาท เนื้อ 11 โล 1320 บาท</v>
+        <v>แอปเปิ้ล 4 ลัง</v>
       </c>
       <c r="F204">
-        <v>2820</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="205">
@@ -5223,16 +5223,16 @@
         <v>May26</v>
       </c>
       <c r="C205" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D205" t="str">
-        <v>Other</v>
+        <v>Transportation</v>
       </c>
       <c r="E205" t="str">
-        <v>ค่าทำความสะอาดตึกชั้น 1</v>
+        <v>น้ำ 20 ขวด 900 ถอดเสื้อ 30 ลูก750 กล่องโฟม 3</v>
       </c>
       <c r="F205">
-        <v>2700</v>
+        <v>4555</v>
       </c>
     </row>
     <row r="206">
@@ -5246,73 +5246,73 @@
         <v>COGS</v>
       </c>
       <c r="D206" t="str">
-        <v>Watermelon</v>
+        <v>Water</v>
       </c>
       <c r="E206" t="str">
-        <v>4-5-2569 เบอร์ 70฿ 60 ลูก ยอด 4,200</v>
+        <v>น้ำมะร้าว 1 ลัง</v>
       </c>
       <c r="F206">
-        <v>8200</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>09/05/2026</v>
+        <v>08/05/2026</v>
       </c>
       <c r="B207" t="str">
         <v>May26</v>
       </c>
       <c r="C207" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D207" t="str">
-        <v>Other</v>
+        <v>Packaging</v>
       </c>
       <c r="E207" t="str">
-        <v>พรหมเช็ดเท้า 1 ผืน</v>
+        <v>6 พ.ค. น้ำ 30 ขวด 1500 บาท เนื้อ 11 โล 1320 บาท</v>
       </c>
       <c r="F207">
-        <v>372</v>
+        <v>2820</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>09/05/2026</v>
+        <v>08/05/2026</v>
       </c>
       <c r="B208" t="str">
         <v>May26</v>
       </c>
       <c r="C208" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D208" t="str">
-        <v>Milk/Conden</v>
+        <v>Other</v>
       </c>
       <c r="E208" t="str">
-        <v>นมข้นจืด 1 ลัง 636</v>
+        <v>ค่าทำความสะอาดตึกชั้น 1</v>
       </c>
       <c r="F208">
-        <v>636</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>09/05/2026</v>
+        <v>08/05/2026</v>
       </c>
       <c r="B209" t="str">
         <v>May26</v>
       </c>
       <c r="C209" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D209" t="str">
-        <v>Other</v>
+        <v>Watermelon</v>
       </c>
       <c r="E209" t="str">
-        <v>ลิ้นชักเก็บเงิน 486</v>
+        <v>4-5-2569 เบอร์ 70฿ 60 ลูก ยอด 4,200</v>
       </c>
       <c r="F209">
-        <v>486</v>
+        <v>8200</v>
       </c>
     </row>
     <row r="210">
@@ -5323,16 +5323,16 @@
         <v>May26</v>
       </c>
       <c r="C210" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D210" t="str">
-        <v>Milk/Conden</v>
+        <v>Other</v>
       </c>
       <c r="E210" t="str">
-        <v>นมข้น 3 ลัง 2,568 + นมข้นจืด 2 ลัง 1,479</v>
+        <v>พรหมเช็ดเท้า 1 ผืน</v>
       </c>
       <c r="F210">
-        <v>4047</v>
+        <v>372</v>
       </c>
     </row>
     <row r="211">
@@ -5346,13 +5346,13 @@
         <v>COGS</v>
       </c>
       <c r="D211" t="str">
-        <v>Packaging</v>
+        <v>Milk/Conden</v>
       </c>
       <c r="E211" t="str">
-        <v>ฝา 1 ลัง 828</v>
+        <v>นมข้นจืด 1 ลัง 636</v>
       </c>
       <c r="F211">
-        <v>828</v>
+        <v>636</v>
       </c>
     </row>
     <row r="212">
@@ -5363,16 +5363,16 @@
         <v>May26</v>
       </c>
       <c r="C212" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D212" t="str">
-        <v>Packaging</v>
+        <v>Other</v>
       </c>
       <c r="E212" t="str">
-        <v>แก้ว3ลัง 5,301</v>
+        <v>ลิ้นชักเก็บเงิน 486</v>
       </c>
       <c r="F212">
-        <v>6132</v>
+        <v>486</v>
       </c>
     </row>
     <row r="213">
@@ -5386,13 +5386,13 @@
         <v>COGS</v>
       </c>
       <c r="D213" t="str">
-        <v>Packaging</v>
+        <v>Milk/Conden</v>
       </c>
       <c r="E213" t="str">
-        <v>ถุงมือ 20 กล่อง 2246 ฝา1ลัง 969</v>
+        <v>นมข้น 3 ลัง 2,568 + นมข้นจืด 2 ลัง 1,479</v>
       </c>
       <c r="F213">
-        <v>4496</v>
+        <v>4047</v>
       </c>
     </row>
     <row r="214">
@@ -5406,38 +5406,38 @@
         <v>COGS</v>
       </c>
       <c r="D214" t="str">
-        <v>Transportation</v>
+        <v>Packaging</v>
       </c>
       <c r="E214" t="str">
-        <v>Lalamove</v>
+        <v>ฝา 1 ลัง 828</v>
       </c>
       <c r="F214">
-        <v>2000</v>
+        <v>828</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>10/05/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="B215" t="str">
         <v>May26</v>
       </c>
       <c r="C215" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D215" t="str">
-        <v>Other</v>
+        <v>Packaging</v>
       </c>
       <c r="E215" t="str">
-        <v>ไฟ 2อัน 422</v>
+        <v>แก้ว3ลัง 5,301</v>
       </c>
       <c r="F215">
-        <v>838</v>
+        <v>6132</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>11/05/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="B216" t="str">
         <v>May26</v>
@@ -5446,18 +5446,18 @@
         <v>COGS</v>
       </c>
       <c r="D216" t="str">
-        <v>Guava</v>
+        <v>Packaging</v>
       </c>
       <c r="E216" t="str">
-        <v>ฝรั่ง 1 ตะกร้า</v>
+        <v>ถุงมือ 20 กล่อง 2246 ฝา1ลัง 969</v>
       </c>
       <c r="F216">
-        <v>600</v>
+        <v>4496</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>11/05/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="B217" t="str">
         <v>May26</v>
@@ -5466,38 +5466,38 @@
         <v>COGS</v>
       </c>
       <c r="D217" t="str">
-        <v>Mango</v>
+        <v>Transportation</v>
       </c>
       <c r="E217" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>Lalamove</v>
       </c>
       <c r="F217">
-        <v>910</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>11/05/2026</v>
+        <v>10/05/2026</v>
       </c>
       <c r="B218" t="str">
         <v>May26</v>
       </c>
       <c r="C218" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D218" t="str">
-        <v>Watermelon</v>
+        <v>Other</v>
       </c>
       <c r="E218" t="str">
-        <v>แตงโม 4000 วันที่ 9-5-26</v>
+        <v>ไฟ 2อัน 422</v>
       </c>
       <c r="F218">
-        <v>4000</v>
+        <v>838</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>12/05/2026</v>
+        <v>11/05/2026</v>
       </c>
       <c r="B219" t="str">
         <v>May26</v>
@@ -5506,38 +5506,38 @@
         <v>COGS</v>
       </c>
       <c r="D219" t="str">
-        <v>Coconut Meat</v>
+        <v>Guava</v>
       </c>
       <c r="E219" t="str">
-        <v>เนื้อมะพร้าว 1 ลัง</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F219">
-        <v>3500</v>
+        <v>600</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>13/05/2026</v>
+        <v>11/05/2026</v>
       </c>
       <c r="B220" t="str">
         <v>May26</v>
       </c>
       <c r="C220" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D220" t="str">
-        <v>Other</v>
+        <v>Mango</v>
       </c>
       <c r="E220" t="str">
-        <v>ที่หนีบ 6ตัว 374 บาท</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F220">
-        <v>374</v>
+        <v>910</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>13/05/2026</v>
+        <v>11/05/2026</v>
       </c>
       <c r="B221" t="str">
         <v>May26</v>
@@ -5546,18 +5546,18 @@
         <v>COGS</v>
       </c>
       <c r="D221" t="str">
-        <v>Pineapple</v>
+        <v>Watermelon</v>
       </c>
       <c r="E221" t="str">
-        <v>09/05/26 สับปะรด 2 ตะกร้า</v>
+        <v>แตงโม 4000 วันที่ 9-5-26</v>
       </c>
       <c r="F221">
-        <v>1008</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>14/05/2026</v>
+        <v>12/05/2026</v>
       </c>
       <c r="B222" t="str">
         <v>May26</v>
@@ -5566,18 +5566,18 @@
         <v>COGS</v>
       </c>
       <c r="D222" t="str">
-        <v>Watermelon</v>
+        <v>Coconut Meat</v>
       </c>
       <c r="E222" t="str">
-        <v>11-5-2569 50 ลูก ยอด 4,000</v>
+        <v>เนื้อมะพร้าว 1 ลัง</v>
       </c>
       <c r="F222">
-        <v>8000</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>14/05/2026</v>
+        <v>13/05/2026</v>
       </c>
       <c r="B223" t="str">
         <v>May26</v>
@@ -5586,33 +5586,33 @@
         <v>OPEX</v>
       </c>
       <c r="D223" t="str">
-        <v>Rental</v>
+        <v>Other</v>
       </c>
       <c r="E223" t="str">
-        <v>ค่าเช่าร้าน 1 พ.ค.</v>
+        <v>ที่หนีบ 6ตัว 374 บาท</v>
       </c>
       <c r="F223">
-        <v>35000</v>
+        <v>374</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>14/05/2026</v>
+        <v>13/05/2026</v>
       </c>
       <c r="B224" t="str">
         <v>May26</v>
       </c>
       <c r="C224" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D224" t="str">
-        <v>Rental</v>
+        <v>Pineapple</v>
       </c>
       <c r="E224" t="str">
-        <v>ค่าเช่าคลัง พ.ค. (B1 ครึ่งหนึ่ง)</v>
+        <v>09/05/26 สับปะรด 2 ตะกร้า</v>
       </c>
       <c r="F224">
-        <v>6000</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="225">
@@ -5626,13 +5626,13 @@
         <v>COGS</v>
       </c>
       <c r="D225" t="str">
-        <v>Guava</v>
+        <v>Watermelon</v>
       </c>
       <c r="E225" t="str">
-        <v>ฝรั่ง 1 ตะกร้า</v>
+        <v>11-5-2569 50 ลูก ยอด 4,000</v>
       </c>
       <c r="F225">
-        <v>600</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="226">
@@ -5643,16 +5643,16 @@
         <v>May26</v>
       </c>
       <c r="C226" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D226" t="str">
-        <v>Apple</v>
+        <v>Rental</v>
       </c>
       <c r="E226" t="str">
-        <v>แอปเปิ้ล 3 ลัง</v>
+        <v>ค่าเช่าร้าน 1 พ.ค.</v>
       </c>
       <c r="F226">
-        <v>1050</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="227">
@@ -5663,21 +5663,21 @@
         <v>May26</v>
       </c>
       <c r="C227" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D227" t="str">
-        <v>Mango</v>
+        <v>Rental</v>
       </c>
       <c r="E227" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>ค่าเช่าคลัง พ.ค. (B1 ครึ่งหนึ่ง)</v>
       </c>
       <c r="F227">
-        <v>875</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>15/05/2026</v>
+        <v>14/05/2026</v>
       </c>
       <c r="B228" t="str">
         <v>May26</v>
@@ -5686,18 +5686,18 @@
         <v>COGS</v>
       </c>
       <c r="D228" t="str">
-        <v>Orange</v>
+        <v>Guava</v>
       </c>
       <c r="E228" t="str">
-        <v>ส้ม 22x22กก 484 กก. x30 = 14,520 + ค่าส่ง 22x55 = 1,210 (15/05/69)</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F228">
-        <v>15730</v>
+        <v>600</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>15/05/2026</v>
+        <v>14/05/2026</v>
       </c>
       <c r="B229" t="str">
         <v>May26</v>
@@ -5706,38 +5706,38 @@
         <v>COGS</v>
       </c>
       <c r="D229" t="str">
-        <v>Orange</v>
+        <v>Apple</v>
       </c>
       <c r="E229" t="str">
-        <v>05/05/69 ส้ม 30x22กก 660กกx30</v>
+        <v>แอปเปิ้ล 3 ลัง</v>
       </c>
       <c r="F229">
-        <v>21450</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>16/05/2026</v>
+        <v>14/05/2026</v>
       </c>
       <c r="B230" t="str">
         <v>May26</v>
       </c>
       <c r="C230" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D230" t="str">
-        <v>Other</v>
+        <v>Mango</v>
       </c>
       <c r="E230" t="str">
-        <v>Police fees -2000 2 head</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F230">
-        <v>4290</v>
+        <v>875</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>16/05/2026</v>
+        <v>15/05/2026</v>
       </c>
       <c r="B231" t="str">
         <v>May26</v>
@@ -5746,18 +5746,18 @@
         <v>COGS</v>
       </c>
       <c r="D231" t="str">
-        <v>Coconut</v>
+        <v>Orange</v>
       </c>
       <c r="E231" t="str">
-        <v>มะพร้าว 20 โล</v>
+        <v>ส้ม 22x22กก 484 กก. x30 = 14,520 + ค่าส่ง 22x55 = 1,210 (15/05/69)</v>
       </c>
       <c r="F231">
-        <v>2400</v>
+        <v>15730</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>16/05/2026</v>
+        <v>15/05/2026</v>
       </c>
       <c r="B232" t="str">
         <v>May26</v>
@@ -5766,13 +5766,13 @@
         <v>COGS</v>
       </c>
       <c r="D232" t="str">
-        <v>Watermelon</v>
+        <v>Orange</v>
       </c>
       <c r="E232" t="str">
-        <v>14/05/26 18 ลูก 504 บาท 16/05/26 18 ลูก</v>
+        <v>05/05/69 ส้ม 30x22กก 660กกx30</v>
       </c>
       <c r="F232">
-        <v>1008</v>
+        <v>21450</v>
       </c>
     </row>
     <row r="233">
@@ -5783,21 +5783,21 @@
         <v>May26</v>
       </c>
       <c r="C233" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D233" t="str">
-        <v>Mango</v>
+        <v>Other</v>
       </c>
       <c r="E233" t="str">
-        <v>มะม่วง 1</v>
+        <v>Police fees -2000 2 head</v>
       </c>
       <c r="F233">
-        <v>875</v>
+        <v>4290</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>19/05/2026</v>
+        <v>16/05/2026</v>
       </c>
       <c r="B234" t="str">
         <v>May26</v>
@@ -5806,18 +5806,18 @@
         <v>COGS</v>
       </c>
       <c r="D234" t="str">
-        <v>Mango</v>
+        <v>Coconut</v>
       </c>
       <c r="E234" t="str">
-        <v>มะม่วง 1 ลัง (25 โล)</v>
+        <v>มะพร้าว 20 โล</v>
       </c>
       <c r="F234">
-        <v>875</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>19/05/2026</v>
+        <v>16/05/2026</v>
       </c>
       <c r="B235" t="str">
         <v>May26</v>
@@ -5826,18 +5826,18 @@
         <v>COGS</v>
       </c>
       <c r="D235" t="str">
-        <v>Guava</v>
+        <v>Watermelon</v>
       </c>
       <c r="E235" t="str">
-        <v>ฝรั่ง 1 ลัง</v>
+        <v>14/05/26 18 ลูก 504 บาท 16/05/26 18 ลูก</v>
       </c>
       <c r="F235">
-        <v>600</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>19/05/2026</v>
+        <v>16/05/2026</v>
       </c>
       <c r="B236" t="str">
         <v>May26</v>
@@ -5846,13 +5846,13 @@
         <v>COGS</v>
       </c>
       <c r="D236" t="str">
-        <v>Apple</v>
+        <v>Mango</v>
       </c>
       <c r="E236" t="str">
-        <v>แอปเปิ้ล 4 ลังครับ</v>
+        <v>มะม่วง 1</v>
       </c>
       <c r="F236">
-        <v>1400</v>
+        <v>875</v>
       </c>
     </row>
     <row r="237">
@@ -5866,18 +5866,18 @@
         <v>COGS</v>
       </c>
       <c r="D237" t="str">
-        <v>Pineapple</v>
+        <v>Mango</v>
       </c>
       <c r="E237" t="str">
-        <v>36*18 648</v>
+        <v>มะม่วง 1 ลัง (25 โล)</v>
       </c>
       <c r="F237">
-        <v>648</v>
+        <v>875</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>22/05/2026</v>
+        <v>19/05/2026</v>
       </c>
       <c r="B238" t="str">
         <v>May26</v>
@@ -5886,18 +5886,18 @@
         <v>COGS</v>
       </c>
       <c r="D238" t="str">
-        <v>Apple</v>
+        <v>Guava</v>
       </c>
       <c r="E238" t="str">
-        <v>แอปเปิ้ล 2 ลัง</v>
+        <v>ฝรั่ง 1 ลัง</v>
       </c>
       <c r="F238">
-        <v>700</v>
+        <v>600</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>22/05/2026</v>
+        <v>19/05/2026</v>
       </c>
       <c r="B239" t="str">
         <v>May26</v>
@@ -5906,18 +5906,18 @@
         <v>COGS</v>
       </c>
       <c r="D239" t="str">
-        <v>Pineapple</v>
+        <v>Apple</v>
       </c>
       <c r="E239" t="str">
-        <v>สับปะรด 18 ลูก</v>
+        <v>แอปเปิ้ล 4 ลังครับ</v>
       </c>
       <c r="F239">
-        <v>522</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>22/05/2026</v>
+        <v>19/05/2026</v>
       </c>
       <c r="B240" t="str">
         <v>May26</v>
@@ -5926,13 +5926,13 @@
         <v>COGS</v>
       </c>
       <c r="D240" t="str">
-        <v>Mango</v>
+        <v>Pineapple</v>
       </c>
       <c r="E240" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>36*18 648</v>
       </c>
       <c r="F240">
-        <v>1000</v>
+        <v>648</v>
       </c>
     </row>
     <row r="241">
@@ -5946,13 +5946,13 @@
         <v>COGS</v>
       </c>
       <c r="D241" t="str">
-        <v>Watermelon</v>
+        <v>Apple</v>
       </c>
       <c r="E241" t="str">
-        <v>16-5-2569ยอด 4,000฿</v>
+        <v>แอปเปิ้ล 2 ลัง</v>
       </c>
       <c r="F241">
-        <v>12000</v>
+        <v>700</v>
       </c>
     </row>
     <row r="242">
@@ -5966,13 +5966,13 @@
         <v>COGS</v>
       </c>
       <c r="D242" t="str">
-        <v>Guava</v>
+        <v>Pineapple</v>
       </c>
       <c r="E242" t="str">
-        <v>ฝรั่ง 1 ตะกร้า</v>
+        <v>สับปะรด 18 ลูก</v>
       </c>
       <c r="F242">
-        <v>600</v>
+        <v>522</v>
       </c>
     </row>
     <row r="243">
@@ -5986,18 +5986,18 @@
         <v>COGS</v>
       </c>
       <c r="D243" t="str">
-        <v>Transportation</v>
+        <v>Mango</v>
       </c>
       <c r="E243" t="str">
-        <v>ค่าขนส่ง</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F243">
-        <v>2000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>23/05/2026</v>
+        <v>22/05/2026</v>
       </c>
       <c r="B244" t="str">
         <v>May26</v>
@@ -6006,18 +6006,18 @@
         <v>COGS</v>
       </c>
       <c r="D244" t="str">
-        <v>Packaging</v>
+        <v>Watermelon</v>
       </c>
       <c r="E244" t="str">
-        <v>แก้ว 3 ลัง</v>
+        <v>16-5-2569ยอด 4,000฿</v>
       </c>
       <c r="F244">
-        <v>4680</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>23/05/2026</v>
+        <v>22/05/2026</v>
       </c>
       <c r="B245" t="str">
         <v>May26</v>
@@ -6026,18 +6026,18 @@
         <v>COGS</v>
       </c>
       <c r="D245" t="str">
-        <v>Packaging</v>
+        <v>Guava</v>
       </c>
       <c r="E245" t="str">
-        <v>ฝา1 788</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F245">
-        <v>2902</v>
+        <v>600</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>23/05/2026</v>
+        <v>22/05/2026</v>
       </c>
       <c r="B246" t="str">
         <v>May26</v>
@@ -6046,18 +6046,18 @@
         <v>COGS</v>
       </c>
       <c r="D246" t="str">
-        <v>Packaging</v>
+        <v>Transportation</v>
       </c>
       <c r="E246" t="str">
-        <v>หลอด20 แพค (767)</v>
+        <v>ค่าขนส่ง</v>
       </c>
       <c r="F246">
-        <v>1502</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>25/05/2026</v>
+        <v>23/05/2026</v>
       </c>
       <c r="B247" t="str">
         <v>May26</v>
@@ -6066,18 +6066,18 @@
         <v>COGS</v>
       </c>
       <c r="D247" t="str">
-        <v>Pineapple</v>
+        <v>Packaging</v>
       </c>
       <c r="E247" t="str">
-        <v>สับปะรด 18 ลูก</v>
+        <v>แก้ว 3 ลัง</v>
       </c>
       <c r="F247">
-        <v>594</v>
+        <v>4680</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>25/05/2026</v>
+        <v>23/05/2026</v>
       </c>
       <c r="B248" t="str">
         <v>May26</v>
@@ -6086,18 +6086,18 @@
         <v>COGS</v>
       </c>
       <c r="D248" t="str">
-        <v>Apple</v>
+        <v>Packaging</v>
       </c>
       <c r="E248" t="str">
-        <v>แอปเปิ้ล 3 ลังครับ</v>
+        <v>ฝา1 788</v>
       </c>
       <c r="F248">
-        <v>1050</v>
+        <v>2902</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>25/05/2026</v>
+        <v>23/05/2026</v>
       </c>
       <c r="B249" t="str">
         <v>May26</v>
@@ -6106,13 +6106,13 @@
         <v>COGS</v>
       </c>
       <c r="D249" t="str">
-        <v>Orange</v>
+        <v>Packaging</v>
       </c>
       <c r="E249" t="str">
-        <v>ค่าส่งส้ม Lalamove หักผ่านบัตร</v>
+        <v>หลอด20 แพค (767)</v>
       </c>
       <c r="F249">
-        <v>1245</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="250">
@@ -6126,13 +6126,13 @@
         <v>COGS</v>
       </c>
       <c r="D250" t="str">
-        <v>Orange</v>
+        <v>Pineapple</v>
       </c>
       <c r="E250" t="str">
-        <v>ส้ม 21x22กก 462 กก. x30 = 13,860 + ค่าส่ง 21x55 = 1,155 (24/05/69)</v>
+        <v>สับปะรด 18 ลูก</v>
       </c>
       <c r="F250">
-        <v>15015</v>
+        <v>594</v>
       </c>
     </row>
     <row r="251">
@@ -6143,16 +6143,16 @@
         <v>May26</v>
       </c>
       <c r="C251" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D251" t="str">
-        <v>Salary</v>
+        <v>Apple</v>
       </c>
       <c r="E251" t="str">
-        <v>เงินเดือนซี เดือนพ.ค. (แก้ไข: ยืนยัน 24,000)</v>
+        <v>แอปเปิ้ล 3 ลังครับ</v>
       </c>
       <c r="F251">
-        <v>24000</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="252">
@@ -6166,13 +6166,13 @@
         <v>COGS</v>
       </c>
       <c r="D252" t="str">
-        <v>Guava</v>
+        <v>Orange</v>
       </c>
       <c r="E252" t="str">
-        <v>ฝรั่ง 1 ตะกร้า</v>
+        <v>ค่าส่งส้ม Lalamove หักผ่านบัตร</v>
       </c>
       <c r="F252">
-        <v>600</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="253">
@@ -6186,18 +6186,18 @@
         <v>COGS</v>
       </c>
       <c r="D253" t="str">
-        <v>Mango</v>
+        <v>Orange</v>
       </c>
       <c r="E253" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>ส้ม 21x22กก 462 กก. x30 = 13,860 + ค่าส่ง 21x55 = 1,155 (24/05/69)</v>
       </c>
       <c r="F253">
-        <v>1000</v>
+        <v>15015</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>27/05/2026</v>
+        <v>25/05/2026</v>
       </c>
       <c r="B254" t="str">
         <v>May26</v>
@@ -6209,35 +6209,35 @@
         <v>Salary</v>
       </c>
       <c r="E254" t="str">
-        <v>เงินเดือนเมน 5/26</v>
+        <v>เงินเดือนซี เดือนพ.ค. (แก้ไข: ยืนยัน 24,000)</v>
       </c>
       <c r="F254">
-        <v>19000</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>28/05/2026</v>
+        <v>25/05/2026</v>
       </c>
       <c r="B255" t="str">
         <v>May26</v>
       </c>
       <c r="C255" t="str">
-        <v>CAPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D255" t="str">
-        <v>Investment</v>
+        <v>Guava</v>
       </c>
       <c r="E255" t="str">
-        <v>เครื่องสกัดเย็น 1</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F255">
-        <v>1065</v>
+        <v>600</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>28/05/2026</v>
+        <v>25/05/2026</v>
       </c>
       <c r="B256" t="str">
         <v>May26</v>
@@ -6246,73 +6246,73 @@
         <v>COGS</v>
       </c>
       <c r="D256" t="str">
-        <v>Coconut</v>
+        <v>Mango</v>
       </c>
       <c r="E256" t="str">
-        <v>มะพร้าวถอดเสื้อ 23 ลูก *35 ราคา 805 ค่าส่ง 150</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F256">
-        <v>955</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>30/05/2026</v>
+        <v>27/05/2026</v>
       </c>
       <c r="B257" t="str">
         <v>May26</v>
       </c>
       <c r="C257" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D257" t="str">
-        <v>Pineapple</v>
+        <v>Salary</v>
       </c>
       <c r="E257" t="str">
-        <v>สับปะรด 18 ลูก</v>
+        <v>เงินเดือนเมน 5/26</v>
       </c>
       <c r="F257">
-        <v>576</v>
+        <v>19000</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>30/05/2026</v>
+        <v>28/05/2026</v>
       </c>
       <c r="B258" t="str">
         <v>May26</v>
       </c>
       <c r="C258" t="str">
-        <v>COGS</v>
+        <v>CAPEX</v>
       </c>
       <c r="D258" t="str">
-        <v>Mango</v>
+        <v>Investment</v>
       </c>
       <c r="E258" t="str">
-        <v>มะม่วง 1 ตะกร้า</v>
+        <v>เครื่องสกัดเย็น 1</v>
       </c>
       <c r="F258">
-        <v>960</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>30/05/2026</v>
+        <v>28/05/2026</v>
       </c>
       <c r="B259" t="str">
         <v>May26</v>
       </c>
       <c r="C259" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D259" t="str">
-        <v>Other</v>
+        <v>Coconut</v>
       </c>
       <c r="E259" t="str">
-        <v>Unknown</v>
+        <v>มะพร้าวถอดเสื้อ 23 ลูก *35 ราคา 805 ค่าส่ง 150</v>
       </c>
       <c r="F259">
-        <v>1050</v>
+        <v>955</v>
       </c>
     </row>
     <row r="260">
@@ -6326,18 +6326,18 @@
         <v>COGS</v>
       </c>
       <c r="D260" t="str">
-        <v>Guava</v>
+        <v>Pineapple</v>
       </c>
       <c r="E260" t="str">
-        <v>ฝรั่ง 1 ตะกร้า</v>
+        <v>สับปะรด 18 ลูก</v>
       </c>
       <c r="F260">
-        <v>600</v>
+        <v>576</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>31/05/2026</v>
+        <v>30/05/2026</v>
       </c>
       <c r="B261" t="str">
         <v>May26</v>
@@ -6346,18 +6346,18 @@
         <v>COGS</v>
       </c>
       <c r="D261" t="str">
-        <v>Stock</v>
+        <v>Mango</v>
       </c>
       <c r="E261" t="str">
-        <v>Stock Adjustment (Allocated to B2)</v>
+        <v>มะม่วง 1 ตะกร้า</v>
       </c>
       <c r="F261">
-        <v>-4830</v>
+        <v>960</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>01/06/2026</v>
+        <v>30/05/2026</v>
       </c>
       <c r="B262" t="str">
         <v>May26</v>
@@ -6366,78 +6366,78 @@
         <v>OPEX</v>
       </c>
       <c r="D262" t="str">
-        <v>Salary</v>
+        <v>Other</v>
       </c>
       <c r="E262" t="str">
         <v>Unknown</v>
       </c>
       <c r="F262">
-        <v>0</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>02/06/2026</v>
+        <v>30/05/2026</v>
       </c>
       <c r="B263" t="str">
-        <v>Jun26</v>
+        <v>May26</v>
       </c>
       <c r="C263" t="str">
         <v>COGS</v>
       </c>
       <c r="D263" t="str">
-        <v>Pineapple</v>
+        <v>Guava</v>
       </c>
       <c r="E263" t="str">
-        <v>สับปะรด ราคา 31*18 ลูก 558</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F263">
-        <v>558</v>
+        <v>600</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>02/06/2026</v>
+        <v>31/05/2026</v>
       </c>
       <c r="B264" t="str">
-        <v>Jun26</v>
+        <v>May26</v>
       </c>
       <c r="C264" t="str">
         <v>COGS</v>
       </c>
       <c r="D264" t="str">
-        <v>Guava</v>
+        <v>Stock</v>
       </c>
       <c r="E264" t="str">
-        <v>ฝรั่ง 1 ตะกร้า</v>
+        <v>Stock Adjustment (Allocated to B2)</v>
       </c>
       <c r="F264">
-        <v>600</v>
+        <v>-4830</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>02/06/2026</v>
+        <v>01/06/2026</v>
       </c>
       <c r="B265" t="str">
-        <v>Jun26</v>
+        <v>May26</v>
       </c>
       <c r="C265" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D265" t="str">
-        <v>Watermelon</v>
+        <v>Salary</v>
       </c>
       <c r="E265" t="str">
-        <v>แตงโม 160 ลูก (25-5-2569: 80 ลูก, 30-5-2569: 80 ลูก)</v>
+        <v>Unknown</v>
       </c>
       <c r="F265">
-        <v>8000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>04/06/2026</v>
+        <v>02/06/2026</v>
       </c>
       <c r="B266" t="str">
         <v>Jun26</v>
@@ -6446,18 +6446,18 @@
         <v>COGS</v>
       </c>
       <c r="D266" t="str">
-        <v>Watermelon</v>
+        <v>Pineapple</v>
       </c>
       <c r="E266" t="str">
-        <v>สลิปรวม: แตงโม 750 (audit fix, was bundled into Pineapple line)</v>
+        <v>สับปะรด ราคา 31*18 ลูก 558</v>
       </c>
       <c r="F266">
-        <v>750</v>
+        <v>558</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>04/06/2026</v>
+        <v>02/06/2026</v>
       </c>
       <c r="B267" t="str">
         <v>Jun26</v>
@@ -6472,12 +6472,12 @@
         <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F267">
-        <v>700</v>
+        <v>600</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>04/06/2026</v>
+        <v>02/06/2026</v>
       </c>
       <c r="B268" t="str">
         <v>Jun26</v>
@@ -6486,13 +6486,13 @@
         <v>COGS</v>
       </c>
       <c r="D268" t="str">
-        <v>Mango</v>
+        <v>Watermelon</v>
       </c>
       <c r="E268" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>แตงโม 160 ลูก (25-5-2569: 80 ลูก, 30-5-2569: 80 ลูก)</v>
       </c>
       <c r="F268">
-        <v>1040</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="269">
@@ -6506,13 +6506,13 @@
         <v>COGS</v>
       </c>
       <c r="D269" t="str">
-        <v>Apple</v>
+        <v>Watermelon</v>
       </c>
       <c r="E269" t="str">
-        <v>แอพเปิ้ล 4 ลัง</v>
+        <v>สลิปรวม: แตงโม 750 (audit fix, was bundled into Pineapple line)</v>
       </c>
       <c r="F269">
-        <v>1400</v>
+        <v>750</v>
       </c>
     </row>
     <row r="270">
@@ -6526,13 +6526,13 @@
         <v>COGS</v>
       </c>
       <c r="D270" t="str">
-        <v>Pineapple</v>
+        <v>Guava</v>
       </c>
       <c r="E270" t="str">
-        <v>สับปะรด 2 ลูก</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F270">
-        <v>36</v>
+        <v>700</v>
       </c>
     </row>
     <row r="271">
@@ -6546,18 +6546,18 @@
         <v>COGS</v>
       </c>
       <c r="D271" t="str">
-        <v>Packaging</v>
+        <v>Mango</v>
       </c>
       <c r="E271" t="str">
-        <v>ขวดใหญ่ 1000ml 98 ใบ 364 ถุงเล็ก 20</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F271">
-        <v>764</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>05/06/2026</v>
+        <v>04/06/2026</v>
       </c>
       <c r="B272" t="str">
         <v>Jun26</v>
@@ -6566,18 +6566,18 @@
         <v>COGS</v>
       </c>
       <c r="D272" t="str">
-        <v>Pineapple</v>
+        <v>Apple</v>
       </c>
       <c r="E272" t="str">
-        <v>สับปะรด 33*18 รวม 594</v>
+        <v>แอพเปิ้ล 4 ลัง</v>
       </c>
       <c r="F272">
-        <v>594</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>05/06/2026</v>
+        <v>04/06/2026</v>
       </c>
       <c r="B273" t="str">
         <v>Jun26</v>
@@ -6586,18 +6586,18 @@
         <v>COGS</v>
       </c>
       <c r="D273" t="str">
-        <v>Watermelon</v>
+        <v>Pineapple</v>
       </c>
       <c r="E273" t="str">
-        <v>แตงโม 100 ลูก (2-6-2569: 50 ลูก, 4-6-2569: 50 ลูก)</v>
+        <v>สับปะรด 2 ลูก</v>
       </c>
       <c r="F273">
-        <v>8000</v>
+        <v>36</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>07/06/2026</v>
+        <v>04/06/2026</v>
       </c>
       <c r="B274" t="str">
         <v>Jun26</v>
@@ -6606,18 +6606,18 @@
         <v>COGS</v>
       </c>
       <c r="D274" t="str">
-        <v>Orange</v>
+        <v>Packaging</v>
       </c>
       <c r="E274" t="str">
-        <v>ส้ม 20x22กก 440กกx30 13,200บาท</v>
+        <v>ขวดใหญ่ 1000ml 98 ใบ 364 ถุงเล็ก 20</v>
       </c>
       <c r="F274">
-        <v>14300</v>
+        <v>764</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>08/06/2026</v>
+        <v>05/06/2026</v>
       </c>
       <c r="B275" t="str">
         <v>Jun26</v>
@@ -6626,18 +6626,18 @@
         <v>COGS</v>
       </c>
       <c r="D275" t="str">
-        <v>Transportation</v>
+        <v>Pineapple</v>
       </c>
       <c r="E275" t="str">
-        <v>Lalamove</v>
+        <v>สับปะรด 33*18 รวม 594</v>
       </c>
       <c r="F275">
-        <v>2000</v>
+        <v>594</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>08/06/2026</v>
+        <v>05/06/2026</v>
       </c>
       <c r="B276" t="str">
         <v>Jun26</v>
@@ -6646,33 +6646,33 @@
         <v>COGS</v>
       </c>
       <c r="D276" t="str">
-        <v>Stock</v>
+        <v>Watermelon</v>
       </c>
       <c r="E276" t="str">
-        <v>Stock June 2026 (B1 ครึ่งหนึ่ง 6,000; B2 ถืออีก 6,000)</v>
+        <v>แตงโม 100 ลูก (2-6-2569: 50 ลูก, 4-6-2569: 50 ลูก)</v>
       </c>
       <c r="F276">
-        <v>6000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>08/06/2026</v>
+        <v>07/06/2026</v>
       </c>
       <c r="B277" t="str">
         <v>Jun26</v>
       </c>
       <c r="C277" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D277" t="str">
-        <v>Rental</v>
+        <v>Orange</v>
       </c>
       <c r="E277" t="str">
-        <v>ค่าเช่าร้านเดือน June (06) b1 35000</v>
+        <v>ส้ม 20x22กก 440กกx30 13,200บาท</v>
       </c>
       <c r="F277">
-        <v>35000</v>
+        <v>14300</v>
       </c>
     </row>
     <row r="278">
@@ -6686,13 +6686,13 @@
         <v>COGS</v>
       </c>
       <c r="D278" t="str">
-        <v>Pineapple</v>
+        <v>Transportation</v>
       </c>
       <c r="E278" t="str">
-        <v>สับปะรด 15 ลูก</v>
+        <v>Lalamove</v>
       </c>
       <c r="F278">
-        <v>504</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="279">
@@ -6706,13 +6706,13 @@
         <v>COGS</v>
       </c>
       <c r="D279" t="str">
-        <v>Mango</v>
+        <v>Stock</v>
       </c>
       <c r="E279" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>Stock June 2026 (B1 ครึ่งหนึ่ง 6,000; B2 ถืออีก 6,000)</v>
       </c>
       <c r="F279">
-        <v>1170</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="280">
@@ -6723,16 +6723,16 @@
         <v>Jun26</v>
       </c>
       <c r="C280" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D280" t="str">
-        <v>Apple</v>
+        <v>Rental</v>
       </c>
       <c r="E280" t="str">
-        <v>แอปเปิ้ล 5 ลัง</v>
+        <v>ค่าเช่าร้านเดือน June (06) b1 35000</v>
       </c>
       <c r="F280">
-        <v>1750</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="281">
@@ -6746,18 +6746,18 @@
         <v>COGS</v>
       </c>
       <c r="D281" t="str">
-        <v>Guava</v>
+        <v>Pineapple</v>
       </c>
       <c r="E281" t="str">
-        <v>ฝรั่ง 1 ตะกร้า</v>
+        <v>สับปะรด 15 ลูก</v>
       </c>
       <c r="F281">
-        <v>700</v>
+        <v>504</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>09/06/2026</v>
+        <v>08/06/2026</v>
       </c>
       <c r="B282" t="str">
         <v>Jun26</v>
@@ -6766,18 +6766,18 @@
         <v>COGS</v>
       </c>
       <c r="D282" t="str">
-        <v>Packaging</v>
+        <v>Mango</v>
       </c>
       <c r="E282" t="str">
-        <v>แก้ว 1937*3 รวม 5,811</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F282">
-        <v>6659</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>09/06/2026</v>
+        <v>08/06/2026</v>
       </c>
       <c r="B283" t="str">
         <v>Jun26</v>
@@ -6786,18 +6786,18 @@
         <v>COGS</v>
       </c>
       <c r="D283" t="str">
-        <v>Packaging</v>
+        <v>Apple</v>
       </c>
       <c r="E283" t="str">
-        <v>หลอด 20 แพ็ก 671</v>
+        <v>แอปเปิ้ล 5 ลัง</v>
       </c>
       <c r="F283">
-        <v>1149</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>09/06/2026</v>
+        <v>08/06/2026</v>
       </c>
       <c r="B284" t="str">
         <v>Jun26</v>
@@ -6806,13 +6806,13 @@
         <v>COGS</v>
       </c>
       <c r="D284" t="str">
-        <v>Packaging</v>
+        <v>Guava</v>
       </c>
       <c r="E284" t="str">
-        <v>ฝา1 714</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F284">
-        <v>714</v>
+        <v>700</v>
       </c>
     </row>
     <row r="285">
@@ -6829,15 +6829,15 @@
         <v>Packaging</v>
       </c>
       <c r="E285" t="str">
-        <v>ถุงขยะ 4แพคใหญ่ 1019</v>
+        <v>แก้ว 1937*3 รวม 5,811</v>
       </c>
       <c r="F285">
-        <v>1830</v>
+        <v>6659</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>11/06/2026</v>
+        <v>09/06/2026</v>
       </c>
       <c r="B286" t="str">
         <v>Jun26</v>
@@ -6846,18 +6846,18 @@
         <v>COGS</v>
       </c>
       <c r="D286" t="str">
-        <v>Guava</v>
+        <v>Packaging</v>
       </c>
       <c r="E286" t="str">
-        <v>ฝรั่ง 1 ลัง</v>
+        <v>หลอด 20 แพ็ก 671</v>
       </c>
       <c r="F286">
-        <v>700</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>12/06/2026</v>
+        <v>09/06/2026</v>
       </c>
       <c r="B287" t="str">
         <v>Jun26</v>
@@ -6866,18 +6866,18 @@
         <v>COGS</v>
       </c>
       <c r="D287" t="str">
-        <v>Coconut Water</v>
+        <v>Packaging</v>
       </c>
       <c r="E287" t="str">
-        <v>น้ำมะพร้าว50*20 1,000</v>
+        <v>ฝา1 714</v>
       </c>
       <c r="F287">
-        <v>2200</v>
+        <v>714</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>12/06/2026</v>
+        <v>09/06/2026</v>
       </c>
       <c r="B288" t="str">
         <v>Jun26</v>
@@ -6886,18 +6886,18 @@
         <v>COGS</v>
       </c>
       <c r="D288" t="str">
-        <v>Mango</v>
+        <v>Packaging</v>
       </c>
       <c r="E288" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>ถุงขยะ 4แพคใหญ่ 1019</v>
       </c>
       <c r="F288">
-        <v>1170</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>12/06/2026</v>
+        <v>11/06/2026</v>
       </c>
       <c r="B289" t="str">
         <v>Jun26</v>
@@ -6906,13 +6906,13 @@
         <v>COGS</v>
       </c>
       <c r="D289" t="str">
-        <v>Apple</v>
+        <v>Guava</v>
       </c>
       <c r="E289" t="str">
-        <v>แอปเปิ้ล 5 ลัง</v>
+        <v>ฝรั่ง 1 ลัง</v>
       </c>
       <c r="F289">
-        <v>1750</v>
+        <v>700</v>
       </c>
     </row>
     <row r="290">
@@ -6926,18 +6926,18 @@
         <v>COGS</v>
       </c>
       <c r="D290" t="str">
-        <v>Pineapple</v>
+        <v>Coconut Water</v>
       </c>
       <c r="E290" t="str">
-        <v>สับปะรด 19 ลูก</v>
+        <v>น้ำมะพร้าว50*20 1,000</v>
       </c>
       <c r="F290">
-        <v>950</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>14/06/2026</v>
+        <v>12/06/2026</v>
       </c>
       <c r="B291" t="str">
         <v>Jun26</v>
@@ -6946,18 +6946,18 @@
         <v>COGS</v>
       </c>
       <c r="D291" t="str">
-        <v>Watermelon</v>
+        <v>Mango</v>
       </c>
       <c r="E291" t="str">
-        <v>แตงโม 90 ลูก (7-6-2569: 45 ลูก, 12-6-2569: 45 ลูก)</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F291">
-        <v>7200</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>15/06/2026</v>
+        <v>12/06/2026</v>
       </c>
       <c r="B292" t="str">
         <v>Jun26</v>
@@ -6966,18 +6966,18 @@
         <v>COGS</v>
       </c>
       <c r="D292" t="str">
-        <v>Pineapple</v>
+        <v>Apple</v>
       </c>
       <c r="E292" t="str">
-        <v>สับปะรด 1 ลูก</v>
+        <v>แอปเปิ้ล 5 ลัง</v>
       </c>
       <c r="F292">
-        <v>50</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>15/06/2026</v>
+        <v>12/06/2026</v>
       </c>
       <c r="B293" t="str">
         <v>Jun26</v>
@@ -6986,18 +6986,18 @@
         <v>COGS</v>
       </c>
       <c r="D293" t="str">
-        <v>Other</v>
+        <v>Pineapple</v>
       </c>
       <c r="E293" t="str">
-        <v>Unknown</v>
+        <v>สับปะรด 19 ลูก</v>
       </c>
       <c r="F293">
-        <v>18</v>
+        <v>950</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>15/06/2026</v>
+        <v>14/06/2026</v>
       </c>
       <c r="B294" t="str">
         <v>Jun26</v>
@@ -7006,13 +7006,13 @@
         <v>COGS</v>
       </c>
       <c r="D294" t="str">
-        <v>Pineapple</v>
+        <v>Watermelon</v>
       </c>
       <c r="E294" t="str">
-        <v>สับปะรด 12 ลูก</v>
+        <v>แตงโม 90 ลูก (7-6-2569: 45 ลูก, 12-6-2569: 45 ลูก)</v>
       </c>
       <c r="F294">
-        <v>525</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="295">
@@ -7026,18 +7026,18 @@
         <v>COGS</v>
       </c>
       <c r="D295" t="str">
-        <v>Guava</v>
+        <v>Pineapple</v>
       </c>
       <c r="E295" t="str">
-        <v>ฝรั่ง 1 ตะกร้า</v>
+        <v>สับปะรด 1 ลูก</v>
       </c>
       <c r="F295">
-        <v>800</v>
+        <v>50</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>17/06/2026</v>
+        <v>15/06/2026</v>
       </c>
       <c r="B296" t="str">
         <v>Jun26</v>
@@ -7046,18 +7046,18 @@
         <v>COGS</v>
       </c>
       <c r="D296" t="str">
-        <v>Orange</v>
+        <v>Other</v>
       </c>
       <c r="E296" t="str">
-        <v>ส้ม 23x22กก 506 กก. x30 = 15,180 + ค่าขนส่ง 23x55 = 1,265 (รอบ 09/06/69)</v>
+        <v>Unknown</v>
       </c>
       <c r="F296">
-        <v>16445</v>
+        <v>18</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>18/06/2026</v>
+        <v>15/06/2026</v>
       </c>
       <c r="B297" t="str">
         <v>Jun26</v>
@@ -7066,18 +7066,18 @@
         <v>COGS</v>
       </c>
       <c r="D297" t="str">
-        <v>Mango</v>
+        <v>Pineapple</v>
       </c>
       <c r="E297" t="str">
-        <v>มะม่วง 1 ลัง</v>
+        <v>สับปะรด 12 ลูก</v>
       </c>
       <c r="F297">
-        <v>1300</v>
+        <v>525</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>18/06/2026</v>
+        <v>15/06/2026</v>
       </c>
       <c r="B298" t="str">
         <v>Jun26</v>
@@ -7086,18 +7086,18 @@
         <v>COGS</v>
       </c>
       <c r="D298" t="str">
-        <v>Coconut Water</v>
+        <v>Guava</v>
       </c>
       <c r="E298" t="str">
-        <v>เนื้อมะพร้าว 20 * 120 2400 น้ำมะพร้าว 20 *</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F298">
-        <v>3400</v>
+        <v>800</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>18/06/2026</v>
+        <v>17/06/2026</v>
       </c>
       <c r="B299" t="str">
         <v>Jun26</v>
@@ -7106,18 +7106,18 @@
         <v>COGS</v>
       </c>
       <c r="D299" t="str">
-        <v>Guava</v>
+        <v>Orange</v>
       </c>
       <c r="E299" t="str">
-        <v>ฝรั่ง 1 ตะกร้า</v>
+        <v>ส้ม 23x22กก 506 กก. x30 = 15,180 + ค่าขนส่ง 23x55 = 1,265 (รอบ 09/06/69)</v>
       </c>
       <c r="F299">
-        <v>800</v>
+        <v>16445</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>19/06/2026</v>
+        <v>18/06/2026</v>
       </c>
       <c r="B300" t="str">
         <v>Jun26</v>
@@ -7126,18 +7126,18 @@
         <v>COGS</v>
       </c>
       <c r="D300" t="str">
-        <v>Coconut Water</v>
+        <v>Mango</v>
       </c>
       <c r="E300" t="str">
-        <v>น้ำมะพร้าว40ลิตร ลิตรละ45บาท</v>
+        <v>มะม่วง 1 ลัง</v>
       </c>
       <c r="F300">
-        <v>5700</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>19/06/2026</v>
+        <v>18/06/2026</v>
       </c>
       <c r="B301" t="str">
         <v>Jun26</v>
@@ -7146,18 +7146,18 @@
         <v>COGS</v>
       </c>
       <c r="D301" t="str">
-        <v>Packaging</v>
+        <v>Coconut Water</v>
       </c>
       <c r="E301" t="str">
-        <v>น้ำยาล้างจาน 7 ถุง ผงซักฟอก 1</v>
+        <v>เนื้อมะพร้าว 20 * 120 2400 น้ำมะพร้าว 20 *</v>
       </c>
       <c r="F301">
-        <v>149</v>
+        <v>3400</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>21/06/2026</v>
+        <v>18/06/2026</v>
       </c>
       <c r="B302" t="str">
         <v>Jun26</v>
@@ -7166,18 +7166,18 @@
         <v>COGS</v>
       </c>
       <c r="D302" t="str">
-        <v>Watermelon</v>
+        <v>Guava</v>
       </c>
       <c r="E302" t="str">
-        <v>15-6-2569 แตงโม 50บาท 50 ลูก ยอด 2,500</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F302">
-        <v>6500</v>
+        <v>800</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>22/06/2026</v>
+        <v>19/06/2026</v>
       </c>
       <c r="B303" t="str">
         <v>Jun26</v>
@@ -7186,18 +7186,18 @@
         <v>COGS</v>
       </c>
       <c r="D303" t="str">
-        <v>Pineapple</v>
+        <v>Coconut Water</v>
       </c>
       <c r="E303" t="str">
-        <v>สับปะรด 15 ลูก</v>
+        <v>น้ำมะพร้าว40ลิตร ลิตรละ45บาท</v>
       </c>
       <c r="F303">
-        <v>700</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>22/06/2026</v>
+        <v>19/06/2026</v>
       </c>
       <c r="B304" t="str">
         <v>Jun26</v>
@@ -7206,18 +7206,18 @@
         <v>COGS</v>
       </c>
       <c r="D304" t="str">
-        <v>Mango</v>
+        <v>Packaging</v>
       </c>
       <c r="E304" t="str">
-        <v>มะม่วง 2 ลัง</v>
+        <v>น้ำยาล้างจาน 7 ถุง ผงซักฟอก 1</v>
       </c>
       <c r="F304">
-        <v>1632</v>
+        <v>149</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>22/06/2026</v>
+        <v>21/06/2026</v>
       </c>
       <c r="B305" t="str">
         <v>Jun26</v>
@@ -7226,13 +7226,13 @@
         <v>COGS</v>
       </c>
       <c r="D305" t="str">
-        <v>Transportation</v>
+        <v>Watermelon</v>
       </c>
       <c r="E305" t="str">
-        <v>Lalamove</v>
+        <v>15-6-2569 แตงโม 50บาท 50 ลูก ยอด 2,500</v>
       </c>
       <c r="F305">
-        <v>2000</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="306">
@@ -7246,13 +7246,13 @@
         <v>COGS</v>
       </c>
       <c r="D306" t="str">
-        <v>Apple</v>
+        <v>Pineapple</v>
       </c>
       <c r="E306" t="str">
-        <v>แอพเปิ้ล 5 ลัง</v>
+        <v>สับปะรด 15 ลูก</v>
       </c>
       <c r="F306">
-        <v>1750</v>
+        <v>700</v>
       </c>
     </row>
     <row r="307">
@@ -7266,13 +7266,13 @@
         <v>COGS</v>
       </c>
       <c r="D307" t="str">
-        <v>Pineapple</v>
+        <v>Mango</v>
       </c>
       <c r="E307" t="str">
-        <v>สับปะรด 15 ลูก</v>
+        <v>มะม่วง 2 ลัง</v>
       </c>
       <c r="F307">
-        <v>700</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="308">
@@ -7286,18 +7286,18 @@
         <v>COGS</v>
       </c>
       <c r="D308" t="str">
-        <v>Guava</v>
+        <v>Transportation</v>
       </c>
       <c r="E308" t="str">
-        <v>ฝรั่ง 1 ลัง</v>
+        <v>Lalamove</v>
       </c>
       <c r="F308">
-        <v>700</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>24/06/2026</v>
+        <v>22/06/2026</v>
       </c>
       <c r="B309" t="str">
         <v>Jun26</v>
@@ -7306,18 +7306,18 @@
         <v>COGS</v>
       </c>
       <c r="D309" t="str">
-        <v>Milk/Conden</v>
+        <v>Apple</v>
       </c>
       <c r="E309" t="str">
-        <v>นมข้นจืด 2,221</v>
+        <v>แอพเปิ้ล 5 ลัง</v>
       </c>
       <c r="F309">
-        <v>5020</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>24/06/2026</v>
+        <v>22/06/2026</v>
       </c>
       <c r="B310" t="str">
         <v>Jun26</v>
@@ -7326,18 +7326,18 @@
         <v>COGS</v>
       </c>
       <c r="D310" t="str">
-        <v>Milk/Conden</v>
+        <v>Pineapple</v>
       </c>
       <c r="E310" t="str">
-        <v>นมข้นจืด1ลัง</v>
+        <v>สับปะรด 15 ลูก</v>
       </c>
       <c r="F310">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>24/06/2026</v>
+        <v>22/06/2026</v>
       </c>
       <c r="B311" t="str">
         <v>Jun26</v>
@@ -7346,18 +7346,18 @@
         <v>COGS</v>
       </c>
       <c r="D311" t="str">
-        <v>Milk/Conden</v>
+        <v>Guava</v>
       </c>
       <c r="E311" t="str">
-        <v>นมข้นหวาน1ลัง</v>
+        <v>ฝรั่ง 1 ลัง</v>
       </c>
       <c r="F311">
-        <v>840</v>
+        <v>700</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>25/06/2026</v>
+        <v>24/06/2026</v>
       </c>
       <c r="B312" t="str">
         <v>Jun26</v>
@@ -7366,18 +7366,18 @@
         <v>COGS</v>
       </c>
       <c r="D312" t="str">
-        <v>Watermelon</v>
+        <v>Milk/Conden</v>
       </c>
       <c r="E312" t="str">
-        <v>แตงโม 22-6-2569 30 ลูก 2400 25-6-2569 40</v>
+        <v>นมข้นจืด 2,221</v>
       </c>
       <c r="F312">
-        <v>6000</v>
+        <v>5020</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>27/06/2026</v>
+        <v>24/06/2026</v>
       </c>
       <c r="B313" t="str">
         <v>Jun26</v>
@@ -7386,18 +7386,18 @@
         <v>COGS</v>
       </c>
       <c r="D313" t="str">
-        <v>Packaging</v>
+        <v>Milk/Conden</v>
       </c>
       <c r="E313" t="str">
-        <v>ถุงมือ20กล่อง 2589</v>
+        <v>นมข้นจืด1ลัง</v>
       </c>
       <c r="F313">
-        <v>4598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>27/06/2026</v>
+        <v>24/06/2026</v>
       </c>
       <c r="B314" t="str">
         <v>Jun26</v>
@@ -7406,38 +7406,38 @@
         <v>COGS</v>
       </c>
       <c r="D314" t="str">
-        <v>Packaging</v>
+        <v>Milk/Conden</v>
       </c>
       <c r="E314" t="str">
-        <v>หลอด 20 แพค</v>
+        <v>นมข้นหวาน1ลัง</v>
       </c>
       <c r="F314">
-        <v>630</v>
+        <v>840</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>27/06/2026</v>
+        <v>25/06/2026</v>
       </c>
       <c r="B315" t="str">
         <v>Jun26</v>
       </c>
       <c r="C315" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D315" t="str">
-        <v>Other</v>
+        <v>Watermelon</v>
       </c>
       <c r="E315" t="str">
-        <v>Unknown</v>
+        <v>แตงโม 22-6-2569 30 ลูก 2400 25-6-2569 40</v>
       </c>
       <c r="F315">
-        <v>317</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>29/06/2026</v>
+        <v>27/06/2026</v>
       </c>
       <c r="B316" t="str">
         <v>Jun26</v>
@@ -7449,15 +7449,15 @@
         <v>Packaging</v>
       </c>
       <c r="E316" t="str">
-        <v>ฝาแก้วภูเขาไฟ 1ลัง(954) 10แถว(987) 5แถว(561)</v>
+        <v>ถุงมือ20กล่อง 2589</v>
       </c>
       <c r="F316">
-        <v>2502</v>
+        <v>4598</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>29/06/2026</v>
+        <v>27/06/2026</v>
       </c>
       <c r="B317" t="str">
         <v>Jun26</v>
@@ -7469,30 +7469,30 @@
         <v>Packaging</v>
       </c>
       <c r="E317" t="str">
-        <v>แก้ว2ลัง 1468*2 2,936</v>
+        <v>หลอด 20 แพค</v>
       </c>
       <c r="F317">
-        <v>3498</v>
+        <v>630</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>29/06/2026</v>
+        <v>27/06/2026</v>
       </c>
       <c r="B318" t="str">
         <v>Jun26</v>
       </c>
       <c r="C318" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D318" t="str">
-        <v>Packaging</v>
+        <v>Other</v>
       </c>
       <c r="E318" t="str">
-        <v>ฝา8แถว</v>
+        <v>Unknown</v>
       </c>
       <c r="F318">
-        <v>896</v>
+        <v>317</v>
       </c>
     </row>
     <row r="319">
@@ -7503,16 +7503,16 @@
         <v>Jun26</v>
       </c>
       <c r="C319" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D319" t="str">
-        <v>Other</v>
+        <v>Packaging</v>
       </c>
       <c r="E319" t="str">
-        <v>สกัดเย็น1เครื่อง</v>
+        <v>ฝาแก้วภูเขาไฟ 1ลัง(954) 10แถว(987) 5แถว(561)</v>
       </c>
       <c r="F319">
-        <v>1402</v>
+        <v>2502</v>
       </c>
     </row>
     <row r="320">
@@ -7526,13 +7526,13 @@
         <v>COGS</v>
       </c>
       <c r="D320" t="str">
-        <v>Guava</v>
+        <v>Packaging</v>
       </c>
       <c r="E320" t="str">
-        <v>ฝรั่ง 1 ตะกร้า</v>
+        <v>แก้ว2ลัง 1468*2 2,936</v>
       </c>
       <c r="F320">
-        <v>800</v>
+        <v>3498</v>
       </c>
     </row>
     <row r="321">
@@ -7543,16 +7543,16 @@
         <v>Jun26</v>
       </c>
       <c r="C321" t="str">
-        <v>EXCLUDED</v>
+        <v>COGS</v>
       </c>
       <c r="D321" t="str">
-        <v>Pass-Through</v>
+        <v>Packaging</v>
       </c>
       <c r="E321" t="str">
-        <v>มังคุด 3 ตะกร้า (จ่ายแทน 1,932 แล้ว ฐนกร โอนคืน 29/06 13:56) - ไม่ใช่ต้นทุน SSJ [bank]</v>
+        <v>ฝา8แถว</v>
       </c>
       <c r="F321">
-        <v>0</v>
+        <v>896</v>
       </c>
     </row>
     <row r="322">
@@ -7569,10 +7569,10 @@
         <v>Other</v>
       </c>
       <c r="E322" t="str">
-        <v>Apple 2 box</v>
+        <v>สกัดเย็น1เครื่อง</v>
       </c>
       <c r="F322">
-        <v>700</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="323">
@@ -7586,13 +7586,13 @@
         <v>COGS</v>
       </c>
       <c r="D323" t="str">
-        <v>Pineapple</v>
+        <v>Guava</v>
       </c>
       <c r="E323" t="str">
-        <v>สับปะรด 15 ลูก</v>
+        <v>ฝรั่ง 1 ตะกร้า</v>
       </c>
       <c r="F323">
-        <v>675</v>
+        <v>800</v>
       </c>
     </row>
     <row r="324">
@@ -7603,21 +7603,21 @@
         <v>Jun26</v>
       </c>
       <c r="C324" t="str">
-        <v>COGS</v>
+        <v>EXCLUDED</v>
       </c>
       <c r="D324" t="str">
-        <v>Orange</v>
+        <v>Pass-Through</v>
       </c>
       <c r="E324" t="str">
-        <v>ส้ม 25x22กก 550 กก. x30 = 16,500 + ค่าขนส่ง 25x55 = 1,375 (รอบ 18/06/69)</v>
+        <v>มังคุด 3 ตะกร้า (จ่ายแทน 1,932 แล้ว ฐนกร โอนคืน 29/06 13:56) - ไม่ใช่ต้นทุน SSJ [bank]</v>
       </c>
       <c r="F324">
-        <v>17815</v>
+        <v>0</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>30/06/2026</v>
+        <v>29/06/2026</v>
       </c>
       <c r="B325" t="str">
         <v>Jun26</v>
@@ -7626,73 +7626,73 @@
         <v>OPEX</v>
       </c>
       <c r="D325" t="str">
-        <v>Salary</v>
+        <v>Other</v>
       </c>
       <c r="E325" t="str">
-        <v>ค่าแรง 4 คน คนคนละ 12000 และ รายวัน 1</v>
+        <v>Apple 2 box</v>
       </c>
       <c r="F325">
-        <v>48400</v>
+        <v>700</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>24/07/2026</v>
+        <v>29/06/2026</v>
       </c>
       <c r="B326" t="str">
-        <v>Jul26</v>
+        <v>Jun26</v>
       </c>
       <c r="C326" t="str">
         <v>COGS</v>
       </c>
       <c r="D326" t="str">
-        <v>Milk/Conden</v>
+        <v>Pineapple</v>
       </c>
       <c r="E326" t="str">
-        <v>นมข้นหวาน 1 ลัง 785 + นมข้นจืด 2 ลัง 1,342</v>
+        <v>สับปะรด 15 ลูก</v>
       </c>
       <c r="F326">
-        <v>2127</v>
+        <v>675</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>24/07/2026</v>
+        <v>29/06/2026</v>
       </c>
       <c r="B327" t="str">
-        <v>Jul26</v>
+        <v>Jun26</v>
       </c>
       <c r="C327" t="str">
         <v>COGS</v>
       </c>
       <c r="D327" t="str">
-        <v>Packaging</v>
+        <v>Orange</v>
       </c>
       <c r="E327" t="str">
-        <v>ฝา 1 ลัง 509</v>
+        <v>ส้ม 25x22กก 550 กก. x30 = 16,500 + ค่าขนส่ง 25x55 = 1,375 (รอบ 18/06/69)</v>
       </c>
       <c r="F327">
-        <v>509</v>
+        <v>17815</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>24/07/2026</v>
+        <v>30/06/2026</v>
       </c>
       <c r="B328" t="str">
-        <v>Jul26</v>
+        <v>Jun26</v>
       </c>
       <c r="C328" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D328" t="str">
-        <v>Milk/Conden</v>
+        <v>Salary</v>
       </c>
       <c r="E328" t="str">
-        <v>นมข้นหวาน 3 ลัง 2,582</v>
+        <v>ค่าแรง 4 คน คนคนละ 12000 และ รายวัน 1</v>
       </c>
       <c r="F328">
-        <v>2582</v>
+        <v>48400</v>
       </c>
     </row>
     <row r="329">
@@ -7706,13 +7706,13 @@
         <v>COGS</v>
       </c>
       <c r="D329" t="str">
-        <v>Packaging</v>
+        <v>Milk/Conden</v>
       </c>
       <c r="E329" t="str">
-        <v>ฝา 1 ลัง 502</v>
+        <v>นมข้นหวาน 1 ลัง 785 + นมข้นจืด 2 ลัง 1,342</v>
       </c>
       <c r="F329">
-        <v>502</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="330">
@@ -7726,13 +7726,13 @@
         <v>COGS</v>
       </c>
       <c r="D330" t="str">
-        <v>Milk/Conden</v>
+        <v>Packaging</v>
       </c>
       <c r="E330" t="str">
-        <v>นมข้นจืด 1 ลัง 751</v>
+        <v>ฝา 1 ลัง 509</v>
       </c>
       <c r="F330">
-        <v>751</v>
+        <v>509</v>
       </c>
     </row>
     <row r="331">
@@ -7746,13 +7746,13 @@
         <v>COGS</v>
       </c>
       <c r="D331" t="str">
-        <v>Packaging</v>
+        <v>Milk/Conden</v>
       </c>
       <c r="E331" t="str">
-        <v>ฝา 1 ลัง 474</v>
+        <v>นมข้นหวาน 3 ลัง 2,582</v>
       </c>
       <c r="F331">
-        <v>474</v>
+        <v>2582</v>
       </c>
     </row>
     <row r="332">
@@ -7766,13 +7766,13 @@
         <v>COGS</v>
       </c>
       <c r="D332" t="str">
-        <v>Stock</v>
+        <v>Packaging</v>
       </c>
       <c r="E332" t="str">
-        <v>ฝา 1 ลัง (LINE_ALBUM_Cost July_260802_4.jpg)</v>
+        <v>ฝา 1 ลัง 502</v>
       </c>
       <c r="F332">
-        <v>472</v>
+        <v>502</v>
       </c>
     </row>
     <row r="333">
@@ -7783,21 +7783,21 @@
         <v>Jul26</v>
       </c>
       <c r="C333" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D333" t="str">
-        <v>Other</v>
+        <v>Milk/Conden</v>
       </c>
       <c r="E333" t="str">
-        <v>Lalamove (LINE_ALBUM_Cost July_260802_5.jpg)</v>
+        <v>นมข้นจืด 1 ลัง 751</v>
       </c>
       <c r="F333">
-        <v>2000</v>
+        <v>751</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>26/07/2026</v>
+        <v>24/07/2026</v>
       </c>
       <c r="B334" t="str">
         <v>Jul26</v>
@@ -7806,18 +7806,18 @@
         <v>COGS</v>
       </c>
       <c r="D334" t="str">
-        <v>Apple</v>
+        <v>Packaging</v>
       </c>
       <c r="E334" t="str">
-        <v>Apple 5 box (LINE_ALBUM_Cost July_260802_6.jpg)</v>
+        <v>ฝา 1 ลัง 474</v>
       </c>
       <c r="F334">
-        <v>2000</v>
+        <v>474</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>26/07/2026</v>
+        <v>24/07/2026</v>
       </c>
       <c r="B335" t="str">
         <v>Jul26</v>
@@ -7826,38 +7826,38 @@
         <v>COGS</v>
       </c>
       <c r="D335" t="str">
-        <v>Guava</v>
+        <v>Stock</v>
       </c>
       <c r="E335" t="str">
-        <v>ฝรั่ง 2 ตะกร้า (LINE_ALBUM_Cost July_260802_7.jpg)</v>
+        <v>ฝา 1 ลัง (LINE_ALBUM_Cost July_260802_4.jpg)</v>
       </c>
       <c r="F335">
-        <v>2000</v>
+        <v>472</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>26/07/2026</v>
+        <v>24/07/2026</v>
       </c>
       <c r="B336" t="str">
         <v>Jul26</v>
       </c>
       <c r="C336" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D336" t="str">
-        <v>Mango</v>
+        <v>Other</v>
       </c>
       <c r="E336" t="str">
-        <v>มะม่วง 3 ลัง 3900 (LINE_ALBUM_Cost July_260802_8.jpg)</v>
+        <v>Lalamove (LINE_ALBUM_Cost July_260802_5.jpg)</v>
       </c>
       <c r="F336">
-        <v>3900</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>27/07/2026</v>
+        <v>26/07/2026</v>
       </c>
       <c r="B337" t="str">
         <v>Jul26</v>
@@ -7866,18 +7866,18 @@
         <v>COGS</v>
       </c>
       <c r="D337" t="str">
-        <v>Coconut</v>
+        <v>Apple</v>
       </c>
       <c r="E337" t="str">
-        <v>น้ำมะพร้าว 30ลิตร 1350 เนื้อ 50kg 5000 น้ำมะพร้าวขวด 920 ค่าส่ง 350 (LINE_ALBUM_Cost July_260802_14.jpg, audit fix - was dated 26/07 citing wrong image, missing ฿920 bottles line)</v>
+        <v>Apple 5 box (LINE_ALBUM_Cost July_260802_6.jpg)</v>
       </c>
       <c r="F337">
-        <v>7620</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>27/07/2026</v>
+        <v>26/07/2026</v>
       </c>
       <c r="B338" t="str">
         <v>Jul26</v>
@@ -7886,18 +7886,18 @@
         <v>COGS</v>
       </c>
       <c r="D338" t="str">
-        <v>Apple</v>
+        <v>Guava</v>
       </c>
       <c r="E338" t="str">
-        <v>Apple 4 box (LINE_ALBUM_Cost July_260802_10.jpg)</v>
+        <v>ฝรั่ง 2 ตะกร้า (LINE_ALBUM_Cost July_260802_7.jpg)</v>
       </c>
       <c r="F338">
-        <v>1600</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>27/07/2026</v>
+        <v>26/07/2026</v>
       </c>
       <c r="B339" t="str">
         <v>Jul26</v>
@@ -7906,13 +7906,13 @@
         <v>COGS</v>
       </c>
       <c r="D339" t="str">
-        <v>Guava</v>
+        <v>Mango</v>
       </c>
       <c r="E339" t="str">
-        <v>ฝรั่ง 2 ตะกร้า (LINE_ALBUM_Cost July_260802_11.jpg)</v>
+        <v>มะม่วง 3 ลัง 3900 (LINE_ALBUM_Cost July_260802_8.jpg)</v>
       </c>
       <c r="F339">
-        <v>2000</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="340">
@@ -7926,13 +7926,13 @@
         <v>COGS</v>
       </c>
       <c r="D340" t="str">
-        <v>Mango</v>
+        <v>Coconut</v>
       </c>
       <c r="E340" t="str">
-        <v>มะม่วง 2 ลัง (LINE_ALBUM_Cost July_260802_12.jpg)</v>
+        <v>น้ำมะพร้าว 30ลิตร 1350 เนื้อ 50kg 5000 น้ำมะพร้าวขวด 920 ค่าส่ง 350 (LINE_ALBUM_Cost July_260802_14.jpg, audit fix - was dated 26/07 citing wrong image, missing ฿920 bottles line)</v>
       </c>
       <c r="F340">
-        <v>2600</v>
+        <v>7620</v>
       </c>
     </row>
     <row r="341">
@@ -7946,38 +7946,38 @@
         <v>COGS</v>
       </c>
       <c r="D341" t="str">
-        <v>Watermelon</v>
+        <v>Apple</v>
       </c>
       <c r="E341" t="str">
-        <v>แตงโม 40 ลูก (LINE_ALBUM_Cost July_260802_13.jpg)</v>
+        <v>Apple 4 box (LINE_ALBUM_Cost July_260802_10.jpg)</v>
       </c>
       <c r="F341">
-        <v>3200</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>28/07/2026</v>
+        <v>27/07/2026</v>
       </c>
       <c r="B342" t="str">
         <v>Jul26</v>
       </c>
       <c r="C342" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D342" t="str">
-        <v>Other</v>
+        <v>Guava</v>
       </c>
       <c r="E342" t="str">
-        <v>Lalamove (LINE_ALBUM_Cost July_260802_14.jpg)</v>
+        <v>ฝรั่ง 2 ตะกร้า (LINE_ALBUM_Cost July_260802_11.jpg)</v>
       </c>
       <c r="F342">
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>28/07/2026</v>
+        <v>27/07/2026</v>
       </c>
       <c r="B343" t="str">
         <v>Jul26</v>
@@ -7986,18 +7986,18 @@
         <v>COGS</v>
       </c>
       <c r="D343" t="str">
-        <v>Guava</v>
+        <v>Mango</v>
       </c>
       <c r="E343" t="str">
-        <v>ฝรั่ง 2 ลัง (LINE_ALBUM_Cost July_260802_15.jpg)</v>
+        <v>มะม่วง 2 ลัง (LINE_ALBUM_Cost July_260802_12.jpg)</v>
       </c>
       <c r="F343">
-        <v>2000</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>28/07/2026</v>
+        <v>27/07/2026</v>
       </c>
       <c r="B344" t="str">
         <v>Jul26</v>
@@ -8006,13 +8006,13 @@
         <v>COGS</v>
       </c>
       <c r="D344" t="str">
-        <v>Apple</v>
+        <v>Watermelon</v>
       </c>
       <c r="E344" t="str">
-        <v>แอปเปิ้ล 5 ลัง (LINE_ALBUM_Cost July_260802_16.jpg, audit fix - was recorded as 4 ลัง/฿1600)</v>
+        <v>แตงโม 40 ลูก (LINE_ALBUM_Cost July_260802_13.jpg)</v>
       </c>
       <c r="F344">
-        <v>2150</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="345">
@@ -8023,16 +8023,16 @@
         <v>Jul26</v>
       </c>
       <c r="C345" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D345" t="str">
-        <v>Mango</v>
+        <v>Other</v>
       </c>
       <c r="E345" t="str">
-        <v>มะม่วง 2 ลัง (LINE_ALBUM_Cost July_260802_17.jpg)</v>
+        <v>Lalamove (LINE_ALBUM_Cost July_260802_14.jpg)</v>
       </c>
       <c r="F345">
-        <v>2600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="346">
@@ -8046,38 +8046,38 @@
         <v>COGS</v>
       </c>
       <c r="D346" t="str">
-        <v>Watermelon</v>
+        <v>Guava</v>
       </c>
       <c r="E346" t="str">
-        <v>แตงโม 40 ลูก (LINE_ALBUM_Cost July_260802_18.jpg)</v>
+        <v>ฝรั่ง 2 ลัง (LINE_ALBUM_Cost July_260802_15.jpg)</v>
       </c>
       <c r="F346">
-        <v>3200</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>29/07/2026</v>
+        <v>28/07/2026</v>
       </c>
       <c r="B347" t="str">
         <v>Jul26</v>
       </c>
       <c r="C347" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D347" t="str">
-        <v>Other</v>
+        <v>Apple</v>
       </c>
       <c r="E347" t="str">
-        <v>ค่าขนส่ง (LINE_ALBUM_Cost July_260802_19.jpg)</v>
+        <v>แอปเปิ้ล 5 ลัง (LINE_ALBUM_Cost July_260802_16.jpg, audit fix - was recorded as 4 ลัง/฿1600)</v>
       </c>
       <c r="F347">
-        <v>2000</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>29/07/2026</v>
+        <v>28/07/2026</v>
       </c>
       <c r="B348" t="str">
         <v>Jul26</v>
@@ -8086,38 +8086,38 @@
         <v>COGS</v>
       </c>
       <c r="D348" t="str">
-        <v>Orange</v>
+        <v>Mango</v>
       </c>
       <c r="E348" t="str">
-        <v>ส้ม 31x22กก 682กกx30 20,460บาท ค่าขนส่ง 31ตกx 50 1550 (LINE_ALBUM_Cost July_260802_20.jpg)</v>
+        <v>มะม่วง 2 ลัง (LINE_ALBUM_Cost July_260802_17.jpg)</v>
       </c>
       <c r="F348">
-        <v>22010</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>30/07/2026</v>
+        <v>28/07/2026</v>
       </c>
       <c r="B349" t="str">
         <v>Jul26</v>
       </c>
       <c r="C349" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D349" t="str">
-        <v>Other</v>
+        <v>Watermelon</v>
       </c>
       <c r="E349" t="str">
-        <v>ตะแกรงคว่ำจาน 6อัน ป้ายไฟ3อัน (LINE_ALBUM_Cost July_260802_21.jpg)</v>
+        <v>แตงโม 40 ลูก (LINE_ALBUM_Cost July_260802_18.jpg)</v>
       </c>
       <c r="F349">
-        <v>1790</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>30/07/2026</v>
+        <v>29/07/2026</v>
       </c>
       <c r="B350" t="str">
         <v>Jul26</v>
@@ -8129,15 +8129,15 @@
         <v>Other</v>
       </c>
       <c r="E350" t="str">
-        <v>ถุงขยะ 5*5แพค (LINE_ALBUM_Cost July_260802_22.jpg)</v>
+        <v>ค่าขนส่ง (LINE_ALBUM_Cost July_260802_19.jpg)</v>
       </c>
       <c r="F350">
-        <v>1101</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>31/07/2026</v>
+        <v>29/07/2026</v>
       </c>
       <c r="B351" t="str">
         <v>Jul26</v>
@@ -8146,38 +8146,38 @@
         <v>COGS</v>
       </c>
       <c r="D351" t="str">
-        <v>Apple</v>
+        <v>Orange</v>
       </c>
       <c r="E351" t="str">
-        <v>แอปเปิ้ล 4 ลัง (LINE_ALBUM_Cost July_260802_23.jpg)</v>
+        <v>ส้ม 31x22กก 682กกx30 20,460บาท ค่าขนส่ง 31ตกx 50 1550 (LINE_ALBUM_Cost July_260802_20.jpg)</v>
       </c>
       <c r="F351">
-        <v>1200</v>
+        <v>22010</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>31/07/2026</v>
+        <v>30/07/2026</v>
       </c>
       <c r="B352" t="str">
         <v>Jul26</v>
       </c>
       <c r="C352" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D352" t="str">
-        <v>Mango</v>
+        <v>Other</v>
       </c>
       <c r="E352" t="str">
-        <v>มะม่วง 4 ลัง (LINE_ALBUM_Cost July_260802_24.jpg)</v>
+        <v>ตะแกรงคว่ำจาน 6อัน ป้ายไฟ3อัน (LINE_ALBUM_Cost July_260802_21.jpg)</v>
       </c>
       <c r="F352">
-        <v>4680</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>31/07/2026</v>
+        <v>30/07/2026</v>
       </c>
       <c r="B353" t="str">
         <v>Jul26</v>
@@ -8189,10 +8189,10 @@
         <v>Other</v>
       </c>
       <c r="E353" t="str">
-        <v>ค่าขนส่ง (LINE_ALBUM_Cost July_260802_25.jpg)</v>
+        <v>ถุงขยะ 5*5แพค (LINE_ALBUM_Cost July_260802_22.jpg)</v>
       </c>
       <c r="F353">
-        <v>2000</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="354">
@@ -8206,13 +8206,13 @@
         <v>COGS</v>
       </c>
       <c r="D354" t="str">
-        <v>Guava</v>
+        <v>Apple</v>
       </c>
       <c r="E354" t="str">
-        <v>ฝรั่ง 3 ลัง (LINE_ALBUM_Cost July_260802_26.jpg)</v>
+        <v>แอปเปิ้ล 4 ลัง (LINE_ALBUM_Cost July_260802_23.jpg)</v>
       </c>
       <c r="F354">
-        <v>3600</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="355">
@@ -8226,13 +8226,13 @@
         <v>COGS</v>
       </c>
       <c r="D355" t="str">
-        <v>Other</v>
+        <v>Mango</v>
       </c>
       <c r="E355" t="str">
-        <v>ทุเรียน 20.6 กิโลกรัม (LINE_ALBUM_Cost July_260802_27.jpg)</v>
+        <v>มะม่วง 4 ลัง (LINE_ALBUM_Cost July_260802_24.jpg)</v>
       </c>
       <c r="F355">
-        <v>2255</v>
+        <v>4680</v>
       </c>
     </row>
     <row r="356">
@@ -8249,15 +8249,15 @@
         <v>Other</v>
       </c>
       <c r="E356" t="str">
-        <v>ตะกร้าแต่งร้าน 3 (LINE_ALBUM_Cost July_260802_28.jpg)</v>
+        <v>ค่าขนส่ง (LINE_ALBUM_Cost July_260802_25.jpg)</v>
       </c>
       <c r="F356">
-        <v>558</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>02/07/2026</v>
+        <v>31/07/2026</v>
       </c>
       <c r="B357" t="str">
         <v>Jul26</v>
@@ -8266,18 +8266,18 @@
         <v>COGS</v>
       </c>
       <c r="D357" t="str">
-        <v>Orange</v>
+        <v>Guava</v>
       </c>
       <c r="E357" t="str">
-        <v>ค่าส่งส้มเดือน 6 (LINE_ALBUM_Cost July_260802_29.jpg)</v>
+        <v>ฝรั่ง 3 ลัง (LINE_ALBUM_Cost July_260802_26.jpg)</v>
       </c>
       <c r="F357">
-        <v>1598</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>03/07/2026</v>
+        <v>31/07/2026</v>
       </c>
       <c r="B358" t="str">
         <v>Jul26</v>
@@ -8286,38 +8286,38 @@
         <v>COGS</v>
       </c>
       <c r="D358" t="str">
-        <v>Pineapple</v>
+        <v>Other</v>
       </c>
       <c r="E358" t="str">
-        <v>1 สับปะรด 15 ลูก 750 2 สับปะรด 15 ลูก 729 (LINE_ALBUM_Cost July_260802_30.jpg)</v>
+        <v>ทุเรียน 20.6 กิโลกรัม (LINE_ALBUM_Cost July_260802_27.jpg)</v>
       </c>
       <c r="F358">
-        <v>1479</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>03/07/2026</v>
+        <v>31/07/2026</v>
       </c>
       <c r="B359" t="str">
         <v>Jul26</v>
       </c>
       <c r="C359" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D359" t="str">
-        <v>Apple</v>
+        <v>Other</v>
       </c>
       <c r="E359" t="str">
-        <v>แอปเปิ้ล 3 ลัง (LINE_ALBUM_Cost July_260802_31.jpg)</v>
+        <v>ตะกร้าแต่งร้าน 3 (LINE_ALBUM_Cost July_260802_28.jpg)</v>
       </c>
       <c r="F359">
-        <v>1140</v>
+        <v>558</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>03/07/2026</v>
+        <v>02/07/2026</v>
       </c>
       <c r="B360" t="str">
         <v>Jul26</v>
@@ -8326,13 +8326,13 @@
         <v>COGS</v>
       </c>
       <c r="D360" t="str">
-        <v>Mango</v>
+        <v>Orange</v>
       </c>
       <c r="E360" t="str">
-        <v>มะม่วง 1 ลัง (LINE_ALBUM_Cost July_260802_32.jpg)</v>
+        <v>ค่าส่งส้มเดือน 6 (LINE_ALBUM_Cost July_260802_29.jpg)</v>
       </c>
       <c r="F360">
-        <v>1040</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="361">
@@ -8346,13 +8346,13 @@
         <v>COGS</v>
       </c>
       <c r="D361" t="str">
-        <v>Guava</v>
+        <v>Pineapple</v>
       </c>
       <c r="E361" t="str">
-        <v>ฝรั่ง 1 ลัง (LINE_ALBUM_Cost July_260802_33.jpg)</v>
+        <v>1 สับปะรด 15 ลูก 750 2 สับปะรด 15 ลูก 729 (LINE_ALBUM_Cost July_260802_30.jpg)</v>
       </c>
       <c r="F361">
-        <v>900</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="362">
@@ -8363,41 +8363,41 @@
         <v>Jul26</v>
       </c>
       <c r="C362" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D362" t="str">
-        <v>Other</v>
+        <v>Apple</v>
       </c>
       <c r="E362" t="str">
-        <v>ค่าส่ง (LINE_ALBUM_Cost July_260802_34.jpg)</v>
+        <v>แอปเปิ้ล 3 ลัง (LINE_ALBUM_Cost July_260802_31.jpg)</v>
       </c>
       <c r="F362">
-        <v>2000</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>06/07/2026</v>
+        <v>03/07/2026</v>
       </c>
       <c r="B363" t="str">
         <v>Jul26</v>
       </c>
       <c r="C363" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D363" t="str">
-        <v>Rental</v>
+        <v>Mango</v>
       </c>
       <c r="E363" t="str">
-        <v>ค่าเช่า stock เดือน june (1/3 split B1) (LINE_ALBUM_Cost July_260802_35.jpg)</v>
+        <v>มะม่วง 1 ลัง (LINE_ALBUM_Cost July_260802_32.jpg)</v>
       </c>
       <c r="F363">
-        <v>4000</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>06/07/2026</v>
+        <v>03/07/2026</v>
       </c>
       <c r="B364" t="str">
         <v>Jul26</v>
@@ -8406,33 +8406,33 @@
         <v>COGS</v>
       </c>
       <c r="D364" t="str">
-        <v>Pineapple</v>
+        <v>Guava</v>
       </c>
       <c r="E364" t="str">
-        <v>สับปะรด 20 ลูก (LINE_ALBUM_Cost July_260802_36.jpg)</v>
+        <v>ฝรั่ง 1 ลัง (LINE_ALBUM_Cost July_260802_33.jpg)</v>
       </c>
       <c r="F364">
-        <v>783</v>
+        <v>900</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>06/07/2026</v>
+        <v>03/07/2026</v>
       </c>
       <c r="B365" t="str">
         <v>Jul26</v>
       </c>
       <c r="C365" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D365" t="str">
-        <v>Mango</v>
+        <v>Other</v>
       </c>
       <c r="E365" t="str">
-        <v>มะม่วง 2 ลัง (LINE_ALBUM_Cost July_260802_37.jpg)</v>
+        <v>ค่าส่ง (LINE_ALBUM_Cost July_260802_34.jpg)</v>
       </c>
       <c r="F365">
-        <v>2340</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="366">
@@ -8443,16 +8443,16 @@
         <v>Jul26</v>
       </c>
       <c r="C366" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D366" t="str">
-        <v>Guava</v>
+        <v>Rental</v>
       </c>
       <c r="E366" t="str">
-        <v>ฝรั่ง 1 ตะกร้า (LINE_ALBUM_Cost July_260802_38.jpg)</v>
+        <v>ค่าเช่า stock เดือน june (1/3 split B1) (LINE_ALBUM_Cost July_260802_35.jpg)</v>
       </c>
       <c r="F366">
-        <v>900</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="367">
@@ -8466,18 +8466,18 @@
         <v>COGS</v>
       </c>
       <c r="D367" t="str">
-        <v>Apple</v>
+        <v>Pineapple</v>
       </c>
       <c r="E367" t="str">
-        <v>แอปเปิ้ล 3 ลัง (LINE_ALBUM_Cost July_260802_39.jpg)</v>
+        <v>สับปะรด 20 ลูก (LINE_ALBUM_Cost July_260802_36.jpg)</v>
       </c>
       <c r="F367">
-        <v>900</v>
+        <v>783</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>08/07/2026</v>
+        <v>06/07/2026</v>
       </c>
       <c r="B368" t="str">
         <v>Jul26</v>
@@ -8486,38 +8486,38 @@
         <v>COGS</v>
       </c>
       <c r="D368" t="str">
-        <v>Watermelon</v>
+        <v>Mango</v>
       </c>
       <c r="E368" t="str">
-        <v>แตงโม 3-7-69 36 ลูก ลูกละ 80 บาท 6-7-69 50 ลูก ลูกละ 80 บาท (LINE_ALBUM_Cost July_260802_40.jpg)</v>
+        <v>มะม่วง 2 ลัง (LINE_ALBUM_Cost July_260802_37.jpg)</v>
       </c>
       <c r="F368">
-        <v>6880</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>08/07/2026</v>
+        <v>06/07/2026</v>
       </c>
       <c r="B369" t="str">
         <v>Jul26</v>
       </c>
       <c r="C369" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D369" t="str">
-        <v>Other</v>
+        <v>Guava</v>
       </c>
       <c r="E369" t="str">
-        <v>เต้น (tent) (LINE_ALBUM_Cost July_260802_41.jpg)</v>
+        <v>ฝรั่ง 1 ตะกร้า (LINE_ALBUM_Cost July_260802_38.jpg)</v>
       </c>
       <c r="F369">
-        <v>1342</v>
+        <v>900</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>09/07/2026</v>
+        <v>06/07/2026</v>
       </c>
       <c r="B370" t="str">
         <v>Jul26</v>
@@ -8526,18 +8526,18 @@
         <v>COGS</v>
       </c>
       <c r="D370" t="str">
-        <v>Coconut</v>
+        <v>Apple</v>
       </c>
       <c r="E370" t="str">
-        <v>น้ำ 25ลิตร ลิตรละ45บาท เนื้อคว้าน 50kg.กิโลละ 100บาท ค่าส่ง350บาท (LINE_ALBUM_Cost July_260802_42.jpg)</v>
+        <v>แอปเปิ้ล 3 ลัง (LINE_ALBUM_Cost July_260802_39.jpg)</v>
       </c>
       <c r="F370">
-        <v>6470</v>
+        <v>900</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>10/07/2026</v>
+        <v>08/07/2026</v>
       </c>
       <c r="B371" t="str">
         <v>Jul26</v>
@@ -8546,38 +8546,38 @@
         <v>COGS</v>
       </c>
       <c r="D371" t="str">
-        <v>Guava</v>
+        <v>Watermelon</v>
       </c>
       <c r="E371" t="str">
-        <v>ฝรั่ง 1 ลัง (LINE_ALBUM_Cost July_260802_43.jpg)</v>
+        <v>แตงโม 3-7-69 36 ลูก ลูกละ 80 บาท 6-7-69 50 ลูก ลูกละ 80 บาท (LINE_ALBUM_Cost July_260802_40.jpg)</v>
       </c>
       <c r="F371">
-        <v>900</v>
+        <v>6880</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>10/07/2026</v>
+        <v>08/07/2026</v>
       </c>
       <c r="B372" t="str">
         <v>Jul26</v>
       </c>
       <c r="C372" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D372" t="str">
-        <v>Apple</v>
+        <v>Other</v>
       </c>
       <c r="E372" t="str">
-        <v>Apple 5 box (LINE_ALBUM_Cost July_260802_44.jpg)</v>
+        <v>เต้น (tent) (LINE_ALBUM_Cost July_260802_41.jpg)</v>
       </c>
       <c r="F372">
-        <v>1500</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>11/07/2026</v>
+        <v>09/07/2026</v>
       </c>
       <c r="B373" t="str">
         <v>Jul26</v>
@@ -8586,18 +8586,18 @@
         <v>COGS</v>
       </c>
       <c r="D373" t="str">
-        <v>Guava</v>
+        <v>Coconut</v>
       </c>
       <c r="E373" t="str">
-        <v>ฝรั่ง 1 ตะกร้า (LINE_ALBUM_Cost July_260802_45.jpg)</v>
+        <v>น้ำ 25ลิตร ลิตรละ45บาท เนื้อคว้าน 50kg.กิโลละ 100บาท ค่าส่ง350บาท (LINE_ALBUM_Cost July_260802_42.jpg)</v>
       </c>
       <c r="F373">
-        <v>900</v>
+        <v>6470</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>11/07/2026</v>
+        <v>10/07/2026</v>
       </c>
       <c r="B374" t="str">
         <v>Jul26</v>
@@ -8606,18 +8606,18 @@
         <v>COGS</v>
       </c>
       <c r="D374" t="str">
-        <v>Mango</v>
+        <v>Guava</v>
       </c>
       <c r="E374" t="str">
-        <v>มะม่วง 3 ลัง (LINE_ALBUM_Cost July_260802_46.jpg)</v>
+        <v>ฝรั่ง 1 ลัง (LINE_ALBUM_Cost July_260802_43.jpg)</v>
       </c>
       <c r="F374">
-        <v>4300</v>
+        <v>900</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>11/07/2026</v>
+        <v>10/07/2026</v>
       </c>
       <c r="B375" t="str">
         <v>Jul26</v>
@@ -8629,35 +8629,35 @@
         <v>Apple</v>
       </c>
       <c r="E375" t="str">
-        <v>แอปเปิ้ล 3 ลัง (LINE_ALBUM_Cost July_260802_47.jpg)</v>
+        <v>Apple 5 box (LINE_ALBUM_Cost July_260802_44.jpg)</v>
       </c>
       <c r="F375">
-        <v>900</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>13/07/2026</v>
+        <v>11/07/2026</v>
       </c>
       <c r="B376" t="str">
         <v>Jul26</v>
       </c>
       <c r="C376" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D376" t="str">
-        <v>Other</v>
+        <v>Guava</v>
       </c>
       <c r="E376" t="str">
-        <v>ค่าขนส่ง (LINE_ALBUM_Cost July_260802_48.jpg)</v>
+        <v>ฝรั่ง 1 ตะกร้า (LINE_ALBUM_Cost July_260802_45.jpg)</v>
       </c>
       <c r="F376">
-        <v>344</v>
+        <v>900</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>13/07/2026</v>
+        <v>11/07/2026</v>
       </c>
       <c r="B377" t="str">
         <v>Jul26</v>
@@ -8666,18 +8666,18 @@
         <v>COGS</v>
       </c>
       <c r="D377" t="str">
-        <v>Packaging</v>
+        <v>Mango</v>
       </c>
       <c r="E377" t="str">
-        <v>ทิชชู4(636) หลอด20 (671) ถุงเล็ก3(605) ถุงใหญ่2(943) (LINE_ALBUM_Cost July_260802_49.jpg)</v>
+        <v>มะม่วง 3 ลัง (LINE_ALBUM_Cost July_260802_46.jpg)</v>
       </c>
       <c r="F377">
-        <v>2855</v>
+        <v>4300</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>13/07/2026</v>
+        <v>11/07/2026</v>
       </c>
       <c r="B378" t="str">
         <v>Jul26</v>
@@ -8686,38 +8686,38 @@
         <v>COGS</v>
       </c>
       <c r="D378" t="str">
-        <v>Packaging</v>
+        <v>Apple</v>
       </c>
       <c r="E378" t="str">
-        <v>แก้ว98 4ลัง 7656-635 7,021 ฝา635 (LINE_ALBUM_Cost July_260802_50.jpg)</v>
+        <v>แอปเปิ้ล 3 ลัง (LINE_ALBUM_Cost July_260802_47.jpg)</v>
       </c>
       <c r="F378">
-        <v>7656</v>
+        <v>900</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>14/07/2026</v>
+        <v>13/07/2026</v>
       </c>
       <c r="B379" t="str">
         <v>Jul26</v>
       </c>
       <c r="C379" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D379" t="str">
-        <v>Pineapple</v>
+        <v>Other</v>
       </c>
       <c r="E379" t="str">
-        <v>11/7/69 10 ลูก 620 14/7/69 25 ลูก 1269 (LINE_ALBUM_Cost July_260802_51.jpg)</v>
+        <v>ค่าขนส่ง (LINE_ALBUM_Cost July_260802_48.jpg)</v>
       </c>
       <c r="F379">
-        <v>1889</v>
+        <v>344</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>14/07/2026</v>
+        <v>13/07/2026</v>
       </c>
       <c r="B380" t="str">
         <v>Jul26</v>
@@ -8726,18 +8726,18 @@
         <v>COGS</v>
       </c>
       <c r="D380" t="str">
-        <v>Apple</v>
+        <v>Packaging</v>
       </c>
       <c r="E380" t="str">
-        <v>Apple 3 ลัง (LINE_ALBUM_Cost July_260802_52.jpg)</v>
+        <v>ทิชชู4(636) หลอด20 (671) ถุงเล็ก3(605) ถุงใหญ่2(943) (LINE_ALBUM_Cost July_260802_49.jpg)</v>
       </c>
       <c r="F380">
-        <v>1200</v>
+        <v>2855</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>15/07/2026</v>
+        <v>13/07/2026</v>
       </c>
       <c r="B381" t="str">
         <v>Jul26</v>
@@ -8746,18 +8746,18 @@
         <v>COGS</v>
       </c>
       <c r="D381" t="str">
-        <v>Guava</v>
+        <v>Packaging</v>
       </c>
       <c r="E381" t="str">
-        <v>ฝรั่ง 2 ตะกร้า ตะกร้าละ 20 โล (LINE_ALBUM_Cost July_260802_53.jpg)</v>
+        <v>แก้ว98 4ลัง 7656-635 7,021 ฝา635 (LINE_ALBUM_Cost July_260802_50.jpg)</v>
       </c>
       <c r="F381">
-        <v>2000</v>
+        <v>7656</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>16/07/2026</v>
+        <v>14/07/2026</v>
       </c>
       <c r="B382" t="str">
         <v>Jul26</v>
@@ -8766,18 +8766,18 @@
         <v>COGS</v>
       </c>
       <c r="D382" t="str">
-        <v>Orange</v>
+        <v>Pineapple</v>
       </c>
       <c r="E382" t="str">
-        <v>รอบ 01/07/69 ส้ม 28x22กก 616กกx30 18,480บาท ค่าขนส่ง 28ตกx 55 1540 (LINE_ALBUM_Cost July_260802_54.jpg)</v>
+        <v>11/7/69 10 ลูก 620 14/7/69 25 ลูก 1269 (LINE_ALBUM_Cost July_260802_51.jpg)</v>
       </c>
       <c r="F382">
-        <v>20020</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>17/07/2026</v>
+        <v>14/07/2026</v>
       </c>
       <c r="B383" t="str">
         <v>Jul26</v>
@@ -8786,18 +8786,18 @@
         <v>COGS</v>
       </c>
       <c r="D383" t="str">
-        <v>Orange</v>
+        <v>Apple</v>
       </c>
       <c r="E383" t="str">
-        <v>ส้ม 125 โล 3450 ค่าส่ง 300 (LINE_ALBUM_Cost July_260802_55.jpg)</v>
+        <v>Apple 3 ลัง (LINE_ALBUM_Cost July_260802_52.jpg)</v>
       </c>
       <c r="F383">
-        <v>3750</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>17/07/2026</v>
+        <v>15/07/2026</v>
       </c>
       <c r="B384" t="str">
         <v>Jul26</v>
@@ -8806,18 +8806,18 @@
         <v>COGS</v>
       </c>
       <c r="D384" t="str">
-        <v>Pineapple</v>
+        <v>Guava</v>
       </c>
       <c r="E384" t="str">
-        <v>สับปะรด 25 ลูก (LINE_ALBUM_Cost July_260802_56.jpg)</v>
+        <v>ฝรั่ง 2 ตะกร้า ตะกร้าละ 20 โล (LINE_ALBUM_Cost July_260802_53.jpg)</v>
       </c>
       <c r="F384">
-        <v>1539</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>17/07/2026</v>
+        <v>16/07/2026</v>
       </c>
       <c r="B385" t="str">
         <v>Jul26</v>
@@ -8826,13 +8826,13 @@
         <v>COGS</v>
       </c>
       <c r="D385" t="str">
-        <v>Watermelon</v>
+        <v>Orange</v>
       </c>
       <c r="E385" t="str">
-        <v>แตงโม 10-7-69 50 ลูก 4000 11-7-69 40 ลูก 3200 (LINE_ALBUM_Cost July_260802_57.jpg)</v>
+        <v>รอบ 01/07/69 ส้ม 28x22กก 616กกx30 18,480บาท ค่าขนส่ง 28ตกx 55 1540 (LINE_ALBUM_Cost July_260802_54.jpg)</v>
       </c>
       <c r="F385">
-        <v>7200</v>
+        <v>20020</v>
       </c>
     </row>
     <row r="386">
@@ -8846,13 +8846,13 @@
         <v>COGS</v>
       </c>
       <c r="D386" t="str">
-        <v>Other</v>
+        <v>Orange</v>
       </c>
       <c r="E386" t="str">
-        <v>ทุเรียน 50 โล โลละ 85 รวม 4250 มัดจำตะกร้า 200 (LINE_ALBUM_Cost July_260802_58.jpg)</v>
+        <v>ส้ม 125 โล 3450 ค่าส่ง 300 (LINE_ALBUM_Cost July_260802_55.jpg)</v>
       </c>
       <c r="F386">
-        <v>4450</v>
+        <v>3750</v>
       </c>
     </row>
     <row r="387">
@@ -8866,13 +8866,13 @@
         <v>COGS</v>
       </c>
       <c r="D387" t="str">
-        <v>Watermelon</v>
+        <v>Pineapple</v>
       </c>
       <c r="E387" t="str">
-        <v>แตงโม 14-7-69 50 ลูก 4000 (LINE_ALBUM_Cost July_260802_59.jpg)</v>
+        <v>สับปะรด 25 ลูก (LINE_ALBUM_Cost July_260802_56.jpg)</v>
       </c>
       <c r="F387">
-        <v>4000</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="388">
@@ -8886,13 +8886,13 @@
         <v>COGS</v>
       </c>
       <c r="D388" t="str">
-        <v>Mango</v>
+        <v>Watermelon</v>
       </c>
       <c r="E388" t="str">
-        <v>มะม่วง 52 โล(2 ตะกร้า) โลละ 50 (LINE_ALBUM_Cost July_260802_60.jpg)</v>
+        <v>แตงโม 10-7-69 50 ลูก 4000 11-7-69 40 ลูก 3200 (LINE_ALBUM_Cost July_260802_57.jpg)</v>
       </c>
       <c r="F388">
-        <v>2600</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="389">
@@ -8906,13 +8906,13 @@
         <v>COGS</v>
       </c>
       <c r="D389" t="str">
-        <v>Guava</v>
+        <v>Other</v>
       </c>
       <c r="E389" t="str">
-        <v>ฝรั่ง 2 ตะกร้า (ตะกร้าละ 20 โล) (LINE_ALBUM_Cost July_260802_61.jpg)</v>
+        <v>ทุเรียน 50 โล โลละ 85 รวม 4250 มัดจำตะกร้า 200 (LINE_ALBUM_Cost July_260802_58.jpg)</v>
       </c>
       <c r="F389">
-        <v>2000</v>
+        <v>4450</v>
       </c>
     </row>
     <row r="390">
@@ -8926,13 +8926,13 @@
         <v>COGS</v>
       </c>
       <c r="D390" t="str">
-        <v>Apple</v>
+        <v>Watermelon</v>
       </c>
       <c r="E390" t="str">
-        <v>แอปเปิ้ล 5 ลัง (LINE_ALBUM_Cost July_260802_62.jpg)</v>
+        <v>แตงโม 14-7-69 50 ลูก 4000 (LINE_ALBUM_Cost July_260802_59.jpg)</v>
       </c>
       <c r="F390">
-        <v>2000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="391">
@@ -8946,18 +8946,18 @@
         <v>COGS</v>
       </c>
       <c r="D391" t="str">
-        <v>Coconut</v>
+        <v>Mango</v>
       </c>
       <c r="E391" t="str">
-        <v>น้ำ 30ลิตร ลิตรละ45บาท เนื้อมะพร้าว 50kg.กิโลละ 100บาท ค่าส่ง350 (LINE_ALBUM_Cost July_260802_63.jpg)</v>
+        <v>มะม่วง 52 โล(2 ตะกร้า) โลละ 50 (LINE_ALBUM_Cost July_260802_60.jpg)</v>
       </c>
       <c r="F391">
-        <v>6700</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>20/07/2026</v>
+        <v>17/07/2026</v>
       </c>
       <c r="B392" t="str">
         <v>Jul26</v>
@@ -8969,7 +8969,7 @@
         <v>Guava</v>
       </c>
       <c r="E392" t="str">
-        <v>ฝรั่ง 2 ตะกร้า (LINE_ALBUM_Cost July_260802_64.jpg)</v>
+        <v>ฝรั่ง 2 ตะกร้า (ตะกร้าละ 20 โล) (LINE_ALBUM_Cost July_260802_61.jpg)</v>
       </c>
       <c r="F392">
         <v>2000</v>
@@ -8977,7 +8977,7 @@
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>20/07/2026</v>
+        <v>17/07/2026</v>
       </c>
       <c r="B393" t="str">
         <v>Jul26</v>
@@ -8986,18 +8986,18 @@
         <v>COGS</v>
       </c>
       <c r="D393" t="str">
-        <v>Pineapple</v>
+        <v>Apple</v>
       </c>
       <c r="E393" t="str">
-        <v>สับปะรด 20 ลูก (LINE_ALBUM_Cost July_260802_65.jpg)</v>
+        <v>แอปเปิ้ล 5 ลัง (LINE_ALBUM_Cost July_260802_62.jpg)</v>
       </c>
       <c r="F393">
-        <v>1296</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>20/07/2026</v>
+        <v>17/07/2026</v>
       </c>
       <c r="B394" t="str">
         <v>Jul26</v>
@@ -9006,13 +9006,13 @@
         <v>COGS</v>
       </c>
       <c r="D394" t="str">
-        <v>Mango</v>
+        <v>Coconut</v>
       </c>
       <c r="E394" t="str">
-        <v>มะม่วง 2 ลัง (LINE_ALBUM_Cost July_260802_66.jpg)</v>
+        <v>น้ำ 30ลิตร ลิตรละ45บาท เนื้อมะพร้าว 50kg.กิโลละ 100บาท ค่าส่ง350 (LINE_ALBUM_Cost July_260802_63.jpg)</v>
       </c>
       <c r="F394">
-        <v>2600</v>
+        <v>6700</v>
       </c>
     </row>
     <row r="395">
@@ -9026,38 +9026,38 @@
         <v>COGS</v>
       </c>
       <c r="D395" t="str">
-        <v>Watermelon</v>
+        <v>Guava</v>
       </c>
       <c r="E395" t="str">
-        <v>แตงโม 17-7-2569 เบอร์ 80บาท 50 ลูก (LINE_ALBUM_Cost July_260802_67.jpg)</v>
+        <v>ฝรั่ง 2 ตะกร้า (LINE_ALBUM_Cost July_260802_64.jpg)</v>
       </c>
       <c r="F395">
-        <v>4000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>21/07/2026</v>
+        <v>20/07/2026</v>
       </c>
       <c r="B396" t="str">
         <v>Jul26</v>
       </c>
       <c r="C396" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D396" t="str">
-        <v>Other</v>
+        <v>Pineapple</v>
       </c>
       <c r="E396" t="str">
-        <v xml:space="preserve"> (LINE_ALBUM_Cost July_260802_68.jpg)</v>
+        <v>สับปะรด 20 ลูก (LINE_ALBUM_Cost July_260802_65.jpg)</v>
       </c>
       <c r="F396">
-        <v>2000</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>22/07/2026</v>
+        <v>20/07/2026</v>
       </c>
       <c r="B397" t="str">
         <v>Jul26</v>
@@ -9066,18 +9066,18 @@
         <v>COGS</v>
       </c>
       <c r="D397" t="str">
-        <v>Orange</v>
+        <v>Mango</v>
       </c>
       <c r="E397" t="str">
-        <v>ส้ม 25x22กก รวม 550กกx30 บ รวม 16500บาท ค่าขนส่ง 25ตกx 50 บ 1250 (LINE_ALBUM_Cost July_260802_69.jpg)</v>
+        <v>มะม่วง 2 ลัง (LINE_ALBUM_Cost July_260802_66.jpg)</v>
       </c>
       <c r="F397">
-        <v>17750</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>22/07/2026</v>
+        <v>20/07/2026</v>
       </c>
       <c r="B398" t="str">
         <v>Jul26</v>
@@ -9086,33 +9086,33 @@
         <v>COGS</v>
       </c>
       <c r="D398" t="str">
-        <v>Apple</v>
+        <v>Watermelon</v>
       </c>
       <c r="E398" t="str">
-        <v>แอปเปิ้ล 4 ลัง (LINE_ALBUM_Cost July_260802_70.jpg)</v>
+        <v>แตงโม 17-7-2569 เบอร์ 80บาท 50 ลูก (LINE_ALBUM_Cost July_260802_67.jpg)</v>
       </c>
       <c r="F398">
-        <v>1600</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>22/07/2026</v>
+        <v>21/07/2026</v>
       </c>
       <c r="B399" t="str">
         <v>Jul26</v>
       </c>
       <c r="C399" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D399" t="str">
-        <v>Mango</v>
+        <v>Other</v>
       </c>
       <c r="E399" t="str">
-        <v>มะม่วง 78 กิโล 3 ลัง (LINE_ALBUM_Cost July_260802_71.jpg)</v>
+        <v xml:space="preserve"> (LINE_ALBUM_Cost July_260802_68.jpg)</v>
       </c>
       <c r="F399">
-        <v>3900</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="400">
@@ -9123,16 +9123,16 @@
         <v>Jul26</v>
       </c>
       <c r="C400" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D400" t="str">
-        <v>Other</v>
+        <v>Orange</v>
       </c>
       <c r="E400" t="str">
-        <v>OPEX Avocado milk (LINE_ALBUM_Cost July_260802_74.jpg)</v>
+        <v>ส้ม 25x22กก รวม 550กกx30 บ รวม 16500บาท ค่าขนส่ง 25ตกx 50 บ 1250 (LINE_ALBUM_Cost July_260802_69.jpg)</v>
       </c>
       <c r="F400">
-        <v>440.75</v>
+        <v>17750</v>
       </c>
     </row>
     <row r="401">
@@ -9143,16 +9143,16 @@
         <v>Jul26</v>
       </c>
       <c r="C401" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D401" t="str">
-        <v>Other</v>
+        <v>Apple</v>
       </c>
       <c r="E401" t="str">
-        <v>Opex knife (LINE_ALBUM_Cost July_260802_75.jpg)</v>
+        <v>แอปเปิ้ล 4 ลัง (LINE_ALBUM_Cost July_260802_70.jpg)</v>
       </c>
       <c r="F401">
-        <v>199</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="402">
@@ -9163,16 +9163,16 @@
         <v>Jul26</v>
       </c>
       <c r="C402" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D402" t="str">
-        <v>Other</v>
+        <v>Mango</v>
       </c>
       <c r="E402" t="str">
-        <v>Opex equipment (LINE_ALBUM_Cost July_260802_76.jpg)</v>
+        <v>มะม่วง 78 กิโล 3 ลัง (LINE_ALBUM_Cost July_260802_71.jpg)</v>
       </c>
       <c r="F402">
-        <v>221</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="403">
@@ -9183,16 +9183,16 @@
         <v>Jul26</v>
       </c>
       <c r="C403" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D403" t="str">
-        <v>Milk/Conden</v>
+        <v>Other</v>
       </c>
       <c r="E403" t="str">
-        <v>นมข้นจืด Falcon (LINE_ALBUM_Cost July_260802_77.jpg)</v>
+        <v>OPEX Avocado milk (LINE_ALBUM_Cost July_260802_74.jpg)</v>
       </c>
       <c r="F403">
-        <v>716</v>
+        <v>440.75</v>
       </c>
     </row>
     <row r="404">
@@ -9209,10 +9209,10 @@
         <v>Other</v>
       </c>
       <c r="E404" t="str">
-        <v>Opex B1 police fee 1000 / person (LINE_ALBUM_Cost July_260802_78.jpg)</v>
+        <v>Opex knife (LINE_ALBUM_Cost July_260802_75.jpg)</v>
       </c>
       <c r="F404">
-        <v>2000</v>
+        <v>199</v>
       </c>
     </row>
     <row r="405">
@@ -9229,10 +9229,10 @@
         <v>Other</v>
       </c>
       <c r="E405" t="str">
-        <v>Opex equipments (LINE_ALBUM_Cost July_260802_79.jpg)</v>
+        <v>Opex equipment (LINE_ALBUM_Cost July_260802_76.jpg)</v>
       </c>
       <c r="F405">
-        <v>506</v>
+        <v>221</v>
       </c>
     </row>
     <row r="406">
@@ -9243,196 +9243,196 @@
         <v>Jul26</v>
       </c>
       <c r="C406" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D406" t="str">
-        <v>Other</v>
+        <v>Milk/Conden</v>
       </c>
       <c r="E406" t="str">
-        <v>Opex other (LINE_ALBUM_Cost July_260802_80.jpg)</v>
+        <v>นมข้นจืด Falcon (LINE_ALBUM_Cost July_260802_77.jpg)</v>
       </c>
       <c r="F406">
-        <v>1918</v>
+        <v>716</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>23/07/2026</v>
+        <v>22/07/2026</v>
       </c>
       <c r="B407" t="str">
         <v>Jul26</v>
       </c>
       <c r="C407" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D407" t="str">
-        <v>Watermelon</v>
+        <v>Other</v>
       </c>
       <c r="E407" t="str">
-        <v>20-7-2569 ราคา 80 - 45ลูก 22-7-2569 ราคา 80 - 30 ลูก 23-7-2569 ราคา 80 - 30 ลูก (LINE_ALBUM_Cost July_260802_81.jpg)</v>
+        <v>Opex B1 police fee 1000 / person (LINE_ALBUM_Cost July_260802_78.jpg)</v>
       </c>
       <c r="F407">
-        <v>8400</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>23/07/2026</v>
+        <v>22/07/2026</v>
       </c>
       <c r="B408" t="str">
         <v>Jul26</v>
       </c>
       <c r="C408" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D408" t="str">
-        <v>Guava</v>
+        <v>Other</v>
       </c>
       <c r="E408" t="str">
-        <v>ฝรั่ง 2 ลัง ลังละ 20 กิโล กิโลละ 50 บาท รวม 2000 บาท (LINE_ALBUM_Cost July_260802_82.jpg)</v>
+        <v>Opex equipments (LINE_ALBUM_Cost July_260802_79.jpg)</v>
       </c>
       <c r="F408">
-        <v>2000</v>
+        <v>506</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>23/07/2026</v>
+        <v>22/07/2026</v>
       </c>
       <c r="B409" t="str">
         <v>Jul26</v>
       </c>
       <c r="C409" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D409" t="str">
-        <v>Pineapple</v>
+        <v>Other</v>
       </c>
       <c r="E409" t="str">
-        <v>สับปะรด 41 กิโล *27 บาท รวม 1107 บาท (LINE_ALBUM_Cost July_260802_83.jpg)</v>
+        <v>Opex other (LINE_ALBUM_Cost July_260802_80.jpg)</v>
       </c>
       <c r="F409">
-        <v>1107</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>31/07/2026</v>
+        <v>23/07/2026</v>
       </c>
       <c r="B410" t="str">
         <v>Jul26</v>
       </c>
       <c r="C410" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D410" t="str">
-        <v>Rental</v>
+        <v>Watermelon</v>
       </c>
       <c r="E410" t="str">
-        <v>ค่าเช่าร้าน B1 ก.ค. (จ่ายเงินสดจากหน้าร้านก่อนนำเข้าบัญชี - ไม่มีสลิป ยืนยันโดยเจ้าของ 28/08)</v>
+        <v>20-7-2569 ราคา 80 - 45ลูก 22-7-2569 ราคา 80 - 30 ลูก 23-7-2569 ราคา 80 - 30 ลูก (LINE_ALBUM_Cost July_260802_81.jpg)</v>
       </c>
       <c r="F410">
-        <v>35000</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>31/07/2026</v>
+        <v>23/07/2026</v>
       </c>
       <c r="B411" t="str">
         <v>Jul26</v>
       </c>
       <c r="C411" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D411" t="str">
-        <v>Salary</v>
+        <v>Guava</v>
       </c>
       <c r="E411" t="str">
-        <v>Salary B1</v>
+        <v>ฝรั่ง 2 ลัง ลังละ 20 กิโล กิโลละ 50 บาท รวม 2000 บาท (LINE_ALBUM_Cost July_260802_82.jpg)</v>
       </c>
       <c r="F411">
-        <v>35000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>23/05/2026</v>
+        <v>23/07/2026</v>
       </c>
       <c r="B412" t="str">
-        <v>May26</v>
+        <v>Jul26</v>
       </c>
       <c r="C412" t="str">
-        <v>EXCLUDED</v>
+        <v>COGS</v>
       </c>
       <c r="D412" t="str">
-        <v>Pass-Through</v>
+        <v>Pineapple</v>
       </c>
       <c r="E412" t="str">
-        <v>มังคุด (รับเงินสด 28,000 แล้วโอนต่อ ฐนกร 23/05 17:23) - ไม่ใช่ต้นทุน SSJ [bank]</v>
+        <v>สับปะรด 41 กิโล *27 บาท รวม 1107 บาท (LINE_ALBUM_Cost July_260802_83.jpg)</v>
       </c>
       <c r="F412">
-        <v>0</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>01/05/2026</v>
+        <v>31/07/2026</v>
       </c>
       <c r="B413" t="str">
-        <v>May26</v>
+        <v>Jul26</v>
       </c>
       <c r="C413" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D413" t="str">
-        <v>Transportation</v>
+        <v>Rental</v>
       </c>
       <c r="E413" t="str">
-        <v>ลาลามูฟ Lalamove [bank]</v>
+        <v>ค่าเช่าร้าน B1 ก.ค. (จ่ายเงินสดจากหน้าร้านก่อนนำเข้าบัญชี - ไม่มีสลิป ยืนยันโดยเจ้าของ 28/08)</v>
       </c>
       <c r="F413">
-        <v>2000</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>07/05/2026</v>
+        <v>31/07/2026</v>
       </c>
       <c r="B414" t="str">
-        <v>May26</v>
+        <v>Jul26</v>
       </c>
       <c r="C414" t="str">
         <v>OPEX</v>
       </c>
       <c r="D414" t="str">
-        <v>Other</v>
+        <v>Salary</v>
       </c>
       <c r="E414" t="str">
-        <v>บจก. อาร์.เอ็น.คลีน ทำความสะอาด [bank]</v>
+        <v>Salary B1</v>
       </c>
       <c r="F414">
-        <v>1000</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>01/05/2026</v>
+        <v>23/05/2026</v>
       </c>
       <c r="B415" t="str">
         <v>May26</v>
       </c>
       <c r="C415" t="str">
-        <v>COGS</v>
+        <v>EXCLUDED</v>
       </c>
       <c r="D415" t="str">
-        <v>Mango</v>
+        <v>Pass-Through</v>
       </c>
       <c r="E415" t="str">
-        <v>LINE Pay Merchant [bank]</v>
+        <v>มังคุด (รับเงินสด 28,000 แล้วโอนต่อ ฐนกร 23/05 17:23) - ไม่ใช่ต้นทุน SSJ [bank]</v>
       </c>
       <c r="F415">
-        <v>780</v>
+        <v>0</v>
       </c>
     </row>
     <row r="416">
@@ -9446,138 +9446,138 @@
         <v>COGS</v>
       </c>
       <c r="D416" t="str">
-        <v>Pineapple</v>
+        <v>Transportation</v>
       </c>
       <c r="E416" t="str">
-        <v>น.ส. สุพิชญา [bank]</v>
+        <v>ลาลามูฟ Lalamove [bank]</v>
       </c>
       <c r="F416">
-        <v>684</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>09/05/2026</v>
+        <v>07/05/2026</v>
       </c>
       <c r="B417" t="str">
         <v>May26</v>
       </c>
       <c r="C417" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D417" t="str">
-        <v>Guava</v>
+        <v>Other</v>
       </c>
       <c r="E417" t="str">
-        <v>ฝรั่ง 1 ตะกร้า (นาง ประนอม) [bank]</v>
+        <v>บจก. อาร์.เอ็น.คลีน ทำความสะอาด [bank]</v>
       </c>
       <c r="F417">
-        <v>600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>30/04/2026</v>
+        <v>01/05/2026</v>
       </c>
       <c r="B418" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C418" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D418" t="str">
-        <v>Marketing</v>
+        <v>Mango</v>
       </c>
       <c r="E418" t="str">
-        <v>ปืนฉีดน้ำ สงกรานต์ (จ่าย 06/05) [bank]</v>
+        <v>LINE Pay Merchant [bank]</v>
       </c>
       <c r="F418">
-        <v>24016</v>
+        <v>780</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>30/04/2026</v>
+        <v>01/05/2026</v>
       </c>
       <c r="B419" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C419" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D419" t="str">
-        <v>Salary</v>
+        <v>Pineapple</v>
       </c>
       <c r="E419" t="str">
-        <v>เงินเดือน เม.ย. (จ่าย 01/05) [bank]</v>
+        <v>น.ส. สุพิชญา [bank]</v>
       </c>
       <c r="F419">
-        <v>31000</v>
+        <v>684</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>04/04/2026</v>
+        <v>09/05/2026</v>
       </c>
       <c r="B420" t="str">
-        <v>Apr26</v>
+        <v>May26</v>
       </c>
       <c r="C420" t="str">
         <v>COGS</v>
       </c>
       <c r="D420" t="str">
-        <v>Packaging</v>
+        <v>Guava</v>
       </c>
       <c r="E420" t="str">
-        <v>Shopee (ทีมจัดซื้อ) [bank SA8285]</v>
+        <v>ฝรั่ง 1 ตะกร้า (นาง ประนอม) [bank]</v>
       </c>
       <c r="F420">
-        <v>11732</v>
+        <v>600</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>05/04/2026</v>
+        <v>30/04/2026</v>
       </c>
       <c r="B421" t="str">
         <v>Apr26</v>
       </c>
       <c r="C421" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D421" t="str">
-        <v>Packaging</v>
+        <v>Marketing</v>
       </c>
       <c r="E421" t="str">
-        <v>Shopee (ทีมจัดซื้อ) [bank SA8285]</v>
+        <v>ปืนฉีดน้ำ สงกรานต์ (จ่าย 06/05) [bank]</v>
       </c>
       <c r="F421">
-        <v>672</v>
+        <v>24016</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>16/04/2026</v>
+        <v>30/04/2026</v>
       </c>
       <c r="B422" t="str">
         <v>Apr26</v>
       </c>
       <c r="C422" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D422" t="str">
-        <v>Packaging</v>
+        <v>Salary</v>
       </c>
       <c r="E422" t="str">
-        <v>Shopee (ทีมจัดซื้อ) [bank SA8285]</v>
+        <v>เงินเดือน เม.ย. (จ่าย 01/05) [bank]</v>
       </c>
       <c r="F422">
-        <v>11560</v>
+        <v>31000</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>20/04/2026</v>
+        <v>04/04/2026</v>
       </c>
       <c r="B423" t="str">
         <v>Apr26</v>
@@ -9592,12 +9592,12 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA8285]</v>
       </c>
       <c r="F423">
-        <v>692</v>
+        <v>11732</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>25/04/2026</v>
+        <v>05/04/2026</v>
       </c>
       <c r="B424" t="str">
         <v>Apr26</v>
@@ -9612,15 +9612,15 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA8285]</v>
       </c>
       <c r="F424">
-        <v>1838</v>
+        <v>672</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>21/06/2026</v>
+        <v>16/04/2026</v>
       </c>
       <c r="B425" t="str">
-        <v>Jun26</v>
+        <v>Apr26</v>
       </c>
       <c r="C425" t="str">
         <v>COGS</v>
@@ -9629,18 +9629,18 @@
         <v>Packaging</v>
       </c>
       <c r="E425" t="str">
-        <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
+        <v>Shopee (ทีมจัดซื้อ) [bank SA8285]</v>
       </c>
       <c r="F425">
-        <v>1377</v>
+        <v>11560</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>21/06/2026</v>
+        <v>20/04/2026</v>
       </c>
       <c r="B426" t="str">
-        <v>Jun26</v>
+        <v>Apr26</v>
       </c>
       <c r="C426" t="str">
         <v>COGS</v>
@@ -9649,18 +9649,18 @@
         <v>Packaging</v>
       </c>
       <c r="E426" t="str">
-        <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
+        <v>Shopee (ทีมจัดซื้อ) [bank SA8285]</v>
       </c>
       <c r="F426">
-        <v>1210</v>
+        <v>692</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>21/06/2026</v>
+        <v>25/04/2026</v>
       </c>
       <c r="B427" t="str">
-        <v>Jun26</v>
+        <v>Apr26</v>
       </c>
       <c r="C427" t="str">
         <v>COGS</v>
@@ -9669,10 +9669,10 @@
         <v>Packaging</v>
       </c>
       <c r="E427" t="str">
-        <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
+        <v>Shopee (ทีมจัดซื้อ) [bank SA8285]</v>
       </c>
       <c r="F427">
-        <v>1210</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="428">
@@ -9692,7 +9692,7 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F428">
-        <v>1242</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="429">
@@ -9712,7 +9712,7 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F429">
-        <v>1232</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="430">
@@ -9732,7 +9732,7 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F430">
-        <v>1286</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="431">
@@ -9752,7 +9752,7 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F431">
-        <v>1295</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="432">
@@ -9772,7 +9772,7 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F432">
-        <v>1445</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="433">
@@ -9792,7 +9792,7 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F433">
-        <v>3051</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="434">
@@ -9812,12 +9812,12 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F434">
-        <v>755</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>29/06/2026</v>
+        <v>21/06/2026</v>
       </c>
       <c r="B435" t="str">
         <v>Jun26</v>
@@ -9832,12 +9832,12 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F435">
-        <v>7766</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>29/06/2026</v>
+        <v>21/06/2026</v>
       </c>
       <c r="B436" t="str">
         <v>Jun26</v>
@@ -9852,12 +9852,12 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F436">
-        <v>539</v>
+        <v>3051</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>29/06/2026</v>
+        <v>21/06/2026</v>
       </c>
       <c r="B437" t="str">
         <v>Jun26</v>
@@ -9872,15 +9872,15 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F437">
-        <v>596</v>
+        <v>755</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>07/07/2026</v>
+        <v>29/06/2026</v>
       </c>
       <c r="B438" t="str">
-        <v>Jul26</v>
+        <v>Jun26</v>
       </c>
       <c r="C438" t="str">
         <v>COGS</v>
@@ -9892,15 +9892,15 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F438">
-        <v>141</v>
+        <v>7766</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>07/07/2026</v>
+        <v>29/06/2026</v>
       </c>
       <c r="B439" t="str">
-        <v>Jul26</v>
+        <v>Jun26</v>
       </c>
       <c r="C439" t="str">
         <v>COGS</v>
@@ -9912,15 +9912,15 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F439">
-        <v>7999</v>
+        <v>539</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>07/07/2026</v>
+        <v>29/06/2026</v>
       </c>
       <c r="B440" t="str">
-        <v>Jul26</v>
+        <v>Jun26</v>
       </c>
       <c r="C440" t="str">
         <v>COGS</v>
@@ -9932,12 +9932,12 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F440">
-        <v>1399</v>
+        <v>596</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>08/07/2026</v>
+        <v>07/07/2026</v>
       </c>
       <c r="B441" t="str">
         <v>Jul26</v>
@@ -9952,12 +9952,12 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F441">
-        <v>9870</v>
+        <v>141</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>24/07/2026</v>
+        <v>07/07/2026</v>
       </c>
       <c r="B442" t="str">
         <v>Jul26</v>
@@ -9972,52 +9972,52 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F442">
-        <v>7410</v>
+        <v>7999</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>26/07/2026</v>
+        <v>07/07/2026</v>
       </c>
       <c r="B443" t="str">
         <v>Jul26</v>
       </c>
       <c r="C443" t="str">
-        <v>CAPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D443" t="str">
-        <v>Investment</v>
+        <v>Packaging</v>
       </c>
       <c r="E443" t="str">
-        <v>เครื่องสกัดเย็น 1 เครื่อง (Shopee, audit fix - was COGS/Packaging)</v>
+        <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F443">
-        <v>1015</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>26/07/2026</v>
+        <v>08/07/2026</v>
       </c>
       <c r="B444" t="str">
         <v>Jul26</v>
       </c>
       <c r="C444" t="str">
-        <v>CAPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D444" t="str">
-        <v>Investment</v>
+        <v>Packaging</v>
       </c>
       <c r="E444" t="str">
-        <v>เครื่องสกัดเย็น 1 เครื่อง (Shopee, audit fix - was COGS/Packaging)</v>
+        <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F444">
-        <v>1087</v>
+        <v>9870</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>27/07/2026</v>
+        <v>24/07/2026</v>
       </c>
       <c r="B445" t="str">
         <v>Jul26</v>
@@ -10032,95 +10032,95 @@
         <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F445">
-        <v>4309</v>
+        <v>7410</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>27/07/2026</v>
+        <v>26/07/2026</v>
       </c>
       <c r="B446" t="str">
         <v>Jul26</v>
       </c>
       <c r="C446" t="str">
-        <v>COGS</v>
+        <v>CAPEX</v>
       </c>
       <c r="D446" t="str">
-        <v>Packaging</v>
+        <v>Investment</v>
       </c>
       <c r="E446" t="str">
-        <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
+        <v>เครื่องสกัดเย็น 1 เครื่อง (Shopee, audit fix - was COGS/Packaging)</v>
       </c>
       <c r="F446">
-        <v>2589</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>31/01/2026</v>
+        <v>26/07/2026</v>
       </c>
       <c r="B447" t="str">
-        <v>Jan26</v>
+        <v>Jul26</v>
       </c>
       <c r="C447" t="str">
-        <v>OPEX</v>
+        <v>CAPEX</v>
       </c>
       <c r="D447" t="str">
-        <v>Rental</v>
+        <v>Investment</v>
       </c>
       <c r="E447" t="str">
-        <v>ค่าเช่าร้าน Jan26 (ปรับตามงบการเงินเจ้าของ)</v>
+        <v>เครื่องสกัดเย็น 1 เครื่อง (Shopee, audit fix - was COGS/Packaging)</v>
       </c>
       <c r="F447">
-        <v>30000</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>28/02/2026</v>
+        <v>27/07/2026</v>
       </c>
       <c r="B448" t="str">
-        <v>Feb26</v>
+        <v>Jul26</v>
       </c>
       <c r="C448" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D448" t="str">
-        <v>Rental</v>
+        <v>Packaging</v>
       </c>
       <c r="E448" t="str">
-        <v>ค่าเช่าร้าน Feb26 (ปรับตามงบการเงินเจ้าของ)</v>
+        <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F448">
-        <v>35000</v>
+        <v>4309</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>28/02/2026</v>
+        <v>27/07/2026</v>
       </c>
       <c r="B449" t="str">
-        <v>Feb26</v>
+        <v>Jul26</v>
       </c>
       <c r="C449" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D449" t="str">
-        <v>Salary</v>
+        <v>Packaging</v>
       </c>
       <c r="E449" t="str">
-        <v>ค่าแรงคนงาน Feb26 (ปรับตามงบการเงินเจ้าของ)</v>
+        <v>Shopee (ทีมจัดซื้อ) [bank SA5601]</v>
       </c>
       <c r="F449">
-        <v>19000</v>
+        <v>2589</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>31/03/2026</v>
+        <v>31/01/2026</v>
       </c>
       <c r="B450" t="str">
-        <v>Mar26</v>
+        <v>Jan26</v>
       </c>
       <c r="C450" t="str">
         <v>OPEX</v>
@@ -10129,18 +10129,18 @@
         <v>Rental</v>
       </c>
       <c r="E450" t="str">
-        <v>ค่าเช่าร้าน Mar26 (ปรับตามงบการเงินเจ้าของ)</v>
+        <v>ค่าเช่าร้าน Jan26 (ปรับตามงบการเงินเจ้าของ)</v>
       </c>
       <c r="F450">
-        <v>35000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>31/03/2026</v>
+        <v>28/02/2026</v>
       </c>
       <c r="B451" t="str">
-        <v>Mar26</v>
+        <v>Feb26</v>
       </c>
       <c r="C451" t="str">
         <v>OPEX</v>
@@ -10149,115 +10149,115 @@
         <v>Rental</v>
       </c>
       <c r="E451" t="str">
-        <v>ค่าเช่าคลัง Mar26 (ปรับตามงบการเงินเจ้าของ)</v>
+        <v>ค่าเช่าร้าน Feb26 (ปรับตามงบการเงินเจ้าของ)</v>
       </c>
       <c r="F451">
-        <v>12000</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>31/03/2026</v>
+        <v>28/02/2026</v>
       </c>
       <c r="B452" t="str">
-        <v>Mar26</v>
+        <v>Feb26</v>
       </c>
       <c r="C452" t="str">
         <v>OPEX</v>
       </c>
       <c r="D452" t="str">
-        <v>Other</v>
+        <v>Salary</v>
       </c>
       <c r="E452" t="str">
-        <v>ค่าน้ำ + ค่าไฟ Mar26 (ปรับตามงบการเงินเจ้าของ)</v>
+        <v>ค่าแรงคนงาน Feb26 (ปรับตามงบการเงินเจ้าของ)</v>
       </c>
       <c r="F452">
-        <v>3229</v>
+        <v>19000</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>22/06/2026</v>
+        <v>31/03/2026</v>
       </c>
       <c r="B453" t="str">
-        <v>Jun26</v>
+        <v>Mar26</v>
       </c>
       <c r="C453" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D453" t="str">
-        <v>Guava</v>
+        <v>Rental</v>
       </c>
       <c r="E453" t="str">
-        <v>ฝรั่ง (นาง ประนอม) [bank]</v>
+        <v>ค่าเช่าร้าน Mar26 (ปรับตามงบการเงินเจ้าของ)</v>
       </c>
       <c r="F453">
-        <v>100</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>25/06/2026</v>
+        <v>31/03/2026</v>
       </c>
       <c r="B454" t="str">
-        <v>Jun26</v>
+        <v>Mar26</v>
       </c>
       <c r="C454" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D454" t="str">
-        <v>Guava</v>
+        <v>Rental</v>
       </c>
       <c r="E454" t="str">
-        <v>ฝรั่ง 1 ตะกร้า (นาง ประนอม) [bank]</v>
+        <v>ค่าเช่าคลัง Mar26 (ปรับตามงบการเงินเจ้าของ)</v>
       </c>
       <c r="F454">
-        <v>800</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>28/07/2026</v>
+        <v>31/03/2026</v>
       </c>
       <c r="B455" t="str">
-        <v>Jul26</v>
+        <v>Mar26</v>
       </c>
       <c r="C455" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D455" t="str">
-        <v>Guava</v>
+        <v>Other</v>
       </c>
       <c r="E455" t="str">
-        <v>ฝรั่ง (นาง ประนอม) [bank]</v>
+        <v>ค่าน้ำ + ค่าไฟ Mar26 (ปรับตามงบการเงินเจ้าของ)</v>
       </c>
       <c r="F455">
-        <v>3000</v>
+        <v>3229</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>20/02/2026</v>
+        <v>22/06/2026</v>
       </c>
       <c r="B456" t="str">
-        <v>Feb26</v>
+        <v>Jun26</v>
       </c>
       <c r="C456" t="str">
         <v>COGS</v>
       </c>
       <c r="D456" t="str">
-        <v>Transportation</v>
+        <v>Guava</v>
       </c>
       <c r="E456" t="str">
-        <v>ค่ารถ (แยกจากใบเสร็จผ้าปิดร้าน 416)</v>
+        <v>ฝรั่ง (นาง ประนอม) [bank]</v>
       </c>
       <c r="F456">
-        <v>198</v>
+        <v>100</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>04/06/2026</v>
+        <v>25/06/2026</v>
       </c>
       <c r="B457" t="str">
         <v>Jun26</v>
@@ -10266,218 +10266,218 @@
         <v>COGS</v>
       </c>
       <c r="D457" t="str">
-        <v>Pineapple</v>
+        <v>Guava</v>
       </c>
       <c r="E457" t="str">
-        <v>สลิปรวม: สับปะรด 750 (audit fix, was bundled)</v>
+        <v>ฝรั่ง 1 ตะกร้า (นาง ประนอม) [bank]</v>
       </c>
       <c r="F457">
-        <v>750</v>
+        <v>800</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>04/06/2026</v>
+        <v>28/07/2026</v>
       </c>
       <c r="B458" t="str">
-        <v>Jun26</v>
+        <v>Jul26</v>
       </c>
       <c r="C458" t="str">
         <v>COGS</v>
       </c>
       <c r="D458" t="str">
-        <v>Orange</v>
+        <v>Guava</v>
       </c>
       <c r="E458" t="str">
-        <v>สลิปรวม: ส้ม 2250 (audit fix, was bundled into Pineapple line)</v>
+        <v>ฝรั่ง (นาง ประนอม) [bank]</v>
       </c>
       <c r="F458">
-        <v>2250</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>04/06/2026</v>
+        <v>20/02/2026</v>
       </c>
       <c r="B459" t="str">
-        <v>Jun26</v>
+        <v>Feb26</v>
       </c>
       <c r="C459" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D459" t="str">
-        <v>Other</v>
+        <v>Transportation</v>
       </c>
       <c r="E459" t="str">
-        <v>ค่าปรับตำรวจ 2 คน (police fee, audit fix - was miscategorized as COGS/Pineapple)</v>
+        <v>ค่ารถ (แยกจากใบเสร็จผ้าปิดร้าน 416)</v>
       </c>
       <c r="F459">
-        <v>2000</v>
+        <v>198</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>26/07/2026</v>
+        <v>04/06/2026</v>
       </c>
       <c r="B460" t="str">
-        <v>Jul26</v>
+        <v>Jun26</v>
       </c>
       <c r="C460" t="str">
-        <v>CAPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D460" t="str">
-        <v>Investment</v>
+        <v>Pineapple</v>
       </c>
       <c r="E460" t="str">
-        <v>งบลงทุน - ทดลองอื่นๆ (LINE_ALBUM_Cost July_260802_8.jpg, audit fix - was bundled into COGS/Mango)</v>
+        <v>สลิปรวม: สับปะรด 750 (audit fix, was bundled)</v>
       </c>
       <c r="F460">
-        <v>810</v>
+        <v>750</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>26/07/2026</v>
+        <v>04/06/2026</v>
       </c>
       <c r="B461" t="str">
-        <v>Jul26</v>
+        <v>Jun26</v>
       </c>
       <c r="C461" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D461" t="str">
-        <v>Other</v>
+        <v>Orange</v>
       </c>
       <c r="E461" t="str">
-        <v>ค่าส่งของ (LINE_ALBUM_Cost July_260802_11.jpg, audit fix - missing entry)</v>
+        <v>สลิปรวม: ส้ม 2250 (audit fix, was bundled into Pineapple line)</v>
       </c>
       <c r="F461">
-        <v>212</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>28/07/2026</v>
+        <v>04/06/2026</v>
       </c>
       <c r="B462" t="str">
-        <v>Jul26</v>
+        <v>Jun26</v>
       </c>
       <c r="C462" t="str">
-        <v>COGS</v>
+        <v>OPEX</v>
       </c>
       <c r="D462" t="str">
-        <v>Pineapple</v>
+        <v>Other</v>
       </c>
       <c r="E462" t="str">
-        <v>สับปะรด 30 ลูก (LINE_ALBUM_Cost July_260802_17.jpg, audit fix - missing entry)</v>
+        <v>ค่าปรับตำรวจ 2 คน (police fee, audit fix - was miscategorized as COGS/Pineapple)</v>
       </c>
       <c r="F462">
-        <v>1188</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>28/07/2026</v>
+        <v>26/07/2026</v>
       </c>
       <c r="B463" t="str">
         <v>Jul26</v>
       </c>
       <c r="C463" t="str">
-        <v>OPEX</v>
+        <v>CAPEX</v>
       </c>
       <c r="D463" t="str">
-        <v>Other</v>
+        <v>Investment</v>
       </c>
       <c r="E463" t="str">
-        <v>ค่าขนส่ง (LINE_ALBUM_Cost July_260802_19.jpg, audit fix - missing entry)</v>
+        <v>งบลงทุน - ทดลองอื่นๆ (LINE_ALBUM_Cost July_260802_8.jpg, audit fix - was bundled into COGS/Mango)</v>
       </c>
       <c r="F463">
-        <v>100</v>
+        <v>810</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>30/04/2026</v>
+        <v>26/07/2026</v>
       </c>
       <c r="B464" t="str">
-        <v>Apr26</v>
+        <v>Jul26</v>
       </c>
       <c r="C464" t="str">
         <v>OPEX</v>
       </c>
       <c r="D464" t="str">
-        <v>Rental</v>
+        <v>Other</v>
       </c>
       <c r="E464" t="str">
-        <v>ค่าเช่า stock เม.ย. (B1 ครึ่งหนึ่ง)</v>
+        <v>ค่าส่งของ (LINE_ALBUM_Cost July_260802_11.jpg, audit fix - missing entry)</v>
       </c>
       <c r="F464">
-        <v>6000</v>
+        <v>212</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>05/03/2026</v>
+        <v>28/07/2026</v>
       </c>
       <c r="B465" t="str">
-        <v>Mar26</v>
+        <v>Jul26</v>
       </c>
       <c r="C465" t="str">
-        <v>OPEX</v>
+        <v>COGS</v>
       </c>
       <c r="D465" t="str">
-        <v>Salary</v>
+        <v>Pineapple</v>
       </c>
       <c r="E465" t="str">
-        <v>เงินเดือนเมน 3/26</v>
+        <v>สับปะรด 30 ลูก (LINE_ALBUM_Cost July_260802_17.jpg, audit fix - missing entry)</v>
       </c>
       <c r="F465">
-        <v>19000</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>27/02/2026</v>
+        <v>28/07/2026</v>
       </c>
       <c r="B466" t="str">
-        <v>Feb26</v>
+        <v>Jul26</v>
       </c>
       <c r="C466" t="str">
         <v>OPEX</v>
       </c>
       <c r="D466" t="str">
-        <v>Investment</v>
+        <v>Other</v>
       </c>
       <c r="E466" t="str">
-        <v>อุปกรณ์ (จากสลิปโอนผู้จัดการ)</v>
+        <v>ค่าขนส่ง (LINE_ALBUM_Cost July_260802_19.jpg, audit fix - missing entry)</v>
       </c>
       <c r="F466">
-        <v>5000</v>
+        <v>100</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>18/03/2026</v>
+        <v>30/04/2026</v>
       </c>
       <c r="B467" t="str">
-        <v>Mar26</v>
+        <v>Apr26</v>
       </c>
       <c r="C467" t="str">
         <v>OPEX</v>
       </c>
       <c r="D467" t="str">
-        <v>Milk/Conden</v>
+        <v>Rental</v>
       </c>
       <c r="E467" t="str">
-        <v>นม + นมข้นหวาน (จากสลิปโอนผู้จัดการ)</v>
+        <v>ค่าเช่า stock เม.ย. (B1 ครึ่งหนึ่ง)</v>
       </c>
       <c r="F467">
-        <v>230</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>01/04/2026</v>
+        <v>05/03/2026</v>
       </c>
       <c r="B468" t="str">
         <v>Mar26</v>
@@ -10489,35 +10489,95 @@
         <v>Salary</v>
       </c>
       <c r="E468" t="str">
-        <v>เงินเดือนพนักงาน 3 คน มี.ค. 26 (จ่าย 01/04) [bank]</v>
+        <v>เงินเดือนเมน 3/26</v>
       </c>
       <c r="F468">
-        <v>24600</v>
+        <v>19000</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>08/06/2026</v>
+        <v>27/02/2026</v>
       </c>
       <c r="B469" t="str">
-        <v>Jun26</v>
+        <v>Feb26</v>
       </c>
       <c r="C469" t="str">
         <v>OPEX</v>
       </c>
       <c r="D469" t="str">
+        <v>Investment</v>
+      </c>
+      <c r="E469" t="str">
+        <v>อุปกรณ์ (จากสลิปโอนผู้จัดการ)</v>
+      </c>
+      <c r="F469">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="str">
+        <v>18/03/2026</v>
+      </c>
+      <c r="B470" t="str">
+        <v>Mar26</v>
+      </c>
+      <c r="C470" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D470" t="str">
+        <v>Milk/Conden</v>
+      </c>
+      <c r="E470" t="str">
+        <v>นม + นมข้นหวาน (จากสลิปโอนผู้จัดการ)</v>
+      </c>
+      <c r="F470">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="str">
+        <v>01/04/2026</v>
+      </c>
+      <c r="B471" t="str">
+        <v>Mar26</v>
+      </c>
+      <c r="C471" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D471" t="str">
+        <v>Salary</v>
+      </c>
+      <c r="E471" t="str">
+        <v>เงินเดือนพนักงาน 3 คน มี.ค. 26 (จ่าย 01/04) [bank]</v>
+      </c>
+      <c r="F471">
+        <v>24600</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="str">
+        <v>08/06/2026</v>
+      </c>
+      <c r="B472" t="str">
+        <v>Jun26</v>
+      </c>
+      <c r="C472" t="str">
+        <v>OPEX</v>
+      </c>
+      <c r="D472" t="str">
         <v>Rental</v>
       </c>
-      <c r="E469" t="str">
+      <c r="E472" t="str">
         <v>ค่าเช่าคลัง มิ.ย. (B1 ครึ่งหนึ่ง ของ 12,000 จากสลิป 47,000 วันที่ 08/06)</v>
       </c>
-      <c r="F469">
+      <c r="F472">
         <v>6000</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F469"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F472"/>
   </ignoredErrors>
 </worksheet>
 </file>
